--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182405322790146</t>
+    <t xml:space="preserve">0.182405292987823</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183056741952896</t>
+    <t xml:space="preserve">0.183056727051735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179148077964783</t>
+    <t xml:space="preserve">0.179148063063622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177845165133476</t>
+    <t xml:space="preserve">0.177845150232315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170027792453766</t>
+    <t xml:space="preserve">0.170027807354927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17589083313942</t>
+    <t xml:space="preserve">0.175890862941742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154393061995506</t>
+    <t xml:space="preserve">0.154393076896667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148530036211014</t>
+    <t xml:space="preserve">0.148530021309853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155239954590797</t>
+    <t xml:space="preserve">0.155239939689636</t>
   </si>
   <si>
     <t xml:space="preserve">0.150484383106232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158301740884781</t>
+    <t xml:space="preserve">0.15830172598362</t>
   </si>
   <si>
     <t xml:space="preserve">0.158953189849854</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.151787266135216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144947052001953</t>
+    <t xml:space="preserve">0.144947066903114</t>
   </si>
   <si>
     <t xml:space="preserve">0.144621342420578</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">0.145012199878693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14722715318203</t>
+    <t xml:space="preserve">0.147227138280869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143969878554344</t>
+    <t xml:space="preserve">0.143969863653183</t>
   </si>
   <si>
     <t xml:space="preserve">0.156607955694199</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">0.176542267203331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172894164919853</t>
+    <t xml:space="preserve">0.172894179821014</t>
   </si>
   <si>
     <t xml:space="preserve">0.169376328587532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162861853837967</t>
+    <t xml:space="preserve">0.162861883640289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160256072878838</t>
+    <t xml:space="preserve">0.160256087779999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155044496059418</t>
+    <t xml:space="preserve">0.155044481158257</t>
   </si>
   <si>
     <t xml:space="preserve">0.161363556981087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166770547628403</t>
+    <t xml:space="preserve">0.166770562529564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164751067757607</t>
+    <t xml:space="preserve">0.164751052856445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183773323893547</t>
+    <t xml:space="preserve">0.183773338794708</t>
   </si>
   <si>
     <t xml:space="preserve">0.183708190917969</t>
@@ -137,64 +137,64 @@
     <t xml:space="preserve">0.177193716168404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171982139348984</t>
+    <t xml:space="preserve">0.171982124447823</t>
   </si>
   <si>
     <t xml:space="preserve">0.195434257388115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199668660759926</t>
+    <t xml:space="preserve">0.199668645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198691487312317</t>
+    <t xml:space="preserve">0.198691472411156</t>
   </si>
   <si>
     <t xml:space="preserve">0.190874129533768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188268318772316</t>
+    <t xml:space="preserve">0.188268303871155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208463221788406</t>
+    <t xml:space="preserve">0.208463191986084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216280549764633</t>
+    <t xml:space="preserve">0.216280609369278</t>
   </si>
   <si>
     <t xml:space="preserve">0.208398029208183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203903093934059</t>
+    <t xml:space="preserve">0.203903049230576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201297238469124</t>
+    <t xml:space="preserve">0.201297268271446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185662537813187</t>
+    <t xml:space="preserve">0.185662522912025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188919767737389</t>
+    <t xml:space="preserve">0.188919752836227</t>
   </si>
   <si>
     <t xml:space="preserve">0.176021113991737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174587950110435</t>
+    <t xml:space="preserve">0.174587920308113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168724909424782</t>
+    <t xml:space="preserve">0.168724879622459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157129108905792</t>
+    <t xml:space="preserve">0.157129138708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172633588314056</t>
+    <t xml:space="preserve">0.172633558511734</t>
   </si>
   <si>
     <t xml:space="preserve">0.16279673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157650291919708</t>
+    <t xml:space="preserve">0.157650277018547</t>
   </si>
   <si>
     <t xml:space="preserve">0.159604638814926</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.163383036851883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192828461527824</t>
+    <t xml:space="preserve">0.192828476428986</t>
   </si>
   <si>
     <t xml:space="preserve">0.194782793521881</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">0.190222665667534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188333451747894</t>
+    <t xml:space="preserve">0.188333436846733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173285037279129</t>
+    <t xml:space="preserve">0.17328505218029</t>
   </si>
   <si>
     <t xml:space="preserve">0.166119083762169</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">0.152438700199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156998842954636</t>
+    <t xml:space="preserve">0.156998857855797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153741627931595</t>
+    <t xml:space="preserve">0.153741598129272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149832934141159</t>
+    <t xml:space="preserve">0.149832904338837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164164766669273</t>
+    <t xml:space="preserve">0.164164781570435</t>
   </si>
   <si>
     <t xml:space="preserve">0.171200409531593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176867976784706</t>
+    <t xml:space="preserve">0.176868006587029</t>
   </si>
   <si>
     <t xml:space="preserve">0.178496614098549</t>
@@ -248,46 +248,46 @@
     <t xml:space="preserve">0.189245492219925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207811757922173</t>
+    <t xml:space="preserve">0.20781172811985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200645864009857</t>
+    <t xml:space="preserve">0.200645819306374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184620216488838</t>
+    <t xml:space="preserve">0.184620201587677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197714328765869</t>
+    <t xml:space="preserve">0.197714313864708</t>
   </si>
   <si>
     <t xml:space="preserve">0.208332911133766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201948717236519</t>
+    <t xml:space="preserve">0.20194873213768</t>
   </si>
   <si>
     <t xml:space="preserve">0.198756620287895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207160264253616</t>
+    <t xml:space="preserve">0.2071603089571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220840722322464</t>
+    <t xml:space="preserve">0.220840692520142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224684238433838</t>
+    <t xml:space="preserve">0.224684223532677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241035595536232</t>
+    <t xml:space="preserve">0.241035535931587</t>
   </si>
   <si>
     <t xml:space="preserve">0.24689856171608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260578989982605</t>
+    <t xml:space="preserve">0.260578960180283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276865154504776</t>
+    <t xml:space="preserve">0.276865184307098</t>
   </si>
   <si>
     <t xml:space="preserve">0.28533399105072</t>
@@ -296,238 +296,238 @@
     <t xml:space="preserve">0.300968766212463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309437543153763</t>
+    <t xml:space="preserve">0.309437572956085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267093449831009</t>
+    <t xml:space="preserve">0.267093509435654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26963409781456</t>
+    <t xml:space="preserve">0.269634127616882</t>
   </si>
   <si>
     <t xml:space="preserve">0.259341269731522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25927609205246</t>
+    <t xml:space="preserve">0.259276121854782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251654148101807</t>
+    <t xml:space="preserve">0.251654177904129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252110213041306</t>
+    <t xml:space="preserve">0.252110183238983</t>
   </si>
   <si>
     <t xml:space="preserve">0.25224044919014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237778335809708</t>
+    <t xml:space="preserve">0.237778320908546</t>
   </si>
   <si>
     <t xml:space="preserve">0.242338463664055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218234896659851</t>
+    <t xml:space="preserve">0.218234941363335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214456513524055</t>
+    <t xml:space="preserve">0.214456528425217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219537824392319</t>
+    <t xml:space="preserve">0.21953783929348</t>
   </si>
   <si>
     <t xml:space="preserve">0.216345697641373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246247157454491</t>
+    <t xml:space="preserve">0.246247142553329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254064500331879</t>
+    <t xml:space="preserve">0.254064530134201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239211514592171</t>
+    <t xml:space="preserve">0.239211529493332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235823974013329</t>
+    <t xml:space="preserve">0.23582398891449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.244292795658112</t>
+    <t xml:space="preserve">0.244292855262756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234521105885506</t>
+    <t xml:space="preserve">0.234521090984344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231263846158981</t>
+    <t xml:space="preserve">0.231263861060143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224749356508255</t>
+    <t xml:space="preserve">0.224749371409416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230482131242752</t>
+    <t xml:space="preserve">0.230482116341591</t>
   </si>
   <si>
     <t xml:space="preserve">0.220905840396881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208528354763985</t>
+    <t xml:space="preserve">0.208528369665146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211720436811447</t>
+    <t xml:space="preserve">0.211720451712608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214326232671738</t>
+    <t xml:space="preserve">0.214326202869415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213674768805504</t>
+    <t xml:space="preserve">0.213674783706665</t>
   </si>
   <si>
     <t xml:space="preserve">0.214977666735649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216410875320435</t>
+    <t xml:space="preserve">0.216410890221596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219668075442314</t>
+    <t xml:space="preserve">0.219668120145798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233869627118111</t>
+    <t xml:space="preserve">0.233869671821594</t>
   </si>
   <si>
     <t xml:space="preserve">0.2278763204813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228853449225426</t>
+    <t xml:space="preserve">0.228853493928909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237843498587608</t>
+    <t xml:space="preserve">0.237843483686447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24292479455471</t>
+    <t xml:space="preserve">0.242924809455872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232697069644928</t>
+    <t xml:space="preserve">0.232697024941444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228006586432457</t>
+    <t xml:space="preserve">0.228006616234779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227746039628983</t>
+    <t xml:space="preserve">0.227746024727821</t>
   </si>
   <si>
     <t xml:space="preserve">0.224814549088478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239732712507248</t>
+    <t xml:space="preserve">0.239732697606087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224944829940796</t>
+    <t xml:space="preserve">0.224944815039635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231459304690361</t>
+    <t xml:space="preserve">0.2314592897892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308004379272461</t>
+    <t xml:space="preserve">0.308004349470139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364810645580292</t>
+    <t xml:space="preserve">0.364810585975647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482071191072464</t>
+    <t xml:space="preserve">0.482071071863174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565456449985504</t>
+    <t xml:space="preserve">0.565456330776215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494448572397232</t>
+    <t xml:space="preserve">0.494448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452756077051163</t>
+    <t xml:space="preserve">0.45275604724884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43744695186615</t>
+    <t xml:space="preserve">0.437446922063828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410411953926086</t>
+    <t xml:space="preserve">0.410411894321442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377839535474777</t>
+    <t xml:space="preserve">0.377839505672455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429303884506226</t>
+    <t xml:space="preserve">0.429303824901581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380771100521088</t>
+    <t xml:space="preserve">0.380771040916443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387611299753189</t>
+    <t xml:space="preserve">0.387611329555511</t>
   </si>
   <si>
     <t xml:space="preserve">0.358947575092316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337775498628616</t>
+    <t xml:space="preserve">0.337775528430939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326375216245651</t>
+    <t xml:space="preserve">0.326375186443329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338426977396011</t>
+    <t xml:space="preserve">0.338426947593689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346570074558258</t>
+    <t xml:space="preserve">0.34657010436058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333541095256805</t>
+    <t xml:space="preserve">0.333541125059128</t>
   </si>
   <si>
     <t xml:space="preserve">0.361553370952606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353735953569412</t>
+    <t xml:space="preserve">0.353736013174057</t>
   </si>
   <si>
     <t xml:space="preserve">0.338752657175064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329958140850067</t>
+    <t xml:space="preserve">0.329958200454712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332889676094055</t>
+    <t xml:space="preserve">0.332889646291733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345267176628113</t>
+    <t xml:space="preserve">0.345267117023468</t>
   </si>
   <si>
     <t xml:space="preserve">0.342009902000427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328980952501297</t>
+    <t xml:space="preserve">0.328980982303619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336146891117096</t>
+    <t xml:space="preserve">0.336146920919418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325723707675934</t>
+    <t xml:space="preserve">0.325723767280579</t>
   </si>
   <si>
     <t xml:space="preserve">0.323117941617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346895813941956</t>
+    <t xml:space="preserve">0.346895843744278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329632431268692</t>
+    <t xml:space="preserve">0.32963240146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328329533338547</t>
+    <t xml:space="preserve">0.328329563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340381324291229</t>
+    <t xml:space="preserve">0.340381354093552</t>
   </si>
   <si>
     <t xml:space="preserve">0.334843993186951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340055584907532</t>
+    <t xml:space="preserve">0.340055614709854</t>
   </si>
   <si>
     <t xml:space="preserve">0.312694787979126</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">0.332238167524338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337449818849564</t>
+    <t xml:space="preserve">0.337449759244919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371325075626373</t>
+    <t xml:space="preserve">0.371325045824051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351781666278839</t>
+    <t xml:space="preserve">0.351781725883484</t>
   </si>
   <si>
     <t xml:space="preserve">0.352433085441589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33093535900116</t>
+    <t xml:space="preserve">0.330935329198837</t>
   </si>
   <si>
     <t xml:space="preserve">0.350153058767319</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">0.339729845523834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403897434473038</t>
+    <t xml:space="preserve">0.40389746427536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383051097393036</t>
+    <t xml:space="preserve">0.383051127195358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38239973783493</t>
+    <t xml:space="preserve">0.382399678230286</t>
   </si>
   <si>
     <t xml:space="preserve">0.383702576160431</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">0.384353995323181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357644647359848</t>
+    <t xml:space="preserve">0.35764467716217</t>
   </si>
   <si>
     <t xml:space="preserve">0.362530499696732</t>
@@ -596,154 +596,154 @@
     <t xml:space="preserve">0.380445331335068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40292027592659</t>
+    <t xml:space="preserve">0.402920305728912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405851781368256</t>
+    <t xml:space="preserve">0.4058518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391519904136658</t>
+    <t xml:space="preserve">0.391519963741302</t>
   </si>
   <si>
     <t xml:space="preserve">0.39086851477623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401291728019714</t>
+    <t xml:space="preserve">0.401291638612747</t>
   </si>
   <si>
     <t xml:space="preserve">0.391194254159927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422789424657822</t>
+    <t xml:space="preserve">0.422789365053177</t>
   </si>
   <si>
     <t xml:space="preserve">0.429955333471298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406503260135651</t>
+    <t xml:space="preserve">0.406503230333328</t>
   </si>
   <si>
     <t xml:space="preserve">0.390542715787888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400640189647675</t>
+    <t xml:space="preserve">0.400640249252319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488585591316223</t>
+    <t xml:space="preserve">0.488585710525513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455361843109131</t>
+    <t xml:space="preserve">0.455361753702164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469042211771011</t>
+    <t xml:space="preserve">0.469042181968689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44949871301651</t>
+    <t xml:space="preserve">0.449498742818832</t>
   </si>
   <si>
     <t xml:space="preserve">0.454058945178986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462527692317963</t>
+    <t xml:space="preserve">0.462527722120285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456013172864914</t>
+    <t xml:space="preserve">0.456013232469559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437772691249847</t>
+    <t xml:space="preserve">0.437772661447525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440378397703171</t>
+    <t xml:space="preserve">0.44037851691246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436469793319702</t>
+    <t xml:space="preserve">0.436469882726669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424743741750717</t>
+    <t xml:space="preserve">0.42474377155304</t>
   </si>
   <si>
     <t xml:space="preserve">0.420835047960281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423440873622894</t>
+    <t xml:space="preserve">0.423440903425217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428652465343475</t>
+    <t xml:space="preserve">0.428652405738831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416926443576813</t>
+    <t xml:space="preserve">0.416926383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448195904493332</t>
+    <t xml:space="preserve">0.44819587469101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432561099529266</t>
+    <t xml:space="preserve">0.432561218738556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479465425014496</t>
+    <t xml:space="preserve">0.479465395212173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442984253168106</t>
+    <t xml:space="preserve">0.442984282970428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414320528507233</t>
+    <t xml:space="preserve">0.4143206179142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433863997459412</t>
+    <t xml:space="preserve">0.433864057064056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439075648784637</t>
+    <t xml:space="preserve">0.43907567858696</t>
   </si>
   <si>
     <t xml:space="preserve">0.42604660987854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413017719984055</t>
+    <t xml:space="preserve">0.413017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419532239437103</t>
+    <t xml:space="preserve">0.419532179832458</t>
   </si>
   <si>
     <t xml:space="preserve">0.396080046892166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397382974624634</t>
+    <t xml:space="preserve">0.397382944822311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402594476938248</t>
+    <t xml:space="preserve">0.402594536542892</t>
   </si>
   <si>
     <t xml:space="preserve">0.418229311704636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446892976760864</t>
+    <t xml:space="preserve">0.446892946958542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435166954994202</t>
+    <t xml:space="preserve">0.435166895389557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422137945890427</t>
+    <t xml:space="preserve">0.422137916088104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409109055995941</t>
+    <t xml:space="preserve">0.409109115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427349537611008</t>
+    <t xml:space="preserve">0.42734956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415623515844345</t>
+    <t xml:space="preserve">0.4156234562397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431258231401443</t>
+    <t xml:space="preserve">0.431258201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375233739614487</t>
+    <t xml:space="preserve">0.375233769416809</t>
   </si>
   <si>
     <t xml:space="preserve">0.379142463207245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376536637544632</t>
+    <t xml:space="preserve">0.37653660774231</t>
   </si>
   <si>
     <t xml:space="preserve">0.353084534406662</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">0.372627943754196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370022177696228</t>
+    <t xml:space="preserve">0.37002220749855</t>
   </si>
   <si>
     <t xml:space="preserve">0.356993228197098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349175900220871</t>
+    <t xml:space="preserve">0.349175840616226</t>
   </si>
   <si>
     <t xml:space="preserve">0.350478738546371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358296155929565</t>
+    <t xml:space="preserve">0.358296126127243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385656923055649</t>
+    <t xml:space="preserve">0.385656952857971</t>
   </si>
   <si>
     <t xml:space="preserve">0.399988740682602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366113483905792</t>
+    <t xml:space="preserve">0.36611345410347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373930841684341</t>
+    <t xml:space="preserve">0.373930871486664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39217135310173</t>
+    <t xml:space="preserve">0.392171442508698</t>
   </si>
   <si>
     <t xml:space="preserve">0.389565587043762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386959820985794</t>
+    <t xml:space="preserve">0.386959791183472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398685872554779</t>
+    <t xml:space="preserve">0.398685842752457</t>
   </si>
   <si>
     <t xml:space="preserve">0.405200302600861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407806187868118</t>
+    <t xml:space="preserve">0.407806098461151</t>
   </si>
   <si>
     <t xml:space="preserve">0.439727008342743</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">0.446241497993469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465784907341003</t>
+    <t xml:space="preserve">0.465784966945648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47229939699173</t>
+    <t xml:space="preserve">0.472299456596375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480856567621231</t>
+    <t xml:space="preserve">0.480856597423553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459325730800629</t>
+    <t xml:space="preserve">0.459325641393661</t>
   </si>
   <si>
     <t xml:space="preserve">0.444971740245819</t>
@@ -824,40 +824,43 @@
     <t xml:space="preserve">0.430617868900299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441383332014084</t>
+    <t xml:space="preserve">0.441383302211761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452148646116257</t>
+    <t xml:space="preserve">0.452148705720901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455737143754959</t>
+    <t xml:space="preserve">0.455737173557281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448560208082199</t>
+    <t xml:space="preserve">0.448560178279877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434206366539001</t>
+    <t xml:space="preserve">0.434206336736679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416263908147812</t>
+    <t xml:space="preserve">0.423440873622894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416263848543167</t>
   </si>
   <si>
     <t xml:space="preserve">0.427029371261597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401909977197647</t>
+    <t xml:space="preserve">0.401910036802292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405498445034027</t>
+    <t xml:space="preserve">0.405498415231705</t>
   </si>
   <si>
     <t xml:space="preserve">0.419852375984192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437794834375381</t>
+    <t xml:space="preserve">0.437794744968414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462914168834686</t>
+    <t xml:space="preserve">0.462914109230042</t>
   </si>
   <si>
     <t xml:space="preserve">0.545449256896973</t>
@@ -866,25 +869,25 @@
     <t xml:space="preserve">0.466502666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473679661750793</t>
+    <t xml:space="preserve">0.473679602146149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470091134309769</t>
+    <t xml:space="preserve">0.470091104507446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412675380706787</t>
+    <t xml:space="preserve">0.412675440311432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409086942672729</t>
+    <t xml:space="preserve">0.409086912870407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394733011722565</t>
+    <t xml:space="preserve">0.394732981920242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387556046247482</t>
+    <t xml:space="preserve">0.387556105852127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37320214509964</t>
+    <t xml:space="preserve">0.373202085494995</t>
   </si>
   <si>
     <t xml:space="preserve">0.383967608213425</t>
@@ -893,25 +896,25 @@
     <t xml:space="preserve">0.398321479558945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3803790807724</t>
+    <t xml:space="preserve">0.380379050970078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353106588125229</t>
+    <t xml:space="preserve">0.353106617927551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35167121887207</t>
+    <t xml:space="preserve">0.351671248674393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36602509021759</t>
+    <t xml:space="preserve">0.366025149822235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358848184347153</t>
+    <t xml:space="preserve">0.35884815454483</t>
   </si>
   <si>
     <t xml:space="preserve">0.344494253396988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322963416576385</t>
+    <t xml:space="preserve">0.322963327169418</t>
   </si>
   <si>
     <t xml:space="preserve">0.325834155082703</t>
@@ -920,34 +923,31 @@
     <t xml:space="preserve">0.301432460546494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268418461084366</t>
+    <t xml:space="preserve">0.268418431282043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288513958454132</t>
+    <t xml:space="preserve">0.288513988256454</t>
   </si>
   <si>
     <t xml:space="preserve">0.272724628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282772392034531</t>
+    <t xml:space="preserve">0.282772362232208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271289259195328</t>
+    <t xml:space="preserve">0.271289229393005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254064530134201</t>
+    <t xml:space="preserve">0.258370727300644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258370697498322</t>
+    <t xml:space="preserve">0.25262913107872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252629101276398</t>
+    <t xml:space="preserve">0.295690923929214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295690894126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297126322984695</t>
+    <t xml:space="preserve">0.297126293182373</t>
   </si>
   <si>
     <t xml:space="preserve">0.28133699297905</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">0.289949327707291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291384667158127</t>
+    <t xml:space="preserve">0.291384756565094</t>
   </si>
   <si>
     <t xml:space="preserve">0.305738687515259</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">0.314350992441177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320092558860779</t>
+    <t xml:space="preserve">0.320092588663101</t>
   </si>
   <si>
     <t xml:space="preserve">0.350235819816589</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">0.337317317724228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331575721502304</t>
+    <t xml:space="preserve">0.331575691699982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355977416038513</t>
+    <t xml:space="preserve">0.355977386236191</t>
   </si>
   <si>
     <t xml:space="preserve">0.376790553331375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391144573688507</t>
+    <t xml:space="preserve">0.391144543886185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340188086032867</t>
+    <t xml:space="preserve">0.34018811583519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343058854341507</t>
+    <t xml:space="preserve">0.343058884143829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348800420761108</t>
+    <t xml:space="preserve">0.348800450563431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36243662238121</t>
+    <t xml:space="preserve">0.362436681985855</t>
   </si>
   <si>
     <t xml:space="preserve">0.357412785291672</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">0.334446489810944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335881859064102</t>
+    <t xml:space="preserve">0.335881888866425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333011120557785</t>
+    <t xml:space="preserve">0.333011150360107</t>
   </si>
   <si>
     <t xml:space="preserve">0.330140382051468</t>
@@ -1019,37 +1019,37 @@
     <t xml:space="preserve">0.328704923391342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315786391496658</t>
+    <t xml:space="preserve">0.315786451101303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308609455823898</t>
+    <t xml:space="preserve">0.308609426021576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294255495071411</t>
+    <t xml:space="preserve">0.294255554676056</t>
   </si>
   <si>
     <t xml:space="preserve">0.298561662435532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274160027503967</t>
+    <t xml:space="preserve">0.274159997701645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277030766010284</t>
+    <t xml:space="preserve">0.277030825614929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269853830337524</t>
+    <t xml:space="preserve">0.269853889942169</t>
   </si>
   <si>
     <t xml:space="preserve">0.275595396757126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279901593923569</t>
+    <t xml:space="preserve">0.279901564121246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287078589200974</t>
+    <t xml:space="preserve">0.287078559398651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302867859601974</t>
+    <t xml:space="preserve">0.302867889404297</t>
   </si>
   <si>
     <t xml:space="preserve">0.307174056768417</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">0.299997091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445466727018356</t>
+    <t xml:space="preserve">0.445466667413712</t>
   </si>
   <si>
     <t xml:space="preserve">0.414205878973007</t>
@@ -1067,88 +1067,88 @@
     <t xml:space="preserve">0.402483075857162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390760242938995</t>
+    <t xml:space="preserve">0.390760272741318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375129818916321</t>
+    <t xml:space="preserve">0.375129848718643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38294506072998</t>
+    <t xml:space="preserve">0.382945090532303</t>
   </si>
   <si>
     <t xml:space="preserve">0.376692891120911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394667834043503</t>
+    <t xml:space="preserve">0.394667863845825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387634217739105</t>
+    <t xml:space="preserve">0.38763415813446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3782559633255</t>
+    <t xml:space="preserve">0.378255903720856</t>
   </si>
   <si>
     <t xml:space="preserve">0.362625539302826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356373369693756</t>
+    <t xml:space="preserve">0.356373339891434</t>
   </si>
   <si>
     <t xml:space="preserve">0.354810297489166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351684272289276</t>
+    <t xml:space="preserve">0.351684212684631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365751564502716</t>
+    <t xml:space="preserve">0.365751594305038</t>
   </si>
   <si>
     <t xml:space="preserve">0.359499484300613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364188581705093</t>
+    <t xml:space="preserve">0.364188551902771</t>
   </si>
   <si>
     <t xml:space="preserve">0.348558157682419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346995145082474</t>
+    <t xml:space="preserve">0.346995174884796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361062496900558</t>
+    <t xml:space="preserve">0.361062467098236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453281909227371</t>
+    <t xml:space="preserve">0.453281879425049</t>
   </si>
   <si>
     <t xml:space="preserve">0.425928741693497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468912363052368</t>
+    <t xml:space="preserve">0.468912392854691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461097151041031</t>
+    <t xml:space="preserve">0.461097121238708</t>
   </si>
   <si>
     <t xml:space="preserve">0.457189530134201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429836302995682</t>
+    <t xml:space="preserve">0.429836273193359</t>
   </si>
   <si>
     <t xml:space="preserve">0.418113529682159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406390696763992</t>
+    <t xml:space="preserve">0.40639066696167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39857542514801</t>
+    <t xml:space="preserve">0.398575484752655</t>
   </si>
   <si>
     <t xml:space="preserve">0.410298258066177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422021090984344</t>
+    <t xml:space="preserve">0.422021120786667</t>
   </si>
   <si>
     <t xml:space="preserve">0.386071145534515</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">0.379818975925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367314666509628</t>
+    <t xml:space="preserve">0.367314636707306</t>
   </si>
   <si>
     <t xml:space="preserve">0.357936412096024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353247314691544</t>
+    <t xml:space="preserve">0.353247255086899</t>
   </si>
   <si>
     <t xml:space="preserve">0.384508103132248</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">0.312608242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329801648855209</t>
+    <t xml:space="preserve">0.329801678657532</t>
   </si>
   <si>
     <t xml:space="preserve">0.331364721059799</t>
@@ -1196,40 +1196,40 @@
     <t xml:space="preserve">0.336053818464279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339179903268814</t>
+    <t xml:space="preserve">0.339179873466492</t>
   </si>
   <si>
     <t xml:space="preserve">0.342305988073349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343869030475616</t>
+    <t xml:space="preserve">0.343869060277939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350121229887009</t>
+    <t xml:space="preserve">0.350121200084686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340742915868759</t>
+    <t xml:space="preserve">0.340742945671082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320423394441605</t>
+    <t xml:space="preserve">0.320423454046249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318860352039337</t>
+    <t xml:space="preserve">0.31886038184166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314171254634857</t>
+    <t xml:space="preserve">0.31417128443718</t>
   </si>
   <si>
     <t xml:space="preserve">0.325112521648407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334490776062012</t>
+    <t xml:space="preserve">0.334490805864334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329168438911438</t>
+    <t xml:space="preserve">0.329168409109116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33408135175705</t>
+    <t xml:space="preserve">0.334081381559372</t>
   </si>
   <si>
     <t xml:space="preserve">0.325893104076385</t>
@@ -1238,76 +1238,76 @@
     <t xml:space="preserve">0.330806076526642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343907296657562</t>
+    <t xml:space="preserve">0.34390726685524</t>
   </si>
   <si>
     <t xml:space="preserve">0.345544934272766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332443714141846</t>
+    <t xml:space="preserve">0.332443743944168</t>
   </si>
   <si>
     <t xml:space="preserve">0.335719019174576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324255436658859</t>
+    <t xml:space="preserve">0.324255466461182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314429551362991</t>
+    <t xml:space="preserve">0.314429521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302965968847275</t>
+    <t xml:space="preserve">0.302965939044952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312791854143143</t>
+    <t xml:space="preserve">0.312791883945465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327530741691589</t>
+    <t xml:space="preserve">0.327530771493912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311154186725616</t>
+    <t xml:space="preserve">0.311154216527939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309516549110413</t>
+    <t xml:space="preserve">0.309516578912735</t>
   </si>
   <si>
     <t xml:space="preserve">0.301328301429749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293140023946762</t>
+    <t xml:space="preserve">0.29313999414444</t>
   </si>
   <si>
     <t xml:space="preserve">0.298052966594696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289864718914032</t>
+    <t xml:space="preserve">0.28986468911171</t>
   </si>
   <si>
     <t xml:space="preserve">0.286589413881302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288227081298828</t>
+    <t xml:space="preserve">0.288227051496506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280038774013519</t>
+    <t xml:space="preserve">0.280038803815842</t>
   </si>
   <si>
     <t xml:space="preserve">0.291502356529236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281676411628723</t>
+    <t xml:space="preserve">0.281676471233368</t>
   </si>
   <si>
     <t xml:space="preserve">0.294777691364288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296415328979492</t>
+    <t xml:space="preserve">0.296415358781815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306241273880005</t>
+    <t xml:space="preserve">0.306241244077682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307878851890564</t>
+    <t xml:space="preserve">0.307878911495209</t>
   </si>
   <si>
     <t xml:space="preserve">0.319342464208603</t>
@@ -1316,46 +1316,46 @@
     <t xml:space="preserve">0.299690663814545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358646154403687</t>
+    <t xml:space="preserve">0.358646184206009</t>
   </si>
   <si>
     <t xml:space="preserve">0.350457906723022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352095603942871</t>
+    <t xml:space="preserve">0.352095574140549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353733241558075</t>
+    <t xml:space="preserve">0.353733211755753</t>
   </si>
   <si>
     <t xml:space="preserve">0.347182601690292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348820298910141</t>
+    <t xml:space="preserve">0.348820269107819</t>
   </si>
   <si>
     <t xml:space="preserve">0.365196824073792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306118369102478</t>
+    <t xml:space="preserve">0.3061183989048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302579432725906</t>
+    <t xml:space="preserve">0.302579462528229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300809949636459</t>
+    <t xml:space="preserve">0.300809979438782</t>
   </si>
   <si>
     <t xml:space="preserve">0.295501559972763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297271013259888</t>
+    <t xml:space="preserve">0.29727104306221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311426758766174</t>
+    <t xml:space="preserve">0.311426788568497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309657335281372</t>
+    <t xml:space="preserve">0.30965730547905</t>
   </si>
   <si>
     <t xml:space="preserve">0.293732076883316</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">0.28842368721962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299040526151657</t>
+    <t xml:space="preserve">0.299040496349335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290193110704422</t>
+    <t xml:space="preserve">0.290193170309067</t>
   </si>
   <si>
     <t xml:space="preserve">0.283115267753601</t>
@@ -1376,61 +1376,61 @@
     <t xml:space="preserve">0.286654204130173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279576271772385</t>
+    <t xml:space="preserve">0.279576331377029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291962653398514</t>
+    <t xml:space="preserve">0.291962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284884691238403</t>
+    <t xml:space="preserve">0.284884750843048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281345784664154</t>
+    <t xml:space="preserve">0.281345814466476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277806878089905</t>
+    <t xml:space="preserve">0.27780681848526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314965754747391</t>
+    <t xml:space="preserve">0.314965724945068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304348915815353</t>
+    <t xml:space="preserve">0.304348945617676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313196271657944</t>
+    <t xml:space="preserve">0.313196212053299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316735208034515</t>
+    <t xml:space="preserve">0.316735178232193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318504691123962</t>
+    <t xml:space="preserve">0.31850466132164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336199402809143</t>
+    <t xml:space="preserve">0.336199343204498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330891013145447</t>
+    <t xml:space="preserve">0.330890953540802</t>
   </si>
   <si>
     <t xml:space="preserve">0.320274144411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325582534074783</t>
+    <t xml:space="preserve">0.325582563877106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323813080787659</t>
+    <t xml:space="preserve">0.323813110589981</t>
   </si>
   <si>
     <t xml:space="preserve">0.322043567895889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321591943502426</t>
+    <t xml:space="preserve">0.321591913700104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310751736164093</t>
+    <t xml:space="preserve">0.310751795768738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307138353586197</t>
+    <t xml:space="preserve">0.307138383388519</t>
   </si>
   <si>
     <t xml:space="preserve">0.314365118741989</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">0.299911558628082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298104912042618</t>
+    <t xml:space="preserve">0.298104882240295</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945059776306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324982434511185</t>
+    <t xml:space="preserve">0.324982464313507</t>
   </si>
   <si>
     <t xml:space="preserve">0.315750032663345</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">0.299131602048874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300978124141693</t>
+    <t xml:space="preserve">0.300978064537048</t>
   </si>
   <si>
     <t xml:space="preserve">0.310210525989532</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">0.304671078920364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295438587665558</t>
+    <t xml:space="preserve">0.29543861746788</t>
   </si>
   <si>
     <t xml:space="preserve">0.293592095375061</t>
@@ -26101,7 +26101,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26127,7 +26127,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26153,7 +26153,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26179,7 +26179,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26205,7 +26205,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26231,7 +26231,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26257,7 +26257,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26283,7 +26283,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26309,7 +26309,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26335,7 +26335,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26361,7 +26361,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26387,7 +26387,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26413,7 +26413,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26439,7 +26439,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26465,7 +26465,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26491,7 +26491,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26543,7 +26543,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26569,7 +26569,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26595,7 +26595,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26621,7 +26621,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26647,7 +26647,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26673,7 +26673,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26699,7 +26699,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26725,7 +26725,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26751,7 +26751,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26777,7 +26777,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26803,7 +26803,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26829,7 +26829,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26855,7 +26855,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26881,7 +26881,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26907,7 +26907,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26933,7 +26933,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26959,7 +26959,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26985,7 +26985,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27011,7 +27011,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27089,7 +27089,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27167,7 +27167,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27193,7 +27193,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27245,7 +27245,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27271,7 +27271,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27297,7 +27297,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27323,7 +27323,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27479,7 +27479,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27505,7 +27505,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27531,7 +27531,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27609,7 +27609,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27635,7 +27635,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28051,7 +28051,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28077,7 +28077,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28103,7 +28103,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28129,7 +28129,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28155,7 +28155,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28181,7 +28181,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28207,7 +28207,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28233,7 +28233,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28259,7 +28259,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28311,7 +28311,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28337,7 +28337,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28363,7 +28363,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28389,7 +28389,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28415,7 +28415,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28441,7 +28441,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28467,7 +28467,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28493,7 +28493,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28519,7 +28519,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28545,7 +28545,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28571,7 +28571,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28649,7 +28649,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28675,7 +28675,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28701,7 +28701,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28727,7 +28727,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28753,7 +28753,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28779,7 +28779,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28805,7 +28805,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28831,7 +28831,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28857,7 +28857,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28883,7 +28883,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28909,7 +28909,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28935,7 +28935,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28961,7 +28961,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28987,7 +28987,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29013,7 +29013,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29039,7 +29039,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29065,7 +29065,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29091,7 +29091,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29117,7 +29117,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29143,7 +29143,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29169,7 +29169,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29273,7 +29273,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29325,7 +29325,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29403,7 +29403,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29429,7 +29429,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29455,7 +29455,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29481,7 +29481,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29507,7 +29507,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29533,7 +29533,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29559,7 +29559,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29585,7 +29585,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29611,7 +29611,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29637,7 +29637,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29663,7 +29663,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29689,7 +29689,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29715,7 +29715,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29741,7 +29741,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29767,7 +29767,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29793,7 +29793,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29819,7 +29819,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29845,7 +29845,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29871,7 +29871,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>307</v>
+        <v>109</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30053,7 +30053,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30183,7 +30183,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30209,7 +30209,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30235,7 +30235,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30287,7 +30287,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30313,7 +30313,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30391,7 +30391,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30781,7 +30781,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30807,7 +30807,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30911,7 +30911,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30963,7 +30963,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30989,7 +30989,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31015,7 +31015,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31119,7 +31119,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31145,7 +31145,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31171,7 +31171,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31223,7 +31223,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31249,7 +31249,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31275,7 +31275,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31301,7 +31301,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31327,7 +31327,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31353,7 +31353,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31379,7 +31379,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31405,7 +31405,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31431,7 +31431,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31457,7 +31457,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31483,7 +31483,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31509,7 +31509,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31535,7 +31535,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31561,7 +31561,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31587,7 +31587,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31613,7 +31613,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31639,7 +31639,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31665,7 +31665,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31691,7 +31691,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31717,7 +31717,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31743,7 +31743,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31769,7 +31769,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31795,7 +31795,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31821,7 +31821,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31847,7 +31847,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31873,7 +31873,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31899,7 +31899,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31951,7 +31951,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31977,7 +31977,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32003,7 +32003,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32055,7 +32055,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32237,7 +32237,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32263,7 +32263,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32289,7 +32289,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32315,7 +32315,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32653,7 +32653,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33147,7 +33147,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34187,7 +34187,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34395,7 +34395,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34421,7 +34421,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34915,7 +34915,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35565,7 +35565,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35591,7 +35591,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35643,7 +35643,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35669,7 +35669,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35695,7 +35695,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35721,7 +35721,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35773,7 +35773,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35799,7 +35799,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35825,7 +35825,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35877,7 +35877,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35903,7 +35903,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35929,7 +35929,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35955,7 +35955,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35981,7 +35981,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36007,7 +36007,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36033,7 +36033,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36059,7 +36059,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36085,7 +36085,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -66664,6 +66664,32 @@
         <v>560</v>
       </c>
       <c r="H2486" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" s="1" t="n">
+        <v>45940.2916666667</v>
+      </c>
+      <c r="B2487" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2487" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="E2487" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="F2487" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="G2487" t="s">
+        <v>560</v>
+      </c>
+      <c r="H2487" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178804159164</t>
+    <t xml:space="preserve">0.179178789258003</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179818704724312</t>
+    <t xml:space="preserve">0.179818719625473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979152321815</t>
+    <t xml:space="preserve">0.175979137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174699306488037</t>
+    <t xml:space="preserve">0.174699321389198</t>
   </si>
   <si>
     <t xml:space="preserve">0.167020231485367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779560089111</t>
+    <t xml:space="preserve">0.172779574990273</t>
   </si>
   <si>
     <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902737975121</t>
+    <t xml:space="preserve">0.145902752876282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493953704834</t>
+    <t xml:space="preserve">0.152493968605995</t>
   </si>
   <si>
     <t xml:space="preserve">0.147822499275208</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">0.156141504645348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517827391624</t>
+    <t xml:space="preserve">0.153517812490463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102330207825</t>
+    <t xml:space="preserve">0.149102345108986</t>
   </si>
   <si>
     <t xml:space="preserve">0.142383143305779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063185572624</t>
+    <t xml:space="preserve">0.142063200473785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447143793106</t>
+    <t xml:space="preserve">0.142447128891945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144622877240181</t>
+    <t xml:space="preserve">0.144622847437859</t>
   </si>
   <si>
     <t xml:space="preserve">0.141423255205154</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">0.173419445753098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169835895299911</t>
+    <t xml:space="preserve">0.169835910201073</t>
   </si>
   <si>
     <t xml:space="preserve">0.166380286216736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981057047844</t>
+    <t xml:space="preserve">0.159981042146683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421365380287</t>
+    <t xml:space="preserve">0.157421380281448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301967144012</t>
+    <t xml:space="preserve">0.152301982045174</t>
   </si>
   <si>
     <t xml:space="preserve">0.158509239554405</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.16382060945034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836832761765</t>
+    <t xml:space="preserve">0.161836847662926</t>
   </si>
   <si>
     <t xml:space="preserve">0.180522605776787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180458649992943</t>
+    <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
     <t xml:space="preserve">0.174059391021729</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">0.168940007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977292299271</t>
+    <t xml:space="preserve">0.191977247595787</t>
   </si>
   <si>
     <t xml:space="preserve">0.19613678753376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176914334297</t>
+    <t xml:space="preserve">0.195176899433136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497764825821</t>
+    <t xml:space="preserve">0.187497809529305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938102960587</t>
+    <t xml:space="preserve">0.184938117861748</t>
   </si>
   <si>
     <t xml:space="preserve">0.204775735735893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454840540886</t>
+    <t xml:space="preserve">0.212454855442047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711765050888</t>
+    <t xml:space="preserve">0.204711779952049</t>
   </si>
   <si>
     <t xml:space="preserve">0.200296297669411</t>
@@ -176,88 +176,88 @@
     <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907546162605</t>
+    <t xml:space="preserve">0.172907516360283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499699354172</t>
+    <t xml:space="preserve">0.171499684453011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165740355849266</t>
+    <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349714517593</t>
+    <t xml:space="preserve">0.154349729418755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579908251762</t>
+    <t xml:space="preserve">0.169579893350601</t>
   </si>
   <si>
     <t xml:space="preserve">0.159917071461678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154861658811569</t>
+    <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781435012817</t>
+    <t xml:space="preserve">0.15678146481514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160493016242981</t>
+    <t xml:space="preserve">0.16049300134182</t>
   </si>
   <si>
     <t xml:space="preserve">0.189417585730553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191337361931801</t>
+    <t xml:space="preserve">0.191337332129478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857849359512</t>
+    <t xml:space="preserve">0.186857864260674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002073645592</t>
+    <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
     <t xml:space="preserve">0.170219853520393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163180664181709</t>
+    <t xml:space="preserve">0.16318067908287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742275476456</t>
+    <t xml:space="preserve">0.149742260575294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221773147583</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022121310234</t>
+    <t xml:space="preserve">0.151022106409073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182568907738</t>
+    <t xml:space="preserve">0.147182583808899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260917782784</t>
+    <t xml:space="preserve">0.161260887980461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168172091245651</t>
+    <t xml:space="preserve">0.168172106146812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739433288574</t>
+    <t xml:space="preserve">0.173739418387413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339251756668</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897991061211</t>
+    <t xml:space="preserve">0.185897976160049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135820269585</t>
+    <t xml:space="preserve">0.204135864973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096675634384</t>
+    <t xml:space="preserve">0.197096645832062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181354522705078</t>
+    <t xml:space="preserve">0.181354537606239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194217011332512</t>
+    <t xml:space="preserve">0.194216996431351</t>
   </si>
   <si>
     <t xml:space="preserve">0.20464776456356</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">0.198376521468163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240870118141</t>
+    <t xml:space="preserve">0.195240914821625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495904803276</t>
+    <t xml:space="preserve">0.203495860099792</t>
   </si>
   <si>
     <t xml:space="preserve">0.216934323310852</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">0.236771956086159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24253123998642</t>
+    <t xml:space="preserve">0.242531284689903</t>
   </si>
   <si>
     <t xml:space="preserve">0.255969673395157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967768669128</t>
+    <t xml:space="preserve">0.271967798471451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28028678894043</t>
+    <t xml:space="preserve">0.280286818742752</t>
   </si>
   <si>
     <t xml:space="preserve">0.295644998550415</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">0.262368947267532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2648646235466</t>
+    <t xml:space="preserve">0.264864653348923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753798246384</t>
+    <t xml:space="preserve">0.254753828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254689812660217</t>
+    <t xml:space="preserve">0.254689782857895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202709317207</t>
+    <t xml:space="preserve">0.247202724218369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650682926178</t>
+    <t xml:space="preserve">0.247650653123856</t>
   </si>
   <si>
     <t xml:space="preserve">0.247778683900833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572348952293</t>
+    <t xml:space="preserve">0.233572334051132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23805183172226</t>
+    <t xml:space="preserve">0.238051816821098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374631643295</t>
+    <t xml:space="preserve">0.214374601840973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663080215454</t>
+    <t xml:space="preserve">0.210663035511971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654462575912</t>
+    <t xml:space="preserve">0.215654492378235</t>
   </si>
   <si>
     <t xml:space="preserve">0.212518811225891</t>
@@ -341,34 +341,34 @@
     <t xml:space="preserve">0.241891369223595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570459127426</t>
+    <t xml:space="preserve">0.249570444226265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980180859566</t>
+    <t xml:space="preserve">0.234980091452599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652572751045</t>
+    <t xml:space="preserve">0.231652528047562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971622824669</t>
+    <t xml:space="preserve">0.239971593022346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372741818428</t>
+    <t xml:space="preserve">0.230372712016106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173119783401</t>
+    <t xml:space="preserve">0.227173089981079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22077389061451</t>
+    <t xml:space="preserve">0.220773831009865</t>
   </si>
   <si>
     <t xml:space="preserve">0.226405218243599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998338699341</t>
+    <t xml:space="preserve">0.21699832379818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204839795827866</t>
+    <t xml:space="preserve">0.204839751124382</t>
   </si>
   <si>
     <t xml:space="preserve">0.207975372672081</t>
@@ -377,58 +377,58 @@
     <t xml:space="preserve">0.210535079240799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.209895133972168</t>
+    <t xml:space="preserve">0.20989516377449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21117502450943</t>
+    <t xml:space="preserve">0.211175039410591</t>
   </si>
   <si>
     <t xml:space="preserve">0.212582811713219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782433748245</t>
+    <t xml:space="preserve">0.215782403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732826352119</t>
+    <t xml:space="preserve">0.229732751846313</t>
   </si>
   <si>
     <t xml:space="preserve">0.223845511674881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805384874344</t>
+    <t xml:space="preserve">0.224805369973183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636349439621</t>
+    <t xml:space="preserve">0.23363633453846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627731800079</t>
+    <t xml:space="preserve">0.238627761602402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580921888351</t>
+    <t xml:space="preserve">0.228580966591835</t>
   </si>
   <si>
     <t xml:space="preserve">0.223973482847214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717480897903</t>
+    <t xml:space="preserve">0.223717495799065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837876200676</t>
+    <t xml:space="preserve">0.220837831497192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492125153542</t>
+    <t xml:space="preserve">0.23549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965802669525</t>
+    <t xml:space="preserve">0.22096586227417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365076541901</t>
+    <t xml:space="preserve">0.227365091443062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556127309799</t>
+    <t xml:space="preserve">0.302556157112122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357608318329</t>
+    <t xml:space="preserve">0.358357578516006</t>
   </si>
   <si>
     <t xml:space="preserve">0.473543912172318</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485702514648438</t>
+    <t xml:space="preserve">0.485702484846115</t>
   </si>
   <si>
     <t xml:space="preserve">0.444747388362885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709106683731</t>
+    <t xml:space="preserve">0.429709136486053</t>
   </si>
   <si>
     <t xml:space="preserve">0.403152257204056</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">0.421710044145584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035686254501</t>
+    <t xml:space="preserve">0.374035745859146</t>
   </si>
   <si>
     <t xml:space="preserve">0.380755007266998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352598249912262</t>
+    <t xml:space="preserve">0.35259822010994</t>
   </si>
   <si>
     <t xml:space="preserve">0.331800699234009</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">0.327641218900681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157911777496</t>
+    <t xml:space="preserve">0.355157941579819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478866577148</t>
+    <t xml:space="preserve">0.347478836774826</t>
   </si>
   <si>
     <t xml:space="preserve">0.332760572433472</t>
@@ -494,37 +494,37 @@
     <t xml:space="preserve">0.32700127363205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159816503525</t>
+    <t xml:space="preserve">0.339159786701202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960149765015</t>
+    <t xml:space="preserve">0.335960209369659</t>
   </si>
   <si>
     <t xml:space="preserve">0.323161721229553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200910568237</t>
+    <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319962114095688</t>
+    <t xml:space="preserve">0.319962084293365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402452230453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759724378586</t>
+    <t xml:space="preserve">0.340759694576263</t>
   </si>
   <si>
     <t xml:space="preserve">0.323801636695862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521835565567</t>
+    <t xml:space="preserve">0.322521775960922</t>
   </si>
   <si>
     <t xml:space="preserve">0.334360390901566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328921049833298</t>
+    <t xml:space="preserve">0.328921020030975</t>
   </si>
   <si>
     <t xml:space="preserve">0.334040462970734</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">0.316122561693192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698521375656</t>
+    <t xml:space="preserve">0.316698431968689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326361328363419</t>
+    <t xml:space="preserve">0.326361358165741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331480711698532</t>
+    <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
     <t xml:space="preserve">0.364756792783737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559120178223</t>
+    <t xml:space="preserve">0.345559149980545</t>
   </si>
   <si>
     <t xml:space="preserve">0.346199035644531</t>
@@ -563,52 +563,52 @@
     <t xml:space="preserve">0.320282071828842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720505237579</t>
+    <t xml:space="preserve">0.333720475435257</t>
   </si>
   <si>
     <t xml:space="preserve">0.396753042936325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275449991226</t>
+    <t xml:space="preserve">0.376275539398193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635534524918</t>
+    <t xml:space="preserve">0.375635474920273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37691542506218</t>
+    <t xml:space="preserve">0.376915335655212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196104049683</t>
+    <t xml:space="preserve">0.370196133852005</t>
   </si>
   <si>
     <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318418979645</t>
+    <t xml:space="preserve">0.351318389177322</t>
   </si>
   <si>
     <t xml:space="preserve">0.356117844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917299985886</t>
+    <t xml:space="preserve">0.360917270183563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715698719025</t>
+    <t xml:space="preserve">0.373715728521347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793169736862</t>
+    <t xml:space="preserve">0.395793199539185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672878742218</t>
+    <t xml:space="preserve">0.398672789335251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38459450006485</t>
+    <t xml:space="preserve">0.384594470262527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954584598541</t>
+    <t xml:space="preserve">0.383954495191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193351268768</t>
+    <t xml:space="preserve">0.394193291664124</t>
   </si>
   <si>
     <t xml:space="preserve">0.384274512529373</t>
@@ -617,34 +617,34 @@
     <t xml:space="preserve">0.415310800075531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42235004901886</t>
+    <t xml:space="preserve">0.422350078821182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312794208527</t>
+    <t xml:space="preserve">0.399312704801559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38363453745842</t>
+    <t xml:space="preserve">0.383634567260742</t>
   </si>
   <si>
     <t xml:space="preserve">0.39355343580246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943245649338</t>
+    <t xml:space="preserve">0.479943186044693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447306990623474</t>
+    <t xml:space="preserve">0.447307020425797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745483636856</t>
+    <t xml:space="preserve">0.460745424032211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547781229019</t>
+    <t xml:space="preserve">0.44154766201973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027249097824</t>
+    <t xml:space="preserve">0.446027189493179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346239566803</t>
+    <t xml:space="preserve">0.454346179962158</t>
   </si>
   <si>
     <t xml:space="preserve">0.447946965694427</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749263286591</t>
+    <t xml:space="preserve">0.428749203681946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230695486069</t>
+    <t xml:space="preserve">0.417230576276779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391053676605</t>
+    <t xml:space="preserve">0.413391083478928</t>
   </si>
   <si>
     <t xml:space="preserve">0.415950745344162</t>
@@ -674,40 +674,40 @@
     <t xml:space="preserve">0.409551471471786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267860889435</t>
+    <t xml:space="preserve">0.440267890691757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909681081772</t>
+    <t xml:space="preserve">0.424909710884094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984250307083</t>
+    <t xml:space="preserve">0.470984220504761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148477554321</t>
+    <t xml:space="preserve">0.435148447751999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406991809606552</t>
+    <t xml:space="preserve">0.406991720199585</t>
   </si>
   <si>
     <t xml:space="preserve">0.426189541816711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431308925151825</t>
+    <t xml:space="preserve">0.43130898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510407209396</t>
+    <t xml:space="preserve">0.418510437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405712008476257</t>
+    <t xml:space="preserve">0.405711948871613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111192941666</t>
+    <t xml:space="preserve">0.41211125254631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38907390832901</t>
+    <t xml:space="preserve">0.389073997735977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390353828668594</t>
+    <t xml:space="preserve">0.390353798866272</t>
   </si>
   <si>
     <t xml:space="preserve">0.395473122596741</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988029956818</t>
+    <t xml:space="preserve">0.438988000154495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469402551651</t>
+    <t xml:space="preserve">0.427469432353973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670914411545</t>
+    <t xml:space="preserve">0.4146708548069</t>
   </si>
   <si>
     <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790267944336</t>
+    <t xml:space="preserve">0.419790327548981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271640539169</t>
+    <t xml:space="preserve">0.408271729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629879951477</t>
+    <t xml:space="preserve">0.423629850149155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596285581589</t>
+    <t xml:space="preserve">0.368596404790878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435867786407</t>
+    <t xml:space="preserve">0.372435957193375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876205921173</t>
+    <t xml:space="preserve">0.369876235723495</t>
   </si>
   <si>
     <t xml:space="preserve">0.346838891506195</t>
@@ -755,109 +755,109 @@
     <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36347696185112</t>
+    <t xml:space="preserve">0.363476932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678503513336</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999398708344</t>
+    <t xml:space="preserve">0.342999368906021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279199838638</t>
+    <t xml:space="preserve">0.344279229640961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958304643631</t>
+    <t xml:space="preserve">0.351958274841309</t>
   </si>
   <si>
     <t xml:space="preserve">0.378835171461105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913430929184</t>
+    <t xml:space="preserve">0.392913520336151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359637409448624</t>
+    <t xml:space="preserve">0.359637439250946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316514253616</t>
+    <t xml:space="preserve">0.367316454648972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234445333481</t>
+    <t xml:space="preserve">0.385234415531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382674723863602</t>
+    <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380114942789078</t>
+    <t xml:space="preserve">0.380115002393723</t>
   </si>
   <si>
     <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032873868942</t>
+    <t xml:space="preserve">0.39803284406662</t>
   </si>
   <si>
     <t xml:space="preserve">0.400592595338821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948840618134</t>
+    <t xml:space="preserve">0.431948870420456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348025083542</t>
+    <t xml:space="preserve">0.438348084688187</t>
   </si>
   <si>
     <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945180177689</t>
+    <t xml:space="preserve">0.463945150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350895404816</t>
+    <t xml:space="preserve">0.472350835800171</t>
   </si>
   <si>
     <t xml:space="preserve">0.451200783252716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100797891617</t>
+    <t xml:space="preserve">0.437100827693939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000812530518</t>
+    <t xml:space="preserve">0.423000752925873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575809001923</t>
+    <t xml:space="preserve">0.433575719594955</t>
   </si>
   <si>
     <t xml:space="preserve">0.444150805473328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675794363022</t>
+    <t xml:space="preserve">0.447675824165344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625756978989</t>
+    <t xml:space="preserve">0.440625816583633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525801420212</t>
+    <t xml:space="preserve">0.426525712013245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41595071554184</t>
+    <t xml:space="preserve">0.415950685739517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900707960129</t>
+    <t xml:space="preserve">0.408900678157806</t>
   </si>
   <si>
     <t xml:space="preserve">0.419475853443146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394800752401352</t>
+    <t xml:space="preserve">0.394800662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325711488724</t>
+    <t xml:space="preserve">0.398325771093369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425816059113</t>
+    <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050820112228</t>
+    <t xml:space="preserve">0.430050790309906</t>
   </si>
   <si>
     <t xml:space="preserve">0.454725831747055</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">0.535800933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250820636749</t>
+    <t xml:space="preserve">0.458250850439072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300887823105</t>
+    <t xml:space="preserve">0.46530082821846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775839328766</t>
+    <t xml:space="preserve">0.461775809526443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375689268112</t>
+    <t xml:space="preserve">0.405375719070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850700378418</t>
+    <t xml:space="preserve">0.401850759983063</t>
   </si>
   <si>
     <t xml:space="preserve">0.387750685214996</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">0.366600632667542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175748348236</t>
+    <t xml:space="preserve">0.377175718545914</t>
   </si>
   <si>
     <t xml:space="preserve">0.391275674104691</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860647201538</t>
+    <t xml:space="preserve">0.346860617399216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450609922409</t>
+    <t xml:space="preserve">0.345450639724731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550625085831</t>
+    <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
     <t xml:space="preserve">0.352500647306442</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">0.338400602340698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250609397888</t>
+    <t xml:space="preserve">0.317250579595566</t>
   </si>
   <si>
     <t xml:space="preserve">0.320070564746857</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">0.277770489454269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490489244461</t>
+    <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24957050383091</t>
+    <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800481557846</t>
+    <t xml:space="preserve">0.253800451755524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248160436749458</t>
+    <t xml:space="preserve">0.248160406947136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460526943207</t>
+    <t xml:space="preserve">0.290460556745529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291870534420013</t>
+    <t xml:space="preserve">0.291870504617691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360511779785</t>
+    <t xml:space="preserve">0.276360481977463</t>
   </si>
   <si>
     <t xml:space="preserve">0.28482049703598</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330609083176</t>
+    <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790534734726</t>
+    <t xml:space="preserve">0.308790564537048</t>
   </si>
   <si>
     <t xml:space="preserve">0.314430564641953</t>
@@ -974,82 +974,82 @@
     <t xml:space="preserve">0.344040602445602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350594758987</t>
+    <t xml:space="preserve">0.331350564956665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325710594654083</t>
+    <t xml:space="preserve">0.325710564851761</t>
   </si>
   <si>
     <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370125591754913</t>
+    <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384225696325302</t>
+    <t xml:space="preserve">0.38422566652298</t>
   </si>
   <si>
     <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990624666214</t>
+    <t xml:space="preserve">0.336990654468536</t>
   </si>
   <si>
     <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025636196136</t>
+    <t xml:space="preserve">0.356025606393814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090669631958</t>
+    <t xml:space="preserve">0.351090580224991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530550003052</t>
+    <t xml:space="preserve">0.328530579805374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940617084503</t>
+    <t xml:space="preserve">0.329940646886826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327120572328568</t>
+    <t xml:space="preserve">0.32712060213089</t>
   </si>
   <si>
     <t xml:space="preserve">0.324300587177277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610549688339</t>
+    <t xml:space="preserve">0.311610579490662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32289057970047</t>
+    <t xml:space="preserve">0.322890549898148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310200601816177</t>
+    <t xml:space="preserve">0.310200542211533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150534629822</t>
+    <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
     <t xml:space="preserve">0.2890505194664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293280512094498</t>
+    <t xml:space="preserve">0.293280571699142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310504198074</t>
+    <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130519151688</t>
+    <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
     <t xml:space="preserve">0.265080481767654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720511674881</t>
+    <t xml:space="preserve">0.270720541477203</t>
   </si>
   <si>
     <t xml:space="preserve">0.274950504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000482082367</t>
+    <t xml:space="preserve">0.282000511884689</t>
   </si>
   <si>
     <t xml:space="preserve">0.297510534524918</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">0.294690519571304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437586933374405</t>
+    <t xml:space="preserve">0.437587022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879037618637</t>
   </si>
   <si>
     <t xml:space="preserve">0.395363658666611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38384822010994</t>
+    <t xml:space="preserve">0.383848249912262</t>
   </si>
   <si>
     <t xml:space="preserve">0.368494302034378</t>
@@ -1079,100 +1079,100 @@
     <t xml:space="preserve">0.376171261072159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370029747486115</t>
+    <t xml:space="preserve">0.37002968788147</t>
   </si>
   <si>
     <t xml:space="preserve">0.38768669962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777418613434</t>
+    <t xml:space="preserve">0.380777448415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565073728561</t>
+    <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211185455322</t>
+    <t xml:space="preserve">0.356211125850677</t>
   </si>
   <si>
     <t xml:space="preserve">0.350069612264633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534196615219</t>
+    <t xml:space="preserve">0.348534226417542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463395118713</t>
+    <t xml:space="preserve">0.345463424921036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281986951828</t>
+    <t xml:space="preserve">0.359281957149506</t>
   </si>
   <si>
     <t xml:space="preserve">0.353140383958817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746541500092</t>
+    <t xml:space="preserve">0.357746511697769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857267379761</t>
+    <t xml:space="preserve">0.340857207775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675769805908</t>
+    <t xml:space="preserve">0.354675799608231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263922214508</t>
+    <t xml:space="preserve">0.445263892412186</t>
   </si>
   <si>
     <t xml:space="preserve">0.418394565582275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617929697037</t>
+    <t xml:space="preserve">0.460617870092392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940911054611</t>
+    <t xml:space="preserve">0.452940881252289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102491140366</t>
+    <t xml:space="preserve">0.449102401733398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233015298843</t>
+    <t xml:space="preserve">0.422233074903488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717695951462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202108383179</t>
+    <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39152517914772</t>
+    <t xml:space="preserve">0.391525208950043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040558099747</t>
+    <t xml:space="preserve">0.403040617704391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556115865707</t>
+    <t xml:space="preserve">0.414556086063385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379242062568665</t>
+    <t xml:space="preserve">0.379242092370987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100489377975</t>
+    <t xml:space="preserve">0.373100459575653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817342996597</t>
+    <t xml:space="preserve">0.360817313194275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351604998111725</t>
+    <t xml:space="preserve">0.35160493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346998810768127</t>
+    <t xml:space="preserve">0.346998780965805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706676721573</t>
+    <t xml:space="preserve">0.37770664691925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958945989609</t>
+    <t xml:space="preserve">0.366958916187286</t>
   </si>
   <si>
     <t xml:space="preserve">0.374635875225067</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">0.322432488203049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305543154478073</t>
+    <t xml:space="preserve">0.305543214082718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307078570127487</t>
+    <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
     <t xml:space="preserve">0.323967933654785</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">0.325503289699554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330109447240829</t>
+    <t xml:space="preserve">0.330109506845474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180218935013</t>
+    <t xml:space="preserve">0.333180248737335</t>
   </si>
   <si>
     <t xml:space="preserve">0.336251050233841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337786495685577</t>
+    <t xml:space="preserve">0.337786436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343927979469299</t>
+    <t xml:space="preserve">0.343928068876266</t>
   </si>
   <si>
     <t xml:space="preserve">0.334715634584427</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">0.308613985776901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319361716508865</t>
+    <t xml:space="preserve">0.319361746311188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32857409119606</t>
+    <t xml:space="preserve">0.328574061393738</t>
   </si>
   <si>
     <t xml:space="preserve">0.323345839977264</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">0.320128470659256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324954569339752</t>
+    <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337824016809464</t>
+    <t xml:space="preserve">0.337823987007141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432686567307</t>
+    <t xml:space="preserve">0.339432746171951</t>
   </si>
   <si>
     <t xml:space="preserve">0.326563239097595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329780608415604</t>
+    <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519830703735</t>
+    <t xml:space="preserve">0.318519800901413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308867692947388</t>
+    <t xml:space="preserve">0.30886772274971</t>
   </si>
   <si>
     <t xml:space="preserve">0.297606855630875</t>
@@ -1265,46 +1265,46 @@
     <t xml:space="preserve">0.307258993387222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737140417099</t>
+    <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650323629379</t>
+    <t xml:space="preserve">0.305650264024734</t>
   </si>
   <si>
     <t xml:space="preserve">0.304041624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998215675354</t>
+    <t xml:space="preserve">0.295998156070709</t>
   </si>
   <si>
     <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780786752701</t>
+    <t xml:space="preserve">0.292780816555023</t>
   </si>
   <si>
     <t xml:space="preserve">0.284737378358841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281520038843155</t>
+    <t xml:space="preserve">0.281520009040833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128678798676</t>
+    <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
     <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346107721329</t>
+    <t xml:space="preserve">0.286346077919006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693940162659</t>
+    <t xml:space="preserve">0.276693999767303</t>
   </si>
   <si>
     <t xml:space="preserve">0.289563477039337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
     <t xml:space="preserve">0.300824254751205</t>
@@ -1316,28 +1316,28 @@
     <t xml:space="preserve">0.313693732023239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294389545917511</t>
+    <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35230216383934</t>
+    <t xml:space="preserve">0.352302193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258785247803</t>
+    <t xml:space="preserve">0.344258725643158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867455005646</t>
+    <t xml:space="preserve">0.345867484807968</t>
   </si>
   <si>
     <t xml:space="preserve">0.347476124763489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34104135632515</t>
+    <t xml:space="preserve">0.341041386127472</t>
   </si>
   <si>
     <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
     <t xml:space="preserve">0.300703495740891</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290274500846863</t>
+    <t xml:space="preserve">0.290274530649185</t>
   </si>
   <si>
     <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305918037891388</t>
+    <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304179906845093</t>
+    <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2885362803936</t>
+    <t xml:space="preserve">0.288536369800568</t>
   </si>
   <si>
     <t xml:space="preserve">0.283321857452393</t>
@@ -1382,43 +1382,43 @@
     <t xml:space="preserve">0.27463099360466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286798149347305</t>
+    <t xml:space="preserve">0.28679820895195</t>
   </si>
   <si>
     <t xml:space="preserve">0.279845505952835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369124650955</t>
+    <t xml:space="preserve">0.276369094848633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27289280295372</t>
+    <t xml:space="preserve">0.272892832756042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394419193268</t>
+    <t xml:space="preserve">0.309394389390945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965364694595</t>
+    <t xml:space="preserve">0.298965394496918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656228542328</t>
+    <t xml:space="preserve">0.307656198740005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132580041885</t>
+    <t xml:space="preserve">0.311132609844208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870770692825</t>
+    <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252468585968</t>
+    <t xml:space="preserve">0.330252438783646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037956237793</t>
+    <t xml:space="preserve">0.325037896633148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314608931541443</t>
+    <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823443889618</t>
+    <t xml:space="preserve">0.319823384284973</t>
   </si>
   <si>
     <t xml:space="preserve">0.318085283041</t>
@@ -1430,19 +1430,19 @@
     <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254936218262</t>
+    <t xml:space="preserve">0.305254995822906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301705449819565</t>
+    <t xml:space="preserve">0.301705479621887</t>
   </si>
   <si>
     <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606506824493</t>
+    <t xml:space="preserve">0.294606536626816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831778526306</t>
+    <t xml:space="preserve">0.292831808328629</t>
   </si>
   <si>
     <t xml:space="preserve">0.303480237722397</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30835098028183</t>
+    <t xml:space="preserve">0.308350950479507</t>
   </si>
   <si>
     <t xml:space="preserve">0.311978667974472</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">0.293840348720551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295654147863388</t>
+    <t xml:space="preserve">0.29565417766571</t>
   </si>
   <si>
     <t xml:space="preserve">0.30472332239151</t>
@@ -1478,25 +1478,25 @@
     <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290212690830231</t>
+    <t xml:space="preserve">0.290212661027908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398861885071</t>
+    <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771203994751</t>
+    <t xml:space="preserve">0.284771233797073</t>
   </si>
   <si>
     <t xml:space="preserve">0.286585032939911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29746800661087</t>
+    <t xml:space="preserve">0.297468036413193</t>
   </si>
   <si>
     <t xml:space="preserve">0.300716459751129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147657394409</t>
+    <t xml:space="preserve">0.295147627592087</t>
   </si>
   <si>
     <t xml:space="preserve">0.308141559362411</t>
@@ -1505,22 +1505,22 @@
     <t xml:space="preserve">0.297003924846649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309997856616974</t>
+    <t xml:space="preserve">0.309997886419296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313710421323776</t>
+    <t xml:space="preserve">0.313710391521454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317422986030579</t>
+    <t xml:space="preserve">0.317422956228256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322991758584976</t>
+    <t xml:space="preserve">0.322991788387299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324848055839539</t>
+    <t xml:space="preserve">0.324848026037216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319279253482819</t>
+    <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
     <t xml:space="preserve">0.334129452705383</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">0.337841957807541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339698284864426</t>
+    <t xml:space="preserve">0.339698255062103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326704323291779</t>
+    <t xml:space="preserve">0.326704293489456</t>
   </si>
   <si>
     <t xml:space="preserve">0.330416858196259</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">0.328126817941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610244750977</t>
+    <t xml:space="preserve">0.337610274553299</t>
   </si>
   <si>
     <t xml:space="preserve">0.331920206546783</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746711730957</t>
+    <t xml:space="preserve">0.316746741533279</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">0.32243674993515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324333488941193</t>
+    <t xml:space="preserve">0.32433345913887</t>
   </si>
   <si>
     <t xml:space="preserve">0.347093731164932</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">0.312953352928162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307263255119324</t>
+    <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
     <t xml:space="preserve">0.360370516777039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887089967728</t>
+    <t xml:space="preserve">0.350887060165405</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">0.354680478572845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377440720796585</t>
+    <t xml:space="preserve">0.377440690994263</t>
   </si>
   <si>
     <t xml:space="preserve">0.405891001224518</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">0.417271107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787710428238</t>
+    <t xml:space="preserve">0.407787680625916</t>
   </si>
   <si>
     <t xml:space="preserve">0.398304253816605</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">0.396407574415207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38123407959938</t>
+    <t xml:space="preserve">0.381234049797058</t>
   </si>
   <si>
     <t xml:space="preserve">0.383130788803101</t>
@@ -1637,25 +1637,25 @@
     <t xml:space="preserve">0.369853943586349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373647302389145</t>
+    <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544011592865</t>
+    <t xml:space="preserve">0.375544041395187</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4020976126194</t>
+    <t xml:space="preserve">0.402097642421722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026545524597</t>
+    <t xml:space="preserve">0.415026515722275</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514023542404</t>
+    <t xml:space="preserve">0.401514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -1698,6 +1698,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.418464630842209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42399999499321</t>
   </si>
 </sst>
 </file>
@@ -66826,6 +66829,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.2916666667</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>562</v>
+      </c>
+      <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178759455681</t>
+    <t xml:space="preserve">0.179178789258003</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -53,43 +53,43 @@
     <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020231485367</t>
+    <t xml:space="preserve">0.167020246386528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779560089111</t>
+    <t xml:space="preserve">0.172779530286789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151662051677704</t>
+    <t xml:space="preserve">0.151662036776543</t>
   </si>
   <si>
     <t xml:space="preserve">0.145902737975121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493953704834</t>
+    <t xml:space="preserve">0.152493938803673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822499275208</t>
+    <t xml:space="preserve">0.147822514176369</t>
   </si>
   <si>
     <t xml:space="preserve">0.1555016040802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141504645348</t>
+    <t xml:space="preserve">0.156141519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517812490463</t>
+    <t xml:space="preserve">0.153517827391624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102330207825</t>
+    <t xml:space="preserve">0.149102345108986</t>
   </si>
   <si>
     <t xml:space="preserve">0.142383128404617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063200473785</t>
+    <t xml:space="preserve">0.142063185572624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447128891945</t>
+    <t xml:space="preserve">0.142447143793106</t>
   </si>
   <si>
     <t xml:space="preserve">0.144622877240181</t>
@@ -101,40 +101,40 @@
     <t xml:space="preserve">0.153837785124779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173419460654259</t>
+    <t xml:space="preserve">0.17341947555542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169835865497589</t>
+    <t xml:space="preserve">0.16983588039875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380286216736</t>
+    <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981071949005</t>
+    <t xml:space="preserve">0.159981042146683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421350479126</t>
+    <t xml:space="preserve">0.15742139518261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301967144012</t>
+    <t xml:space="preserve">0.152301952242851</t>
   </si>
   <si>
     <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16382060945034</t>
+    <t xml:space="preserve">0.163820624351501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836847662926</t>
+    <t xml:space="preserve">0.161836832761765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522620677948</t>
+    <t xml:space="preserve">0.180522635579109</t>
   </si>
   <si>
     <t xml:space="preserve">0.180458649992943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17405940592289</t>
+    <t xml:space="preserve">0.174059420824051</t>
   </si>
   <si>
     <t xml:space="preserve">0.168940007686615</t>
@@ -143,64 +143,64 @@
     <t xml:space="preserve">0.191977277398109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136757731438</t>
+    <t xml:space="preserve">0.19613678753376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176899433136</t>
+    <t xml:space="preserve">0.195176884531975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497824430466</t>
+    <t xml:space="preserve">0.187497794628143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18493814766407</t>
+    <t xml:space="preserve">0.184938102960587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775705933571</t>
+    <t xml:space="preserve">0.204775735735893</t>
   </si>
   <si>
     <t xml:space="preserve">0.212454840540886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711750149727</t>
+    <t xml:space="preserve">0.204711779952049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200296312570572</t>
+    <t xml:space="preserve">0.20029628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736546397209</t>
+    <t xml:space="preserve">0.197736606001854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18237841129303</t>
+    <t xml:space="preserve">0.182378381490707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578018426895</t>
+    <t xml:space="preserve">0.185578033328056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907546162605</t>
+    <t xml:space="preserve">0.172907516360283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499714255333</t>
+    <t xml:space="preserve">0.171499669551849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165740385651588</t>
+    <t xml:space="preserve">0.165740370750427</t>
   </si>
   <si>
     <t xml:space="preserve">0.154349729418755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579908251762</t>
+    <t xml:space="preserve">0.169579923152924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917071461678</t>
+    <t xml:space="preserve">0.159917056560516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154861643910408</t>
+    <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781479716301</t>
+    <t xml:space="preserve">0.156781435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160492986440659</t>
+    <t xml:space="preserve">0.16049300134182</t>
   </si>
   <si>
     <t xml:space="preserve">0.189417570829391</t>
@@ -209,64 +209,64 @@
     <t xml:space="preserve">0.191337332129478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857879161835</t>
+    <t xml:space="preserve">0.186857864260674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002103447914</t>
+    <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170219838619232</t>
+    <t xml:space="preserve">0.170219868421555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163180664181709</t>
+    <t xml:space="preserve">0.16318067908287</t>
   </si>
   <si>
     <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221728444099</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022106409073</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182554006577</t>
+    <t xml:space="preserve">0.147182583808899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260917782784</t>
+    <t xml:space="preserve">0.161260887980461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16817207634449</t>
+    <t xml:space="preserve">0.168172106146812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739418387413</t>
+    <t xml:space="preserve">0.173739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339251756668</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
     <t xml:space="preserve">0.185897961258888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135850071907</t>
+    <t xml:space="preserve">0.204135835170746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096660733223</t>
+    <t xml:space="preserve">0.197096690535545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181354507803917</t>
+    <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
     <t xml:space="preserve">0.194217011332512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204647779464722</t>
+    <t xml:space="preserve">0.20464776456356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376521468163</t>
+    <t xml:space="preserve">0.198376476764679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240870118141</t>
+    <t xml:space="preserve">0.19524085521698</t>
   </si>
   <si>
     <t xml:space="preserve">0.203495904803276</t>
@@ -278,91 +278,91 @@
     <t xml:space="preserve">0.220709890127182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23677197098732</t>
+    <t xml:space="preserve">0.236771941184998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531254887581</t>
+    <t xml:space="preserve">0.242531269788742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969673395157</t>
+    <t xml:space="preserve">0.255969703197479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967768669128</t>
+    <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286759138107</t>
+    <t xml:space="preserve">0.28028678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644998550415</t>
+    <t xml:space="preserve">0.295645028352737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303964048624039</t>
+    <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262368977069855</t>
+    <t xml:space="preserve">0.262368947267532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264864653348923</t>
+    <t xml:space="preserve">0.2648646235466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753798246384</t>
+    <t xml:space="preserve">0.254753828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25468984246254</t>
+    <t xml:space="preserve">0.254689872264862</t>
   </si>
   <si>
     <t xml:space="preserve">0.24720273911953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650623321533</t>
+    <t xml:space="preserve">0.247650668025017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778654098511</t>
+    <t xml:space="preserve">0.247778683900833</t>
   </si>
   <si>
     <t xml:space="preserve">0.233572348952293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238051891326904</t>
+    <t xml:space="preserve">0.238051816821098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374616742134</t>
+    <t xml:space="preserve">0.214374646544456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663035511971</t>
+    <t xml:space="preserve">0.210663065314293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654447674751</t>
+    <t xml:space="preserve">0.215654492378235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518811225891</t>
+    <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
     <t xml:space="preserve">0.241891369223595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570429325104</t>
+    <t xml:space="preserve">0.249570444226265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980136156082</t>
+    <t xml:space="preserve">0.234980180859566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652542948723</t>
+    <t xml:space="preserve">0.231652572751045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971607923508</t>
+    <t xml:space="preserve">0.239971622824669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372726917267</t>
+    <t xml:space="preserve">0.230372741818428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173089981079</t>
+    <t xml:space="preserve">0.227173119783401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773845911026</t>
+    <t xml:space="preserve">0.22077389061451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405173540115</t>
+    <t xml:space="preserve">0.226405218243599</t>
   </si>
   <si>
     <t xml:space="preserve">0.216998308897018</t>
@@ -377,289 +377,289 @@
     <t xml:space="preserve">0.210535064339638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20989516377449</t>
+    <t xml:space="preserve">0.209895148873329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211175009608269</t>
+    <t xml:space="preserve">0.211174979805946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582811713219</t>
+    <t xml:space="preserve">0.21258282661438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782433748245</t>
+    <t xml:space="preserve">0.215782463550568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732826352119</t>
+    <t xml:space="preserve">0.229732811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845481872559</t>
+    <t xml:space="preserve">0.223845526576042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805384874344</t>
+    <t xml:space="preserve">0.224805355072021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636364340782</t>
+    <t xml:space="preserve">0.233636319637299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627731800079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580936789513</t>
+    <t xml:space="preserve">0.228580921888351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973482847214</t>
+    <t xml:space="preserve">0.223973467946053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717495799065</t>
+    <t xml:space="preserve">0.223717540502548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22083780169487</t>
+    <t xml:space="preserve">0.220837816596031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492095351219</t>
+    <t xml:space="preserve">0.23549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965832471848</t>
+    <t xml:space="preserve">0.220965817570686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365091443062</t>
+    <t xml:space="preserve">0.227365076541901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556216716766</t>
+    <t xml:space="preserve">0.302556157112122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357518911362</t>
+    <t xml:space="preserve">0.358357578516006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47354394197464</t>
+    <t xml:space="preserve">0.473543882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454194545746</t>
+    <t xml:space="preserve">0.555454254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48570242524147</t>
+    <t xml:space="preserve">0.485702455043793</t>
   </si>
   <si>
     <t xml:space="preserve">0.444747388362885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709166288376</t>
+    <t xml:space="preserve">0.429709196090698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152287006378</t>
+    <t xml:space="preserve">0.403152227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37115603685379</t>
+    <t xml:space="preserve">0.371156066656113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710073947906</t>
+    <t xml:space="preserve">0.421709954738617</t>
   </si>
   <si>
     <t xml:space="preserve">0.374035716056824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754917860031</t>
+    <t xml:space="preserve">0.380754977464676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352598249912262</t>
+    <t xml:space="preserve">0.352598279714584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331800729036331</t>
+    <t xml:space="preserve">0.331800669431686</t>
   </si>
   <si>
     <t xml:space="preserve">0.320602029561996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332440674304962</t>
+    <t xml:space="preserve">0.332440614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340439677238464</t>
+    <t xml:space="preserve">0.340439736843109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641218900681</t>
+    <t xml:space="preserve">0.327641248703003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157911777496</t>
+    <t xml:space="preserve">0.355157881975174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478836774826</t>
+    <t xml:space="preserve">0.347478866577148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760572433472</t>
+    <t xml:space="preserve">0.332760602235794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121624231339</t>
+    <t xml:space="preserve">0.324121594429016</t>
   </si>
   <si>
     <t xml:space="preserve">0.327001303434372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159816503525</t>
+    <t xml:space="preserve">0.339159846305847</t>
   </si>
   <si>
     <t xml:space="preserve">0.335960209369659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161751031876</t>
+    <t xml:space="preserve">0.323161721229553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200910568237</t>
+    <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31996214389801</t>
+    <t xml:space="preserve">0.319962084293365</t>
   </si>
   <si>
     <t xml:space="preserve">0.317402422428131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759634971619</t>
+    <t xml:space="preserve">0.340759664773941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801636695862</t>
+    <t xml:space="preserve">0.323801606893539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521835565567</t>
+    <t xml:space="preserve">0.322521775960922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360390901566</t>
+    <t xml:space="preserve">0.334360420703888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328920990228653</t>
+    <t xml:space="preserve">0.328921020030975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040462970734</t>
+    <t xml:space="preserve">0.334040492773056</t>
   </si>
   <si>
     <t xml:space="preserve">0.307163625955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122561693192</t>
+    <t xml:space="preserve">0.316122591495514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698431968689</t>
+    <t xml:space="preserve">0.316698521375656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326361328363419</t>
+    <t xml:space="preserve">0.326361358165741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331480771303177</t>
+    <t xml:space="preserve">0.331480741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36475682258606</t>
+    <t xml:space="preserve">0.364756762981415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559120178223</t>
+    <t xml:space="preserve">0.345559060573578</t>
   </si>
   <si>
     <t xml:space="preserve">0.346199005842209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081497430801</t>
+    <t xml:space="preserve">0.325081557035446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959361314774</t>
+    <t xml:space="preserve">0.343959301710129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282101631165</t>
+    <t xml:space="preserve">0.320282131433487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720445632935</t>
+    <t xml:space="preserve">0.333720505237579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753042936325</t>
+    <t xml:space="preserve">0.396752953529358</t>
   </si>
   <si>
     <t xml:space="preserve">0.376275420188904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635534524918</t>
+    <t xml:space="preserve">0.37563556432724</t>
   </si>
   <si>
     <t xml:space="preserve">0.376915365457535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196223258972</t>
+    <t xml:space="preserve">0.370196163654327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555310726166</t>
+    <t xml:space="preserve">0.377555340528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35131847858429</t>
+    <t xml:space="preserve">0.351318418979645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117904186249</t>
+    <t xml:space="preserve">0.356117874383926</t>
   </si>
   <si>
     <t xml:space="preserve">0.360917299985886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715758323669</t>
+    <t xml:space="preserve">0.373715728521347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793169736862</t>
+    <t xml:space="preserve">0.39579313993454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672789335251</t>
+    <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594440460205</t>
+    <t xml:space="preserve">0.384594410657883</t>
   </si>
   <si>
     <t xml:space="preserve">0.383954554796219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193321466446</t>
+    <t xml:space="preserve">0.394193381071091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274572134018</t>
+    <t xml:space="preserve">0.384274423122406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310889482498</t>
+    <t xml:space="preserve">0.415310919284821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422350019216537</t>
+    <t xml:space="preserve">0.422349959611893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312764406204</t>
+    <t xml:space="preserve">0.399312734603882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634567260742</t>
+    <t xml:space="preserve">0.38363453745842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39355343580246</t>
+    <t xml:space="preserve">0.393553406000137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943215847015</t>
+    <t xml:space="preserve">0.479943245649338</t>
   </si>
   <si>
     <t xml:space="preserve">0.447307050228119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745453834534</t>
+    <t xml:space="preserve">0.460745483636856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547691822052</t>
+    <t xml:space="preserve">0.441547781229019</t>
   </si>
   <si>
     <t xml:space="preserve">0.446027219295502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346179962158</t>
+    <t xml:space="preserve">0.454346239566803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447946965694427</t>
+    <t xml:space="preserve">0.447946935892105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430029153823853</t>
+    <t xml:space="preserve">0.430029034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588845491409</t>
+    <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749233484268</t>
+    <t xml:space="preserve">0.428749293088913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230606079102</t>
+    <t xml:space="preserve">0.417230665683746</t>
   </si>
   <si>
     <t xml:space="preserve">0.413391053676605</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">0.421070128679276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551411867142</t>
+    <t xml:space="preserve">0.409551471471786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267831087112</t>
+    <t xml:space="preserve">0.44026792049408</t>
   </si>
   <si>
     <t xml:space="preserve">0.424909681081772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984190702438</t>
+    <t xml:space="preserve">0.470984220504761</t>
   </si>
   <si>
     <t xml:space="preserve">0.435148477554321</t>
@@ -689,82 +689,82 @@
     <t xml:space="preserve">0.406991809606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189482212067</t>
+    <t xml:space="preserve">0.426189571619034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431308895349503</t>
+    <t xml:space="preserve">0.43130898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510466814041</t>
+    <t xml:space="preserve">0.418510407209396</t>
   </si>
   <si>
     <t xml:space="preserve">0.405711978673935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111163139343</t>
+    <t xml:space="preserve">0.412111222743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073967933655</t>
+    <t xml:space="preserve">0.389073997735977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390353798866272</t>
+    <t xml:space="preserve">0.39035376906395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473092794418</t>
+    <t xml:space="preserve">0.395473212003708</t>
   </si>
   <si>
     <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988000154495</t>
+    <t xml:space="preserve">0.438987970352173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469372749329</t>
+    <t xml:space="preserve">0.427469432353973</t>
   </si>
   <si>
     <t xml:space="preserve">0.414670914411545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872485876083</t>
+    <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790327548981</t>
+    <t xml:space="preserve">0.419790297746658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271700143814</t>
+    <t xml:space="preserve">0.408271670341492</t>
   </si>
   <si>
     <t xml:space="preserve">0.42362979054451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596374988556</t>
+    <t xml:space="preserve">0.368596345186234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435986995697</t>
+    <t xml:space="preserve">0.37243589758873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36987629532814</t>
+    <t xml:space="preserve">0.369876205921173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346838921308517</t>
+    <t xml:space="preserve">0.34683895111084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335320323705673</t>
+    <t xml:space="preserve">0.335320293903351</t>
   </si>
   <si>
     <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36347696185112</t>
+    <t xml:space="preserve">0.363476932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678503513336</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999428510666</t>
+    <t xml:space="preserve">0.342999339103699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279229640961</t>
+    <t xml:space="preserve">0.344279199838638</t>
   </si>
   <si>
     <t xml:space="preserve">0.351958364248276</t>
@@ -773,142 +773,139 @@
     <t xml:space="preserve">0.378835141658783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913460731506</t>
+    <t xml:space="preserve">0.392913520336151</t>
   </si>
   <si>
     <t xml:space="preserve">0.359637409448624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316484451294</t>
+    <t xml:space="preserve">0.367316544055939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234355926514</t>
+    <t xml:space="preserve">0.385234326124191</t>
   </si>
   <si>
     <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380114942789078</t>
+    <t xml:space="preserve">0.380115002393723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633629798889</t>
+    <t xml:space="preserve">0.391633659601212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39803284406662</t>
+    <t xml:space="preserve">0.398032814264297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592625141144</t>
+    <t xml:space="preserve">0.400592565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948810815811</t>
+    <t xml:space="preserve">0.431948870420456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348144292831</t>
+    <t xml:space="preserve">0.438348084688187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545787096024</t>
+    <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945060968399</t>
+    <t xml:space="preserve">0.463945180177689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350865602493</t>
+    <t xml:space="preserve">0.472350895404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200723648071</t>
+    <t xml:space="preserve">0.451200753450394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100797891617</t>
+    <t xml:space="preserve">0.43710070848465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000752925873</t>
+    <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
     <t xml:space="preserve">0.433575809001923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150805473328</t>
+    <t xml:space="preserve">0.444150775671005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675853967667</t>
+    <t xml:space="preserve">0.447675794363022</t>
   </si>
   <si>
     <t xml:space="preserve">0.440625816583633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525801420212</t>
+    <t xml:space="preserve">0.426525831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408900707960129</t>
+    <t xml:space="preserve">0.408900767564774</t>
   </si>
   <si>
     <t xml:space="preserve">0.419475793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394800662994385</t>
+    <t xml:space="preserve">0.394800752401352</t>
   </si>
   <si>
     <t xml:space="preserve">0.398325681686401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425756454468</t>
+    <t xml:space="preserve">0.412425696849823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050790309906</t>
+    <t xml:space="preserve">0.430050760507584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725801944733</t>
+    <t xml:space="preserve">0.454725861549377</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250910043716</t>
+    <t xml:space="preserve">0.458250880241394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300887823105</t>
+    <t xml:space="preserve">0.465300798416138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775839328766</t>
+    <t xml:space="preserve">0.461775809526443</t>
   </si>
   <si>
     <t xml:space="preserve">0.405375689268112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850759983063</t>
+    <t xml:space="preserve">0.401850700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750744819641</t>
+    <t xml:space="preserve">0.387750715017319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700707435608</t>
+    <t xml:space="preserve">0.380700647830963</t>
   </si>
   <si>
     <t xml:space="preserve">0.366600632667542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175658941269</t>
+    <t xml:space="preserve">0.377175688743591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275703907013</t>
+    <t xml:space="preserve">0.391275644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650640249252</t>
+    <t xml:space="preserve">0.373650670051575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860647201538</t>
+    <t xml:space="preserve">0.346860706806183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450699329376</t>
+    <t xml:space="preserve">0.345450609922409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550654888153</t>
+    <t xml:space="preserve">0.359550625085831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352500647306442</t>
+    <t xml:space="preserve">0.35250061750412</t>
   </si>
   <si>
     <t xml:space="preserve">0.338400602340698</t>
@@ -923,19 +920,22 @@
     <t xml:space="preserve">0.296100527048111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263670533895493</t>
+    <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283410519361496</t>
+    <t xml:space="preserve">0.283410489559174</t>
   </si>
   <si>
     <t xml:space="preserve">0.267900496721268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770519256592</t>
+    <t xml:space="preserve">0.277770549058914</t>
   </si>
   <si>
     <t xml:space="preserve">0.266490489244461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
     <t xml:space="preserve">0.253800481557846</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">0.248160436749458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460497140884</t>
+    <t xml:space="preserve">0.290460467338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.291870534420013</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">0.284820526838303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286230534315109</t>
+    <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
     <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790504932404</t>
+    <t xml:space="preserve">0.308790534734726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31443053483963</t>
+    <t xml:space="preserve">0.314430564641953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040602445602</t>
+    <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350594758987</t>
+    <t xml:space="preserve">0.33135062456131</t>
   </si>
   <si>
     <t xml:space="preserve">0.325710624456406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680572748184</t>
+    <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37012568116188</t>
+    <t xml:space="preserve">0.370125651359558</t>
   </si>
   <si>
     <t xml:space="preserve">0.384225726127625</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990624666214</t>
+    <t xml:space="preserve">0.336990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630684375763</t>
+    <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025636196136</t>
+    <t xml:space="preserve">0.356025606393814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090669631958</t>
+    <t xml:space="preserve">0.351090639829636</t>
   </si>
   <si>
     <t xml:space="preserve">0.328530579805374</t>
@@ -1010,79 +1010,79 @@
     <t xml:space="preserve">0.327120572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300557374954</t>
+    <t xml:space="preserve">0.324300616979599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610579490662</t>
+    <t xml:space="preserve">0.311610549688339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32289057970047</t>
+    <t xml:space="preserve">0.322890549898148</t>
   </si>
   <si>
     <t xml:space="preserve">0.310200542211533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150534629822</t>
+    <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289050549268723</t>
+    <t xml:space="preserve">0.2890505194664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293280512094498</t>
+    <t xml:space="preserve">0.293280571699142</t>
   </si>
   <si>
     <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27213054895401</t>
+    <t xml:space="preserve">0.272130519151688</t>
   </si>
   <si>
     <t xml:space="preserve">0.265080451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720452070236</t>
+    <t xml:space="preserve">0.270720511674881</t>
   </si>
   <si>
     <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000482082367</t>
+    <t xml:space="preserve">0.282000511884689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297510534524918</t>
+    <t xml:space="preserve">0.297510504722595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301740527153015</t>
+    <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690579175949</t>
+    <t xml:space="preserve">0.294690549373627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43758699297905</t>
+    <t xml:space="preserve">0.437586963176727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879156827927</t>
   </si>
   <si>
     <t xml:space="preserve">0.395363658666611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383848279714584</t>
+    <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368494272232056</t>
+    <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171290874481</t>
+    <t xml:space="preserve">0.376171261072159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370029658079147</t>
+    <t xml:space="preserve">0.370029717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387686729431152</t>
+    <t xml:space="preserve">0.387686669826508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777448415756</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
     <t xml:space="preserve">0.371565073728561</t>
@@ -1091,19 +1091,19 @@
     <t xml:space="preserve">0.356211155653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069582462311</t>
+    <t xml:space="preserve">0.350069612264633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534196615219</t>
+    <t xml:space="preserve">0.348534226417542</t>
   </si>
   <si>
     <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281957149506</t>
+    <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140413761139</t>
+    <t xml:space="preserve">0.353140383958817</t>
   </si>
   <si>
     <t xml:space="preserve">0.357746571302414</t>
@@ -1112,25 +1112,25 @@
     <t xml:space="preserve">0.34239262342453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857267379761</t>
+    <t xml:space="preserve">0.340857237577438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675740003586</t>
+    <t xml:space="preserve">0.354675769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263922214508</t>
+    <t xml:space="preserve">0.445263981819153</t>
   </si>
   <si>
     <t xml:space="preserve">0.418394595384598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617959499359</t>
+    <t xml:space="preserve">0.460617899894714</t>
   </si>
   <si>
     <t xml:space="preserve">0.452940940856934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102491140366</t>
+    <t xml:space="preserve">0.449102401733398</t>
   </si>
   <si>
     <t xml:space="preserve">0.422233074903488</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391525149345398</t>
+    <t xml:space="preserve">0.39152517914772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040587902069</t>
+    <t xml:space="preserve">0.403040617704391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556115865707</t>
+    <t xml:space="preserve">0.414556086063385</t>
   </si>
   <si>
     <t xml:space="preserve">0.379242062568665</t>
@@ -1157,28 +1157,28 @@
     <t xml:space="preserve">0.373100489377975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817313194275</t>
+    <t xml:space="preserve">0.36081737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351604998111725</t>
+    <t xml:space="preserve">0.35160493850708</t>
   </si>
   <si>
     <t xml:space="preserve">0.346998810768127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706676721573</t>
+    <t xml:space="preserve">0.377706736326218</t>
   </si>
   <si>
     <t xml:space="preserve">0.366958916187286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37463590502739</t>
+    <t xml:space="preserve">0.374635875225067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423530340195</t>
+    <t xml:space="preserve">0.365423500537872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432547807693</t>
+    <t xml:space="preserve">0.322432518005371</t>
   </si>
   <si>
     <t xml:space="preserve">0.305543184280396</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323967933654785</t>
+    <t xml:space="preserve">0.32396787405014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503319501877</t>
+    <t xml:space="preserve">0.325503289699554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330109447240829</t>
+    <t xml:space="preserve">0.330109477043152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180248737335</t>
+    <t xml:space="preserve">0.333180278539658</t>
   </si>
   <si>
     <t xml:space="preserve">0.336251020431519</t>
@@ -1205,10 +1205,10 @@
     <t xml:space="preserve">0.337786436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928068876266</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715664386749</t>
+    <t xml:space="preserve">0.334715634584427</t>
   </si>
   <si>
     <t xml:space="preserve">0.31475555896759</t>
@@ -1217,79 +1217,79 @@
     <t xml:space="preserve">0.313220113515854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308614015579224</t>
+    <t xml:space="preserve">0.308613955974579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319361716508865</t>
+    <t xml:space="preserve">0.31936177611351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328574031591415</t>
+    <t xml:space="preserve">0.32857409119606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345869779587</t>
+    <t xml:space="preserve">0.323345899581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.328171879053116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128470659256</t>
+    <t xml:space="preserve">0.320128500461578</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337824046611786</t>
+    <t xml:space="preserve">0.337823957204819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432716369629</t>
+    <t xml:space="preserve">0.339432686567307</t>
   </si>
   <si>
     <t xml:space="preserve">0.326563239097595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329780608415604</t>
+    <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
     <t xml:space="preserve">0.318519771099091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308867663145065</t>
+    <t xml:space="preserve">0.308867692947388</t>
   </si>
   <si>
     <t xml:space="preserve">0.297606855630875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3072589635849</t>
+    <t xml:space="preserve">0.307258993387222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737200021744</t>
+    <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650293827057</t>
+    <t xml:space="preserve">0.305650264024734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041653871536</t>
+    <t xml:space="preserve">0.304041594266891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998185873032</t>
+    <t xml:space="preserve">0.295998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780846357346</t>
+    <t xml:space="preserve">0.292780786752701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737378358841</t>
+    <t xml:space="preserve">0.284737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28151997923851</t>
+    <t xml:space="preserve">0.281520038843155</t>
   </si>
   <si>
     <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085300207138</t>
+    <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
     <t xml:space="preserve">0.286346077919006</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">0.276693940162659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563447237015</t>
+    <t xml:space="preserve">0.289563477039337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
     <t xml:space="preserve">0.300824254751205</t>
@@ -1310,28 +1310,28 @@
     <t xml:space="preserve">0.302432924509048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693732023239</t>
+    <t xml:space="preserve">0.313693702220917</t>
   </si>
   <si>
     <t xml:space="preserve">0.294389486312866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35230216383934</t>
+    <t xml:space="preserve">0.352302193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34425875544548</t>
+    <t xml:space="preserve">0.344258725643158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867514610291</t>
+    <t xml:space="preserve">0.345867455005646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347476154565811</t>
+    <t xml:space="preserve">0.347476124763489</t>
   </si>
   <si>
     <t xml:space="preserve">0.341041386127472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650055885315</t>
+    <t xml:space="preserve">0.342650085687637</t>
   </si>
   <si>
     <t xml:space="preserve">0.358736962080002</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295489013195038</t>
+    <t xml:space="preserve">0.295489072799683</t>
   </si>
   <si>
     <t xml:space="preserve">0.290274530649185</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30417987704277</t>
+    <t xml:space="preserve">0.304179906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536310195923</t>
+    <t xml:space="preserve">0.288536339998245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283321857452393</t>
+    <t xml:space="preserve">0.28332182765007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29375085234642</t>
+    <t xml:space="preserve">0.293750882148743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285059988498688</t>
+    <t xml:space="preserve">0.28506001830101</t>
   </si>
   <si>
     <t xml:space="preserve">0.278107285499573</t>
@@ -1379,25 +1379,25 @@
     <t xml:space="preserve">0.27463099360466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286798179149628</t>
+    <t xml:space="preserve">0.28679820895195</t>
   </si>
   <si>
     <t xml:space="preserve">0.279845476150513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369124650955</t>
+    <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272892832756042</t>
+    <t xml:space="preserve">0.27289280295372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394419193268</t>
+    <t xml:space="preserve">0.309394389390945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965394496918</t>
+    <t xml:space="preserve">0.298965364694595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656228542328</t>
+    <t xml:space="preserve">0.307656198740005</t>
   </si>
   <si>
     <t xml:space="preserve">0.311132580041885</t>
@@ -1406,49 +1406,49 @@
     <t xml:space="preserve">0.312870770692825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252468585968</t>
+    <t xml:space="preserve">0.330252408981323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037986040115</t>
+    <t xml:space="preserve">0.325037956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314608931541443</t>
+    <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823384284973</t>
+    <t xml:space="preserve">0.319823443889618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085253238678</t>
+    <t xml:space="preserve">0.318085223436356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316347122192383</t>
+    <t xml:space="preserve">0.316347062587738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315903395414352</t>
+    <t xml:space="preserve">0.31590336561203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254995822906</t>
+    <t xml:space="preserve">0.305254936218262</t>
   </si>
   <si>
     <t xml:space="preserve">0.301705479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804392814636</t>
+    <t xml:space="preserve">0.308804482221603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606506824493</t>
+    <t xml:space="preserve">0.294606536626816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831808328629</t>
+    <t xml:space="preserve">0.292831778526306</t>
   </si>
   <si>
     <t xml:space="preserve">0.303480237722397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233924150467</t>
+    <t xml:space="preserve">0.319233983755112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31016480922699</t>
+    <t xml:space="preserve">0.310164839029312</t>
   </si>
   <si>
     <t xml:space="preserve">0.30835098028183</t>
@@ -1460,52 +1460,52 @@
     <t xml:space="preserve">0.306537181138992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026489973068</t>
+    <t xml:space="preserve">0.292026519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293840378522873</t>
+    <t xml:space="preserve">0.293840348720551</t>
   </si>
   <si>
     <t xml:space="preserve">0.29565417766571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304723352193832</t>
+    <t xml:space="preserve">0.30472332239151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29928183555603</t>
+    <t xml:space="preserve">0.299281805753708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290212661027908</t>
+    <t xml:space="preserve">0.290212690830231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398861885071</t>
+    <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771233797073</t>
+    <t xml:space="preserve">0.284771174192429</t>
   </si>
   <si>
     <t xml:space="preserve">0.286585062742233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297468036413193</t>
+    <t xml:space="preserve">0.297467976808548</t>
   </si>
   <si>
     <t xml:space="preserve">0.300716489553452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147657394409</t>
+    <t xml:space="preserve">0.295147627592087</t>
   </si>
   <si>
     <t xml:space="preserve">0.308141559362411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297003895044327</t>
+    <t xml:space="preserve">0.297003954648972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309997886419296</t>
+    <t xml:space="preserve">0.309997856616974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313710421323776</t>
+    <t xml:space="preserve">0.313710391521454</t>
   </si>
   <si>
     <t xml:space="preserve">0.317422956228256</t>
@@ -1514,64 +1514,64 @@
     <t xml:space="preserve">0.322991758584976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324848026037216</t>
+    <t xml:space="preserve">0.324848055839539</t>
   </si>
   <si>
     <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334129452705383</t>
+    <t xml:space="preserve">0.334129422903061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337841987609863</t>
+    <t xml:space="preserve">0.337841957807541</t>
   </si>
   <si>
     <t xml:space="preserve">0.339698255062103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326704293489456</t>
+    <t xml:space="preserve">0.326704323291779</t>
   </si>
   <si>
     <t xml:space="preserve">0.330416887998581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330023497343063</t>
+    <t xml:space="preserve">0.330023527145386</t>
   </si>
   <si>
     <t xml:space="preserve">0.335713595151901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328126817941666</t>
+    <t xml:space="preserve">0.328126847743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610274553299</t>
+    <t xml:space="preserve">0.337610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331920206546783</t>
+    <t xml:space="preserve">0.331920236349106</t>
   </si>
   <si>
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746741533279</t>
+    <t xml:space="preserve">0.316746711730957</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341403663158417</t>
+    <t xml:space="preserve">0.341403633356094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32243674993515</t>
+    <t xml:space="preserve">0.322436779737473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32433345913887</t>
+    <t xml:space="preserve">0.324333488941193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347093731164932</t>
+    <t xml:space="preserve">0.34709370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339506983757019</t>
+    <t xml:space="preserve">0.339506953954697</t>
   </si>
   <si>
     <t xml:space="preserve">0.312953352928162</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360370516777039</t>
+    <t xml:space="preserve">0.360370486974716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887060165405</t>
+    <t xml:space="preserve">0.350887089967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354680478572845</t>
+    <t xml:space="preserve">0.354680448770523</t>
   </si>
   <si>
     <t xml:space="preserve">0.377440690994263</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">0.405891001224518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426754534244537</t>
+    <t xml:space="preserve">0.42675456404686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415374428033829</t>
+    <t xml:space="preserve">0.415374457836151</t>
   </si>
   <si>
     <t xml:space="preserve">0.424857884645462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417271107435226</t>
+    <t xml:space="preserve">0.417271137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787680625916</t>
+    <t xml:space="preserve">0.407787710428238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398304253816605</t>
+    <t xml:space="preserve">0.398304224014282</t>
   </si>
   <si>
     <t xml:space="preserve">0.400200933218002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396407574415207</t>
+    <t xml:space="preserve">0.396407604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381234049797058</t>
+    <t xml:space="preserve">0.38123407959938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383130788803101</t>
+    <t xml:space="preserve">0.383130759000778</t>
   </si>
   <si>
     <t xml:space="preserve">0.37933737039566</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544041395187</t>
+    <t xml:space="preserve">0.375544011592865</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402097642421722</t>
+    <t xml:space="preserve">0.4020976126194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026515722275</t>
+    <t xml:space="preserve">0.415026545524597</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514053344727</t>
+    <t xml:space="preserve">0.401514023542404</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -26107,7 +26107,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26133,7 +26133,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26159,7 +26159,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26185,7 +26185,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26211,7 +26211,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26237,7 +26237,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26263,7 +26263,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26289,7 +26289,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26315,7 +26315,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26341,7 +26341,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26367,7 +26367,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26393,7 +26393,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26419,7 +26419,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26445,7 +26445,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26471,7 +26471,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26497,7 +26497,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26549,7 +26549,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26575,7 +26575,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26601,7 +26601,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26627,7 +26627,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26653,7 +26653,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26679,7 +26679,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26705,7 +26705,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26731,7 +26731,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26757,7 +26757,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26783,7 +26783,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26809,7 +26809,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26835,7 +26835,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26861,7 +26861,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26887,7 +26887,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26913,7 +26913,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26939,7 +26939,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26965,7 +26965,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26991,7 +26991,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27017,7 +27017,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27095,7 +27095,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27173,7 +27173,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27199,7 +27199,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27251,7 +27251,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27277,7 +27277,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27303,7 +27303,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27329,7 +27329,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27485,7 +27485,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27511,7 +27511,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27537,7 +27537,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27615,7 +27615,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27641,7 +27641,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28057,7 +28057,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28083,7 +28083,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28109,7 +28109,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28135,7 +28135,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28161,7 +28161,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28187,7 +28187,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28213,7 +28213,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28239,7 +28239,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28265,7 +28265,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28317,7 +28317,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28343,7 +28343,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28369,7 +28369,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28395,7 +28395,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28421,7 +28421,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28447,7 +28447,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28473,7 +28473,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28499,7 +28499,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28525,7 +28525,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28551,7 +28551,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28577,7 +28577,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28655,7 +28655,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28681,7 +28681,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28707,7 +28707,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28733,7 +28733,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28759,7 +28759,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28785,7 +28785,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28811,7 +28811,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28837,7 +28837,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28863,7 +28863,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28889,7 +28889,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28915,7 +28915,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28941,7 +28941,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28967,7 +28967,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28993,7 +28993,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29019,7 +29019,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29045,7 +29045,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29071,7 +29071,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29097,7 +29097,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29149,7 +29149,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29175,7 +29175,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29279,7 +29279,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29331,7 +29331,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29409,7 +29409,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29461,7 +29461,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29487,7 +29487,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29513,7 +29513,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29539,7 +29539,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29565,7 +29565,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29591,7 +29591,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29617,7 +29617,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29643,7 +29643,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29669,7 +29669,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30059,7 +30059,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30319,7 +30319,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31541,7 +31541,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31749,7 +31749,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31775,7 +31775,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31801,7 +31801,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31827,7 +31827,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31879,7 +31879,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31957,7 +31957,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31983,7 +31983,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32009,7 +32009,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32243,7 +32243,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32269,7 +32269,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32295,7 +32295,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32321,7 +32321,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32659,7 +32659,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33153,7 +33153,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34193,7 +34193,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34401,7 +34401,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34427,7 +34427,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34921,7 +34921,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35571,7 +35571,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35597,7 +35597,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35649,7 +35649,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35675,7 +35675,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35701,7 +35701,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35727,7 +35727,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35779,7 +35779,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35805,7 +35805,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35831,7 +35831,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35883,7 +35883,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35909,7 +35909,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35935,7 +35935,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35961,7 +35961,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35987,7 +35987,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36013,7 +36013,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36039,7 +36039,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36065,7 +36065,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36091,7 +36091,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -66883,7 +66883,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.2988773148</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>4000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.179818704724312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979182124138</t>
+    <t xml:space="preserve">0.175979167222977</t>
   </si>
   <si>
     <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020216584206</t>
+    <t xml:space="preserve">0.167020246386528</t>
   </si>
   <si>
     <t xml:space="preserve">0.17277954518795</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">0.145902723073959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493968605995</t>
+    <t xml:space="preserve">0.152493953704834</t>
   </si>
   <si>
     <t xml:space="preserve">0.147822499275208</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.1555016040802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141519546509</t>
+    <t xml:space="preserve">0.15614153444767</t>
   </si>
   <si>
     <t xml:space="preserve">0.153517827391624</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.149102345108986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142383143305779</t>
+    <t xml:space="preserve">0.142383113503456</t>
   </si>
   <si>
     <t xml:space="preserve">0.142063170671463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447113990784</t>
+    <t xml:space="preserve">0.142447143793106</t>
   </si>
   <si>
     <t xml:space="preserve">0.144622877240181</t>
@@ -104,46 +104,46 @@
     <t xml:space="preserve">0.17341947555542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169835865497589</t>
+    <t xml:space="preserve">0.16983588039875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380271315575</t>
+    <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981086850166</t>
+    <t xml:space="preserve">0.159981071949005</t>
   </si>
   <si>
     <t xml:space="preserve">0.157421365380287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301967144012</t>
+    <t xml:space="preserve">0.152301952242851</t>
   </si>
   <si>
     <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163820624351501</t>
+    <t xml:space="preserve">0.163820579648018</t>
   </si>
   <si>
     <t xml:space="preserve">0.161836832761765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522620677948</t>
+    <t xml:space="preserve">0.180522605776787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180458649992943</t>
+    <t xml:space="preserve">0.180458664894104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17405940592289</t>
+    <t xml:space="preserve">0.174059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168939992785454</t>
+    <t xml:space="preserve">0.168939977884293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977277398109</t>
+    <t xml:space="preserve">0.191977262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136802434921</t>
+    <t xml:space="preserve">0.196136742830276</t>
   </si>
   <si>
     <t xml:space="preserve">0.195176899433136</t>
@@ -152,103 +152,103 @@
     <t xml:space="preserve">0.187497809529305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938117861748</t>
+    <t xml:space="preserve">0.184938102960587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775765538216</t>
+    <t xml:space="preserve">0.204775735735893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454870343208</t>
+    <t xml:space="preserve">0.212454840540886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711765050888</t>
+    <t xml:space="preserve">0.204711750149727</t>
   </si>
   <si>
     <t xml:space="preserve">0.20029628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19773656129837</t>
+    <t xml:space="preserve">0.197736576199532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182378396391869</t>
+    <t xml:space="preserve">0.182378381490707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578033328056</t>
+    <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
     <t xml:space="preserve">0.172907546162605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499684453011</t>
+    <t xml:space="preserve">0.171499699354172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165740385651588</t>
+    <t xml:space="preserve">0.16574040055275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349729418755</t>
+    <t xml:space="preserve">0.154349714517593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579893350601</t>
+    <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917086362839</t>
+    <t xml:space="preserve">0.159917056560516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15486167371273</t>
+    <t xml:space="preserve">0.154861658811569</t>
   </si>
   <si>
     <t xml:space="preserve">0.156781435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16049300134182</t>
+    <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417585730553</t>
+    <t xml:space="preserve">0.18941755592823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191337332129478</t>
+    <t xml:space="preserve">0.191337361931801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857849359512</t>
+    <t xml:space="preserve">0.186857864260674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002088546753</t>
+    <t xml:space="preserve">0.185002103447914</t>
   </si>
   <si>
     <t xml:space="preserve">0.170219838619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16318067908287</t>
+    <t xml:space="preserve">0.163180664181709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742260575294</t>
+    <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221728444099</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022106409073</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182583808899</t>
+    <t xml:space="preserve">0.14718259871006</t>
   </si>
   <si>
     <t xml:space="preserve">0.161260917782784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16817207634449</t>
+    <t xml:space="preserve">0.168172091245651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739418387413</t>
+    <t xml:space="preserve">0.173739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339251756668</t>
+    <t xml:space="preserve">0.175339221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897976160049</t>
+    <t xml:space="preserve">0.185897961258888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135820269585</t>
+    <t xml:space="preserve">0.204135835170746</t>
   </si>
   <si>
     <t xml:space="preserve">0.197096660733223</t>
@@ -263,73 +263,73 @@
     <t xml:space="preserve">0.20464776456356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376536369324</t>
+    <t xml:space="preserve">0.198376506567001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240870118141</t>
+    <t xml:space="preserve">0.195240885019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495889902115</t>
+    <t xml:space="preserve">0.203495875000954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21693429350853</t>
+    <t xml:space="preserve">0.216934323310852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22070986032486</t>
+    <t xml:space="preserve">0.220709875226021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236771985888481</t>
+    <t xml:space="preserve">0.236772000789642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531269788742</t>
+    <t xml:space="preserve">0.242531254887581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969703197479</t>
+    <t xml:space="preserve">0.255969673395157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967798471451</t>
+    <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28028678894043</t>
+    <t xml:space="preserve">0.280286818742752</t>
   </si>
   <si>
     <t xml:space="preserve">0.295644998550415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303964018821716</t>
+    <t xml:space="preserve">0.303963989019394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26236891746521</t>
+    <t xml:space="preserve">0.262368947267532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264864653348923</t>
+    <t xml:space="preserve">0.2648646235466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753887653351</t>
+    <t xml:space="preserve">0.254753798246384</t>
   </si>
   <si>
     <t xml:space="preserve">0.25468984246254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202709317207</t>
+    <t xml:space="preserve">0.247202724218369</t>
   </si>
   <si>
     <t xml:space="preserve">0.247650653123856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778683900833</t>
+    <t xml:space="preserve">0.247778654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572334051132</t>
+    <t xml:space="preserve">0.233572319149971</t>
   </si>
   <si>
     <t xml:space="preserve">0.238051801919937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374631643295</t>
+    <t xml:space="preserve">0.214374646544456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663065314293</t>
+    <t xml:space="preserve">0.210663050413132</t>
   </si>
   <si>
     <t xml:space="preserve">0.215654492378235</t>
@@ -338,46 +338,46 @@
     <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891369223595</t>
+    <t xml:space="preserve">0.241891354322433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570429325104</t>
+    <t xml:space="preserve">0.249570414423943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980195760727</t>
+    <t xml:space="preserve">0.234980151057243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652587652206</t>
+    <t xml:space="preserve">0.231652557849884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971548318863</t>
+    <t xml:space="preserve">0.239971593022346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372756719589</t>
+    <t xml:space="preserve">0.230372726917267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173119783401</t>
+    <t xml:space="preserve">0.22717310488224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22077389061451</t>
+    <t xml:space="preserve">0.220773845911026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405218243599</t>
+    <t xml:space="preserve">0.226405203342438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998293995857</t>
+    <t xml:space="preserve">0.216998338699341</t>
   </si>
   <si>
     <t xml:space="preserve">0.204839736223221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207975372672081</t>
+    <t xml:space="preserve">0.20797535777092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21053509414196</t>
+    <t xml:space="preserve">0.210535034537315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.209895148873329</t>
+    <t xml:space="preserve">0.20989516377449</t>
   </si>
   <si>
     <t xml:space="preserve">0.211175009608269</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">0.212582796812057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782463550568</t>
+    <t xml:space="preserve">0.215782448649406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732811450958</t>
+    <t xml:space="preserve">0.229732796549797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845511674881</t>
+    <t xml:space="preserve">0.22384549677372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805399775505</t>
+    <t xml:space="preserve">0.224805414676666</t>
   </si>
   <si>
     <t xml:space="preserve">0.233636304736137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627761602402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22858090698719</t>
+    <t xml:space="preserve">0.228580936789513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973467946053</t>
+    <t xml:space="preserve">0.223973527550697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717495799065</t>
+    <t xml:space="preserve">0.223717510700226</t>
   </si>
   <si>
     <t xml:space="preserve">0.220837846398354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492154955864</t>
+    <t xml:space="preserve">0.235492140054703</t>
   </si>
   <si>
     <t xml:space="preserve">0.220965817570686</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">0.358357578516006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473543971776962</t>
+    <t xml:space="preserve">0.473544001579285</t>
   </si>
   <si>
     <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485702514648438</t>
+    <t xml:space="preserve">0.48570254445076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444747298955917</t>
+    <t xml:space="preserve">0.444747388362885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709166288376</t>
+    <t xml:space="preserve">0.429709136486053</t>
   </si>
   <si>
     <t xml:space="preserve">0.403152287006378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371156066656113</t>
+    <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710073947906</t>
+    <t xml:space="preserve">0.421710014343262</t>
   </si>
   <si>
     <t xml:space="preserve">0.374035716056824</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">0.380754947662354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35259822010994</t>
+    <t xml:space="preserve">0.352598249912262</t>
   </si>
   <si>
     <t xml:space="preserve">0.331800669431686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602029561996</t>
+    <t xml:space="preserve">0.320602059364319</t>
   </si>
   <si>
     <t xml:space="preserve">0.33244064450264</t>
@@ -476,58 +476,58 @@
     <t xml:space="preserve">0.340439677238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641248703003</t>
+    <t xml:space="preserve">0.327641159296036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157941579819</t>
+    <t xml:space="preserve">0.355157971382141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478836774826</t>
+    <t xml:space="preserve">0.347478866577148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760542631149</t>
+    <t xml:space="preserve">0.332760602235794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121594429016</t>
+    <t xml:space="preserve">0.324121624231339</t>
   </si>
   <si>
     <t xml:space="preserve">0.32700127363205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159786701202</t>
+    <t xml:space="preserve">0.339159816503525</t>
   </si>
   <si>
     <t xml:space="preserve">0.335960179567337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161751031876</t>
+    <t xml:space="preserve">0.323161721229553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200910568237</t>
+    <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319962173700333</t>
+    <t xml:space="preserve">0.31996214389801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759694576263</t>
+    <t xml:space="preserve">0.340759664773941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801606893539</t>
+    <t xml:space="preserve">0.323801636695862</t>
   </si>
   <si>
     <t xml:space="preserve">0.322521835565567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360420703888</t>
+    <t xml:space="preserve">0.334360390901566</t>
   </si>
   <si>
     <t xml:space="preserve">0.328921020030975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040433168411</t>
+    <t xml:space="preserve">0.334040492773056</t>
   </si>
   <si>
     <t xml:space="preserve">0.307163625955582</t>
@@ -536,85 +536,85 @@
     <t xml:space="preserve">0.316122561693192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698461771011</t>
+    <t xml:space="preserve">0.316698521375656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326361358165741</t>
+    <t xml:space="preserve">0.326361328363419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331480771303177</t>
+    <t xml:space="preserve">0.331480801105499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364756792783737</t>
+    <t xml:space="preserve">0.364756762981415</t>
   </si>
   <si>
     <t xml:space="preserve">0.3455590903759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199035644531</t>
+    <t xml:space="preserve">0.346199005842209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081527233124</t>
+    <t xml:space="preserve">0.325081557035446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959331512451</t>
+    <t xml:space="preserve">0.343959301710129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282101631165</t>
+    <t xml:space="preserve">0.320282071828842</t>
   </si>
   <si>
     <t xml:space="preserve">0.333720475435257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753072738647</t>
+    <t xml:space="preserve">0.396753013134003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275479793549</t>
+    <t xml:space="preserve">0.376275449991226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37563556432724</t>
+    <t xml:space="preserve">0.375635594129562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376915365457535</t>
+    <t xml:space="preserve">0.376915395259857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196133852005</t>
+    <t xml:space="preserve">0.370196163654327</t>
   </si>
   <si>
     <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318418979645</t>
+    <t xml:space="preserve">0.351318389177322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117844581604</t>
+    <t xml:space="preserve">0.356117874383926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917299985886</t>
+    <t xml:space="preserve">0.360917329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715698719025</t>
+    <t xml:space="preserve">0.373715728521347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793199539185</t>
+    <t xml:space="preserve">0.39579313993454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672789335251</t>
+    <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38459450006485</t>
+    <t xml:space="preserve">0.384594470262527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954554796219</t>
+    <t xml:space="preserve">0.383954524993896</t>
   </si>
   <si>
     <t xml:space="preserve">0.394193321466446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274512529373</t>
+    <t xml:space="preserve">0.384274452924728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310800075531</t>
+    <t xml:space="preserve">0.415310829877853</t>
   </si>
   <si>
     <t xml:space="preserve">0.422350019216537</t>
@@ -623,133 +623,133 @@
     <t xml:space="preserve">0.399312734603882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634567260742</t>
+    <t xml:space="preserve">0.383634597063065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553465604782</t>
+    <t xml:space="preserve">0.393553376197815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943096637726</t>
+    <t xml:space="preserve">0.479943186044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.447307020425797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745513439178</t>
+    <t xml:space="preserve">0.460745453834534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547781229019</t>
+    <t xml:space="preserve">0.441547691822052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027249097824</t>
+    <t xml:space="preserve">0.446027219295502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346239566803</t>
+    <t xml:space="preserve">0.454346209764481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447946935892105</t>
+    <t xml:space="preserve">0.447947055101395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430029064416885</t>
+    <t xml:space="preserve">0.430029034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588785886765</t>
+    <t xml:space="preserve">0.43258872628212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749263286591</t>
+    <t xml:space="preserve">0.428749293088913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230665683746</t>
+    <t xml:space="preserve">0.417230635881424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391053676605</t>
+    <t xml:space="preserve">0.413391083478928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
+    <t xml:space="preserve">0.41595071554184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42107018828392</t>
+    <t xml:space="preserve">0.421070069074631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551531076431</t>
+    <t xml:space="preserve">0.409551471471786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267950296402</t>
+    <t xml:space="preserve">0.440267890691757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909740686417</t>
+    <t xml:space="preserve">0.424909681081772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984309911728</t>
+    <t xml:space="preserve">0.470984280109406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148507356644</t>
+    <t xml:space="preserve">0.435148417949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40699177980423</t>
+    <t xml:space="preserve">0.406991750001907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189571619034</t>
+    <t xml:space="preserve">0.426189482212067</t>
   </si>
   <si>
     <t xml:space="preserve">0.43130898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510466814041</t>
+    <t xml:space="preserve">0.418510526418686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405711948871613</t>
+    <t xml:space="preserve">0.405711978673935</t>
   </si>
   <si>
     <t xml:space="preserve">0.412111192941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073967933655</t>
+    <t xml:space="preserve">0.389073938131332</t>
   </si>
   <si>
     <t xml:space="preserve">0.390353798866272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473122596741</t>
+    <t xml:space="preserve">0.395473152399063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831391811371</t>
+    <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988089561462</t>
+    <t xml:space="preserve">0.438988029956818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469432353973</t>
+    <t xml:space="preserve">0.427469372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670884609222</t>
+    <t xml:space="preserve">0.414670914411545</t>
   </si>
   <si>
     <t xml:space="preserve">0.401872366666794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790297746658</t>
+    <t xml:space="preserve">0.419790327548981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271640539169</t>
+    <t xml:space="preserve">0.408271670341492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629909753799</t>
+    <t xml:space="preserve">0.423629850149155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596374988556</t>
+    <t xml:space="preserve">0.368596315383911</t>
   </si>
   <si>
     <t xml:space="preserve">0.372435927391052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876235723495</t>
+    <t xml:space="preserve">0.369876205921173</t>
   </si>
   <si>
     <t xml:space="preserve">0.34683895111084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335320323705673</t>
+    <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
     <t xml:space="preserve">0.366036683320999</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">0.36347696185112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678503513336</t>
+    <t xml:space="preserve">0.350678443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999368906021</t>
+    <t xml:space="preserve">0.342999398708344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279229640961</t>
+    <t xml:space="preserve">0.344279259443283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958364248276</t>
+    <t xml:space="preserve">0.351958334445953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835171461105</t>
+    <t xml:space="preserve">0.378835111856461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913520336151</t>
+    <t xml:space="preserve">0.392913460731506</t>
   </si>
   <si>
     <t xml:space="preserve">0.359637409448624</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">0.367316514253616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234385728836</t>
+    <t xml:space="preserve">0.385234445333481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382674664258957</t>
+    <t xml:space="preserve">0.382674723863602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3801149725914</t>
+    <t xml:space="preserve">0.380115002393723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633599996567</t>
+    <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032814264297</t>
+    <t xml:space="preserve">0.39803284406662</t>
   </si>
   <si>
     <t xml:space="preserve">0.400592565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948870420456</t>
+    <t xml:space="preserve">0.431948900222778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348144292831</t>
+    <t xml:space="preserve">0.438348114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545816898346</t>
+    <t xml:space="preserve">0.457545846700668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945120573044</t>
+    <t xml:space="preserve">0.463945150375366</t>
   </si>
   <si>
     <t xml:space="preserve">0.472350835800171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200783252716</t>
+    <t xml:space="preserve">0.451200813055038</t>
   </si>
   <si>
     <t xml:space="preserve">0.437100797891617</t>
@@ -824,31 +824,31 @@
     <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4335757791996</t>
+    <t xml:space="preserve">0.433575749397278</t>
   </si>
   <si>
     <t xml:space="preserve">0.444150805473328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675853967667</t>
+    <t xml:space="preserve">0.447675794363022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625816583633</t>
+    <t xml:space="preserve">0.440625786781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525801420212</t>
+    <t xml:space="preserve">0.426525741815567</t>
   </si>
   <si>
     <t xml:space="preserve">0.408900737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475823640823</t>
+    <t xml:space="preserve">0.419475764036179</t>
   </si>
   <si>
     <t xml:space="preserve">0.39480072259903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325741291046</t>
+    <t xml:space="preserve">0.398325711488724</t>
   </si>
   <si>
     <t xml:space="preserve">0.412425726652145</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">0.45472577214241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800993442535</t>
+    <t xml:space="preserve">0.535800874233246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250820636749</t>
+    <t xml:space="preserve">0.458250790834427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46530082821846</t>
+    <t xml:space="preserve">0.465300768613815</t>
   </si>
   <si>
     <t xml:space="preserve">0.461775809526443</t>
@@ -875,76 +875,76 @@
     <t xml:space="preserve">0.405375719070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850759983063</t>
+    <t xml:space="preserve">0.401850670576096</t>
   </si>
   <si>
     <t xml:space="preserve">0.387750715017319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38070073723793</t>
+    <t xml:space="preserve">0.380700677633286</t>
   </si>
   <si>
     <t xml:space="preserve">0.366600632667542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175748348236</t>
+    <t xml:space="preserve">0.377175718545914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275733709335</t>
+    <t xml:space="preserve">0.391275703907013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650670051575</t>
+    <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34686067700386</t>
+    <t xml:space="preserve">0.346860647201538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450639724731</t>
+    <t xml:space="preserve">0.345450609922409</t>
   </si>
   <si>
     <t xml:space="preserve">0.359550625085831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352500647306442</t>
+    <t xml:space="preserve">0.35250061750412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400602340698</t>
+    <t xml:space="preserve">0.338400572538376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250579595566</t>
+    <t xml:space="preserve">0.317250549793243</t>
   </si>
   <si>
     <t xml:space="preserve">0.320070594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296100527048111</t>
+    <t xml:space="preserve">0.296100497245789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26367050409317</t>
+    <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900496721268</t>
+    <t xml:space="preserve">0.267900437116623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770489454269</t>
+    <t xml:space="preserve">0.277770519256592</t>
   </si>
   <si>
     <t xml:space="preserve">0.266490489244461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800481557846</t>
+    <t xml:space="preserve">0.253800421953201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248160436749458</t>
+    <t xml:space="preserve">0.248160392045975</t>
   </si>
   <si>
     <t xml:space="preserve">0.290460526943207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291870564222336</t>
+    <t xml:space="preserve">0.291870534420013</t>
   </si>
   <si>
     <t xml:space="preserve">0.276360511779785</t>
@@ -959,37 +959,37 @@
     <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790504932404</t>
+    <t xml:space="preserve">0.308790564537048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31443053483963</t>
+    <t xml:space="preserve">0.314430594444275</t>
   </si>
   <si>
     <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350594758987</t>
+    <t xml:space="preserve">0.331350564956665</t>
   </si>
   <si>
     <t xml:space="preserve">0.325710624456406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680602550507</t>
+    <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37012568116188</t>
+    <t xml:space="preserve">0.370125651359558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38422566652298</t>
+    <t xml:space="preserve">0.384225696325302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170579910278</t>
+    <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990624666214</t>
+    <t xml:space="preserve">0.336990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630624771118</t>
+    <t xml:space="preserve">0.342630654573441</t>
   </si>
   <si>
     <t xml:space="preserve">0.356025665998459</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">0.328530579805374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940617084503</t>
+    <t xml:space="preserve">0.329940587282181</t>
   </si>
   <si>
     <t xml:space="preserve">0.327120542526245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300587177277</t>
+    <t xml:space="preserve">0.324300616979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.311610549688339</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310200542211533</t>
+    <t xml:space="preserve">0.310200572013855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150564432144</t>
+    <t xml:space="preserve">0.303150504827499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289050549268723</t>
+    <t xml:space="preserve">0.289050459861755</t>
   </si>
   <si>
     <t xml:space="preserve">0.293280512094498</t>
@@ -1031,46 +1031,46 @@
     <t xml:space="preserve">0.269310504198074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130519151688</t>
+    <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265080451965332</t>
+    <t xml:space="preserve">0.26508042216301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720511674881</t>
+    <t xml:space="preserve">0.270720452070236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950444698334</t>
+    <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
     <t xml:space="preserve">0.282000482082367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297510504722595</t>
+    <t xml:space="preserve">0.297510534524918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301740527153015</t>
+    <t xml:space="preserve">0.30174058675766</t>
   </si>
   <si>
     <t xml:space="preserve">0.294690549373627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437587052583694</t>
+    <t xml:space="preserve">0.437586933374405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879097223282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363658666611</t>
+    <t xml:space="preserve">0.395363688468933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383848279714584</t>
+    <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
     <t xml:space="preserve">0.368494272232056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171290874481</t>
+    <t xml:space="preserve">0.376171261072159</t>
   </si>
   <si>
     <t xml:space="preserve">0.37002968788147</t>
@@ -1079,52 +1079,52 @@
     <t xml:space="preserve">0.387686729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777418613434</t>
+    <t xml:space="preserve">0.380777448415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565073728561</t>
+    <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
     <t xml:space="preserve">0.356211125850677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069582462311</t>
+    <t xml:space="preserve">0.350069552659988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534196615219</t>
+    <t xml:space="preserve">0.348534226417542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463424921036</t>
+    <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281957149506</t>
+    <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140383958817</t>
+    <t xml:space="preserve">0.353140413761139</t>
   </si>
   <si>
     <t xml:space="preserve">0.357746541500092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857237577438</t>
+    <t xml:space="preserve">0.340857177972794</t>
   </si>
   <si>
     <t xml:space="preserve">0.354675799608231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263922214508</t>
+    <t xml:space="preserve">0.44526395201683</t>
   </si>
   <si>
     <t xml:space="preserve">0.418394565582275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617929697037</t>
+    <t xml:space="preserve">0.460617899894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940911054611</t>
+    <t xml:space="preserve">0.452940881252289</t>
   </si>
   <si>
     <t xml:space="preserve">0.449102431535721</t>
@@ -1139,46 +1139,46 @@
     <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391525149345398</t>
+    <t xml:space="preserve">0.39152517914772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040647506714</t>
+    <t xml:space="preserve">0.403040617704391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41455614566803</t>
+    <t xml:space="preserve">0.414556086063385</t>
   </si>
   <si>
     <t xml:space="preserve">0.379242032766342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100489377975</t>
+    <t xml:space="preserve">0.373100519180298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817342996597</t>
+    <t xml:space="preserve">0.360817313194275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351604998111725</t>
+    <t xml:space="preserve">0.351604968309402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34699884057045</t>
+    <t xml:space="preserve">0.346998780965805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706706523895</t>
+    <t xml:space="preserve">0.377706676721573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958916187286</t>
+    <t xml:space="preserve">0.366958886384964</t>
   </si>
   <si>
     <t xml:space="preserve">0.37463590502739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423500537872</t>
+    <t xml:space="preserve">0.365423530340195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432518005371</t>
+    <t xml:space="preserve">0.322432488203049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305543184280396</t>
+    <t xml:space="preserve">0.305543154478073</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078570127487</t>
@@ -1187,31 +1187,31 @@
     <t xml:space="preserve">0.323967903852463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503289699554</t>
+    <t xml:space="preserve">0.325503259897232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330109477043152</t>
+    <t xml:space="preserve">0.330109447240829</t>
   </si>
   <si>
     <t xml:space="preserve">0.333180278539658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336250990629196</t>
+    <t xml:space="preserve">0.336251050233841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337786436080933</t>
+    <t xml:space="preserve">0.337786465883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928039073944</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715664386749</t>
+    <t xml:space="preserve">0.334715634584427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314755588769913</t>
+    <t xml:space="preserve">0.314755499362946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220143318176</t>
+    <t xml:space="preserve">0.313220173120499</t>
   </si>
   <si>
     <t xml:space="preserve">0.308613985776901</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">0.319361716508865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328574061393738</t>
+    <t xml:space="preserve">0.328574120998383</t>
   </si>
   <si>
     <t xml:space="preserve">0.323345869779587</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">0.328171908855438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128470659256</t>
+    <t xml:space="preserve">0.320128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337824016809464</t>
+    <t xml:space="preserve">0.337823987007141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432716369629</t>
+    <t xml:space="preserve">0.339432686567307</t>
   </si>
   <si>
     <t xml:space="preserve">0.326563209295273</t>
@@ -1247,28 +1247,28 @@
     <t xml:space="preserve">0.329780548810959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519771099091</t>
+    <t xml:space="preserve">0.318519800901413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30886772274971</t>
+    <t xml:space="preserve">0.308867633342743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606885433197</t>
+    <t xml:space="preserve">0.297606915235519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307258933782578</t>
+    <t xml:space="preserve">0.307258993387222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737200021744</t>
+    <t xml:space="preserve">0.321737140417099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650293827057</t>
+    <t xml:space="preserve">0.305650264024734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041594266891</t>
+    <t xml:space="preserve">0.304041624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998185873032</t>
+    <t xml:space="preserve">0.295998156070709</t>
   </si>
   <si>
     <t xml:space="preserve">0.287954747676849</t>
@@ -1277,34 +1277,34 @@
     <t xml:space="preserve">0.292780786752701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737408161163</t>
+    <t xml:space="preserve">0.284737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281520009040833</t>
+    <t xml:space="preserve">0.281520038843155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128708600998</t>
+    <t xml:space="preserve">0.283128648996353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085300207138</t>
+    <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346107721329</t>
+    <t xml:space="preserve">0.286346077919006</t>
   </si>
   <si>
     <t xml:space="preserve">0.276693969964981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563477039337</t>
+    <t xml:space="preserve">0.289563417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291172116994858</t>
+    <t xml:space="preserve">0.29117214679718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824284553528</t>
+    <t xml:space="preserve">0.300824224948883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432924509048</t>
+    <t xml:space="preserve">0.302432894706726</t>
   </si>
   <si>
     <t xml:space="preserve">0.313693732023239</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">0.294389486312866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35230216383934</t>
+    <t xml:space="preserve">0.352302193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34425875544548</t>
+    <t xml:space="preserve">0.344258785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867484807968</t>
+    <t xml:space="preserve">0.345867425203323</t>
   </si>
   <si>
     <t xml:space="preserve">0.347476154565811</t>
@@ -1328,37 +1328,37 @@
     <t xml:space="preserve">0.34104135632515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650055885315</t>
+    <t xml:space="preserve">0.342650085687637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300703525543213</t>
+    <t xml:space="preserve">0.300703555345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.2972272336483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295489013195038</t>
+    <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
     <t xml:space="preserve">0.290274500846863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29201266169548</t>
+    <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30591806769371</t>
+    <t xml:space="preserve">0.305918037891388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30417987704277</t>
+    <t xml:space="preserve">0.304179906845093</t>
   </si>
   <si>
     <t xml:space="preserve">0.288536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283321797847748</t>
+    <t xml:space="preserve">0.283321887254715</t>
   </si>
   <si>
     <t xml:space="preserve">0.29375085234642</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">0.278107315301895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28158363699913</t>
+    <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
     <t xml:space="preserve">0.27463099360466</t>
@@ -1382,37 +1382,37 @@
     <t xml:space="preserve">0.279845505952835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369124650955</t>
+    <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272892832756042</t>
+    <t xml:space="preserve">0.27289280295372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394419193268</t>
+    <t xml:space="preserve">0.309394389390945</t>
   </si>
   <si>
     <t xml:space="preserve">0.298965364694595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656228542328</t>
+    <t xml:space="preserve">0.307656198740005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132550239563</t>
+    <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870770692825</t>
+    <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252468585968</t>
+    <t xml:space="preserve">0.330252408981323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037986040115</t>
+    <t xml:space="preserve">0.325037926435471</t>
   </si>
   <si>
     <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823443889618</t>
+    <t xml:space="preserve">0.319823414087296</t>
   </si>
   <si>
     <t xml:space="preserve">0.318085253238678</t>
@@ -1421,31 +1421,31 @@
     <t xml:space="preserve">0.316347062587738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315903395414352</t>
+    <t xml:space="preserve">0.31590336561203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254936218262</t>
+    <t xml:space="preserve">0.305254966020584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301705479621887</t>
+    <t xml:space="preserve">0.30170550942421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804452419281</t>
+    <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606506824493</t>
+    <t xml:space="preserve">0.294606477022171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831808328629</t>
+    <t xml:space="preserve">0.292831838130951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480267524719</t>
+    <t xml:space="preserve">0.303480237722397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233953952789</t>
+    <t xml:space="preserve">0.319233924150467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31016480922699</t>
+    <t xml:space="preserve">0.310164839029312</t>
   </si>
   <si>
     <t xml:space="preserve">0.308351010084152</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">0.311978667974472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306537181138992</t>
+    <t xml:space="preserve">0.30653715133667</t>
   </si>
   <si>
     <t xml:space="preserve">0.292026519775391</t>
@@ -1463,25 +1463,25 @@
     <t xml:space="preserve">0.293840348720551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295654147863388</t>
+    <t xml:space="preserve">0.295654207468033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304723352193832</t>
+    <t xml:space="preserve">0.304723292589188</t>
   </si>
   <si>
     <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290212690830231</t>
+    <t xml:space="preserve">0.290212661027908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398861885071</t>
+    <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
     <t xml:space="preserve">0.284771203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585062742233</t>
+    <t xml:space="preserve">0.286585032939911</t>
   </si>
   <si>
     <t xml:space="preserve">0.29746800661087</t>
@@ -1490,19 +1490,19 @@
     <t xml:space="preserve">0.300716489553452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147657394409</t>
+    <t xml:space="preserve">0.295147627592087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308141559362411</t>
+    <t xml:space="preserve">0.308141529560089</t>
   </si>
   <si>
     <t xml:space="preserve">0.297003924846649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309997886419296</t>
+    <t xml:space="preserve">0.309997856616974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313710421323776</t>
+    <t xml:space="preserve">0.313710391521454</t>
   </si>
   <si>
     <t xml:space="preserve">0.317422956228256</t>
@@ -1514,61 +1514,61 @@
     <t xml:space="preserve">0.324848055839539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319279253482819</t>
+    <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334129452705383</t>
+    <t xml:space="preserve">0.334129422903061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337841987609863</t>
+    <t xml:space="preserve">0.337841957807541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339698284864426</t>
+    <t xml:space="preserve">0.339698255062103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326704323291779</t>
+    <t xml:space="preserve">0.326704293489456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330416887998581</t>
+    <t xml:space="preserve">0.330416858196259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330023497343063</t>
+    <t xml:space="preserve">0.330023527145386</t>
   </si>
   <si>
     <t xml:space="preserve">0.335713595151901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328126817941666</t>
+    <t xml:space="preserve">0.328126847743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610274553299</t>
+    <t xml:space="preserve">0.337610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331920206546783</t>
+    <t xml:space="preserve">0.331920236349106</t>
   </si>
   <si>
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746741533279</t>
+    <t xml:space="preserve">0.316746711730957</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341403663158417</t>
+    <t xml:space="preserve">0.341403633356094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32243674993515</t>
+    <t xml:space="preserve">0.322436779737473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32433345913887</t>
+    <t xml:space="preserve">0.324333488941193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347093731164932</t>
+    <t xml:space="preserve">0.34709370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339506983757019</t>
+    <t xml:space="preserve">0.339506953954697</t>
   </si>
   <si>
     <t xml:space="preserve">0.312953352928162</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360370516777039</t>
+    <t xml:space="preserve">0.360370486974716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887060165405</t>
+    <t xml:space="preserve">0.350887089967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354680478572845</t>
+    <t xml:space="preserve">0.354680448770523</t>
   </si>
   <si>
     <t xml:space="preserve">0.377440690994263</t>
@@ -1595,34 +1595,34 @@
     <t xml:space="preserve">0.405891001224518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426754534244537</t>
+    <t xml:space="preserve">0.42675456404686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415374428033829</t>
+    <t xml:space="preserve">0.415374457836151</t>
   </si>
   <si>
     <t xml:space="preserve">0.424857884645462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417271107435226</t>
+    <t xml:space="preserve">0.417271137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787680625916</t>
+    <t xml:space="preserve">0.407787710428238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398304253816605</t>
+    <t xml:space="preserve">0.398304224014282</t>
   </si>
   <si>
     <t xml:space="preserve">0.400200933218002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396407574415207</t>
+    <t xml:space="preserve">0.396407604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381234049797058</t>
+    <t xml:space="preserve">0.38123407959938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383130788803101</t>
+    <t xml:space="preserve">0.383130759000778</t>
   </si>
   <si>
     <t xml:space="preserve">0.37933737039566</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544041395187</t>
+    <t xml:space="preserve">0.375544011592865</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402097642421722</t>
+    <t xml:space="preserve">0.4020976126194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026515722275</t>
+    <t xml:space="preserve">0.415026545524597</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514053344727</t>
+    <t xml:space="preserve">0.401514023542404</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -1698,6 +1698,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.421999990940094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418000012636185</t>
   </si>
 </sst>
 </file>
@@ -66930,6 +66933,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.2916666667</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>561</v>
+      </c>
+      <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6643287037</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>562</v>
+      </c>
+      <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -44,49 +44,49 @@
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179818704724312</t>
+    <t xml:space="preserve">0.179818689823151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979167222977</t>
+    <t xml:space="preserve">0.175979152321815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174699306488037</t>
+    <t xml:space="preserve">0.174699336290359</t>
   </si>
   <si>
     <t xml:space="preserve">0.167020246386528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17277954518795</t>
+    <t xml:space="preserve">0.172779530286789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151662051677704</t>
+    <t xml:space="preserve">0.151662036776543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902723073959</t>
+    <t xml:space="preserve">0.145902752876282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493953704834</t>
+    <t xml:space="preserve">0.152493968605995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822499275208</t>
+    <t xml:space="preserve">0.147822514176369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1555016040802</t>
+    <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15614153444767</t>
+    <t xml:space="preserve">0.156141504645348</t>
   </si>
   <si>
     <t xml:space="preserve">0.153517827391624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102345108986</t>
+    <t xml:space="preserve">0.149102330207825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142383113503456</t>
+    <t xml:space="preserve">0.142383143305779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063170671463</t>
+    <t xml:space="preserve">0.142063185572624</t>
   </si>
   <si>
     <t xml:space="preserve">0.142447143793106</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.144622877240181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141423270106316</t>
+    <t xml:space="preserve">0.141423255205154</t>
   </si>
   <si>
     <t xml:space="preserve">0.15383780002594</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">0.16983588039875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380301117897</t>
+    <t xml:space="preserve">0.166380271315575</t>
   </si>
   <si>
     <t xml:space="preserve">0.159981071949005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421365380287</t>
+    <t xml:space="preserve">0.157421380281448</t>
   </si>
   <si>
     <t xml:space="preserve">0.152301952242851</t>
@@ -122,28 +122,28 @@
     <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163820579648018</t>
+    <t xml:space="preserve">0.16382060945034</t>
   </si>
   <si>
     <t xml:space="preserve">0.161836832761765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522605776787</t>
+    <t xml:space="preserve">0.18052265048027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180458664894104</t>
+    <t xml:space="preserve">0.180458649992943</t>
   </si>
   <si>
     <t xml:space="preserve">0.174059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168939977884293</t>
+    <t xml:space="preserve">0.168940007686615</t>
   </si>
   <si>
     <t xml:space="preserve">0.191977262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136742830276</t>
+    <t xml:space="preserve">0.196136757731438</t>
   </si>
   <si>
     <t xml:space="preserve">0.195176899433136</t>
@@ -152,67 +152,67 @@
     <t xml:space="preserve">0.187497809529305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938102960587</t>
+    <t xml:space="preserve">0.184938117861748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775735735893</t>
+    <t xml:space="preserve">0.204775765538216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454840540886</t>
+    <t xml:space="preserve">0.212454825639725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711750149727</t>
+    <t xml:space="preserve">0.204711765050888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20029628276825</t>
+    <t xml:space="preserve">0.200296267867088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736576199532</t>
+    <t xml:space="preserve">0.197736531496048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182378381490707</t>
+    <t xml:space="preserve">0.182378396391869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578018426895</t>
+    <t xml:space="preserve">0.185578033328056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907546162605</t>
+    <t xml:space="preserve">0.172907531261444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499699354172</t>
+    <t xml:space="preserve">0.171499669551849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16574040055275</t>
+    <t xml:space="preserve">0.165740370750427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349714517593</t>
+    <t xml:space="preserve">0.154349744319916</t>
   </si>
   <si>
     <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917056560516</t>
+    <t xml:space="preserve">0.159917086362839</t>
   </si>
   <si>
     <t xml:space="preserve">0.154861658811569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781435012817</t>
+    <t xml:space="preserve">0.156781420111656</t>
   </si>
   <si>
     <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18941755592823</t>
+    <t xml:space="preserve">0.189417570829391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191337361931801</t>
+    <t xml:space="preserve">0.191337332129478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857864260674</t>
+    <t xml:space="preserve">0.186857879161835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002103447914</t>
+    <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
     <t xml:space="preserve">0.170219838619232</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14718259871006</t>
+    <t xml:space="preserve">0.147182568907738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260917782784</t>
+    <t xml:space="preserve">0.161260932683945</t>
   </si>
   <si>
     <t xml:space="preserve">0.168172091245651</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">0.173739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339221954346</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897961258888</t>
+    <t xml:space="preserve">0.185897976160049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135835170746</t>
+    <t xml:space="preserve">0.204135820269585</t>
   </si>
   <si>
     <t xml:space="preserve">0.197096660733223</t>
@@ -257,46 +257,46 @@
     <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194216996431351</t>
+    <t xml:space="preserve">0.194217041134834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20464776456356</t>
+    <t xml:space="preserve">0.204647749662399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376506567001</t>
+    <t xml:space="preserve">0.198376521468163</t>
   </si>
   <si>
     <t xml:space="preserve">0.195240885019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495875000954</t>
+    <t xml:space="preserve">0.203495889902115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934323310852</t>
+    <t xml:space="preserve">0.216934308409691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709875226021</t>
+    <t xml:space="preserve">0.220709830522537</t>
   </si>
   <si>
     <t xml:space="preserve">0.236772000789642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531254887581</t>
+    <t xml:space="preserve">0.242531284689903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969673395157</t>
+    <t xml:space="preserve">0.255969703197479</t>
   </si>
   <si>
     <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286818742752</t>
+    <t xml:space="preserve">0.280286878347397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644998550415</t>
+    <t xml:space="preserve">0.295645028352737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303963989019394</t>
+    <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
     <t xml:space="preserve">0.262368947267532</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.254753798246384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25468984246254</t>
+    <t xml:space="preserve">0.254689812660217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202724218369</t>
+    <t xml:space="preserve">0.247202754020691</t>
   </si>
   <si>
     <t xml:space="preserve">0.247650653123856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778654098511</t>
+    <t xml:space="preserve">0.247778624296188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572319149971</t>
+    <t xml:space="preserve">0.233572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238051801919937</t>
+    <t xml:space="preserve">0.238051787018776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374646544456</t>
+    <t xml:space="preserve">0.214374616742134</t>
   </si>
   <si>
     <t xml:space="preserve">0.210663050413132</t>
@@ -338,43 +338,43 @@
     <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891354322433</t>
+    <t xml:space="preserve">0.241891369223595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570414423943</t>
+    <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980151057243</t>
+    <t xml:space="preserve">0.234980180859566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652557849884</t>
+    <t xml:space="preserve">0.231652587652206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971593022346</t>
+    <t xml:space="preserve">0.239971563220024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372726917267</t>
+    <t xml:space="preserve">0.230372712016106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22717310488224</t>
+    <t xml:space="preserve">0.227173089981079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773845911026</t>
+    <t xml:space="preserve">0.220773860812187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405203342438</t>
+    <t xml:space="preserve">0.226405188441277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998338699341</t>
+    <t xml:space="preserve">0.21699832379818</t>
   </si>
   <si>
     <t xml:space="preserve">0.204839736223221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20797535777092</t>
+    <t xml:space="preserve">0.207975387573242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535034537315</t>
+    <t xml:space="preserve">0.210535064339638</t>
   </si>
   <si>
     <t xml:space="preserve">0.20989516377449</t>
@@ -383,49 +383,49 @@
     <t xml:space="preserve">0.211175009608269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582796812057</t>
+    <t xml:space="preserve">0.212582871317863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782448649406</t>
+    <t xml:space="preserve">0.215782478451729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732796549797</t>
+    <t xml:space="preserve">0.229732811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22384549677372</t>
+    <t xml:space="preserve">0.223845511674881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805414676666</t>
+    <t xml:space="preserve">0.224805369973183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636304736137</t>
+    <t xml:space="preserve">0.233636364340782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627761602402</t>
+    <t xml:space="preserve">0.238627776503563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580936789513</t>
+    <t xml:space="preserve">0.228580921888351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973527550697</t>
+    <t xml:space="preserve">0.223973512649536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717510700226</t>
+    <t xml:space="preserve">0.223717495799065</t>
   </si>
   <si>
     <t xml:space="preserve">0.220837846398354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492140054703</t>
+    <t xml:space="preserve">0.235492080450058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965817570686</t>
+    <t xml:space="preserve">0.220965832471848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365091443062</t>
+    <t xml:space="preserve">0.227365076541901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556186914444</t>
+    <t xml:space="preserve">0.302556157112122</t>
   </si>
   <si>
     <t xml:space="preserve">0.358357578516006</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48570254445076</t>
+    <t xml:space="preserve">0.485702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444747388362885</t>
+    <t xml:space="preserve">0.44474732875824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709136486053</t>
+    <t xml:space="preserve">0.429709166288376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152287006378</t>
+    <t xml:space="preserve">0.403152257204056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37115603685379</t>
+    <t xml:space="preserve">0.371156066656113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710014343262</t>
+    <t xml:space="preserve">0.421710103750229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035716056824</t>
+    <t xml:space="preserve">0.374035745859146</t>
   </si>
   <si>
     <t xml:space="preserve">0.380754947662354</t>
@@ -464,46 +464,46 @@
     <t xml:space="preserve">0.352598249912262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331800669431686</t>
+    <t xml:space="preserve">0.331800729036331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602059364319</t>
+    <t xml:space="preserve">0.320602029561996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33244064450264</t>
+    <t xml:space="preserve">0.332440614700317</t>
   </si>
   <si>
     <t xml:space="preserve">0.340439677238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641159296036</t>
+    <t xml:space="preserve">0.327641218900681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157971382141</t>
+    <t xml:space="preserve">0.355157911777496</t>
   </si>
   <si>
     <t xml:space="preserve">0.347478866577148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760602235794</t>
+    <t xml:space="preserve">0.332760542631149</t>
   </si>
   <si>
     <t xml:space="preserve">0.324121624231339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32700127363205</t>
+    <t xml:space="preserve">0.327001303434372</t>
   </si>
   <si>
     <t xml:space="preserve">0.339159816503525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960179567337</t>
+    <t xml:space="preserve">0.335960149765015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161721229553</t>
+    <t xml:space="preserve">0.323161751031876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200880765915</t>
+    <t xml:space="preserve">0.330200910568237</t>
   </si>
   <si>
     <t xml:space="preserve">0.31996214389801</t>
@@ -512,19 +512,19 @@
     <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759664773941</t>
+    <t xml:space="preserve">0.340759694576263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801636695862</t>
+    <t xml:space="preserve">0.323801606893539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521835565567</t>
+    <t xml:space="preserve">0.322521865367889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360390901566</t>
+    <t xml:space="preserve">0.334360361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328921020030975</t>
+    <t xml:space="preserve">0.328921049833298</t>
   </si>
   <si>
     <t xml:space="preserve">0.334040492773056</t>
@@ -536,22 +536,22 @@
     <t xml:space="preserve">0.316122561693192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698521375656</t>
+    <t xml:space="preserve">0.316698431968689</t>
   </si>
   <si>
     <t xml:space="preserve">0.326361328363419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331480801105499</t>
+    <t xml:space="preserve">0.331480741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364756762981415</t>
+    <t xml:space="preserve">0.364756792783737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3455590903759</t>
+    <t xml:space="preserve">0.345559060573578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199005842209</t>
+    <t xml:space="preserve">0.346199035644531</t>
   </si>
   <si>
     <t xml:space="preserve">0.325081557035446</t>
@@ -566,43 +566,43 @@
     <t xml:space="preserve">0.333720475435257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753013134003</t>
+    <t xml:space="preserve">0.396753042936325</t>
   </si>
   <si>
     <t xml:space="preserve">0.376275449991226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635594129562</t>
+    <t xml:space="preserve">0.375635534524918</t>
   </si>
   <si>
     <t xml:space="preserve">0.376915395259857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196163654327</t>
+    <t xml:space="preserve">0.37019619345665</t>
   </si>
   <si>
     <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318389177322</t>
+    <t xml:space="preserve">0.351318418979645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117874383926</t>
+    <t xml:space="preserve">0.356117844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917329788208</t>
+    <t xml:space="preserve">0.360917299985886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715728521347</t>
+    <t xml:space="preserve">0.373715758323669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39579313993454</t>
+    <t xml:space="preserve">0.395793169736862</t>
   </si>
   <si>
     <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594470262527</t>
+    <t xml:space="preserve">0.38459450006485</t>
   </si>
   <si>
     <t xml:space="preserve">0.383954524993896</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">0.394193321466446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274452924728</t>
+    <t xml:space="preserve">0.384274482727051</t>
   </si>
   <si>
     <t xml:space="preserve">0.415310829877853</t>
@@ -620,280 +620,280 @@
     <t xml:space="preserve">0.422350019216537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312734603882</t>
+    <t xml:space="preserve">0.399312674999237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634597063065</t>
+    <t xml:space="preserve">0.383634626865387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553376197815</t>
+    <t xml:space="preserve">0.393553406000137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943186044693</t>
+    <t xml:space="preserve">0.479943126440048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447307020425797</t>
+    <t xml:space="preserve">0.447306960821152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745453834534</t>
+    <t xml:space="preserve">0.460745424032211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547691822052</t>
+    <t xml:space="preserve">0.441547721624374</t>
   </si>
   <si>
     <t xml:space="preserve">0.446027219295502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346209764481</t>
+    <t xml:space="preserve">0.454346179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447947055101395</t>
+    <t xml:space="preserve">0.447947025299072</t>
   </si>
   <si>
     <t xml:space="preserve">0.430029034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43258872628212</t>
+    <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749293088913</t>
+    <t xml:space="preserve">0.428749233484268</t>
   </si>
   <si>
     <t xml:space="preserve">0.417230635881424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391083478928</t>
+    <t xml:space="preserve">0.413391023874283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41595071554184</t>
+    <t xml:space="preserve">0.415950775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070069074631</t>
+    <t xml:space="preserve">0.421070128679276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551471471786</t>
+    <t xml:space="preserve">0.409551531076431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267890691757</t>
+    <t xml:space="preserve">0.440267860889435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909681081772</t>
+    <t xml:space="preserve">0.424909651279449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984280109406</t>
+    <t xml:space="preserve">0.470984160900116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148417949677</t>
+    <t xml:space="preserve">0.435148537158966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406991750001907</t>
+    <t xml:space="preserve">0.40699177980423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189482212067</t>
+    <t xml:space="preserve">0.426189541816711</t>
   </si>
   <si>
     <t xml:space="preserve">0.43130898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510526418686</t>
+    <t xml:space="preserve">0.418510377407074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405711978673935</t>
+    <t xml:space="preserve">0.405711948871613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111192941666</t>
+    <t xml:space="preserve">0.41211125254631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073938131332</t>
+    <t xml:space="preserve">0.38907390832901</t>
   </si>
   <si>
     <t xml:space="preserve">0.390353798866272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473152399063</t>
+    <t xml:space="preserve">0.395473062992096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831362009048</t>
+    <t xml:space="preserve">0.410831332206726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988029956818</t>
+    <t xml:space="preserve">0.438988119363785</t>
   </si>
   <si>
     <t xml:space="preserve">0.427469372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670914411545</t>
+    <t xml:space="preserve">0.414670884609222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872366666794</t>
+    <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
     <t xml:space="preserve">0.419790327548981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271670341492</t>
+    <t xml:space="preserve">0.408271640539169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629850149155</t>
+    <t xml:space="preserve">0.423629820346832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596315383911</t>
+    <t xml:space="preserve">0.368596345186234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435927391052</t>
+    <t xml:space="preserve">0.37243589758873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876205921173</t>
+    <t xml:space="preserve">0.369876235723495</t>
   </si>
   <si>
     <t xml:space="preserve">0.34683895111084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335320264101028</t>
+    <t xml:space="preserve">0.335320293903351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366036683320999</t>
+    <t xml:space="preserve">0.366036713123322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36347696185112</t>
+    <t xml:space="preserve">0.363476991653442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678443908691</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999398708344</t>
+    <t xml:space="preserve">0.342999339103699</t>
   </si>
   <si>
     <t xml:space="preserve">0.344279259443283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958334445953</t>
+    <t xml:space="preserve">0.351958304643631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835111856461</t>
+    <t xml:space="preserve">0.378835141658783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913460731506</t>
+    <t xml:space="preserve">0.392913550138474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359637409448624</t>
+    <t xml:space="preserve">0.359637379646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316514253616</t>
+    <t xml:space="preserve">0.367316544055939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234445333481</t>
+    <t xml:space="preserve">0.385234385728836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382674723863602</t>
+    <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380115002393723</t>
+    <t xml:space="preserve">0.3801149725914</t>
   </si>
   <si>
     <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39803284406662</t>
+    <t xml:space="preserve">0.398032873868942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592565536499</t>
+    <t xml:space="preserve">0.400592535734177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948900222778</t>
+    <t xml:space="preserve">0.431948870420456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348114490509</t>
+    <t xml:space="preserve">0.438348144292831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545846700668</t>
+    <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945150375366</t>
+    <t xml:space="preserve">0.463945001363754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350835800171</t>
+    <t xml:space="preserve">0.472350865602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200813055038</t>
+    <t xml:space="preserve">0.451200753450394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100797891617</t>
+    <t xml:space="preserve">0.437100738286972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000782728195</t>
+    <t xml:space="preserve">0.423000812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575749397278</t>
+    <t xml:space="preserve">0.433575809001923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150805473328</t>
+    <t xml:space="preserve">0.44415083527565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675794363022</t>
+    <t xml:space="preserve">0.447675764560699</t>
   </si>
   <si>
     <t xml:space="preserve">0.440625786781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525741815567</t>
+    <t xml:space="preserve">0.426525831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900737762451</t>
+    <t xml:space="preserve">0.408900678157806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475764036179</t>
+    <t xml:space="preserve">0.419475823640823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39480072259903</t>
+    <t xml:space="preserve">0.394800662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325711488724</t>
+    <t xml:space="preserve">0.398325741291046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425726652145</t>
+    <t xml:space="preserve">0.412425696849823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050820112228</t>
+    <t xml:space="preserve">0.430050790309906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45472577214241</t>
+    <t xml:space="preserve">0.454725831747055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800874233246</t>
+    <t xml:space="preserve">0.535800993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250790834427</t>
+    <t xml:space="preserve">0.458250731229782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300768613815</t>
+    <t xml:space="preserve">0.465300917625427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775809526443</t>
+    <t xml:space="preserve">0.461775839328766</t>
   </si>
   <si>
     <t xml:space="preserve">0.405375719070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850670576096</t>
+    <t xml:space="preserve">0.40185073018074</t>
   </si>
   <si>
     <t xml:space="preserve">0.387750715017319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700677633286</t>
+    <t xml:space="preserve">0.38070073723793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366600632667542</t>
+    <t xml:space="preserve">0.366600662469864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175718545914</t>
+    <t xml:space="preserve">0.377175778150558</t>
   </si>
   <si>
     <t xml:space="preserve">0.391275703907013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650640249252</t>
+    <t xml:space="preserve">0.37365061044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.346860647201538</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">0.345450609922409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550625085831</t>
+    <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35250061750412</t>
+    <t xml:space="preserve">0.352500647306442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400572538376</t>
+    <t xml:space="preserve">0.338400632143021</t>
   </si>
   <si>
     <t xml:space="preserve">0.317250549793243</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">0.296100497245789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263670474290848</t>
+    <t xml:space="preserve">0.26367050409317</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900437116623</t>
+    <t xml:space="preserve">0.267900496721268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770519256592</t>
+    <t xml:space="preserve">0.277770489454269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490489244461</t>
+    <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800421953201</t>
+    <t xml:space="preserve">0.253800481557846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248160392045975</t>
+    <t xml:space="preserve">0.248160436749458</t>
   </si>
   <si>
     <t xml:space="preserve">0.290460526943207</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">0.291870534420013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360511779785</t>
+    <t xml:space="preserve">0.276360481977463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820526838303</t>
+    <t xml:space="preserve">0.28482049703598</t>
   </si>
   <si>
     <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330549478531</t>
+    <t xml:space="preserve">0.300330579280853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790564537048</t>
+    <t xml:space="preserve">0.308790534734726</t>
   </si>
   <si>
     <t xml:space="preserve">0.314430594444275</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350564956665</t>
+    <t xml:space="preserve">0.331350594758987</t>
   </si>
   <si>
     <t xml:space="preserve">0.325710624456406</t>
@@ -977,43 +977,43 @@
     <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370125651359558</t>
+    <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384225696325302</t>
+    <t xml:space="preserve">0.384225726127625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170609712601</t>
+    <t xml:space="preserve">0.334170579910278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990594863892</t>
+    <t xml:space="preserve">0.336990624666214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630654573441</t>
+    <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025665998459</t>
+    <t xml:space="preserve">0.356025636196136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090639829636</t>
+    <t xml:space="preserve">0.351090610027313</t>
   </si>
   <si>
     <t xml:space="preserve">0.328530579805374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940587282181</t>
+    <t xml:space="preserve">0.329940617084503</t>
   </si>
   <si>
     <t xml:space="preserve">0.327120542526245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300616979599</t>
+    <t xml:space="preserve">0.324300557374954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610549688339</t>
+    <t xml:space="preserve">0.311610579490662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32289057970047</t>
+    <t xml:space="preserve">0.322890549898148</t>
   </si>
   <si>
     <t xml:space="preserve">0.310200572013855</t>
@@ -1022,55 +1022,55 @@
     <t xml:space="preserve">0.303150504827499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289050459861755</t>
+    <t xml:space="preserve">0.2890505194664</t>
   </si>
   <si>
     <t xml:space="preserve">0.293280512094498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310504198074</t>
+    <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
     <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26508042216301</t>
+    <t xml:space="preserve">0.265080451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720452070236</t>
+    <t xml:space="preserve">0.270720511674881</t>
   </si>
   <si>
     <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000482082367</t>
+    <t xml:space="preserve">0.282000511884689</t>
   </si>
   <si>
     <t xml:space="preserve">0.297510534524918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30174058675766</t>
+    <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
     <t xml:space="preserve">0.294690549373627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437586933374405</t>
+    <t xml:space="preserve">0.437586963176727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879097223282</t>
+    <t xml:space="preserve">0.406879037618637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363688468933</t>
+    <t xml:space="preserve">0.395363628864288</t>
   </si>
   <si>
     <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368494272232056</t>
+    <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171261072159</t>
+    <t xml:space="preserve">0.376171231269836</t>
   </si>
   <si>
     <t xml:space="preserve">0.37002968788147</t>
@@ -1079,61 +1079,61 @@
     <t xml:space="preserve">0.387686729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777448415756</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
     <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211125850677</t>
+    <t xml:space="preserve">0.356211096048355</t>
   </si>
   <si>
     <t xml:space="preserve">0.350069552659988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534226417542</t>
+    <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
     <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281927347183</t>
+    <t xml:space="preserve">0.359281957149506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140413761139</t>
+    <t xml:space="preserve">0.353140354156494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746541500092</t>
+    <t xml:space="preserve">0.357746511697769</t>
   </si>
   <si>
     <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857177972794</t>
+    <t xml:space="preserve">0.340857207775116</t>
   </si>
   <si>
     <t xml:space="preserve">0.354675799608231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44526395201683</t>
+    <t xml:space="preserve">0.445263922214508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394565582275</t>
+    <t xml:space="preserve">0.41839462518692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617899894714</t>
+    <t xml:space="preserve">0.460617929697037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940881252289</t>
+    <t xml:space="preserve">0.452940911054611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102431535721</t>
+    <t xml:space="preserve">0.449102371931076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233074903488</t>
+    <t xml:space="preserve">0.422233045101166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717695951462</t>
   </si>
   <si>
     <t xml:space="preserve">0.399202138185501</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">0.39152517914772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040617704391</t>
+    <t xml:space="preserve">0.403040587902069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556086063385</t>
+    <t xml:space="preserve">0.414556115865707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379242032766342</t>
+    <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100519180298</t>
+    <t xml:space="preserve">0.373100489377975</t>
   </si>
   <si>
     <t xml:space="preserve">0.360817313194275</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">0.346998780965805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706676721573</t>
+    <t xml:space="preserve">0.37770664691925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958886384964</t>
+    <t xml:space="preserve">0.366958916187286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37463590502739</t>
+    <t xml:space="preserve">0.374635875225067</t>
   </si>
   <si>
     <t xml:space="preserve">0.365423530340195</t>
@@ -1178,55 +1178,55 @@
     <t xml:space="preserve">0.322432488203049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305543154478073</t>
+    <t xml:space="preserve">0.305543184280396</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078570127487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323967903852463</t>
+    <t xml:space="preserve">0.323967844247818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503259897232</t>
+    <t xml:space="preserve">0.325503289699554</t>
   </si>
   <si>
     <t xml:space="preserve">0.330109447240829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180278539658</t>
+    <t xml:space="preserve">0.333180248737335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251050233841</t>
+    <t xml:space="preserve">0.336251020431519</t>
   </si>
   <si>
     <t xml:space="preserve">0.337786465883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928009271622</t>
+    <t xml:space="preserve">0.343928039073944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715634584427</t>
+    <t xml:space="preserve">0.334715664386749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314755499362946</t>
+    <t xml:space="preserve">0.31475555896759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220173120499</t>
+    <t xml:space="preserve">0.313220143318176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308613985776901</t>
+    <t xml:space="preserve">0.308613955974579</t>
   </si>
   <si>
     <t xml:space="preserve">0.319361716508865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328574120998383</t>
+    <t xml:space="preserve">0.32857409119606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345869779587</t>
+    <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328171908855438</t>
+    <t xml:space="preserve">0.328171879053116</t>
   </si>
   <si>
     <t xml:space="preserve">0.320128440856934</t>
@@ -1238,34 +1238,34 @@
     <t xml:space="preserve">0.337823987007141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432686567307</t>
+    <t xml:space="preserve">0.339432716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326563209295273</t>
+    <t xml:space="preserve">0.32656317949295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329780548810959</t>
+    <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
     <t xml:space="preserve">0.318519800901413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308867633342743</t>
+    <t xml:space="preserve">0.308867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606915235519</t>
+    <t xml:space="preserve">0.297606855630875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307258993387222</t>
+    <t xml:space="preserve">0.3072589635849</t>
   </si>
   <si>
     <t xml:space="preserve">0.321737140417099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650264024734</t>
+    <t xml:space="preserve">0.305650293827057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041624069214</t>
+    <t xml:space="preserve">0.304041564464569</t>
   </si>
   <si>
     <t xml:space="preserve">0.295998156070709</t>
@@ -1277,16 +1277,16 @@
     <t xml:space="preserve">0.292780786752701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737348556519</t>
+    <t xml:space="preserve">0.284737378358841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281520038843155</t>
+    <t xml:space="preserve">0.281519949436188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128648996353</t>
+    <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085270404816</t>
+    <t xml:space="preserve">0.275085240602493</t>
   </si>
   <si>
     <t xml:space="preserve">0.286346077919006</t>
@@ -1295,28 +1295,28 @@
     <t xml:space="preserve">0.276693969964981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563417434692</t>
+    <t xml:space="preserve">0.289563447237015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
     <t xml:space="preserve">0.300824224948883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432894706726</t>
+    <t xml:space="preserve">0.302432924509048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693732023239</t>
+    <t xml:space="preserve">0.313693702220917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294389486312866</t>
+    <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302193641663</t>
+    <t xml:space="preserve">0.35230216383934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258785247803</t>
+    <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
     <t xml:space="preserve">0.345867425203323</t>
@@ -1325,22 +1325,22 @@
     <t xml:space="preserve">0.347476154565811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34104135632515</t>
+    <t xml:space="preserve">0.341041386127472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650085687637</t>
+    <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
     <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300703555345535</t>
+    <t xml:space="preserve">0.300703525543213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2972272336483</t>
+    <t xml:space="preserve">0.297227174043655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29548904299736</t>
+    <t xml:space="preserve">0.295489013195038</t>
   </si>
   <si>
     <t xml:space="preserve">0.290274500846863</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305918037891388</t>
+    <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304179906845093</t>
+    <t xml:space="preserve">0.304179847240448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536310195923</t>
+    <t xml:space="preserve">0.288536339998245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283321887254715</t>
+    <t xml:space="preserve">0.283321797847748</t>
   </si>
   <si>
     <t xml:space="preserve">0.29375085234642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28506001830101</t>
+    <t xml:space="preserve">0.285059988498688</t>
   </si>
   <si>
     <t xml:space="preserve">0.278107315301895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281583666801453</t>
+    <t xml:space="preserve">0.28158363699913</t>
   </si>
   <si>
     <t xml:space="preserve">0.27463099360466</t>
@@ -1385,25 +1385,25 @@
     <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27289280295372</t>
+    <t xml:space="preserve">0.272892832756042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394389390945</t>
+    <t xml:space="preserve">0.309394419193268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965364694595</t>
+    <t xml:space="preserve">0.298965394496918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656198740005</t>
+    <t xml:space="preserve">0.307656228542328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132580041885</t>
+    <t xml:space="preserve">0.311132609844208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870740890503</t>
+    <t xml:space="preserve">0.312870770692825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252408981323</t>
+    <t xml:space="preserve">0.330252438783646</t>
   </si>
   <si>
     <t xml:space="preserve">0.325037926435471</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">0.319823414087296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085253238678</t>
+    <t xml:space="preserve">0.318085223436356</t>
   </si>
   <si>
     <t xml:space="preserve">0.316347062587738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31590336561203</t>
+    <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254966020584</t>
+    <t xml:space="preserve">0.305254995822906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30170550942421</t>
+    <t xml:space="preserve">0.301705479621887</t>
   </si>
   <si>
     <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606477022171</t>
+    <t xml:space="preserve">0.294606506824493</t>
   </si>
   <si>
     <t xml:space="preserve">0.292831838130951</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">0.319233924150467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310164839029312</t>
+    <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308351010084152</t>
+    <t xml:space="preserve">0.30835098028183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311978667974472</t>
+    <t xml:space="preserve">0.31197863817215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30653715133667</t>
+    <t xml:space="preserve">0.306537181138992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026519775391</t>
+    <t xml:space="preserve">0.292026489973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293840348720551</t>
+    <t xml:space="preserve">0.293840378522873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295654207468033</t>
+    <t xml:space="preserve">0.29565417766571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304723292589188</t>
+    <t xml:space="preserve">0.304723352193832</t>
   </si>
   <si>
     <t xml:space="preserve">0.29928183555603</t>
@@ -1475,34 +1475,34 @@
     <t xml:space="preserve">0.290212661027908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398832082748</t>
+    <t xml:space="preserve">0.288398861885071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771203994751</t>
+    <t xml:space="preserve">0.284771233797073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585032939911</t>
+    <t xml:space="preserve">0.286585062742233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29746800661087</t>
+    <t xml:space="preserve">0.297468036413193</t>
   </si>
   <si>
     <t xml:space="preserve">0.300716489553452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147627592087</t>
+    <t xml:space="preserve">0.295147657394409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308141529560089</t>
+    <t xml:space="preserve">0.308141559362411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297003924846649</t>
+    <t xml:space="preserve">0.297003895044327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309997856616974</t>
+    <t xml:space="preserve">0.309997886419296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313710391521454</t>
+    <t xml:space="preserve">0.313710421323776</t>
   </si>
   <si>
     <t xml:space="preserve">0.317422956228256</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">0.322991758584976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324848055839539</t>
+    <t xml:space="preserve">0.324848026037216</t>
   </si>
   <si>
     <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334129422903061</t>
+    <t xml:space="preserve">0.334129452705383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337841957807541</t>
+    <t xml:space="preserve">0.337841987609863</t>
   </si>
   <si>
     <t xml:space="preserve">0.339698255062103</t>
@@ -1529,46 +1529,46 @@
     <t xml:space="preserve">0.326704293489456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330416858196259</t>
+    <t xml:space="preserve">0.330416887998581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330023527145386</t>
+    <t xml:space="preserve">0.330023497343063</t>
   </si>
   <si>
     <t xml:space="preserve">0.335713595151901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328126847743988</t>
+    <t xml:space="preserve">0.328126817941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610244750977</t>
+    <t xml:space="preserve">0.337610274553299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331920236349106</t>
+    <t xml:space="preserve">0.331920206546783</t>
   </si>
   <si>
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746711730957</t>
+    <t xml:space="preserve">0.316746741533279</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341403633356094</t>
+    <t xml:space="preserve">0.341403663158417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322436779737473</t>
+    <t xml:space="preserve">0.32243674993515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324333488941193</t>
+    <t xml:space="preserve">0.32433345913887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34709370136261</t>
+    <t xml:space="preserve">0.347093731164932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339506953954697</t>
+    <t xml:space="preserve">0.339506983757019</t>
   </si>
   <si>
     <t xml:space="preserve">0.312953352928162</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360370486974716</t>
+    <t xml:space="preserve">0.360370516777039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887089967728</t>
+    <t xml:space="preserve">0.350887060165405</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354680448770523</t>
+    <t xml:space="preserve">0.354680478572845</t>
   </si>
   <si>
     <t xml:space="preserve">0.377440690994263</t>
@@ -1595,34 +1595,34 @@
     <t xml:space="preserve">0.405891001224518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42675456404686</t>
+    <t xml:space="preserve">0.426754534244537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415374457836151</t>
+    <t xml:space="preserve">0.415374428033829</t>
   </si>
   <si>
     <t xml:space="preserve">0.424857884645462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417271137237549</t>
+    <t xml:space="preserve">0.417271107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787710428238</t>
+    <t xml:space="preserve">0.407787680625916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398304224014282</t>
+    <t xml:space="preserve">0.398304253816605</t>
   </si>
   <si>
     <t xml:space="preserve">0.400200933218002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396407604217529</t>
+    <t xml:space="preserve">0.396407574415207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38123407959938</t>
+    <t xml:space="preserve">0.381234049797058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383130759000778</t>
+    <t xml:space="preserve">0.383130788803101</t>
   </si>
   <si>
     <t xml:space="preserve">0.37933737039566</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544011592865</t>
+    <t xml:space="preserve">0.375544041395187</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4020976126194</t>
+    <t xml:space="preserve">0.402097642421722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026545524597</t>
+    <t xml:space="preserve">0.415026515722275</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514023542404</t>
+    <t xml:space="preserve">0.401514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -66961,7 +66961,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6643287037</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>4000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178774356842</t>
+    <t xml:space="preserve">0.179178789258003</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179818719625473</t>
+    <t xml:space="preserve">0.179818704724312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979182124138</t>
+    <t xml:space="preserve">0.175979167222977</t>
   </si>
   <si>
     <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020216584206</t>
+    <t xml:space="preserve">0.167020231485367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779574990273</t>
+    <t xml:space="preserve">0.172779589891434</t>
   </si>
   <si>
     <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902708172798</t>
+    <t xml:space="preserve">0.145902752876282</t>
   </si>
   <si>
     <t xml:space="preserve">0.152493938803673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822499275208</t>
+    <t xml:space="preserve">0.147822484374046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155501574277878</t>
+    <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141504645348</t>
+    <t xml:space="preserve">0.156141519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517827391624</t>
+    <t xml:space="preserve">0.153517812490463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102360010147</t>
+    <t xml:space="preserve">0.149102330207825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14238315820694</t>
+    <t xml:space="preserve">0.142383143305779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063185572624</t>
+    <t xml:space="preserve">0.142063170671463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447128891945</t>
+    <t xml:space="preserve">0.142447143793106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14462286233902</t>
+    <t xml:space="preserve">0.144622877240181</t>
   </si>
   <si>
     <t xml:space="preserve">0.141423270106316</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">0.173419460654259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169835865497589</t>
+    <t xml:space="preserve">0.169835895299911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380286216736</t>
+    <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981042146683</t>
+    <t xml:space="preserve">0.159981057047844</t>
   </si>
   <si>
     <t xml:space="preserve">0.157421350479126</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174059420824051</t>
+    <t xml:space="preserve">0.17405940592289</t>
   </si>
   <si>
     <t xml:space="preserve">0.168940007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977292299271</t>
+    <t xml:space="preserve">0.191977262496948</t>
   </si>
   <si>
     <t xml:space="preserve">0.196136802434921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176899433136</t>
+    <t xml:space="preserve">0.195176884531975</t>
   </si>
   <si>
     <t xml:space="preserve">0.187497794628143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938088059425</t>
+    <t xml:space="preserve">0.184938117861748</t>
   </si>
   <si>
     <t xml:space="preserve">0.204775750637054</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">0.212454840540886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711735248566</t>
+    <t xml:space="preserve">0.204711750149727</t>
   </si>
   <si>
     <t xml:space="preserve">0.20029628276825</t>
@@ -170,85 +170,85 @@
     <t xml:space="preserve">0.19773656129837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182378426194191</t>
+    <t xml:space="preserve">0.182378396391869</t>
   </si>
   <si>
     <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907516360283</t>
+    <t xml:space="preserve">0.172907531261444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499699354172</t>
+    <t xml:space="preserve">0.171499684453011</t>
   </si>
   <si>
     <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349729418755</t>
+    <t xml:space="preserve">0.154349714517593</t>
   </si>
   <si>
     <t xml:space="preserve">0.169579923152924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917071461678</t>
+    <t xml:space="preserve">0.159917056560516</t>
   </si>
   <si>
     <t xml:space="preserve">0.154861643910408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781449913979</t>
+    <t xml:space="preserve">0.156781435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16049300134182</t>
+    <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18941755592823</t>
+    <t xml:space="preserve">0.189417570829391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191337376832962</t>
+    <t xml:space="preserve">0.191337361931801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857849359512</t>
+    <t xml:space="preserve">0.186857879161835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002088546753</t>
+    <t xml:space="preserve">0.185002073645592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170219823718071</t>
+    <t xml:space="preserve">0.170219838619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.163180664181709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742290377617</t>
+    <t xml:space="preserve">0.149742260575294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221728444099</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022136211395</t>
+    <t xml:space="preserve">0.151022106409073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182568907738</t>
+    <t xml:space="preserve">0.147182583808899</t>
   </si>
   <si>
     <t xml:space="preserve">0.161260917782784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168172091245651</t>
+    <t xml:space="preserve">0.16817207634449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739403486252</t>
+    <t xml:space="preserve">0.173739418387413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339221954346</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897991061211</t>
+    <t xml:space="preserve">0.185897976160049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135864973068</t>
+    <t xml:space="preserve">0.204135805368423</t>
   </si>
   <si>
     <t xml:space="preserve">0.197096675634384</t>
@@ -257,124 +257,124 @@
     <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194216996431351</t>
+    <t xml:space="preserve">0.194217011332512</t>
   </si>
   <si>
     <t xml:space="preserve">0.204647749662399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19837649166584</t>
+    <t xml:space="preserve">0.198376506567001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240885019302</t>
+    <t xml:space="preserve">0.195240899920464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495919704437</t>
+    <t xml:space="preserve">0.203495904803276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934278607368</t>
+    <t xml:space="preserve">0.21693429350853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22070986032486</t>
+    <t xml:space="preserve">0.220709875226021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236772000789642</t>
+    <t xml:space="preserve">0.236771941184998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531269788742</t>
+    <t xml:space="preserve">0.242531284689903</t>
   </si>
   <si>
     <t xml:space="preserve">0.255969703197479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967798471451</t>
+    <t xml:space="preserve">0.271967738866806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28028678894043</t>
+    <t xml:space="preserve">0.280286848545074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644998550415</t>
+    <t xml:space="preserve">0.295644968748093</t>
   </si>
   <si>
     <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262368947267532</t>
+    <t xml:space="preserve">0.26236891746521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2648646235466</t>
+    <t xml:space="preserve">0.264864653348923</t>
   </si>
   <si>
     <t xml:space="preserve">0.254753828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254689872264862</t>
+    <t xml:space="preserve">0.25468984246254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202709317207</t>
+    <t xml:space="preserve">0.24720273911953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650653123856</t>
+    <t xml:space="preserve">0.247650682926178</t>
   </si>
   <si>
     <t xml:space="preserve">0.247778668999672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572363853455</t>
+    <t xml:space="preserve">0.233572319149971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23805183172226</t>
+    <t xml:space="preserve">0.238051816821098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374661445618</t>
+    <t xml:space="preserve">0.214374631643295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663005709648</t>
+    <t xml:space="preserve">0.210663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">0.215654492378235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518826127052</t>
+    <t xml:space="preserve">0.212518855929375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891339421272</t>
+    <t xml:space="preserve">0.241891354322433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570444226265</t>
+    <t xml:space="preserve">0.249570459127426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980180859566</t>
+    <t xml:space="preserve">0.234980195760727</t>
   </si>
   <si>
     <t xml:space="preserve">0.231652557849884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971578121185</t>
+    <t xml:space="preserve">0.239971593022346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372712016106</t>
+    <t xml:space="preserve">0.230372682213783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173075079918</t>
+    <t xml:space="preserve">0.227173119783401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773875713348</t>
+    <t xml:space="preserve">0.220773860812187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405218243599</t>
+    <t xml:space="preserve">0.226405188441277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21699832379818</t>
+    <t xml:space="preserve">0.216998279094696</t>
   </si>
   <si>
     <t xml:space="preserve">0.204839736223221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20797535777092</t>
+    <t xml:space="preserve">0.207975372672081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21053509414196</t>
+    <t xml:space="preserve">0.210535064339638</t>
   </si>
   <si>
     <t xml:space="preserve">0.209895133972168</t>
@@ -383,67 +383,67 @@
     <t xml:space="preserve">0.21117502450943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21258282661438</t>
+    <t xml:space="preserve">0.212582856416702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782448649406</t>
+    <t xml:space="preserve">0.215782478451729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732781648636</t>
+    <t xml:space="preserve">0.229732826352119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22384549677372</t>
+    <t xml:space="preserve">0.223845437169075</t>
   </si>
   <si>
     <t xml:space="preserve">0.224805384874344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636349439621</t>
+    <t xml:space="preserve">0.233636304736137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627761602402</t>
+    <t xml:space="preserve">0.238627746701241</t>
   </si>
   <si>
     <t xml:space="preserve">0.228580921888351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973453044891</t>
+    <t xml:space="preserve">0.223973527550697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717525601387</t>
+    <t xml:space="preserve">0.223717510700226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837861299515</t>
+    <t xml:space="preserve">0.220837846398354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23549211025238</t>
+    <t xml:space="preserve">0.235492125153542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965817570686</t>
+    <t xml:space="preserve">0.220965847373009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365121245384</t>
+    <t xml:space="preserve">0.227365061640739</t>
   </si>
   <si>
     <t xml:space="preserve">0.302556127309799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357548713684</t>
+    <t xml:space="preserve">0.358357578516006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473544001579285</t>
+    <t xml:space="preserve">0.473543882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454134941101</t>
+    <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48570254445076</t>
+    <t xml:space="preserve">0.485702455043793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444747269153595</t>
+    <t xml:space="preserve">0.44474732875824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709136486053</t>
+    <t xml:space="preserve">0.429709106683731</t>
   </si>
   <si>
     <t xml:space="preserve">0.403152257204056</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710103750229</t>
+    <t xml:space="preserve">0.421710073947906</t>
   </si>
   <si>
     <t xml:space="preserve">0.374035745859146</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">0.380754977464676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352598249912262</t>
+    <t xml:space="preserve">0.35259822010994</t>
   </si>
   <si>
     <t xml:space="preserve">0.331800699234009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602029561996</t>
+    <t xml:space="preserve">0.320602059364319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33244064450264</t>
+    <t xml:space="preserve">0.332440614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340439647436142</t>
+    <t xml:space="preserve">0.340439677238464</t>
   </si>
   <si>
     <t xml:space="preserve">0.327641218900681</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">0.355157971382141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478806972504</t>
+    <t xml:space="preserve">0.347478836774826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760572433472</t>
+    <t xml:space="preserve">0.332760602235794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121624231339</t>
+    <t xml:space="preserve">0.324121654033661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327001243829727</t>
+    <t xml:space="preserve">0.32700127363205</t>
   </si>
   <si>
     <t xml:space="preserve">0.339159846305847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960239171982</t>
+    <t xml:space="preserve">0.335960179567337</t>
   </si>
   <si>
     <t xml:space="preserve">0.323161721229553</t>
@@ -506,34 +506,34 @@
     <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319962084293365</t>
+    <t xml:space="preserve">0.319962114095688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402392625809</t>
+    <t xml:space="preserve">0.317402422428131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759724378586</t>
+    <t xml:space="preserve">0.340759694576263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801636695862</t>
+    <t xml:space="preserve">0.323801577091217</t>
   </si>
   <si>
     <t xml:space="preserve">0.322521835565567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360361099243</t>
+    <t xml:space="preserve">0.334360390901566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32892107963562</t>
+    <t xml:space="preserve">0.328921049833298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040433168411</t>
+    <t xml:space="preserve">0.334040462970734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163625955582</t>
+    <t xml:space="preserve">0.307163655757904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122561693192</t>
+    <t xml:space="preserve">0.316122621297836</t>
   </si>
   <si>
     <t xml:space="preserve">0.316698491573334</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364756852388382</t>
+    <t xml:space="preserve">0.364756792783737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559149980545</t>
+    <t xml:space="preserve">0.345559179782867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199065446854</t>
+    <t xml:space="preserve">0.346199035644531</t>
   </si>
   <si>
     <t xml:space="preserve">0.325081527233124</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">0.333720505237579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39675298333168</t>
+    <t xml:space="preserve">0.396753013134003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275449991226</t>
+    <t xml:space="preserve">0.376275420188904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635594129562</t>
+    <t xml:space="preserve">0.37563556432724</t>
   </si>
   <si>
     <t xml:space="preserve">0.376915365457535</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">0.370196133852005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555221319199</t>
+    <t xml:space="preserve">0.377555310726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318418979645</t>
+    <t xml:space="preserve">0.351318448781967</t>
   </si>
   <si>
     <t xml:space="preserve">0.356117844581604</t>
@@ -593,25 +593,25 @@
     <t xml:space="preserve">0.360917270183563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715698719025</t>
+    <t xml:space="preserve">0.373715758323669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793110132217</t>
+    <t xml:space="preserve">0.39579313993454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672878742218</t>
+    <t xml:space="preserve">0.398672848939896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594470262527</t>
+    <t xml:space="preserve">0.384594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954584598541</t>
+    <t xml:space="preserve">0.383954524993896</t>
   </si>
   <si>
     <t xml:space="preserve">0.394193351268768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274482727051</t>
+    <t xml:space="preserve">0.384274512529373</t>
   </si>
   <si>
     <t xml:space="preserve">0.415310800075531</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">0.383634626865387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39355343580246</t>
+    <t xml:space="preserve">0.393553406000137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943156242371</t>
+    <t xml:space="preserve">0.479943186044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.447307050228119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745424032211</t>
+    <t xml:space="preserve">0.460745364427567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547751426697</t>
+    <t xml:space="preserve">0.441547721624374</t>
   </si>
   <si>
     <t xml:space="preserve">0.446027249097824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346150159836</t>
+    <t xml:space="preserve">0.454346239566803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447946906089783</t>
+    <t xml:space="preserve">0.447947055101395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430029064416885</t>
+    <t xml:space="preserve">0.430029094219208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588815689087</t>
+    <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749322891235</t>
+    <t xml:space="preserve">0.428749263286591</t>
   </si>
   <si>
     <t xml:space="preserve">0.417230606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391083478928</t>
+    <t xml:space="preserve">0.413391053676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41595071554184</t>
+    <t xml:space="preserve">0.415950745344162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42107018828392</t>
+    <t xml:space="preserve">0.421070128679276</t>
   </si>
   <si>
     <t xml:space="preserve">0.409551501274109</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">0.424909681081772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984220504761</t>
+    <t xml:space="preserve">0.470984250307083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148447751999</t>
+    <t xml:space="preserve">0.435148477554321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406991839408875</t>
+    <t xml:space="preserve">0.406991809606552</t>
   </si>
   <si>
     <t xml:space="preserve">0.426189571619034</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">0.418510437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405711978673935</t>
+    <t xml:space="preserve">0.40571191906929</t>
   </si>
   <si>
     <t xml:space="preserve">0.412111163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073938131332</t>
+    <t xml:space="preserve">0.38907390832901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390353798866272</t>
+    <t xml:space="preserve">0.39035376906395</t>
   </si>
   <si>
     <t xml:space="preserve">0.395473122596741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831362009048</t>
+    <t xml:space="preserve">0.410831421613693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43898805975914</t>
+    <t xml:space="preserve">0.438988089561462</t>
   </si>
   <si>
     <t xml:space="preserve">0.427469402551651</t>
@@ -725,262 +725,262 @@
     <t xml:space="preserve">0.414670884609222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872396469116</t>
+    <t xml:space="preserve">0.401872456073761</t>
   </si>
   <si>
     <t xml:space="preserve">0.419790267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271729946136</t>
+    <t xml:space="preserve">0.408271610736847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629850149155</t>
+    <t xml:space="preserve">0.423629879951477</t>
   </si>
   <si>
     <t xml:space="preserve">0.368596345186234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435867786407</t>
+    <t xml:space="preserve">0.372435927391052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876176118851</t>
+    <t xml:space="preserve">0.369876235723495</t>
   </si>
   <si>
     <t xml:space="preserve">0.346838921308517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335320234298706</t>
+    <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366036713123322</t>
+    <t xml:space="preserve">0.366036653518677</t>
   </si>
   <si>
     <t xml:space="preserve">0.363477021455765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678443908691</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999398708344</t>
+    <t xml:space="preserve">0.342999368906021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279259443283</t>
+    <t xml:space="preserve">0.344279229640961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958364248276</t>
+    <t xml:space="preserve">0.351958334445953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835111856461</t>
+    <t xml:space="preserve">0.378835141658783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913460731506</t>
+    <t xml:space="preserve">0.392913490533829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359637439250946</t>
+    <t xml:space="preserve">0.359637409448624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316544055939</t>
+    <t xml:space="preserve">0.367316484451294</t>
   </si>
   <si>
     <t xml:space="preserve">0.385234385728836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382674753665924</t>
+    <t xml:space="preserve">0.382674723863602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380114942789078</t>
+    <t xml:space="preserve">0.3801149725914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633570194244</t>
+    <t xml:space="preserve">0.391633599996567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032814264297</t>
+    <t xml:space="preserve">0.398032873868942</t>
   </si>
   <si>
     <t xml:space="preserve">0.400592565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948810815811</t>
+    <t xml:space="preserve">0.431948840618134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348114490509</t>
+    <t xml:space="preserve">0.438348054885864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545816898346</t>
+    <t xml:space="preserve">0.457545787096024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945150375366</t>
+    <t xml:space="preserve">0.463945090770721</t>
   </si>
   <si>
     <t xml:space="preserve">0.472350865602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200783252716</t>
+    <t xml:space="preserve">0.451200872659683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100738286972</t>
+    <t xml:space="preserve">0.437100797891617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42300084233284</t>
+    <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575838804245</t>
+    <t xml:space="preserve">0.433575868606567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150865077972</t>
+    <t xml:space="preserve">0.444150745868683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675824165344</t>
+    <t xml:space="preserve">0.447675734758377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625846385956</t>
+    <t xml:space="preserve">0.440625816583633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525741815567</t>
+    <t xml:space="preserve">0.426525831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950655937195</t>
+    <t xml:space="preserve">0.408900648355484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900707960129</t>
+    <t xml:space="preserve">0.419475764036179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475793838501</t>
+    <t xml:space="preserve">0.394800752401352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39480072259903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398325741291046</t>
+    <t xml:space="preserve">0.398325681686401</t>
   </si>
   <si>
     <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050730705261</t>
+    <t xml:space="preserve">0.430050820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725861549377</t>
+    <t xml:space="preserve">0.454725831747055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53580105304718</t>
+    <t xml:space="preserve">0.535800933837891</t>
   </si>
   <si>
     <t xml:space="preserve">0.458250790834427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300917625427</t>
+    <t xml:space="preserve">0.46530082821846</t>
   </si>
   <si>
     <t xml:space="preserve">0.461775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375719070435</t>
+    <t xml:space="preserve">0.405375689268112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40185073018074</t>
+    <t xml:space="preserve">0.401850700378418</t>
   </si>
   <si>
     <t xml:space="preserve">0.387750715017319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700707435608</t>
+    <t xml:space="preserve">0.380700677633286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366600602865219</t>
+    <t xml:space="preserve">0.366600662469864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175748348236</t>
+    <t xml:space="preserve">0.377175718545914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275703907013</t>
+    <t xml:space="preserve">0.391275763511658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650640249252</t>
+    <t xml:space="preserve">0.373650670051575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860617399216</t>
+    <t xml:space="preserve">0.346860587596893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450609922409</t>
+    <t xml:space="preserve">0.345450639724731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550684690475</t>
+    <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
     <t xml:space="preserve">0.35250061750412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400602340698</t>
+    <t xml:space="preserve">0.338400632143021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250579595566</t>
+    <t xml:space="preserve">0.317250549793243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320070564746857</t>
+    <t xml:space="preserve">0.320070534944534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296100556850433</t>
+    <t xml:space="preserve">0.296100527048111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263670474290848</t>
+    <t xml:space="preserve">0.26367050409317</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26790052652359</t>
+    <t xml:space="preserve">0.267900466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770459651947</t>
+    <t xml:space="preserve">0.277770489454269</t>
   </si>
   <si>
     <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800421953201</t>
+    <t xml:space="preserve">0.249570488929749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248160496354103</t>
+    <t xml:space="preserve">0.253800481557846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460526943207</t>
+    <t xml:space="preserve">0.24816045165062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290460497140884</t>
   </si>
   <si>
     <t xml:space="preserve">0.291870534420013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360481977463</t>
+    <t xml:space="preserve">0.276360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820526838303</t>
+    <t xml:space="preserve">0.28482049703598</t>
   </si>
   <si>
     <t xml:space="preserve">0.286230534315109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330489873886</t>
+    <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790564537048</t>
+    <t xml:space="preserve">0.308790594339371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314430624246597</t>
+    <t xml:space="preserve">0.314430594444275</t>
   </si>
   <si>
     <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33135062456131</t>
+    <t xml:space="preserve">0.331350564956665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325710594654083</t>
+    <t xml:space="preserve">0.325710564851761</t>
   </si>
   <si>
     <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37012568116188</t>
+    <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
     <t xml:space="preserve">0.384225696325302</t>
@@ -989,28 +989,28 @@
     <t xml:space="preserve">0.334170639514923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990624666214</t>
+    <t xml:space="preserve">0.336990594863892</t>
   </si>
   <si>
     <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025636196136</t>
+    <t xml:space="preserve">0.356025665998459</t>
   </si>
   <si>
     <t xml:space="preserve">0.351090610027313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530550003052</t>
+    <t xml:space="preserve">0.328530609607697</t>
   </si>
   <si>
     <t xml:space="preserve">0.329940617084503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327120542526245</t>
+    <t xml:space="preserve">0.327120631933212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300587177277</t>
+    <t xml:space="preserve">0.324300616979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.311610549688339</t>
@@ -1019,148 +1019,148 @@
     <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310200542211533</t>
+    <t xml:space="preserve">0.31020051240921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150504827499</t>
+    <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2890505194664</t>
+    <t xml:space="preserve">0.289050489664078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293280571699142</t>
+    <t xml:space="preserve">0.29328054189682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310534000397</t>
+    <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
     <t xml:space="preserve">0.272130519151688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26508042216301</t>
+    <t xml:space="preserve">0.265080511569977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720511674881</t>
+    <t xml:space="preserve">0.270720541477203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950474500656</t>
+    <t xml:space="preserve">0.274950504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000511884689</t>
+    <t xml:space="preserve">0.282000541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297510534524918</t>
+    <t xml:space="preserve">0.297510594129562</t>
   </si>
   <si>
     <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690549373627</t>
+    <t xml:space="preserve">0.294690519571304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43758699297905</t>
+    <t xml:space="preserve">0.437586963176727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879156827927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363658666611</t>
+    <t xml:space="preserve">0.395363688468933</t>
   </si>
   <si>
     <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368494302034378</t>
+    <t xml:space="preserve">0.3684943318367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171261072159</t>
+    <t xml:space="preserve">0.376171290874481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370029658079147</t>
+    <t xml:space="preserve">0.370029717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387686729431152</t>
+    <t xml:space="preserve">0.387686759233475</t>
   </si>
   <si>
     <t xml:space="preserve">0.380777448415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565073728561</t>
+    <t xml:space="preserve">0.371565043926239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211125850677</t>
+    <t xml:space="preserve">0.356211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069552659988</t>
+    <t xml:space="preserve">0.350069582462311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534226417542</t>
+    <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463424921036</t>
+    <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
     <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140383958817</t>
+    <t xml:space="preserve">0.353140413761139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746541500092</t>
+    <t xml:space="preserve">0.357746571302414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342392683029175</t>
+    <t xml:space="preserve">0.34239262342453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857237577438</t>
+    <t xml:space="preserve">0.340857267379761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675829410553</t>
+    <t xml:space="preserve">0.354675740003586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263922214508</t>
+    <t xml:space="preserve">0.445263892412186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394535779953</t>
+    <t xml:space="preserve">0.418394595384598</t>
   </si>
   <si>
     <t xml:space="preserve">0.460617929697037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940821647644</t>
+    <t xml:space="preserve">0.452940911054611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102431535721</t>
+    <t xml:space="preserve">0.449102401733398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233104705811</t>
+    <t xml:space="preserve">0.422233074903488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717636346817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202138185501</t>
+    <t xml:space="preserve">0.399202167987823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391525208950043</t>
+    <t xml:space="preserve">0.39152517914772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040647506714</t>
+    <t xml:space="preserve">0.403040587902069</t>
   </si>
   <si>
     <t xml:space="preserve">0.414556115865707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37924200296402</t>
+    <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100489377975</t>
+    <t xml:space="preserve">0.373100519180298</t>
   </si>
   <si>
     <t xml:space="preserve">0.360817313194275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351604968309402</t>
+    <t xml:space="preserve">0.351604998111725</t>
   </si>
   <si>
     <t xml:space="preserve">0.346998810768127</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">0.37770664691925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958916187286</t>
+    <t xml:space="preserve">0.366958886384964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374635845422745</t>
+    <t xml:space="preserve">0.37463590502739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423560142517</t>
+    <t xml:space="preserve">0.365423500537872</t>
   </si>
   <si>
     <t xml:space="preserve">0.322432488203049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30554324388504</t>
+    <t xml:space="preserve">0.305543184280396</t>
   </si>
   <si>
     <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32396787405014</t>
+    <t xml:space="preserve">0.323967933654785</t>
   </si>
   <si>
     <t xml:space="preserve">0.325503289699554</t>
@@ -1199,40 +1199,40 @@
     <t xml:space="preserve">0.333180248737335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251020431519</t>
+    <t xml:space="preserve">0.336251080036163</t>
   </si>
   <si>
     <t xml:space="preserve">0.33778640627861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928039073944</t>
+    <t xml:space="preserve">0.343928068876266</t>
   </si>
   <si>
     <t xml:space="preserve">0.334715634584427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31475555896759</t>
+    <t xml:space="preserve">0.314755529165268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220173120499</t>
+    <t xml:space="preserve">0.313220143318176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308613985776901</t>
+    <t xml:space="preserve">0.308614015579224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319361746311188</t>
+    <t xml:space="preserve">0.31936177611351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328574120998383</t>
+    <t xml:space="preserve">0.32857409119606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345869779587</t>
+    <t xml:space="preserve">0.323345899581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.328171879053116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128500461578</t>
+    <t xml:space="preserve">0.320128470659256</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
@@ -1241,16 +1241,16 @@
     <t xml:space="preserve">0.337823987007141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432716369629</t>
+    <t xml:space="preserve">0.339432686567307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326563239097595</t>
+    <t xml:space="preserve">0.32656317949295</t>
   </si>
   <si>
     <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519771099091</t>
+    <t xml:space="preserve">0.318519800901413</t>
   </si>
   <si>
     <t xml:space="preserve">0.308867663145065</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">0.297606855630875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307259023189545</t>
+    <t xml:space="preserve">0.3072589635849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737170219421</t>
+    <t xml:space="preserve">0.321737140417099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650323629379</t>
+    <t xml:space="preserve">0.305650293827057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041594266891</t>
+    <t xml:space="preserve">0.304041564464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998185873032</t>
+    <t xml:space="preserve">0.295998156070709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287954747676849</t>
+    <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780786752701</t>
+    <t xml:space="preserve">0.292780846357346</t>
   </si>
   <si>
     <t xml:space="preserve">0.284737408161163</t>
@@ -1292,40 +1292,40 @@
     <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346048116684</t>
+    <t xml:space="preserve">0.286346077919006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693969964981</t>
+    <t xml:space="preserve">0.276693940162659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563447237015</t>
+    <t xml:space="preserve">0.289563417434692</t>
   </si>
   <si>
     <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824254751205</t>
+    <t xml:space="preserve">0.300824195146561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432894706726</t>
+    <t xml:space="preserve">0.302432864904404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693761825562</t>
+    <t xml:space="preserve">0.313693702220917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294389486312866</t>
+    <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302193641663</t>
+    <t xml:space="preserve">0.352302134037018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258785247803</t>
+    <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867484807968</t>
+    <t xml:space="preserve">0.345867455005646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347476184368134</t>
+    <t xml:space="preserve">0.347476154565811</t>
   </si>
   <si>
     <t xml:space="preserve">0.341041386127472</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">0.342650085687637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736991882324</t>
+    <t xml:space="preserve">0.358736902475357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300703525543213</t>
+    <t xml:space="preserve">0.300703495740891</t>
   </si>
   <si>
     <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295489072799683</t>
+    <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290274560451508</t>
+    <t xml:space="preserve">0.290274530649185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292012691497803</t>
+    <t xml:space="preserve">0.292012721300125</t>
   </si>
   <si>
     <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304179847240448</t>
+    <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
     <t xml:space="preserve">0.288536339998245</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">0.283321857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29375085234642</t>
+    <t xml:space="preserve">0.293750822544098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285060048103333</t>
+    <t xml:space="preserve">0.285059988498688</t>
   </si>
   <si>
     <t xml:space="preserve">0.278107315301895</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274630963802338</t>
+    <t xml:space="preserve">0.27463099360466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286798149347305</t>
+    <t xml:space="preserve">0.286798179149628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279845505952835</t>
+    <t xml:space="preserve">0.279845476150513</t>
   </si>
   <si>
     <t xml:space="preserve">0.276369154453278</t>
@@ -1391,31 +1391,31 @@
     <t xml:space="preserve">0.27289280295372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394359588623</t>
+    <t xml:space="preserve">0.309394419193268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965364694595</t>
+    <t xml:space="preserve">0.298965394496918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30765625834465</t>
+    <t xml:space="preserve">0.307656228542328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132580041885</t>
+    <t xml:space="preserve">0.311132609844208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870740890503</t>
+    <t xml:space="preserve">0.312870711088181</t>
   </si>
   <si>
     <t xml:space="preserve">0.330252468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037956237793</t>
+    <t xml:space="preserve">0.325037926435471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31460890173912</t>
+    <t xml:space="preserve">0.314608871936798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823414087296</t>
+    <t xml:space="preserve">0.319823443889618</t>
   </si>
   <si>
     <t xml:space="preserve">0.318085253238678</t>
@@ -1424,43 +1424,43 @@
     <t xml:space="preserve">0.316347062587738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31590336561203</t>
+    <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
     <t xml:space="preserve">0.305254966020584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301705479621887</t>
+    <t xml:space="preserve">0.30170550942421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804422616959</t>
+    <t xml:space="preserve">0.308804452419281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606536626816</t>
+    <t xml:space="preserve">0.294606506824493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831778526306</t>
+    <t xml:space="preserve">0.292831808328629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480207920074</t>
+    <t xml:space="preserve">0.303480237722397</t>
   </si>
   <si>
     <t xml:space="preserve">0.319233953952789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31016480922699</t>
+    <t xml:space="preserve">0.310164839029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30835098028183</t>
+    <t xml:space="preserve">0.308351010084152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31197863817215</t>
+    <t xml:space="preserve">0.311978667974472</t>
   </si>
   <si>
     <t xml:space="preserve">0.30653715133667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026519775391</t>
+    <t xml:space="preserve">0.292026489973068</t>
   </si>
   <si>
     <t xml:space="preserve">0.293840348720551</t>
@@ -1472,37 +1472,37 @@
     <t xml:space="preserve">0.30472332239151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299281805753708</t>
+    <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
     <t xml:space="preserve">0.290212690830231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398861885071</t>
+    <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771203994751</t>
+    <t xml:space="preserve">0.284771174192429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585032939911</t>
+    <t xml:space="preserve">0.286585062742233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297468036413193</t>
+    <t xml:space="preserve">0.297467976808548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300716459751129</t>
+    <t xml:space="preserve">0.300716489553452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147657394409</t>
+    <t xml:space="preserve">0.295147627592087</t>
   </si>
   <si>
     <t xml:space="preserve">0.308141559362411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297003924846649</t>
+    <t xml:space="preserve">0.297003954648972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309997886419296</t>
+    <t xml:space="preserve">0.309997856616974</t>
   </si>
   <si>
     <t xml:space="preserve">0.313710391521454</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">0.317422956228256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322991788387299</t>
+    <t xml:space="preserve">0.322991758584976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324848026037216</t>
+    <t xml:space="preserve">0.324848055839539</t>
   </si>
   <si>
     <t xml:space="preserve">0.319279223680496</t>
@@ -1532,46 +1532,46 @@
     <t xml:space="preserve">0.326704323291779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330416858196259</t>
+    <t xml:space="preserve">0.330416887998581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330023497343063</t>
+    <t xml:space="preserve">0.330023527145386</t>
   </si>
   <si>
     <t xml:space="preserve">0.335713595151901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328126817941666</t>
+    <t xml:space="preserve">0.328126847743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610274553299</t>
+    <t xml:space="preserve">0.337610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331920206546783</t>
+    <t xml:space="preserve">0.331920236349106</t>
   </si>
   <si>
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746741533279</t>
+    <t xml:space="preserve">0.316746711730957</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341403663158417</t>
+    <t xml:space="preserve">0.341403633356094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32243674993515</t>
+    <t xml:space="preserve">0.322436779737473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32433345913887</t>
+    <t xml:space="preserve">0.324333488941193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347093731164932</t>
+    <t xml:space="preserve">0.34709370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339506983757019</t>
+    <t xml:space="preserve">0.339506953954697</t>
   </si>
   <si>
     <t xml:space="preserve">0.312953352928162</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360370516777039</t>
+    <t xml:space="preserve">0.360370486974716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887060165405</t>
+    <t xml:space="preserve">0.350887089967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354680478572845</t>
+    <t xml:space="preserve">0.354680448770523</t>
   </si>
   <si>
     <t xml:space="preserve">0.377440690994263</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">0.405891001224518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426754534244537</t>
+    <t xml:space="preserve">0.42675456404686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415374428033829</t>
+    <t xml:space="preserve">0.415374457836151</t>
   </si>
   <si>
     <t xml:space="preserve">0.424857884645462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417271107435226</t>
+    <t xml:space="preserve">0.417271137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787680625916</t>
+    <t xml:space="preserve">0.407787710428238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398304253816605</t>
+    <t xml:space="preserve">0.398304224014282</t>
   </si>
   <si>
     <t xml:space="preserve">0.400200933218002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396407574415207</t>
+    <t xml:space="preserve">0.396407604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381234049797058</t>
+    <t xml:space="preserve">0.38123407959938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383130788803101</t>
+    <t xml:space="preserve">0.383130759000778</t>
   </si>
   <si>
     <t xml:space="preserve">0.37933737039566</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544041395187</t>
+    <t xml:space="preserve">0.375544011592865</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402097642421722</t>
+    <t xml:space="preserve">0.4020976126194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026515722275</t>
+    <t xml:space="preserve">0.415026545524597</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514053344727</t>
+    <t xml:space="preserve">0.401514023542404</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -26113,7 +26113,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26139,7 +26139,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26165,7 +26165,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26191,7 +26191,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26217,7 +26217,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26243,7 +26243,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26269,7 +26269,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26295,7 +26295,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26321,7 +26321,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26347,7 +26347,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26373,7 +26373,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26399,7 +26399,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26425,7 +26425,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26451,7 +26451,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26477,7 +26477,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26503,7 +26503,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26555,7 +26555,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26581,7 +26581,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26607,7 +26607,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26633,7 +26633,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26659,7 +26659,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26685,7 +26685,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26711,7 +26711,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26737,7 +26737,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26763,7 +26763,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26789,7 +26789,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26815,7 +26815,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26841,7 +26841,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26867,7 +26867,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26893,7 +26893,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26919,7 +26919,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26945,7 +26945,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26971,7 +26971,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26997,7 +26997,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27023,7 +27023,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27101,7 +27101,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27179,7 +27179,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27205,7 +27205,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27257,7 +27257,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27283,7 +27283,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27309,7 +27309,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27335,7 +27335,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27491,7 +27491,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27517,7 +27517,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27543,7 +27543,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27621,7 +27621,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27647,7 +27647,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28063,7 +28063,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28089,7 +28089,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28115,7 +28115,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28141,7 +28141,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28167,7 +28167,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28193,7 +28193,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28219,7 +28219,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28245,7 +28245,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28271,7 +28271,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28323,7 +28323,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28349,7 +28349,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28375,7 +28375,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28401,7 +28401,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28427,7 +28427,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28453,7 +28453,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28479,7 +28479,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28505,7 +28505,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28531,7 +28531,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28557,7 +28557,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28583,7 +28583,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28661,7 +28661,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28687,7 +28687,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28713,7 +28713,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28739,7 +28739,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28765,7 +28765,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28791,7 +28791,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28817,7 +28817,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28843,7 +28843,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28869,7 +28869,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28895,7 +28895,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28921,7 +28921,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28947,7 +28947,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28973,7 +28973,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28999,7 +28999,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29025,7 +29025,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29051,7 +29051,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29077,7 +29077,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29103,7 +29103,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29129,7 +29129,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29155,7 +29155,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29181,7 +29181,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29285,7 +29285,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29337,7 +29337,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29415,7 +29415,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29441,7 +29441,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29467,7 +29467,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29493,7 +29493,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29519,7 +29519,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29545,7 +29545,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29571,7 +29571,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29597,7 +29597,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29623,7 +29623,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29649,7 +29649,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29675,7 +29675,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29701,7 +29701,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29727,7 +29727,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29753,7 +29753,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29779,7 +29779,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29805,7 +29805,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29831,7 +29831,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29857,7 +29857,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29883,7 +29883,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30065,7 +30065,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30195,7 +30195,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30221,7 +30221,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30247,7 +30247,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30299,7 +30299,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30325,7 +30325,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30403,7 +30403,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30793,7 +30793,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30819,7 +30819,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30923,7 +30923,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30975,7 +30975,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31001,7 +31001,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31027,7 +31027,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31131,7 +31131,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31157,7 +31157,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31183,7 +31183,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31235,7 +31235,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31261,7 +31261,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31287,7 +31287,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31313,7 +31313,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31339,7 +31339,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31365,7 +31365,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31391,7 +31391,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31417,7 +31417,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31443,7 +31443,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31469,7 +31469,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31495,7 +31495,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31521,7 +31521,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31547,7 +31547,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31573,7 +31573,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31599,7 +31599,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31625,7 +31625,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31651,7 +31651,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31677,7 +31677,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31703,7 +31703,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31729,7 +31729,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31755,7 +31755,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31781,7 +31781,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31807,7 +31807,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31833,7 +31833,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31859,7 +31859,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31885,7 +31885,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31911,7 +31911,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31963,7 +31963,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31989,7 +31989,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32015,7 +32015,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32067,7 +32067,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32249,7 +32249,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32275,7 +32275,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32301,7 +32301,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32327,7 +32327,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32665,7 +32665,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33159,7 +33159,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34199,7 +34199,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34407,7 +34407,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34433,7 +34433,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34927,7 +34927,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35577,7 +35577,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35603,7 +35603,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35655,7 +35655,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35681,7 +35681,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35707,7 +35707,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35733,7 +35733,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35785,7 +35785,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35811,7 +35811,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35837,7 +35837,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35889,7 +35889,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35915,7 +35915,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35941,7 +35941,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35967,7 +35967,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35993,7 +35993,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36019,7 +36019,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36045,7 +36045,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36071,7 +36071,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36097,7 +36097,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -67066,6 +67066,32 @@
         <v>564</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.3333333333</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>564</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178789258003</t>
+    <t xml:space="preserve">0.179178759455681</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -56,46 +56,46 @@
     <t xml:space="preserve">0.167020231485367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779589891434</t>
+    <t xml:space="preserve">0.17277954518795</t>
   </si>
   <si>
     <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902752876282</t>
+    <t xml:space="preserve">0.145902708172798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493938803673</t>
+    <t xml:space="preserve">0.152493953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822484374046</t>
+    <t xml:space="preserve">0.147822514176369</t>
   </si>
   <si>
     <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141519546509</t>
+    <t xml:space="preserve">0.156141489744186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517812490463</t>
+    <t xml:space="preserve">0.153517827391624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102330207825</t>
+    <t xml:space="preserve">0.149102345108986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142383143305779</t>
+    <t xml:space="preserve">0.142383113503456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063170671463</t>
+    <t xml:space="preserve">0.142063200473785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447143793106</t>
+    <t xml:space="preserve">0.142447128891945</t>
   </si>
   <si>
     <t xml:space="preserve">0.144622877240181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141423270106316</t>
+    <t xml:space="preserve">0.141423240303993</t>
   </si>
   <si>
     <t xml:space="preserve">0.153837785124779</t>
@@ -104,76 +104,76 @@
     <t xml:space="preserve">0.173419460654259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169835895299911</t>
+    <t xml:space="preserve">0.16983588039875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380301117897</t>
+    <t xml:space="preserve">0.166380286216736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981057047844</t>
+    <t xml:space="preserve">0.159981042146683</t>
   </si>
   <si>
     <t xml:space="preserve">0.157421350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301967144012</t>
+    <t xml:space="preserve">0.152301982045174</t>
   </si>
   <si>
     <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16382060945034</t>
+    <t xml:space="preserve">0.163820594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836832761765</t>
+    <t xml:space="preserve">0.161836847662926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522620677948</t>
+    <t xml:space="preserve">0.180522635579109</t>
   </si>
   <si>
     <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17405940592289</t>
+    <t xml:space="preserve">0.174059420824051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168940007686615</t>
+    <t xml:space="preserve">0.168939977884293</t>
   </si>
   <si>
     <t xml:space="preserve">0.191977262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136802434921</t>
+    <t xml:space="preserve">0.196136772632599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176884531975</t>
+    <t xml:space="preserve">0.195176899433136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497794628143</t>
+    <t xml:space="preserve">0.187497824430466</t>
   </si>
   <si>
     <t xml:space="preserve">0.184938117861748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775750637054</t>
+    <t xml:space="preserve">0.204775735735893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454840540886</t>
+    <t xml:space="preserve">0.212454855442047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711750149727</t>
+    <t xml:space="preserve">0.204711765050888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20029628276825</t>
+    <t xml:space="preserve">0.200296312570572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19773656129837</t>
+    <t xml:space="preserve">0.197736576199532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182378396391869</t>
+    <t xml:space="preserve">0.18237841129303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578018426895</t>
+    <t xml:space="preserve">0.185578033328056</t>
   </si>
   <si>
     <t xml:space="preserve">0.172907531261444</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349714517593</t>
+    <t xml:space="preserve">0.154349729418755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579923152924</t>
+    <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917056560516</t>
+    <t xml:space="preserve">0.159917071461678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154861643910408</t>
+    <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
     <t xml:space="preserve">0.156781435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160493016242981</t>
+    <t xml:space="preserve">0.160492986440659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417570829391</t>
+    <t xml:space="preserve">0.189417615532875</t>
   </si>
   <si>
     <t xml:space="preserve">0.191337361931801</t>
@@ -218,37 +218,37 @@
     <t xml:space="preserve">0.170219838619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163180664181709</t>
+    <t xml:space="preserve">0.163180693984032</t>
   </si>
   <si>
     <t xml:space="preserve">0.149742260575294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221743345261</t>
+    <t xml:space="preserve">0.154221728444099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022106409073</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182583808899</t>
+    <t xml:space="preserve">0.147182568907738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260917782784</t>
+    <t xml:space="preserve">0.161260887980461</t>
   </si>
   <si>
     <t xml:space="preserve">0.16817207634449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739418387413</t>
+    <t xml:space="preserve">0.173739433288574</t>
   </si>
   <si>
     <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897976160049</t>
+    <t xml:space="preserve">0.185897946357727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135805368423</t>
+    <t xml:space="preserve">0.204135835170746</t>
   </si>
   <si>
     <t xml:space="preserve">0.197096675634384</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194217011332512</t>
+    <t xml:space="preserve">0.194216996431351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204647749662399</t>
+    <t xml:space="preserve">0.204647779464722</t>
   </si>
   <si>
     <t xml:space="preserve">0.198376506567001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240899920464</t>
+    <t xml:space="preserve">0.195240885019302</t>
   </si>
   <si>
     <t xml:space="preserve">0.203495904803276</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">0.21693429350853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709875226021</t>
+    <t xml:space="preserve">0.220709845423698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236771941184998</t>
+    <t xml:space="preserve">0.23677197098732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531284689903</t>
+    <t xml:space="preserve">0.242531269788742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969703197479</t>
+    <t xml:space="preserve">0.255969673395157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967738866806</t>
+    <t xml:space="preserve">0.271967798471451</t>
   </si>
   <si>
     <t xml:space="preserve">0.280286848545074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644968748093</t>
+    <t xml:space="preserve">0.295645028352737</t>
   </si>
   <si>
     <t xml:space="preserve">0.303964018821716</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">0.264864653348923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753828048706</t>
+    <t xml:space="preserve">0.254753798246384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25468984246254</t>
+    <t xml:space="preserve">0.254689872264862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24720273911953</t>
+    <t xml:space="preserve">0.247202754020691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650682926178</t>
+    <t xml:space="preserve">0.247650638222694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778668999672</t>
+    <t xml:space="preserve">0.247778683900833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572319149971</t>
+    <t xml:space="preserve">0.233572348952293</t>
   </si>
   <si>
     <t xml:space="preserve">0.238051816821098</t>
@@ -329,199 +329,199 @@
     <t xml:space="preserve">0.214374631643295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663080215454</t>
+    <t xml:space="preserve">0.210663065314293</t>
   </si>
   <si>
     <t xml:space="preserve">0.215654492378235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518855929375</t>
+    <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891354322433</t>
+    <t xml:space="preserve">0.241891369223595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570459127426</t>
+    <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980195760727</t>
+    <t xml:space="preserve">0.234980180859566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652557849884</t>
+    <t xml:space="preserve">0.231652572751045</t>
   </si>
   <si>
     <t xml:space="preserve">0.239971593022346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372682213783</t>
+    <t xml:space="preserve">0.230372697114944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173119783401</t>
+    <t xml:space="preserve">0.227173045277596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773860812187</t>
+    <t xml:space="preserve">0.22077389061451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405188441277</t>
+    <t xml:space="preserve">0.22640523314476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998279094696</t>
+    <t xml:space="preserve">0.21699832379818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204839736223221</t>
+    <t xml:space="preserve">0.204839780926704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207975372672081</t>
+    <t xml:space="preserve">0.207975342869759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535064339638</t>
+    <t xml:space="preserve">0.210535049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.209895133972168</t>
+    <t xml:space="preserve">0.209895178675652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21117502450943</t>
+    <t xml:space="preserve">0.211174994707108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582856416702</t>
+    <t xml:space="preserve">0.212582811713219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782478451729</t>
+    <t xml:space="preserve">0.215782418847084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732826352119</t>
+    <t xml:space="preserve">0.229732796549797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845437169075</t>
+    <t xml:space="preserve">0.223845526576042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805384874344</t>
+    <t xml:space="preserve">0.224805414676666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636304736137</t>
+    <t xml:space="preserve">0.233636319637299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627761602402</t>
   </si>
   <si>
     <t xml:space="preserve">0.228580921888351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973527550697</t>
+    <t xml:space="preserve">0.223973482847214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717510700226</t>
+    <t xml:space="preserve">0.223717525601387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837846398354</t>
+    <t xml:space="preserve">0.220837861299515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492125153542</t>
+    <t xml:space="preserve">0.235492080450058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965847373009</t>
+    <t xml:space="preserve">0.220965877175331</t>
   </si>
   <si>
     <t xml:space="preserve">0.227365061640739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556127309799</t>
+    <t xml:space="preserve">0.302556157112122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357578516006</t>
+    <t xml:space="preserve">0.358357518911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473543882369995</t>
+    <t xml:space="preserve">0.47354394197464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454194545746</t>
+    <t xml:space="preserve">0.555454254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485702455043793</t>
+    <t xml:space="preserve">0.485702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44474732875824</t>
+    <t xml:space="preserve">0.444747388362885</t>
   </si>
   <si>
     <t xml:space="preserve">0.429709106683731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152257204056</t>
+    <t xml:space="preserve">0.403152227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37115603685379</t>
+    <t xml:space="preserve">0.371156066656113</t>
   </si>
   <si>
     <t xml:space="preserve">0.421710073947906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035745859146</t>
+    <t xml:space="preserve">0.374035716056824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754977464676</t>
+    <t xml:space="preserve">0.380754917860031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35259822010994</t>
+    <t xml:space="preserve">0.352598249912262</t>
   </si>
   <si>
     <t xml:space="preserve">0.331800699234009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602059364319</t>
+    <t xml:space="preserve">0.320602029561996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332440614700317</t>
+    <t xml:space="preserve">0.332440674304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.340439677238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641218900681</t>
+    <t xml:space="preserve">0.327641189098358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157971382141</t>
+    <t xml:space="preserve">0.355157941579819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478836774826</t>
+    <t xml:space="preserve">0.347478866577148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760602235794</t>
+    <t xml:space="preserve">0.332760572433472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121654033661</t>
+    <t xml:space="preserve">0.324121624231339</t>
   </si>
   <si>
     <t xml:space="preserve">0.32700127363205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159846305847</t>
+    <t xml:space="preserve">0.339159816503525</t>
   </si>
   <si>
     <t xml:space="preserve">0.335960179567337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161721229553</t>
+    <t xml:space="preserve">0.323161751031876</t>
   </si>
   <si>
     <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319962114095688</t>
+    <t xml:space="preserve">0.319962084293365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
     <t xml:space="preserve">0.340759694576263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801577091217</t>
+    <t xml:space="preserve">0.323801606893539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521835565567</t>
+    <t xml:space="preserve">0.322521775960922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360390901566</t>
+    <t xml:space="preserve">0.334360420703888</t>
   </si>
   <si>
     <t xml:space="preserve">0.328921049833298</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">0.307163655757904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122621297836</t>
+    <t xml:space="preserve">0.316122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698491573334</t>
+    <t xml:space="preserve">0.316698551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326361328363419</t>
+    <t xml:space="preserve">0.326361387968063</t>
   </si>
   <si>
     <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364756792783737</t>
+    <t xml:space="preserve">0.36475682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559179782867</t>
+    <t xml:space="preserve">0.3455590903759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199035644531</t>
+    <t xml:space="preserve">0.346198976039886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081527233124</t>
+    <t xml:space="preserve">0.325081557035446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959271907806</t>
+    <t xml:space="preserve">0.343959301710129</t>
   </si>
   <si>
     <t xml:space="preserve">0.320282101631165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720505237579</t>
+    <t xml:space="preserve">0.333720445632935</t>
   </si>
   <si>
     <t xml:space="preserve">0.396753013134003</t>
@@ -572,19 +572,19 @@
     <t xml:space="preserve">0.376275420188904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37563556432724</t>
+    <t xml:space="preserve">0.375635534524918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376915365457535</t>
+    <t xml:space="preserve">0.376915335655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.370196133852005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555310726166</t>
+    <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318448781967</t>
+    <t xml:space="preserve">0.351318418979645</t>
   </si>
   <si>
     <t xml:space="preserve">0.356117844581604</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">0.373715758323669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39579313993454</t>
+    <t xml:space="preserve">0.395793110132217</t>
   </si>
   <si>
     <t xml:space="preserve">0.398672848939896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594440460205</t>
+    <t xml:space="preserve">0.384594410657883</t>
   </si>
   <si>
     <t xml:space="preserve">0.383954524993896</t>
@@ -611,136 +611,136 @@
     <t xml:space="preserve">0.394193351268768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274512529373</t>
+    <t xml:space="preserve">0.384274452924728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310800075531</t>
+    <t xml:space="preserve">0.415310829877853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42235004901886</t>
+    <t xml:space="preserve">0.422349989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312734603882</t>
+    <t xml:space="preserve">0.399312674999237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634626865387</t>
+    <t xml:space="preserve">0.383634567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553406000137</t>
+    <t xml:space="preserve">0.393553346395493</t>
   </si>
   <si>
     <t xml:space="preserve">0.479943186044693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447307050228119</t>
+    <t xml:space="preserve">0.447307080030441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745364427567</t>
+    <t xml:space="preserve">0.460745394229889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547721624374</t>
+    <t xml:space="preserve">0.441547781229019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027249097824</t>
+    <t xml:space="preserve">0.446027159690857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346239566803</t>
+    <t xml:space="preserve">0.454346090555191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447947055101395</t>
+    <t xml:space="preserve">0.447946965694427</t>
   </si>
   <si>
     <t xml:space="preserve">0.430029094219208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588785886765</t>
+    <t xml:space="preserve">0.432588756084442</t>
   </si>
   <si>
     <t xml:space="preserve">0.428749263286591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230606079102</t>
+    <t xml:space="preserve">0.417230635881424</t>
   </si>
   <si>
     <t xml:space="preserve">0.413391053676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
+    <t xml:space="preserve">0.415950685739517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070128679276</t>
+    <t xml:space="preserve">0.421070098876953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551501274109</t>
+    <t xml:space="preserve">0.409551471471786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267860889435</t>
+    <t xml:space="preserve">0.440267831087112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909681081772</t>
+    <t xml:space="preserve">0.424909710884094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984250307083</t>
+    <t xml:space="preserve">0.470984160900116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148477554321</t>
+    <t xml:space="preserve">0.435148507356644</t>
   </si>
   <si>
     <t xml:space="preserve">0.406991809606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189571619034</t>
+    <t xml:space="preserve">0.426189512014389</t>
   </si>
   <si>
     <t xml:space="preserve">0.43130898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510437011719</t>
+    <t xml:space="preserve">0.418510466814041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40571191906929</t>
+    <t xml:space="preserve">0.405711978673935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111163139343</t>
+    <t xml:space="preserve">0.412111222743988</t>
   </si>
   <si>
     <t xml:space="preserve">0.38907390832901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39035376906395</t>
+    <t xml:space="preserve">0.390353798866272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473122596741</t>
+    <t xml:space="preserve">0.395473152399063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831421613693</t>
+    <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988089561462</t>
+    <t xml:space="preserve">0.438988029956818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469402551651</t>
+    <t xml:space="preserve">0.427469372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670884609222</t>
+    <t xml:space="preserve">0.414670914411545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872456073761</t>
+    <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790267944336</t>
+    <t xml:space="preserve">0.419790357351303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271610736847</t>
+    <t xml:space="preserve">0.408271670341492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629879951477</t>
+    <t xml:space="preserve">0.423629820346832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596345186234</t>
+    <t xml:space="preserve">0.368596315383911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435927391052</t>
+    <t xml:space="preserve">0.372435957193375</t>
   </si>
   <si>
     <t xml:space="preserve">0.369876235723495</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366036653518677</t>
+    <t xml:space="preserve">0.366036713123322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363477021455765</t>
+    <t xml:space="preserve">0.36347696185112</t>
   </si>
   <si>
     <t xml:space="preserve">0.350678473711014</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">0.342999368906021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279229640961</t>
+    <t xml:space="preserve">0.344279259443283</t>
   </si>
   <si>
     <t xml:space="preserve">0.351958334445953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835141658783</t>
+    <t xml:space="preserve">0.37883523106575</t>
   </si>
   <si>
     <t xml:space="preserve">0.392913490533829</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">0.359637409448624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316484451294</t>
+    <t xml:space="preserve">0.367316544055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.385234385728836</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">0.382674723863602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3801149725914</t>
+    <t xml:space="preserve">0.380114942789078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633599996567</t>
+    <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
     <t xml:space="preserve">0.398032873868942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592565536499</t>
+    <t xml:space="preserve">0.400592625141144</t>
   </si>
   <si>
     <t xml:space="preserve">0.431948840618134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348054885864</t>
+    <t xml:space="preserve">0.438348114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545787096024</t>
+    <t xml:space="preserve">0.457545846700668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945090770721</t>
+    <t xml:space="preserve">0.463945060968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350865602493</t>
+    <t xml:space="preserve">0.472350805997849</t>
   </si>
   <si>
     <t xml:space="preserve">0.451200872659683</t>
@@ -821,52 +821,52 @@
     <t xml:space="preserve">0.437100797891617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000782728195</t>
+    <t xml:space="preserve">0.423000752925873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575868606567</t>
+    <t xml:space="preserve">0.433575749397278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150745868683</t>
+    <t xml:space="preserve">0.44415083527565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675734758377</t>
+    <t xml:space="preserve">0.447675853967667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625816583633</t>
+    <t xml:space="preserve">0.440625846385956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525831222534</t>
+    <t xml:space="preserve">0.426525801420212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900648355484</t>
+    <t xml:space="preserve">0.408900678157806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475764036179</t>
+    <t xml:space="preserve">0.419475734233856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394800752401352</t>
+    <t xml:space="preserve">0.394800662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325681686401</t>
+    <t xml:space="preserve">0.398325741291046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425726652145</t>
+    <t xml:space="preserve">0.412425667047501</t>
   </si>
   <si>
     <t xml:space="preserve">0.430050820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725831747055</t>
+    <t xml:space="preserve">0.454725801944733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800933837891</t>
+    <t xml:space="preserve">0.535800874233246</t>
   </si>
   <si>
     <t xml:space="preserve">0.458250790834427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46530082821846</t>
+    <t xml:space="preserve">0.465300887823105</t>
   </si>
   <si>
     <t xml:space="preserve">0.461775779724121</t>
@@ -890,61 +890,61 @@
     <t xml:space="preserve">0.377175718545914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275763511658</t>
+    <t xml:space="preserve">0.391275644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650670051575</t>
+    <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860587596893</t>
+    <t xml:space="preserve">0.346860647201538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450639724731</t>
+    <t xml:space="preserve">0.345450609922409</t>
   </si>
   <si>
     <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35250061750412</t>
+    <t xml:space="preserve">0.352500647306442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400632143021</t>
+    <t xml:space="preserve">0.338400602340698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250549793243</t>
+    <t xml:space="preserve">0.317250579595566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320070534944534</t>
+    <t xml:space="preserve">0.320070594549179</t>
   </si>
   <si>
     <t xml:space="preserve">0.296100527048111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26367050409317</t>
+    <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283410519361496</t>
+    <t xml:space="preserve">0.283410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900466918945</t>
+    <t xml:space="preserve">0.267900437116623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770489454269</t>
+    <t xml:space="preserve">0.277770519256592</t>
   </si>
   <si>
     <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570488929749</t>
+    <t xml:space="preserve">0.24957050383091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800481557846</t>
+    <t xml:space="preserve">0.253800451755524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24816045165062</t>
+    <t xml:space="preserve">0.248160421848297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460497140884</t>
+    <t xml:space="preserve">0.290460526943207</t>
   </si>
   <si>
     <t xml:space="preserve">0.291870534420013</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.276360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28482049703598</t>
+    <t xml:space="preserve">0.284820526838303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286230534315109</t>
+    <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330549478531</t>
+    <t xml:space="preserve">0.300330579280853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790594339371</t>
+    <t xml:space="preserve">0.308790564537048</t>
   </si>
   <si>
     <t xml:space="preserve">0.314430594444275</t>
@@ -971,10 +971,10 @@
     <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350564956665</t>
+    <t xml:space="preserve">0.33135062456131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325710564851761</t>
+    <t xml:space="preserve">0.325710624456406</t>
   </si>
   <si>
     <t xml:space="preserve">0.349680632352829</t>
@@ -986,163 +986,163 @@
     <t xml:space="preserve">0.384225696325302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170639514923</t>
+    <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990594863892</t>
+    <t xml:space="preserve">0.336990624666214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630624771118</t>
+    <t xml:space="preserve">0.342630594968796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025665998459</t>
+    <t xml:space="preserve">0.356025636196136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090610027313</t>
+    <t xml:space="preserve">0.351090639829636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530609607697</t>
+    <t xml:space="preserve">0.328530550003052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940617084503</t>
+    <t xml:space="preserve">0.329940587282181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327120631933212</t>
+    <t xml:space="preserve">0.327120542526245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300616979599</t>
+    <t xml:space="preserve">0.324300587177277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610549688339</t>
+    <t xml:space="preserve">0.311610519886017</t>
   </si>
   <si>
     <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31020051240921</t>
+    <t xml:space="preserve">0.310200572013855</t>
   </si>
   <si>
     <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289050489664078</t>
+    <t xml:space="preserve">0.2890505194664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29328054189682</t>
+    <t xml:space="preserve">0.293280512094498</t>
   </si>
   <si>
     <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130519151688</t>
+    <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265080511569977</t>
+    <t xml:space="preserve">0.265080451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720541477203</t>
+    <t xml:space="preserve">0.270720511674881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950504302979</t>
+    <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000541687012</t>
+    <t xml:space="preserve">0.282000482082367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297510594129562</t>
+    <t xml:space="preserve">0.297510534524918</t>
   </si>
   <si>
     <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690519571304</t>
+    <t xml:space="preserve">0.294690549373627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437586963176727</t>
+    <t xml:space="preserve">0.437586933374405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879156827927</t>
+    <t xml:space="preserve">0.406879127025604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363688468933</t>
+    <t xml:space="preserve">0.395363658666611</t>
   </si>
   <si>
     <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3684943318367</t>
+    <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171290874481</t>
+    <t xml:space="preserve">0.376171261072159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370029717683792</t>
+    <t xml:space="preserve">0.37002968788147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387686759233475</t>
+    <t xml:space="preserve">0.38768669962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777448415756</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565043926239</t>
+    <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211185455322</t>
+    <t xml:space="preserve">0.356211155653</t>
   </si>
   <si>
     <t xml:space="preserve">0.350069582462311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534196615219</t>
+    <t xml:space="preserve">0.348534256219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463395118713</t>
+    <t xml:space="preserve">0.345463424921036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281927347183</t>
+    <t xml:space="preserve">0.359281957149506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140413761139</t>
+    <t xml:space="preserve">0.353140354156494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746571302414</t>
+    <t xml:space="preserve">0.357746541500092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857267379761</t>
+    <t xml:space="preserve">0.340857237577438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675740003586</t>
+    <t xml:space="preserve">0.354675799608231</t>
   </si>
   <si>
     <t xml:space="preserve">0.445263892412186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394595384598</t>
+    <t xml:space="preserve">0.41839462518692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617929697037</t>
+    <t xml:space="preserve">0.460617810487747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940911054611</t>
+    <t xml:space="preserve">0.452940881252289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102401733398</t>
+    <t xml:space="preserve">0.449102431535721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233074903488</t>
+    <t xml:space="preserve">0.422233104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717636346817</t>
+    <t xml:space="preserve">0.410717666149139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202167987823</t>
+    <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39152517914772</t>
+    <t xml:space="preserve">0.391525208950043</t>
   </si>
   <si>
     <t xml:space="preserve">0.403040587902069</t>
@@ -1154,31 +1154,31 @@
     <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100519180298</t>
+    <t xml:space="preserve">0.373100489377975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817313194275</t>
+    <t xml:space="preserve">0.36081737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351604998111725</t>
+    <t xml:space="preserve">0.351604968309402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346998810768127</t>
+    <t xml:space="preserve">0.34699884057045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37770664691925</t>
+    <t xml:space="preserve">0.377706676721573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958886384964</t>
+    <t xml:space="preserve">0.366958945989609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37463590502739</t>
+    <t xml:space="preserve">0.374635875225067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423500537872</t>
+    <t xml:space="preserve">0.365423530340195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432488203049</t>
+    <t xml:space="preserve">0.322432547807693</t>
   </si>
   <si>
     <t xml:space="preserve">0.305543184280396</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323967933654785</t>
+    <t xml:space="preserve">0.323967903852463</t>
   </si>
   <si>
     <t xml:space="preserve">0.325503289699554</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">0.336251080036163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33778640627861</t>
+    <t xml:space="preserve">0.337786436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928068876266</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715634584427</t>
+    <t xml:space="preserve">0.334715664386749</t>
   </si>
   <si>
     <t xml:space="preserve">0.314755529165268</t>
@@ -1226,58 +1226,58 @@
     <t xml:space="preserve">0.32857409119606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345899581909</t>
+    <t xml:space="preserve">0.323345869779587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328171879053116</t>
+    <t xml:space="preserve">0.328171908855438</t>
   </si>
   <si>
     <t xml:space="preserve">0.320128470659256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32495453953743</t>
+    <t xml:space="preserve">0.324954569339752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337823987007141</t>
+    <t xml:space="preserve">0.337824046611786</t>
   </si>
   <si>
     <t xml:space="preserve">0.339432686567307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32656317949295</t>
+    <t xml:space="preserve">0.326563209295273</t>
   </si>
   <si>
     <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519800901413</t>
+    <t xml:space="preserve">0.318519830703735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308867663145065</t>
+    <t xml:space="preserve">0.308867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606855630875</t>
+    <t xml:space="preserve">0.297606885433197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3072589635849</t>
+    <t xml:space="preserve">0.307258993387222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737140417099</t>
+    <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
     <t xml:space="preserve">0.305650293827057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041564464569</t>
+    <t xml:space="preserve">0.304041653871536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998156070709</t>
+    <t xml:space="preserve">0.295998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780846357346</t>
+    <t xml:space="preserve">0.292780816555023</t>
   </si>
   <si>
     <t xml:space="preserve">0.284737408161163</t>
@@ -1292,37 +1292,37 @@
     <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346077919006</t>
+    <t xml:space="preserve">0.286346107721329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693940162659</t>
+    <t xml:space="preserve">0.276693969964981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563417434692</t>
+    <t xml:space="preserve">0.289563477039337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291172116994858</t>
+    <t xml:space="preserve">0.29117214679718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824195146561</t>
+    <t xml:space="preserve">0.300824254751205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432864904404</t>
+    <t xml:space="preserve">0.302432924509048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693702220917</t>
+    <t xml:space="preserve">0.313693732023239</t>
   </si>
   <si>
     <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302134037018</t>
+    <t xml:space="preserve">0.352302223443985</t>
   </si>
   <si>
     <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867455005646</t>
+    <t xml:space="preserve">0.345867425203323</t>
   </si>
   <si>
     <t xml:space="preserve">0.347476154565811</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">0.341041386127472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650085687637</t>
+    <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736902475357</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300703495740891</t>
+    <t xml:space="preserve">0.300703525543213</t>
   </si>
   <si>
     <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29548904299736</t>
+    <t xml:space="preserve">0.295489013195038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290274530649185</t>
+    <t xml:space="preserve">0.290274500846863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292012721300125</t>
+    <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
     <t xml:space="preserve">0.30591806769371</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536339998245</t>
+    <t xml:space="preserve">0.288536310195923</t>
   </si>
   <si>
     <t xml:space="preserve">0.283321857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293750822544098</t>
+    <t xml:space="preserve">0.29375085234642</t>
   </si>
   <si>
     <t xml:space="preserve">0.285059988498688</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27463099360466</t>
+    <t xml:space="preserve">0.274630963802338</t>
   </si>
   <si>
     <t xml:space="preserve">0.286798179149628</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">0.279845476150513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369154453278</t>
+    <t xml:space="preserve">0.276369124650955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27289280295372</t>
+    <t xml:space="preserve">0.272892773151398</t>
   </si>
   <si>
     <t xml:space="preserve">0.309394419193268</t>
@@ -1397,22 +1397,22 @@
     <t xml:space="preserve">0.298965394496918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656228542328</t>
+    <t xml:space="preserve">0.30765625834465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132609844208</t>
+    <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870711088181</t>
+    <t xml:space="preserve">0.312870770692825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252468585968</t>
+    <t xml:space="preserve">0.330252438783646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037926435471</t>
+    <t xml:space="preserve">0.325037956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314608871936798</t>
+    <t xml:space="preserve">0.314608931541443</t>
   </si>
   <si>
     <t xml:space="preserve">0.319823443889618</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">0.318085253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316347062587738</t>
+    <t xml:space="preserve">0.31634709239006</t>
   </si>
   <si>
     <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254966020584</t>
+    <t xml:space="preserve">0.305254995822906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30170550942421</t>
+    <t xml:space="preserve">0.301705479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804452419281</t>
+    <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
     <t xml:space="preserve">0.294606506824493</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">0.319233953952789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310164839029312</t>
+    <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308351010084152</t>
+    <t xml:space="preserve">0.308350950479507</t>
   </si>
   <si>
     <t xml:space="preserve">0.311978667974472</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771174192429</t>
+    <t xml:space="preserve">0.284771203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585062742233</t>
+    <t xml:space="preserve">0.286585032939911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297467976808548</t>
+    <t xml:space="preserve">0.297468036413193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300716489553452</t>
+    <t xml:space="preserve">0.300716459751129</t>
   </si>
   <si>
     <t xml:space="preserve">0.295147627592087</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">0.308141559362411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297003954648972</t>
+    <t xml:space="preserve">0.297003924846649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309997856616974</t>
+    <t xml:space="preserve">0.309997886419296</t>
   </si>
   <si>
     <t xml:space="preserve">0.313710391521454</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">0.317422956228256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322991758584976</t>
+    <t xml:space="preserve">0.322991788387299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324848055839539</t>
+    <t xml:space="preserve">0.324848026037216</t>
   </si>
   <si>
     <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334129422903061</t>
+    <t xml:space="preserve">0.334129452705383</t>
   </si>
   <si>
     <t xml:space="preserve">0.337841957807541</t>
@@ -1529,49 +1529,49 @@
     <t xml:space="preserve">0.339698255062103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326704323291779</t>
+    <t xml:space="preserve">0.326704293489456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330416887998581</t>
+    <t xml:space="preserve">0.330416858196259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330023527145386</t>
+    <t xml:space="preserve">0.330023497343063</t>
   </si>
   <si>
     <t xml:space="preserve">0.335713595151901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328126847743988</t>
+    <t xml:space="preserve">0.328126817941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610244750977</t>
+    <t xml:space="preserve">0.337610274553299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331920236349106</t>
+    <t xml:space="preserve">0.331920206546783</t>
   </si>
   <si>
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746711730957</t>
+    <t xml:space="preserve">0.316746741533279</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341403633356094</t>
+    <t xml:space="preserve">0.341403663158417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322436779737473</t>
+    <t xml:space="preserve">0.32243674993515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324333488941193</t>
+    <t xml:space="preserve">0.32433345913887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34709370136261</t>
+    <t xml:space="preserve">0.347093731164932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339506953954697</t>
+    <t xml:space="preserve">0.339506983757019</t>
   </si>
   <si>
     <t xml:space="preserve">0.312953352928162</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360370486974716</t>
+    <t xml:space="preserve">0.360370516777039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887089967728</t>
+    <t xml:space="preserve">0.350887060165405</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354680448770523</t>
+    <t xml:space="preserve">0.354680478572845</t>
   </si>
   <si>
     <t xml:space="preserve">0.377440690994263</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">0.405891001224518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42675456404686</t>
+    <t xml:space="preserve">0.426754534244537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415374457836151</t>
+    <t xml:space="preserve">0.415374428033829</t>
   </si>
   <si>
     <t xml:space="preserve">0.424857884645462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417271137237549</t>
+    <t xml:space="preserve">0.417271107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787710428238</t>
+    <t xml:space="preserve">0.407787680625916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398304224014282</t>
+    <t xml:space="preserve">0.398304253816605</t>
   </si>
   <si>
     <t xml:space="preserve">0.400200933218002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396407604217529</t>
+    <t xml:space="preserve">0.396407574415207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38123407959938</t>
+    <t xml:space="preserve">0.381234049797058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383130759000778</t>
+    <t xml:space="preserve">0.383130788803101</t>
   </si>
   <si>
     <t xml:space="preserve">0.37933737039566</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544011592865</t>
+    <t xml:space="preserve">0.375544041395187</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4020976126194</t>
+    <t xml:space="preserve">0.402097642421722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026545524597</t>
+    <t xml:space="preserve">0.415026515722275</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514023542404</t>
+    <t xml:space="preserve">0.401514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -67095,6 +67095,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.3333333333</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>564</v>
+      </c>
+      <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178789258003</t>
+    <t xml:space="preserve">0.179178774356842</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179818704724312</t>
+    <t xml:space="preserve">0.179818674921989</t>
   </si>
   <si>
     <t xml:space="preserve">0.175979167222977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174699321389198</t>
+    <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
     <t xml:space="preserve">0.167020246386528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779560089111</t>
+    <t xml:space="preserve">0.17277954518795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151662066578865</t>
+    <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
     <t xml:space="preserve">0.145902708172798</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">0.147822514176369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155501589179039</t>
+    <t xml:space="preserve">0.155501574277878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15614153444767</t>
+    <t xml:space="preserve">0.156141519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517827391624</t>
+    <t xml:space="preserve">0.153517812490463</t>
   </si>
   <si>
     <t xml:space="preserve">0.149102345108986</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">0.142383143305779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063185572624</t>
+    <t xml:space="preserve">0.142063170671463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447128891945</t>
+    <t xml:space="preserve">0.142447143793106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14462286233902</t>
+    <t xml:space="preserve">0.144622877240181</t>
   </si>
   <si>
     <t xml:space="preserve">0.141423270106316</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">0.15383780002594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173419460654259</t>
+    <t xml:space="preserve">0.17341947555542</t>
   </si>
   <si>
     <t xml:space="preserve">0.169835895299911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380271315575</t>
+    <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
     <t xml:space="preserve">0.159981071949005</t>
@@ -122,79 +122,79 @@
     <t xml:space="preserve">0.158509254455566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16382060945034</t>
+    <t xml:space="preserve">0.163820594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836832761765</t>
+    <t xml:space="preserve">0.161836847662926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522635579109</t>
+    <t xml:space="preserve">0.180522605776787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18045862019062</t>
+    <t xml:space="preserve">0.180458664894104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17405940592289</t>
+    <t xml:space="preserve">0.174059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168939992785454</t>
+    <t xml:space="preserve">0.168940007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977292299271</t>
+    <t xml:space="preserve">0.191977247595787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136772632599</t>
+    <t xml:space="preserve">0.196136757731438</t>
   </si>
   <si>
     <t xml:space="preserve">0.195176884531975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497794628143</t>
+    <t xml:space="preserve">0.187497824430466</t>
   </si>
   <si>
     <t xml:space="preserve">0.184938117861748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775750637054</t>
+    <t xml:space="preserve">0.204775735735893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454855442047</t>
+    <t xml:space="preserve">0.212454825639725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711779952049</t>
+    <t xml:space="preserve">0.204711765050888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200296267867088</t>
+    <t xml:space="preserve">0.200296252965927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736591100693</t>
+    <t xml:space="preserve">0.197736576199532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182378396391869</t>
+    <t xml:space="preserve">0.18237841129303</t>
   </si>
   <si>
     <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907546162605</t>
+    <t xml:space="preserve">0.172907561063766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499669551849</t>
+    <t xml:space="preserve">0.171499699354172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165740385651588</t>
+    <t xml:space="preserve">0.16574040055275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349714517593</t>
+    <t xml:space="preserve">0.154349729418755</t>
   </si>
   <si>
     <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917056560516</t>
+    <t xml:space="preserve">0.159917071461678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154861658811569</t>
+    <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
     <t xml:space="preserve">0.156781435012817</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">0.16049300134182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417570829391</t>
+    <t xml:space="preserve">0.189417585730553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191337332129478</t>
+    <t xml:space="preserve">0.191337376832962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857894062996</t>
+    <t xml:space="preserve">0.186857864260674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002088546753</t>
+    <t xml:space="preserve">0.185002073645592</t>
   </si>
   <si>
     <t xml:space="preserve">0.170219853520393</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221713542938</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
     <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182568907738</t>
+    <t xml:space="preserve">0.147182583808899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260917782784</t>
+    <t xml:space="preserve">0.161260887980461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168172106146812</t>
+    <t xml:space="preserve">0.168172091245651</t>
   </si>
   <si>
     <t xml:space="preserve">0.173739418387413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339221954346</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
     <t xml:space="preserve">0.185897976160049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135835170746</t>
+    <t xml:space="preserve">0.204135850071907</t>
   </si>
   <si>
     <t xml:space="preserve">0.197096660733223</t>
@@ -257,40 +257,40 @@
     <t xml:space="preserve">0.181354537606239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194217011332512</t>
+    <t xml:space="preserve">0.19421698153019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20464776456356</t>
+    <t xml:space="preserve">0.204647749662399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376521468163</t>
+    <t xml:space="preserve">0.198376506567001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240885019302</t>
+    <t xml:space="preserve">0.195240899920464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495889902115</t>
+    <t xml:space="preserve">0.203495919704437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934308409691</t>
+    <t xml:space="preserve">0.216934278607368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709830522537</t>
+    <t xml:space="preserve">0.220709875226021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236771985888481</t>
+    <t xml:space="preserve">0.236772000789642</t>
   </si>
   <si>
     <t xml:space="preserve">0.242531284689903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969673395157</t>
+    <t xml:space="preserve">0.255969703197479</t>
   </si>
   <si>
     <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286848545074</t>
+    <t xml:space="preserve">0.280286818742752</t>
   </si>
   <si>
     <t xml:space="preserve">0.295645028352737</t>
@@ -299,76 +299,76 @@
     <t xml:space="preserve">0.303963989019394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26236891746521</t>
+    <t xml:space="preserve">0.262368947267532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2648646235466</t>
+    <t xml:space="preserve">0.264864653348923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753828048706</t>
+    <t xml:space="preserve">0.254753857851028</t>
   </si>
   <si>
     <t xml:space="preserve">0.25468984246254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202754020691</t>
+    <t xml:space="preserve">0.24720273911953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2476507127285</t>
+    <t xml:space="preserve">0.247650682926178</t>
   </si>
   <si>
     <t xml:space="preserve">0.247778654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572348952293</t>
+    <t xml:space="preserve">0.233572319149971</t>
   </si>
   <si>
     <t xml:space="preserve">0.238051801919937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374631643295</t>
+    <t xml:space="preserve">0.214374646544456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663065314293</t>
+    <t xml:space="preserve">0.210663080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654492378235</t>
+    <t xml:space="preserve">0.215654477477074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518811225891</t>
+    <t xml:space="preserve">0.212518870830536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891369223595</t>
+    <t xml:space="preserve">0.241891354322433</t>
   </si>
   <si>
     <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980165958405</t>
+    <t xml:space="preserve">0.234980151057243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652557849884</t>
+    <t xml:space="preserve">0.231652587652206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971578121185</t>
+    <t xml:space="preserve">0.239971607923508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372726917267</t>
+    <t xml:space="preserve">0.230372697114944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173075079918</t>
+    <t xml:space="preserve">0.22717310488224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773845911026</t>
+    <t xml:space="preserve">0.220773831009865</t>
   </si>
   <si>
     <t xml:space="preserve">0.226405203342438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998338699341</t>
+    <t xml:space="preserve">0.21699832379818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204839736223221</t>
+    <t xml:space="preserve">0.204839751124382</t>
   </si>
   <si>
     <t xml:space="preserve">0.20797535777092</t>
@@ -377,67 +377,67 @@
     <t xml:space="preserve">0.210535079240799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.209895148873329</t>
+    <t xml:space="preserve">0.209895178675652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211174979805946</t>
+    <t xml:space="preserve">0.211174994707108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582781910896</t>
+    <t xml:space="preserve">0.21258282661438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782463550568</t>
+    <t xml:space="preserve">0.215782433748245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732811450958</t>
+    <t xml:space="preserve">0.229732826352119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22384549677372</t>
+    <t xml:space="preserve">0.223845526576042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805369973183</t>
+    <t xml:space="preserve">0.224805444478989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636319637299</t>
+    <t xml:space="preserve">0.23363633453846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627731800079</t>
+    <t xml:space="preserve">0.238627746701241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580951690674</t>
+    <t xml:space="preserve">0.228580936789513</t>
   </si>
   <si>
     <t xml:space="preserve">0.223973497748375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717465996742</t>
+    <t xml:space="preserve">0.223717510700226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837846398354</t>
+    <t xml:space="preserve">0.220837816596031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492154955864</t>
+    <t xml:space="preserve">0.235492080450058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965832471848</t>
+    <t xml:space="preserve">0.220965847373009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365106344223</t>
+    <t xml:space="preserve">0.227365061640739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556157112122</t>
+    <t xml:space="preserve">0.302556186914444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357578516006</t>
+    <t xml:space="preserve">0.358357548713684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473543971776962</t>
+    <t xml:space="preserve">0.473544001579285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454134941101</t>
+    <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485702604055405</t>
+    <t xml:space="preserve">0.48570254445076</t>
   </si>
   <si>
     <t xml:space="preserve">0.44474732875824</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.429709166288376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152227401733</t>
+    <t xml:space="preserve">0.403152257204056</t>
   </si>
   <si>
     <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710073947906</t>
+    <t xml:space="preserve">0.421710014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035805463791</t>
+    <t xml:space="preserve">0.374035716056824</t>
   </si>
   <si>
     <t xml:space="preserve">0.380754947662354</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">0.331800669431686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602059364319</t>
+    <t xml:space="preserve">0.320602029561996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332440614700317</t>
+    <t xml:space="preserve">0.332440674304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.340439707040787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641218900681</t>
+    <t xml:space="preserve">0.327641189098358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157941579819</t>
+    <t xml:space="preserve">0.355158030986786</t>
   </si>
   <si>
     <t xml:space="preserve">0.347478836774826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760542631149</t>
+    <t xml:space="preserve">0.332760602235794</t>
   </si>
   <si>
     <t xml:space="preserve">0.324121624231339</t>
@@ -500,25 +500,25 @@
     <t xml:space="preserve">0.335960209369659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161751031876</t>
+    <t xml:space="preserve">0.323161721229553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200880765915</t>
+    <t xml:space="preserve">0.330200910568237</t>
   </si>
   <si>
     <t xml:space="preserve">0.31996214389801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759664773941</t>
+    <t xml:space="preserve">0.340759724378586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801636695862</t>
+    <t xml:space="preserve">0.323801666498184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521835565567</t>
+    <t xml:space="preserve">0.322521775960922</t>
   </si>
   <si>
     <t xml:space="preserve">0.334360420703888</t>
@@ -530,25 +530,25 @@
     <t xml:space="preserve">0.334040492773056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163625955582</t>
+    <t xml:space="preserve">0.307163655757904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122531890869</t>
+    <t xml:space="preserve">0.316122561693192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698461771011</t>
+    <t xml:space="preserve">0.316698521375656</t>
   </si>
   <si>
     <t xml:space="preserve">0.326361387968063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331480771303177</t>
+    <t xml:space="preserve">0.331480801105499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364756792783737</t>
+    <t xml:space="preserve">0.36475682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559120178223</t>
+    <t xml:space="preserve">0.3455590903759</t>
   </si>
   <si>
     <t xml:space="preserve">0.346199035644531</t>
@@ -557,94 +557,94 @@
     <t xml:space="preserve">0.325081527233124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959301710129</t>
+    <t xml:space="preserve">0.343959271907806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282131433487</t>
+    <t xml:space="preserve">0.320282101631165</t>
   </si>
   <si>
     <t xml:space="preserve">0.333720475435257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753042936325</t>
+    <t xml:space="preserve">0.396753013134003</t>
   </si>
   <si>
     <t xml:space="preserve">0.376275449991226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635534524918</t>
+    <t xml:space="preserve">0.375635504722595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376915395259857</t>
+    <t xml:space="preserve">0.376915365457535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37019619345665</t>
+    <t xml:space="preserve">0.370196163654327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555280923843</t>
+    <t xml:space="preserve">0.377555310726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318418979645</t>
+    <t xml:space="preserve">0.351318389177322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117874383926</t>
+    <t xml:space="preserve">0.356117844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917240381241</t>
+    <t xml:space="preserve">0.360917329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715788125992</t>
+    <t xml:space="preserve">0.373715728521347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793169736862</t>
+    <t xml:space="preserve">0.395793199539185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672819137573</t>
+    <t xml:space="preserve">0.398672789335251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594470262527</t>
+    <t xml:space="preserve">0.38459450006485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954584598541</t>
+    <t xml:space="preserve">0.383954495191574</t>
   </si>
   <si>
     <t xml:space="preserve">0.394193321466446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274482727051</t>
+    <t xml:space="preserve">0.384274512529373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310889482498</t>
+    <t xml:space="preserve">0.415310829877853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422349959611893</t>
+    <t xml:space="preserve">0.422349989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312704801559</t>
+    <t xml:space="preserve">0.399312734603882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634597063065</t>
+    <t xml:space="preserve">0.383634567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553346395493</t>
+    <t xml:space="preserve">0.393553406000137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943156242371</t>
+    <t xml:space="preserve">0.479943215847015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447307080030441</t>
+    <t xml:space="preserve">0.447307020425797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745453834534</t>
+    <t xml:space="preserve">0.460745394229889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547691822052</t>
+    <t xml:space="preserve">0.44154766201973</t>
   </si>
   <si>
     <t xml:space="preserve">0.446027159690857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346150159836</t>
+    <t xml:space="preserve">0.454346209764481</t>
   </si>
   <si>
     <t xml:space="preserve">0.44794699549675</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">0.430029064416885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588785886765</t>
+    <t xml:space="preserve">0.432588815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749263286591</t>
+    <t xml:space="preserve">0.428749293088913</t>
   </si>
   <si>
     <t xml:space="preserve">0.417230606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391053676605</t>
+    <t xml:space="preserve">0.413391023874283</t>
   </si>
   <si>
     <t xml:space="preserve">0.41595071554184</t>
@@ -671,73 +671,73 @@
     <t xml:space="preserve">0.421070158481598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551501274109</t>
+    <t xml:space="preserve">0.409551471471786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44026792049408</t>
+    <t xml:space="preserve">0.440267950296402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909710884094</t>
+    <t xml:space="preserve">0.424909651279449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984309911728</t>
+    <t xml:space="preserve">0.470984160900116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148417949677</t>
+    <t xml:space="preserve">0.435148537158966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40699177980423</t>
+    <t xml:space="preserve">0.406991839408875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189571619034</t>
+    <t xml:space="preserve">0.426189512014389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43130898475647</t>
+    <t xml:space="preserve">0.431308954954147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510466814041</t>
+    <t xml:space="preserve">0.418510437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405712008476257</t>
+    <t xml:space="preserve">0.405711978673935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111192941666</t>
+    <t xml:space="preserve">0.41211125254631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073938131332</t>
+    <t xml:space="preserve">0.38907390832901</t>
   </si>
   <si>
     <t xml:space="preserve">0.39035376906395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473182201385</t>
+    <t xml:space="preserve">0.395473152399063</t>
   </si>
   <si>
     <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988000154495</t>
+    <t xml:space="preserve">0.438988029956818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469372749329</t>
+    <t xml:space="preserve">0.427469432353973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4146708548069</t>
+    <t xml:space="preserve">0.414670914411545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872456073761</t>
+    <t xml:space="preserve">0.401872396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790297746658</t>
+    <t xml:space="preserve">0.419790357351303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271670341492</t>
+    <t xml:space="preserve">0.408271700143814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629850149155</t>
+    <t xml:space="preserve">0.423629939556122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596315383911</t>
+    <t xml:space="preserve">0.368596345186234</t>
   </si>
   <si>
     <t xml:space="preserve">0.37243589758873</t>
@@ -746,37 +746,37 @@
     <t xml:space="preserve">0.369876235723495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346838921308517</t>
+    <t xml:space="preserve">0.34683895111084</t>
   </si>
   <si>
     <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366036713123322</t>
+    <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363476991653442</t>
+    <t xml:space="preserve">0.36347696185112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678443908691</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999339103699</t>
+    <t xml:space="preserve">0.342999398708344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279229640961</t>
+    <t xml:space="preserve">0.344279199838638</t>
   </si>
   <si>
     <t xml:space="preserve">0.351958334445953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835141658783</t>
+    <t xml:space="preserve">0.378835171461105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913520336151</t>
+    <t xml:space="preserve">0.392913490533829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359637409448624</t>
+    <t xml:space="preserve">0.359637349843979</t>
   </si>
   <si>
     <t xml:space="preserve">0.367316484451294</t>
@@ -785,103 +785,103 @@
     <t xml:space="preserve">0.385234385728836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382674664258957</t>
+    <t xml:space="preserve">0.382674753665924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3801149725914</t>
+    <t xml:space="preserve">0.380114942789078</t>
   </si>
   <si>
     <t xml:space="preserve">0.391633659601212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39803284406662</t>
+    <t xml:space="preserve">0.398032814264297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592535734177</t>
+    <t xml:space="preserve">0.400592505931854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948781013489</t>
+    <t xml:space="preserve">0.431948810815811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348084688187</t>
+    <t xml:space="preserve">0.438348114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545787096024</t>
+    <t xml:space="preserve">0.457545846700668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945150375366</t>
+    <t xml:space="preserve">0.463945090770721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350805997849</t>
+    <t xml:space="preserve">0.472350835800171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200783252716</t>
+    <t xml:space="preserve">0.451200753450394</t>
   </si>
   <si>
     <t xml:space="preserve">0.437100768089294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000782728195</t>
+    <t xml:space="preserve">0.42300084233284</t>
   </si>
   <si>
     <t xml:space="preserve">0.433575809001923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44415083527565</t>
+    <t xml:space="preserve">0.444150865077972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675853967667</t>
+    <t xml:space="preserve">0.447675764560699</t>
   </si>
   <si>
     <t xml:space="preserve">0.440625756978989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525771617889</t>
+    <t xml:space="preserve">0.426525741815567</t>
   </si>
   <si>
     <t xml:space="preserve">0.408900737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475764036179</t>
+    <t xml:space="preserve">0.419475793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39480072259903</t>
+    <t xml:space="preserve">0.394800662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325741291046</t>
+    <t xml:space="preserve">0.398325711488724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425696849823</t>
+    <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050820112228</t>
+    <t xml:space="preserve">0.430050790309906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725801944733</t>
+    <t xml:space="preserve">0.45472577214241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800933837891</t>
+    <t xml:space="preserve">0.535800993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250820636749</t>
+    <t xml:space="preserve">0.458250850439072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300798416138</t>
+    <t xml:space="preserve">0.465300887823105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775749921799</t>
+    <t xml:space="preserve">0.461775809526443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375778675079</t>
+    <t xml:space="preserve">0.405375719070435</t>
   </si>
   <si>
     <t xml:space="preserve">0.40185073018074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750685214996</t>
+    <t xml:space="preserve">0.387750744819641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700677633286</t>
+    <t xml:space="preserve">0.38070073723793</t>
   </si>
   <si>
     <t xml:space="preserve">0.366600632667542</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.377175688743591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275674104691</t>
+    <t xml:space="preserve">0.391275733709335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650699853897</t>
+    <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
     <t xml:space="preserve">0.346860617399216</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">0.338400602340698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250579595566</t>
+    <t xml:space="preserve">0.317250549793243</t>
   </si>
   <si>
     <t xml:space="preserve">0.320070564746857</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">0.296100497245789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263670474290848</t>
+    <t xml:space="preserve">0.26367050409317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283410549163818</t>
+    <t xml:space="preserve">0.283410519361496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900466918945</t>
+    <t xml:space="preserve">0.267900496721268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770489454269</t>
+    <t xml:space="preserve">0.277770519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490429639816</t>
+    <t xml:space="preserve">0.266490519046783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800511360168</t>
+    <t xml:space="preserve">0.253800421953201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248160436749458</t>
+    <t xml:space="preserve">0.24816045165062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460526943207</t>
+    <t xml:space="preserve">0.290460467338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.291870534420013</t>
@@ -953,82 +953,82 @@
     <t xml:space="preserve">0.284820526838303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286230504512787</t>
+    <t xml:space="preserve">0.286230534315109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330549478531</t>
+    <t xml:space="preserve">0.300330579280853</t>
   </si>
   <si>
     <t xml:space="preserve">0.308790564537048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31443053483963</t>
+    <t xml:space="preserve">0.314430594444275</t>
   </si>
   <si>
     <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33135062456131</t>
+    <t xml:space="preserve">0.331350594758987</t>
   </si>
   <si>
     <t xml:space="preserve">0.325710564851761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680632352829</t>
+    <t xml:space="preserve">0.349680602550507</t>
   </si>
   <si>
     <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384225726127625</t>
+    <t xml:space="preserve">0.384225696325302</t>
   </si>
   <si>
     <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990654468536</t>
+    <t xml:space="preserve">0.336990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630624771118</t>
+    <t xml:space="preserve">0.342630684375763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025636196136</t>
+    <t xml:space="preserve">0.356025665998459</t>
   </si>
   <si>
     <t xml:space="preserve">0.351090639829636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530579805374</t>
+    <t xml:space="preserve">0.328530609607697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940587282181</t>
+    <t xml:space="preserve">0.329940617084503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327120631933212</t>
+    <t xml:space="preserve">0.327120572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300557374954</t>
+    <t xml:space="preserve">0.324300616979599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610579490662</t>
+    <t xml:space="preserve">0.311610549688339</t>
   </si>
   <si>
     <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31020051240921</t>
+    <t xml:space="preserve">0.310200542211533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150594234467</t>
+    <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
     <t xml:space="preserve">0.289050549268723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293280512094498</t>
+    <t xml:space="preserve">0.293280482292175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310504198074</t>
+    <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
     <t xml:space="preserve">0.272130489349365</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">0.265080451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720452070236</t>
+    <t xml:space="preserve">0.270720511674881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950504302979</t>
+    <t xml:space="preserve">0.274950444698334</t>
   </si>
   <si>
     <t xml:space="preserve">0.282000511884689</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">0.297510534524918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301740527153015</t>
+    <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690519571304</t>
+    <t xml:space="preserve">0.294690549373627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437587022781372</t>
+    <t xml:space="preserve">0.43758699297905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879097223282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363658666611</t>
+    <t xml:space="preserve">0.395363718271255</t>
   </si>
   <si>
     <t xml:space="preserve">0.38384822010994</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">0.37002968788147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38768669962883</t>
+    <t xml:space="preserve">0.387686729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777448415756</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565073728561</t>
+    <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
     <t xml:space="preserve">0.356211155653</t>
@@ -1091,94 +1091,94 @@
     <t xml:space="preserve">0.350069582462311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534166812897</t>
+    <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463424921036</t>
+    <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
     <t xml:space="preserve">0.359281957149506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140354156494</t>
+    <t xml:space="preserve">0.353140413761139</t>
   </si>
   <si>
     <t xml:space="preserve">0.357746571302414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
     <t xml:space="preserve">0.340857237577438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675769805908</t>
+    <t xml:space="preserve">0.354675740003586</t>
   </si>
   <si>
     <t xml:space="preserve">0.44526395201683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394595384598</t>
+    <t xml:space="preserve">0.418394565582275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46061784029007</t>
+    <t xml:space="preserve">0.460617959499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940851449966</t>
+    <t xml:space="preserve">0.452940881252289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102371931076</t>
+    <t xml:space="preserve">0.449102401733398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233045101166</t>
+    <t xml:space="preserve">0.422233104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717606544495</t>
+    <t xml:space="preserve">0.410717636346817</t>
   </si>
   <si>
     <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391525238752365</t>
+    <t xml:space="preserve">0.391525208950043</t>
   </si>
   <si>
     <t xml:space="preserve">0.403040587902069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556115865707</t>
+    <t xml:space="preserve">0.41455614566803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379242032766342</t>
+    <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100489377975</t>
+    <t xml:space="preserve">0.37310054898262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817313194275</t>
+    <t xml:space="preserve">0.360817342996597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351605027914047</t>
+    <t xml:space="preserve">0.351604968309402</t>
   </si>
   <si>
     <t xml:space="preserve">0.346998810768127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706617116928</t>
+    <t xml:space="preserve">0.37770664691925</t>
   </si>
   <si>
     <t xml:space="preserve">0.366958886384964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374635875225067</t>
+    <t xml:space="preserve">0.37463590502739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423530340195</t>
+    <t xml:space="preserve">0.365423500537872</t>
   </si>
   <si>
     <t xml:space="preserve">0.322432488203049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305543214082718</t>
+    <t xml:space="preserve">0.305543184280396</t>
   </si>
   <si>
     <t xml:space="preserve">0.30707859992981</t>
@@ -1187,52 +1187,52 @@
     <t xml:space="preserve">0.323967903852463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503289699554</t>
+    <t xml:space="preserve">0.325503319501877</t>
   </si>
   <si>
     <t xml:space="preserve">0.330109506845474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180248737335</t>
+    <t xml:space="preserve">0.33318030834198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251020431519</t>
+    <t xml:space="preserve">0.336251050233841</t>
   </si>
   <si>
     <t xml:space="preserve">0.337786436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928039073944</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715664386749</t>
+    <t xml:space="preserve">0.334715634584427</t>
   </si>
   <si>
     <t xml:space="preserve">0.314755588769913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220173120499</t>
+    <t xml:space="preserve">0.313220202922821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308613955974579</t>
+    <t xml:space="preserve">0.308613985776901</t>
   </si>
   <si>
     <t xml:space="preserve">0.319361686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328574120998383</t>
+    <t xml:space="preserve">0.32857409119606</t>
   </si>
   <si>
     <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328171879053116</t>
+    <t xml:space="preserve">0.328171938657761</t>
   </si>
   <si>
     <t xml:space="preserve">0.320128470659256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324954569339752</t>
+    <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
     <t xml:space="preserve">0.337823987007141</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">0.326563239097595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329780608415604</t>
+    <t xml:space="preserve">0.329780638217926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519771099091</t>
+    <t xml:space="preserve">0.318519741296768</t>
   </si>
   <si>
     <t xml:space="preserve">0.308867692947388</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">0.297606855630875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307258993387222</t>
+    <t xml:space="preserve">0.3072589635849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737229824066</t>
+    <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
     <t xml:space="preserve">0.305650323629379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041594266891</t>
+    <t xml:space="preserve">0.304041653871536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998156070709</t>
+    <t xml:space="preserve">0.295998185873032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287954747676849</t>
+    <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
     <t xml:space="preserve">0.292780816555023</t>
@@ -1280,43 +1280,43 @@
     <t xml:space="preserve">0.284737408161163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281519949436188</t>
+    <t xml:space="preserve">0.281520009040833</t>
   </si>
   <si>
     <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085270404816</t>
+    <t xml:space="preserve">0.27508533000946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346107721329</t>
+    <t xml:space="preserve">0.286346048116684</t>
   </si>
   <si>
     <t xml:space="preserve">0.276693969964981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563447237015</t>
+    <t xml:space="preserve">0.289563417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
     <t xml:space="preserve">0.300824254751205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432954311371</t>
+    <t xml:space="preserve">0.302432924509048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693732023239</t>
+    <t xml:space="preserve">0.313693702220917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294389516115189</t>
+    <t xml:space="preserve">0.294389486312866</t>
   </si>
   <si>
     <t xml:space="preserve">0.352302193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258785247803</t>
+    <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
     <t xml:space="preserve">0.345867484807968</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">0.341041415929794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650085687637</t>
+    <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
     <t xml:space="preserve">0.300703555345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297227174043655</t>
+    <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
     <t xml:space="preserve">0.29548904299736</t>
@@ -1346,31 +1346,31 @@
     <t xml:space="preserve">0.290274530649185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29201266169548</t>
+    <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30591806769371</t>
+    <t xml:space="preserve">0.305918037891388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30417987704277</t>
+    <t xml:space="preserve">0.304179847240448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536339998245</t>
+    <t xml:space="preserve">0.288536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283321857452393</t>
+    <t xml:space="preserve">0.28332182765007</t>
   </si>
   <si>
     <t xml:space="preserve">0.293750882148743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285059988498688</t>
+    <t xml:space="preserve">0.28506001830101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278107315301895</t>
+    <t xml:space="preserve">0.278107285499573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281583666801453</t>
+    <t xml:space="preserve">0.28158363699913</t>
   </si>
   <si>
     <t xml:space="preserve">0.27463099360466</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">0.309394389390945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965394496918</t>
+    <t xml:space="preserve">0.298965364694595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656228542328</t>
+    <t xml:space="preserve">0.30765625834465</t>
   </si>
   <si>
     <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870740890503</t>
+    <t xml:space="preserve">0.312870770692825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252438783646</t>
+    <t xml:space="preserve">0.330252468585968</t>
   </si>
   <si>
     <t xml:space="preserve">0.325037956237793</t>
@@ -1412,46 +1412,46 @@
     <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823414087296</t>
+    <t xml:space="preserve">0.319823384284973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085223436356</t>
+    <t xml:space="preserve">0.318085283041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316347062587738</t>
+    <t xml:space="preserve">0.31634709239006</t>
   </si>
   <si>
     <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254995822906</t>
+    <t xml:space="preserve">0.305254966020584</t>
   </si>
   <si>
     <t xml:space="preserve">0.301705479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804392814636</t>
+    <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
     <t xml:space="preserve">0.294606506824493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831808328629</t>
+    <t xml:space="preserve">0.292831838130951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480237722397</t>
+    <t xml:space="preserve">0.303480207920074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233953952789</t>
+    <t xml:space="preserve">0.319233924150467</t>
   </si>
   <si>
     <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308350950479507</t>
+    <t xml:space="preserve">0.30835098028183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311978667974472</t>
+    <t xml:space="preserve">0.31197863817215</t>
   </si>
   <si>
     <t xml:space="preserve">0.306537181138992</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">0.292026519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293840348720551</t>
+    <t xml:space="preserve">0.293840318918228</t>
   </si>
   <si>
     <t xml:space="preserve">0.29565417766571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304723292589188</t>
+    <t xml:space="preserve">0.30472332239151</t>
   </si>
   <si>
     <t xml:space="preserve">0.299281865358353</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">0.288398861885071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771233797073</t>
+    <t xml:space="preserve">0.284771203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585032939911</t>
+    <t xml:space="preserve">0.286585062742233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297467976808548</t>
+    <t xml:space="preserve">0.29746800661087</t>
   </si>
   <si>
     <t xml:space="preserve">0.300716459751129</t>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178759455681</t>
+    <t xml:space="preserve">0.179178774356842</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020246386528</t>
+    <t xml:space="preserve">0.167020231485367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17277954518795</t>
+    <t xml:space="preserve">0.172779574990273</t>
   </si>
   <si>
     <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902723073959</t>
+    <t xml:space="preserve">0.145902708172798</t>
   </si>
   <si>
     <t xml:space="preserve">0.152493953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822484374046</t>
+    <t xml:space="preserve">0.147822499275208</t>
   </si>
   <si>
     <t xml:space="preserve">0.155501589179039</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">0.156141504645348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517812490463</t>
+    <t xml:space="preserve">0.153517827391624</t>
   </si>
   <si>
     <t xml:space="preserve">0.149102345108986</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">0.142383143305779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063200473785</t>
+    <t xml:space="preserve">0.142063170671463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447113990784</t>
+    <t xml:space="preserve">0.142447128891945</t>
   </si>
   <si>
     <t xml:space="preserve">0.144622877240181</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">0.141423255205154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15383780002594</t>
+    <t xml:space="preserve">0.153837814927101</t>
   </si>
   <si>
     <t xml:space="preserve">0.173419460654259</t>
@@ -107,49 +107,49 @@
     <t xml:space="preserve">0.16983588039875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380286216736</t>
+    <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981071949005</t>
+    <t xml:space="preserve">0.159981057047844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421380281448</t>
+    <t xml:space="preserve">0.157421350479126</t>
   </si>
   <si>
     <t xml:space="preserve">0.152301967144012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158509224653244</t>
+    <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
     <t xml:space="preserve">0.163820594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836832761765</t>
+    <t xml:space="preserve">0.161836847662926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522605776787</t>
+    <t xml:space="preserve">0.180522635579109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18045862019062</t>
+    <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
     <t xml:space="preserve">0.174059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168939992785454</t>
+    <t xml:space="preserve">0.168939977884293</t>
   </si>
   <si>
     <t xml:space="preserve">0.191977292299271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19613678753376</t>
+    <t xml:space="preserve">0.196136757731438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176899433136</t>
+    <t xml:space="preserve">0.195176869630814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497794628143</t>
+    <t xml:space="preserve">0.187497809529305</t>
   </si>
   <si>
     <t xml:space="preserve">0.184938132762909</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">0.204775750637054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454855442047</t>
+    <t xml:space="preserve">0.212454870343208</t>
   </si>
   <si>
     <t xml:space="preserve">0.204711750149727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20029628276825</t>
+    <t xml:space="preserve">0.200296312570572</t>
   </si>
   <si>
     <t xml:space="preserve">0.197736576199532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18237841129303</t>
+    <t xml:space="preserve">0.182378396391869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578033328056</t>
+    <t xml:space="preserve">0.185578003525734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907531261444</t>
+    <t xml:space="preserve">0.172907546162605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499714255333</t>
+    <t xml:space="preserve">0.171499699354172</t>
   </si>
   <si>
     <t xml:space="preserve">0.165740385651588</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">0.154349729418755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579938054085</t>
+    <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917056560516</t>
+    <t xml:space="preserve">0.159917086362839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154861658811569</t>
+    <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
     <t xml:space="preserve">0.156781435012817</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417585730553</t>
+    <t xml:space="preserve">0.189417570829391</t>
   </si>
   <si>
     <t xml:space="preserve">0.191337332129478</t>
@@ -215,67 +215,67 @@
     <t xml:space="preserve">0.185002073645592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170219838619232</t>
+    <t xml:space="preserve">0.170219853520393</t>
   </si>
   <si>
     <t xml:space="preserve">0.163180693984032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742275476456</t>
+    <t xml:space="preserve">0.149742290377617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221728444099</t>
+    <t xml:space="preserve">0.154221713542938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022136211395</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14718259871006</t>
+    <t xml:space="preserve">0.147182568907738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260917782784</t>
+    <t xml:space="preserve">0.161260902881622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168172091245651</t>
+    <t xml:space="preserve">0.168172106146812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739433288574</t>
+    <t xml:space="preserve">0.173739418387413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339251756668</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
     <t xml:space="preserve">0.185897976160049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135850071907</t>
+    <t xml:space="preserve">0.204135864973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096660733223</t>
+    <t xml:space="preserve">0.197096675634384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181354522705078</t>
+    <t xml:space="preserve">0.181354507803917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194217026233673</t>
+    <t xml:space="preserve">0.194216996431351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204647749662399</t>
+    <t xml:space="preserve">0.204647779464722</t>
   </si>
   <si>
     <t xml:space="preserve">0.198376506567001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240870118141</t>
+    <t xml:space="preserve">0.195240885019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495919704437</t>
+    <t xml:space="preserve">0.203495904803276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934323310852</t>
+    <t xml:space="preserve">0.216934308409691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22070986032486</t>
+    <t xml:space="preserve">0.220709875226021</t>
   </si>
   <si>
     <t xml:space="preserve">0.23677197098732</t>
@@ -290,223 +290,223 @@
     <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28028678894043</t>
+    <t xml:space="preserve">0.280286848545074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644968748093</t>
+    <t xml:space="preserve">0.295644998550415</t>
   </si>
   <si>
     <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262368977069855</t>
+    <t xml:space="preserve">0.26236891746521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2648646235466</t>
+    <t xml:space="preserve">0.264864653348923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753857851028</t>
+    <t xml:space="preserve">0.254753828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25468984246254</t>
+    <t xml:space="preserve">0.254689782857895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24720273911953</t>
+    <t xml:space="preserve">0.247202724218369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650682926178</t>
+    <t xml:space="preserve">0.2476507127285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778654098511</t>
+    <t xml:space="preserve">0.247778683900833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572348952293</t>
+    <t xml:space="preserve">0.233572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238051801919937</t>
+    <t xml:space="preserve">0.238051816821098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374616742134</t>
+    <t xml:space="preserve">0.214374631643295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663035511971</t>
+    <t xml:space="preserve">0.210663065314293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654477477074</t>
+    <t xml:space="preserve">0.215654447674751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518826127052</t>
+    <t xml:space="preserve">0.212518811225891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891399025917</t>
+    <t xml:space="preserve">0.241891369223595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570444226265</t>
+    <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980151057243</t>
+    <t xml:space="preserve">0.234980165958405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652587652206</t>
+    <t xml:space="preserve">0.231652572751045</t>
   </si>
   <si>
     <t xml:space="preserve">0.239971593022346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372786521912</t>
+    <t xml:space="preserve">0.230372741818428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173045277596</t>
+    <t xml:space="preserve">0.227173089981079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773845911026</t>
+    <t xml:space="preserve">0.220773860812187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405173540115</t>
+    <t xml:space="preserve">0.226405203342438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21699832379818</t>
+    <t xml:space="preserve">0.216998353600502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204839751124382</t>
+    <t xml:space="preserve">0.20483972132206</t>
   </si>
   <si>
     <t xml:space="preserve">0.20797535777092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535079240799</t>
+    <t xml:space="preserve">0.210535064339638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.209895133972168</t>
+    <t xml:space="preserve">0.20989516377449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211174964904785</t>
+    <t xml:space="preserve">0.21117502450943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582856416702</t>
+    <t xml:space="preserve">0.21258282661438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782433748245</t>
+    <t xml:space="preserve">0.215782448649406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732796549797</t>
+    <t xml:space="preserve">0.229732781648636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845466971397</t>
+    <t xml:space="preserve">0.223845481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805384874344</t>
+    <t xml:space="preserve">0.224805399775505</t>
   </si>
   <si>
     <t xml:space="preserve">0.23363633453846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627761602402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22858090698719</t>
+    <t xml:space="preserve">0.228580936789513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973512649536</t>
+    <t xml:space="preserve">0.223973482847214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717540502548</t>
+    <t xml:space="preserve">0.223717495799065</t>
   </si>
   <si>
     <t xml:space="preserve">0.220837816596031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23549211025238</t>
+    <t xml:space="preserve">0.235492095351219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22096586227417</t>
+    <t xml:space="preserve">0.220965817570686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365106344223</t>
+    <t xml:space="preserve">0.227365091443062</t>
   </si>
   <si>
     <t xml:space="preserve">0.302556157112122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357518911362</t>
+    <t xml:space="preserve">0.358357548713684</t>
   </si>
   <si>
     <t xml:space="preserve">0.47354394197464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454313755035</t>
+    <t xml:space="preserve">0.555454254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48570254445076</t>
+    <t xml:space="preserve">0.485702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444747298955917</t>
+    <t xml:space="preserve">0.44474732875824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709166288376</t>
+    <t xml:space="preserve">0.429709136486053</t>
   </si>
   <si>
     <t xml:space="preserve">0.403152257204056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371156066656113</t>
+    <t xml:space="preserve">0.371156007051468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710103750229</t>
+    <t xml:space="preserve">0.421710073947906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035686254501</t>
+    <t xml:space="preserve">0.374035745859146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754888057709</t>
+    <t xml:space="preserve">0.380754977464676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352598279714584</t>
+    <t xml:space="preserve">0.352598249912262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331800669431686</t>
+    <t xml:space="preserve">0.331800699234009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602059364319</t>
+    <t xml:space="preserve">0.320602029561996</t>
   </si>
   <si>
     <t xml:space="preserve">0.33244064450264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340439677238464</t>
+    <t xml:space="preserve">0.340439707040787</t>
   </si>
   <si>
     <t xml:space="preserve">0.327641189098358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157941579819</t>
+    <t xml:space="preserve">0.355157911777496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478866577148</t>
+    <t xml:space="preserve">0.347478836774826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760572433472</t>
+    <t xml:space="preserve">0.332760602235794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121654033661</t>
+    <t xml:space="preserve">0.324121624231339</t>
   </si>
   <si>
     <t xml:space="preserve">0.327001243829727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33915987610817</t>
+    <t xml:space="preserve">0.339159816503525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960209369659</t>
+    <t xml:space="preserve">0.335960179567337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161721229553</t>
+    <t xml:space="preserve">0.323161780834198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200880765915</t>
+    <t xml:space="preserve">0.33020082116127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31996214389801</t>
+    <t xml:space="preserve">0.319962114095688</t>
   </si>
   <si>
     <t xml:space="preserve">0.317402392625809</t>
@@ -518,25 +518,25 @@
     <t xml:space="preserve">0.323801666498184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521835565567</t>
+    <t xml:space="preserve">0.322521805763245</t>
   </si>
   <si>
     <t xml:space="preserve">0.334360361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328921049833298</t>
+    <t xml:space="preserve">0.32892107963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040492773056</t>
+    <t xml:space="preserve">0.334040462970734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163596153259</t>
+    <t xml:space="preserve">0.307163685560226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122561693192</t>
+    <t xml:space="preserve">0.316122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698521375656</t>
+    <t xml:space="preserve">0.316698491573334</t>
   </si>
   <si>
     <t xml:space="preserve">0.326361387968063</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36475682258606</t>
+    <t xml:space="preserve">0.364756792783737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3455590903759</t>
+    <t xml:space="preserve">0.345559149980545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199005842209</t>
+    <t xml:space="preserve">0.346198976039886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081557035446</t>
+    <t xml:space="preserve">0.325081527233124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959301710129</t>
+    <t xml:space="preserve">0.343959331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282101631165</t>
+    <t xml:space="preserve">0.32028204202652</t>
   </si>
   <si>
     <t xml:space="preserve">0.333720475435257</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.396753013134003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275479793549</t>
+    <t xml:space="preserve">0.376275420188904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37563556432724</t>
+    <t xml:space="preserve">0.375635534524918</t>
   </si>
   <si>
     <t xml:space="preserve">0.376915365457535</t>
@@ -581,94 +581,94 @@
     <t xml:space="preserve">0.370196133852005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555280923843</t>
+    <t xml:space="preserve">0.377555251121521</t>
   </si>
   <si>
     <t xml:space="preserve">0.35131847858429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117904186249</t>
+    <t xml:space="preserve">0.356117844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917240381241</t>
+    <t xml:space="preserve">0.360917270183563</t>
   </si>
   <si>
     <t xml:space="preserve">0.373715758323669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39579313993454</t>
+    <t xml:space="preserve">0.395793110132217</t>
   </si>
   <si>
     <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594470262527</t>
+    <t xml:space="preserve">0.384594410657883</t>
   </si>
   <si>
     <t xml:space="preserve">0.383954584598541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193321466446</t>
+    <t xml:space="preserve">0.394193351268768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274482727051</t>
+    <t xml:space="preserve">0.384274452924728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310800075531</t>
+    <t xml:space="preserve">0.415310829877853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42234992980957</t>
+    <t xml:space="preserve">0.42235004901886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312674999237</t>
+    <t xml:space="preserve">0.399312734603882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634597063065</t>
+    <t xml:space="preserve">0.38363453745842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39355343580246</t>
+    <t xml:space="preserve">0.393553376197815</t>
   </si>
   <si>
     <t xml:space="preserve">0.479943186044693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447306990623474</t>
+    <t xml:space="preserve">0.447307020425797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745573043823</t>
+    <t xml:space="preserve">0.460745483636856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547691822052</t>
+    <t xml:space="preserve">0.441547721624374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027129888535</t>
+    <t xml:space="preserve">0.446027219295502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346090555191</t>
+    <t xml:space="preserve">0.454346179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447947025299072</t>
+    <t xml:space="preserve">0.447946965694427</t>
   </si>
   <si>
     <t xml:space="preserve">0.430029094219208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588785886765</t>
+    <t xml:space="preserve">0.432588815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749233484268</t>
+    <t xml:space="preserve">0.428749263286591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230635881424</t>
+    <t xml:space="preserve">0.417230576276779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391053676605</t>
+    <t xml:space="preserve">0.41339111328125</t>
   </si>
   <si>
     <t xml:space="preserve">0.41595071554184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070158481598</t>
+    <t xml:space="preserve">0.421070128679276</t>
   </si>
   <si>
     <t xml:space="preserve">0.409551501274109</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">0.440267890691757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909710884094</t>
+    <t xml:space="preserve">0.424909740686417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984220504761</t>
+    <t xml:space="preserve">0.470984190702438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148507356644</t>
+    <t xml:space="preserve">0.435148417949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406991839408875</t>
+    <t xml:space="preserve">0.406991809606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189631223679</t>
+    <t xml:space="preserve">0.426189541816711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431308954954147</t>
+    <t xml:space="preserve">0.431308895349503</t>
   </si>
   <si>
     <t xml:space="preserve">0.418510407209396</t>
@@ -701,19 +701,19 @@
     <t xml:space="preserve">0.405711948871613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111222743988</t>
+    <t xml:space="preserve">0.412111133337021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073938131332</t>
+    <t xml:space="preserve">0.389073967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390353798866272</t>
+    <t xml:space="preserve">0.390353739261627</t>
   </si>
   <si>
     <t xml:space="preserve">0.395473152399063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831362009048</t>
+    <t xml:space="preserve">0.410831391811371</t>
   </si>
   <si>
     <t xml:space="preserve">0.438988000154495</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">0.427469402551651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670944213867</t>
+    <t xml:space="preserve">0.4146708548069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872366666794</t>
+    <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790267944336</t>
+    <t xml:space="preserve">0.419790327548981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271700143814</t>
+    <t xml:space="preserve">0.408271729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629850149155</t>
+    <t xml:space="preserve">0.42362979054451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596315383911</t>
+    <t xml:space="preserve">0.368596345186234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435867786407</t>
+    <t xml:space="preserve">0.37243589758873</t>
   </si>
   <si>
     <t xml:space="preserve">0.369876265525818</t>
@@ -749,37 +749,37 @@
     <t xml:space="preserve">0.346838921308517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335320353507996</t>
+    <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
     <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36347696185112</t>
+    <t xml:space="preserve">0.363476932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678503513336</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999428510666</t>
+    <t xml:space="preserve">0.342999398708344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279259443283</t>
+    <t xml:space="preserve">0.344279199838638</t>
   </si>
   <si>
     <t xml:space="preserve">0.351958304643631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835171461105</t>
+    <t xml:space="preserve">0.378835141658783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913490533829</t>
+    <t xml:space="preserve">0.392913579940796</t>
   </si>
   <si>
     <t xml:space="preserve">0.359637439250946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316484451294</t>
+    <t xml:space="preserve">0.367316544055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.385234385728836</t>
@@ -788,100 +788,100 @@
     <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380115032196045</t>
+    <t xml:space="preserve">0.380115002393723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633599996567</t>
+    <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032873868942</t>
+    <t xml:space="preserve">0.39803284406662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592565536499</t>
+    <t xml:space="preserve">0.400592625141144</t>
   </si>
   <si>
     <t xml:space="preserve">0.431948840618134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348054885864</t>
+    <t xml:space="preserve">0.438348114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545787096024</t>
+    <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945031166077</t>
+    <t xml:space="preserve">0.463945090770721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350835800171</t>
+    <t xml:space="preserve">0.472350865602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200813055038</t>
+    <t xml:space="preserve">0.451200783252716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100827693939</t>
+    <t xml:space="preserve">0.437100738286972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000812530518</t>
+    <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4335757791996</t>
+    <t xml:space="preserve">0.433575749397278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150805473328</t>
+    <t xml:space="preserve">0.444150775671005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675824165344</t>
+    <t xml:space="preserve">0.447675794363022</t>
   </si>
   <si>
     <t xml:space="preserve">0.440625756978989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525831222534</t>
+    <t xml:space="preserve">0.426525771617889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900737762451</t>
+    <t xml:space="preserve">0.408900678157806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475734233856</t>
+    <t xml:space="preserve">0.419475823640823</t>
   </si>
   <si>
     <t xml:space="preserve">0.394800662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325711488724</t>
+    <t xml:space="preserve">0.398325741291046</t>
   </si>
   <si>
     <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050790309906</t>
+    <t xml:space="preserve">0.430050730705261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725801944733</t>
+    <t xml:space="preserve">0.454725831747055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800874233246</t>
+    <t xml:space="preserve">0.535800993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250790834427</t>
+    <t xml:space="preserve">0.458250761032104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46530082821846</t>
+    <t xml:space="preserve">0.465300887823105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775809526443</t>
+    <t xml:space="preserve">0.461775839328766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375748872757</t>
+    <t xml:space="preserve">0.405375719070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850700378418</t>
+    <t xml:space="preserve">0.401850670576096</t>
   </si>
   <si>
     <t xml:space="preserve">0.387750685214996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700647830963</t>
+    <t xml:space="preserve">0.38070073723793</t>
   </si>
   <si>
     <t xml:space="preserve">0.366600662469864</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">0.377175718545914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275703907013</t>
+    <t xml:space="preserve">0.391275674104691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650670051575</t>
+    <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860617399216</t>
+    <t xml:space="preserve">0.346860587596893</t>
   </si>
   <si>
     <t xml:space="preserve">0.345450609922409</t>
@@ -908,40 +908,40 @@
     <t xml:space="preserve">0.352500647306442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400572538376</t>
+    <t xml:space="preserve">0.338400661945343</t>
   </si>
   <si>
     <t xml:space="preserve">0.317250579595566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320070534944534</t>
+    <t xml:space="preserve">0.320070594549179</t>
   </si>
   <si>
     <t xml:space="preserve">0.296100527048111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263670474290848</t>
+    <t xml:space="preserve">0.26367050409317</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900437116623</t>
+    <t xml:space="preserve">0.267900496721268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770519256592</t>
+    <t xml:space="preserve">0.277770489454269</t>
   </si>
   <si>
     <t xml:space="preserve">0.266490489244461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570414423943</t>
+    <t xml:space="preserve">0.249570444226265</t>
   </si>
   <si>
     <t xml:space="preserve">0.253800481557846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24816045165062</t>
+    <t xml:space="preserve">0.248160436749458</t>
   </si>
   <si>
     <t xml:space="preserve">0.290460526943207</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.291870534420013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360511779785</t>
+    <t xml:space="preserve">0.276360481977463</t>
   </si>
   <si>
     <t xml:space="preserve">0.284820526838303</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330519676208</t>
+    <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
     <t xml:space="preserve">0.308790594339371</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">0.314430564641953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040602445602</t>
+    <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
     <t xml:space="preserve">0.331350564956665</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370125651359558</t>
+    <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
     <t xml:space="preserve">0.384225696325302</t>
@@ -989,64 +989,64 @@
     <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990594863892</t>
+    <t xml:space="preserve">0.336990624666214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630594968796</t>
+    <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025665998459</t>
+    <t xml:space="preserve">0.356025636196136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090639829636</t>
+    <t xml:space="preserve">0.351090669631958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530579805374</t>
+    <t xml:space="preserve">0.328530609607697</t>
   </si>
   <si>
     <t xml:space="preserve">0.329940617084503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327120572328568</t>
+    <t xml:space="preserve">0.32712060213089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300616979599</t>
+    <t xml:space="preserve">0.324300557374954</t>
   </si>
   <si>
     <t xml:space="preserve">0.311610549688339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322890609502792</t>
+    <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
     <t xml:space="preserve">0.310200572013855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150534629822</t>
+    <t xml:space="preserve">0.303150504827499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289050549268723</t>
+    <t xml:space="preserve">0.2890505194664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293280512094498</t>
+    <t xml:space="preserve">0.29328054189682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310474395752</t>
+    <t xml:space="preserve">0.269310504198074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130489349365</t>
+    <t xml:space="preserve">0.272130459547043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265080481767654</t>
+    <t xml:space="preserve">0.26508042216301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720511674881</t>
+    <t xml:space="preserve">0.270720481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950474500656</t>
+    <t xml:space="preserve">0.274950504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000482082367</t>
+    <t xml:space="preserve">0.282000511884689</t>
   </si>
   <si>
     <t xml:space="preserve">0.297510534524918</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">0.437586963176727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879067420959</t>
   </si>
   <si>
     <t xml:space="preserve">0.395363658666611</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">0.383848249912262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368494272232056</t>
+    <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171261072159</t>
+    <t xml:space="preserve">0.376171231269836</t>
   </si>
   <si>
     <t xml:space="preserve">0.37002968788147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387686729431152</t>
+    <t xml:space="preserve">0.38768669962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777448415756</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
     <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211155653</t>
+    <t xml:space="preserve">0.356211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069552659988</t>
+    <t xml:space="preserve">0.350069582462311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534166812897</t>
+    <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
     <t xml:space="preserve">0.345463424921036</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">0.359281957149506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140413761139</t>
+    <t xml:space="preserve">0.353140354156494</t>
   </si>
   <si>
     <t xml:space="preserve">0.357746541500092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857237577438</t>
+    <t xml:space="preserve">0.340857207775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675740003586</t>
+    <t xml:space="preserve">0.354675769805908</t>
   </si>
   <si>
     <t xml:space="preserve">0.44526395201683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394565582275</t>
+    <t xml:space="preserve">0.41839462518692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617929697037</t>
+    <t xml:space="preserve">0.46061784029007</t>
   </si>
   <si>
     <t xml:space="preserve">0.452940881252289</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">0.449102431535721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233045101166</t>
+    <t xml:space="preserve">0.422233074903488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717636346817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202167987823</t>
+    <t xml:space="preserve">0.399202108383179</t>
   </si>
   <si>
     <t xml:space="preserve">0.391525208950043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040617704391</t>
+    <t xml:space="preserve">0.403040558099747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556056261063</t>
+    <t xml:space="preserve">0.41455614566803</t>
   </si>
   <si>
     <t xml:space="preserve">0.379242062568665</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">0.373100459575653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817313194275</t>
+    <t xml:space="preserve">0.360817342996597</t>
   </si>
   <si>
     <t xml:space="preserve">0.351604998111725</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">0.37770664691925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958886384964</t>
+    <t xml:space="preserve">0.366958916187286</t>
   </si>
   <si>
     <t xml:space="preserve">0.374635845422745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423560142517</t>
+    <t xml:space="preserve">0.365423530340195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432518005371</t>
+    <t xml:space="preserve">0.322432488203049</t>
   </si>
   <si>
     <t xml:space="preserve">0.305543184280396</t>
@@ -1196,25 +1196,25 @@
     <t xml:space="preserve">0.330109477043152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180278539658</t>
+    <t xml:space="preserve">0.333180248737335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251080036163</t>
+    <t xml:space="preserve">0.336251020431519</t>
   </si>
   <si>
     <t xml:space="preserve">0.337786465883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928039073944</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715634584427</t>
+    <t xml:space="preserve">0.334715664386749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314755588769913</t>
+    <t xml:space="preserve">0.314755529165268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220173120499</t>
+    <t xml:space="preserve">0.313220113515854</t>
   </si>
   <si>
     <t xml:space="preserve">0.308613985776901</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328171908855438</t>
+    <t xml:space="preserve">0.328171849250793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128440856934</t>
+    <t xml:space="preserve">0.320128411054611</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337824016809464</t>
+    <t xml:space="preserve">0.337823987007141</t>
   </si>
   <si>
     <t xml:space="preserve">0.339432716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326563239097595</t>
+    <t xml:space="preserve">0.326563268899918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329780608415604</t>
+    <t xml:space="preserve">0.329780548810959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519800901413</t>
+    <t xml:space="preserve">0.318519830703735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30886772274971</t>
+    <t xml:space="preserve">0.308867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606855630875</t>
+    <t xml:space="preserve">0.297606885433197</t>
   </si>
   <si>
     <t xml:space="preserve">0.307258993387222</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650264024734</t>
+    <t xml:space="preserve">0.305650293827057</t>
   </si>
   <si>
     <t xml:space="preserve">0.304041624069214</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780786752701</t>
+    <t xml:space="preserve">0.292780816555023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737378358841</t>
+    <t xml:space="preserve">0.284737408161163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281520009040833</t>
+    <t xml:space="preserve">0.28151997923851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128708600998</t>
+    <t xml:space="preserve">0.283128678798676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085240602493</t>
+    <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
     <t xml:space="preserve">0.286346107721329</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">0.276693969964981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563477039337</t>
+    <t xml:space="preserve">0.289563447237015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
     <t xml:space="preserve">0.300824254751205</t>
@@ -1316,34 +1316,34 @@
     <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302193641663</t>
+    <t xml:space="preserve">0.352302134037018</t>
   </si>
   <si>
     <t xml:space="preserve">0.344258725643158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867425203323</t>
+    <t xml:space="preserve">0.345867455005646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347476124763489</t>
+    <t xml:space="preserve">0.347476154565811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341041386127472</t>
+    <t xml:space="preserve">0.341041415929794</t>
   </si>
   <si>
     <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
     <t xml:space="preserve">0.300703525543213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297227203845978</t>
+    <t xml:space="preserve">0.2972272336483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295489013195038</t>
+    <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
     <t xml:space="preserve">0.290274530649185</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305918097496033</t>
+    <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
     <t xml:space="preserve">0.304179906845093</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">0.288536339998245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283321857452393</t>
+    <t xml:space="preserve">0.28332182765007</t>
   </si>
   <si>
     <t xml:space="preserve">0.29375085234642</t>
@@ -1379,31 +1379,31 @@
     <t xml:space="preserve">0.27463099360466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286798179149628</t>
+    <t xml:space="preserve">0.28679820895195</t>
   </si>
   <si>
     <t xml:space="preserve">0.279845535755157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2763691842556</t>
+    <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27289280295372</t>
+    <t xml:space="preserve">0.272892773151398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394419193268</t>
+    <t xml:space="preserve">0.30939444899559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965394496918</t>
+    <t xml:space="preserve">0.298965364694595</t>
   </si>
   <si>
     <t xml:space="preserve">0.307656198740005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132609844208</t>
+    <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870770692825</t>
+    <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
     <t xml:space="preserve">0.330252438783646</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823414087296</t>
+    <t xml:space="preserve">0.319823384284973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085253238678</t>
+    <t xml:space="preserve">0.318085223436356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316347062587738</t>
+    <t xml:space="preserve">0.316347122192383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315903395414352</t>
+    <t xml:space="preserve">0.315903425216675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254995822906</t>
+    <t xml:space="preserve">0.305254966020584</t>
   </si>
   <si>
     <t xml:space="preserve">0.301705479621887</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">0.294606506824493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831778526306</t>
+    <t xml:space="preserve">0.292831808328629</t>
   </si>
   <si>
     <t xml:space="preserve">0.303480237722397</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">0.30653715133667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026519775391</t>
+    <t xml:space="preserve">0.292026489973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293840378522873</t>
+    <t xml:space="preserve">0.293840348720551</t>
   </si>
   <si>
     <t xml:space="preserve">0.29565417766571</t>
@@ -1472,28 +1472,28 @@
     <t xml:space="preserve">0.30472332239151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299281805753708</t>
+    <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290212661027908</t>
+    <t xml:space="preserve">0.290212690830231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398861885071</t>
+    <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771233797073</t>
+    <t xml:space="preserve">0.284771203994751</t>
   </si>
   <si>
     <t xml:space="preserve">0.286585032939911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29746800661087</t>
+    <t xml:space="preserve">0.297468036413193</t>
   </si>
   <si>
     <t xml:space="preserve">0.300716459751129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147657394409</t>
+    <t xml:space="preserve">0.295147627592087</t>
   </si>
   <si>
     <t xml:space="preserve">0.308141559362411</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334129422903061</t>
+    <t xml:space="preserve">0.334129452705383</t>
   </si>
   <si>
     <t xml:space="preserve">0.337841957807541</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">0.339698255062103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326704323291779</t>
+    <t xml:space="preserve">0.326704293489456</t>
   </si>
   <si>
     <t xml:space="preserve">0.330416858196259</t>
@@ -67384,6 +67384,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.3333333333</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>565</v>
+      </c>
+      <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178774356842</t>
+    <t xml:space="preserve">0.179178789258003</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">0.179818719625473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979152321815</t>
+    <t xml:space="preserve">0.175979182124138</t>
   </si>
   <si>
     <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020231485367</t>
+    <t xml:space="preserve">0.167020261287689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779574990273</t>
+    <t xml:space="preserve">0.172779560089111</t>
   </si>
   <si>
     <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902708172798</t>
+    <t xml:space="preserve">0.145902723073959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493953704834</t>
+    <t xml:space="preserve">0.152493923902512</t>
   </si>
   <si>
     <t xml:space="preserve">0.147822499275208</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141504645348</t>
+    <t xml:space="preserve">0.156141489744186</t>
   </si>
   <si>
     <t xml:space="preserve">0.153517827391624</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">0.144622877240181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141423255205154</t>
+    <t xml:space="preserve">0.141423270106316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153837814927101</t>
+    <t xml:space="preserve">0.15383780002594</t>
   </si>
   <si>
     <t xml:space="preserve">0.173419460654259</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">0.16983588039875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380301117897</t>
+    <t xml:space="preserve">0.166380286216736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981057047844</t>
+    <t xml:space="preserve">0.159981071949005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421350479126</t>
+    <t xml:space="preserve">0.157421380281448</t>
   </si>
   <si>
     <t xml:space="preserve">0.152301967144012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158509239554405</t>
+    <t xml:space="preserve">0.158509224653244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163820594549179</t>
+    <t xml:space="preserve">0.163820624351501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836847662926</t>
+    <t xml:space="preserve">0.161836832761765</t>
   </si>
   <si>
     <t xml:space="preserve">0.180522635579109</t>
@@ -134,52 +134,52 @@
     <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174059391021729</t>
+    <t xml:space="preserve">0.17405940592289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168939977884293</t>
+    <t xml:space="preserve">0.168939992785454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977292299271</t>
+    <t xml:space="preserve">0.191977277398109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136757731438</t>
+    <t xml:space="preserve">0.196136772632599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176869630814</t>
+    <t xml:space="preserve">0.195176884531975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497809529305</t>
+    <t xml:space="preserve">0.187497839331627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938132762909</t>
+    <t xml:space="preserve">0.184938102960587</t>
   </si>
   <si>
     <t xml:space="preserve">0.204775750637054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454870343208</t>
+    <t xml:space="preserve">0.212454825639725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711750149727</t>
+    <t xml:space="preserve">0.204711765050888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200296312570572</t>
+    <t xml:space="preserve">0.20029628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736576199532</t>
+    <t xml:space="preserve">0.197736591100693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182378396391869</t>
+    <t xml:space="preserve">0.18237841129303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578003525734</t>
+    <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907546162605</t>
+    <t xml:space="preserve">0.172907531261444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499699354172</t>
+    <t xml:space="preserve">0.171499684453011</t>
   </si>
   <si>
     <t xml:space="preserve">0.165740385651588</t>
@@ -188,73 +188,73 @@
     <t xml:space="preserve">0.154349729418755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579908251762</t>
+    <t xml:space="preserve">0.169579923152924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917086362839</t>
+    <t xml:space="preserve">0.159917056560516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15486167371273</t>
+    <t xml:space="preserve">0.154861658811569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781435012817</t>
+    <t xml:space="preserve">0.156781449913979</t>
   </si>
   <si>
     <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417570829391</t>
+    <t xml:space="preserve">0.189417600631714</t>
   </si>
   <si>
     <t xml:space="preserve">0.191337332129478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857879161835</t>
+    <t xml:space="preserve">0.186857849359512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002073645592</t>
+    <t xml:space="preserve">0.185002103447914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170219853520393</t>
+    <t xml:space="preserve">0.170219868421555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163180693984032</t>
+    <t xml:space="preserve">0.163180664181709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742290377617</t>
+    <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221713542938</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022121310234</t>
+    <t xml:space="preserve">0.151022136211395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182568907738</t>
+    <t xml:space="preserve">0.147182554006577</t>
   </si>
   <si>
     <t xml:space="preserve">0.161260902881622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168172106146812</t>
+    <t xml:space="preserve">0.168172091245651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739418387413</t>
+    <t xml:space="preserve">0.173739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339236855507</t>
+    <t xml:space="preserve">0.175339221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897976160049</t>
+    <t xml:space="preserve">0.185897946357727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135864973068</t>
+    <t xml:space="preserve">0.204135835170746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096675634384</t>
+    <t xml:space="preserve">0.197096645832062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181354507803917</t>
+    <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
     <t xml:space="preserve">0.194216996431351</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">0.204647779464722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376506567001</t>
+    <t xml:space="preserve">0.198376551270485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240885019302</t>
+    <t xml:space="preserve">0.195240914821625</t>
   </si>
   <si>
     <t xml:space="preserve">0.203495904803276</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">0.216934308409691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709875226021</t>
+    <t xml:space="preserve">0.22070986032486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23677197098732</t>
+    <t xml:space="preserve">0.236771941184998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531284689903</t>
+    <t xml:space="preserve">0.242531299591064</t>
   </si>
   <si>
     <t xml:space="preserve">0.255969673395157</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286848545074</t>
+    <t xml:space="preserve">0.28028678894043</t>
   </si>
   <si>
     <t xml:space="preserve">0.295644998550415</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26236891746521</t>
+    <t xml:space="preserve">0.262368947267532</t>
   </si>
   <si>
     <t xml:space="preserve">0.264864653348923</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.254753828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254689782857895</t>
+    <t xml:space="preserve">0.25468984246254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202724218369</t>
+    <t xml:space="preserve">0.24720273911953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2476507127285</t>
+    <t xml:space="preserve">0.247650653123856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778683900833</t>
+    <t xml:space="preserve">0.24777863919735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572363853455</t>
+    <t xml:space="preserve">0.233572348952293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238051816821098</t>
+    <t xml:space="preserve">0.238051846623421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374631643295</t>
+    <t xml:space="preserve">0.214374601840973</t>
   </si>
   <si>
     <t xml:space="preserve">0.210663065314293</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">0.215654447674751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518811225891</t>
+    <t xml:space="preserve">0.212518826127052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891369223595</t>
+    <t xml:space="preserve">0.241891399025917</t>
   </si>
   <si>
     <t xml:space="preserve">0.249570474028587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980165958405</t>
+    <t xml:space="preserve">0.234980210661888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652572751045</t>
+    <t xml:space="preserve">0.231652557849884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971593022346</t>
+    <t xml:space="preserve">0.239971578121185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372741818428</t>
+    <t xml:space="preserve">0.230372712016106</t>
   </si>
   <si>
     <t xml:space="preserve">0.227173089981079</t>
@@ -362,28 +362,28 @@
     <t xml:space="preserve">0.220773860812187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405203342438</t>
+    <t xml:space="preserve">0.226405173540115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998353600502</t>
+    <t xml:space="preserve">0.216998308897018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20483972132206</t>
+    <t xml:space="preserve">0.204839751124382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20797535777092</t>
+    <t xml:space="preserve">0.207975387573242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535064339638</t>
+    <t xml:space="preserve">0.21053509414196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20989516377449</t>
+    <t xml:space="preserve">0.209895148873329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21117502450943</t>
+    <t xml:space="preserve">0.211175009608269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21258282661438</t>
+    <t xml:space="preserve">0.212582841515541</t>
   </si>
   <si>
     <t xml:space="preserve">0.215782448649406</t>
@@ -395,46 +395,46 @@
     <t xml:space="preserve">0.223845481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805399775505</t>
+    <t xml:space="preserve">0.224805355072021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23363633453846</t>
+    <t xml:space="preserve">0.233636364340782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627761602402</t>
+    <t xml:space="preserve">0.238627746701241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580936789513</t>
+    <t xml:space="preserve">0.228580951690674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973482847214</t>
+    <t xml:space="preserve">0.223973453044891</t>
   </si>
   <si>
     <t xml:space="preserve">0.223717495799065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837816596031</t>
+    <t xml:space="preserve">0.220837846398354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492095351219</t>
+    <t xml:space="preserve">0.23549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965817570686</t>
+    <t xml:space="preserve">0.220965832471848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365091443062</t>
+    <t xml:space="preserve">0.227365061640739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556157112122</t>
+    <t xml:space="preserve">0.302556186914444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357548713684</t>
+    <t xml:space="preserve">0.358357578516006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47354394197464</t>
+    <t xml:space="preserve">0.473543882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454254150391</t>
+    <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
     <t xml:space="preserve">0.485702514648438</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">0.429709136486053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152257204056</t>
+    <t xml:space="preserve">0.403152197599411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371156007051468</t>
+    <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
     <t xml:space="preserve">0.421710073947906</t>
@@ -458,118 +458,118 @@
     <t xml:space="preserve">0.374035745859146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754977464676</t>
+    <t xml:space="preserve">0.380754888057709</t>
   </si>
   <si>
     <t xml:space="preserve">0.352598249912262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331800699234009</t>
+    <t xml:space="preserve">0.331800669431686</t>
   </si>
   <si>
     <t xml:space="preserve">0.320602029561996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33244064450264</t>
+    <t xml:space="preserve">0.332440674304962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340439707040787</t>
+    <t xml:space="preserve">0.340439736843109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641189098358</t>
+    <t xml:space="preserve">0.327641248703003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157911777496</t>
+    <t xml:space="preserve">0.355157941579819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478836774826</t>
+    <t xml:space="preserve">0.347478866577148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760602235794</t>
+    <t xml:space="preserve">0.332760572433472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121624231339</t>
+    <t xml:space="preserve">0.324121654033661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327001243829727</t>
+    <t xml:space="preserve">0.32700127363205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159816503525</t>
+    <t xml:space="preserve">0.339159846305847</t>
   </si>
   <si>
     <t xml:space="preserve">0.335960179567337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161780834198</t>
+    <t xml:space="preserve">0.323161751031876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33020082116127</t>
+    <t xml:space="preserve">0.330200910568237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319962114095688</t>
+    <t xml:space="preserve">0.31996214389801</t>
   </si>
   <si>
     <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759694576263</t>
+    <t xml:space="preserve">0.340759664773941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801666498184</t>
+    <t xml:space="preserve">0.323801636695862</t>
   </si>
   <si>
     <t xml:space="preserve">0.322521805763245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360361099243</t>
+    <t xml:space="preserve">0.334360390901566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32892107963562</t>
+    <t xml:space="preserve">0.328921020030975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040462970734</t>
+    <t xml:space="preserve">0.334040522575378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163685560226</t>
+    <t xml:space="preserve">0.307163655757904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122531890869</t>
+    <t xml:space="preserve">0.316122591495514</t>
   </si>
   <si>
     <t xml:space="preserve">0.316698491573334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326361387968063</t>
+    <t xml:space="preserve">0.326361328363419</t>
   </si>
   <si>
     <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364756792783737</t>
+    <t xml:space="preserve">0.36475682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559149980545</t>
+    <t xml:space="preserve">0.345559120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346198976039886</t>
+    <t xml:space="preserve">0.346199035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081527233124</t>
+    <t xml:space="preserve">0.325081467628479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959331512451</t>
+    <t xml:space="preserve">0.343959301710129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32028204202652</t>
+    <t xml:space="preserve">0.320282101631165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720475435257</t>
+    <t xml:space="preserve">0.333720415830612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753013134003</t>
+    <t xml:space="preserve">0.39675310254097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275420188904</t>
+    <t xml:space="preserve">0.376275479793549</t>
   </si>
   <si>
     <t xml:space="preserve">0.375635534524918</t>
@@ -581,61 +581,61 @@
     <t xml:space="preserve">0.370196133852005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555251121521</t>
+    <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35131847858429</t>
+    <t xml:space="preserve">0.351318418979645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117844581604</t>
+    <t xml:space="preserve">0.356117874383926</t>
   </si>
   <si>
     <t xml:space="preserve">0.360917270183563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715758323669</t>
+    <t xml:space="preserve">0.373715698719025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793110132217</t>
+    <t xml:space="preserve">0.395793169736862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672819137573</t>
+    <t xml:space="preserve">0.398672759532928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594410657883</t>
+    <t xml:space="preserve">0.384594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954584598541</t>
+    <t xml:space="preserve">0.383954554796219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193351268768</t>
+    <t xml:space="preserve">0.394193291664124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274452924728</t>
+    <t xml:space="preserve">0.384274542331696</t>
   </si>
   <si>
     <t xml:space="preserve">0.415310829877853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42235004901886</t>
+    <t xml:space="preserve">0.422350019216537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312734603882</t>
+    <t xml:space="preserve">0.399312704801559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38363453745842</t>
+    <t xml:space="preserve">0.383634597063065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553376197815</t>
+    <t xml:space="preserve">0.39355343580246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943186044693</t>
+    <t xml:space="preserve">0.479943156242371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447307020425797</t>
+    <t xml:space="preserve">0.447307080030441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745483636856</t>
+    <t xml:space="preserve">0.460745424032211</t>
   </si>
   <si>
     <t xml:space="preserve">0.441547721624374</t>
@@ -647,49 +647,49 @@
     <t xml:space="preserve">0.454346179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447946965694427</t>
+    <t xml:space="preserve">0.447946906089783</t>
   </si>
   <si>
     <t xml:space="preserve">0.430029094219208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588815689087</t>
+    <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749263286591</t>
+    <t xml:space="preserve">0.428749203681946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230576276779</t>
+    <t xml:space="preserve">0.417230606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41339111328125</t>
+    <t xml:space="preserve">0.413391053676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41595071554184</t>
+    <t xml:space="preserve">0.415950775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070128679276</t>
+    <t xml:space="preserve">0.42107018828392</t>
   </si>
   <si>
     <t xml:space="preserve">0.409551501274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267890691757</t>
+    <t xml:space="preserve">0.440267860889435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909740686417</t>
+    <t xml:space="preserve">0.424909651279449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984190702438</t>
+    <t xml:space="preserve">0.470984220504761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148417949677</t>
+    <t xml:space="preserve">0.435148477554321</t>
   </si>
   <si>
     <t xml:space="preserve">0.406991809606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189541816711</t>
+    <t xml:space="preserve">0.426189601421356</t>
   </si>
   <si>
     <t xml:space="preserve">0.431308895349503</t>
@@ -698,43 +698,43 @@
     <t xml:space="preserve">0.418510407209396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405711948871613</t>
+    <t xml:space="preserve">0.405711978673935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111133337021</t>
+    <t xml:space="preserve">0.412111163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073967933655</t>
+    <t xml:space="preserve">0.389073938131332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390353739261627</t>
+    <t xml:space="preserve">0.39035376906395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473152399063</t>
+    <t xml:space="preserve">0.395473182201385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831391811371</t>
+    <t xml:space="preserve">0.410831332206726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988000154495</t>
+    <t xml:space="preserve">0.438988029956818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469402551651</t>
+    <t xml:space="preserve">0.427469342947006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4146708548069</t>
+    <t xml:space="preserve">0.414670884609222</t>
   </si>
   <si>
     <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790327548981</t>
+    <t xml:space="preserve">0.419790297746658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271729946136</t>
+    <t xml:space="preserve">0.408271670341492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42362979054451</t>
+    <t xml:space="preserve">0.423629820346832</t>
   </si>
   <si>
     <t xml:space="preserve">0.368596345186234</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">0.37243589758873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876265525818</t>
+    <t xml:space="preserve">0.369876205921173</t>
   </si>
   <si>
     <t xml:space="preserve">0.346838921308517</t>
@@ -752,55 +752,55 @@
     <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366036683320999</t>
+    <t xml:space="preserve">0.366036623716354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363476932048798</t>
+    <t xml:space="preserve">0.363476991653442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678473711014</t>
+    <t xml:space="preserve">0.350678443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999398708344</t>
+    <t xml:space="preserve">0.342999368906021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279199838638</t>
+    <t xml:space="preserve">0.344279259443283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958304643631</t>
+    <t xml:space="preserve">0.351958364248276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835141658783</t>
+    <t xml:space="preserve">0.378835201263428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913579940796</t>
+    <t xml:space="preserve">0.392913520336151</t>
   </si>
   <si>
     <t xml:space="preserve">0.359637439250946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316544055939</t>
+    <t xml:space="preserve">0.367316484451294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234385728836</t>
+    <t xml:space="preserve">0.385234355926514</t>
   </si>
   <si>
     <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380115002393723</t>
+    <t xml:space="preserve">0.3801149725914</t>
   </si>
   <si>
     <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39803284406662</t>
+    <t xml:space="preserve">0.398032903671265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592625141144</t>
+    <t xml:space="preserve">0.400592565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948840618134</t>
+    <t xml:space="preserve">0.431948870420456</t>
   </si>
   <si>
     <t xml:space="preserve">0.438348114490509</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945090770721</t>
+    <t xml:space="preserve">0.463945060968399</t>
   </si>
   <si>
     <t xml:space="preserve">0.472350865602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200783252716</t>
+    <t xml:space="preserve">0.451200813055038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100738286972</t>
+    <t xml:space="preserve">0.437100827693939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000782728195</t>
+    <t xml:space="preserve">0.423000812530518</t>
   </si>
   <si>
     <t xml:space="preserve">0.433575749397278</t>
@@ -830,97 +830,100 @@
     <t xml:space="preserve">0.444150775671005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675794363022</t>
+    <t xml:space="preserve">0.447675824165344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625756978989</t>
+    <t xml:space="preserve">0.440625786781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525771617889</t>
+    <t xml:space="preserve">0.426525801420212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900678157806</t>
+    <t xml:space="preserve">0.415950745344162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475823640823</t>
+    <t xml:space="preserve">0.408900707960129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394800662994385</t>
+    <t xml:space="preserve">0.419475764036179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325741291046</t>
+    <t xml:space="preserve">0.394800752401352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398325711488724</t>
   </si>
   <si>
     <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050730705261</t>
+    <t xml:space="preserve">0.430050760507584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725831747055</t>
+    <t xml:space="preserve">0.454725801944733</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250761032104</t>
+    <t xml:space="preserve">0.458250820636749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300887823105</t>
+    <t xml:space="preserve">0.465300858020782</t>
   </si>
   <si>
     <t xml:space="preserve">0.461775839328766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375719070435</t>
+    <t xml:space="preserve">0.405375748872757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850670576096</t>
+    <t xml:space="preserve">0.401850700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750685214996</t>
+    <t xml:space="preserve">0.387750744819641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38070073723793</t>
+    <t xml:space="preserve">0.380700707435608</t>
   </si>
   <si>
     <t xml:space="preserve">0.366600662469864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175718545914</t>
+    <t xml:space="preserve">0.377175658941269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275674104691</t>
+    <t xml:space="preserve">0.391275644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650640249252</t>
+    <t xml:space="preserve">0.373650699853897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860587596893</t>
+    <t xml:space="preserve">0.346860647201538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450609922409</t>
+    <t xml:space="preserve">0.345450639724731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550654888153</t>
+    <t xml:space="preserve">0.359550625085831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352500647306442</t>
+    <t xml:space="preserve">0.35250061750412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400661945343</t>
+    <t xml:space="preserve">0.338400602340698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250579595566</t>
+    <t xml:space="preserve">0.317250549793243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320070594549179</t>
+    <t xml:space="preserve">0.320070564746857</t>
   </si>
   <si>
     <t xml:space="preserve">0.296100527048111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26367050409317</t>
+    <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
@@ -932,10 +935,7 @@
     <t xml:space="preserve">0.277770489454269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490489244461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249570444226265</t>
+    <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
     <t xml:space="preserve">0.253800481557846</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">0.248160436749458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460526943207</t>
+    <t xml:space="preserve">0.290460467338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.291870534420013</t>
@@ -953,70 +953,70 @@
     <t xml:space="preserve">0.276360481977463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820526838303</t>
+    <t xml:space="preserve">0.284820556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286230504512787</t>
+    <t xml:space="preserve">0.286230474710464</t>
   </si>
   <si>
     <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790594339371</t>
+    <t xml:space="preserve">0.308790534734726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314430564641953</t>
+    <t xml:space="preserve">0.314430594444275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040632247925</t>
+    <t xml:space="preserve">0.344040602445602</t>
   </si>
   <si>
     <t xml:space="preserve">0.331350564956665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325710564851761</t>
+    <t xml:space="preserve">0.325710594654083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680632352829</t>
+    <t xml:space="preserve">0.349680602550507</t>
   </si>
   <si>
     <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384225696325302</t>
+    <t xml:space="preserve">0.38422566652298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170609712601</t>
+    <t xml:space="preserve">0.334170639514923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990624666214</t>
+    <t xml:space="preserve">0.336990565061569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630624771118</t>
+    <t xml:space="preserve">0.342630594968796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025636196136</t>
+    <t xml:space="preserve">0.356025665998459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090669631958</t>
+    <t xml:space="preserve">0.351090610027313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530609607697</t>
+    <t xml:space="preserve">0.328530579805374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940617084503</t>
+    <t xml:space="preserve">0.329940557479858</t>
   </si>
   <si>
     <t xml:space="preserve">0.32712060213089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300557374954</t>
+    <t xml:space="preserve">0.324300527572632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610549688339</t>
+    <t xml:space="preserve">0.311610579490662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32289057970047</t>
+    <t xml:space="preserve">0.322890609502792</t>
   </si>
   <si>
     <t xml:space="preserve">0.310200572013855</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">0.29328054189682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310504198074</t>
+    <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130459547043</t>
+    <t xml:space="preserve">0.27213054895401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26508042216301</t>
+    <t xml:space="preserve">0.265080481767654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720481872559</t>
+    <t xml:space="preserve">0.270720511674881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950504302979</t>
+    <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
     <t xml:space="preserve">0.282000511884689</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690519571304</t>
+    <t xml:space="preserve">0.294690579175949</t>
   </si>
   <si>
     <t xml:space="preserve">0.437586963176727</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">0.406879067420959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363658666611</t>
+    <t xml:space="preserve">0.395363628864288</t>
   </si>
   <si>
     <t xml:space="preserve">0.383848249912262</t>
@@ -1073,208 +1073,208 @@
     <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171231269836</t>
+    <t xml:space="preserve">0.376171261072159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37002968788147</t>
+    <t xml:space="preserve">0.370029658079147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38768669962883</t>
+    <t xml:space="preserve">0.387686729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777418613434</t>
+    <t xml:space="preserve">0.380777388811111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565103530884</t>
+    <t xml:space="preserve">0.371565073728561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211185455322</t>
+    <t xml:space="preserve">0.356211155653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069582462311</t>
+    <t xml:space="preserve">0.350069552659988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534196615219</t>
+    <t xml:space="preserve">0.348534226417542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463424921036</t>
+    <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
     <t xml:space="preserve">0.359281957149506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140354156494</t>
+    <t xml:space="preserve">0.353140383958817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746541500092</t>
+    <t xml:space="preserve">0.357746511697769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342392653226852</t>
+    <t xml:space="preserve">0.34239262342453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857207775116</t>
+    <t xml:space="preserve">0.340857237577438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675769805908</t>
+    <t xml:space="preserve">0.354675799608231</t>
   </si>
   <si>
     <t xml:space="preserve">0.44526395201683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41839462518692</t>
+    <t xml:space="preserve">0.418394595384598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46061784029007</t>
+    <t xml:space="preserve">0.460617929697037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940881252289</t>
+    <t xml:space="preserve">0.452940911054611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102431535721</t>
+    <t xml:space="preserve">0.449102342128754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233074903488</t>
+    <t xml:space="preserve">0.422233045101166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717636346817</t>
+    <t xml:space="preserve">0.410717666149139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202108383179</t>
+    <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
     <t xml:space="preserve">0.391525208950043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040558099747</t>
+    <t xml:space="preserve">0.403040587902069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41455614566803</t>
+    <t xml:space="preserve">0.414556175470352</t>
   </si>
   <si>
     <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100459575653</t>
+    <t xml:space="preserve">0.373100489377975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817342996597</t>
+    <t xml:space="preserve">0.360817313194275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351604998111725</t>
+    <t xml:space="preserve">0.351604968309402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346998780965805</t>
+    <t xml:space="preserve">0.34699884057045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37770664691925</t>
+    <t xml:space="preserve">0.377706676721573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958916187286</t>
+    <t xml:space="preserve">0.366958886384964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374635845422745</t>
+    <t xml:space="preserve">0.374635875225067</t>
   </si>
   <si>
     <t xml:space="preserve">0.365423530340195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432488203049</t>
+    <t xml:space="preserve">0.322432518005371</t>
   </si>
   <si>
     <t xml:space="preserve">0.305543184280396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307078570127487</t>
+    <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323967903852463</t>
+    <t xml:space="preserve">0.323967933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503289699554</t>
+    <t xml:space="preserve">0.325503319501877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330109477043152</t>
+    <t xml:space="preserve">0.330109447240829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180248737335</t>
+    <t xml:space="preserve">0.333180278539658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251020431519</t>
+    <t xml:space="preserve">0.336251050233841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337786465883255</t>
+    <t xml:space="preserve">0.33778640627861</t>
   </si>
   <si>
     <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715664386749</t>
+    <t xml:space="preserve">0.334715634584427</t>
   </si>
   <si>
     <t xml:space="preserve">0.314755529165268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220113515854</t>
+    <t xml:space="preserve">0.313220143318176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308613985776901</t>
+    <t xml:space="preserve">0.308613955974579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319361716508865</t>
+    <t xml:space="preserve">0.31936177611351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32857409119606</t>
+    <t xml:space="preserve">0.328574061393738</t>
   </si>
   <si>
     <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328171849250793</t>
+    <t xml:space="preserve">0.328171879053116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128411054611</t>
+    <t xml:space="preserve">0.320128470659256</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337823987007141</t>
+    <t xml:space="preserve">0.337824016809464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432716369629</t>
+    <t xml:space="preserve">0.339432746171951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326563268899918</t>
+    <t xml:space="preserve">0.32656317949295</t>
   </si>
   <si>
     <t xml:space="preserve">0.329780548810959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519830703735</t>
+    <t xml:space="preserve">0.318519800901413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308867692947388</t>
+    <t xml:space="preserve">0.308867663145065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606885433197</t>
+    <t xml:space="preserve">0.297606855630875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307258993387222</t>
+    <t xml:space="preserve">0.307259023189545</t>
   </si>
   <si>
     <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650293827057</t>
+    <t xml:space="preserve">0.305650323629379</t>
   </si>
   <si>
     <t xml:space="preserve">0.304041624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998185873032</t>
+    <t xml:space="preserve">0.295998156070709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287954777479172</t>
+    <t xml:space="preserve">0.287954747676849</t>
   </si>
   <si>
     <t xml:space="preserve">0.292780816555023</t>
@@ -1283,31 +1283,31 @@
     <t xml:space="preserve">0.284737408161163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28151997923851</t>
+    <t xml:space="preserve">0.281520009040833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128678798676</t>
+    <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
     <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346107721329</t>
+    <t xml:space="preserve">0.286346077919006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693969964981</t>
+    <t xml:space="preserve">0.276693999767303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563447237015</t>
+    <t xml:space="preserve">0.289563417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291172116994858</t>
+    <t xml:space="preserve">0.29117214679718</t>
   </si>
   <si>
     <t xml:space="preserve">0.300824254751205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432954311371</t>
+    <t xml:space="preserve">0.302432924509048</t>
   </si>
   <si>
     <t xml:space="preserve">0.313693732023239</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302134037018</t>
+    <t xml:space="preserve">0.352302193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258725643158</t>
+    <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867455005646</t>
+    <t xml:space="preserve">0.345867425203323</t>
   </si>
   <si>
     <t xml:space="preserve">0.347476154565811</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736962080002</t>
+    <t xml:space="preserve">0.358736932277679</t>
   </si>
   <si>
     <t xml:space="preserve">0.300703525543213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2972272336483</t>
+    <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
     <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290274530649185</t>
+    <t xml:space="preserve">0.290274560451508</t>
   </si>
   <si>
     <t xml:space="preserve">0.292012691497803</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304179906845093</t>
+    <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536339998245</t>
+    <t xml:space="preserve">0.288536310195923</t>
   </si>
   <si>
     <t xml:space="preserve">0.28332182765007</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">0.29375085234642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28506001830101</t>
+    <t xml:space="preserve">0.285060048103333</t>
   </si>
   <si>
     <t xml:space="preserve">0.278107315301895</t>
@@ -1376,55 +1376,55 @@
     <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27463099360466</t>
+    <t xml:space="preserve">0.274630963802338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28679820895195</t>
+    <t xml:space="preserve">0.286798179149628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279845535755157</t>
+    <t xml:space="preserve">0.279845505952835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369154453278</t>
+    <t xml:space="preserve">0.276369124650955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272892773151398</t>
+    <t xml:space="preserve">0.27289280295372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30939444899559</t>
+    <t xml:space="preserve">0.309394389390945</t>
   </si>
   <si>
     <t xml:space="preserve">0.298965364694595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656198740005</t>
+    <t xml:space="preserve">0.307656228542328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132580041885</t>
+    <t xml:space="preserve">0.311132609844208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870740890503</t>
+    <t xml:space="preserve">0.312870770692825</t>
   </si>
   <si>
     <t xml:space="preserve">0.330252438783646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037926435471</t>
+    <t xml:space="preserve">0.325037956237793</t>
   </si>
   <si>
     <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823384284973</t>
+    <t xml:space="preserve">0.319823414087296</t>
   </si>
   <si>
     <t xml:space="preserve">0.318085223436356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316347122192383</t>
+    <t xml:space="preserve">0.31634709239006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315903425216675</t>
+    <t xml:space="preserve">0.31590336561203</t>
   </si>
   <si>
     <t xml:space="preserve">0.305254966020584</t>
@@ -1433,34 +1433,34 @@
     <t xml:space="preserve">0.301705479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804392814636</t>
+    <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606506824493</t>
+    <t xml:space="preserve">0.294606536626816</t>
   </si>
   <si>
     <t xml:space="preserve">0.292831808328629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480237722397</t>
+    <t xml:space="preserve">0.303480207920074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233953952789</t>
+    <t xml:space="preserve">0.319233924150467</t>
   </si>
   <si>
     <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308350950479507</t>
+    <t xml:space="preserve">0.30835098028183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311978667974472</t>
+    <t xml:space="preserve">0.31197863817215</t>
   </si>
   <si>
     <t xml:space="preserve">0.30653715133667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026489973068</t>
+    <t xml:space="preserve">0.292026519775391</t>
   </si>
   <si>
     <t xml:space="preserve">0.293840348720551</t>
@@ -26116,7 +26116,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26142,7 +26142,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26168,7 +26168,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26194,7 +26194,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26220,7 +26220,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26246,7 +26246,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26272,7 +26272,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26298,7 +26298,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26324,7 +26324,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26350,7 +26350,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26376,7 +26376,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26402,7 +26402,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26428,7 +26428,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26454,7 +26454,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26480,7 +26480,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26506,7 +26506,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26558,7 +26558,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26584,7 +26584,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26610,7 +26610,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26636,7 +26636,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26662,7 +26662,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26688,7 +26688,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26714,7 +26714,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26740,7 +26740,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26766,7 +26766,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26792,7 +26792,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26818,7 +26818,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26844,7 +26844,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26870,7 +26870,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26896,7 +26896,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26922,7 +26922,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26948,7 +26948,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26974,7 +26974,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27000,7 +27000,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27026,7 +27026,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27104,7 +27104,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27182,7 +27182,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27208,7 +27208,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27260,7 +27260,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27286,7 +27286,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27312,7 +27312,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27338,7 +27338,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27494,7 +27494,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27520,7 +27520,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27546,7 +27546,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27624,7 +27624,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27650,7 +27650,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28066,7 +28066,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28092,7 +28092,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28118,7 +28118,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28144,7 +28144,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28170,7 +28170,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28196,7 +28196,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28222,7 +28222,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28248,7 +28248,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28274,7 +28274,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28326,7 +28326,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28352,7 +28352,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28378,7 +28378,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28404,7 +28404,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28430,7 +28430,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28456,7 +28456,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28482,7 +28482,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28508,7 +28508,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28534,7 +28534,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28560,7 +28560,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28586,7 +28586,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28664,7 +28664,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28690,7 +28690,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28716,7 +28716,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28742,7 +28742,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28768,7 +28768,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28794,7 +28794,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28820,7 +28820,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28846,7 +28846,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28872,7 +28872,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28898,7 +28898,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28924,7 +28924,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28950,7 +28950,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28976,7 +28976,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29002,7 +29002,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29028,7 +29028,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29054,7 +29054,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29080,7 +29080,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29106,7 +29106,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29132,7 +29132,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29158,7 +29158,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29184,7 +29184,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29288,7 +29288,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29340,7 +29340,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29418,7 +29418,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29444,7 +29444,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29470,7 +29470,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29496,7 +29496,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29522,7 +29522,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29548,7 +29548,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29574,7 +29574,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29600,7 +29600,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29626,7 +29626,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29652,7 +29652,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29678,7 +29678,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29704,7 +29704,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29730,7 +29730,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29756,7 +29756,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29782,7 +29782,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29808,7 +29808,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29834,7 +29834,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29860,7 +29860,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29886,7 +29886,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>307</v>
+        <v>109</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30068,7 +30068,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30198,7 +30198,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30224,7 +30224,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30250,7 +30250,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30302,7 +30302,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30328,7 +30328,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30406,7 +30406,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30796,7 +30796,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30822,7 +30822,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30926,7 +30926,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30978,7 +30978,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31004,7 +31004,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31030,7 +31030,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31134,7 +31134,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31160,7 +31160,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31186,7 +31186,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31238,7 +31238,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31264,7 +31264,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31290,7 +31290,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31316,7 +31316,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31342,7 +31342,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31368,7 +31368,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31394,7 +31394,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31420,7 +31420,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31446,7 +31446,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31472,7 +31472,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31498,7 +31498,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31524,7 +31524,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31550,7 +31550,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31576,7 +31576,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31602,7 +31602,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31628,7 +31628,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31654,7 +31654,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31680,7 +31680,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31706,7 +31706,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31732,7 +31732,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31758,7 +31758,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31784,7 +31784,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31810,7 +31810,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31836,7 +31836,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31862,7 +31862,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31888,7 +31888,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31914,7 +31914,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31966,7 +31966,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31992,7 +31992,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32018,7 +32018,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32070,7 +32070,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32252,7 +32252,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32278,7 +32278,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32304,7 +32304,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32330,7 +32330,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32668,7 +32668,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33162,7 +33162,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34202,7 +34202,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34410,7 +34410,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34436,7 +34436,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34930,7 +34930,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35580,7 +35580,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35606,7 +35606,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35658,7 +35658,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35710,7 +35710,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35736,7 +35736,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35788,7 +35788,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35814,7 +35814,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35840,7 +35840,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35892,7 +35892,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35918,7 +35918,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35944,7 +35944,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35970,7 +35970,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35996,7 +35996,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36022,7 +36022,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36048,7 +36048,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36074,7 +36074,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36100,7 +36100,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -67407,6 +67407,32 @@
         <v>565</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.3333333333</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>565</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">0.179818719625473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979182124138</t>
+    <t xml:space="preserve">0.175979167222977</t>
   </si>
   <si>
     <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020261287689</t>
+    <t xml:space="preserve">0.167020246386528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779560089111</t>
+    <t xml:space="preserve">0.172779530286789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151662051677704</t>
+    <t xml:space="preserve">0.151662066578865</t>
   </si>
   <si>
     <t xml:space="preserve">0.145902723073959</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">0.152493923902512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822499275208</t>
+    <t xml:space="preserve">0.147822514176369</t>
   </si>
   <si>
     <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141489744186</t>
+    <t xml:space="preserve">0.156141519546509</t>
   </si>
   <si>
     <t xml:space="preserve">0.153517827391624</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.142383143305779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063170671463</t>
+    <t xml:space="preserve">0.142063200473785</t>
   </si>
   <si>
     <t xml:space="preserve">0.142447128891945</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">0.144622877240181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141423270106316</t>
+    <t xml:space="preserve">0.141423255205154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15383780002594</t>
+    <t xml:space="preserve">0.153837785124779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173419460654259</t>
+    <t xml:space="preserve">0.173419490456581</t>
   </si>
   <si>
     <t xml:space="preserve">0.16983588039875</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">0.166380286216736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981071949005</t>
+    <t xml:space="preserve">0.159981057047844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421380281448</t>
+    <t xml:space="preserve">0.15742139518261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301967144012</t>
+    <t xml:space="preserve">0.152301952242851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158509224653244</t>
+    <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
     <t xml:space="preserve">0.163820624351501</t>
@@ -128,91 +128,91 @@
     <t xml:space="preserve">0.161836832761765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522635579109</t>
+    <t xml:space="preserve">0.180522620677948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180458635091782</t>
+    <t xml:space="preserve">0.18045862019062</t>
   </si>
   <si>
     <t xml:space="preserve">0.17405940592289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168939992785454</t>
+    <t xml:space="preserve">0.168940007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977277398109</t>
+    <t xml:space="preserve">0.191977307200432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136772632599</t>
+    <t xml:space="preserve">0.19613678753376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176884531975</t>
+    <t xml:space="preserve">0.195176899433136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497839331627</t>
+    <t xml:space="preserve">0.187497809529305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938102960587</t>
+    <t xml:space="preserve">0.184938088059425</t>
   </si>
   <si>
     <t xml:space="preserve">0.204775750637054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454825639725</t>
+    <t xml:space="preserve">0.212454855442047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711765050888</t>
+    <t xml:space="preserve">0.204711779952049</t>
   </si>
   <si>
     <t xml:space="preserve">0.20029628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736591100693</t>
+    <t xml:space="preserve">0.197736546397209</t>
   </si>
   <si>
     <t xml:space="preserve">0.18237841129303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578018426895</t>
+    <t xml:space="preserve">0.185578033328056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907531261444</t>
+    <t xml:space="preserve">0.172907546162605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499684453011</t>
+    <t xml:space="preserve">0.171499699354172</t>
   </si>
   <si>
     <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349729418755</t>
+    <t xml:space="preserve">0.154349744319916</t>
   </si>
   <si>
     <t xml:space="preserve">0.169579923152924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917056560516</t>
+    <t xml:space="preserve">0.159917086362839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154861658811569</t>
+    <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781449913979</t>
+    <t xml:space="preserve">0.156781435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160493016242981</t>
+    <t xml:space="preserve">0.16049300134182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417600631714</t>
+    <t xml:space="preserve">0.189417570829391</t>
   </si>
   <si>
     <t xml:space="preserve">0.191337332129478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857849359512</t>
+    <t xml:space="preserve">0.186857864260674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002103447914</t>
+    <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
     <t xml:space="preserve">0.170219868421555</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221743345261</t>
+    <t xml:space="preserve">0.154221728444099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022136211395</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182554006577</t>
+    <t xml:space="preserve">0.147182568907738</t>
   </si>
   <si>
     <t xml:space="preserve">0.161260902881622</t>
@@ -239,70 +239,70 @@
     <t xml:space="preserve">0.168172091245651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739433288574</t>
+    <t xml:space="preserve">0.173739418387413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339221954346</t>
+    <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897946357727</t>
+    <t xml:space="preserve">0.185897961258888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135835170746</t>
+    <t xml:space="preserve">0.204135850071907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096645832062</t>
+    <t xml:space="preserve">0.197096660733223</t>
   </si>
   <si>
     <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194216996431351</t>
+    <t xml:space="preserve">0.19421698153019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204647779464722</t>
+    <t xml:space="preserve">0.20464776456356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376551270485</t>
+    <t xml:space="preserve">0.198376521468163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240914821625</t>
+    <t xml:space="preserve">0.195240870118141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495904803276</t>
+    <t xml:space="preserve">0.203495889902115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934308409691</t>
+    <t xml:space="preserve">0.21693429350853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22070986032486</t>
+    <t xml:space="preserve">0.220709845423698</t>
   </si>
   <si>
     <t xml:space="preserve">0.236771941184998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531299591064</t>
+    <t xml:space="preserve">0.242531269788742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969673395157</t>
+    <t xml:space="preserve">0.255969703197479</t>
   </si>
   <si>
     <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28028678894043</t>
+    <t xml:space="preserve">0.280286818742752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644998550415</t>
+    <t xml:space="preserve">0.295645028352737</t>
   </si>
   <si>
     <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262368947267532</t>
+    <t xml:space="preserve">0.26236891746521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264864653348923</t>
+    <t xml:space="preserve">0.2648646235466</t>
   </si>
   <si>
     <t xml:space="preserve">0.254753828048706</t>
@@ -314,76 +314,76 @@
     <t xml:space="preserve">0.24720273911953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650653123856</t>
+    <t xml:space="preserve">0.247650668025017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24777863919735</t>
+    <t xml:space="preserve">0.247778654098511</t>
   </si>
   <si>
     <t xml:space="preserve">0.233572348952293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238051846623421</t>
+    <t xml:space="preserve">0.238051816821098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374601840973</t>
+    <t xml:space="preserve">0.214374616742134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663065314293</t>
+    <t xml:space="preserve">0.210663080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654447674751</t>
+    <t xml:space="preserve">0.215654477477074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518826127052</t>
+    <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891399025917</t>
+    <t xml:space="preserve">0.241891339421272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570474028587</t>
+    <t xml:space="preserve">0.249570414423943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980210661888</t>
+    <t xml:space="preserve">0.234980180859566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652557849884</t>
+    <t xml:space="preserve">0.231652572751045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971578121185</t>
+    <t xml:space="preserve">0.239971622824669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372712016106</t>
+    <t xml:space="preserve">0.230372697114944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173089981079</t>
+    <t xml:space="preserve">0.227173075079918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773860812187</t>
+    <t xml:space="preserve">0.220773845911026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405173540115</t>
+    <t xml:space="preserve">0.226405188441277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998308897018</t>
+    <t xml:space="preserve">0.216998293995857</t>
   </si>
   <si>
     <t xml:space="preserve">0.204839751124382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207975387573242</t>
+    <t xml:space="preserve">0.207975372672081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21053509414196</t>
+    <t xml:space="preserve">0.210535079240799</t>
   </si>
   <si>
     <t xml:space="preserve">0.209895148873329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211175009608269</t>
+    <t xml:space="preserve">0.211174994707108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582841515541</t>
+    <t xml:space="preserve">0.212582796812057</t>
   </si>
   <si>
     <t xml:space="preserve">0.215782448649406</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">0.229732781648636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845481872559</t>
+    <t xml:space="preserve">0.22384549677372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805355072021</t>
+    <t xml:space="preserve">0.224805369973183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636364340782</t>
+    <t xml:space="preserve">0.233636319637299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627791404724</t>
   </si>
   <si>
     <t xml:space="preserve">0.228580951690674</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">0.223717495799065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837846398354</t>
+    <t xml:space="preserve">0.220837816596031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23549211025238</t>
+    <t xml:space="preserve">0.235492125153542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965832471848</t>
+    <t xml:space="preserve">0.220965817570686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365061640739</t>
+    <t xml:space="preserve">0.227365091443062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556186914444</t>
+    <t xml:space="preserve">0.302556127309799</t>
   </si>
   <si>
     <t xml:space="preserve">0.358357578516006</t>
@@ -440,34 +440,34 @@
     <t xml:space="preserve">0.485702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44474732875824</t>
+    <t xml:space="preserve">0.444747298955917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709136486053</t>
+    <t xml:space="preserve">0.429709076881409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152197599411</t>
+    <t xml:space="preserve">0.403152257204056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37115603685379</t>
+    <t xml:space="preserve">0.371156066656113</t>
   </si>
   <si>
     <t xml:space="preserve">0.421710073947906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035745859146</t>
+    <t xml:space="preserve">0.374035716056824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754888057709</t>
+    <t xml:space="preserve">0.380754917860031</t>
   </si>
   <si>
     <t xml:space="preserve">0.352598249912262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331800669431686</t>
+    <t xml:space="preserve">0.331800639629364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602029561996</t>
+    <t xml:space="preserve">0.320601999759674</t>
   </si>
   <si>
     <t xml:space="preserve">0.332440674304962</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">0.355157941579819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478866577148</t>
+    <t xml:space="preserve">0.347478836774826</t>
   </si>
   <si>
     <t xml:space="preserve">0.332760572433472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121654033661</t>
+    <t xml:space="preserve">0.324121594429016</t>
   </si>
   <si>
     <t xml:space="preserve">0.32700127363205</t>
@@ -500,16 +500,16 @@
     <t xml:space="preserve">0.335960179567337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161751031876</t>
+    <t xml:space="preserve">0.323161721229553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330200910568237</t>
+    <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31996214389801</t>
+    <t xml:space="preserve">0.319962114095688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402392625809</t>
+    <t xml:space="preserve">0.317402422428131</t>
   </si>
   <si>
     <t xml:space="preserve">0.340759664773941</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">0.322521805763245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360390901566</t>
+    <t xml:space="preserve">0.334360420703888</t>
   </si>
   <si>
     <t xml:space="preserve">0.328921020030975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040522575378</t>
+    <t xml:space="preserve">0.334040492773056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163655757904</t>
+    <t xml:space="preserve">0.307163625955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122591495514</t>
+    <t xml:space="preserve">0.316122561693192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698491573334</t>
+    <t xml:space="preserve">0.316698521375656</t>
   </si>
   <si>
     <t xml:space="preserve">0.326361328363419</t>
@@ -548,181 +548,181 @@
     <t xml:space="preserve">0.36475682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559120178223</t>
+    <t xml:space="preserve">0.345559060573578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199035644531</t>
+    <t xml:space="preserve">0.346199005842209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081467628479</t>
+    <t xml:space="preserve">0.325081527233124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959301710129</t>
+    <t xml:space="preserve">0.343959331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282101631165</t>
+    <t xml:space="preserve">0.320282131433487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720415830612</t>
+    <t xml:space="preserve">0.333720505237579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39675310254097</t>
+    <t xml:space="preserve">0.396753042936325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275479793549</t>
+    <t xml:space="preserve">0.376275420188904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635534524918</t>
+    <t xml:space="preserve">0.37563556432724</t>
   </si>
   <si>
     <t xml:space="preserve">0.376915365457535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196133852005</t>
+    <t xml:space="preserve">0.370196163654327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555280923843</t>
+    <t xml:space="preserve">0.377555310726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318418979645</t>
+    <t xml:space="preserve">0.351318389177322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117874383926</t>
+    <t xml:space="preserve">0.356117814779282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917270183563</t>
+    <t xml:space="preserve">0.360917240381241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715698719025</t>
+    <t xml:space="preserve">0.373715728521347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395793169736862</t>
+    <t xml:space="preserve">0.395793110132217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672759532928</t>
+    <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
     <t xml:space="preserve">0.384594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954554796219</t>
+    <t xml:space="preserve">0.383954614400864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193291664124</t>
+    <t xml:space="preserve">0.394193321466446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274542331696</t>
+    <t xml:space="preserve">0.384274512529373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310829877853</t>
+    <t xml:space="preserve">0.415310740470886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422350019216537</t>
+    <t xml:space="preserve">0.422349989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312704801559</t>
+    <t xml:space="preserve">0.399312674999237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383634597063065</t>
+    <t xml:space="preserve">0.383634567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39355343580246</t>
+    <t xml:space="preserve">0.393553346395493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943156242371</t>
+    <t xml:space="preserve">0.479943245649338</t>
   </si>
   <si>
     <t xml:space="preserve">0.447307080030441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745424032211</t>
+    <t xml:space="preserve">0.460745394229889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547721624374</t>
+    <t xml:space="preserve">0.441547691822052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027219295502</t>
+    <t xml:space="preserve">0.446027249097824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346179962158</t>
+    <t xml:space="preserve">0.454346150159836</t>
   </si>
   <si>
     <t xml:space="preserve">0.447946906089783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430029094219208</t>
+    <t xml:space="preserve">0.43002912402153</t>
   </si>
   <si>
     <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749203681946</t>
+    <t xml:space="preserve">0.428749233484268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230606079102</t>
+    <t xml:space="preserve">0.417230576276779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413391053676605</t>
+    <t xml:space="preserve">0.41339111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950775146484</t>
+    <t xml:space="preserve">0.415950745344162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42107018828392</t>
+    <t xml:space="preserve">0.421070158481598</t>
   </si>
   <si>
     <t xml:space="preserve">0.409551501274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267860889435</t>
+    <t xml:space="preserve">0.440267831087112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909651279449</t>
+    <t xml:space="preserve">0.424909710884094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984220504761</t>
+    <t xml:space="preserve">0.470984250307083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148477554321</t>
+    <t xml:space="preserve">0.435148447751999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406991809606552</t>
+    <t xml:space="preserve">0.40699177980423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189601421356</t>
+    <t xml:space="preserve">0.426189571619034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431308895349503</t>
+    <t xml:space="preserve">0.431308954954147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510407209396</t>
+    <t xml:space="preserve">0.418510466814041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405711978673935</t>
+    <t xml:space="preserve">0.405712008476257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111163139343</t>
+    <t xml:space="preserve">0.412111192941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073938131332</t>
+    <t xml:space="preserve">0.389073967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39035376906395</t>
+    <t xml:space="preserve">0.390353798866272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473182201385</t>
+    <t xml:space="preserve">0.395473092794418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410831332206726</t>
+    <t xml:space="preserve">0.410831391811371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438988029956818</t>
+    <t xml:space="preserve">0.438988000154495</t>
   </si>
   <si>
     <t xml:space="preserve">0.427469342947006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670884609222</t>
+    <t xml:space="preserve">0.414670914411545</t>
   </si>
   <si>
     <t xml:space="preserve">0.401872426271439</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">0.419790297746658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271670341492</t>
+    <t xml:space="preserve">0.408271700143814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629820346832</t>
+    <t xml:space="preserve">0.423629909753799</t>
   </si>
   <si>
     <t xml:space="preserve">0.368596345186234</t>
@@ -743,58 +743,58 @@
     <t xml:space="preserve">0.37243589758873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876205921173</t>
+    <t xml:space="preserve">0.369876176118851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346838921308517</t>
+    <t xml:space="preserve">0.346838980913162</t>
   </si>
   <si>
     <t xml:space="preserve">0.335320264101028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366036623716354</t>
+    <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
     <t xml:space="preserve">0.363476991653442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678443908691</t>
+    <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999368906021</t>
+    <t xml:space="preserve">0.342999398708344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279259443283</t>
+    <t xml:space="preserve">0.344279199838638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958364248276</t>
+    <t xml:space="preserve">0.351958334445953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835201263428</t>
+    <t xml:space="preserve">0.378835141658783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913520336151</t>
+    <t xml:space="preserve">0.392913490533829</t>
   </si>
   <si>
     <t xml:space="preserve">0.359637439250946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316484451294</t>
+    <t xml:space="preserve">0.367316514253616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234355926514</t>
+    <t xml:space="preserve">0.385234385728836</t>
   </si>
   <si>
     <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3801149725914</t>
+    <t xml:space="preserve">0.380115002393723</t>
   </si>
   <si>
     <t xml:space="preserve">0.391633629798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032903671265</t>
+    <t xml:space="preserve">0.398032814264297</t>
   </si>
   <si>
     <t xml:space="preserve">0.400592565536499</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">0.431948870420456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438348114490509</t>
+    <t xml:space="preserve">0.438348025083542</t>
   </si>
   <si>
     <t xml:space="preserve">0.457545816898346</t>
@@ -812,40 +812,37 @@
     <t xml:space="preserve">0.463945060968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350865602493</t>
+    <t xml:space="preserve">0.472350805997849</t>
   </si>
   <si>
     <t xml:space="preserve">0.451200813055038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100827693939</t>
+    <t xml:space="preserve">0.437100768089294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000812530518</t>
+    <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575749397278</t>
+    <t xml:space="preserve">0.433575809001923</t>
   </si>
   <si>
     <t xml:space="preserve">0.444150775671005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675824165344</t>
+    <t xml:space="preserve">0.447675734758377</t>
   </si>
   <si>
     <t xml:space="preserve">0.440625786781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525801420212</t>
+    <t xml:space="preserve">0.426525741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
+    <t xml:space="preserve">0.408900797367096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900707960129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419475764036179</t>
+    <t xml:space="preserve">0.419475734233856</t>
   </si>
   <si>
     <t xml:space="preserve">0.394800752401352</t>
@@ -854,52 +851,52 @@
     <t xml:space="preserve">0.398325711488724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425726652145</t>
+    <t xml:space="preserve">0.41242578625679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050760507584</t>
+    <t xml:space="preserve">0.430050849914551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725801944733</t>
+    <t xml:space="preserve">0.454725921154022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800993442535</t>
+    <t xml:space="preserve">0.535800933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250820636749</t>
+    <t xml:space="preserve">0.458250790834427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300858020782</t>
+    <t xml:space="preserve">0.46530082821846</t>
   </si>
   <si>
     <t xml:space="preserve">0.461775839328766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375748872757</t>
+    <t xml:space="preserve">0.40537565946579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850700378418</t>
+    <t xml:space="preserve">0.401850759983063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750744819641</t>
+    <t xml:space="preserve">0.387750715017319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700707435608</t>
+    <t xml:space="preserve">0.380700677633286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366600662469864</t>
+    <t xml:space="preserve">0.366600632667542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175658941269</t>
+    <t xml:space="preserve">0.377175688743591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275644302368</t>
+    <t xml:space="preserve">0.391275703907013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650699853897</t>
+    <t xml:space="preserve">0.373650670051575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860647201538</t>
+    <t xml:space="preserve">0.34686067700386</t>
   </si>
   <si>
     <t xml:space="preserve">0.345450639724731</t>
@@ -908,37 +905,40 @@
     <t xml:space="preserve">0.359550625085831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35250061750412</t>
+    <t xml:space="preserve">0.352500647306442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400602340698</t>
+    <t xml:space="preserve">0.338400572538376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250549793243</t>
+    <t xml:space="preserve">0.317250579595566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320070564746857</t>
+    <t xml:space="preserve">0.320070534944534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296100527048111</t>
+    <t xml:space="preserve">0.296100497245789</t>
   </si>
   <si>
     <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283410519361496</t>
+    <t xml:space="preserve">0.283410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900496721268</t>
+    <t xml:space="preserve">0.267900466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770489454269</t>
+    <t xml:space="preserve">0.277770519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490459442139</t>
+    <t xml:space="preserve">0.266490489244461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800481557846</t>
+    <t xml:space="preserve">0.249570444226265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253800451755524</t>
   </si>
   <si>
     <t xml:space="preserve">0.248160436749458</t>
@@ -950,103 +950,103 @@
     <t xml:space="preserve">0.291870534420013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360481977463</t>
+    <t xml:space="preserve">0.276360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820556640625</t>
+    <t xml:space="preserve">0.284820526838303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286230474710464</t>
+    <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330549478531</t>
+    <t xml:space="preserve">0.300330579280853</t>
   </si>
   <si>
     <t xml:space="preserve">0.308790534734726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314430594444275</t>
+    <t xml:space="preserve">0.314430564641953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040602445602</t>
+    <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350564956665</t>
+    <t xml:space="preserve">0.33135062456131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325710594654083</t>
+    <t xml:space="preserve">0.325710624456406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680602550507</t>
+    <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370125621557236</t>
+    <t xml:space="preserve">0.370125651359558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38422566652298</t>
+    <t xml:space="preserve">0.384225726127625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170639514923</t>
+    <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990565061569</t>
+    <t xml:space="preserve">0.336990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630594968796</t>
+    <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025665998459</t>
+    <t xml:space="preserve">0.356025636196136</t>
   </si>
   <si>
     <t xml:space="preserve">0.351090610027313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530579805374</t>
+    <t xml:space="preserve">0.328530550003052</t>
   </si>
   <si>
     <t xml:space="preserve">0.329940557479858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32712060213089</t>
+    <t xml:space="preserve">0.327120572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300527572632</t>
+    <t xml:space="preserve">0.324300616979599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610579490662</t>
+    <t xml:space="preserve">0.311610519886017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322890609502792</t>
+    <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
     <t xml:space="preserve">0.310200572013855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150504827499</t>
+    <t xml:space="preserve">0.303150534629822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2890505194664</t>
+    <t xml:space="preserve">0.289050489664078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29328054189682</t>
+    <t xml:space="preserve">0.293280571699142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269310474395752</t>
+    <t xml:space="preserve">0.269310504198074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27213054895401</t>
+    <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
     <t xml:space="preserve">0.265080481767654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720511674881</t>
+    <t xml:space="preserve">0.270720481872559</t>
   </si>
   <si>
     <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000511884689</t>
+    <t xml:space="preserve">0.282000541687012</t>
   </si>
   <si>
     <t xml:space="preserve">0.297510534524918</t>
@@ -1058,49 +1058,49 @@
     <t xml:space="preserve">0.294690579175949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437586963176727</t>
+    <t xml:space="preserve">0.437587022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879067420959</t>
+    <t xml:space="preserve">0.406879156827927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363628864288</t>
+    <t xml:space="preserve">0.395363688468933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383848249912262</t>
+    <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
     <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171261072159</t>
+    <t xml:space="preserve">0.376171320676804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370029658079147</t>
+    <t xml:space="preserve">0.37002968788147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387686729431152</t>
+    <t xml:space="preserve">0.38768669962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777388811111</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
     <t xml:space="preserve">0.371565073728561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211155653</t>
+    <t xml:space="preserve">0.356211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069552659988</t>
+    <t xml:space="preserve">0.350069582462311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534226417542</t>
+    <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
     <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281957149506</t>
+    <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
     <t xml:space="preserve">0.353140383958817</t>
@@ -1112,52 +1112,52 @@
     <t xml:space="preserve">0.34239262342453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857237577438</t>
+    <t xml:space="preserve">0.340857207775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675799608231</t>
+    <t xml:space="preserve">0.354675769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44526395201683</t>
+    <t xml:space="preserve">0.445264011621475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394595384598</t>
+    <t xml:space="preserve">0.41839462518692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617929697037</t>
+    <t xml:space="preserve">0.460617899894714</t>
   </si>
   <si>
     <t xml:space="preserve">0.452940911054611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102342128754</t>
+    <t xml:space="preserve">0.449102491140366</t>
   </si>
   <si>
     <t xml:space="preserve">0.422233045101166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717636346817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202138185501</t>
+    <t xml:space="preserve">0.399202167987823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391525208950043</t>
+    <t xml:space="preserve">0.391525149345398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040587902069</t>
+    <t xml:space="preserve">0.403040617704391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556175470352</t>
+    <t xml:space="preserve">0.414556115865707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379242062568665</t>
+    <t xml:space="preserve">0.379242092370987</t>
   </si>
   <si>
     <t xml:space="preserve">0.373100489377975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360817313194275</t>
+    <t xml:space="preserve">0.360817342996597</t>
   </si>
   <si>
     <t xml:space="preserve">0.351604968309402</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">0.34699884057045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706676721573</t>
+    <t xml:space="preserve">0.377706706523895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958886384964</t>
+    <t xml:space="preserve">0.366958916187286</t>
   </si>
   <si>
     <t xml:space="preserve">0.374635875225067</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">0.365423530340195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432518005371</t>
+    <t xml:space="preserve">0.322432458400726</t>
   </si>
   <si>
     <t xml:space="preserve">0.305543184280396</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323967933654785</t>
+    <t xml:space="preserve">0.323967903852463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503319501877</t>
+    <t xml:space="preserve">0.325503289699554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330109447240829</t>
+    <t xml:space="preserve">0.330109477043152</t>
   </si>
   <si>
     <t xml:space="preserve">0.333180278539658</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">0.336251050233841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33778640627861</t>
+    <t xml:space="preserve">0.337786465883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928009271622</t>
+    <t xml:space="preserve">0.343928039073944</t>
   </si>
   <si>
     <t xml:space="preserve">0.334715634584427</t>
@@ -1214,25 +1214,25 @@
     <t xml:space="preserve">0.314755529165268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220143318176</t>
+    <t xml:space="preserve">0.313220113515854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308613955974579</t>
+    <t xml:space="preserve">0.308614045381546</t>
   </si>
   <si>
     <t xml:space="preserve">0.31936177611351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328574061393738</t>
+    <t xml:space="preserve">0.328574120998383</t>
   </si>
   <si>
     <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328171879053116</t>
+    <t xml:space="preserve">0.328171908855438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128470659256</t>
+    <t xml:space="preserve">0.320128500461578</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
@@ -1241,46 +1241,46 @@
     <t xml:space="preserve">0.337824016809464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432746171951</t>
+    <t xml:space="preserve">0.339432716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32656317949295</t>
+    <t xml:space="preserve">0.326563239097595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329780548810959</t>
+    <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519800901413</t>
+    <t xml:space="preserve">0.318519741296768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308867663145065</t>
+    <t xml:space="preserve">0.308867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606855630875</t>
+    <t xml:space="preserve">0.297606915235519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307259023189545</t>
+    <t xml:space="preserve">0.307258993387222</t>
   </si>
   <si>
     <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650323629379</t>
+    <t xml:space="preserve">0.305650293827057</t>
   </si>
   <si>
     <t xml:space="preserve">0.304041624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998156070709</t>
+    <t xml:space="preserve">0.295998185873032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287954747676849</t>
+    <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780816555023</t>
+    <t xml:space="preserve">0.292780786752701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737408161163</t>
+    <t xml:space="preserve">0.284737378358841</t>
   </si>
   <si>
     <t xml:space="preserve">0.281520009040833</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085270404816</t>
+    <t xml:space="preserve">0.275085240602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346077919006</t>
+    <t xml:space="preserve">0.286346107721329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693999767303</t>
+    <t xml:space="preserve">0.276693940162659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563417434692</t>
+    <t xml:space="preserve">0.289563447237015</t>
   </si>
   <si>
     <t xml:space="preserve">0.29117214679718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824254751205</t>
+    <t xml:space="preserve">0.300824224948883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432924509048</t>
+    <t xml:space="preserve">0.302432954311371</t>
   </si>
   <si>
     <t xml:space="preserve">0.313693732023239</t>
@@ -1322,34 +1322,34 @@
     <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867425203323</t>
+    <t xml:space="preserve">0.345867484807968</t>
   </si>
   <si>
     <t xml:space="preserve">0.347476154565811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341041415929794</t>
+    <t xml:space="preserve">0.341041386127472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34265011548996</t>
+    <t xml:space="preserve">0.342650085687637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300703525543213</t>
+    <t xml:space="preserve">0.300703555345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297227203845978</t>
+    <t xml:space="preserve">0.297227174043655</t>
   </si>
   <si>
     <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290274560451508</t>
+    <t xml:space="preserve">0.290274530649185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292012691497803</t>
+    <t xml:space="preserve">0.29201266169548</t>
   </si>
   <si>
     <t xml:space="preserve">0.30591806769371</t>
@@ -1358,25 +1358,25 @@
     <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536310195923</t>
+    <t xml:space="preserve">0.288536339998245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28332182765007</t>
+    <t xml:space="preserve">0.283321857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29375085234642</t>
+    <t xml:space="preserve">0.293750882148743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285060048103333</t>
+    <t xml:space="preserve">0.28506001830101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278107315301895</t>
+    <t xml:space="preserve">0.278107285499573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281583666801453</t>
+    <t xml:space="preserve">0.281583696603775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274630963802338</t>
+    <t xml:space="preserve">0.27463099360466</t>
   </si>
   <si>
     <t xml:space="preserve">0.286798179149628</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">0.279845505952835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369124650955</t>
+    <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27289280295372</t>
+    <t xml:space="preserve">0.272892862558365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394389390945</t>
+    <t xml:space="preserve">0.309394419193268</t>
   </si>
   <si>
     <t xml:space="preserve">0.298965364694595</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">0.307656228542328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132609844208</t>
+    <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870770692825</t>
+    <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
     <t xml:space="preserve">0.330252438783646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037956237793</t>
+    <t xml:space="preserve">0.325037926435471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31460890173912</t>
+    <t xml:space="preserve">0.314608931541443</t>
   </si>
   <si>
     <t xml:space="preserve">0.319823414087296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085223436356</t>
+    <t xml:space="preserve">0.318085253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31634709239006</t>
+    <t xml:space="preserve">0.316347032785416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31590336561203</t>
+    <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
     <t xml:space="preserve">0.305254966020584</t>
@@ -1436,70 +1436,70 @@
     <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606536626816</t>
+    <t xml:space="preserve">0.294606506824493</t>
   </si>
   <si>
     <t xml:space="preserve">0.292831808328629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480207920074</t>
+    <t xml:space="preserve">0.303480237722397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233924150467</t>
+    <t xml:space="preserve">0.319233953952789</t>
   </si>
   <si>
     <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30835098028183</t>
+    <t xml:space="preserve">0.308350950479507</t>
   </si>
   <si>
     <t xml:space="preserve">0.31197863817215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30653715133667</t>
+    <t xml:space="preserve">0.306537181138992</t>
   </si>
   <si>
     <t xml:space="preserve">0.292026519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293840348720551</t>
+    <t xml:space="preserve">0.293840378522873</t>
   </si>
   <si>
     <t xml:space="preserve">0.29565417766571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30472332239151</t>
+    <t xml:space="preserve">0.304723292589188</t>
   </si>
   <si>
     <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290212690830231</t>
+    <t xml:space="preserve">0.290212631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288398832082748</t>
+    <t xml:space="preserve">0.288398861885071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771203994751</t>
+    <t xml:space="preserve">0.284771263599396</t>
   </si>
   <si>
     <t xml:space="preserve">0.286585032939911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297468036413193</t>
+    <t xml:space="preserve">0.29746800661087</t>
   </si>
   <si>
     <t xml:space="preserve">0.300716459751129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295147627592087</t>
+    <t xml:space="preserve">0.295147657394409</t>
   </si>
   <si>
     <t xml:space="preserve">0.308141559362411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297003924846649</t>
+    <t xml:space="preserve">0.297003895044327</t>
   </si>
   <si>
     <t xml:space="preserve">0.309997886419296</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">0.317422956228256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322991788387299</t>
+    <t xml:space="preserve">0.322991758584976</t>
   </si>
   <si>
     <t xml:space="preserve">0.324848026037216</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">0.319279223680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334129452705383</t>
+    <t xml:space="preserve">0.334129422903061</t>
   </si>
   <si>
     <t xml:space="preserve">0.337841957807541</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">0.328126817941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610274553299</t>
+    <t xml:space="preserve">0.337610244750977</t>
   </si>
   <si>
     <t xml:space="preserve">0.331920206546783</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746741533279</t>
+    <t xml:space="preserve">0.316746711730957</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">0.32243674993515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32433345913887</t>
+    <t xml:space="preserve">0.324333488941193</t>
   </si>
   <si>
     <t xml:space="preserve">0.347093731164932</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">0.312953352928162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307263284921646</t>
+    <t xml:space="preserve">0.307263255119324</t>
   </si>
   <si>
     <t xml:space="preserve">0.360370516777039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887060165405</t>
+    <t xml:space="preserve">0.350887089967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">0.354680478572845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377440690994263</t>
+    <t xml:space="preserve">0.377440720796585</t>
   </si>
   <si>
     <t xml:space="preserve">0.405891001224518</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">0.417271107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787680625916</t>
+    <t xml:space="preserve">0.407787710428238</t>
   </si>
   <si>
     <t xml:space="preserve">0.398304253816605</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">0.396407574415207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381234049797058</t>
+    <t xml:space="preserve">0.38123407959938</t>
   </si>
   <si>
     <t xml:space="preserve">0.383130788803101</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">0.369853943586349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373647332191467</t>
+    <t xml:space="preserve">0.373647302389145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544041395187</t>
+    <t xml:space="preserve">0.375544011592865</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402097642421722</t>
+    <t xml:space="preserve">0.4020976126194</t>
   </si>
   <si>
     <t xml:space="preserve">0.415026515722275</t>
@@ -26116,7 +26116,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26142,7 +26142,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26168,7 +26168,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26194,7 +26194,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26220,7 +26220,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26246,7 +26246,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26272,7 +26272,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26298,7 +26298,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26324,7 +26324,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26350,7 +26350,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26376,7 +26376,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26402,7 +26402,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26428,7 +26428,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26454,7 +26454,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26480,7 +26480,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26506,7 +26506,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26558,7 +26558,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26584,7 +26584,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26610,7 +26610,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26636,7 +26636,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26662,7 +26662,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26688,7 +26688,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26714,7 +26714,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26740,7 +26740,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26766,7 +26766,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26792,7 +26792,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26818,7 +26818,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26844,7 +26844,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26870,7 +26870,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26896,7 +26896,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26922,7 +26922,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26948,7 +26948,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26974,7 +26974,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27000,7 +27000,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27026,7 +27026,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27104,7 +27104,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27182,7 +27182,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27208,7 +27208,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27260,7 +27260,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27286,7 +27286,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27312,7 +27312,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27338,7 +27338,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27494,7 +27494,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27520,7 +27520,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27546,7 +27546,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27624,7 +27624,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27650,7 +27650,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28066,7 +28066,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28092,7 +28092,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28118,7 +28118,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28144,7 +28144,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28170,7 +28170,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28196,7 +28196,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28222,7 +28222,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28248,7 +28248,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28274,7 +28274,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28326,7 +28326,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28352,7 +28352,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28378,7 +28378,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28404,7 +28404,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28430,7 +28430,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28456,7 +28456,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28482,7 +28482,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28508,7 +28508,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28534,7 +28534,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28560,7 +28560,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28586,7 +28586,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28664,7 +28664,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28690,7 +28690,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28716,7 +28716,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28742,7 +28742,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28768,7 +28768,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28794,7 +28794,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28820,7 +28820,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28846,7 +28846,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28872,7 +28872,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28898,7 +28898,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28924,7 +28924,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28950,7 +28950,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28976,7 +28976,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29002,7 +29002,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29028,7 +29028,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29054,7 +29054,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29080,7 +29080,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29106,7 +29106,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29132,7 +29132,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29158,7 +29158,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29184,7 +29184,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29288,7 +29288,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29340,7 +29340,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29418,7 +29418,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29444,7 +29444,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29470,7 +29470,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29496,7 +29496,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29522,7 +29522,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29548,7 +29548,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29574,7 +29574,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29600,7 +29600,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29626,7 +29626,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29652,7 +29652,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29678,7 +29678,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29704,7 +29704,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29730,7 +29730,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29756,7 +29756,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29782,7 +29782,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29808,7 +29808,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29834,7 +29834,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29860,7 +29860,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29886,7 +29886,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30068,7 +30068,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30198,7 +30198,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30224,7 +30224,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30250,7 +30250,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30302,7 +30302,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30328,7 +30328,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30406,7 +30406,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30796,7 +30796,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30822,7 +30822,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30926,7 +30926,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30978,7 +30978,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31004,7 +31004,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31030,7 +31030,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31134,7 +31134,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31160,7 +31160,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31186,7 +31186,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31238,7 +31238,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31264,7 +31264,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31290,7 +31290,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31316,7 +31316,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31342,7 +31342,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31368,7 +31368,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31394,7 +31394,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31420,7 +31420,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31446,7 +31446,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31472,7 +31472,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31498,7 +31498,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31524,7 +31524,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31550,7 +31550,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31576,7 +31576,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31602,7 +31602,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31628,7 +31628,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31654,7 +31654,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31680,7 +31680,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31706,7 +31706,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31732,7 +31732,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31758,7 +31758,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31784,7 +31784,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31810,7 +31810,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31836,7 +31836,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31862,7 +31862,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31888,7 +31888,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31914,7 +31914,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31966,7 +31966,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31992,7 +31992,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32018,7 +32018,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32070,7 +32070,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32252,7 +32252,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32278,7 +32278,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32304,7 +32304,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32330,7 +32330,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32668,7 +32668,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33162,7 +33162,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34202,7 +34202,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34410,7 +34410,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34436,7 +34436,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34930,7 +34930,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35580,7 +35580,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35606,7 +35606,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35658,7 +35658,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35710,7 +35710,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35736,7 +35736,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35788,7 +35788,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35814,7 +35814,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35840,7 +35840,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35892,7 +35892,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35918,7 +35918,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35944,7 +35944,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35970,7 +35970,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35996,7 +35996,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36022,7 +36022,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36048,7 +36048,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36074,7 +36074,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36100,7 +36100,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -67433,6 +67433,32 @@
         <v>565</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.3333333333</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>565</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179178789258003</t>
+    <t xml:space="preserve">0.17917874455452</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179818719625473</t>
+    <t xml:space="preserve">0.179818674921989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979152321815</t>
+    <t xml:space="preserve">0.175979182124138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174699336290359</t>
+    <t xml:space="preserve">0.174699306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167020216584206</t>
+    <t xml:space="preserve">0.167020246386528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779530286789</t>
+    <t xml:space="preserve">0.172779574990273</t>
   </si>
   <si>
     <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902723073959</t>
+    <t xml:space="preserve">0.145902708172798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493968605995</t>
+    <t xml:space="preserve">0.152493953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822499275208</t>
+    <t xml:space="preserve">0.14782252907753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155501574277878</t>
+    <t xml:space="preserve">0.1555016040802</t>
   </si>
   <si>
     <t xml:space="preserve">0.156141519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517827391624</t>
+    <t xml:space="preserve">0.153517812490463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102330207825</t>
+    <t xml:space="preserve">0.149102345108986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142383143305779</t>
+    <t xml:space="preserve">0.142383128404617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142063170671463</t>
+    <t xml:space="preserve">0.142063185572624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142447143793106</t>
+    <t xml:space="preserve">0.142447113990784</t>
   </si>
   <si>
     <t xml:space="preserve">0.14462286233902</t>
@@ -98,52 +98,52 @@
     <t xml:space="preserve">0.141423255205154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15383780002594</t>
+    <t xml:space="preserve">0.153837770223618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173419445753098</t>
+    <t xml:space="preserve">0.17341947555542</t>
   </si>
   <si>
     <t xml:space="preserve">0.169835895299911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380286216736</t>
+    <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981071949005</t>
+    <t xml:space="preserve">0.159981057047844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421365380287</t>
+    <t xml:space="preserve">0.157421380281448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301982045174</t>
+    <t xml:space="preserve">0.152301952242851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158509224653244</t>
+    <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
     <t xml:space="preserve">0.163820594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836832761765</t>
+    <t xml:space="preserve">0.161836862564087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522605776787</t>
+    <t xml:space="preserve">0.180522635579109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18045862019062</t>
+    <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
     <t xml:space="preserve">0.174059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168940007686615</t>
+    <t xml:space="preserve">0.168939992785454</t>
   </si>
   <si>
     <t xml:space="preserve">0.191977262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136742830276</t>
+    <t xml:space="preserve">0.196136772632599</t>
   </si>
   <si>
     <t xml:space="preserve">0.195176914334297</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">0.187497794628143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184938132762909</t>
+    <t xml:space="preserve">0.184938073158264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775720834732</t>
+    <t xml:space="preserve">0.204775765538216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454825639725</t>
+    <t xml:space="preserve">0.212454870343208</t>
   </si>
   <si>
     <t xml:space="preserve">0.204711765050888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200296312570572</t>
+    <t xml:space="preserve">0.200296252965927</t>
   </si>
   <si>
     <t xml:space="preserve">0.19773656129837</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">0.182378396391869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578048229218</t>
+    <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907516360283</t>
+    <t xml:space="preserve">0.172907546162605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499714255333</t>
+    <t xml:space="preserve">0.171499669551849</t>
   </si>
   <si>
     <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349729418755</t>
+    <t xml:space="preserve">0.154349714517593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579923152924</t>
+    <t xml:space="preserve">0.169579893350601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917041659355</t>
+    <t xml:space="preserve">0.159917056560516</t>
   </si>
   <si>
     <t xml:space="preserve">0.154861658811569</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">0.156781435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160492986440659</t>
+    <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417585730553</t>
+    <t xml:space="preserve">0.18941755592823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191337317228317</t>
+    <t xml:space="preserve">0.191337332129478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857879161835</t>
+    <t xml:space="preserve">0.186857864260674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002073645592</t>
+    <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
     <t xml:space="preserve">0.170219853520393</t>
@@ -224,85 +224,85 @@
     <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221743345261</t>
+    <t xml:space="preserve">0.154221758246422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022136211395</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
     <t xml:space="preserve">0.147182568907738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260887980461</t>
+    <t xml:space="preserve">0.161260902881622</t>
   </si>
   <si>
     <t xml:space="preserve">0.168172091245651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173739463090897</t>
+    <t xml:space="preserve">0.173739403486252</t>
   </si>
   <si>
     <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897991061211</t>
+    <t xml:space="preserve">0.185897976160049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135805368423</t>
+    <t xml:space="preserve">0.204135850071907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096675634384</t>
+    <t xml:space="preserve">0.197096645832062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181354522705078</t>
+    <t xml:space="preserve">0.181354537606239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194217041134834</t>
+    <t xml:space="preserve">0.194217011332512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20464776456356</t>
+    <t xml:space="preserve">0.204647749662399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376506567001</t>
+    <t xml:space="preserve">0.198376521468163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240870118141</t>
+    <t xml:space="preserve">0.195240899920464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495919704437</t>
+    <t xml:space="preserve">0.203495889902115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934323310852</t>
+    <t xml:space="preserve">0.216934308409691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709890127182</t>
+    <t xml:space="preserve">0.220709919929504</t>
   </si>
   <si>
     <t xml:space="preserve">0.23677197098732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531284689903</t>
+    <t xml:space="preserve">0.242531299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969703197479</t>
+    <t xml:space="preserve">0.255969732999802</t>
   </si>
   <si>
     <t xml:space="preserve">0.271967798471451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286848545074</t>
+    <t xml:space="preserve">0.280286818742752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295644998550415</t>
+    <t xml:space="preserve">0.29564505815506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303963989019394</t>
+    <t xml:space="preserve">0.303964018821716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262368947267532</t>
+    <t xml:space="preserve">0.26236891746521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2648646235466</t>
+    <t xml:space="preserve">0.264864683151245</t>
   </si>
   <si>
     <t xml:space="preserve">0.254753828048706</t>
@@ -311,52 +311,52 @@
     <t xml:space="preserve">0.25468984246254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202709317207</t>
+    <t xml:space="preserve">0.24720273911953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650653123856</t>
+    <t xml:space="preserve">0.247650623321533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778668999672</t>
+    <t xml:space="preserve">0.247778654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572319149971</t>
+    <t xml:space="preserve">0.233572348952293</t>
   </si>
   <si>
     <t xml:space="preserve">0.238051801919937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374586939812</t>
+    <t xml:space="preserve">0.214374601840973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663065314293</t>
+    <t xml:space="preserve">0.210663080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654507279396</t>
+    <t xml:space="preserve">0.215654477477074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518811225891</t>
+    <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241891339421272</t>
+    <t xml:space="preserve">0.241891384124756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570429325104</t>
+    <t xml:space="preserve">0.249570459127426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980180859566</t>
+    <t xml:space="preserve">0.234980151057243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652557849884</t>
+    <t xml:space="preserve">0.231652572751045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971593022346</t>
+    <t xml:space="preserve">0.239971578121185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372726917267</t>
+    <t xml:space="preserve">0.230372712016106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173089981079</t>
+    <t xml:space="preserve">0.227173134684563</t>
   </si>
   <si>
     <t xml:space="preserve">0.220773860812187</t>
@@ -371,94 +371,94 @@
     <t xml:space="preserve">0.204839766025543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207975372672081</t>
+    <t xml:space="preserve">0.20797535777092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535079240799</t>
+    <t xml:space="preserve">0.210535064339638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20989516377449</t>
+    <t xml:space="preserve">0.209895148873329</t>
   </si>
   <si>
     <t xml:space="preserve">0.21117502450943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582841515541</t>
+    <t xml:space="preserve">0.212582811713219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782448649406</t>
+    <t xml:space="preserve">0.215782418847084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732811450958</t>
+    <t xml:space="preserve">0.229732796549797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845481872559</t>
+    <t xml:space="preserve">0.223845466971397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805355072021</t>
+    <t xml:space="preserve">0.224805384874344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636319637299</t>
+    <t xml:space="preserve">0.23363633453846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627716898918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580936789513</t>
+    <t xml:space="preserve">0.22858090698719</t>
   </si>
   <si>
     <t xml:space="preserve">0.223973482847214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717510700226</t>
+    <t xml:space="preserve">0.223717495799065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837831497192</t>
+    <t xml:space="preserve">0.220837861299515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235492140054703</t>
+    <t xml:space="preserve">0.23549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965847373009</t>
+    <t xml:space="preserve">0.220965802669525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365091443062</t>
+    <t xml:space="preserve">0.227365076541901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556157112122</t>
+    <t xml:space="preserve">0.302556186914444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358357578516006</t>
+    <t xml:space="preserve">0.358357489109039</t>
   </si>
   <si>
     <t xml:space="preserve">0.47354394197464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454254150391</t>
+    <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485702514648438</t>
+    <t xml:space="preserve">0.485702484846115</t>
   </si>
   <si>
     <t xml:space="preserve">0.444747358560562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709106683731</t>
+    <t xml:space="preserve">0.429709136486053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152316808701</t>
+    <t xml:space="preserve">0.403152287006378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371156096458435</t>
+    <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710073947906</t>
+    <t xml:space="preserve">0.421710044145584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035686254501</t>
+    <t xml:space="preserve">0.374035745859146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754888057709</t>
+    <t xml:space="preserve">0.380754947662354</t>
   </si>
   <si>
     <t xml:space="preserve">0.352598249912262</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">0.331800669431686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602029561996</t>
+    <t xml:space="preserve">0.320602059364319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332440733909607</t>
+    <t xml:space="preserve">0.33244064450264</t>
   </si>
   <si>
     <t xml:space="preserve">0.340439707040787</t>
@@ -479,64 +479,64 @@
     <t xml:space="preserve">0.327641189098358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157971382141</t>
+    <t xml:space="preserve">0.355158030986786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347478926181793</t>
+    <t xml:space="preserve">0.347478806972504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760572433472</t>
+    <t xml:space="preserve">0.332760602235794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121654033661</t>
+    <t xml:space="preserve">0.324121624231339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327001243829727</t>
+    <t xml:space="preserve">0.327001303434372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159846305847</t>
+    <t xml:space="preserve">0.339159786701202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960179567337</t>
+    <t xml:space="preserve">0.335960149765015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161751031876</t>
+    <t xml:space="preserve">0.323161780834198</t>
   </si>
   <si>
     <t xml:space="preserve">0.330200910568237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31996214389801</t>
+    <t xml:space="preserve">0.319962114095688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402452230453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759694576263</t>
+    <t xml:space="preserve">0.340759664773941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801696300507</t>
+    <t xml:space="preserve">0.323801666498184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521775960922</t>
+    <t xml:space="preserve">0.322521805763245</t>
   </si>
   <si>
     <t xml:space="preserve">0.334360390901566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32892107963562</t>
+    <t xml:space="preserve">0.328921049833298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334040433168411</t>
+    <t xml:space="preserve">0.334040492773056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163625955582</t>
+    <t xml:space="preserve">0.307163655757904</t>
   </si>
   <si>
     <t xml:space="preserve">0.316122591495514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698521375656</t>
+    <t xml:space="preserve">0.316698491573334</t>
   </si>
   <si>
     <t xml:space="preserve">0.326361358165741</t>
@@ -548,52 +548,52 @@
     <t xml:space="preserve">0.364756792783737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559060573578</t>
+    <t xml:space="preserve">0.345559149980545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346199035644531</t>
+    <t xml:space="preserve">0.346199005842209</t>
   </si>
   <si>
     <t xml:space="preserve">0.325081527233124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959301710129</t>
+    <t xml:space="preserve">0.343959331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282101631165</t>
+    <t xml:space="preserve">0.320282131433487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720505237579</t>
+    <t xml:space="preserve">0.333720445632935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753013134003</t>
+    <t xml:space="preserve">0.396753042936325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275449991226</t>
+    <t xml:space="preserve">0.376275479793549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635534524918</t>
+    <t xml:space="preserve">0.375635504722595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376915395259857</t>
+    <t xml:space="preserve">0.376915335655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.370196163654327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555310726166</t>
+    <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351318418979645</t>
+    <t xml:space="preserve">0.351318389177322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117904186249</t>
+    <t xml:space="preserve">0.356117844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917240381241</t>
+    <t xml:space="preserve">0.360917270183563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715758323669</t>
+    <t xml:space="preserve">0.373715728521347</t>
   </si>
   <si>
     <t xml:space="preserve">0.395793110132217</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594440460205</t>
+    <t xml:space="preserve">0.38459450006485</t>
   </si>
   <si>
     <t xml:space="preserve">0.383954524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193351268768</t>
+    <t xml:space="preserve">0.394193291664124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274423122406</t>
+    <t xml:space="preserve">0.384274482727051</t>
   </si>
   <si>
     <t xml:space="preserve">0.415310859680176</t>
@@ -620,82 +620,82 @@
     <t xml:space="preserve">0.42235004901886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312674999237</t>
+    <t xml:space="preserve">0.399312704801559</t>
   </si>
   <si>
     <t xml:space="preserve">0.383634597063065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553376197815</t>
+    <t xml:space="preserve">0.39355343580246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943186044693</t>
+    <t xml:space="preserve">0.479943156242371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447307020425797</t>
+    <t xml:space="preserve">0.447307080030441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745453834534</t>
+    <t xml:space="preserve">0.460745424032211</t>
   </si>
   <si>
     <t xml:space="preserve">0.441547721624374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027189493179</t>
+    <t xml:space="preserve">0.446027278900146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346179962158</t>
+    <t xml:space="preserve">0.454346269369125</t>
   </si>
   <si>
     <t xml:space="preserve">0.447946965694427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43002912402153</t>
+    <t xml:space="preserve">0.430029064416885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588785886765</t>
+    <t xml:space="preserve">0.432588756084442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749173879623</t>
+    <t xml:space="preserve">0.428749203681946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230576276779</t>
+    <t xml:space="preserve">0.417230635881424</t>
   </si>
   <si>
     <t xml:space="preserve">0.413391083478928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
+    <t xml:space="preserve">0.41595071554184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070158481598</t>
+    <t xml:space="preserve">0.421070128679276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551441669464</t>
+    <t xml:space="preserve">0.409551531076431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267890691757</t>
+    <t xml:space="preserve">0.44026792049408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909651279449</t>
+    <t xml:space="preserve">0.424909740686417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470984280109406</t>
+    <t xml:space="preserve">0.470984220504761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148507356644</t>
+    <t xml:space="preserve">0.435148447751999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406991839408875</t>
+    <t xml:space="preserve">0.40699177980423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189452409744</t>
+    <t xml:space="preserve">0.426189571619034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431309014558792</t>
+    <t xml:space="preserve">0.431308954954147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510407209396</t>
+    <t xml:space="preserve">0.418510556221008</t>
   </si>
   <si>
     <t xml:space="preserve">0.405711978673935</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">0.412111222743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389073938131332</t>
+    <t xml:space="preserve">0.389073878526688</t>
   </si>
   <si>
     <t xml:space="preserve">0.390353828668594</t>
@@ -716,37 +716,37 @@
     <t xml:space="preserve">0.410831391811371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43898794054985</t>
+    <t xml:space="preserve">0.438988029956818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469402551651</t>
+    <t xml:space="preserve">0.427469342947006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670944213867</t>
+    <t xml:space="preserve">0.4146708548069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872396469116</t>
+    <t xml:space="preserve">0.401872456073761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419790327548981</t>
+    <t xml:space="preserve">0.419790297746658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271610736847</t>
+    <t xml:space="preserve">0.408271700143814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629850149155</t>
+    <t xml:space="preserve">0.423629879951477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596345186234</t>
+    <t xml:space="preserve">0.368596315383911</t>
   </si>
   <si>
     <t xml:space="preserve">0.37243589758873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369876265525818</t>
+    <t xml:space="preserve">0.369876146316528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346838891506195</t>
+    <t xml:space="preserve">0.34683895111084</t>
   </si>
   <si>
     <t xml:space="preserve">0.335320293903351</t>
@@ -761,148 +761,148 @@
     <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999428510666</t>
+    <t xml:space="preserve">0.342999339103699</t>
   </si>
   <si>
     <t xml:space="preserve">0.344279199838638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958304643631</t>
+    <t xml:space="preserve">0.351958364248276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835171461105</t>
+    <t xml:space="preserve">0.378835111856461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913490533829</t>
+    <t xml:space="preserve">0.392913520336151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359637439250946</t>
+    <t xml:space="preserve">0.359637349843979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316484451294</t>
+    <t xml:space="preserve">0.367316514253616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385234415531158</t>
+    <t xml:space="preserve">0.385234385728836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382674634456635</t>
+    <t xml:space="preserve">0.382674664258957</t>
   </si>
   <si>
     <t xml:space="preserve">0.380115032196045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633629798889</t>
+    <t xml:space="preserve">0.391633659601212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032814264297</t>
+    <t xml:space="preserve">0.39803284406662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592625141144</t>
+    <t xml:space="preserve">0.400592505931854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948930025101</t>
+    <t xml:space="preserve">0.431948840618134</t>
   </si>
   <si>
     <t xml:space="preserve">0.438348084688187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545846700668</t>
+    <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945120573044</t>
+    <t xml:space="preserve">0.463945060968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350925207138</t>
+    <t xml:space="preserve">0.472350835800171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200753450394</t>
+    <t xml:space="preserve">0.451200813055038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100738286972</t>
+    <t xml:space="preserve">0.437100797891617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000752925873</t>
+    <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575719594955</t>
+    <t xml:space="preserve">0.4335757791996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150805473328</t>
+    <t xml:space="preserve">0.44415083527565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675764560699</t>
+    <t xml:space="preserve">0.447675794363022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625756978989</t>
+    <t xml:space="preserve">0.440625816583633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525831222534</t>
+    <t xml:space="preserve">0.426525801420212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900767564774</t>
+    <t xml:space="preserve">0.408900707960129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419475734233856</t>
+    <t xml:space="preserve">0.419475853443146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39480072259903</t>
+    <t xml:space="preserve">0.394800662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325711488724</t>
+    <t xml:space="preserve">0.398325681686401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425756454468</t>
+    <t xml:space="preserve">0.41242578625679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050849914551</t>
+    <t xml:space="preserve">0.430050820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725801944733</t>
+    <t xml:space="preserve">0.45472577214241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800874233246</t>
+    <t xml:space="preserve">0.535800993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250850439072</t>
+    <t xml:space="preserve">0.458250880241394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46530082821846</t>
+    <t xml:space="preserve">0.465300858020782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775898933411</t>
+    <t xml:space="preserve">0.461775809526443</t>
   </si>
   <si>
     <t xml:space="preserve">0.405375748872757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40185073018074</t>
+    <t xml:space="preserve">0.401850700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750715017319</t>
+    <t xml:space="preserve">0.387750744819641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700647830963</t>
+    <t xml:space="preserve">0.380700707435608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366600692272186</t>
+    <t xml:space="preserve">0.366600632667542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175718545914</t>
+    <t xml:space="preserve">0.377175688743591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275733709335</t>
+    <t xml:space="preserve">0.391275763511658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650670051575</t>
+    <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860587596893</t>
+    <t xml:space="preserve">0.346860647201538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450580120087</t>
+    <t xml:space="preserve">0.345450609922409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550714492798</t>
+    <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
     <t xml:space="preserve">0.35250061750412</t>
@@ -917,55 +917,55 @@
     <t xml:space="preserve">0.320070594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296100556850433</t>
+    <t xml:space="preserve">0.296100497245789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26367050409317</t>
+    <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900437116623</t>
+    <t xml:space="preserve">0.267900496721268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770549058914</t>
+    <t xml:space="preserve">0.277770519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490489244461</t>
+    <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800451755524</t>
+    <t xml:space="preserve">0.253800481557846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24816045165062</t>
+    <t xml:space="preserve">0.248160406947136</t>
   </si>
   <si>
     <t xml:space="preserve">0.290460526943207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291870504617691</t>
+    <t xml:space="preserve">0.291870534420013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360511779785</t>
+    <t xml:space="preserve">0.27636045217514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820526838303</t>
+    <t xml:space="preserve">0.28482049703598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286230504512787</t>
+    <t xml:space="preserve">0.286230534315109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330519676208</t>
+    <t xml:space="preserve">0.300330489873886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790564537048</t>
+    <t xml:space="preserve">0.308790594339371</t>
   </si>
   <si>
     <t xml:space="preserve">0.314430564641953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040602445602</t>
+    <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
     <t xml:space="preserve">0.331350594758987</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">0.325710624456406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680602550507</t>
+    <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
     <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38422566652298</t>
+    <t xml:space="preserve">0.384225696325302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170609712601</t>
+    <t xml:space="preserve">0.334170550107956</t>
   </si>
   <si>
     <t xml:space="preserve">0.336990594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630624771118</t>
+    <t xml:space="preserve">0.342630654573441</t>
   </si>
   <si>
     <t xml:space="preserve">0.356025636196136</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">0.351090639829636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530609607697</t>
+    <t xml:space="preserve">0.328530579805374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329940617084503</t>
+    <t xml:space="preserve">0.329940557479858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32712060213089</t>
+    <t xml:space="preserve">0.327120572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300587177277</t>
+    <t xml:space="preserve">0.324300646781921</t>
   </si>
   <si>
     <t xml:space="preserve">0.311610549688339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322890520095825</t>
+    <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310200572013855</t>
+    <t xml:space="preserve">0.310200542211533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150534629822</t>
+    <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
     <t xml:space="preserve">0.289050549268723</t>
@@ -1031,43 +1031,43 @@
     <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130489349365</t>
+    <t xml:space="preserve">0.272130519151688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265080481767654</t>
+    <t xml:space="preserve">0.265080451965332</t>
   </si>
   <si>
     <t xml:space="preserve">0.270720481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950474500656</t>
+    <t xml:space="preserve">0.274950534105301</t>
   </si>
   <si>
     <t xml:space="preserve">0.282000482082367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297510534524918</t>
+    <t xml:space="preserve">0.29751056432724</t>
   </si>
   <si>
     <t xml:space="preserve">0.301740556955338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690549373627</t>
+    <t xml:space="preserve">0.294690579175949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437586963176727</t>
+    <t xml:space="preserve">0.437586933374405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879127025604</t>
+    <t xml:space="preserve">0.406879067420959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363658666611</t>
+    <t xml:space="preserve">0.395363688468933</t>
   </si>
   <si>
     <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368494242429733</t>
+    <t xml:space="preserve">0.368494302034378</t>
   </si>
   <si>
     <t xml:space="preserve">0.376171261072159</t>
@@ -1088,67 +1088,67 @@
     <t xml:space="preserve">0.356211125850677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069612264633</t>
+    <t xml:space="preserve">0.350069552659988</t>
   </si>
   <si>
     <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463424921036</t>
+    <t xml:space="preserve">0.345463365316391</t>
   </si>
   <si>
     <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140354156494</t>
+    <t xml:space="preserve">0.353140383958817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746571302414</t>
+    <t xml:space="preserve">0.357746541500092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857267379761</t>
+    <t xml:space="preserve">0.340857207775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675740003586</t>
+    <t xml:space="preserve">0.354675799608231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263981819153</t>
+    <t xml:space="preserve">0.445263922214508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394565582275</t>
+    <t xml:space="preserve">0.418394595384598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617959499359</t>
+    <t xml:space="preserve">0.460617899894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940851449966</t>
+    <t xml:space="preserve">0.452940881252289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102401733398</t>
+    <t xml:space="preserve">0.449102431535721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422233045101166</t>
+    <t xml:space="preserve">0.422233104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717636346817</t>
   </si>
   <si>
     <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391525208950043</t>
+    <t xml:space="preserve">0.39152517914772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040647506714</t>
+    <t xml:space="preserve">0.403040617704391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556056261063</t>
+    <t xml:space="preserve">0.414556175470352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379242092370987</t>
+    <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
     <t xml:space="preserve">0.373100489377975</t>
@@ -1163,25 +1163,25 @@
     <t xml:space="preserve">0.346998810768127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706706523895</t>
+    <t xml:space="preserve">0.37770664691925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958916187286</t>
+    <t xml:space="preserve">0.366958886384964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374635875225067</t>
+    <t xml:space="preserve">0.37463590502739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423530340195</t>
+    <t xml:space="preserve">0.365423500537872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432488203049</t>
+    <t xml:space="preserve">0.322432458400726</t>
   </si>
   <si>
     <t xml:space="preserve">0.305543154478073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307078570127487</t>
+    <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
     <t xml:space="preserve">0.323967903852463</t>
@@ -1193,37 +1193,37 @@
     <t xml:space="preserve">0.330109477043152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180248737335</t>
+    <t xml:space="preserve">0.333180278539658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251050233841</t>
+    <t xml:space="preserve">0.336251020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33778640627861</t>
+    <t xml:space="preserve">0.337786436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928039073944</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
     <t xml:space="preserve">0.334715664386749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31475555896759</t>
+    <t xml:space="preserve">0.314755529165268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220202922821</t>
+    <t xml:space="preserve">0.313220173120499</t>
   </si>
   <si>
     <t xml:space="preserve">0.308613985776901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31936177611351</t>
+    <t xml:space="preserve">0.319361716508865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32857409119606</t>
+    <t xml:space="preserve">0.328574120998383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345869779587</t>
+    <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.328171908855438</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">0.320128440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32495453953743</t>
+    <t xml:space="preserve">0.324954509735107</t>
   </si>
   <si>
     <t xml:space="preserve">0.337823957204819</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">0.308867663145065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606825828552</t>
+    <t xml:space="preserve">0.297606915235519</t>
   </si>
   <si>
     <t xml:space="preserve">0.307258993387222</t>
@@ -1274,64 +1274,64 @@
     <t xml:space="preserve">0.287954747676849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780786752701</t>
+    <t xml:space="preserve">0.292780816555023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737318754196</t>
+    <t xml:space="preserve">0.284737378358841</t>
   </si>
   <si>
     <t xml:space="preserve">0.28151997923851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128708600998</t>
+    <t xml:space="preserve">0.283128678798676</t>
   </si>
   <si>
     <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346048116684</t>
+    <t xml:space="preserve">0.286346077919006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693969964981</t>
+    <t xml:space="preserve">0.276693940162659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289563447237015</t>
+    <t xml:space="preserve">0.289563417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291172116994858</t>
+    <t xml:space="preserve">0.291172087192535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824224948883</t>
+    <t xml:space="preserve">0.300824254751205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432924509048</t>
+    <t xml:space="preserve">0.302432864904404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693702220917</t>
+    <t xml:space="preserve">0.313693732023239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294389545917511</t>
+    <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
     <t xml:space="preserve">0.35230216383934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34425875544548</t>
+    <t xml:space="preserve">0.344258785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867425203323</t>
+    <t xml:space="preserve">0.345867455005646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347476154565811</t>
+    <t xml:space="preserve">0.347476124763489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34104135632515</t>
+    <t xml:space="preserve">0.341041386127472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650085687637</t>
+    <t xml:space="preserve">0.342650055885315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
     <t xml:space="preserve">0.300703525543213</t>
@@ -1340,40 +1340,40 @@
     <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29548904299736</t>
+    <t xml:space="preserve">0.295489013195038</t>
   </si>
   <si>
     <t xml:space="preserve">0.290274530649185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292012721300125</t>
+    <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305918097496033</t>
+    <t xml:space="preserve">0.305918037891388</t>
   </si>
   <si>
     <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536339998245</t>
+    <t xml:space="preserve">0.288536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28332182765007</t>
+    <t xml:space="preserve">0.283321857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293750882148743</t>
+    <t xml:space="preserve">0.29375085234642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285059988498688</t>
+    <t xml:space="preserve">0.28506001830101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278107315301895</t>
+    <t xml:space="preserve">0.278107285499573</t>
   </si>
   <si>
     <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274631023406982</t>
+    <t xml:space="preserve">0.274630963802338</t>
   </si>
   <si>
     <t xml:space="preserve">0.286798179149628</t>
@@ -1382,31 +1382,31 @@
     <t xml:space="preserve">0.279845505952835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2763691842556</t>
+    <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272892773151398</t>
+    <t xml:space="preserve">0.27289280295372</t>
   </si>
   <si>
     <t xml:space="preserve">0.309394389390945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29896542429924</t>
+    <t xml:space="preserve">0.298965394496918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656168937683</t>
+    <t xml:space="preserve">0.307656228542328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132580041885</t>
+    <t xml:space="preserve">0.311132609844208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870770692825</t>
+    <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252438783646</t>
+    <t xml:space="preserve">0.330252408981323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037926435471</t>
+    <t xml:space="preserve">0.325037956237793</t>
   </si>
   <si>
     <t xml:space="preserve">0.31460890173912</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">0.319823414087296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085312843323</t>
+    <t xml:space="preserve">0.318085253238678</t>
   </si>
   <si>
     <t xml:space="preserve">0.316347062587738</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">0.31590336561203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254995822906</t>
+    <t xml:space="preserve">0.305254966020584</t>
   </si>
   <si>
     <t xml:space="preserve">0.30170550942421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804422616959</t>
+    <t xml:space="preserve">0.308804452419281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606506824493</t>
+    <t xml:space="preserve">0.294606477022171</t>
   </si>
   <si>
     <t xml:space="preserve">0.292831808328629</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">0.303480237722397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233953952789</t>
+    <t xml:space="preserve">0.319233924150467</t>
   </si>
   <si>
     <t xml:space="preserve">0.310164839029312</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">0.293840348720551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295654147863388</t>
+    <t xml:space="preserve">0.295654207468033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30472332239151</t>
+    <t xml:space="preserve">0.304723292589188</t>
   </si>
   <si>
     <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290212690830231</t>
+    <t xml:space="preserve">0.290212661027908</t>
   </si>
   <si>
     <t xml:space="preserve">0.288398832082748</t>
@@ -1713,6 +1713,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.428000003099442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433999985456467</t>
   </si>
 </sst>
 </file>
@@ -67623,7 +67626,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.4991435185</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>24000</v>
@@ -67644,6 +67647,32 @@
         <v>562</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.3489699074</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>0.433999985456467</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>0.433999985456467</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>567</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="571">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.179818689823151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979167222977</t>
+    <t xml:space="preserve">0.175979182124138</t>
   </si>
   <si>
     <t xml:space="preserve">0.174699321389198</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">0.167020231485367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17277954518795</t>
+    <t xml:space="preserve">0.172779560089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151662036776543</t>
+    <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902723073959</t>
+    <t xml:space="preserve">0.145902708172798</t>
   </si>
   <si>
     <t xml:space="preserve">0.152493938803673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822514176369</t>
+    <t xml:space="preserve">0.14782252907753</t>
   </si>
   <si>
     <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141519546509</t>
+    <t xml:space="preserve">0.156141474843025</t>
   </si>
   <si>
     <t xml:space="preserve">0.153517827391624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102360010147</t>
+    <t xml:space="preserve">0.149102345108986</t>
   </si>
   <si>
     <t xml:space="preserve">0.142383143305779</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">0.142447158694267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14462286233902</t>
+    <t xml:space="preserve">0.144622892141342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141423270106316</t>
+    <t xml:space="preserve">0.141423240303993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153837785124779</t>
+    <t xml:space="preserve">0.153837770223618</t>
   </si>
   <si>
     <t xml:space="preserve">0.17341947555542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169835865497589</t>
+    <t xml:space="preserve">0.169835910201073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166380301117897</t>
+    <t xml:space="preserve">0.166380286216736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981057047844</t>
+    <t xml:space="preserve">0.159981071949005</t>
   </si>
   <si>
     <t xml:space="preserve">0.157421365380287</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.16382060945034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836832761765</t>
+    <t xml:space="preserve">0.161836847662926</t>
   </si>
   <si>
     <t xml:space="preserve">0.180522620677948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18045862019062</t>
+    <t xml:space="preserve">0.180458649992943</t>
   </si>
   <si>
     <t xml:space="preserve">0.17405940592289</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">0.168939977884293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191977292299271</t>
+    <t xml:space="preserve">0.191977307200432</t>
   </si>
   <si>
     <t xml:space="preserve">0.196136772632599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195176899433136</t>
+    <t xml:space="preserve">0.195176884531975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497824430466</t>
+    <t xml:space="preserve">0.187497809529305</t>
   </si>
   <si>
     <t xml:space="preserve">0.184938117861748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204775720834732</t>
+    <t xml:space="preserve">0.204775750637054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454855442047</t>
+    <t xml:space="preserve">0.212454840540886</t>
   </si>
   <si>
     <t xml:space="preserve">0.204711750149727</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">0.200296267867088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736576199532</t>
+    <t xml:space="preserve">0.19773656129837</t>
   </si>
   <si>
     <t xml:space="preserve">0.18237841129303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578048229218</t>
+    <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907546162605</t>
+    <t xml:space="preserve">0.172907531261444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171499699354172</t>
+    <t xml:space="preserve">0.171499684453011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165740370750427</t>
+    <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
     <t xml:space="preserve">0.154349729418755</t>
@@ -191,52 +191,52 @@
     <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917086362839</t>
+    <t xml:space="preserve">0.159917041659355</t>
   </si>
   <si>
     <t xml:space="preserve">0.15486167371273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781435012817</t>
+    <t xml:space="preserve">0.156781449913979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160492986440659</t>
+    <t xml:space="preserve">0.16049300134182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417585730553</t>
+    <t xml:space="preserve">0.189417570829391</t>
   </si>
   <si>
     <t xml:space="preserve">0.19133734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857879161835</t>
+    <t xml:space="preserve">0.186857894062996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185002073645592</t>
+    <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170219823718071</t>
+    <t xml:space="preserve">0.170219868421555</t>
   </si>
   <si>
     <t xml:space="preserve">0.163180664181709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742275476456</t>
+    <t xml:space="preserve">0.149742290377617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221728444099</t>
+    <t xml:space="preserve">0.154221743345261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151022136211395</t>
+    <t xml:space="preserve">0.151022121310234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147182583808899</t>
+    <t xml:space="preserve">0.147182568907738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161260887980461</t>
+    <t xml:space="preserve">0.161260902881622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168172091245651</t>
+    <t xml:space="preserve">0.16817207634449</t>
   </si>
   <si>
     <t xml:space="preserve">0.173739418387413</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">0.175339236855507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897991061211</t>
+    <t xml:space="preserve">0.185898005962372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204135835170746</t>
+    <t xml:space="preserve">0.204135879874229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096660733223</t>
+    <t xml:space="preserve">0.197096690535545</t>
   </si>
   <si>
     <t xml:space="preserve">0.181354522705078</t>
@@ -260,121 +260,121 @@
     <t xml:space="preserve">0.194216996431351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204647749662399</t>
+    <t xml:space="preserve">0.20464776456356</t>
   </si>
   <si>
     <t xml:space="preserve">0.198376521468163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.195240870118141</t>
+    <t xml:space="preserve">0.195240885019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.203495889902115</t>
+    <t xml:space="preserve">0.203495919704437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21693429350853</t>
+    <t xml:space="preserve">0.216934278607368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709905028343</t>
+    <t xml:space="preserve">0.22070986032486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236771911382675</t>
+    <t xml:space="preserve">0.23677197098732</t>
   </si>
   <si>
     <t xml:space="preserve">0.242531269788742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969673395157</t>
+    <t xml:space="preserve">0.255969703197479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967768669128</t>
+    <t xml:space="preserve">0.271967828273773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286818742752</t>
+    <t xml:space="preserve">0.280286848545074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295645028352737</t>
+    <t xml:space="preserve">0.29564505815506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303964018821716</t>
+    <t xml:space="preserve">0.303963989019394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262368977069855</t>
+    <t xml:space="preserve">0.262368947267532</t>
   </si>
   <si>
     <t xml:space="preserve">0.2648646235466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753798246384</t>
+    <t xml:space="preserve">0.254753828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25468984246254</t>
+    <t xml:space="preserve">0.254689872264862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24720273911953</t>
+    <t xml:space="preserve">0.247202754020691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650668025017</t>
+    <t xml:space="preserve">0.247650697827339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778683900833</t>
+    <t xml:space="preserve">0.247778654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572378754616</t>
+    <t xml:space="preserve">0.233572348952293</t>
   </si>
   <si>
     <t xml:space="preserve">0.238051816821098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214374631643295</t>
+    <t xml:space="preserve">0.214374601840973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663020610809</t>
+    <t xml:space="preserve">0.210663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">0.215654477477074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212518855929375</t>
+    <t xml:space="preserve">0.212518841028214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24189130961895</t>
+    <t xml:space="preserve">0.241891339421272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249570459127426</t>
+    <t xml:space="preserve">0.249570414423943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234980136156082</t>
+    <t xml:space="preserve">0.234980180859566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652542948723</t>
+    <t xml:space="preserve">0.231652572751045</t>
   </si>
   <si>
     <t xml:space="preserve">0.239971563220024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372697114944</t>
+    <t xml:space="preserve">0.23037277162075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227173089981079</t>
+    <t xml:space="preserve">0.22717310488224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773816108704</t>
+    <t xml:space="preserve">0.22077389061451</t>
   </si>
   <si>
     <t xml:space="preserve">0.226405203342438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998308897018</t>
+    <t xml:space="preserve">0.216998338699341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204839766025543</t>
+    <t xml:space="preserve">0.204839736223221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20797535777092</t>
+    <t xml:space="preserve">0.207975372672081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535064339638</t>
+    <t xml:space="preserve">0.210535034537315</t>
   </si>
   <si>
     <t xml:space="preserve">0.209895148873329</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">0.212582841515541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782463550568</t>
+    <t xml:space="preserve">0.215782433748245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229732781648636</t>
+    <t xml:space="preserve">0.229732811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845481872559</t>
+    <t xml:space="preserve">0.223845466971397</t>
   </si>
   <si>
     <t xml:space="preserve">0.224805399775505</t>
@@ -401,28 +401,28 @@
     <t xml:space="preserve">0.233636349439621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627746701241</t>
+    <t xml:space="preserve">0.238627761602402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580951690674</t>
+    <t xml:space="preserve">0.228580921888351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973512649536</t>
+    <t xml:space="preserve">0.223973482847214</t>
   </si>
   <si>
     <t xml:space="preserve">0.223717525601387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837831497192</t>
+    <t xml:space="preserve">0.220837846398354</t>
   </si>
   <si>
     <t xml:space="preserve">0.235492125153542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220965802669525</t>
+    <t xml:space="preserve">0.220965847373009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227365091443062</t>
+    <t xml:space="preserve">0.227365076541901</t>
   </si>
   <si>
     <t xml:space="preserve">0.302556186914444</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">0.358357548713684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47354382276535</t>
+    <t xml:space="preserve">0.47354394197464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454134941101</t>
+    <t xml:space="preserve">0.555454194545746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485702484846115</t>
+    <t xml:space="preserve">0.485702574253082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444747298955917</t>
+    <t xml:space="preserve">0.44474732875824</t>
   </si>
   <si>
     <t xml:space="preserve">0.429709136486053</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">0.403152227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371156096458435</t>
+    <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710073947906</t>
+    <t xml:space="preserve">0.421710014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035716056824</t>
+    <t xml:space="preserve">0.374035745859146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380754977464676</t>
+    <t xml:space="preserve">0.380754947662354</t>
   </si>
   <si>
     <t xml:space="preserve">0.352598249912262</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">0.331800669431686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602029561996</t>
+    <t xml:space="preserve">0.320602059364319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33244064450264</t>
+    <t xml:space="preserve">0.332440674304962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340439647436142</t>
+    <t xml:space="preserve">0.340439736843109</t>
   </si>
   <si>
     <t xml:space="preserve">0.327641218900681</t>
@@ -485,43 +485,43 @@
     <t xml:space="preserve">0.347478836774826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332760602235794</t>
+    <t xml:space="preserve">0.332760572433472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324121624231339</t>
+    <t xml:space="preserve">0.324121594429016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327001214027405</t>
+    <t xml:space="preserve">0.327001243829727</t>
   </si>
   <si>
     <t xml:space="preserve">0.339159816503525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960239171982</t>
+    <t xml:space="preserve">0.335960209369659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323161721229553</t>
+    <t xml:space="preserve">0.323161751031876</t>
   </si>
   <si>
     <t xml:space="preserve">0.330200880765915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319962114095688</t>
+    <t xml:space="preserve">0.31996214389801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759724378586</t>
+    <t xml:space="preserve">0.340759664773941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323801636695862</t>
+    <t xml:space="preserve">0.323801666498184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322521775960922</t>
+    <t xml:space="preserve">0.322521805763245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334360390901566</t>
+    <t xml:space="preserve">0.334360331296921</t>
   </si>
   <si>
     <t xml:space="preserve">0.328921049833298</t>
@@ -530,37 +530,37 @@
     <t xml:space="preserve">0.334040462970734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163655757904</t>
+    <t xml:space="preserve">0.307163625955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122591495514</t>
+    <t xml:space="preserve">0.316122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698461771011</t>
+    <t xml:space="preserve">0.316698521375656</t>
   </si>
   <si>
     <t xml:space="preserve">0.326361328363419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331480741500854</t>
+    <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
     <t xml:space="preserve">0.36475682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3455590903759</t>
+    <t xml:space="preserve">0.345559120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346198976039886</t>
+    <t xml:space="preserve">0.346199035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081467628479</t>
+    <t xml:space="preserve">0.325081557035446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959271907806</t>
+    <t xml:space="preserve">0.343959301710129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282131433487</t>
+    <t xml:space="preserve">0.320282071828842</t>
   </si>
   <si>
     <t xml:space="preserve">0.333720505237579</t>
@@ -569,175 +569,175 @@
     <t xml:space="preserve">0.396753042936325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275449991226</t>
+    <t xml:space="preserve">0.376275479793549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37563556432724</t>
+    <t xml:space="preserve">0.375635504722595</t>
   </si>
   <si>
     <t xml:space="preserve">0.376915365457535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196104049683</t>
+    <t xml:space="preserve">0.370196133852005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555310726166</t>
+    <t xml:space="preserve">0.377555280923843</t>
   </si>
   <si>
     <t xml:space="preserve">0.351318448781967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356117814779282</t>
+    <t xml:space="preserve">0.356117874383926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360917240381241</t>
+    <t xml:space="preserve">0.360917299985886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715758323669</t>
+    <t xml:space="preserve">0.373715788125992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39579313993454</t>
+    <t xml:space="preserve">0.395793110132217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398672848939896</t>
+    <t xml:space="preserve">0.398672819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384594559669495</t>
+    <t xml:space="preserve">0.384594470262527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383954584598541</t>
+    <t xml:space="preserve">0.383954614400864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193321466446</t>
+    <t xml:space="preserve">0.394193381071091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384274423122406</t>
+    <t xml:space="preserve">0.384274542331696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310800075531</t>
+    <t xml:space="preserve">0.415310859680176</t>
   </si>
   <si>
     <t xml:space="preserve">0.422350019216537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399312704801559</t>
+    <t xml:space="preserve">0.399312764406204</t>
   </si>
   <si>
     <t xml:space="preserve">0.38363453745842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553346395493</t>
+    <t xml:space="preserve">0.393553406000137</t>
   </si>
   <si>
     <t xml:space="preserve">0.479943126440048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447307020425797</t>
+    <t xml:space="preserve">0.447307050228119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745394229889</t>
+    <t xml:space="preserve">0.460745543241501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547632217407</t>
+    <t xml:space="preserve">0.441547781229019</t>
   </si>
   <si>
     <t xml:space="preserve">0.446027219295502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454346179962158</t>
+    <t xml:space="preserve">0.454346209764481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447947025299072</t>
+    <t xml:space="preserve">0.447946965694427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430029094219208</t>
+    <t xml:space="preserve">0.43002912402153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588785886765</t>
+    <t xml:space="preserve">0.43258872628212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428749263286591</t>
+    <t xml:space="preserve">0.428749203681946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417230546474457</t>
+    <t xml:space="preserve">0.417230695486069</t>
   </si>
   <si>
     <t xml:space="preserve">0.413391053676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41595071554184</t>
+    <t xml:space="preserve">0.415950745344162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070128679276</t>
+    <t xml:space="preserve">0.421070069074631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409551441669464</t>
+    <t xml:space="preserve">0.409551501274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267860889435</t>
+    <t xml:space="preserve">0.440267831087112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909710884094</t>
+    <t xml:space="preserve">0.424909681081772</t>
   </si>
   <si>
     <t xml:space="preserve">0.470984250307083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148477554321</t>
+    <t xml:space="preserve">0.435148447751999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40699177980423</t>
+    <t xml:space="preserve">0.406991839408875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189541816711</t>
+    <t xml:space="preserve">0.426189571619034</t>
   </si>
   <si>
     <t xml:space="preserve">0.431308954954147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510407209396</t>
+    <t xml:space="preserve">0.418510437011719</t>
   </si>
   <si>
     <t xml:space="preserve">0.405711948871613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111192941666</t>
+    <t xml:space="preserve">0.412111222743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38907390832901</t>
+    <t xml:space="preserve">0.389073967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390353798866272</t>
+    <t xml:space="preserve">0.39035376906395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473152399063</t>
+    <t xml:space="preserve">0.395473122596741</t>
   </si>
   <si>
     <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438987970352173</t>
+    <t xml:space="preserve">0.438988089561462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469402551651</t>
+    <t xml:space="preserve">0.427469491958618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670914411545</t>
+    <t xml:space="preserve">0.414670884609222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872366666794</t>
+    <t xml:space="preserve">0.401872396469116</t>
   </si>
   <si>
     <t xml:space="preserve">0.419790297746658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408271670341492</t>
+    <t xml:space="preserve">0.408271759748459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423629850149155</t>
+    <t xml:space="preserve">0.42362979054451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596345186234</t>
+    <t xml:space="preserve">0.368596315383911</t>
   </si>
   <si>
     <t xml:space="preserve">0.372435927391052</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363477021455765</t>
+    <t xml:space="preserve">0.36347696185112</t>
   </si>
   <si>
     <t xml:space="preserve">0.350678473711014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342999398708344</t>
+    <t xml:space="preserve">0.342999368906021</t>
   </si>
   <si>
     <t xml:space="preserve">0.344279229640961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958334445953</t>
+    <t xml:space="preserve">0.351958364248276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835171461105</t>
+    <t xml:space="preserve">0.378835141658783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913490533829</t>
+    <t xml:space="preserve">0.392913430929184</t>
   </si>
   <si>
     <t xml:space="preserve">0.359637379646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316544055939</t>
+    <t xml:space="preserve">0.367316514253616</t>
   </si>
   <si>
     <t xml:space="preserve">0.385234445333481</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">0.382674694061279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3801149725914</t>
+    <t xml:space="preserve">0.380115002393723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633659601212</t>
+    <t xml:space="preserve">0.391633570194244</t>
   </si>
   <si>
     <t xml:space="preserve">0.398032873868942</t>
@@ -800,61 +800,58 @@
     <t xml:space="preserve">0.400592535734177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431948900222778</t>
+    <t xml:space="preserve">0.431948810815811</t>
   </si>
   <si>
     <t xml:space="preserve">0.438348084688187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545816898346</t>
+    <t xml:space="preserve">0.457545906305313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945120573044</t>
+    <t xml:space="preserve">0.463945060968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472350925207138</t>
+    <t xml:space="preserve">0.472350895404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200753450394</t>
+    <t xml:space="preserve">0.451200813055038</t>
   </si>
   <si>
     <t xml:space="preserve">0.437100827693939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423000812530518</t>
+    <t xml:space="preserve">0.423000782728195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433575749397278</t>
+    <t xml:space="preserve">0.433575809001923</t>
   </si>
   <si>
     <t xml:space="preserve">0.444150775671005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675794363022</t>
+    <t xml:space="preserve">0.447675853967667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625756978989</t>
+    <t xml:space="preserve">0.440625846385956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525771617889</t>
+    <t xml:space="preserve">0.426525741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
+    <t xml:space="preserve">0.408900678157806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408900737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419475823640823</t>
+    <t xml:space="preserve">0.419475764036179</t>
   </si>
   <si>
     <t xml:space="preserve">0.394800692796707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325741291046</t>
+    <t xml:space="preserve">0.398325771093369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425756454468</t>
+    <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
     <t xml:space="preserve">0.430050760507584</t>
@@ -866,28 +863,28 @@
     <t xml:space="preserve">0.535800933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250790834427</t>
+    <t xml:space="preserve">0.458250820636749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46530082821846</t>
+    <t xml:space="preserve">0.465300887823105</t>
   </si>
   <si>
     <t xml:space="preserve">0.461775809526443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375719070435</t>
+    <t xml:space="preserve">0.405375689268112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850759983063</t>
+    <t xml:space="preserve">0.40185073018074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750685214996</t>
+    <t xml:space="preserve">0.387750715017319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380700707435608</t>
+    <t xml:space="preserve">0.38070073723793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366600662469864</t>
+    <t xml:space="preserve">0.366600632667542</t>
   </si>
   <si>
     <t xml:space="preserve">0.377175688743591</t>
@@ -896,25 +893,25 @@
     <t xml:space="preserve">0.391275733709335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650640249252</t>
+    <t xml:space="preserve">0.37365061044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.346860647201538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345450609922409</t>
+    <t xml:space="preserve">0.345450669527054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550595283508</t>
+    <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352500647306442</t>
+    <t xml:space="preserve">0.35250061750412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400602340698</t>
+    <t xml:space="preserve">0.338400572538376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317250549793243</t>
+    <t xml:space="preserve">0.317250579595566</t>
   </si>
   <si>
     <t xml:space="preserve">0.320070564746857</t>
@@ -923,7 +920,7 @@
     <t xml:space="preserve">0.296100527048111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263670444488525</t>
+    <t xml:space="preserve">0.263670474290848</t>
   </si>
   <si>
     <t xml:space="preserve">0.283410519361496</t>
@@ -932,46 +929,49 @@
     <t xml:space="preserve">0.267900466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770489454269</t>
+    <t xml:space="preserve">0.277770519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266490489244461</t>
+    <t xml:space="preserve">0.266490429639816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253800451755524</t>
+    <t xml:space="preserve">0.249570444226265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253800511360168</t>
   </si>
   <si>
     <t xml:space="preserve">0.248160436749458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290460556745529</t>
+    <t xml:space="preserve">0.290460497140884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291870504617691</t>
+    <t xml:space="preserve">0.291870564222336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276360511779785</t>
+    <t xml:space="preserve">0.27636045217514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820556640625</t>
+    <t xml:space="preserve">0.28482049703598</t>
   </si>
   <si>
     <t xml:space="preserve">0.286230504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300330519676208</t>
+    <t xml:space="preserve">0.300330549478531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308790564537048</t>
+    <t xml:space="preserve">0.308790534734726</t>
   </si>
   <si>
     <t xml:space="preserve">0.314430594444275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040632247925</t>
+    <t xml:space="preserve">0.344040602445602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33135062456131</t>
+    <t xml:space="preserve">0.331350594758987</t>
   </si>
   <si>
     <t xml:space="preserve">0.325710624456406</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">0.349680632352829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370125651359558</t>
+    <t xml:space="preserve">0.37012568116188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38422566652298</t>
+    <t xml:space="preserve">0.384225726127625</t>
   </si>
   <si>
     <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336990624666214</t>
+    <t xml:space="preserve">0.336990565061569</t>
   </si>
   <si>
     <t xml:space="preserve">0.342630594968796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025606393814</t>
+    <t xml:space="preserve">0.356025665998459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090669631958</t>
+    <t xml:space="preserve">0.351090639829636</t>
   </si>
   <si>
     <t xml:space="preserve">0.328530609607697</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">0.327120572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324300616979599</t>
+    <t xml:space="preserve">0.324300587177277</t>
   </si>
   <si>
     <t xml:space="preserve">0.311610549688339</t>
@@ -1022,112 +1022,112 @@
     <t xml:space="preserve">0.310200572013855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150594234467</t>
+    <t xml:space="preserve">0.303150564432144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2890505194664</t>
+    <t xml:space="preserve">0.289050489664078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29328054189682</t>
+    <t xml:space="preserve">0.293280571699142</t>
   </si>
   <si>
     <t xml:space="preserve">0.269310504198074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130519151688</t>
+    <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265080451965332</t>
+    <t xml:space="preserve">0.265080481767654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270720511674881</t>
+    <t xml:space="preserve">0.270720481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950504302979</t>
+    <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
     <t xml:space="preserve">0.282000511884689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297510504722595</t>
+    <t xml:space="preserve">0.297510534524918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301740527153015</t>
+    <t xml:space="preserve">0.30174058675766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690549373627</t>
+    <t xml:space="preserve">0.294690489768982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437587022781372</t>
+    <t xml:space="preserve">0.43758699297905</t>
   </si>
   <si>
     <t xml:space="preserve">0.406879067420959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395363628864288</t>
+    <t xml:space="preserve">0.395363688468933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383848249912262</t>
+    <t xml:space="preserve">0.38384822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3684943318367</t>
+    <t xml:space="preserve">0.368494272232056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171290874481</t>
+    <t xml:space="preserve">0.376171320676804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370029658079147</t>
+    <t xml:space="preserve">0.370029717683792</t>
   </si>
   <si>
     <t xml:space="preserve">0.387686729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777448415756</t>
+    <t xml:space="preserve">0.380777418613434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371565073728561</t>
+    <t xml:space="preserve">0.371565103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211096048355</t>
+    <t xml:space="preserve">0.356211155653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350069612264633</t>
+    <t xml:space="preserve">0.350069582462311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348534166812897</t>
+    <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463424921036</t>
+    <t xml:space="preserve">0.345463395118713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281957149506</t>
+    <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140383958817</t>
+    <t xml:space="preserve">0.353140354156494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746541500092</t>
+    <t xml:space="preserve">0.357746601104736</t>
   </si>
   <si>
     <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857237577438</t>
+    <t xml:space="preserve">0.340857207775116</t>
   </si>
   <si>
     <t xml:space="preserve">0.354675769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263981819153</t>
+    <t xml:space="preserve">0.445263892412186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418394535779953</t>
+    <t xml:space="preserve">0.418394595384598</t>
   </si>
   <si>
     <t xml:space="preserve">0.460617899894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452940821647644</t>
+    <t xml:space="preserve">0.452940911054611</t>
   </si>
   <si>
     <t xml:space="preserve">0.449102431535721</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">0.410717636346817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399202197790146</t>
+    <t xml:space="preserve">0.399202138185501</t>
   </si>
   <si>
     <t xml:space="preserve">0.391525208950043</t>
@@ -1151,31 +1151,31 @@
     <t xml:space="preserve">0.41455614566803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379242032766342</t>
+    <t xml:space="preserve">0.379242062568665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373100489377975</t>
+    <t xml:space="preserve">0.373100459575653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36081737279892</t>
+    <t xml:space="preserve">0.360817342996597</t>
   </si>
   <si>
     <t xml:space="preserve">0.351604968309402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346998810768127</t>
+    <t xml:space="preserve">0.346998780965805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37770664691925</t>
+    <t xml:space="preserve">0.377706676721573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958916187286</t>
+    <t xml:space="preserve">0.366958886384964</t>
   </si>
   <si>
     <t xml:space="preserve">0.374635875225067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365423560142517</t>
+    <t xml:space="preserve">0.365423530340195</t>
   </si>
   <si>
     <t xml:space="preserve">0.322432518005371</t>
@@ -1187,52 +1187,52 @@
     <t xml:space="preserve">0.30707859992981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32396787405014</t>
+    <t xml:space="preserve">0.323967903852463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503259897232</t>
+    <t xml:space="preserve">0.325503289699554</t>
   </si>
   <si>
     <t xml:space="preserve">0.330109506845474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333180278539658</t>
+    <t xml:space="preserve">0.333180248737335</t>
   </si>
   <si>
     <t xml:space="preserve">0.336251050233841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337786436080933</t>
+    <t xml:space="preserve">0.337786465883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928068876266</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334715664386749</t>
+    <t xml:space="preserve">0.334715634584427</t>
   </si>
   <si>
     <t xml:space="preserve">0.314755529165268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313220143318176</t>
+    <t xml:space="preserve">0.313220173120499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308614045381546</t>
+    <t xml:space="preserve">0.308614015579224</t>
   </si>
   <si>
     <t xml:space="preserve">0.31936177611351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32857409119606</t>
+    <t xml:space="preserve">0.328574120998383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345869779587</t>
+    <t xml:space="preserve">0.323345810174942</t>
   </si>
   <si>
     <t xml:space="preserve">0.328171908855438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128530263901</t>
+    <t xml:space="preserve">0.320128500461578</t>
   </si>
   <si>
     <t xml:space="preserve">0.324954569339752</t>
@@ -1241,10 +1241,10 @@
     <t xml:space="preserve">0.337824016809464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432716369629</t>
+    <t xml:space="preserve">0.339432686567307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32656317949295</t>
+    <t xml:space="preserve">0.326563239097595</t>
   </si>
   <si>
     <t xml:space="preserve">0.329780578613281</t>
@@ -1259,88 +1259,88 @@
     <t xml:space="preserve">0.297606915235519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307259023189545</t>
+    <t xml:space="preserve">0.3072589635849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737229824066</t>
+    <t xml:space="preserve">0.321737170219421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650353431702</t>
+    <t xml:space="preserve">0.305650293827057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304041564464569</t>
+    <t xml:space="preserve">0.304041594266891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295998215675354</t>
+    <t xml:space="preserve">0.295998185873032</t>
   </si>
   <si>
     <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780816555023</t>
+    <t xml:space="preserve">0.292780846357346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737378358841</t>
+    <t xml:space="preserve">0.284737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28151997923851</t>
+    <t xml:space="preserve">0.281520009040833</t>
   </si>
   <si>
     <t xml:space="preserve">0.283128708600998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275085270404816</t>
+    <t xml:space="preserve">0.275085300207138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286346077919006</t>
+    <t xml:space="preserve">0.286346107721329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276693999767303</t>
+    <t xml:space="preserve">0.276693969964981</t>
   </si>
   <si>
     <t xml:space="preserve">0.289563447237015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172087192535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824254751205</t>
+    <t xml:space="preserve">0.300824224948883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432894706726</t>
+    <t xml:space="preserve">0.302432984113693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313693702220917</t>
+    <t xml:space="preserve">0.313693732023239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294389545917511</t>
+    <t xml:space="preserve">0.294389456510544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302193641663</t>
+    <t xml:space="preserve">0.352302223443985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258785247803</t>
+    <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
     <t xml:space="preserve">0.345867484807968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347476124763489</t>
+    <t xml:space="preserve">0.347476154565811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341041386127472</t>
+    <t xml:space="preserve">0.341041445732117</t>
   </si>
   <si>
     <t xml:space="preserve">0.342650085687637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358736932277679</t>
+    <t xml:space="preserve">0.358736962080002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300703495740891</t>
+    <t xml:space="preserve">0.300703525543213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297227203845978</t>
+    <t xml:space="preserve">0.2972272336483</t>
   </si>
   <si>
     <t xml:space="preserve">0.295489013195038</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">0.290274500846863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29201266169548</t>
+    <t xml:space="preserve">0.292012691497803</t>
   </si>
   <si>
     <t xml:space="preserve">0.30591806769371</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">0.288536339998245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28332182765007</t>
+    <t xml:space="preserve">0.283321857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293750882148743</t>
+    <t xml:space="preserve">0.293750911951065</t>
   </si>
   <si>
     <t xml:space="preserve">0.285059988498688</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274631023406982</t>
+    <t xml:space="preserve">0.27463099360466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286798179149628</t>
+    <t xml:space="preserve">0.286798238754272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279845476150513</t>
+    <t xml:space="preserve">0.279845535755157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276369124650955</t>
+    <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
     <t xml:space="preserve">0.272892773151398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394389390945</t>
+    <t xml:space="preserve">0.30939444899559</t>
   </si>
   <si>
     <t xml:space="preserve">0.298965394496918</t>
@@ -1400,67 +1400,67 @@
     <t xml:space="preserve">0.307656198740005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311132550239563</t>
+    <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
     <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33025249838829</t>
+    <t xml:space="preserve">0.330252438783646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037956237793</t>
+    <t xml:space="preserve">0.325037896633148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314608931541443</t>
+    <t xml:space="preserve">0.314608871936798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319823443889618</t>
+    <t xml:space="preserve">0.319823414087296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085283041</t>
+    <t xml:space="preserve">0.318085193634033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31634709239006</t>
+    <t xml:space="preserve">0.316347122192383</t>
   </si>
   <si>
     <t xml:space="preserve">0.315903395414352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305254936218262</t>
+    <t xml:space="preserve">0.305254966020584</t>
   </si>
   <si>
     <t xml:space="preserve">0.30170550942421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804452419281</t>
+    <t xml:space="preserve">0.308804422616959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294606536626816</t>
+    <t xml:space="preserve">0.294606506824493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292831808328629</t>
+    <t xml:space="preserve">0.292831778526306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480237722397</t>
+    <t xml:space="preserve">0.303480267524719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319233953952789</t>
+    <t xml:space="preserve">0.319233983755112</t>
   </si>
   <si>
     <t xml:space="preserve">0.31016480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30835098028183</t>
+    <t xml:space="preserve">0.308350950479507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31197863817215</t>
+    <t xml:space="preserve">0.311978667974472</t>
   </si>
   <si>
     <t xml:space="preserve">0.30653715133667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026519775391</t>
+    <t xml:space="preserve">0.292026489973068</t>
   </si>
   <si>
     <t xml:space="preserve">0.293840348720551</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">0.30472332239151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299281865358353</t>
+    <t xml:space="preserve">0.299281805753708</t>
   </si>
   <si>
     <t xml:space="preserve">0.290212690830231</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">0.288398861885071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771174192429</t>
+    <t xml:space="preserve">0.284771203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585062742233</t>
+    <t xml:space="preserve">0.286585032939911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29746800661087</t>
+    <t xml:space="preserve">0.297468036413193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300716489553452</t>
+    <t xml:space="preserve">0.300716459751129</t>
   </si>
   <si>
     <t xml:space="preserve">0.295147657394409</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">0.326704323291779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330416887998581</t>
+    <t xml:space="preserve">0.330416858196259</t>
   </si>
   <si>
     <t xml:space="preserve">0.330023497343063</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">0.328126817941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337610244750977</t>
+    <t xml:space="preserve">0.337610274553299</t>
   </si>
   <si>
     <t xml:space="preserve">0.331920206546783</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">0.32623016834259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316746711730957</t>
+    <t xml:space="preserve">0.316746741533279</t>
   </si>
   <si>
     <t xml:space="preserve">0.314850002527237</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">0.32243674993515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324333488941193</t>
+    <t xml:space="preserve">0.32433345913887</t>
   </si>
   <si>
     <t xml:space="preserve">0.347093731164932</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">0.312953352928162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307263255119324</t>
+    <t xml:space="preserve">0.307263284921646</t>
   </si>
   <si>
     <t xml:space="preserve">0.360370516777039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350887089967728</t>
+    <t xml:space="preserve">0.350887060165405</t>
   </si>
   <si>
     <t xml:space="preserve">0.343300312757492</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">0.354680478572845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377440720796585</t>
+    <t xml:space="preserve">0.377440690994263</t>
   </si>
   <si>
     <t xml:space="preserve">0.405891001224518</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">0.417271107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407787710428238</t>
+    <t xml:space="preserve">0.407787680625916</t>
   </si>
   <si>
     <t xml:space="preserve">0.398304253816605</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">0.396407574415207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38123407959938</t>
+    <t xml:space="preserve">0.381234049797058</t>
   </si>
   <si>
     <t xml:space="preserve">0.383130788803101</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">0.369853943586349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373647302389145</t>
+    <t xml:space="preserve">0.373647332191467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375544011592865</t>
+    <t xml:space="preserve">0.375544041395187</t>
   </si>
   <si>
     <t xml:space="preserve">0.385027438402176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4020976126194</t>
+    <t xml:space="preserve">0.402097642421722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415026545524597</t>
+    <t xml:space="preserve">0.415026515722275</t>
   </si>
   <si>
     <t xml:space="preserve">0.399583697319031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401514023542404</t>
+    <t xml:space="preserve">0.401514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">0.413096159696579</t>
@@ -1722,6 +1722,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.435999989509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437999993562698</t>
   </si>
 </sst>
 </file>
@@ -26128,7 +26131,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26154,7 +26157,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26180,7 +26183,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26206,7 +26209,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26232,7 +26235,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26258,7 +26261,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26284,7 +26287,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26310,7 +26313,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26336,7 +26339,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26362,7 +26365,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26388,7 +26391,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26414,7 +26417,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26440,7 +26443,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26466,7 +26469,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26492,7 +26495,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26518,7 +26521,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26570,7 +26573,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26596,7 +26599,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26622,7 +26625,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26648,7 +26651,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26674,7 +26677,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26700,7 +26703,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26726,7 +26729,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26752,7 +26755,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26778,7 +26781,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26804,7 +26807,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26830,7 +26833,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26856,7 +26859,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26882,7 +26885,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26908,7 +26911,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26934,7 +26937,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26960,7 +26963,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26986,7 +26989,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27012,7 +27015,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27038,7 +27041,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27116,7 +27119,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27194,7 +27197,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27220,7 +27223,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27272,7 +27275,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27298,7 +27301,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27324,7 +27327,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27350,7 +27353,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27506,7 +27509,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27532,7 +27535,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27558,7 +27561,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27636,7 +27639,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27662,7 +27665,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28078,7 +28081,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28104,7 +28107,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28130,7 +28133,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28156,7 +28159,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28182,7 +28185,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28208,7 +28211,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28234,7 +28237,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28260,7 +28263,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28286,7 +28289,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28338,7 +28341,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28364,7 +28367,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28390,7 +28393,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28416,7 +28419,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28442,7 +28445,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28468,7 +28471,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28494,7 +28497,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28520,7 +28523,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28546,7 +28549,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28572,7 +28575,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28598,7 +28601,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28676,7 +28679,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28702,7 +28705,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28728,7 +28731,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28754,7 +28757,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28780,7 +28783,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28806,7 +28809,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28832,7 +28835,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28858,7 +28861,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28884,7 +28887,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28910,7 +28913,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28936,7 +28939,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28962,7 +28965,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28988,7 +28991,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29014,7 +29017,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29040,7 +29043,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29066,7 +29069,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29092,7 +29095,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29118,7 +29121,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29144,7 +29147,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29170,7 +29173,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29196,7 +29199,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29300,7 +29303,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29352,7 +29355,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29430,7 +29433,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29456,7 +29459,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29482,7 +29485,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29508,7 +29511,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29534,7 +29537,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29560,7 +29563,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29586,7 +29589,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29612,7 +29615,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29638,7 +29641,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29664,7 +29667,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29690,7 +29693,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29716,7 +29719,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29742,7 +29745,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29768,7 +29771,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29794,7 +29797,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29820,7 +29823,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29846,7 +29849,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29872,7 +29875,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29898,7 +29901,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30080,7 +30083,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30210,7 +30213,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30236,7 +30239,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30262,7 +30265,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30314,7 +30317,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30340,7 +30343,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30418,7 +30421,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30808,7 +30811,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30834,7 +30837,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30938,7 +30941,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30990,7 +30993,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31016,7 +31019,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31042,7 +31045,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31146,7 +31149,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31172,7 +31175,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31198,7 +31201,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31250,7 +31253,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31276,7 +31279,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31302,7 +31305,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31328,7 +31331,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31354,7 +31357,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31380,7 +31383,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31406,7 +31409,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31432,7 +31435,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31458,7 +31461,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31484,7 +31487,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31510,7 +31513,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31536,7 +31539,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31562,7 +31565,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31588,7 +31591,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31614,7 +31617,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31640,7 +31643,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31666,7 +31669,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31692,7 +31695,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31718,7 +31721,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31744,7 +31747,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31770,7 +31773,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31796,7 +31799,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31822,7 +31825,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31848,7 +31851,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31874,7 +31877,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31900,7 +31903,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31926,7 +31929,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31978,7 +31981,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32004,7 +32007,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32030,7 +32033,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32082,7 +32085,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32264,7 +32267,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32290,7 +32293,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32316,7 +32319,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32342,7 +32345,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32680,7 +32683,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33174,7 +33177,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34214,7 +34217,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34422,7 +34425,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34448,7 +34451,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34942,7 +34945,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35592,7 +35595,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35618,7 +35621,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35670,7 +35673,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35696,7 +35699,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35722,7 +35725,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35748,7 +35751,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35800,7 +35803,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35826,7 +35829,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35852,7 +35855,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35904,7 +35907,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35930,7 +35933,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35956,7 +35959,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35982,7 +35985,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36008,7 +36011,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36034,7 +36037,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36060,7 +36063,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36086,7 +36089,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36112,7 +36115,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -67710,7 +67713,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.684837963</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>8000</v>
@@ -67731,6 +67734,32 @@
         <v>569</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6853009259</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>0.433999985456467</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>0.433999985456467</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>570</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179818719625473</t>
+    <t xml:space="preserve">0.179818689823151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175979152321815</t>
+    <t xml:space="preserve">0.175979182124138</t>
   </si>
   <si>
     <t xml:space="preserve">0.174699306488037</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">0.167020231485367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172779560089111</t>
+    <t xml:space="preserve">0.17277954518795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151662036776543</t>
+    <t xml:space="preserve">0.151662051677704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145902737975121</t>
+    <t xml:space="preserve">0.145902723073959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152493953704834</t>
+    <t xml:space="preserve">0.152493938803673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147822514176369</t>
+    <t xml:space="preserve">0.147822499275208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155501574277878</t>
+    <t xml:space="preserve">0.155501589179039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156141504645348</t>
+    <t xml:space="preserve">0.156141519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153517827391624</t>
+    <t xml:space="preserve">0.153517842292786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149102345108986</t>
+    <t xml:space="preserve">0.149102315306664</t>
   </si>
   <si>
     <t xml:space="preserve">0.142383143305779</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">0.142447128891945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144622877240181</t>
+    <t xml:space="preserve">0.14462286233902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141423270106316</t>
+    <t xml:space="preserve">0.141423240303993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153837785124779</t>
+    <t xml:space="preserve">0.15383780002594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173419430851936</t>
+    <t xml:space="preserve">0.173419460654259</t>
   </si>
   <si>
     <t xml:space="preserve">0.16983588039875</t>
@@ -110,46 +110,46 @@
     <t xml:space="preserve">0.166380301117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159981071949005</t>
+    <t xml:space="preserve">0.159981057047844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157421365380287</t>
+    <t xml:space="preserve">0.157421350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152301952242851</t>
+    <t xml:space="preserve">0.152301967144012</t>
   </si>
   <si>
     <t xml:space="preserve">0.158509239554405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163820624351501</t>
+    <t xml:space="preserve">0.163820594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161836847662926</t>
+    <t xml:space="preserve">0.161836862564087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180522635579109</t>
+    <t xml:space="preserve">0.180522620677948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180458679795265</t>
+    <t xml:space="preserve">0.180458635091782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174059435725212</t>
+    <t xml:space="preserve">0.174059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168940007686615</t>
+    <t xml:space="preserve">0.168939977884293</t>
   </si>
   <si>
     <t xml:space="preserve">0.191977292299271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196136772632599</t>
+    <t xml:space="preserve">0.19613678753376</t>
   </si>
   <si>
     <t xml:space="preserve">0.195176899433136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187497809529305</t>
+    <t xml:space="preserve">0.187497824430466</t>
   </si>
   <si>
     <t xml:space="preserve">0.184938102960587</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">0.204775750637054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212454840540886</t>
+    <t xml:space="preserve">0.212454825639725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204711779952049</t>
+    <t xml:space="preserve">0.204711750149727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20029628276825</t>
+    <t xml:space="preserve">0.200296267867088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197736591100693</t>
+    <t xml:space="preserve">0.197736606001854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18237841129303</t>
+    <t xml:space="preserve">0.182378381490707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185578003525734</t>
+    <t xml:space="preserve">0.185578018426895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172907516360283</t>
+    <t xml:space="preserve">0.172907546162605</t>
   </si>
   <si>
     <t xml:space="preserve">0.171499684453011</t>
@@ -185,46 +185,46 @@
     <t xml:space="preserve">0.165740385651588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154349729418755</t>
+    <t xml:space="preserve">0.154349714517593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169579923152924</t>
+    <t xml:space="preserve">0.169579908251762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159917056560516</t>
+    <t xml:space="preserve">0.159917086362839</t>
   </si>
   <si>
     <t xml:space="preserve">0.154861643910408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156781435012817</t>
+    <t xml:space="preserve">0.156781449913979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16049300134182</t>
+    <t xml:space="preserve">0.160493016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.189417585730553</t>
+    <t xml:space="preserve">0.18941755592823</t>
   </si>
   <si>
     <t xml:space="preserve">0.19133734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186857864260674</t>
+    <t xml:space="preserve">0.186857879161835</t>
   </si>
   <si>
     <t xml:space="preserve">0.185002088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170219883322716</t>
+    <t xml:space="preserve">0.170219838619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163180664181709</t>
+    <t xml:space="preserve">0.16318067908287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149742260575294</t>
+    <t xml:space="preserve">0.149742275476456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154221743345261</t>
+    <t xml:space="preserve">0.154221728444099</t>
   </si>
   <si>
     <t xml:space="preserve">0.151022121310234</t>
@@ -242,28 +242,28 @@
     <t xml:space="preserve">0.173739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175339221954346</t>
+    <t xml:space="preserve">0.175339251756668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185897976160049</t>
+    <t xml:space="preserve">0.185897961258888</t>
   </si>
   <si>
     <t xml:space="preserve">0.204135820269585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197096675634384</t>
+    <t xml:space="preserve">0.197096630930901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181354537606239</t>
+    <t xml:space="preserve">0.181354522705078</t>
   </si>
   <si>
     <t xml:space="preserve">0.194217011332512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204647779464722</t>
+    <t xml:space="preserve">0.204647749662399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.198376536369324</t>
+    <t xml:space="preserve">0.198376521468163</t>
   </si>
   <si>
     <t xml:space="preserve">0.195240870118141</t>
@@ -272,28 +272,28 @@
     <t xml:space="preserve">0.203495904803276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216934278607368</t>
+    <t xml:space="preserve">0.216934323310852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220709875226021</t>
+    <t xml:space="preserve">0.220709845423698</t>
   </si>
   <si>
     <t xml:space="preserve">0.236771985888481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242531314492226</t>
+    <t xml:space="preserve">0.242531299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255969703197479</t>
+    <t xml:space="preserve">0.255969673395157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271967828273773</t>
+    <t xml:space="preserve">0.271967798471451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280286848545074</t>
+    <t xml:space="preserve">0.280286818742752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295645028352737</t>
+    <t xml:space="preserve">0.295644998550415</t>
   </si>
   <si>
     <t xml:space="preserve">0.303963989019394</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">0.26236891746521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264864653348923</t>
+    <t xml:space="preserve">0.2648646235466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254753828048706</t>
+    <t xml:space="preserve">0.254753857851028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254689872264862</t>
+    <t xml:space="preserve">0.25468984246254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247202679514885</t>
+    <t xml:space="preserve">0.247202709317207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247650682926178</t>
+    <t xml:space="preserve">0.2476507127285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.247778698801994</t>
+    <t xml:space="preserve">0.247778654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233572348952293</t>
+    <t xml:space="preserve">0.233572393655777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238051846623421</t>
+    <t xml:space="preserve">0.23805183172226</t>
   </si>
   <si>
     <t xml:space="preserve">0.214374616742134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210663095116615</t>
+    <t xml:space="preserve">0.210663065314293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215654462575912</t>
+    <t xml:space="preserve">0.215654477477074</t>
   </si>
   <si>
     <t xml:space="preserve">0.212518841028214</t>
@@ -347,73 +347,73 @@
     <t xml:space="preserve">0.234980180859566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231652587652206</t>
+    <t xml:space="preserve">0.231652542948723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239971607923508</t>
+    <t xml:space="preserve">0.239971593022346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230372756719589</t>
+    <t xml:space="preserve">0.230372726917267</t>
   </si>
   <si>
     <t xml:space="preserve">0.227173119783401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220773860812187</t>
+    <t xml:space="preserve">0.220773875713348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226405188441277</t>
+    <t xml:space="preserve">0.226405218243599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216998338699341</t>
+    <t xml:space="preserve">0.216998293995857</t>
   </si>
   <si>
     <t xml:space="preserve">0.204839766025543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207975342869759</t>
+    <t xml:space="preserve">0.207975372672081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210535064339638</t>
+    <t xml:space="preserve">0.21053509414196</t>
   </si>
   <si>
     <t xml:space="preserve">0.209895178675652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211175039410591</t>
+    <t xml:space="preserve">0.211174979805946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.212582811713219</t>
+    <t xml:space="preserve">0.212582781910896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215782463550568</t>
+    <t xml:space="preserve">0.215782433748245</t>
   </si>
   <si>
     <t xml:space="preserve">0.229732826352119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223845526576042</t>
+    <t xml:space="preserve">0.223845452070236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224805355072021</t>
+    <t xml:space="preserve">0.224805384874344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233636364340782</t>
+    <t xml:space="preserve">0.233636349439621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238627761602402</t>
+    <t xml:space="preserve">0.238627731800079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228580951690674</t>
+    <t xml:space="preserve">0.228580966591835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223973482847214</t>
+    <t xml:space="preserve">0.223973453044891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223717525601387</t>
+    <t xml:space="preserve">0.223717510700226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220837861299515</t>
+    <t xml:space="preserve">0.220837816596031</t>
   </si>
   <si>
     <t xml:space="preserve">0.235492125153542</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.227365091443062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302556157112122</t>
+    <t xml:space="preserve">0.302556216716766</t>
   </si>
   <si>
     <t xml:space="preserve">0.358357578516006</t>
@@ -434,52 +434,52 @@
     <t xml:space="preserve">0.473543971776962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555454194545746</t>
+    <t xml:space="preserve">0.555454254150391</t>
   </si>
   <si>
     <t xml:space="preserve">0.485702484846115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444747269153595</t>
+    <t xml:space="preserve">0.444747418165207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429709166288376</t>
+    <t xml:space="preserve">0.429709136486053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403152257204056</t>
+    <t xml:space="preserve">0.403152287006378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371156007051468</t>
+    <t xml:space="preserve">0.37115603685379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421710103750229</t>
+    <t xml:space="preserve">0.421710044145584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374035686254501</t>
+    <t xml:space="preserve">0.374035716056824</t>
   </si>
   <si>
     <t xml:space="preserve">0.380754917860031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352598279714584</t>
+    <t xml:space="preserve">0.35259822010994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331800699234009</t>
+    <t xml:space="preserve">0.331800729036331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320602029561996</t>
+    <t xml:space="preserve">0.320602089166641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33244064450264</t>
+    <t xml:space="preserve">0.332440674304962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340439766645432</t>
+    <t xml:space="preserve">0.340439677238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327641248703003</t>
+    <t xml:space="preserve">0.327641189098358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355157971382141</t>
+    <t xml:space="preserve">0.355157941579819</t>
   </si>
   <si>
     <t xml:space="preserve">0.347478866577148</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">0.32700127363205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339159846305847</t>
+    <t xml:space="preserve">0.339159816503525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335960209369659</t>
+    <t xml:space="preserve">0.335960149765015</t>
   </si>
   <si>
     <t xml:space="preserve">0.323161751031876</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">0.330200910568237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31996214389801</t>
+    <t xml:space="preserve">0.319962114095688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317402422428131</t>
+    <t xml:space="preserve">0.317402392625809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340759724378586</t>
+    <t xml:space="preserve">0.340759664773941</t>
   </si>
   <si>
     <t xml:space="preserve">0.323801636695862</t>
@@ -521,82 +521,82 @@
     <t xml:space="preserve">0.322521835565567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33436045050621</t>
+    <t xml:space="preserve">0.334360390901566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32892107963562</t>
+    <t xml:space="preserve">0.328921020030975</t>
   </si>
   <si>
     <t xml:space="preserve">0.334040462970734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307163566350937</t>
+    <t xml:space="preserve">0.307163596153259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316122591495514</t>
+    <t xml:space="preserve">0.316122561693192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316698491573334</t>
+    <t xml:space="preserve">0.316698521375656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326361328363419</t>
+    <t xml:space="preserve">0.326361358165741</t>
   </si>
   <si>
     <t xml:space="preserve">0.331480771303177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36475682258606</t>
+    <t xml:space="preserve">0.364756762981415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345559120178223</t>
+    <t xml:space="preserve">0.3455590903759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346198976039886</t>
+    <t xml:space="preserve">0.346199035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325081557035446</t>
+    <t xml:space="preserve">0.325081527233124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343959271907806</t>
+    <t xml:space="preserve">0.343959301710129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320282101631165</t>
+    <t xml:space="preserve">0.320282071828842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333720505237579</t>
+    <t xml:space="preserve">0.333720475435257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396753072738647</t>
+    <t xml:space="preserve">0.396753042936325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376275420188904</t>
+    <t xml:space="preserve">0.376275449991226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375635504722595</t>
+    <t xml:space="preserve">0.375635534524918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376915335655212</t>
+    <t xml:space="preserve">0.376915395259857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370196133852005</t>
+    <t xml:space="preserve">0.37019619345665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377555340528488</t>
+    <t xml:space="preserve">0.377555310726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35131847858429</t>
+    <t xml:space="preserve">0.351318448781967</t>
   </si>
   <si>
     <t xml:space="preserve">0.356117874383926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36091735959053</t>
+    <t xml:space="preserve">0.360917270183563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373715728521347</t>
+    <t xml:space="preserve">0.373715758323669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39579313993454</t>
+    <t xml:space="preserve">0.395793169736862</t>
   </si>
   <si>
     <t xml:space="preserve">0.398672819137573</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">0.383954584598541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394193351268768</t>
+    <t xml:space="preserve">0.394193261861801</t>
   </si>
   <si>
     <t xml:space="preserve">0.384274482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415310800075531</t>
+    <t xml:space="preserve">0.415310829877853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422350078821182</t>
+    <t xml:space="preserve">0.422349959611893</t>
   </si>
   <si>
     <t xml:space="preserve">0.399312704801559</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">0.383634567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393553406000137</t>
+    <t xml:space="preserve">0.39355343580246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479943215847015</t>
+    <t xml:space="preserve">0.479943186044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.447306990623474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460745513439178</t>
+    <t xml:space="preserve">0.460745453834534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441547721624374</t>
+    <t xml:space="preserve">0.441547751426697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446027278900146</t>
+    <t xml:space="preserve">0.446027189493179</t>
   </si>
   <si>
     <t xml:space="preserve">0.454346239566803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447946965694427</t>
+    <t xml:space="preserve">0.447946906089783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430029153823853</t>
+    <t xml:space="preserve">0.430029034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432588815689087</t>
+    <t xml:space="preserve">0.432588785886765</t>
   </si>
   <si>
     <t xml:space="preserve">0.428749233484268</t>
@@ -665,43 +665,43 @@
     <t xml:space="preserve">0.413391053676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950685739517</t>
+    <t xml:space="preserve">0.415950745344162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421070128679276</t>
+    <t xml:space="preserve">0.42107018828392</t>
   </si>
   <si>
     <t xml:space="preserve">0.409551501274109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440267890691757</t>
+    <t xml:space="preserve">0.440267831087112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424909681081772</t>
+    <t xml:space="preserve">0.424909651279449</t>
   </si>
   <si>
     <t xml:space="preserve">0.470984250307083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435148537158966</t>
+    <t xml:space="preserve">0.435148447751999</t>
   </si>
   <si>
     <t xml:space="preserve">0.406991809606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426189512014389</t>
+    <t xml:space="preserve">0.426189541816711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431308925151825</t>
+    <t xml:space="preserve">0.431308954954147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418510407209396</t>
+    <t xml:space="preserve">0.418510466814041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405712008476257</t>
+    <t xml:space="preserve">0.40571203827858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412111222743988</t>
+    <t xml:space="preserve">0.412111133337021</t>
   </si>
   <si>
     <t xml:space="preserve">0.389073938131332</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">0.390353798866272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395473182201385</t>
+    <t xml:space="preserve">0.395473212003708</t>
   </si>
   <si>
     <t xml:space="preserve">0.410831362009048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438987970352173</t>
+    <t xml:space="preserve">0.438988089561462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427469432353973</t>
+    <t xml:space="preserve">0.427469342947006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414670884609222</t>
+    <t xml:space="preserve">0.4146708548069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401872456073761</t>
+    <t xml:space="preserve">0.401872426271439</t>
   </si>
   <si>
     <t xml:space="preserve">0.419790357351303</t>
@@ -737,49 +737,49 @@
     <t xml:space="preserve">0.423629820346832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368596255779266</t>
+    <t xml:space="preserve">0.368596345186234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372435927391052</t>
+    <t xml:space="preserve">0.372435957193375</t>
   </si>
   <si>
     <t xml:space="preserve">0.369876205921173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346838861703873</t>
+    <t xml:space="preserve">0.346838921308517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335320264101028</t>
+    <t xml:space="preserve">0.335320323705673</t>
   </si>
   <si>
     <t xml:space="preserve">0.366036683320999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363476932048798</t>
+    <t xml:space="preserve">0.36347696185112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350678443908691</t>
+    <t xml:space="preserve">0.350678503513336</t>
   </si>
   <si>
     <t xml:space="preserve">0.342999368906021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344279199838638</t>
+    <t xml:space="preserve">0.344279229640961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351958304643631</t>
+    <t xml:space="preserve">0.351958364248276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378835171461105</t>
+    <t xml:space="preserve">0.378835111856461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392913460731506</t>
+    <t xml:space="preserve">0.392913520336151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359637439250946</t>
+    <t xml:space="preserve">0.359637379646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367316484451294</t>
+    <t xml:space="preserve">0.367316544055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.385234385728836</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">0.382674694061279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380115002393723</t>
+    <t xml:space="preserve">0.380114942789078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391633629798889</t>
+    <t xml:space="preserve">0.391633599996567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398032873868942</t>
+    <t xml:space="preserve">0.39803284406662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400592565536499</t>
+    <t xml:space="preserve">0.400592535734177</t>
   </si>
   <si>
     <t xml:space="preserve">0.431948870420456</t>
@@ -806,43 +806,40 @@
     <t xml:space="preserve">0.438348144292831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457545787096024</t>
+    <t xml:space="preserve">0.457545816898346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463945001363754</t>
+    <t xml:space="preserve">0.463945150375366</t>
   </si>
   <si>
     <t xml:space="preserve">0.472350835800171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451200783252716</t>
+    <t xml:space="preserve">0.451200842857361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437100827693939</t>
+    <t xml:space="preserve">0.437100797891617</t>
   </si>
   <si>
     <t xml:space="preserve">0.423000812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4335757791996</t>
+    <t xml:space="preserve">0.433575809001923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444150745868683</t>
+    <t xml:space="preserve">0.444150805473328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447675764560699</t>
+    <t xml:space="preserve">0.447675853967667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440625756978989</t>
+    <t xml:space="preserve">0.440625846385956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426525712013245</t>
+    <t xml:space="preserve">0.426525741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415950745344162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408900678157806</t>
+    <t xml:space="preserve">0.408900737762451</t>
   </si>
   <si>
     <t xml:space="preserve">0.419475764036179</t>
@@ -851,37 +848,37 @@
     <t xml:space="preserve">0.39480072259903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398325741291046</t>
+    <t xml:space="preserve">0.398325711488724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412425667047501</t>
+    <t xml:space="preserve">0.412425726652145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430050760507584</t>
+    <t xml:space="preserve">0.430050820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454725801944733</t>
+    <t xml:space="preserve">0.45472577214241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535800993442535</t>
+    <t xml:space="preserve">0.535800874233246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458250761032104</t>
+    <t xml:space="preserve">0.458250820636749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465300917625427</t>
+    <t xml:space="preserve">0.465300798416138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461775898933411</t>
+    <t xml:space="preserve">0.461775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405375719070435</t>
+    <t xml:space="preserve">0.405375689268112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401850700378418</t>
+    <t xml:space="preserve">0.401850670576096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387750685214996</t>
+    <t xml:space="preserve">0.387750744819641</t>
   </si>
   <si>
     <t xml:space="preserve">0.380700677633286</t>
@@ -890,58 +887,61 @@
     <t xml:space="preserve">0.366600662469864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377175748348236</t>
+    <t xml:space="preserve">0.377175718545914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391275733709335</t>
+    <t xml:space="preserve">0.391275703907013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373650699853897</t>
+    <t xml:space="preserve">0.373650640249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346860647201538</t>
+    <t xml:space="preserve">0.346860617399216</t>
   </si>
   <si>
     <t xml:space="preserve">0.345450639724731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359550625085831</t>
+    <t xml:space="preserve">0.359550654888153</t>
   </si>
   <si>
     <t xml:space="preserve">0.35250061750412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338400542736053</t>
+    <t xml:space="preserve">0.338400572538376</t>
   </si>
   <si>
     <t xml:space="preserve">0.317250549793243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320070564746857</t>
+    <t xml:space="preserve">0.320070594549179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296100527048111</t>
+    <t xml:space="preserve">0.296100556850433</t>
   </si>
   <si>
     <t xml:space="preserve">0.26367050409317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283410519361496</t>
+    <t xml:space="preserve">0.283410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267900496721268</t>
+    <t xml:space="preserve">0.267900437116623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277770519256592</t>
+    <t xml:space="preserve">0.277770429849625</t>
   </si>
   <si>
     <t xml:space="preserve">0.266490459442139</t>
   </si>
   <si>
+    <t xml:space="preserve">0.249570488929749</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.253800451755524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248160421848297</t>
+    <t xml:space="preserve">0.248160436749458</t>
   </si>
   <si>
     <t xml:space="preserve">0.290460497140884</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">0.276360481977463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284820526838303</t>
+    <t xml:space="preserve">0.284820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">0.286230504512787</t>
@@ -965,76 +965,76 @@
     <t xml:space="preserve">0.308790564537048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314430564641953</t>
+    <t xml:space="preserve">0.31443053483963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344040602445602</t>
+    <t xml:space="preserve">0.344040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331350594758987</t>
+    <t xml:space="preserve">0.331350564956665</t>
   </si>
   <si>
     <t xml:space="preserve">0.325710624456406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349680632352829</t>
+    <t xml:space="preserve">0.349680602550507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370125710964203</t>
+    <t xml:space="preserve">0.370125621557236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384225726127625</t>
+    <t xml:space="preserve">0.38422566652298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334170579910278</t>
+    <t xml:space="preserve">0.334170609712601</t>
   </si>
   <si>
     <t xml:space="preserve">0.336990565061569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342630594968796</t>
+    <t xml:space="preserve">0.342630624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356025636196136</t>
+    <t xml:space="preserve">0.356025665998459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351090580224991</t>
+    <t xml:space="preserve">0.351090639829636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328530579805374</t>
+    <t xml:space="preserve">0.328530550003052</t>
   </si>
   <si>
     <t xml:space="preserve">0.329940617084503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327120631933212</t>
+    <t xml:space="preserve">0.327120542526245</t>
   </si>
   <si>
     <t xml:space="preserve">0.324300587177277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311610549688339</t>
+    <t xml:space="preserve">0.311610519886017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322890609502792</t>
+    <t xml:space="preserve">0.32289057970047</t>
   </si>
   <si>
     <t xml:space="preserve">0.310200542211533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303150564432144</t>
+    <t xml:space="preserve">0.303150504827499</t>
   </si>
   <si>
     <t xml:space="preserve">0.2890505194664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293280482292175</t>
+    <t xml:space="preserve">0.293280512094498</t>
   </si>
   <si>
     <t xml:space="preserve">0.269310474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272130519151688</t>
+    <t xml:space="preserve">0.272130489349365</t>
   </si>
   <si>
     <t xml:space="preserve">0.265080481767654</t>
@@ -1043,37 +1043,37 @@
     <t xml:space="preserve">0.270720481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274950504302979</t>
+    <t xml:space="preserve">0.274950474500656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282000541687012</t>
+    <t xml:space="preserve">0.282000482082367</t>
   </si>
   <si>
     <t xml:space="preserve">0.297510504722595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30174058675766</t>
+    <t xml:space="preserve">0.301740527153015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294690519571304</t>
+    <t xml:space="preserve">0.294690549373627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437586963176727</t>
+    <t xml:space="preserve">0.437587022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879156827927</t>
+    <t xml:space="preserve">0.406879097223282</t>
   </si>
   <si>
     <t xml:space="preserve">0.395363658666611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38384822010994</t>
+    <t xml:space="preserve">0.383848249912262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368494242429733</t>
+    <t xml:space="preserve">0.3684943318367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376171290874481</t>
+    <t xml:space="preserve">0.376171261072159</t>
   </si>
   <si>
     <t xml:space="preserve">0.37002968788147</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">0.38768669962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380777478218079</t>
+    <t xml:space="preserve">0.380777448415756</t>
   </si>
   <si>
     <t xml:space="preserve">0.371565043926239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356211185455322</t>
+    <t xml:space="preserve">0.356211155653</t>
   </si>
   <si>
     <t xml:space="preserve">0.350069612264633</t>
@@ -1097,46 +1097,46 @@
     <t xml:space="preserve">0.348534196615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345463395118713</t>
+    <t xml:space="preserve">0.345463424921036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359281957149506</t>
+    <t xml:space="preserve">0.359281927347183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353140413761139</t>
+    <t xml:space="preserve">0.353140383958817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357746541500092</t>
+    <t xml:space="preserve">0.357746571302414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34239262342453</t>
+    <t xml:space="preserve">0.342392653226852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340857267379761</t>
+    <t xml:space="preserve">0.340857237577438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354675799608231</t>
+    <t xml:space="preserve">0.354675769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445263892412186</t>
+    <t xml:space="preserve">0.44526395201683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41839462518692</t>
+    <t xml:space="preserve">0.418394565582275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460617929697037</t>
+    <t xml:space="preserve">0.46061784029007</t>
   </si>
   <si>
     <t xml:space="preserve">0.452940911054611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449102371931076</t>
+    <t xml:space="preserve">0.449102401733398</t>
   </si>
   <si>
     <t xml:space="preserve">0.422233045101166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410717666149139</t>
+    <t xml:space="preserve">0.410717695951462</t>
   </si>
   <si>
     <t xml:space="preserve">0.399202138185501</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">0.39152517914772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403040677309036</t>
+    <t xml:space="preserve">0.403040647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414556086063385</t>
+    <t xml:space="preserve">0.414556115865707</t>
   </si>
   <si>
     <t xml:space="preserve">0.379242062568665</t>
@@ -1160,37 +1160,37 @@
     <t xml:space="preserve">0.360817313194275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351605027914047</t>
+    <t xml:space="preserve">0.351604968309402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34699884057045</t>
+    <t xml:space="preserve">0.346998810768127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377706676721573</t>
+    <t xml:space="preserve">0.377706706523895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366958856582642</t>
+    <t xml:space="preserve">0.366958945989609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374635875225067</t>
+    <t xml:space="preserve">0.37463590502739</t>
   </si>
   <si>
     <t xml:space="preserve">0.365423500537872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322432488203049</t>
+    <t xml:space="preserve">0.322432518005371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305543214082718</t>
+    <t xml:space="preserve">0.305543184280396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30707859992981</t>
+    <t xml:space="preserve">0.307078570127487</t>
   </si>
   <si>
     <t xml:space="preserve">0.32396787405014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325503319501877</t>
+    <t xml:space="preserve">0.325503259897232</t>
   </si>
   <si>
     <t xml:space="preserve">0.330109506845474</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">0.333180248737335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336251080036163</t>
+    <t xml:space="preserve">0.336251020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337786436080933</t>
+    <t xml:space="preserve">0.33778640627861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343928039073944</t>
+    <t xml:space="preserve">0.343928009271622</t>
   </si>
   <si>
     <t xml:space="preserve">0.334715634584427</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">0.308614015579224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319361686706543</t>
+    <t xml:space="preserve">0.319361746311188</t>
   </si>
   <si>
     <t xml:space="preserve">0.328574120998383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323345869779587</t>
+    <t xml:space="preserve">0.323345839977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.328171879053116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320128500461578</t>
+    <t xml:space="preserve">0.320128470659256</t>
   </si>
   <si>
     <t xml:space="preserve">0.32495453953743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337823987007141</t>
+    <t xml:space="preserve">0.337824016809464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339432656764984</t>
+    <t xml:space="preserve">0.339432716369629</t>
   </si>
   <si>
     <t xml:space="preserve">0.326563209295273</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">0.329780578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318519771099091</t>
+    <t xml:space="preserve">0.318519800901413</t>
   </si>
   <si>
     <t xml:space="preserve">0.308867663145065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297606885433197</t>
+    <t xml:space="preserve">0.297606855630875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3072589635849</t>
+    <t xml:space="preserve">0.307258993387222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321737170219421</t>
+    <t xml:space="preserve">0.321737200021744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305650293827057</t>
+    <t xml:space="preserve">0.305650264024734</t>
   </si>
   <si>
     <t xml:space="preserve">0.304041594266891</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">0.295998185873032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287954747676849</t>
+    <t xml:space="preserve">0.287954777479172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292780786752701</t>
+    <t xml:space="preserve">0.292780846357346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284737348556519</t>
+    <t xml:space="preserve">0.284737408161163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28151997923851</t>
+    <t xml:space="preserve">0.281520009040833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283128648996353</t>
+    <t xml:space="preserve">0.283128678798676</t>
   </si>
   <si>
     <t xml:space="preserve">0.275085270404816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286345988512039</t>
+    <t xml:space="preserve">0.286346137523651</t>
   </si>
   <si>
     <t xml:space="preserve">0.276693940162659</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">0.289563447237015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29117214679718</t>
+    <t xml:space="preserve">0.291172116994858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300824254751205</t>
+    <t xml:space="preserve">0.300824224948883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302432894706726</t>
+    <t xml:space="preserve">0.302432954311371</t>
   </si>
   <si>
     <t xml:space="preserve">0.313693732023239</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">0.294389516115189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352302193641663</t>
+    <t xml:space="preserve">0.35230216383934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344258785247803</t>
+    <t xml:space="preserve">0.34425875544548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345867455005646</t>
+    <t xml:space="preserve">0.345867484807968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347476154565811</t>
+    <t xml:space="preserve">0.347476124763489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341041386127472</t>
+    <t xml:space="preserve">0.34104135632515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342650085687637</t>
+    <t xml:space="preserve">0.34265011548996</t>
   </si>
   <si>
     <t xml:space="preserve">0.358736932277679</t>
@@ -1340,88 +1340,88 @@
     <t xml:space="preserve">0.300703525543213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2972272336483</t>
+    <t xml:space="preserve">0.297227203845978</t>
   </si>
   <si>
     <t xml:space="preserve">0.29548904299736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290274530649185</t>
+    <t xml:space="preserve">0.290274500846863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292012721300125</t>
+    <t xml:space="preserve">0.29201266169548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305918008089066</t>
+    <t xml:space="preserve">0.30591806769371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304179847240448</t>
+    <t xml:space="preserve">0.30417987704277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288536339998245</t>
+    <t xml:space="preserve">0.288536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283321857452393</t>
+    <t xml:space="preserve">0.283321797847748</t>
   </si>
   <si>
     <t xml:space="preserve">0.29375085234642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28506001830101</t>
+    <t xml:space="preserve">0.285059988498688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278107285499573</t>
+    <t xml:space="preserve">0.278107315301895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28158363699913</t>
+    <t xml:space="preserve">0.281583666801453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27463099360466</t>
+    <t xml:space="preserve">0.274631023406982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28679820895195</t>
+    <t xml:space="preserve">0.286798179149628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279845505952835</t>
+    <t xml:space="preserve">0.279845476150513</t>
   </si>
   <si>
     <t xml:space="preserve">0.276369154453278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272892832756042</t>
+    <t xml:space="preserve">0.272892773151398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309394329786301</t>
+    <t xml:space="preserve">0.309394419193268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298965394496918</t>
+    <t xml:space="preserve">0.298965364694595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307656198740005</t>
+    <t xml:space="preserve">0.307656228542328</t>
   </si>
   <si>
     <t xml:space="preserve">0.311132580041885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312870770692825</t>
+    <t xml:space="preserve">0.312870740890503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330252438783646</t>
+    <t xml:space="preserve">0.330252468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325037956237793</t>
+    <t xml:space="preserve">0.325037926435471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314608931541443</t>
+    <t xml:space="preserve">0.31460890173912</t>
   </si>
   <si>
     <t xml:space="preserve">0.319823443889618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318085283041</t>
+    <t xml:space="preserve">0.318085253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316347062587738</t>
+    <t xml:space="preserve">0.31634709239006</t>
   </si>
   <si>
     <t xml:space="preserve">0.315903395414352</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">0.30170550942421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308804422616959</t>
+    <t xml:space="preserve">0.308804452419281</t>
   </si>
   <si>
     <t xml:space="preserve">0.294606506824493</t>
@@ -1442,37 +1442,37 @@
     <t xml:space="preserve">0.292831808328629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303480297327042</t>
+    <t xml:space="preserve">0.303480237722397</t>
   </si>
   <si>
     <t xml:space="preserve">0.319233953952789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31016480922699</t>
+    <t xml:space="preserve">0.310164839029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30835098028183</t>
+    <t xml:space="preserve">0.308351010084152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31197863817215</t>
+    <t xml:space="preserve">0.311978667974472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306537181138992</t>
+    <t xml:space="preserve">0.30653715133667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292026519775391</t>
+    <t xml:space="preserve">0.292026489973068</t>
   </si>
   <si>
     <t xml:space="preserve">0.293840348720551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295654147863388</t>
+    <t xml:space="preserve">0.29565417766571</t>
   </si>
   <si>
     <t xml:space="preserve">0.30472332239151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299281805753708</t>
+    <t xml:space="preserve">0.29928183555603</t>
   </si>
   <si>
     <t xml:space="preserve">0.290212690830231</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">0.288398832082748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284771203994751</t>
+    <t xml:space="preserve">0.284771174192429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286585032939911</t>
+    <t xml:space="preserve">0.286585062742233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29746800661087</t>
+    <t xml:space="preserve">0.297467976808548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300716459751129</t>
+    <t xml:space="preserve">0.300716489553452</t>
   </si>
   <si>
     <t xml:space="preserve">0.295147627592087</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">0.308141559362411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297003924846649</t>
+    <t xml:space="preserve">0.297003954648972</t>
   </si>
   <si>
     <t xml:space="preserve">0.309997856616974</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">0.317422956228256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322991728782654</t>
+    <t xml:space="preserve">0.322991758584976</t>
   </si>
   <si>
     <t xml:space="preserve">0.324848055839539</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">0.339698255062103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326704293489456</t>
+    <t xml:space="preserve">0.326704323291779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330416858196259</t>
+    <t xml:space="preserve">0.330416887998581</t>
   </si>
   <si>
     <t xml:space="preserve">0.330023527145386</t>
@@ -26131,7 +26131,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26157,7 +26157,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26183,7 +26183,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26209,7 +26209,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26235,7 +26235,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26261,7 +26261,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26287,7 +26287,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26313,7 +26313,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26339,7 +26339,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26365,7 +26365,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26391,7 +26391,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26417,7 +26417,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26443,7 +26443,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26469,7 +26469,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26495,7 +26495,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26521,7 +26521,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26573,7 +26573,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26599,7 +26599,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26625,7 +26625,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26651,7 +26651,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26677,7 +26677,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26703,7 +26703,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26729,7 +26729,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26755,7 +26755,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26781,7 +26781,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26807,7 +26807,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26833,7 +26833,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26859,7 +26859,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26885,7 +26885,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26911,7 +26911,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26937,7 +26937,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26963,7 +26963,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26989,7 +26989,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27015,7 +27015,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27041,7 +27041,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27119,7 +27119,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27197,7 +27197,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27223,7 +27223,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27275,7 +27275,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27301,7 +27301,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27327,7 +27327,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27353,7 +27353,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27509,7 +27509,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27535,7 +27535,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27561,7 +27561,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27639,7 +27639,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27665,7 +27665,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28081,7 +28081,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28107,7 +28107,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28133,7 +28133,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28159,7 +28159,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28185,7 +28185,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28211,7 +28211,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28237,7 +28237,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28263,7 +28263,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28289,7 +28289,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28341,7 +28341,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28367,7 +28367,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28393,7 +28393,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28419,7 +28419,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28445,7 +28445,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28471,7 +28471,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28497,7 +28497,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28523,7 +28523,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28549,7 +28549,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28575,7 +28575,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28601,7 +28601,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28679,7 +28679,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28705,7 +28705,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28731,7 +28731,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28757,7 +28757,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28783,7 +28783,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28809,7 +28809,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28835,7 +28835,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28861,7 +28861,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28887,7 +28887,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28913,7 +28913,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28939,7 +28939,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28965,7 +28965,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28991,7 +28991,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29017,7 +29017,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29043,7 +29043,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29069,7 +29069,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29095,7 +29095,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29121,7 +29121,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29147,7 +29147,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29173,7 +29173,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29199,7 +29199,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29303,7 +29303,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29355,7 +29355,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29433,7 +29433,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29459,7 +29459,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29485,7 +29485,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29511,7 +29511,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29537,7 +29537,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29563,7 +29563,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29589,7 +29589,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29615,7 +29615,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29641,7 +29641,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29667,7 +29667,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29693,7 +29693,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29719,7 +29719,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29745,7 +29745,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29771,7 +29771,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29797,7 +29797,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29823,7 +29823,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29849,7 +29849,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29875,7 +29875,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29901,7 +29901,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30083,7 +30083,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30213,7 +30213,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30239,7 +30239,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30265,7 +30265,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30317,7 +30317,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30343,7 +30343,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30421,7 +30421,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30811,7 +30811,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30837,7 +30837,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30941,7 +30941,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30993,7 +30993,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31019,7 +31019,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31045,7 +31045,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31149,7 +31149,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31175,7 +31175,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31201,7 +31201,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31253,7 +31253,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31279,7 +31279,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31305,7 +31305,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31331,7 +31331,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31357,7 +31357,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31383,7 +31383,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31409,7 +31409,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31435,7 +31435,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31461,7 +31461,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31487,7 +31487,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31513,7 +31513,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31539,7 +31539,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31565,7 +31565,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31591,7 +31591,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31617,7 +31617,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31643,7 +31643,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31669,7 +31669,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31695,7 +31695,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31721,7 +31721,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31747,7 +31747,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31773,7 +31773,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31799,7 +31799,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31825,7 +31825,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31851,7 +31851,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31877,7 +31877,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31903,7 +31903,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31929,7 +31929,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31981,7 +31981,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32007,7 +32007,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32033,7 +32033,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32085,7 +32085,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32267,7 +32267,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32293,7 +32293,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32319,7 +32319,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32345,7 +32345,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32683,7 +32683,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33177,7 +33177,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34217,7 +34217,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34425,7 +34425,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34451,7 +34451,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34945,7 +34945,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35595,7 +35595,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35621,7 +35621,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35673,7 +35673,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35699,7 +35699,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35725,7 +35725,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35751,7 +35751,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35803,7 +35803,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35829,7 +35829,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35855,7 +35855,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35907,7 +35907,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35933,7 +35933,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35959,7 +35959,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35985,7 +35985,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36011,7 +36011,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36037,7 +36037,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36063,7 +36063,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36089,7 +36089,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36115,7 +36115,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -67843,7 +67843,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.5316782407</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>4000</v>
@@ -67864,6 +67864,32 @@
         <v>562</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6912268518</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>562</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994351506233</t>
+    <t xml:space="preserve">0.175994336605072</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -50,145 +50,145 @@
     <t xml:space="preserve">0.172851577401161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594470739365</t>
+    <t xml:space="preserve">0.171594485640526</t>
   </si>
   <si>
     <t xml:space="preserve">0.164051860570908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16970881819725</t>
+    <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966625332832</t>
+    <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309682607651</t>
+    <t xml:space="preserve">0.143309652805328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783760309219</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195335149765</t>
+    <t xml:space="preserve">0.145195320248604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737930417061</t>
+    <t xml:space="preserve">0.152737945318222</t>
   </si>
   <si>
     <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.150789439678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1464524269104</t>
+    <t xml:space="preserve">0.146452397108078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852643013</t>
+    <t xml:space="preserve">0.139852628111839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538377523422</t>
+    <t xml:space="preserve">0.139538362622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915481209755</t>
+    <t xml:space="preserve">0.139915496110916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052575945854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909816741943</t>
+    <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337364077568</t>
+    <t xml:space="preserve">0.170337378978729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817471385002</t>
+    <t xml:space="preserve">0.166817456483841</t>
   </si>
   <si>
     <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137811183929</t>
+    <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623612761497</t>
+    <t xml:space="preserve">0.154623597860336</t>
   </si>
   <si>
     <t xml:space="preserve">0.149595186114311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692145228386</t>
+    <t xml:space="preserve">0.155692115426064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909101366997</t>
+    <t xml:space="preserve">0.160909131169319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960595726967</t>
+    <t xml:space="preserve">0.158960610628128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314281463623</t>
+    <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17725145816803</t>
+    <t xml:space="preserve">0.177251443266869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965924859047</t>
+    <t xml:space="preserve">0.170965939760208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937513113022</t>
+    <t xml:space="preserve">0.165937528014183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565343618393</t>
+    <t xml:space="preserve">0.188565358519554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650943994522</t>
+    <t xml:space="preserve">0.1926509141922</t>
   </si>
   <si>
     <t xml:space="preserve">0.191708102822304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165507555008</t>
+    <t xml:space="preserve">0.184165522456169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651309132576</t>
+    <t xml:space="preserve">0.181651279330254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136395335197</t>
+    <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678960800171</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073512434959</t>
+    <t xml:space="preserve">0.201073527336121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736514568329</t>
+    <t xml:space="preserve">0.19673652946949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222286343575</t>
+    <t xml:space="preserve">0.194222301244736</t>
   </si>
   <si>
     <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279840111732</t>
+    <t xml:space="preserve">0.182279855012894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834539294243</t>
+    <t xml:space="preserve">0.16983450949192</t>
   </si>
   <si>
     <t xml:space="preserve">0.168451711535454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794768810272</t>
+    <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606574654579</t>
+    <t xml:space="preserve">0.151606544852257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16656605899334</t>
+    <t xml:space="preserve">0.166566073894501</t>
   </si>
   <si>
     <t xml:space="preserve">0.157074943184853</t>
@@ -197,121 +197,121 @@
     <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995037078857</t>
+    <t xml:space="preserve">0.15399506688118</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051174998283</t>
+    <t xml:space="preserve">0.186051160097122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936812639236</t>
+    <t xml:space="preserve">0.187936827540398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536931872368</t>
+    <t xml:space="preserve">0.18353696167469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714162230492</t>
+    <t xml:space="preserve">0.181714132428169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194589972496</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16028057038784</t>
+    <t xml:space="preserve">0.160280555486679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080972790718</t>
+    <t xml:space="preserve">0.147080942988396</t>
   </si>
   <si>
     <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338064551353</t>
+    <t xml:space="preserve">0.148338094353676</t>
   </si>
   <si>
     <t xml:space="preserve">0.144566759467125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394888043404</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183246135712</t>
+    <t xml:space="preserve">0.165183275938034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651644468307</t>
+    <t xml:space="preserve">0.170651629567146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223016619682</t>
+    <t xml:space="preserve">0.172223031520844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594120502472</t>
+    <t xml:space="preserve">0.182594135403633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20050784945488</t>
+    <t xml:space="preserve">0.200507789850235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.193593740463257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131401538849</t>
+    <t xml:space="preserve">0.178131386637688</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010704040527</t>
+    <t xml:space="preserve">0.201010629534721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850876927376</t>
+    <t xml:space="preserve">0.194850891828537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770970821381</t>
+    <t xml:space="preserve">0.191770955920219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19987927377224</t>
+    <t xml:space="preserve">0.199879303574562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078871369362</t>
+    <t xml:space="preserve">0.213078811764717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787308454514</t>
+    <t xml:space="preserve">0.216787323355675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563942670822</t>
+    <t xml:space="preserve">0.232563897967339</t>
   </si>
   <si>
     <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420468091965</t>
+    <t xml:space="preserve">0.251420527696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26713427901268</t>
+    <t xml:space="preserve">0.267134249210358</t>
   </si>
   <si>
     <t xml:space="preserve">0.275305390357971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29039067029953</t>
+    <t xml:space="preserve">0.290390640497208</t>
   </si>
   <si>
     <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257706016302109</t>
+    <t xml:space="preserve">0.257705986499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157346725464</t>
+    <t xml:space="preserve">0.260157376527786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250226199626923</t>
+    <t xml:space="preserve">0.250226259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163346529007</t>
+    <t xml:space="preserve">0.250163376331329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24280934035778</t>
+    <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
     <t xml:space="preserve">0.243249297142029</t>
@@ -323,58 +323,58 @@
     <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821034431458</t>
+    <t xml:space="preserve">0.233821004629135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564702749252</t>
+    <t xml:space="preserve">0.21056467294693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919103860855</t>
+    <t xml:space="preserve">0.20691904425621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821764707565</t>
+    <t xml:space="preserve">0.211821749806404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20874185860157</t>
+    <t xml:space="preserve">0.208741843700409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592339515686</t>
+    <t xml:space="preserve">0.237592369318008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134919881821</t>
+    <t xml:space="preserve">0.245134934782982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230804026126862</t>
+    <t xml:space="preserve">0.230803996324539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535516023636</t>
+    <t xml:space="preserve">0.227535530924797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706672072411</t>
+    <t xml:space="preserve">0.235706642270088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278454065323</t>
+    <t xml:space="preserve">0.226278394460678</t>
   </si>
   <si>
     <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850146651268</t>
+    <t xml:space="preserve">0.216850161552429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381412982941</t>
+    <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141694664955</t>
+    <t xml:space="preserve">0.213141664862633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20119920372963</t>
+    <t xml:space="preserve">0.201199233531952</t>
   </si>
   <si>
     <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793367862701</t>
+    <t xml:space="preserve">0.20679335296154</t>
   </si>
   <si>
     <t xml:space="preserve">0.206164792180061</t>
@@ -383,145 +383,145 @@
     <t xml:space="preserve">0.207421869039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804681897163</t>
+    <t xml:space="preserve">0.208804696798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947470903397</t>
+    <t xml:space="preserve">0.211947441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649908185005</t>
+    <t xml:space="preserve">0.225649878382683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867169857025</t>
+    <t xml:space="preserve">0.219867184758186</t>
   </si>
   <si>
     <t xml:space="preserve">0.220810055732727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484066367149</t>
+    <t xml:space="preserve">0.229484051465988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386786818504</t>
+    <t xml:space="preserve">0.234386742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22451850771904</t>
+    <t xml:space="preserve">0.224518492817879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992876052856</t>
+    <t xml:space="preserve">0.219992890954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741493463516</t>
+    <t xml:space="preserve">0.219741478562355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216913014650345</t>
+    <t xml:space="preserve">0.216913029551506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306880712509</t>
+    <t xml:space="preserve">0.231306821107864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038705945015</t>
+    <t xml:space="preserve">0.217038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324209451675</t>
+    <t xml:space="preserve">0.223324239253998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297178953886032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988703012466</t>
+    <t xml:space="preserve">0.351988673210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127885341644</t>
+    <t xml:space="preserve">0.465127795934677</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070420980453</t>
+    <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43684309720993</t>
+    <t xml:space="preserve">0.436843007802963</t>
   </si>
   <si>
     <t xml:space="preserve">0.422072142362595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987272262573</t>
+    <t xml:space="preserve">0.395987242460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559680223465</t>
+    <t xml:space="preserve">0.364559710025787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41421514749527</t>
+    <t xml:space="preserve">0.414215236902237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388188838959</t>
+    <t xml:space="preserve">0.367388159036636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373988002538681</t>
+    <t xml:space="preserve">0.373987972736359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331685781479</t>
+    <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
     <t xml:space="preserve">0.3259037733078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904093742371</t>
+    <t xml:space="preserve">0.314904123544693</t>
   </si>
   <si>
     <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389179944992</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818202733994</t>
+    <t xml:space="preserve">0.321818262338638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845928907394</t>
+    <t xml:space="preserve">0.348845899105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303288936615</t>
+    <t xml:space="preserve">0.341303259134293</t>
   </si>
   <si>
     <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361192941666</t>
+    <t xml:space="preserve">0.318361222743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189612150192</t>
+    <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132117986679</t>
+    <t xml:space="preserve">0.333132147789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989343881607</t>
+    <t xml:space="preserve">0.329989314079285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418396472931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332386255264</t>
+    <t xml:space="preserve">0.324332416057587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275622367859</t>
+    <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761379241943</t>
+    <t xml:space="preserve">0.311761409044266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703594446182</t>
+    <t xml:space="preserve">0.334703534841537</t>
   </si>
   <si>
     <t xml:space="preserve">0.318046867847443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789776086807</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417986631393</t>
+    <t xml:space="preserve">0.328417927026749</t>
   </si>
   <si>
     <t xml:space="preserve">0.323075294494629</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">0.301704555749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504257678986</t>
+    <t xml:space="preserve">0.31050431728363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069965362549</t>
+    <t xml:space="preserve">0.311070024967194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561140775681</t>
+    <t xml:space="preserve">0.320561110973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589537620544</t>
+    <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
     <t xml:space="preserve">0.358274191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417636394501</t>
+    <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34004619717598</t>
+    <t xml:space="preserve">0.340046167373657</t>
   </si>
   <si>
     <t xml:space="preserve">0.319304049015045</t>
@@ -560,145 +560,145 @@
     <t xml:space="preserve">0.337846279144287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589858055115</t>
+    <t xml:space="preserve">0.314589887857437</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789455652237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701753854752</t>
+    <t xml:space="preserve">0.389701783657074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588136672974</t>
+    <t xml:space="preserve">0.369588077068329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959575891495</t>
+    <t xml:space="preserve">0.368959605693817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37021666765213</t>
+    <t xml:space="preserve">0.370216578245163</t>
   </si>
   <si>
     <t xml:space="preserve">0.363616794347763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845198631287</t>
+    <t xml:space="preserve">0.370845168828964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074564218521</t>
+    <t xml:space="preserve">0.345074623823166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788725376129</t>
+    <t xml:space="preserve">0.349788695573807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35450291633606</t>
+    <t xml:space="preserve">0.354502886533737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073863744736</t>
+    <t xml:space="preserve">0.36707392334938</t>
   </si>
   <si>
     <t xml:space="preserve">0.388758957386017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587376594543</t>
+    <t xml:space="preserve">0.391587466001511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759218215942</t>
+    <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130687236786</t>
+    <t xml:space="preserve">0.377130717039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377445012331009</t>
+    <t xml:space="preserve">0.377444952726364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929748296738</t>
+    <t xml:space="preserve">0.407929688692093</t>
   </si>
   <si>
     <t xml:space="preserve">0.414843738079071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215967178345</t>
+    <t xml:space="preserve">0.392215937376022</t>
   </si>
   <si>
     <t xml:space="preserve">0.376816391944885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386559039354324</t>
+    <t xml:space="preserve">0.386559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413344144821</t>
+    <t xml:space="preserve">0.471413284540176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357221126556</t>
+    <t xml:space="preserve">0.439357280731201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556908130646</t>
+    <t xml:space="preserve">0.452556788921356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700293302536</t>
+    <t xml:space="preserve">0.433700323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100159168243</t>
+    <t xml:space="preserve">0.438100218772888</t>
   </si>
   <si>
     <t xml:space="preserve">0.446271300315857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985752105713</t>
+    <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386348247528</t>
+    <t xml:space="preserve">0.422386467456818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900531768799</t>
+    <t xml:space="preserve">0.424900621175766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129405498505</t>
+    <t xml:space="preserve">0.42112934589386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815430641174</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044036149979</t>
+    <t xml:space="preserve">0.406044125556946</t>
   </si>
   <si>
     <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586735725403</t>
+    <t xml:space="preserve">0.41358670592308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272790670395</t>
+    <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443261146545</t>
+    <t xml:space="preserve">0.432443231344223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357921600342</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613761425018</t>
+    <t xml:space="preserve">0.462613642215729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42741471529007</t>
+    <t xml:space="preserve">0.427414864301682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758547544479</t>
+    <t xml:space="preserve">0.399758607149124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615102767944</t>
+    <t xml:space="preserve">0.418615132570267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643529415131</t>
+    <t xml:space="preserve">0.423643499612808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072462797165</t>
+    <t xml:space="preserve">0.41107240319252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501336574554</t>
+    <t xml:space="preserve">0.398501425981522</t>
   </si>
   <si>
     <t xml:space="preserve">0.404786944389343</t>
@@ -710,67 +710,67 @@
     <t xml:space="preserve">0.383416205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444572687149</t>
+    <t xml:space="preserve">0.388444602489471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529852628708</t>
+    <t xml:space="preserve">0.403529912233353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43118616938591</t>
+    <t xml:space="preserve">0.431186079978943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872164726257</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301157712936</t>
+    <t xml:space="preserve">0.407301187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730061292648</t>
+    <t xml:space="preserve">0.394730180501938</t>
   </si>
   <si>
     <t xml:space="preserve">0.412329584360123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40101569890976</t>
+    <t xml:space="preserve">0.40101557970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100829839706</t>
+    <t xml:space="preserve">0.416100859642029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045466899872</t>
+    <t xml:space="preserve">0.362045496702194</t>
   </si>
   <si>
     <t xml:space="preserve">0.365816801786423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302618265152</t>
+    <t xml:space="preserve">0.363302558660507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674728155136</t>
+    <t xml:space="preserve">0.340674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360842704773</t>
+    <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531313180923</t>
+    <t xml:space="preserve">0.359531223773956</t>
   </si>
   <si>
     <t xml:space="preserve">0.357017070055008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446033239365</t>
+    <t xml:space="preserve">0.344446063041687</t>
   </si>
   <si>
     <t xml:space="preserve">0.336903423070908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160514831543</t>
+    <t xml:space="preserve">0.338160544633865</t>
   </si>
   <si>
     <t xml:space="preserve">0.345703154802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102349996567</t>
+    <t xml:space="preserve">0.372102320194244</t>
   </si>
   <si>
     <t xml:space="preserve">0.385930418968201</t>
@@ -779,109 +779,109 @@
     <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788375139236</t>
+    <t xml:space="preserve">0.360788345336914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387808799744</t>
+    <t xml:space="preserve">0.378387778997421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873625278473</t>
+    <t xml:space="preserve">0.375873655080795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359382152557</t>
+    <t xml:space="preserve">0.373359322547913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673327207565</t>
+    <t xml:space="preserve">0.384673267602921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958845615387</t>
+    <t xml:space="preserve">0.390958815813065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393473029136658</t>
+    <t xml:space="preserve">0.39347305893898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272090196609</t>
+    <t xml:space="preserve">0.424272000789642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557519197464</t>
+    <t xml:space="preserve">0.430557548999786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414104223251</t>
+    <t xml:space="preserve">0.449414074420929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699592828751</t>
+    <t xml:space="preserve">0.455699622631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463956147432327</t>
+    <t xml:space="preserve">0.46395605802536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181902170181</t>
+    <t xml:space="preserve">0.443181872367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332435131073</t>
+    <t xml:space="preserve">0.429332464933395</t>
   </si>
   <si>
     <t xml:space="preserve">0.415482968091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870090723038</t>
+    <t xml:space="preserve">0.42587012052536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257153749466</t>
+    <t xml:space="preserve">0.436257123947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719527959824</t>
+    <t xml:space="preserve">0.439719468355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794839143753</t>
+    <t xml:space="preserve">0.432794868946075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945372104645</t>
+    <t xml:space="preserve">0.4189453125</t>
   </si>
   <si>
     <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020713090897</t>
+    <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
     <t xml:space="preserve">0.387784153223038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246467828751</t>
+    <t xml:space="preserve">0.391246557235718</t>
   </si>
   <si>
     <t xml:space="preserve">0.405095875263214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422407686710358</t>
+    <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644186973572</t>
+    <t xml:space="preserve">0.446644216775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278376579285</t>
+    <t xml:space="preserve">0.526278436183929</t>
   </si>
   <si>
     <t xml:space="preserve">0.450106561183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031220197678</t>
+    <t xml:space="preserve">0.45703125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568905591965</t>
+    <t xml:space="preserve">0.45356884598732</t>
   </si>
   <si>
     <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708842039108</t>
+    <t xml:space="preserve">0.394708871841431</t>
   </si>
   <si>
     <t xml:space="preserve">0.380859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934715986252</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085219144821</t>
@@ -896,28 +896,28 @@
     <t xml:space="preserve">0.367009967565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696066617966</t>
+    <t xml:space="preserve">0.340696036815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311093091965</t>
+    <t xml:space="preserve">0.339311152696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160560131073</t>
+    <t xml:space="preserve">0.353160530328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34623584151268</t>
+    <t xml:space="preserve">0.346235811710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386404275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612248420715</t>
+    <t xml:space="preserve">0.311612218618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31438210606575</t>
+    <t xml:space="preserve">0.314382135868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838122367859</t>
+    <t xml:space="preserve">0.290838092565536</t>
   </si>
   <si>
     <t xml:space="preserve">0.258984386920929</t>
@@ -926,46 +926,46 @@
     <t xml:space="preserve">0.278373569250107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139188289642</t>
+    <t xml:space="preserve">0.263139218091965</t>
   </si>
   <si>
     <t xml:space="preserve">0.272833824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754274368286</t>
+    <t xml:space="preserve">0.261754333972931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134934782982</t>
+    <t xml:space="preserve">0.245134994387627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289825558662</t>
+    <t xml:space="preserve">0.249289765954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243749991059303</t>
+    <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298317670822</t>
+    <t xml:space="preserve">0.2852982878685</t>
   </si>
   <si>
     <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448880434036</t>
+    <t xml:space="preserve">0.271448850631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758512973785</t>
+    <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
     <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
     <t xml:space="preserve">0.303302556276321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842390775681</t>
+    <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
     <t xml:space="preserve">0.337926179170609</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">0.377397030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231543302536</t>
+    <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
     <t xml:space="preserve">0.331001430749893</t>
@@ -995,67 +995,67 @@
     <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698156118393</t>
+    <t xml:space="preserve">0.349698215723038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850867986679</t>
+    <t xml:space="preserve">0.344850838184357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691798210144</t>
+    <t xml:space="preserve">0.322691738605499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076741933823</t>
+    <t xml:space="preserve">0.324076652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306794881821</t>
+    <t xml:space="preserve">0.321306854486465</t>
   </si>
   <si>
     <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072503328323</t>
+    <t xml:space="preserve">0.306072443723679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31715202331543</t>
+    <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
     <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762811183929</t>
+    <t xml:space="preserve">0.297762840986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913403749466</t>
+    <t xml:space="preserve">0.283913344144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288068175315857</t>
+    <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524161815643</t>
+    <t xml:space="preserve">0.264524191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294079065323</t>
+    <t xml:space="preserve">0.267294049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369300842285</t>
+    <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909165143967</t>
+    <t xml:space="preserve">0.265909105539322</t>
   </si>
   <si>
     <t xml:space="preserve">0.270063906908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988625526428</t>
+    <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223006486893</t>
+    <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377897262573</t>
+    <t xml:space="preserve">0.296377927064896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28945317864418</t>
+    <t xml:space="preserve">0.289453119039536</t>
   </si>
   <si>
     <t xml:space="preserve">0.429810017347336</t>
@@ -1073,61 +1073,61 @@
     <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485765695572</t>
+    <t xml:space="preserve">0.369485825300217</t>
   </si>
   <si>
     <t xml:space="preserve">0.363453328609467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796551704407</t>
+    <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
     <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880367517471</t>
+    <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847990036011</t>
+    <t xml:space="preserve">0.343847960233688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339843511581</t>
+    <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
     <t xml:space="preserve">0.339323669672012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.352896571159363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34686416387558</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388514041901</t>
+    <t xml:space="preserve">0.351388454437256</t>
   </si>
   <si>
     <t xml:space="preserve">0.336307466030121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799408912659</t>
+    <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
     <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350481748581</t>
+    <t xml:space="preserve">0.437350511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958647727966</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431529760361</t>
+    <t xml:space="preserve">0.452431559562683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444891035556793</t>
+    <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
     <t xml:space="preserve">0.441120713949203</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">0.403418183326721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566843509674</t>
+    <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
     <t xml:space="preserve">0.395877569913864</t>
@@ -1160,28 +1160,28 @@
     <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356106758118</t>
+    <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
     <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993912220001</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437124967575</t>
+    <t xml:space="preserve">0.360437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977678775787</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
     <t xml:space="preserve">0.358929038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316702097654343</t>
+    <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112903118134</t>
+    <t xml:space="preserve">0.300112932920456</t>
   </si>
   <si>
     <t xml:space="preserve">0.30162101984024</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">0.318210154771805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718301296234</t>
+    <t xml:space="preserve">0.319718271493912</t>
   </si>
   <si>
     <t xml:space="preserve">0.324242621660233</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">0.330274999141693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3317831158638</t>
+    <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
     <t xml:space="preserve">0.337815552949905</t>
@@ -1220,148 +1220,148 @@
     <t xml:space="preserve">0.303129136562347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685834407806</t>
+    <t xml:space="preserve">0.313685894012451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734534740448</t>
+    <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
     <t xml:space="preserve">0.317599177360535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322339504957199</t>
+    <t xml:space="preserve">0.322339475154877</t>
   </si>
   <si>
     <t xml:space="preserve">0.314438998699188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319179266691208</t>
+    <t xml:space="preserve">0.31917929649353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820070743561</t>
+    <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400160074234</t>
+    <t xml:space="preserve">0.333400100469589</t>
   </si>
   <si>
     <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32391956448555</t>
+    <t xml:space="preserve">0.323919594287872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31285884976387</t>
+    <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378343582153</t>
+    <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317718267441</t>
+    <t xml:space="preserve">0.292317628860474</t>
   </si>
   <si>
     <t xml:space="preserve">0.30179825425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019117832184</t>
+    <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
     <t xml:space="preserve">0.300218135118484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638045787811</t>
+    <t xml:space="preserve">0.298638075590134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737628936768</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837063074112</t>
+    <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577331066132</t>
+    <t xml:space="preserve">0.287577390670776</t>
   </si>
   <si>
     <t xml:space="preserve">0.279676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096795082092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196348428726</t>
+    <t xml:space="preserve">0.270196288824081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257063150406</t>
+    <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776437759399</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997241735458</t>
+    <t xml:space="preserve">0.285997301340103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477837324142</t>
+    <t xml:space="preserve">0.295477867126465</t>
   </si>
   <si>
     <t xml:space="preserve">0.297057956457138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118611574173</t>
+    <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157450199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040844917297</t>
+    <t xml:space="preserve">0.34604087471962</t>
   </si>
   <si>
     <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720547199249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3413006067276</t>
+    <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980189800262</t>
+    <t xml:space="preserve">0.334980219602585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336560308933258</t>
+    <t xml:space="preserve">0.33656033873558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361261844635</t>
+    <t xml:space="preserve">0.352361291646957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359283685684</t>
+    <t xml:space="preserve">0.295359313488007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944772005081</t>
+    <t xml:space="preserve">0.291944742202759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237456560135</t>
+    <t xml:space="preserve">0.290237426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115629434586</t>
+    <t xml:space="preserve">0.285115659236908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822915077209</t>
+    <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
     <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29877382516861</t>
+    <t xml:space="preserve">0.298773854970932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408343791962</t>
+    <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286516666412</t>
+    <t xml:space="preserve">0.278286457061768</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530200719833</t>
@@ -1370,79 +1370,79 @@
     <t xml:space="preserve">0.279993802309036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164659738541</t>
+    <t xml:space="preserve">0.273164689540863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579201221466</t>
+    <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750148057938</t>
+    <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28170108795166</t>
+    <t xml:space="preserve">0.281701028347015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871975183487</t>
+    <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457374095917</t>
+    <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042862415314</t>
+    <t xml:space="preserve">0.268042832612991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895682096481</t>
+    <t xml:space="preserve">0.303895711898804</t>
   </si>
   <si>
     <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188396453857</t>
+    <t xml:space="preserve">0.302188366651535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602967739105</t>
+    <t xml:space="preserve">0.305602997541428</t>
   </si>
   <si>
     <t xml:space="preserve">0.307310253381729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383020401001</t>
+    <t xml:space="preserve">0.324383050203323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261252880096</t>
+    <t xml:space="preserve">0.319261163473129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017539024353</t>
+    <t xml:space="preserve">0.309017509222031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139366149902</t>
+    <t xml:space="preserve">0.314139395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432110309601</t>
+    <t xml:space="preserve">0.312432140111923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724824666977</t>
+    <t xml:space="preserve">0.310724794864655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310288965702057</t>
+    <t xml:space="preserve">0.310289025306702</t>
   </si>
   <si>
     <t xml:space="preserve">0.299829840660095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343445777893</t>
+    <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
     <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289370626211166</t>
+    <t xml:space="preserve">0.289370596408844</t>
   </si>
   <si>
     <t xml:space="preserve">0.287627428770065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086673021317</t>
+    <t xml:space="preserve">0.298086643218994</t>
   </si>
   <si>
     <t xml:space="preserve">0.313560366630554</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306433975696564</t>
+    <t xml:space="preserve">0.306434035301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089197397232</t>
+    <t xml:space="preserve">0.301089227199554</t>
   </si>
   <si>
     <t xml:space="preserve">0.286836475133896</t>
@@ -1466,19 +1466,19 @@
     <t xml:space="preserve">0.288618087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399670600891</t>
+    <t xml:space="preserve">0.290399640798569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307614564896</t>
+    <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962895870209</t>
+    <t xml:space="preserve">0.293962836265564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054922103882</t>
+    <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273309469223</t>
+    <t xml:space="preserve">0.283273279666901</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710114002228</t>
@@ -1487,67 +1487,67 @@
     <t xml:space="preserve">0.281491726636887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292181253433228</t>
+    <t xml:space="preserve">0.29218128323555</t>
   </si>
   <si>
     <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902150630951</t>
   </si>
   <si>
     <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291725426912308</t>
+    <t xml:space="preserve">0.291725397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488390684128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308134973049164</t>
+    <t xml:space="preserve">0.308135002851486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781525611877</t>
+    <t xml:space="preserve">0.311781585216522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317251414060593</t>
+    <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191131353378</t>
+    <t xml:space="preserve">0.328191101551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.331837683916092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660960197449</t>
+    <t xml:space="preserve">0.333660989999771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897966623306</t>
+    <t xml:space="preserve">0.320897936820984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324544548988342</t>
+    <t xml:space="preserve">0.32454451918602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158191680908</t>
+    <t xml:space="preserve">0.324158161878586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32974711060524</t>
+    <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610083580017</t>
+    <t xml:space="preserve">0.331610113382339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021134853363</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
     <t xml:space="preserve">0.320432215929031</t>
@@ -1571,28 +1571,28 @@
     <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473116159439</t>
+    <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391405105591</t>
+    <t xml:space="preserve">0.307391375303268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
     <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344650954008102</t>
+    <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199002504349</t>
+    <t xml:space="preserve">0.337199032306671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376899957657</t>
+    <t xml:space="preserve">0.348376929759979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732605457306</t>
+    <t xml:space="preserve">0.370732635259628</t>
   </si>
   <si>
     <t xml:space="preserve">0.398677289485931</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540292263031</t>
+    <t xml:space="preserve">0.400540322065353</t>
   </si>
   <si>
     <t xml:space="preserve">0.3912253677845</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362454414368</t>
+    <t xml:space="preserve">0.389362424612045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458581209183</t>
+    <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
     <t xml:space="preserve">0.37632155418396</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">0.372595608234406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363280713558197</t>
+    <t xml:space="preserve">0.363280743360519</t>
   </si>
   <si>
     <t xml:space="preserve">0.367006689310074</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">0.378184527158737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951373338699</t>
+    <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170202970505</t>
+    <t xml:space="preserve">0.398170232772827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274209022522</t>
+    <t xml:space="preserve">0.396274149417877</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403858363628387</t>
+    <t xml:space="preserve">0.40385839343071</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097760915756</t>
+    <t xml:space="preserve">0.409097731113434</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605693340302</t>
+    <t xml:space="preserve">0.422605663537979</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -68211,16 +68211,16 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6778587963</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>56000</v>
+        <v>60000</v>
       </c>
       <c r="C2544" t="n">
         <v>0.550000011920929</v>
       </c>
       <c r="D2544" t="n">
-        <v>0.540000021457672</v>
+        <v>0.524999976158142</v>
       </c>
       <c r="E2544" t="n">
         <v>0.550000011920929</v>
@@ -68232,6 +68232,32 @@
         <v>580</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6910185185</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622867584229</t>
+    <t xml:space="preserve">0.176622897386551</t>
   </si>
   <si>
     <t xml:space="preserve">0.172851577401161</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">0.171594485640526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051860570908</t>
+    <t xml:space="preserve">0.164051845669746</t>
   </si>
   <si>
     <t xml:space="preserve">0.169708833098412</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309652805328</t>
+    <t xml:space="preserve">0.14330966770649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783730506897</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195320248604</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789439678192</t>
+    <t xml:space="preserve">0.150789424777031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146452397108078</t>
+    <t xml:space="preserve">0.1464524269104</t>
   </si>
   <si>
     <t xml:space="preserve">0.139852628111839</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.139538362622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915496110916</t>
+    <t xml:space="preserve">0.139915481209755</t>
   </si>
   <si>
     <t xml:space="preserve">0.142052575945854</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337378978729</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817456483841</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
     <t xml:space="preserve">0.163423299789429</t>
@@ -113,46 +113,46 @@
     <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623597860336</t>
+    <t xml:space="preserve">0.154623612761497</t>
   </si>
   <si>
     <t xml:space="preserve">0.149595186114311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692115426064</t>
+    <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909131169319</t>
+    <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960610628128</t>
+    <t xml:space="preserve">0.158960580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314296364784</t>
+    <t xml:space="preserve">0.177314281463623</t>
   </si>
   <si>
     <t xml:space="preserve">0.177251443266869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965939760208</t>
+    <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937528014183</t>
+    <t xml:space="preserve">0.165937498211861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565358519554</t>
+    <t xml:space="preserve">0.188565373420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1926509141922</t>
+    <t xml:space="preserve">0.192650943994522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708102822304</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
     <t xml:space="preserve">0.184165522456169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651279330254</t>
+    <t xml:space="preserve">0.181651294231415</t>
   </si>
   <si>
     <t xml:space="preserve">0.201136380434036</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073527336121</t>
+    <t xml:space="preserve">0.201073542237282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19673652946949</t>
+    <t xml:space="preserve">0.196736514568329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222301244736</t>
+    <t xml:space="preserve">0.194222316145897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137095808983</t>
+    <t xml:space="preserve">0.179137080907822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279855012894</t>
+    <t xml:space="preserve">0.182279825210571</t>
   </si>
   <si>
     <t xml:space="preserve">0.16983450949192</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606544852257</t>
+    <t xml:space="preserve">0.151606529951096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566073894501</t>
+    <t xml:space="preserve">0.166566044092178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074943184853</t>
+    <t xml:space="preserve">0.157074958086014</t>
   </si>
   <si>
     <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15399506688118</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640650868416</t>
@@ -206,67 +206,67 @@
     <t xml:space="preserve">0.186051160097122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936827540398</t>
+    <t xml:space="preserve">0.187936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18353696167469</t>
+    <t xml:space="preserve">0.183536946773529</t>
   </si>
   <si>
     <t xml:space="preserve">0.181714132428169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194619774818</t>
+    <t xml:space="preserve">0.16719463467598</t>
   </si>
   <si>
     <t xml:space="preserve">0.160280555486679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080942988396</t>
+    <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480838656425</t>
+    <t xml:space="preserve">0.151480823755264</t>
   </si>
   <si>
     <t xml:space="preserve">0.148338094353676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566759467125</t>
+    <t xml:space="preserve">0.144566789269447</t>
   </si>
   <si>
     <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183275938034</t>
+    <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651629567146</t>
+    <t xml:space="preserve">0.17065167427063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223031520844</t>
+    <t xml:space="preserve">0.17222298681736</t>
   </si>
   <si>
     <t xml:space="preserve">0.182594135403633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507789850235</t>
+    <t xml:space="preserve">0.200507834553719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593740463257</t>
+    <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131386637688</t>
+    <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010629534721</t>
+    <t xml:space="preserve">0.201010689139366</t>
   </si>
   <si>
     <t xml:space="preserve">0.194850891828537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770955920219</t>
+    <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
     <t xml:space="preserve">0.199879303574562</t>
@@ -275,118 +275,118 @@
     <t xml:space="preserve">0.213078811764717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787323355675</t>
+    <t xml:space="preserve">0.216787308454514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563897967339</t>
+    <t xml:space="preserve">0.232563927769661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220885396004</t>
+    <t xml:space="preserve">0.238220915198326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420527696609</t>
+    <t xml:space="preserve">0.251420468091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134249210358</t>
+    <t xml:space="preserve">0.267134219408035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305390357971</t>
+    <t xml:space="preserve">0.275305420160294</t>
   </si>
   <si>
     <t xml:space="preserve">0.290390640497208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561811447144</t>
+    <t xml:space="preserve">0.298561751842499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705986499786</t>
+    <t xml:space="preserve">0.257705956697464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157376527786</t>
+    <t xml:space="preserve">0.260157316923141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250226259231567</t>
+    <t xml:space="preserve">0.2502261698246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163376331329</t>
+    <t xml:space="preserve">0.250163406133652</t>
   </si>
   <si>
     <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249297142029</t>
+    <t xml:space="preserve">0.243249341845512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375048041344</t>
+    <t xml:space="preserve">0.243375018239021</t>
   </si>
   <si>
     <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821004629135</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21056467294693</t>
+    <t xml:space="preserve">0.210564658045769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20691904425621</t>
+    <t xml:space="preserve">0.206919059157372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821749806404</t>
+    <t xml:space="preserve">0.211821779608727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741843700409</t>
+    <t xml:space="preserve">0.20874185860157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592369318008</t>
+    <t xml:space="preserve">0.237592309713364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134934782982</t>
+    <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
     <t xml:space="preserve">0.230803996324539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535530924797</t>
+    <t xml:space="preserve">0.227535516023636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706642270088</t>
+    <t xml:space="preserve">0.235706731677055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278394460678</t>
+    <t xml:space="preserve">0.226278454065323</t>
   </si>
   <si>
     <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850161552429</t>
+    <t xml:space="preserve">0.216850146651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381427884102</t>
+    <t xml:space="preserve">0.222381457686424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141664862633</t>
+    <t xml:space="preserve">0.213141679763794</t>
   </si>
   <si>
     <t xml:space="preserve">0.201199233531952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279139637947</t>
+    <t xml:space="preserve">0.204279124736786</t>
   </si>
   <si>
     <t xml:space="preserve">0.20679335296154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164792180061</t>
+    <t xml:space="preserve">0.2061647772789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421869039536</t>
+    <t xml:space="preserve">0.20742192864418</t>
   </si>
   <si>
     <t xml:space="preserve">0.208804696798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947441101074</t>
+    <t xml:space="preserve">0.211947470903397</t>
   </si>
   <si>
     <t xml:space="preserve">0.225649878382683</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">0.219867184758186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810055732727</t>
+    <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
     <t xml:space="preserve">0.229484051465988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386742115021</t>
+    <t xml:space="preserve">0.23438672721386</t>
   </si>
   <si>
     <t xml:space="preserve">0.224518492817879</t>
@@ -410,100 +410,100 @@
     <t xml:space="preserve">0.219992890954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741478562355</t>
+    <t xml:space="preserve">0.219741493463516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216913029551506</t>
+    <t xml:space="preserve">0.216912984848022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306821107864</t>
+    <t xml:space="preserve">0.231306836009026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038750648499</t>
+    <t xml:space="preserve">0.217038705945015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324239253998</t>
+    <t xml:space="preserve">0.223324283957481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178953886032</t>
+    <t xml:space="preserve">0.297178983688354</t>
   </si>
   <si>
     <t xml:space="preserve">0.351988673210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127795934677</t>
+    <t xml:space="preserve">0.465127855539322</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070361375809</t>
+    <t xml:space="preserve">0.477070420980453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843007802963</t>
+    <t xml:space="preserve">0.43684309720993</t>
   </si>
   <si>
     <t xml:space="preserve">0.422072142362595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987242460251</t>
+    <t xml:space="preserve">0.395987212657928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559710025787</t>
+    <t xml:space="preserve">0.364559650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215236902237</t>
+    <t xml:space="preserve">0.414215266704559</t>
   </si>
   <si>
     <t xml:space="preserve">0.367388159036636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987972736359</t>
+    <t xml:space="preserve">0.373988002538681</t>
   </si>
   <si>
     <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3259037733078</t>
+    <t xml:space="preserve">0.325903803110123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904123544693</t>
+    <t xml:space="preserve">0.314904153347015</t>
   </si>
   <si>
     <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389239549637</t>
+    <t xml:space="preserve">0.334389269351959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818262338638</t>
+    <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
     <t xml:space="preserve">0.348845899105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303259134293</t>
+    <t xml:space="preserve">0.34130334854126</t>
   </si>
   <si>
     <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361222743988</t>
+    <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189641952515</t>
+    <t xml:space="preserve">0.32118958234787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132147789001</t>
+    <t xml:space="preserve">0.333132088184357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989314079285</t>
+    <t xml:space="preserve">0.329989373683929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418396472931</t>
+    <t xml:space="preserve">0.317418336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332416057587</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
     <t xml:space="preserve">0.314275592565536</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">0.334703534841537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046867847443</t>
+    <t xml:space="preserve">0.318046897649765</t>
   </si>
   <si>
     <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417927026749</t>
+    <t xml:space="preserve">0.328418016433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075294494629</t>
+    <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103721141815</t>
+    <t xml:space="preserve">0.328103691339493</t>
   </si>
   <si>
     <t xml:space="preserve">0.301704555749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31050431728363</t>
+    <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311070024967194</t>
+    <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
     <t xml:space="preserve">0.320561110973358</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274191617966</t>
+    <t xml:space="preserve">0.358274161815643</t>
   </si>
   <si>
     <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046167373657</t>
+    <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304049015045</t>
+    <t xml:space="preserve">0.3193039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846279144287</t>
+    <t xml:space="preserve">0.337846249341965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589887857437</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789455652237</t>
@@ -569,79 +569,79 @@
     <t xml:space="preserve">0.389701783657074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588077068329</t>
+    <t xml:space="preserve">0.369588166475296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959605693817</t>
+    <t xml:space="preserve">0.36895951628685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216578245163</t>
+    <t xml:space="preserve">0.370216637849808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616794347763</t>
+    <t xml:space="preserve">0.363616913557053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845168828964</t>
+    <t xml:space="preserve">0.370845198631287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074623823166</t>
+    <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788695573807</t>
+    <t xml:space="preserve">0.349788784980774</t>
   </si>
   <si>
     <t xml:space="preserve">0.354502886533737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36707392334938</t>
+    <t xml:space="preserve">0.367073893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758957386017</t>
+    <t xml:space="preserve">0.388758897781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587466001511</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
     <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130717039108</t>
+    <t xml:space="preserve">0.377130746841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187480926514</t>
+    <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444952726364</t>
+    <t xml:space="preserve">0.377444982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929688692093</t>
+    <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843738079071</t>
+    <t xml:space="preserve">0.414843857288361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215937376022</t>
+    <t xml:space="preserve">0.392215967178345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376816391944885</t>
+    <t xml:space="preserve">0.37681645154953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386559009552002</t>
+    <t xml:space="preserve">0.38655897974968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413284540176</t>
+    <t xml:space="preserve">0.471413463354111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357280731201</t>
+    <t xml:space="preserve">0.439357310533524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556788921356</t>
+    <t xml:space="preserve">0.452556908130646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700323104858</t>
+    <t xml:space="preserve">0.433700293302536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100218772888</t>
+    <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
     <t xml:space="preserve">0.446271300315857</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386467456818</t>
+    <t xml:space="preserve">0.422386288642883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900621175766</t>
+    <t xml:space="preserve">0.424900650978088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42112934589386</t>
+    <t xml:space="preserve">0.421129316091537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815400838852</t>
+    <t xml:space="preserve">0.409815430641174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044125556946</t>
+    <t xml:space="preserve">0.406044095754623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558279275894</t>
+    <t xml:space="preserve">0.408558249473572</t>
   </si>
   <si>
     <t xml:space="preserve">0.41358670592308</t>
@@ -674,52 +674,52 @@
     <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443231344223</t>
+    <t xml:space="preserve">0.432443171739578</t>
   </si>
   <si>
     <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613642215729</t>
+    <t xml:space="preserve">0.462613672018051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414864301682</t>
+    <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
     <t xml:space="preserve">0.399758607149124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615132570267</t>
+    <t xml:space="preserve">0.418615072965622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643499612808</t>
+    <t xml:space="preserve">0.423643559217453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41107240319252</t>
+    <t xml:space="preserve">0.411072432994843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501425981522</t>
+    <t xml:space="preserve">0.398501366376877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786944389343</t>
+    <t xml:space="preserve">0.404787003993988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159113883972</t>
+    <t xml:space="preserve">0.382159054279327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416205644608</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444602489471</t>
+    <t xml:space="preserve">0.388444632291794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529912233353</t>
+    <t xml:space="preserve">0.40352988243103</t>
   </si>
   <si>
     <t xml:space="preserve">0.431186079978943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41987219452858</t>
+    <t xml:space="preserve">0.419872224330902</t>
   </si>
   <si>
     <t xml:space="preserve">0.407301187515259</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">0.394730180501938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329584360123</t>
+    <t xml:space="preserve">0.4123295545578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40101557970047</t>
+    <t xml:space="preserve">0.401015669107437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100859642029</t>
+    <t xml:space="preserve">0.416100889444351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045496702194</t>
+    <t xml:space="preserve">0.362045407295227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816801786423</t>
+    <t xml:space="preserve">0.3658167719841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302558660507</t>
+    <t xml:space="preserve">0.36330258846283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674757957458</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360812902451</t>
+    <t xml:space="preserve">0.329360842704773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531223773956</t>
+    <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017070055008</t>
+    <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446063041687</t>
+    <t xml:space="preserve">0.34444597363472</t>
   </si>
   <si>
     <t xml:space="preserve">0.336903423070908</t>
@@ -773,79 +773,79 @@
     <t xml:space="preserve">0.372102320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930418968201</t>
+    <t xml:space="preserve">0.385930389165878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245735168457</t>
+    <t xml:space="preserve">0.353245794773102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788345336914</t>
+    <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387778997421</t>
+    <t xml:space="preserve">0.378387838602066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873655080795</t>
+    <t xml:space="preserve">0.375873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359322547913</t>
+    <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673267602921</t>
+    <t xml:space="preserve">0.384673357009888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958815813065</t>
+    <t xml:space="preserve">0.390958786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39347305893898</t>
+    <t xml:space="preserve">0.393473029136658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272000789642</t>
+    <t xml:space="preserve">0.424272030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557548999786</t>
+    <t xml:space="preserve">0.430557519197464</t>
   </si>
   <si>
     <t xml:space="preserve">0.449414074420929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699622631073</t>
+    <t xml:space="preserve">0.455699652433395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46395605802536</t>
+    <t xml:space="preserve">0.463955998420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181872367859</t>
+    <t xml:space="preserve">0.443181782960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332464933395</t>
+    <t xml:space="preserve">0.429332405328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415482968091965</t>
+    <t xml:space="preserve">0.415483057498932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42587012052536</t>
+    <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257123947144</t>
+    <t xml:space="preserve">0.436257094144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719468355179</t>
+    <t xml:space="preserve">0.439719498157501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794868946075</t>
+    <t xml:space="preserve">0.432794749736786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4189453125</t>
+    <t xml:space="preserve">0.418945372104645</t>
   </si>
   <si>
     <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020653486252</t>
+    <t xml:space="preserve">0.412020593881607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784153223038</t>
+    <t xml:space="preserve">0.387784123420715</t>
   </si>
   <si>
     <t xml:space="preserve">0.391246557235718</t>
@@ -854,103 +854,103 @@
     <t xml:space="preserve">0.405095875263214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
+    <t xml:space="preserve">0.422407686710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644216775894</t>
+    <t xml:space="preserve">0.446644186973572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106561183929</t>
+    <t xml:space="preserve">0.450106501579285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45703125</t>
+    <t xml:space="preserve">0.457031399011612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45356884598732</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171186447144</t>
+    <t xml:space="preserve">0.398171216249466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708871841431</t>
+    <t xml:space="preserve">0.394708812236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859375</t>
+    <t xml:space="preserve">0.380859404802322</t>
   </si>
   <si>
     <t xml:space="preserve">0.373934715986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360085219144821</t>
+    <t xml:space="preserve">0.360085189342499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472341775894</t>
+    <t xml:space="preserve">0.370472371578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38432177901268</t>
+    <t xml:space="preserve">0.384321749210358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009967565536</t>
+    <t xml:space="preserve">0.367009907960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696036815643</t>
+    <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311152696609</t>
+    <t xml:space="preserve">0.339311093091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160530328751</t>
+    <t xml:space="preserve">0.353160500526428</t>
   </si>
   <si>
     <t xml:space="preserve">0.346235811710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386404275894</t>
+    <t xml:space="preserve">0.332386344671249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612218618393</t>
+    <t xml:space="preserve">0.311612159013748</t>
   </si>
   <si>
     <t xml:space="preserve">0.314382135868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838092565536</t>
+    <t xml:space="preserve">0.290838122367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984386920929</t>
+    <t xml:space="preserve">0.258984416723251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373569250107</t>
+    <t xml:space="preserve">0.278373628854752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.272833853960037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754333972931</t>
+    <t xml:space="preserve">0.261754274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134994387627</t>
+    <t xml:space="preserve">0.245134979486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289765954018</t>
+    <t xml:space="preserve">0.249289810657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750005960464</t>
+    <t xml:space="preserve">0.243750020861626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2852982878685</t>
+    <t xml:space="preserve">0.285298347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683261394501</t>
+    <t xml:space="preserve">0.286683291196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448850631714</t>
+    <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
     <t xml:space="preserve">0.279758542776108</t>
@@ -959,31 +959,31 @@
     <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992923736572</t>
+    <t xml:space="preserve">0.29499289393425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302556276321</t>
+    <t xml:space="preserve">0.303302586078644</t>
   </si>
   <si>
     <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926179170609</t>
+    <t xml:space="preserve">0.337926119565964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461685657501</t>
+    <t xml:space="preserve">0.325461626052856</t>
   </si>
   <si>
     <t xml:space="preserve">0.319921910762787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465954065323</t>
+    <t xml:space="preserve">0.343465924263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547563552856</t>
+    <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397030591965</t>
+    <t xml:space="preserve">0.377397000789642</t>
   </si>
   <si>
     <t xml:space="preserve">0.328231573104858</t>
@@ -992,25 +992,25 @@
     <t xml:space="preserve">0.331001430749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336541205644608</t>
+    <t xml:space="preserve">0.33654123544693</t>
   </si>
   <si>
     <t xml:space="preserve">0.349698215723038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850838184357</t>
+    <t xml:space="preserve">0.344850867986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691738605499</t>
+    <t xml:space="preserve">0.322691768407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076652526855</t>
+    <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306854486465</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536937236786</t>
+    <t xml:space="preserve">0.318536967039108</t>
   </si>
   <si>
     <t xml:space="preserve">0.306072443723679</t>
@@ -1019,31 +1019,31 @@
     <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687529802322</t>
+    <t xml:space="preserve">0.3046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.297762840986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913344144821</t>
+    <t xml:space="preserve">0.283913373947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288068205118179</t>
+    <t xml:space="preserve">0.288068234920502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524191617966</t>
+    <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294049263</t>
+    <t xml:space="preserve">0.267294019460678</t>
   </si>
   <si>
     <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909105539322</t>
+    <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063906908035</t>
+    <t xml:space="preserve">0.270063936710358</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
@@ -1052,43 +1052,43 @@
     <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377927064896</t>
+    <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453119039536</t>
+    <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429810017347336</t>
+    <t xml:space="preserve">0.429809957742691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647861719131</t>
+    <t xml:space="preserve">0.399647802114487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337045907974</t>
+    <t xml:space="preserve">0.388337105512619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026319503784</t>
+    <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945241689682</t>
+    <t xml:space="preserve">0.36194521188736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485825300217</t>
+    <t xml:space="preserve">0.369485765695572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453328609467</t>
+    <t xml:space="preserve">0.363453358411789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374010056257248</t>
+    <t xml:space="preserve">0.37401008605957</t>
   </si>
   <si>
     <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880397319794</t>
+    <t xml:space="preserve">0.349880367517471</t>
   </si>
   <si>
     <t xml:space="preserve">0.343847960233688</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323669672012</t>
+    <t xml:space="preserve">0.339323580265045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896571159363</t>
+    <t xml:space="preserve">0.352896600961685</t>
   </si>
   <si>
     <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388454437256</t>
+    <t xml:space="preserve">0.351388484239578</t>
   </si>
   <si>
     <t xml:space="preserve">0.336307466030121</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">0.437350511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958677530289</t>
+    <t xml:space="preserve">0.410958617925644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431559562683</t>
+    <t xml:space="preserve">0.452431619167328</t>
   </si>
   <si>
     <t xml:space="preserve">0.444891005754471</t>
@@ -1133,31 +1133,31 @@
     <t xml:space="preserve">0.441120713949203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728909730911</t>
+    <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
     <t xml:space="preserve">0.403418183326721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107307910919</t>
+    <t xml:space="preserve">0.392107278108597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566813707352</t>
+    <t xml:space="preserve">0.384566783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877569913864</t>
+    <t xml:space="preserve">0.395877599716187</t>
   </si>
   <si>
     <t xml:space="preserve">0.407188415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501969337463</t>
+    <t xml:space="preserve">0.372501999139786</t>
   </si>
   <si>
     <t xml:space="preserve">0.36646956205368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404717683792</t>
+    <t xml:space="preserve">0.354404658079147</t>
   </si>
   <si>
     <t xml:space="preserve">0.345356076955795</t>
@@ -1169,46 +1169,46 @@
     <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437095165253</t>
+    <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977648973465</t>
+    <t xml:space="preserve">0.367977619171143</t>
   </si>
   <si>
     <t xml:space="preserve">0.358929038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31670206785202</t>
+    <t xml:space="preserve">0.316702127456665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112932920456</t>
+    <t xml:space="preserve">0.300112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30162101984024</t>
+    <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210154771805</t>
+    <t xml:space="preserve">0.318210184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718331098557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324242621660233</t>
+    <t xml:space="preserve">0.324242651462555</t>
   </si>
   <si>
     <t xml:space="preserve">0.327258825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330274999141693</t>
+    <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783145666122</t>
+    <t xml:space="preserve">0.3317831158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337815552949905</t>
+    <t xml:space="preserve">0.337815523147583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766942024231</t>
+    <t xml:space="preserve">0.328766912221909</t>
   </si>
   <si>
     <t xml:space="preserve">0.309161573648453</t>
@@ -1217,49 +1217,49 @@
     <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129136562347</t>
+    <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685894012451</t>
+    <t xml:space="preserve">0.313685923814774</t>
   </si>
   <si>
     <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599177360535</t>
+    <t xml:space="preserve">0.317599207162857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322339475154877</t>
+    <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314439028501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31917929649353</t>
+    <t xml:space="preserve">0.319179266691208</t>
   </si>
   <si>
     <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400100469589</t>
+    <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759385824203</t>
+    <t xml:space="preserve">0.320759356021881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919594287872</t>
+    <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
     <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378313779831</t>
+    <t xml:space="preserve">0.303378343582153</t>
   </si>
   <si>
     <t xml:space="preserve">0.292317628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30179825425148</t>
+    <t xml:space="preserve">0.301798194646835</t>
   </si>
   <si>
     <t xml:space="preserve">0.316019088029861</t>
@@ -1268,46 +1268,46 @@
     <t xml:space="preserve">0.300218135118484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638075590134</t>
+    <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737569332123</t>
+    <t xml:space="preserve">0.2907375395298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837092876434</t>
+    <t xml:space="preserve">0.282837063074112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577390670776</t>
+    <t xml:space="preserve">0.287577301263809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676914215088</t>
+    <t xml:space="preserve">0.279676884412766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516705751419</t>
+    <t xml:space="preserve">0.276516675949097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096795082092</t>
+    <t xml:space="preserve">0.27809676527977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196288824081</t>
+    <t xml:space="preserve">0.270196318626404</t>
   </si>
   <si>
     <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776437759399</t>
+    <t xml:space="preserve">0.271776407957077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417152404785</t>
+    <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997301340103</t>
+    <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477867126465</t>
+    <t xml:space="preserve">0.295477837324142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057956457138</t>
+    <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
     <t xml:space="preserve">0.308118581771851</t>
@@ -1316,52 +1316,52 @@
     <t xml:space="preserve">0.289157450199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34604087471962</t>
+    <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140428066254</t>
+    <t xml:space="preserve">0.338140457868576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720547199249</t>
+    <t xml:space="preserve">0.339720487594604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341300636529922</t>
+    <t xml:space="preserve">0.3413006067276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980219602585</t>
+    <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560279130936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.35236132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359313488007</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944742202759</t>
+    <t xml:space="preserve">0.291944772005081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237426757812</t>
+    <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115659236908</t>
+    <t xml:space="preserve">0.285115629434586</t>
   </si>
   <si>
     <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481140613556</t>
+    <t xml:space="preserve">0.300481110811234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298773854970932</t>
+    <t xml:space="preserve">0.29877382516861</t>
   </si>
   <si>
     <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286457061768</t>
+    <t xml:space="preserve">0.278286516666412</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530200719833</t>
@@ -1370,46 +1370,46 @@
     <t xml:space="preserve">0.279993802309036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164689540863</t>
+    <t xml:space="preserve">0.273164629936218</t>
   </si>
   <si>
     <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750118255615</t>
+    <t xml:space="preserve">0.269750148057938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701028347015</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871945381165</t>
+    <t xml:space="preserve">0.274871975183487</t>
   </si>
   <si>
     <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042832612991</t>
+    <t xml:space="preserve">0.268042802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895711898804</t>
+    <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293652027845383</t>
+    <t xml:space="preserve">0.29365199804306</t>
   </si>
   <si>
     <t xml:space="preserve">0.302188366651535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602997541428</t>
+    <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310253381729</t>
+    <t xml:space="preserve">0.307310312986374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383050203323</t>
+    <t xml:space="preserve">0.324383020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261163473129</t>
+    <t xml:space="preserve">0.319261193275452</t>
   </si>
   <si>
     <t xml:space="preserve">0.309017509222031</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">0.314139395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432140111923</t>
+    <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
     <t xml:space="preserve">0.310724794864655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310289025306702</t>
+    <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829840660095</t>
+    <t xml:space="preserve">0.29982978105545</t>
   </si>
   <si>
     <t xml:space="preserve">0.296343415975571</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289370596408844</t>
+    <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627428770065</t>
+    <t xml:space="preserve">0.287627458572388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086643218994</t>
+    <t xml:space="preserve">0.298086673021317</t>
   </si>
   <si>
     <t xml:space="preserve">0.313560366630554</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306434035301208</t>
+    <t xml:space="preserve">0.306434005498886</t>
   </si>
   <si>
     <t xml:space="preserve">0.301089227199554</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">0.286836475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618087768555</t>
+    <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399640798569</t>
+    <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307644367218</t>
+    <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962836265564</t>
+    <t xml:space="preserve">0.293962806463242</t>
   </si>
   <si>
     <t xml:space="preserve">0.285054892301559</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491726636887</t>
+    <t xml:space="preserve">0.281491696834564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29218128323555</t>
+    <t xml:space="preserve">0.292181223630905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295371979475021</t>
+    <t xml:space="preserve">0.295372009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902150630951</t>
+    <t xml:space="preserve">0.289902120828629</t>
   </si>
   <si>
     <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291725397109985</t>
+    <t xml:space="preserve">0.29172545671463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304488390684128</t>
+    <t xml:space="preserve">0.30448842048645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308135002851486</t>
+    <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781585216522</t>
+    <t xml:space="preserve">0.3117815554142</t>
   </si>
   <si>
     <t xml:space="preserve">0.31725138425827</t>
@@ -1523,115 +1523,115 @@
     <t xml:space="preserve">0.328191101551056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331837683916092</t>
+    <t xml:space="preserve">0.33183765411377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660989999771</t>
+    <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897936820984</t>
+    <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32454451918602</t>
+    <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158161878586</t>
+    <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322295188903809</t>
+    <t xml:space="preserve">0.322295218706131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610113382339</t>
+    <t xml:space="preserve">0.331610053777695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021164655685</t>
+    <t xml:space="preserve">0.326021194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432215929031</t>
+    <t xml:space="preserve">0.320432245731354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117351055145</t>
+    <t xml:space="preserve">0.311117321252823</t>
   </si>
   <si>
     <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335336059331894</t>
+    <t xml:space="preserve">0.335336029529572</t>
   </si>
   <si>
     <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569242954254</t>
+    <t xml:space="preserve">0.318569272756577</t>
   </si>
   <si>
     <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473086357117</t>
+    <t xml:space="preserve">0.333473056554794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391375303268</t>
+    <t xml:space="preserve">0.307391405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802426576614</t>
+    <t xml:space="preserve">0.301802456378937</t>
   </si>
   <si>
     <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34465092420578</t>
+    <t xml:space="preserve">0.344650954008102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199032306671</t>
+    <t xml:space="preserve">0.337199002504349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376929759979</t>
+    <t xml:space="preserve">0.348376899957657</t>
   </si>
   <si>
     <t xml:space="preserve">0.370732635259628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677289485931</t>
+    <t xml:space="preserve">0.398677319288254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170051813126</t>
+    <t xml:space="preserve">0.419170081615448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40799218416214</t>
+    <t xml:space="preserve">0.407992213964462</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409855157136917</t>
+    <t xml:space="preserve">0.40985518693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540322065353</t>
+    <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
     <t xml:space="preserve">0.3912253677845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393088340759277</t>
+    <t xml:space="preserve">0.3930883705616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362424612045</t>
+    <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
     <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37632155418396</t>
+    <t xml:space="preserve">0.376321583986282</t>
   </si>
   <si>
     <t xml:space="preserve">0.372595608234406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363280743360519</t>
+    <t xml:space="preserve">0.363280713558197</t>
   </si>
   <si>
     <t xml:space="preserve">0.367006689310074</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407650470733643</t>
+    <t xml:space="preserve">0.407650500535965</t>
   </si>
   <si>
     <t xml:space="preserve">0.392482101917267</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170232772827</t>
+    <t xml:space="preserve">0.398170202970505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274149417877</t>
+    <t xml:space="preserve">0.396274209022522</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097731113434</t>
+    <t xml:space="preserve">0.409097760915756</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605663537979</t>
+    <t xml:space="preserve">0.422605693340302</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -68237,7 +68237,7 @@
     </row>
     <row r="2545">
       <c r="A2545" s="1" t="n">
-        <v>46029.6910185185</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2545" t="n">
         <v>28000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994336605072</t>
+    <t xml:space="preserve">0.175994321703911</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622897386551</t>
+    <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851577401161</t>
+    <t xml:space="preserve">0.172851592302322</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594485640526</t>
@@ -56,46 +56,46 @@
     <t xml:space="preserve">0.164051845669746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169708833098412</t>
+    <t xml:space="preserve">0.16970881819725</t>
   </si>
   <si>
     <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14330966770649</t>
+    <t xml:space="preserve">0.143309652805328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783730506897</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195320248604</t>
+    <t xml:space="preserve">0.145195335149765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737945318222</t>
+    <t xml:space="preserve">0.152737930417061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15336649119854</t>
+    <t xml:space="preserve">0.153366476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.15078940987587</t>
   </si>
   <si>
     <t xml:space="preserve">0.1464524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852628111839</t>
+    <t xml:space="preserve">0.139852657914162</t>
   </si>
   <si>
     <t xml:space="preserve">0.139538362622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915481209755</t>
+    <t xml:space="preserve">0.139915511012077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052575945854</t>
+    <t xml:space="preserve">0.142052546143532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909801840782</t>
+    <t xml:space="preserve">0.138909831643105</t>
   </si>
   <si>
     <t xml:space="preserve">0.15110370516777</t>
@@ -107,118 +107,118 @@
     <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423299789429</t>
+    <t xml:space="preserve">0.163423284888268</t>
   </si>
   <si>
     <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623612761497</t>
+    <t xml:space="preserve">0.154623597860336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595186114311</t>
+    <t xml:space="preserve">0.14959517121315</t>
   </si>
   <si>
     <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909116268158</t>
+    <t xml:space="preserve">0.160909101366997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960580825806</t>
+    <t xml:space="preserve">0.158960610628128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314281463623</t>
+    <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
     <t xml:space="preserve">0.177251443266869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965924859047</t>
+    <t xml:space="preserve">0.170965939760208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937498211861</t>
+    <t xml:space="preserve">0.165937483310699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565373420715</t>
+    <t xml:space="preserve">0.188565343618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650943994522</t>
+    <t xml:space="preserve">0.1926509141922</t>
   </si>
   <si>
     <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165522456169</t>
+    <t xml:space="preserve">0.18416553735733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651294231415</t>
+    <t xml:space="preserve">0.181651309132576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136380434036</t>
+    <t xml:space="preserve">0.201136365532875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678990602493</t>
+    <t xml:space="preserve">0.208678960800171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073542237282</t>
+    <t xml:space="preserve">0.201073512434959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736514568329</t>
+    <t xml:space="preserve">0.196736499667168</t>
   </si>
   <si>
     <t xml:space="preserve">0.194222316145897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137080907822</t>
+    <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
     <t xml:space="preserve">0.182279825210571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16983450949192</t>
+    <t xml:space="preserve">0.169834524393082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451711535454</t>
+    <t xml:space="preserve">0.168451696634293</t>
   </si>
   <si>
     <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606529951096</t>
+    <t xml:space="preserve">0.151606544852257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566044092178</t>
+    <t xml:space="preserve">0.16656605899334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074958086014</t>
+    <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
     <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995051980019</t>
+    <t xml:space="preserve">0.15399506688118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640650868416</t>
+    <t xml:space="preserve">0.157640635967255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051160097122</t>
+    <t xml:space="preserve">0.186051115393639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936782836914</t>
+    <t xml:space="preserve">0.187936797738075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536946773529</t>
+    <t xml:space="preserve">0.183536931872368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714132428169</t>
+    <t xml:space="preserve">0.18171414732933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16719463467598</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160280555486679</t>
+    <t xml:space="preserve">0.16028057038784</t>
   </si>
   <si>
     <t xml:space="preserve">0.147080972790718</t>
@@ -227,121 +227,121 @@
     <t xml:space="preserve">0.151480823755264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338094353676</t>
+    <t xml:space="preserve">0.148338079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566789269447</t>
+    <t xml:space="preserve">0.144566774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394902944565</t>
+    <t xml:space="preserve">0.158394888043404</t>
   </si>
   <si>
     <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17065167427063</t>
+    <t xml:space="preserve">0.170651659369469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17222298681736</t>
+    <t xml:space="preserve">0.172223001718521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594135403633</t>
+    <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507834553719</t>
+    <t xml:space="preserve">0.20050784945488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.193593740463257</t>
   </si>
   <si>
     <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765291452408</t>
+    <t xml:space="preserve">0.190765276551247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010689139366</t>
+    <t xml:space="preserve">0.201010629534721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850891828537</t>
+    <t xml:space="preserve">0.194850862026215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770970821381</t>
+    <t xml:space="preserve">0.191770985722542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879303574562</t>
+    <t xml:space="preserve">0.19987927377224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078811764717</t>
+    <t xml:space="preserve">0.213078826665878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787308454514</t>
+    <t xml:space="preserve">0.216787323355675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563927769661</t>
+    <t xml:space="preserve">0.232563897967339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220915198326</t>
+    <t xml:space="preserve">0.23822084069252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420468091965</t>
+    <t xml:space="preserve">0.251420527696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134219408035</t>
+    <t xml:space="preserve">0.26713427901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305420160294</t>
+    <t xml:space="preserve">0.275305449962616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290390640497208</t>
+    <t xml:space="preserve">0.29039067029953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561751842499</t>
+    <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705956697464</t>
+    <t xml:space="preserve">0.257706016302109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157316923141</t>
+    <t xml:space="preserve">0.260157287120819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2502261698246</t>
+    <t xml:space="preserve">0.250226229429245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163406133652</t>
+    <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809310555458</t>
+    <t xml:space="preserve">0.242809265851974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249341845512</t>
+    <t xml:space="preserve">0.243249297142029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375018239021</t>
+    <t xml:space="preserve">0.24337500333786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421183466911</t>
+    <t xml:space="preserve">0.229421198368073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821049332619</t>
+    <t xml:space="preserve">0.23382106423378</t>
   </si>
   <si>
     <t xml:space="preserve">0.210564658045769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919059157372</t>
+    <t xml:space="preserve">0.206919074058533</t>
   </si>
   <si>
     <t xml:space="preserve">0.211821779608727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20874185860157</t>
+    <t xml:space="preserve">0.208741843700409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592309713364</t>
+    <t xml:space="preserve">0.237592354416847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134949684143</t>
+    <t xml:space="preserve">0.245134964585304</t>
   </si>
   <si>
     <t xml:space="preserve">0.230803996324539</t>
@@ -350,94 +350,94 @@
     <t xml:space="preserve">0.227535516023636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706731677055</t>
+    <t xml:space="preserve">0.235706672072411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278454065323</t>
+    <t xml:space="preserve">0.226278409361839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135650157928</t>
+    <t xml:space="preserve">0.223135694861412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850146651268</t>
+    <t xml:space="preserve">0.21685017645359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381457686424</t>
+    <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141679763794</t>
+    <t xml:space="preserve">0.213141709566116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199233531952</t>
+    <t xml:space="preserve">0.201199218630791</t>
   </si>
   <si>
     <t xml:space="preserve">0.204279124736786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20679335296154</t>
+    <t xml:space="preserve">0.206793338060379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2061647772789</t>
+    <t xml:space="preserve">0.206164762377739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20742192864418</t>
+    <t xml:space="preserve">0.207421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804696798325</t>
+    <t xml:space="preserve">0.208804681897163</t>
   </si>
   <si>
     <t xml:space="preserve">0.211947470903397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649878382683</t>
+    <t xml:space="preserve">0.225649908185005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867184758186</t>
+    <t xml:space="preserve">0.21986722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810025930405</t>
+    <t xml:space="preserve">0.220810040831566</t>
   </si>
   <si>
     <t xml:space="preserve">0.229484051465988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23438672721386</t>
+    <t xml:space="preserve">0.234386757016182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518492817879</t>
+    <t xml:space="preserve">0.224518448114395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992890954018</t>
+    <t xml:space="preserve">0.21999292075634</t>
   </si>
   <si>
     <t xml:space="preserve">0.219741493463516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912984848022</t>
+    <t xml:space="preserve">0.216913014650345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306836009026</t>
+    <t xml:space="preserve">0.231306850910187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038705945015</t>
+    <t xml:space="preserve">0.217038691043854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324283957481</t>
+    <t xml:space="preserve">0.223324239253998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297178953886032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988673210144</t>
+    <t xml:space="preserve">0.351988643407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127855539322</t>
+    <t xml:space="preserve">0.465127795934677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582413673401</t>
+    <t xml:space="preserve">0.545582354068756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070420980453</t>
+    <t xml:space="preserve">0.477070331573486</t>
   </si>
   <si>
     <t xml:space="preserve">0.43684309720993</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.422072142362595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987212657928</t>
+    <t xml:space="preserve">0.395987242460251</t>
   </si>
   <si>
     <t xml:space="preserve">0.364559650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215266704559</t>
+    <t xml:space="preserve">0.414215207099915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388159036636</t>
+    <t xml:space="preserve">0.367388129234314</t>
   </si>
   <si>
     <t xml:space="preserve">0.373988002538681</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903803110123</t>
+    <t xml:space="preserve">0.325903743505478</t>
   </si>
   <si>
     <t xml:space="preserve">0.314904153347015</t>
@@ -473,55 +473,55 @@
     <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389269351959</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818232536316</t>
+    <t xml:space="preserve">0.321818202733994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845899105072</t>
+    <t xml:space="preserve">0.348845928907394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34130334854126</t>
+    <t xml:space="preserve">0.341303318738937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846599578857</t>
+    <t xml:space="preserve">0.326846569776535</t>
   </si>
   <si>
     <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32118958234787</t>
+    <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132088184357</t>
+    <t xml:space="preserve">0.333132117986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989373683929</t>
+    <t xml:space="preserve">0.329989403486252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418307065964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332386255264</t>
+    <t xml:space="preserve">0.324332356452942</t>
   </si>
   <si>
     <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761409044266</t>
+    <t xml:space="preserve">0.311761349439621</t>
   </si>
   <si>
     <t xml:space="preserve">0.334703534841537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046897649765</t>
+    <t xml:space="preserve">0.318046867847443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31678980588913</t>
+    <t xml:space="preserve">0.316789776086807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328418016433716</t>
+    <t xml:space="preserve">0.328417986631393</t>
   </si>
   <si>
     <t xml:space="preserve">0.323075324296951</t>
@@ -536,55 +536,55 @@
     <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069995164871</t>
+    <t xml:space="preserve">0.311069965362549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561110973358</t>
+    <t xml:space="preserve">0.320561140775681</t>
   </si>
   <si>
     <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274161815643</t>
+    <t xml:space="preserve">0.358274191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417666196823</t>
+    <t xml:space="preserve">0.339417636394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34004619717598</t>
+    <t xml:space="preserve">0.340046137571335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3193039894104</t>
+    <t xml:space="preserve">0.319304019212723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846249341965</t>
+    <t xml:space="preserve">0.337846308946609</t>
   </si>
   <si>
     <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327789455652237</t>
+    <t xml:space="preserve">0.327789485454559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701783657074</t>
+    <t xml:space="preserve">0.389701724052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588166475296</t>
+    <t xml:space="preserve">0.369588106870651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36895951628685</t>
+    <t xml:space="preserve">0.368959546089172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216637849808</t>
+    <t xml:space="preserve">0.370216608047485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616913557053</t>
+    <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845198631287</t>
+    <t xml:space="preserve">0.370845228433609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074594020844</t>
+    <t xml:space="preserve">0.345074653625488</t>
   </si>
   <si>
     <t xml:space="preserve">0.349788784980774</t>
@@ -593,67 +593,67 @@
     <t xml:space="preserve">0.354502886533737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073893547058</t>
+    <t xml:space="preserve">0.367073863744736</t>
   </si>
   <si>
     <t xml:space="preserve">0.388758897781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587376594543</t>
+    <t xml:space="preserve">0.391587406396866</t>
   </si>
   <si>
     <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130746841431</t>
+    <t xml:space="preserve">0.377130687236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444982528687</t>
+    <t xml:space="preserve">0.377444952726364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.407929688692093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843857288361</t>
+    <t xml:space="preserve">0.414843797683716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215967178345</t>
+    <t xml:space="preserve">0.392215877771378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37681645154953</t>
+    <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38655897974968</t>
+    <t xml:space="preserve">0.386559069156647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413463354111</t>
+    <t xml:space="preserve">0.471413344144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357310533524</t>
+    <t xml:space="preserve">0.439357221126556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556908130646</t>
+    <t xml:space="preserve">0.452556818723679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700293302536</t>
+    <t xml:space="preserve">0.433700352907181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100188970566</t>
+    <t xml:space="preserve">0.438100159168243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271300315857</t>
+    <t xml:space="preserve">0.446271389722824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985781908035</t>
+    <t xml:space="preserve">0.43998584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386288642883</t>
+    <t xml:space="preserve">0.42238637804985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900650978088</t>
+    <t xml:space="preserve">0.424900591373444</t>
   </si>
   <si>
     <t xml:space="preserve">0.421129316091537</t>
@@ -662,49 +662,49 @@
     <t xml:space="preserve">0.409815430641174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044095754623</t>
+    <t xml:space="preserve">0.406044125556946</t>
   </si>
   <si>
     <t xml:space="preserve">0.408558249473572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41358670592308</t>
+    <t xml:space="preserve">0.413586676120758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272760868073</t>
+    <t xml:space="preserve">0.40227273106575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443171739578</t>
+    <t xml:space="preserve">0.432443201541901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357981204987</t>
+    <t xml:space="preserve">0.417357921600342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613672018051</t>
+    <t xml:space="preserve">0.462613701820374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414834499359</t>
+    <t xml:space="preserve">0.427414774894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758607149124</t>
+    <t xml:space="preserve">0.399758547544479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615072965622</t>
+    <t xml:space="preserve">0.418615102767944</t>
   </si>
   <si>
     <t xml:space="preserve">0.423643559217453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072432994843</t>
+    <t xml:space="preserve">0.41107252240181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501366376877</t>
+    <t xml:space="preserve">0.398501485586166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404787003993988</t>
+    <t xml:space="preserve">0.404786914587021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159054279327</t>
+    <t xml:space="preserve">0.38215908408165</t>
   </si>
   <si>
     <t xml:space="preserve">0.38341623544693</t>
@@ -713,142 +713,145 @@
     <t xml:space="preserve">0.388444632291794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40352988243103</t>
+    <t xml:space="preserve">0.403529852628708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186079978943</t>
+    <t xml:space="preserve">0.431186139583588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872224330902</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301187515259</t>
+    <t xml:space="preserve">0.407301157712936</t>
   </si>
   <si>
     <t xml:space="preserve">0.394730180501938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4123295545578</t>
+    <t xml:space="preserve">0.412329524755478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015669107437</t>
+    <t xml:space="preserve">0.40101569890976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100889444351</t>
+    <t xml:space="preserve">0.416100829839706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045407295227</t>
+    <t xml:space="preserve">0.362045437097549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3658167719841</t>
+    <t xml:space="preserve">0.36581689119339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36330258846283</t>
+    <t xml:space="preserve">0.363302618265152</t>
   </si>
   <si>
     <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360842704773</t>
+    <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531283378601</t>
+    <t xml:space="preserve">0.359531223773956</t>
   </si>
   <si>
     <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34444597363472</t>
+    <t xml:space="preserve">0.344446003437042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903423070908</t>
+    <t xml:space="preserve">0.336903393268585</t>
   </si>
   <si>
     <t xml:space="preserve">0.338160544633865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703154802322</t>
+    <t xml:space="preserve">0.345703184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102320194244</t>
+    <t xml:space="preserve">0.372102230787277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930389165878</t>
+    <t xml:space="preserve">0.385930478572845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245794773102</t>
+    <t xml:space="preserve">0.353245764970779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788375139236</t>
+    <t xml:space="preserve">0.360788434743881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387838602066</t>
+    <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873565673828</t>
+    <t xml:space="preserve">0.375873595476151</t>
   </si>
   <si>
     <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673357009888</t>
+    <t xml:space="preserve">0.384673297405243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958786010742</t>
+    <t xml:space="preserve">0.390958875417709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393473029136658</t>
+    <t xml:space="preserve">0.393472999334335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557519197464</t>
+    <t xml:space="preserve">0.430557578802109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414074420929</t>
+    <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
     <t xml:space="preserve">0.455699652433395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955998420715</t>
+    <t xml:space="preserve">0.463956028223038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181782960892</t>
+    <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
     <t xml:space="preserve">0.429332405328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483057498932</t>
+    <t xml:space="preserve">0.415482968091965</t>
   </si>
   <si>
     <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257094144821</t>
+    <t xml:space="preserve">0.436257153749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719498157501</t>
+    <t xml:space="preserve">0.439719527959824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794749736786</t>
+    <t xml:space="preserve">0.432794779539108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945372104645</t>
+    <t xml:space="preserve">0.418945342302322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633560657501</t>
+    <t xml:space="preserve">0.408558309078217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020593881607</t>
+    <t xml:space="preserve">0.401633530855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784123420715</t>
+    <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246557235718</t>
+    <t xml:space="preserve">0.387784093618393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391246467828751</t>
   </si>
   <si>
     <t xml:space="preserve">0.405095875263214</t>
@@ -860,34 +863,34 @@
     <t xml:space="preserve">0.446644186973572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278495788574</t>
+    <t xml:space="preserve">0.526278436183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106501579285</t>
+    <t xml:space="preserve">0.450106531381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031399011612</t>
+    <t xml:space="preserve">0.457031309604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568935394287</t>
+    <t xml:space="preserve">0.453568875789642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171216249466</t>
+    <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708812236786</t>
+    <t xml:space="preserve">0.394708842039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859404802322</t>
+    <t xml:space="preserve">0.380859434604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934715986252</t>
+    <t xml:space="preserve">0.373934686183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360085189342499</t>
+    <t xml:space="preserve">0.360085219144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472371578217</t>
+    <t xml:space="preserve">0.370472311973572</t>
   </si>
   <si>
     <t xml:space="preserve">0.384321749210358</t>
@@ -902,31 +905,31 @@
     <t xml:space="preserve">0.339311093091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160500526428</t>
+    <t xml:space="preserve">0.353160470724106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235811710358</t>
+    <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386344671249</t>
+    <t xml:space="preserve">0.332386374473572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612159013748</t>
+    <t xml:space="preserve">0.311612188816071</t>
   </si>
   <si>
     <t xml:space="preserve">0.314382135868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838122367859</t>
+    <t xml:space="preserve">0.290838062763214</t>
   </si>
   <si>
     <t xml:space="preserve">0.258984416723251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373628854752</t>
+    <t xml:space="preserve">0.278373569250107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139247894287</t>
+    <t xml:space="preserve">0.263139218091965</t>
   </si>
   <si>
     <t xml:space="preserve">0.272833853960037</t>
@@ -935,31 +938,28 @@
     <t xml:space="preserve">0.261754274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134979486465</t>
+    <t xml:space="preserve">0.249289780855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289810657501</t>
+    <t xml:space="preserve">0.243749961256981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750020861626</t>
+    <t xml:space="preserve">0.285298317670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298347473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286683291196823</t>
+    <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
     <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758542776108</t>
+    <t xml:space="preserve">0.27975857257843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143486499786</t>
+    <t xml:space="preserve">0.281143456697464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29499289393425</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
     <t xml:space="preserve">0.303302586078644</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926119565964</t>
+    <t xml:space="preserve">0.337926179170609</t>
   </si>
   <si>
     <t xml:space="preserve">0.325461626052856</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">0.343465924263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547593355179</t>
+    <t xml:space="preserve">0.363547563552856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397000789642</t>
+    <t xml:space="preserve">0.377397090196609</t>
   </si>
   <si>
     <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001430749893</t>
+    <t xml:space="preserve">0.331001490354538</t>
   </si>
   <si>
     <t xml:space="preserve">0.33654123544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698215723038</t>
+    <t xml:space="preserve">0.349698185920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850867986679</t>
+    <t xml:space="preserve">0.344850897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691768407822</t>
+    <t xml:space="preserve">0.322691798210144</t>
   </si>
   <si>
     <t xml:space="preserve">0.3240767121315</t>
@@ -1013,28 +1013,28 @@
     <t xml:space="preserve">0.318536967039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072443723679</t>
+    <t xml:space="preserve">0.306072473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317151993513107</t>
+    <t xml:space="preserve">0.317152082920074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3046875</t>
+    <t xml:space="preserve">0.304687589406967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762840986252</t>
+    <t xml:space="preserve">0.297762811183929</t>
   </si>
   <si>
     <t xml:space="preserve">0.283913373947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288068234920502</t>
+    <t xml:space="preserve">0.288068145513535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524161815643</t>
+    <t xml:space="preserve">0.264524132013321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294019460678</t>
+    <t xml:space="preserve">0.267294108867645</t>
   </si>
   <si>
     <t xml:space="preserve">0.260369330644608</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063936710358</t>
+    <t xml:space="preserve">0.27006396651268</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223036289215</t>
+    <t xml:space="preserve">0.292223006486893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377867460251</t>
+    <t xml:space="preserve">0.296377897262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809957742691</t>
+    <t xml:space="preserve">0.429809987545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647802114487</t>
+    <t xml:space="preserve">0.399647831916809</t>
   </si>
   <si>
     <t xml:space="preserve">0.388337105512619</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36194521188736</t>
+    <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485765695572</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
     <t xml:space="preserve">0.363453358411789</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010115861893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961445331573</t>
+    <t xml:space="preserve">0.364961475133896</t>
   </si>
   <si>
     <t xml:space="preserve">0.349880367517471</t>
@@ -1097,67 +1097,67 @@
     <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323580265045</t>
+    <t xml:space="preserve">0.339323669672012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.352896571159363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864193677902</t>
+    <t xml:space="preserve">0.34686416387558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388484239578</t>
+    <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307466030121</t>
+    <t xml:space="preserve">0.336307495832443</t>
   </si>
   <si>
     <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372310400009</t>
+    <t xml:space="preserve">0.348372280597687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350511550903</t>
+    <t xml:space="preserve">0.437350481748581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958617925644</t>
+    <t xml:space="preserve">0.410958707332611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431619167328</t>
+    <t xml:space="preserve">0.452431589365005</t>
   </si>
   <si>
     <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120713949203</t>
+    <t xml:space="preserve">0.441120743751526</t>
   </si>
   <si>
     <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418183326721</t>
+    <t xml:space="preserve">0.403418123722076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107278108597</t>
+    <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
     <t xml:space="preserve">0.384566783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877599716187</t>
+    <t xml:space="preserve">0.395877569913864</t>
   </si>
   <si>
     <t xml:space="preserve">0.407188415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501999139786</t>
+    <t xml:space="preserve">0.372501969337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36646956205368</t>
+    <t xml:space="preserve">0.366469532251358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404658079147</t>
+    <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
     <t xml:space="preserve">0.345356076955795</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437124967575</t>
+    <t xml:space="preserve">0.360437154769897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977619171143</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929038047791</t>
+    <t xml:space="preserve">0.358929067850113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316702127456665</t>
+    <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
     <t xml:space="preserve">0.300112962722778</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210184574127</t>
+    <t xml:space="preserve">0.318210244178772</t>
   </si>
   <si>
     <t xml:space="preserve">0.319718331098557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324242651462555</t>
+    <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
     <t xml:space="preserve">0.327258825302124</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3317831158638</t>
+    <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337815523147583</t>
+    <t xml:space="preserve">0.33781561255455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766912221909</t>
+    <t xml:space="preserve">0.328766942024231</t>
   </si>
   <si>
     <t xml:space="preserve">0.309161573648453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653456926346</t>
+    <t xml:space="preserve">0.307653427124023</t>
   </si>
   <si>
     <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685923814774</t>
+    <t xml:space="preserve">0.313685894012451</t>
   </si>
   <si>
     <t xml:space="preserve">0.322734504938126</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">0.317599207162857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322339445352554</t>
+    <t xml:space="preserve">0.322339475154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314439028501511</t>
+    <t xml:space="preserve">0.314438998699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.319179266691208</t>
@@ -1250,52 +1250,52 @@
     <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858909368515</t>
+    <t xml:space="preserve">0.31285884976387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378343582153</t>
+    <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317628860474</t>
+    <t xml:space="preserve">0.292317658662796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798194646835</t>
+    <t xml:space="preserve">0.301798284053802</t>
   </si>
   <si>
     <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218135118484</t>
+    <t xml:space="preserve">0.300218105316162</t>
   </si>
   <si>
     <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2907375395298</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837063074112</t>
+    <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577301263809</t>
+    <t xml:space="preserve">0.287577331066132</t>
   </si>
   <si>
     <t xml:space="preserve">0.279676884412766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516735553741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27809676527977</t>
+    <t xml:space="preserve">0.278096824884415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196318626404</t>
+    <t xml:space="preserve">0.270196348428726</t>
   </si>
   <si>
     <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776467561722</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417182207108</t>
@@ -1307,31 +1307,31 @@
     <t xml:space="preserve">0.295477837324142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057926654816</t>
+    <t xml:space="preserve">0.297057956457138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118581771851</t>
+    <t xml:space="preserve">0.308118611574173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289157450199127</t>
+    <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040904521942</t>
+    <t xml:space="preserve">0.34604087471962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140457868576</t>
+    <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720487594604</t>
+    <t xml:space="preserve">0.339720517396927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3413006067276</t>
+    <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
     <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336560279130936</t>
+    <t xml:space="preserve">0.336560308933258</t>
   </si>
   <si>
     <t xml:space="preserve">0.35236132144928</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481110811234</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
     <t xml:space="preserve">0.29877382516861</t>
@@ -1361,19 +1361,19 @@
     <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286516666412</t>
+    <t xml:space="preserve">0.27828648686409</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993802309036</t>
+    <t xml:space="preserve">0.279993712902069</t>
   </si>
   <si>
     <t xml:space="preserve">0.273164629936218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579231023788</t>
+    <t xml:space="preserve">0.276579201221466</t>
   </si>
   <si>
     <t xml:space="preserve">0.269750148057938</t>
@@ -1382,40 +1382,40 @@
     <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871975183487</t>
+    <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457403898239</t>
+    <t xml:space="preserve">0.271457374095917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042802810669</t>
+    <t xml:space="preserve">0.268042862415314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895682096481</t>
+    <t xml:space="preserve">0.303895652294159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188366651535</t>
+    <t xml:space="preserve">0.30218842625618</t>
   </si>
   <si>
     <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310312986374</t>
+    <t xml:space="preserve">0.307310283184052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383020401001</t>
+    <t xml:space="preserve">0.324382990598679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261193275452</t>
+    <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017509222031</t>
+    <t xml:space="preserve">0.309017539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139395952225</t>
+    <t xml:space="preserve">0.31413933634758</t>
   </si>
   <si>
     <t xml:space="preserve">0.312432080507278</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29982978105545</t>
+    <t xml:space="preserve">0.299829840660095</t>
   </si>
   <si>
     <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316205739975</t>
+    <t xml:space="preserve">0.303316175937653</t>
   </si>
   <si>
     <t xml:space="preserve">0.289370626211166</t>
@@ -1442,40 +1442,40 @@
     <t xml:space="preserve">0.287627458572388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086673021317</t>
+    <t xml:space="preserve">0.298086613416672</t>
   </si>
   <si>
     <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304652392864227</t>
+    <t xml:space="preserve">0.30465242266655</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306434005498886</t>
+    <t xml:space="preserve">0.306434035301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089227199554</t>
+    <t xml:space="preserve">0.301089257001877</t>
   </si>
   <si>
     <t xml:space="preserve">0.286836475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618057966232</t>
+    <t xml:space="preserve">0.288618087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399670600891</t>
+    <t xml:space="preserve">0.290399640798569</t>
   </si>
   <si>
     <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962806463242</t>
+    <t xml:space="preserve">0.293962895870209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054892301559</t>
+    <t xml:space="preserve">0.285054862499237</t>
   </si>
   <si>
     <t xml:space="preserve">0.283273279666901</t>
@@ -1484,73 +1484,73 @@
     <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491696834564</t>
+    <t xml:space="preserve">0.281491726636887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292181223630905</t>
+    <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902150630951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302665114402771</t>
+    <t xml:space="preserve">0.302665084600449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29172545671463</t>
+    <t xml:space="preserve">0.291725397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488390684128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308134973049164</t>
+    <t xml:space="preserve">0.308135002851486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3117815554142</t>
+    <t xml:space="preserve">0.311781585216522</t>
   </si>
   <si>
     <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074690341949</t>
+    <t xml:space="preserve">0.319074660539627</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191101551056</t>
+    <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33183765411377</t>
+    <t xml:space="preserve">0.331837683916092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660960197449</t>
+    <t xml:space="preserve">0.333660989999771</t>
   </si>
   <si>
     <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324544548988342</t>
+    <t xml:space="preserve">0.32454451918602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158191680908</t>
+    <t xml:space="preserve">0.324158161878586</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322295218706131</t>
+    <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610053777695</t>
+    <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021194458008</t>
+    <t xml:space="preserve">0.326021134853363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432245731354</t>
+    <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
     <t xml:space="preserve">0.311117321252823</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335336029529572</t>
+    <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
     <t xml:space="preserve">0.316706269979477</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">0.318569272756577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340924978256226</t>
+    <t xml:space="preserve">0.340925008058548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473056554794</t>
+    <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
     <t xml:space="preserve">0.307391405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
     <t xml:space="preserve">0.353965818881989</t>
@@ -1595,28 +1595,28 @@
     <t xml:space="preserve">0.370732635259628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677319288254</t>
+    <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170081615448</t>
+    <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407992213964462</t>
+    <t xml:space="preserve">0.40799218416214</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40985518693924</t>
+    <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540292263031</t>
+    <t xml:space="preserve">0.400540322065353</t>
   </si>
   <si>
     <t xml:space="preserve">0.3912253677845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3930883705616</t>
+    <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
     <t xml:space="preserve">0.389362454414368</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">0.363280713558197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367006689310074</t>
+    <t xml:space="preserve">0.367006659507751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869662284851</t>
+    <t xml:space="preserve">0.368869632482529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378184527158737</t>
+    <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
     <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407650500535965</t>
+    <t xml:space="preserve">0.407650470733643</t>
   </si>
   <si>
     <t xml:space="preserve">0.392482101917267</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40385839343071</t>
+    <t xml:space="preserve">0.403858363628387</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
@@ -1755,6 +1755,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.524999976158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540000021457672</t>
   </si>
 </sst>
 </file>
@@ -26161,7 +26164,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26187,7 +26190,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26213,7 +26216,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26239,7 +26242,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26265,7 +26268,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26291,7 +26294,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26317,7 +26320,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26343,7 +26346,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26369,7 +26372,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26395,7 +26398,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26421,7 +26424,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26447,7 +26450,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26473,7 +26476,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26499,7 +26502,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26525,7 +26528,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26551,7 +26554,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26603,7 +26606,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26629,7 +26632,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26655,7 +26658,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26681,7 +26684,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26707,7 +26710,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26733,7 +26736,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26759,7 +26762,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26785,7 +26788,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26811,7 +26814,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26837,7 +26840,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26863,7 +26866,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26889,7 +26892,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26915,7 +26918,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26941,7 +26944,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26967,7 +26970,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26993,7 +26996,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27019,7 +27022,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27045,7 +27048,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27071,7 +27074,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27149,7 +27152,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27227,7 +27230,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27253,7 +27256,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27305,7 +27308,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27331,7 +27334,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27357,7 +27360,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27383,7 +27386,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27539,7 +27542,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27565,7 +27568,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27591,7 +27594,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27669,7 +27672,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27695,7 +27698,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28111,7 +28114,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28137,7 +28140,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28163,7 +28166,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28189,7 +28192,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28215,7 +28218,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28241,7 +28244,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28267,7 +28270,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28293,7 +28296,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28319,7 +28322,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28371,7 +28374,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28397,7 +28400,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28423,7 +28426,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28449,7 +28452,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28475,7 +28478,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28501,7 +28504,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28527,7 +28530,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28553,7 +28556,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28579,7 +28582,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28605,7 +28608,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28631,7 +28634,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28709,7 +28712,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28735,7 +28738,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28761,7 +28764,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28787,7 +28790,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28813,7 +28816,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28839,7 +28842,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28865,7 +28868,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28891,7 +28894,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28917,7 +28920,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28943,7 +28946,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28969,7 +28972,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28995,7 +28998,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29021,7 +29024,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29047,7 +29050,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29073,7 +29076,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29099,7 +29102,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29125,7 +29128,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29151,7 +29154,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29177,7 +29180,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29203,7 +29206,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29229,7 +29232,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29333,7 +29336,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29385,7 +29388,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29463,7 +29466,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29489,7 +29492,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29515,7 +29518,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29541,7 +29544,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29567,7 +29570,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29593,7 +29596,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29619,7 +29622,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29645,7 +29648,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29671,7 +29674,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29697,7 +29700,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29723,7 +29726,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29749,7 +29752,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29775,7 +29778,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29801,7 +29804,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29827,7 +29830,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29853,7 +29856,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29879,7 +29882,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29905,7 +29908,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29931,7 +29934,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>307</v>
+        <v>109</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30113,7 +30116,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30243,7 +30246,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30269,7 +30272,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30295,7 +30298,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30347,7 +30350,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30373,7 +30376,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30451,7 +30454,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30841,7 +30844,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30867,7 +30870,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30971,7 +30974,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31023,7 +31026,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31049,7 +31052,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31075,7 +31078,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31179,7 +31182,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31205,7 +31208,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31231,7 +31234,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31283,7 +31286,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31309,7 +31312,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31335,7 +31338,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31361,7 +31364,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31387,7 +31390,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31413,7 +31416,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31439,7 +31442,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31465,7 +31468,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31491,7 +31494,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31517,7 +31520,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31543,7 +31546,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31569,7 +31572,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31595,7 +31598,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31621,7 +31624,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31647,7 +31650,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31673,7 +31676,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31699,7 +31702,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31725,7 +31728,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31751,7 +31754,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31777,7 +31780,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31803,7 +31806,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31829,7 +31832,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31855,7 +31858,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31881,7 +31884,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31907,7 +31910,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31933,7 +31936,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31959,7 +31962,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32011,7 +32014,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32037,7 +32040,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32063,7 +32066,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32115,7 +32118,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32297,7 +32300,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32323,7 +32326,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32349,7 +32352,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32375,7 +32378,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32713,7 +32716,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33207,7 +33210,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34247,7 +34250,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34455,7 +34458,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34481,7 +34484,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34975,7 +34978,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35625,7 +35628,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35651,7 +35654,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35703,7 +35706,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35729,7 +35732,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35755,7 +35758,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35781,7 +35784,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35833,7 +35836,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35859,7 +35862,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35885,7 +35888,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35937,7 +35940,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35963,7 +35966,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35989,7 +35992,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36015,7 +36018,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36041,7 +36044,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36067,7 +36070,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36093,7 +36096,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36119,7 +36122,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36145,7 +36148,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -68258,6 +68261,58 @@
         <v>579</v>
       </c>
       <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.3333333333</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.5946180556</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994336605072</t>
+    <t xml:space="preserve">0.17599430680275</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851592302322</t>
+    <t xml:space="preserve">0.1728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594455838203</t>
+    <t xml:space="preserve">0.171594470739365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051830768585</t>
+    <t xml:space="preserve">0.164051875472069</t>
   </si>
   <si>
     <t xml:space="preserve">0.16970881819725</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14330966770649</t>
+    <t xml:space="preserve">0.143309682607651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783760309219</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195335149765</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.150789439678192</t>
   </si>
   <si>
     <t xml:space="preserve">0.1464524269104</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">0.139852613210678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538377523422</t>
+    <t xml:space="preserve">0.1395383477211</t>
   </si>
   <si>
     <t xml:space="preserve">0.139915496110916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052546143532</t>
+    <t xml:space="preserve">0.142052575945854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909816741943</t>
+    <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
     <t xml:space="preserve">0.15110370516777</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817456483841</t>
+    <t xml:space="preserve">0.166817501187325</t>
   </si>
   <si>
     <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137796282768</t>
+    <t xml:space="preserve">0.157137811183929</t>
   </si>
   <si>
     <t xml:space="preserve">0.154623597860336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14959517121315</t>
+    <t xml:space="preserve">0.149595186114311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692160129547</t>
+    <t xml:space="preserve">0.155692115426064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909071564674</t>
+    <t xml:space="preserve">0.160909101366997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960610628128</t>
+    <t xml:space="preserve">0.158960595726967</t>
   </si>
   <si>
     <t xml:space="preserve">0.177314266562462</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965909957886</t>
+    <t xml:space="preserve">0.170965939760208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937483310699</t>
+    <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565373420715</t>
+    <t xml:space="preserve">0.188565358519554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650899291039</t>
+    <t xml:space="preserve">0.192650958895683</t>
   </si>
   <si>
     <t xml:space="preserve">0.191708117723465</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">0.184165507555008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651309132576</t>
+    <t xml:space="preserve">0.181651294231415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136395335197</t>
+    <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
     <t xml:space="preserve">0.208678990602493</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">0.201073512434959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736499667168</t>
+    <t xml:space="preserve">0.19673652946949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222316145897</t>
+    <t xml:space="preserve">0.194222271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137080907822</t>
+    <t xml:space="preserve">0.179137110710144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279825210571</t>
+    <t xml:space="preserve">0.182279855012894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834569096565</t>
+    <t xml:space="preserve">0.169834554195404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451711535454</t>
+    <t xml:space="preserve">0.168451726436615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794783711433</t>
+    <t xml:space="preserve">0.162794768810272</t>
   </si>
   <si>
     <t xml:space="preserve">0.151606544852257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566044092178</t>
+    <t xml:space="preserve">0.166566029191017</t>
   </si>
   <si>
     <t xml:space="preserve">0.157074928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109384536743</t>
+    <t xml:space="preserve">0.152109399437904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995037078857</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640635967255</t>
@@ -206,88 +206,88 @@
     <t xml:space="preserve">0.186051160097122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936797738075</t>
+    <t xml:space="preserve">0.187936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536916971207</t>
+    <t xml:space="preserve">0.183536946773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714162230492</t>
+    <t xml:space="preserve">0.181714132428169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194604873657</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160280555486679</t>
+    <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080957889557</t>
+    <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480853557587</t>
+    <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338079452515</t>
+    <t xml:space="preserve">0.148338094353676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566759467125</t>
+    <t xml:space="preserve">0.144566774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394888043404</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183261036873</t>
+    <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651659369469</t>
+    <t xml:space="preserve">0.170651629567146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223001718521</t>
+    <t xml:space="preserve">0.172223016619682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594105601311</t>
+    <t xml:space="preserve">0.18259409070015</t>
   </si>
   <si>
     <t xml:space="preserve">0.200507834553719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593755364418</t>
+    <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131386637688</t>
+    <t xml:space="preserve">0.17813141644001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765306353569</t>
+    <t xml:space="preserve">0.190765276551247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010629534721</t>
+    <t xml:space="preserve">0.201010674238205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850862026215</t>
+    <t xml:space="preserve">0.194850876927376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770985722542</t>
+    <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879288673401</t>
+    <t xml:space="preserve">0.199879258871078</t>
   </si>
   <si>
     <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787338256836</t>
+    <t xml:space="preserve">0.216787308454514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563942670822</t>
+    <t xml:space="preserve">0.232563927769661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220900297165</t>
+    <t xml:space="preserve">0.238220930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420438289642</t>
+    <t xml:space="preserve">0.251420468091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26713427901268</t>
+    <t xml:space="preserve">0.267134308815002</t>
   </si>
   <si>
     <t xml:space="preserve">0.275305449962616</t>
@@ -302,61 +302,61 @@
     <t xml:space="preserve">0.257706016302109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157346725464</t>
+    <t xml:space="preserve">0.260157376527786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250226199626923</t>
+    <t xml:space="preserve">0.250226229429245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163346529007</t>
+    <t xml:space="preserve">0.250163376331329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809295654297</t>
+    <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
     <t xml:space="preserve">0.243249267339706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375048041344</t>
+    <t xml:space="preserve">0.24337500333786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421198368073</t>
+    <t xml:space="preserve">0.22942116856575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23382106423378</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564643144608</t>
+    <t xml:space="preserve">0.210564658045769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919059157372</t>
+    <t xml:space="preserve">0.206919074058533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821764707565</t>
+    <t xml:space="preserve">0.211821794509888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20874185860157</t>
+    <t xml:space="preserve">0.208741828799248</t>
   </si>
   <si>
     <t xml:space="preserve">0.237592324614525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134979486465</t>
+    <t xml:space="preserve">0.245134964585304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803996324539</t>
+    <t xml:space="preserve">0.230803981423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535560727119</t>
+    <t xml:space="preserve">0.227535530924797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706672072411</t>
+    <t xml:space="preserve">0.235706716775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278409361839</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135635256767</t>
+    <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
     <t xml:space="preserve">0.216850146651268</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141694664955</t>
+    <t xml:space="preserve">0.213141724467278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199233531952</t>
+    <t xml:space="preserve">0.201199263334274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279169440269</t>
+    <t xml:space="preserve">0.204279124736786</t>
   </si>
   <si>
     <t xml:space="preserve">0.206793338060379</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">0.206164792180061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421913743019</t>
+    <t xml:space="preserve">0.207421883940697</t>
   </si>
   <si>
     <t xml:space="preserve">0.208804681897163</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">0.22564984858036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867199659348</t>
+    <t xml:space="preserve">0.219867184758186</t>
   </si>
   <si>
     <t xml:space="preserve">0.220810040831566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484021663666</t>
+    <t xml:space="preserve">0.229484051465988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386801719666</t>
+    <t xml:space="preserve">0.234386742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518477916718</t>
+    <t xml:space="preserve">0.224518463015556</t>
   </si>
   <si>
     <t xml:space="preserve">0.219992950558662</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">0.219741508364677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912984848022</t>
+    <t xml:space="preserve">0.216913014650345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306836009026</t>
+    <t xml:space="preserve">0.231306821107864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038691043854</t>
+    <t xml:space="preserve">0.217038750648499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324283957481</t>
+    <t xml:space="preserve">0.223324209451675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988673210144</t>
+    <t xml:space="preserve">0.351988613605499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127885341644</t>
+    <t xml:space="preserve">0.465127855539322</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582473278046</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">0.477070331573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843067407608</t>
+    <t xml:space="preserve">0.43684309720993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072142362595</t>
+    <t xml:space="preserve">0.422072172164917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987242460251</t>
+    <t xml:space="preserve">0.395987212657928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559650421143</t>
+    <t xml:space="preserve">0.364559710025787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215177297592</t>
+    <t xml:space="preserve">0.414215266704559</t>
   </si>
   <si>
     <t xml:space="preserve">0.367388159036636</t>
@@ -464,25 +464,25 @@
     <t xml:space="preserve">0.346331685781479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903713703156</t>
+    <t xml:space="preserve">0.3259037733078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904153347015</t>
+    <t xml:space="preserve">0.314904093742371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532334089279</t>
+    <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389209747314</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818143129349</t>
+    <t xml:space="preserve">0.321818202733994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845958709717</t>
+    <t xml:space="preserve">0.34884586930275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303318738937</t>
+    <t xml:space="preserve">0.341303259134293</t>
   </si>
   <si>
     <t xml:space="preserve">0.326846599578857</t>
@@ -491,187 +491,187 @@
     <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189671754837</t>
+    <t xml:space="preserve">0.321189612150192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132088184357</t>
+    <t xml:space="preserve">0.333132058382034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989343881607</t>
+    <t xml:space="preserve">0.329989314079285</t>
   </si>
   <si>
     <t xml:space="preserve">0.317418336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332356452942</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275592565536</t>
+    <t xml:space="preserve">0.314275622367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761409044266</t>
+    <t xml:space="preserve">0.311761438846588</t>
   </si>
   <si>
     <t xml:space="preserve">0.334703534841537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046897649765</t>
+    <t xml:space="preserve">0.318046927452087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789776086807</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417956829071</t>
+    <t xml:space="preserve">0.328418016433716</t>
   </si>
   <si>
     <t xml:space="preserve">0.323075294494629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32810366153717</t>
+    <t xml:space="preserve">0.328103750944138</t>
   </si>
   <si>
     <t xml:space="preserve">0.301704555749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504257678986</t>
+    <t xml:space="preserve">0.31050431728363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069965362549</t>
+    <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561110973358</t>
+    <t xml:space="preserve">0.320561081171036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589567422867</t>
+    <t xml:space="preserve">0.325589537620544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274161815643</t>
+    <t xml:space="preserve">0.358274221420288</t>
   </si>
   <si>
     <t xml:space="preserve">0.339417636394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046226978302</t>
+    <t xml:space="preserve">0.340046167373657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304019212723</t>
+    <t xml:space="preserve">0.319304049015045</t>
   </si>
   <si>
     <t xml:space="preserve">0.337846308946609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589887857437</t>
+    <t xml:space="preserve">0.314589858055115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327789425849915</t>
+    <t xml:space="preserve">0.327789396047592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701724052429</t>
+    <t xml:space="preserve">0.389701753854752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588106870651</t>
+    <t xml:space="preserve">0.369588166475296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959605693817</t>
+    <t xml:space="preserve">0.368959486484528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37021666765213</t>
+    <t xml:space="preserve">0.370216608047485</t>
   </si>
   <si>
     <t xml:space="preserve">0.363616824150085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845198631287</t>
+    <t xml:space="preserve">0.370845168828964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074594020844</t>
+    <t xml:space="preserve">0.345074623823166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788755178452</t>
+    <t xml:space="preserve">0.349788725376129</t>
   </si>
   <si>
     <t xml:space="preserve">0.354502856731415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073833942413</t>
+    <t xml:space="preserve">0.367073893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758897781372</t>
+    <t xml:space="preserve">0.388758838176727</t>
   </si>
   <si>
     <t xml:space="preserve">0.391587406396866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759277820587</t>
+    <t xml:space="preserve">0.37775930762291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130746841431</t>
+    <t xml:space="preserve">0.377130717039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187510728836</t>
+    <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377445012331009</t>
+    <t xml:space="preserve">0.377444893121719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.407929688692093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843827486038</t>
+    <t xml:space="preserve">0.414843767881393</t>
   </si>
   <si>
     <t xml:space="preserve">0.392215937376022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376816421747208</t>
+    <t xml:space="preserve">0.37681645154953</t>
   </si>
   <si>
     <t xml:space="preserve">0.386558949947357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413344144821</t>
+    <t xml:space="preserve">0.471413433551788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357221126556</t>
+    <t xml:space="preserve">0.439357250928879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556818723679</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
     <t xml:space="preserve">0.433700293302536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100278377533</t>
+    <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271270513535</t>
+    <t xml:space="preserve">0.446271300315857</t>
   </si>
   <si>
     <t xml:space="preserve">0.439985901117325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386348247528</t>
+    <t xml:space="preserve">0.422386407852173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900650978088</t>
+    <t xml:space="preserve">0.424900591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129286289215</t>
+    <t xml:space="preserve">0.421129316091537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815430641174</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
     <t xml:space="preserve">0.406044125556946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558338880539</t>
+    <t xml:space="preserve">0.408558249473572</t>
   </si>
   <si>
     <t xml:space="preserve">0.413586676120758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272790670395</t>
+    <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
     <t xml:space="preserve">0.432443231344223</t>
@@ -680,52 +680,52 @@
     <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613672018051</t>
+    <t xml:space="preserve">0.462613642215729</t>
   </si>
   <si>
     <t xml:space="preserve">0.427414774894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758577346802</t>
+    <t xml:space="preserve">0.399758517742157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4186150431633</t>
+    <t xml:space="preserve">0.418615072965622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643529415131</t>
+    <t xml:space="preserve">0.423643589019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072462797165</t>
+    <t xml:space="preserve">0.41107240319252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501455783844</t>
+    <t xml:space="preserve">0.398501425981522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786944389343</t>
+    <t xml:space="preserve">0.404786974191666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38215908408165</t>
+    <t xml:space="preserve">0.382159113883972</t>
   </si>
   <si>
     <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444632291794</t>
+    <t xml:space="preserve">0.388444542884827</t>
   </si>
   <si>
     <t xml:space="preserve">0.403529912233353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43118616938591</t>
+    <t xml:space="preserve">0.43118605017662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872224330902</t>
+    <t xml:space="preserve">0.419872164726257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301157712936</t>
+    <t xml:space="preserve">0.407301187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730180501938</t>
+    <t xml:space="preserve">0.394730150699615</t>
   </si>
   <si>
     <t xml:space="preserve">0.412329584360123</t>
@@ -734,46 +734,46 @@
     <t xml:space="preserve">0.401015669107437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100859642029</t>
+    <t xml:space="preserve">0.416100889444351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045377492905</t>
+    <t xml:space="preserve">0.362045437097549</t>
   </si>
   <si>
     <t xml:space="preserve">0.365816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302618265152</t>
+    <t xml:space="preserve">0.36330258846283</t>
   </si>
   <si>
     <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360753297806</t>
+    <t xml:space="preserve">0.329360842704773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531253576279</t>
+    <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017010450363</t>
+    <t xml:space="preserve">0.357017070055008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446003437042</t>
+    <t xml:space="preserve">0.344446033239365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903423070908</t>
+    <t xml:space="preserve">0.33690345287323</t>
   </si>
   <si>
     <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703184604645</t>
+    <t xml:space="preserve">0.345703125</t>
   </si>
   <si>
     <t xml:space="preserve">0.372102320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930418968201</t>
+    <t xml:space="preserve">0.385930478572845</t>
   </si>
   <si>
     <t xml:space="preserve">0.353245764970779</t>
@@ -785,106 +785,106 @@
     <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873595476151</t>
+    <t xml:space="preserve">0.375873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359382152557</t>
+    <t xml:space="preserve">0.373359441757202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673357009888</t>
+    <t xml:space="preserve">0.384673327207565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39095875620842</t>
+    <t xml:space="preserve">0.390958845615387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393472999334335</t>
+    <t xml:space="preserve">0.39347305893898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557489395142</t>
+    <t xml:space="preserve">0.430557578802109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414134025574</t>
+    <t xml:space="preserve">0.449414044618607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699682235718</t>
+    <t xml:space="preserve">0.455699622631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955998420715</t>
+    <t xml:space="preserve">0.463955968618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181872367859</t>
+    <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332405328751</t>
+    <t xml:space="preserve">0.429332435131073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483027696609</t>
+    <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
     <t xml:space="preserve">0.425870031118393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257153749466</t>
+    <t xml:space="preserve">0.436257094144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719468355179</t>
+    <t xml:space="preserve">0.439719498157501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794809341431</t>
+    <t xml:space="preserve">0.432794749736786</t>
   </si>
   <si>
     <t xml:space="preserve">0.4189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558249473572</t>
+    <t xml:space="preserve">0.408558219671249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633530855179</t>
+    <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020623683929</t>
+    <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784093618393</t>
+    <t xml:space="preserve">0.387784063816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246438026428</t>
+    <t xml:space="preserve">0.391246527433395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095934867859</t>
+    <t xml:space="preserve">0.405095845460892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422407746315002</t>
+    <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644157171249</t>
+    <t xml:space="preserve">0.446644246578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106620788574</t>
+    <t xml:space="preserve">0.450106561183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45703136920929</t>
+    <t xml:space="preserve">0.457031279802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568875789642</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
     <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708842039108</t>
+    <t xml:space="preserve">0.394708871841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859464406967</t>
+    <t xml:space="preserve">0.380859345197678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934656381607</t>
+    <t xml:space="preserve">0.373934715986252</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085219144821</t>
@@ -893,73 +893,73 @@
     <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38432177901268</t>
+    <t xml:space="preserve">0.384321719408035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009878158569</t>
+    <t xml:space="preserve">0.367009907960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696007013321</t>
+    <t xml:space="preserve">0.340696036815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311093091965</t>
+    <t xml:space="preserve">0.339311122894287</t>
   </si>
   <si>
     <t xml:space="preserve">0.353160500526428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235781908035</t>
+    <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386344671249</t>
+    <t xml:space="preserve">0.332386374473572</t>
   </si>
   <si>
     <t xml:space="preserve">0.311612248420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314382135868073</t>
+    <t xml:space="preserve">0.314382165670395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838062763214</t>
+    <t xml:space="preserve">0.290838122367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984386920929</t>
+    <t xml:space="preserve">0.258984357118607</t>
   </si>
   <si>
     <t xml:space="preserve">0.278373628854752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.27283388376236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754274368286</t>
+    <t xml:space="preserve">0.261754244565964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289765954018</t>
+    <t xml:space="preserve">0.249289810657501</t>
   </si>
   <si>
     <t xml:space="preserve">0.243750020861626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2852982878685</t>
+    <t xml:space="preserve">0.285298347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683291196823</t>
+    <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
     <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758512973785</t>
+    <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143486499786</t>
+    <t xml:space="preserve">0.281143546104431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
     <t xml:space="preserve">0.303302615880966</t>
@@ -968,58 +968,58 @@
     <t xml:space="preserve">0.308842390775681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926119565964</t>
+    <t xml:space="preserve">0.337926179170609</t>
   </si>
   <si>
     <t xml:space="preserve">0.325461655855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921910762787</t>
+    <t xml:space="preserve">0.319921940565109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465924263</t>
+    <t xml:space="preserve">0.343465954065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547593355179</t>
+    <t xml:space="preserve">0.363547533750534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397060394287</t>
+    <t xml:space="preserve">0.377397090196609</t>
   </si>
   <si>
     <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001460552216</t>
+    <t xml:space="preserve">0.331001430749893</t>
   </si>
   <si>
     <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698185920715</t>
+    <t xml:space="preserve">0.349698156118393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850867986679</t>
+    <t xml:space="preserve">0.344850897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691798210144</t>
+    <t xml:space="preserve">0.322691768407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076682329178</t>
+    <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
     <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536937236786</t>
+    <t xml:space="preserve">0.318536996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072473526001</t>
+    <t xml:space="preserve">0.306072443723679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31715202331543</t>
+    <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3046875</t>
+    <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
     <t xml:space="preserve">0.297762811183929</t>
@@ -1028,37 +1028,37 @@
     <t xml:space="preserve">0.283913403749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288068205118179</t>
+    <t xml:space="preserve">0.288068234920502</t>
   </si>
   <si>
     <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294049263</t>
+    <t xml:space="preserve">0.267294079065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369300842285</t>
+    <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909105539322</t>
+    <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27006396651268</t>
+    <t xml:space="preserve">0.270063936710358</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223006486893</t>
+    <t xml:space="preserve">0.292223066091537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377837657928</t>
+    <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28945317864418</t>
+    <t xml:space="preserve">0.289453119039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809927940369</t>
+    <t xml:space="preserve">0.429810017347336</t>
   </si>
   <si>
     <t xml:space="preserve">0.399647802114487</t>
@@ -1067,91 +1067,91 @@
     <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026289701462</t>
+    <t xml:space="preserve">0.377026319503784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36194521188736</t>
+    <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485765695572</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453388214111</t>
+    <t xml:space="preserve">0.363453328609467</t>
   </si>
   <si>
     <t xml:space="preserve">0.380796551704407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010115861893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961445331573</t>
+    <t xml:space="preserve">0.364961475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880397319794</t>
+    <t xml:space="preserve">0.349880367517471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847960233688</t>
+    <t xml:space="preserve">0.343847990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339932918549</t>
+    <t xml:space="preserve">0.342339903116226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323699474335</t>
+    <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">0.352896600961685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34686416387558</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388514041901</t>
+    <t xml:space="preserve">0.351388454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307495832443</t>
+    <t xml:space="preserve">0.336307466030121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799349308014</t>
+    <t xml:space="preserve">0.334799319505692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372340202332</t>
+    <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
     <t xml:space="preserve">0.437350481748581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958677530289</t>
+    <t xml:space="preserve">0.410958707332611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431589365005</t>
+    <t xml:space="preserve">0.452431529760361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444891005754471</t>
+    <t xml:space="preserve">0.444890975952148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120803356171</t>
+    <t xml:space="preserve">0.441120713949203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728969335556</t>
+    <t xml:space="preserve">0.414728879928589</t>
   </si>
   <si>
     <t xml:space="preserve">0.403418153524399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
     <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877599716187</t>
+    <t xml:space="preserve">0.395877540111542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188385725021</t>
+    <t xml:space="preserve">0.407188445329666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501969337463</t>
+    <t xml:space="preserve">0.372501999139786</t>
   </si>
   <si>
     <t xml:space="preserve">0.366469532251358</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356106758118</t>
+    <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831726789474</t>
+    <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
     <t xml:space="preserve">0.370993852615356</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">0.360437154769897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977619171143</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
     <t xml:space="preserve">0.358929008245468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31670206785202</t>
+    <t xml:space="preserve">0.316702097654343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112903118134</t>
+    <t xml:space="preserve">0.300112962722778</t>
   </si>
   <si>
     <t xml:space="preserve">0.30162101984024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210184574127</t>
+    <t xml:space="preserve">0.31821021437645</t>
   </si>
   <si>
     <t xml:space="preserve">0.319718301296234</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258855104446</t>
+    <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33027508854866</t>
+    <t xml:space="preserve">0.330275058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783145666122</t>
+    <t xml:space="preserve">0.3317831158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337815552949905</t>
+    <t xml:space="preserve">0.337815582752228</t>
   </si>
   <si>
     <t xml:space="preserve">0.328766912221909</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129136562347</t>
+    <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685864210129</t>
+    <t xml:space="preserve">0.313685894012451</t>
   </si>
   <si>
     <t xml:space="preserve">0.322734504938126</t>
@@ -1235,31 +1235,31 @@
     <t xml:space="preserve">0.314438968896866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31917929649353</t>
+    <t xml:space="preserve">0.319179326295853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820011138916</t>
+    <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400130271912</t>
+    <t xml:space="preserve">0.333400160074234</t>
   </si>
   <si>
     <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32391956448555</t>
+    <t xml:space="preserve">0.323919594287872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858909368515</t>
+    <t xml:space="preserve">0.312858879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317688465118</t>
+    <t xml:space="preserve">0.292317628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798194646835</t>
+    <t xml:space="preserve">0.301798224449158</t>
   </si>
   <si>
     <t xml:space="preserve">0.316019088029861</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2907375395298</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837092876434</t>
+    <t xml:space="preserve">0.282837063074112</t>
   </si>
   <si>
     <t xml:space="preserve">0.287577360868454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676884412766</t>
+    <t xml:space="preserve">0.279676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516735553741</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096795082092</t>
+    <t xml:space="preserve">0.27809676527977</t>
   </si>
   <si>
     <t xml:space="preserve">0.270196348428726</t>
@@ -1295,43 +1295,43 @@
     <t xml:space="preserve">0.281256973743439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776437759399</t>
+    <t xml:space="preserve">0.271776407957077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417182207108</t>
+    <t xml:space="preserve">0.284417241811752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997271537781</t>
+    <t xml:space="preserve">0.285997241735458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477837324142</t>
+    <t xml:space="preserve">0.295477867126465</t>
   </si>
   <si>
     <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118641376495</t>
+    <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157509803772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040934324265</t>
+    <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140428066254</t>
+    <t xml:space="preserve">0.338140457868576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720487594604</t>
   </si>
   <si>
     <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980249404907</t>
+    <t xml:space="preserve">0.334980219602585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560308933258</t>
   </si>
   <si>
     <t xml:space="preserve">0.352361291646957</t>
@@ -1343,37 +1343,37 @@
     <t xml:space="preserve">0.291944772005081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237456560135</t>
+    <t xml:space="preserve">0.29023739695549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115599632263</t>
+    <t xml:space="preserve">0.285115569829941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822855472565</t>
+    <t xml:space="preserve">0.286822915077209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481110811234</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
     <t xml:space="preserve">0.298773884773254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408313989639</t>
+    <t xml:space="preserve">0.283408343791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27828648686409</t>
+    <t xml:space="preserve">0.278286516666412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288530230522156</t>
+    <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993861913681</t>
+    <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
     <t xml:space="preserve">0.273164659738541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579231023788</t>
+    <t xml:space="preserve">0.276579260826111</t>
   </si>
   <si>
     <t xml:space="preserve">0.269750088453293</t>
@@ -1385,58 +1385,58 @@
     <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457403898239</t>
+    <t xml:space="preserve">0.271457344293594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042862415314</t>
+    <t xml:space="preserve">0.268042832612991</t>
   </si>
   <si>
     <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293652027845383</t>
+    <t xml:space="preserve">0.29365199804306</t>
   </si>
   <si>
     <t xml:space="preserve">0.302188396453857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602967739105</t>
+    <t xml:space="preserve">0.305602997541428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310253381729</t>
+    <t xml:space="preserve">0.307310283184052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383020401001</t>
+    <t xml:space="preserve">0.324383050203323</t>
   </si>
   <si>
     <t xml:space="preserve">0.319261193275452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017509222031</t>
+    <t xml:space="preserve">0.309017449617386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31413933634758</t>
+    <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432080507278</t>
+    <t xml:space="preserve">0.312432110309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724794864655</t>
+    <t xml:space="preserve">0.310724824666977</t>
   </si>
   <si>
     <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829840660095</t>
+    <t xml:space="preserve">0.29982978105545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343445777893</t>
+    <t xml:space="preserve">0.296343386173248</t>
   </si>
   <si>
     <t xml:space="preserve">0.303316235542297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289370596408844</t>
+    <t xml:space="preserve">0.289370656013489</t>
   </si>
   <si>
     <t xml:space="preserve">0.287627458572388</t>
@@ -1448,46 +1448,46 @@
     <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304652452468872</t>
+    <t xml:space="preserve">0.304652392864227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302870839834213</t>
+    <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
     <t xml:space="preserve">0.306434035301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089227199554</t>
+    <t xml:space="preserve">0.301089257001877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836504936218</t>
+    <t xml:space="preserve">0.286836475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618087768555</t>
+    <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399700403214</t>
+    <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307614564896</t>
+    <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962866067886</t>
+    <t xml:space="preserve">0.293962836265564</t>
   </si>
   <si>
     <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273309469223</t>
+    <t xml:space="preserve">0.283273279666901</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491696834564</t>
+    <t xml:space="preserve">0.281491726636887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29218128323555</t>
+    <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
     <t xml:space="preserve">0.295372009277344</t>
@@ -1502,76 +1502,76 @@
     <t xml:space="preserve">0.291725426912308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488450288773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308135002851486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781585216522</t>
+    <t xml:space="preserve">0.3117815554142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317251414060593</t>
+    <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074720144272</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604861497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191101551056</t>
+    <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33183765411377</t>
+    <t xml:space="preserve">0.331837683916092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660960197449</t>
+    <t xml:space="preserve">0.333660989999771</t>
   </si>
   <si>
     <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32454451918602</t>
+    <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158191680908</t>
+    <t xml:space="preserve">0.324158161878586</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322295218706131</t>
+    <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610053777695</t>
+    <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021194458008</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
     <t xml:space="preserve">0.320432245731354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117321252823</t>
+    <t xml:space="preserve">0.311117351055145</t>
   </si>
   <si>
     <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335336029529572</t>
+    <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316706269979477</t>
+    <t xml:space="preserve">0.316706240177155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569272756577</t>
+    <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340924978256226</t>
+    <t xml:space="preserve">0.340925008058548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473056554794</t>
+    <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
     <t xml:space="preserve">0.307391405105591</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344650954008102</t>
+    <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
     <t xml:space="preserve">0.337199002504349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376899957657</t>
+    <t xml:space="preserve">0.348376929759979</t>
   </si>
   <si>
     <t xml:space="preserve">0.370732635259628</t>
@@ -1598,31 +1598,31 @@
     <t xml:space="preserve">0.398677319288254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170081615448</t>
+    <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407992213964462</t>
+    <t xml:space="preserve">0.40799218416214</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40985518693924</t>
+    <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540292263031</t>
+    <t xml:space="preserve">0.400540262460709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3912253677845</t>
+    <t xml:space="preserve">0.391225397586823</t>
   </si>
   <si>
     <t xml:space="preserve">0.3930883705616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362454414368</t>
+    <t xml:space="preserve">0.389362424612045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458611011505</t>
+    <t xml:space="preserve">0.374458581209183</t>
   </si>
   <si>
     <t xml:space="preserve">0.376321583986282</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869662284851</t>
+    <t xml:space="preserve">0.368869692087173</t>
   </si>
   <si>
     <t xml:space="preserve">0.378184527158737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951343536377</t>
+    <t xml:space="preserve">0.394951373338699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407650500535965</t>
+    <t xml:space="preserve">0.407650470733643</t>
   </si>
   <si>
     <t xml:space="preserve">0.392482101917267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394378125667572</t>
+    <t xml:space="preserve">0.394378155469894</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754417181015</t>
@@ -1767,6 +1767,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.579999983310699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595000028610229</t>
   </si>
 </sst>
 </file>
@@ -68405,7 +68408,7 @@
     </row>
     <row r="2551">
       <c r="A2551" s="1" t="n">
-        <v>46037.5849537037</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B2551" t="n">
         <v>52000</v>
@@ -68426,6 +68429,32 @@
         <v>584</v>
       </c>
       <c r="H2551" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" s="1" t="n">
+        <v>46038.6865162037</v>
+      </c>
+      <c r="B2552" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C2552" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="D2552" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="E2552" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="F2552" t="n">
+        <v>0.595000028610229</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>585</v>
+      </c>
+      <c r="H2552" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851577401161</t>
+    <t xml:space="preserve">0.1728515625</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594485640526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16405189037323</t>
+    <t xml:space="preserve">0.164051845669746</t>
   </si>
   <si>
     <t xml:space="preserve">0.16970881819725</t>
@@ -62,25 +62,25 @@
     <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14330966770649</t>
+    <t xml:space="preserve">0.143309682607651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783760309219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195335149765</t>
+    <t xml:space="preserve">0.145195305347443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737930417061</t>
+    <t xml:space="preserve">0.1527379155159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153366476297379</t>
+    <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789439678192</t>
+    <t xml:space="preserve">0.150789424777031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1464524269104</t>
+    <t xml:space="preserve">0.146452412009239</t>
   </si>
   <si>
     <t xml:space="preserve">0.139852643013</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">0.142052546143532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909816741943</t>
+    <t xml:space="preserve">0.138909786939621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151103720068932</t>
+    <t xml:space="preserve">0.151103690266609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337349176407</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817486286163</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16342331469059</t>
+    <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
     <t xml:space="preserve">0.157137811183929</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909101366997</t>
+    <t xml:space="preserve">0.160909131169319</t>
   </si>
   <si>
     <t xml:space="preserve">0.158960595726967</t>
@@ -131,55 +131,55 @@
     <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251413464546</t>
+    <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965939760208</t>
+    <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937528014183</t>
+    <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565373420715</t>
+    <t xml:space="preserve">0.188565358519554</t>
   </si>
   <si>
     <t xml:space="preserve">0.192650929093361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708087921143</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165492653847</t>
+    <t xml:space="preserve">0.184165507555008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651324033737</t>
+    <t xml:space="preserve">0.181651279330254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136365532875</t>
+    <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678960800171</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073542237282</t>
+    <t xml:space="preserve">0.201073572039604</t>
   </si>
   <si>
     <t xml:space="preserve">0.196736514568329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222271442413</t>
+    <t xml:space="preserve">0.194222316145897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137095808983</t>
+    <t xml:space="preserve">0.179137080907822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279825210571</t>
+    <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834539294243</t>
+    <t xml:space="preserve">0.169834524393082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451711535454</t>
+    <t xml:space="preserve">0.168451726436615</t>
   </si>
   <si>
     <t xml:space="preserve">0.16279473900795</t>
@@ -188,121 +188,121 @@
     <t xml:space="preserve">0.151606544852257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566029191017</t>
+    <t xml:space="preserve">0.166566044092178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074928283691</t>
+    <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109399437904</t>
+    <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995037078857</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640635967255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051145195961</t>
+    <t xml:space="preserve">0.186051174998283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936782836914</t>
+    <t xml:space="preserve">0.187936812639236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536946773529</t>
+    <t xml:space="preserve">0.18353696167469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18171414732933</t>
+    <t xml:space="preserve">0.181714117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194604873657</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160280555486679</t>
+    <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080972790718</t>
+    <t xml:space="preserve">0.147080987691879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480838656425</t>
+    <t xml:space="preserve">0.151480853557587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338079452515</t>
+    <t xml:space="preserve">0.148338064551353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566774368286</t>
+    <t xml:space="preserve">0.144566789269447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394917845726</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183246135712</t>
+    <t xml:space="preserve">0.165183261036873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651644468307</t>
+    <t xml:space="preserve">0.170651659369469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223001718521</t>
+    <t xml:space="preserve">0.172223046422005</t>
   </si>
   <si>
     <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507819652557</t>
+    <t xml:space="preserve">0.200507804751396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.19359378516674</t>
   </si>
   <si>
     <t xml:space="preserve">0.17813141644001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765291452408</t>
+    <t xml:space="preserve">0.190765276551247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010659337044</t>
+    <t xml:space="preserve">0.201010704040527</t>
   </si>
   <si>
     <t xml:space="preserve">0.194850862026215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770955920219</t>
+    <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19987927377224</t>
+    <t xml:space="preserve">0.199879243969917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078871369362</t>
+    <t xml:space="preserve">0.213078811764717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21678726375103</t>
+    <t xml:space="preserve">0.216787293553352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232564002275467</t>
+    <t xml:space="preserve">0.232563957571983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220915198326</t>
+    <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420468091965</t>
+    <t xml:space="preserve">0.251420527696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134249210358</t>
+    <t xml:space="preserve">0.267134219408035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305390357971</t>
+    <t xml:space="preserve">0.275305449962616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29039067029953</t>
+    <t xml:space="preserve">0.290390610694885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561781644821</t>
+    <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705956697464</t>
+    <t xml:space="preserve">0.257705986499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157316923141</t>
+    <t xml:space="preserve">0.260157346725464</t>
   </si>
   <si>
     <t xml:space="preserve">0.250226199626923</t>
@@ -311,91 +311,91 @@
     <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809310555458</t>
+    <t xml:space="preserve">0.242809325456619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249282240868</t>
+    <t xml:space="preserve">0.243249297142029</t>
   </si>
   <si>
     <t xml:space="preserve">0.243375033140182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421153664589</t>
+    <t xml:space="preserve">0.22942116856575</t>
   </si>
   <si>
     <t xml:space="preserve">0.23382106423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564658045769</t>
+    <t xml:space="preserve">0.210564643144608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20691904425621</t>
+    <t xml:space="preserve">0.206919029355049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821794509888</t>
+    <t xml:space="preserve">0.211821779608727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741843700409</t>
+    <t xml:space="preserve">0.20874185860157</t>
   </si>
   <si>
     <t xml:space="preserve">0.237592324614525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134949684143</t>
+    <t xml:space="preserve">0.245134964585304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803966522217</t>
+    <t xml:space="preserve">0.2308040112257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535560727119</t>
+    <t xml:space="preserve">0.227535530924797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706657171249</t>
+    <t xml:space="preserve">0.235706672072411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278409361839</t>
+    <t xml:space="preserve">0.226278454065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135694861412</t>
+    <t xml:space="preserve">0.223135679960251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850146651268</t>
+    <t xml:space="preserve">0.216850131750107</t>
   </si>
   <si>
     <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141739368439</t>
+    <t xml:space="preserve">0.213141679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199248433113</t>
+    <t xml:space="preserve">0.201199263334274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279094934464</t>
+    <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793338060379</t>
+    <t xml:space="preserve">0.20679335296154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164807081223</t>
+    <t xml:space="preserve">0.2061647772789</t>
   </si>
   <si>
     <t xml:space="preserve">0.207421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804666996002</t>
+    <t xml:space="preserve">0.208804711699486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947426199913</t>
+    <t xml:space="preserve">0.211947500705719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649893283844</t>
+    <t xml:space="preserve">0.22564984858036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867214560509</t>
+    <t xml:space="preserve">0.219867199659348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810040831566</t>
+    <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
     <t xml:space="preserve">0.229484051465988</t>
@@ -404,25 +404,25 @@
     <t xml:space="preserve">0.234386742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22451850771904</t>
+    <t xml:space="preserve">0.224518492817879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21999292075634</t>
+    <t xml:space="preserve">0.219992890954018</t>
   </si>
   <si>
     <t xml:space="preserve">0.219741463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912984848022</t>
+    <t xml:space="preserve">0.216912999749184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306821107864</t>
+    <t xml:space="preserve">0.231306836009026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038705945015</t>
+    <t xml:space="preserve">0.21703876554966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324254155159</t>
+    <t xml:space="preserve">0.22332426905632</t>
   </si>
   <si>
     <t xml:space="preserve">0.297178983688354</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">0.351988643407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465128004550934</t>
+    <t xml:space="preserve">0.465127915143967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582413673401</t>
+    <t xml:space="preserve">0.545582473278046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070301771164</t>
+    <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843007802963</t>
+    <t xml:space="preserve">0.436843067407608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072201967239</t>
+    <t xml:space="preserve">0.42207208275795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987272262573</t>
+    <t xml:space="preserve">0.395987302064896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559650421143</t>
+    <t xml:space="preserve">0.364559680223465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215236902237</t>
+    <t xml:space="preserve">0.414215207099915</t>
   </si>
   <si>
     <t xml:space="preserve">0.367388159036636</t>
@@ -461,49 +461,49 @@
     <t xml:space="preserve">0.373987972736359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331685781479</t>
+    <t xml:space="preserve">0.346331745386124</t>
   </si>
   <si>
     <t xml:space="preserve">0.3259037733078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904063940048</t>
+    <t xml:space="preserve">0.314904093742371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532363891602</t>
+    <t xml:space="preserve">0.326532334089279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389209747314</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818202733994</t>
+    <t xml:space="preserve">0.321818262338638</t>
   </si>
   <si>
     <t xml:space="preserve">0.348845899105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303288936615</t>
+    <t xml:space="preserve">0.341303318738937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32684662938118</t>
+    <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361163139343</t>
+    <t xml:space="preserve">0.318361192941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189671754837</t>
+    <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132058382034</t>
+    <t xml:space="preserve">0.333132088184357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989314079285</t>
+    <t xml:space="preserve">0.329989373683929</t>
   </si>
   <si>
     <t xml:space="preserve">0.317418336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332356452942</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
     <t xml:space="preserve">0.314275622367859</t>
@@ -515,106 +515,106 @@
     <t xml:space="preserve">0.33470356464386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046897649765</t>
+    <t xml:space="preserve">0.318046867847443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789835691452</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417986631393</t>
+    <t xml:space="preserve">0.328418016433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075294494629</t>
+    <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32810378074646</t>
+    <t xml:space="preserve">0.328103691339493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704615354538</t>
+    <t xml:space="preserve">0.301704525947571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504257678986</t>
+    <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069935560226</t>
+    <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561110973358</t>
+    <t xml:space="preserve">0.320561081171036</t>
   </si>
   <si>
     <t xml:space="preserve">0.3255894780159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274191617966</t>
+    <t xml:space="preserve">0.358274161815643</t>
   </si>
   <si>
     <t xml:space="preserve">0.339417636394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046226978302</t>
+    <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
     <t xml:space="preserve">0.319304019212723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846279144287</t>
+    <t xml:space="preserve">0.337846338748932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589887857437</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327789396047592</t>
+    <t xml:space="preserve">0.327789485454559</t>
   </si>
   <si>
     <t xml:space="preserve">0.389701724052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588106870651</t>
+    <t xml:space="preserve">0.369588077068329</t>
   </si>
   <si>
     <t xml:space="preserve">0.368959546089172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216637849808</t>
+    <t xml:space="preserve">0.370216697454453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616824150085</t>
+    <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
     <t xml:space="preserve">0.370845228433609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074623823166</t>
+    <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788784980774</t>
+    <t xml:space="preserve">0.349788695573807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502826929092</t>
+    <t xml:space="preserve">0.354502856731415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073893547058</t>
+    <t xml:space="preserve">0.36707392334938</t>
   </si>
   <si>
     <t xml:space="preserve">0.388758927583694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587406396866</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759218215942</t>
+    <t xml:space="preserve">0.37775930762291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130746841431</t>
+    <t xml:space="preserve">0.377130717039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187570333481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444893121719</t>
+    <t xml:space="preserve">0.377444982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929688692093</t>
+    <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
     <t xml:space="preserve">0.414843797683716</t>
@@ -623,157 +623,157 @@
     <t xml:space="preserve">0.392215937376022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376816362142563</t>
+    <t xml:space="preserve">0.376816481351852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386559009552002</t>
+    <t xml:space="preserve">0.386558949947357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413314342499</t>
+    <t xml:space="preserve">0.471413344144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357310533524</t>
+    <t xml:space="preserve">0.439357250928879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556818723679</t>
+    <t xml:space="preserve">0.452556908130646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700293302536</t>
+    <t xml:space="preserve">0.433700263500214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100188970566</t>
+    <t xml:space="preserve">0.438100218772888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271389722824</t>
+    <t xml:space="preserve">0.446271359920502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43998584151268</t>
+    <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
     <t xml:space="preserve">0.422386348247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900591373444</t>
+    <t xml:space="preserve">0.424900621175766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129316091537</t>
+    <t xml:space="preserve">0.421129286289215</t>
   </si>
   <si>
     <t xml:space="preserve">0.409815430641174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044095754623</t>
+    <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558189868927</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586676120758</t>
+    <t xml:space="preserve">0.41358670592308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40227273106575</t>
+    <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443201541901</t>
+    <t xml:space="preserve">0.432443231344223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357921600342</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613642215729</t>
+    <t xml:space="preserve">0.462613672018051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414774894714</t>
+    <t xml:space="preserve">0.427414804697037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758547544479</t>
+    <t xml:space="preserve">0.399758487939835</t>
   </si>
   <si>
     <t xml:space="preserve">0.418615132570267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643589019775</t>
+    <t xml:space="preserve">0.423643559217453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41107240319252</t>
+    <t xml:space="preserve">0.411072432994843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501396179199</t>
+    <t xml:space="preserve">0.398501455783844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404787003993988</t>
+    <t xml:space="preserve">0.404786914587021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159173488617</t>
+    <t xml:space="preserve">0.382159054279327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416175842285</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444542884827</t>
+    <t xml:space="preserve">0.388444632291794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529852628708</t>
+    <t xml:space="preserve">0.40352988243103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186079978943</t>
+    <t xml:space="preserve">0.431186139583588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872164726257</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301247119904</t>
+    <t xml:space="preserve">0.407301127910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730091094971</t>
+    <t xml:space="preserve">0.39473021030426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329614162445</t>
+    <t xml:space="preserve">0.4123295545578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015639305115</t>
+    <t xml:space="preserve">0.401015609502792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100859642029</t>
+    <t xml:space="preserve">0.416100919246674</t>
   </si>
   <si>
     <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816831588745</t>
+    <t xml:space="preserve">0.365816801786423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302648067474</t>
+    <t xml:space="preserve">0.363302558660507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674698352814</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360812902451</t>
+    <t xml:space="preserve">0.329360842704773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531283378601</t>
+    <t xml:space="preserve">0.359531223773956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017040252686</t>
+    <t xml:space="preserve">0.357017129659653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446003437042</t>
+    <t xml:space="preserve">0.344446092844009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903423070908</t>
+    <t xml:space="preserve">0.33690345287323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160485029221</t>
+    <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703154802322</t>
+    <t xml:space="preserve">0.345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102290391922</t>
+    <t xml:space="preserve">0.372102349996567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930448770523</t>
+    <t xml:space="preserve">0.385930389165878</t>
   </si>
   <si>
     <t xml:space="preserve">0.353245735168457</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387778997421</t>
+    <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873565673828</t>
+    <t xml:space="preserve">0.375873625278473</t>
   </si>
   <si>
     <t xml:space="preserve">0.373359382152557</t>
@@ -794,22 +794,22 @@
     <t xml:space="preserve">0.384673327207565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958845615387</t>
+    <t xml:space="preserve">0.390958815813065</t>
   </si>
   <si>
     <t xml:space="preserve">0.393473029136658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557638406754</t>
+    <t xml:space="preserve">0.430557548999786</t>
   </si>
   <si>
     <t xml:space="preserve">0.449414134025574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699622631073</t>
+    <t xml:space="preserve">0.455699652433395</t>
   </si>
   <si>
     <t xml:space="preserve">0.463955998420715</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332435131073</t>
+    <t xml:space="preserve">0.429332375526428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415482968091965</t>
+    <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870090723038</t>
+    <t xml:space="preserve">0.425870031118393</t>
   </si>
   <si>
     <t xml:space="preserve">0.436257094144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719438552856</t>
+    <t xml:space="preserve">0.439719468355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794779539108</t>
+    <t xml:space="preserve">0.432794809341431</t>
   </si>
   <si>
     <t xml:space="preserve">0.418945372104645</t>
@@ -842,40 +842,40 @@
     <t xml:space="preserve">0.401633530855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020593881607</t>
+    <t xml:space="preserve">0.412020683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784063816071</t>
+    <t xml:space="preserve">0.387784153223038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246467828751</t>
+    <t xml:space="preserve">0.391246497631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095875263214</t>
+    <t xml:space="preserve">0.405095905065536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
+    <t xml:space="preserve">0.422407746315002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644216775894</t>
+    <t xml:space="preserve">0.446644246578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278376579285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106531381607</t>
+    <t xml:space="preserve">0.450106590986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031309604645</t>
+    <t xml:space="preserve">0.457031279802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568875789642</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171216249466</t>
+    <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708812236786</t>
+    <t xml:space="preserve">0.394708842039108</t>
   </si>
   <si>
     <t xml:space="preserve">0.380859375</t>
@@ -887,19 +887,19 @@
     <t xml:space="preserve">0.360085219144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472371578217</t>
+    <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
     <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009907960892</t>
+    <t xml:space="preserve">0.367009997367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696066617966</t>
+    <t xml:space="preserve">0.340696007013321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311063289642</t>
+    <t xml:space="preserve">0.339311093091965</t>
   </si>
   <si>
     <t xml:space="preserve">0.353160530328751</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">0.311612248420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314382135868073</t>
+    <t xml:space="preserve">0.314382076263428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838092565536</t>
+    <t xml:space="preserve">0.290838122367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984386920929</t>
+    <t xml:space="preserve">0.258984357118607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373539447784</t>
+    <t xml:space="preserve">0.278373599052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139188289642</t>
   </si>
   <si>
     <t xml:space="preserve">0.272833794355392</t>
@@ -935,37 +935,37 @@
     <t xml:space="preserve">0.261754244565964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289810657501</t>
+    <t xml:space="preserve">0.24928979575634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750005960464</t>
+    <t xml:space="preserve">0.243750035762787</t>
   </si>
   <si>
     <t xml:space="preserve">0.2852982878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683231592178</t>
+    <t xml:space="preserve">0.286683291196823</t>
   </si>
   <si>
     <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758542776108</t>
+    <t xml:space="preserve">0.279758512973785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143486499786</t>
+    <t xml:space="preserve">0.281143456697464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302526473999</t>
+    <t xml:space="preserve">0.303302586078644</t>
   </si>
   <si>
     <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926149368286</t>
+    <t xml:space="preserve">0.337926119565964</t>
   </si>
   <si>
     <t xml:space="preserve">0.325461655855179</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">0.319921880960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465894460678</t>
+    <t xml:space="preserve">0.343465924263</t>
   </si>
   <si>
     <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397030591965</t>
+    <t xml:space="preserve">0.377397090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231513500214</t>
+    <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001460552216</t>
+    <t xml:space="preserve">0.331001430749893</t>
   </si>
   <si>
     <t xml:space="preserve">0.336541205644608</t>
@@ -1001,52 +1001,52 @@
     <t xml:space="preserve">0.322691768407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076682329178</t>
+    <t xml:space="preserve">0.324076741933823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306824684143</t>
+    <t xml:space="preserve">0.321306854486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536907434464</t>
+    <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072473526001</t>
+    <t xml:space="preserve">0.306072443723679</t>
   </si>
   <si>
     <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3046875</t>
+    <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762751579285</t>
+    <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
     <t xml:space="preserve">0.283913344144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288068175315857</t>
+    <t xml:space="preserve">0.288068234920502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524191617966</t>
+    <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294019460678</t>
+    <t xml:space="preserve">0.267294049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369271039963</t>
+    <t xml:space="preserve">0.260369300842285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909105539322</t>
+    <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063906908035</t>
+    <t xml:space="preserve">0.270063936710358</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223036289215</t>
+    <t xml:space="preserve">0.292223066091537</t>
   </si>
   <si>
     <t xml:space="preserve">0.296377867460251</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809957742691</t>
+    <t xml:space="preserve">0.429809987545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647802114487</t>
+    <t xml:space="preserve">0.399647861719131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337075710297</t>
+    <t xml:space="preserve">0.388337045907974</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">0.361945271492004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36948573589325</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453328609467</t>
+    <t xml:space="preserve">0.363453358411789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380796581506729</t>
@@ -1082,67 +1082,67 @@
     <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961475133896</t>
+    <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880367517471</t>
+    <t xml:space="preserve">0.349880427122116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847930431366</t>
+    <t xml:space="preserve">0.343847990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339903116226</t>
+    <t xml:space="preserve">0.342339843511581</t>
   </si>
   <si>
     <t xml:space="preserve">0.339323669672012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896571159363</t>
+    <t xml:space="preserve">0.352896600961685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864134073257</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388454437256</t>
+    <t xml:space="preserve">0.351388484239578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307466030121</t>
+    <t xml:space="preserve">0.336307436227798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799319505692</t>
+    <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372310400009</t>
+    <t xml:space="preserve">0.348372280597687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350481748581</t>
+    <t xml:space="preserve">0.437350451946259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958647727966</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431529760361</t>
+    <t xml:space="preserve">0.452431559562683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444890975952148</t>
+    <t xml:space="preserve">0.444891035556793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120743751526</t>
+    <t xml:space="preserve">0.441120773553848</t>
   </si>
   <si>
     <t xml:space="preserve">0.414728909730911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418153524399</t>
+    <t xml:space="preserve">0.403418183326721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107307910919</t>
+    <t xml:space="preserve">0.392107337713242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566843509674</t>
+    <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877569913864</t>
+    <t xml:space="preserve">0.395877599716187</t>
   </si>
   <si>
     <t xml:space="preserve">0.407188385725021</t>
@@ -1154,103 +1154,103 @@
     <t xml:space="preserve">0.366469532251358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35440468788147</t>
+    <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356106758118</t>
+    <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831726789474</t>
+    <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993852615356</t>
+    <t xml:space="preserve">0.370993822813034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437154769897</t>
+    <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
     <t xml:space="preserve">0.367977619171143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929038047791</t>
+    <t xml:space="preserve">0.358929008245468</t>
   </si>
   <si>
     <t xml:space="preserve">0.316702097654343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112932920456</t>
+    <t xml:space="preserve">0.300112903118134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30162101984024</t>
+    <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210184574127</t>
+    <t xml:space="preserve">0.31821021437645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718301296234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32424259185791</t>
+    <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258795499802</t>
+    <t xml:space="preserve">0.327258825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330274969339371</t>
+    <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3317831158638</t>
+    <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
     <t xml:space="preserve">0.337815552949905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766942024231</t>
+    <t xml:space="preserve">0.328766912221909</t>
   </si>
   <si>
     <t xml:space="preserve">0.30916154384613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653397321701</t>
+    <t xml:space="preserve">0.307653427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129076957703</t>
+    <t xml:space="preserve">0.303129136562347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685864210129</t>
+    <t xml:space="preserve">0.313685923814774</t>
   </si>
   <si>
     <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599147558212</t>
+    <t xml:space="preserve">0.317599207162857</t>
   </si>
   <si>
     <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314438939094543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319179326295853</t>
+    <t xml:space="preserve">0.319179266691208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820011138916</t>
+    <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400189876556</t>
+    <t xml:space="preserve">0.333400100469589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759385824203</t>
+    <t xml:space="preserve">0.320759415626526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32391956448555</t>
+    <t xml:space="preserve">0.323919504880905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858909368515</t>
+    <t xml:space="preserve">0.312858879566193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378373384476</t>
+    <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
     <t xml:space="preserve">0.292317658662796</t>
@@ -1259,67 +1259,67 @@
     <t xml:space="preserve">0.301798224449158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019058227539</t>
+    <t xml:space="preserve">0.316019117832184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218135118484</t>
+    <t xml:space="preserve">0.300218194723129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638015985489</t>
+    <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
     <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837063074112</t>
+    <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577390670776</t>
+    <t xml:space="preserve">0.287577360868454</t>
   </si>
   <si>
     <t xml:space="preserve">0.279676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096795082092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196348428726</t>
+    <t xml:space="preserve">0.270196318626404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257033348083</t>
+    <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776467561722</t>
+    <t xml:space="preserve">0.271776407957077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417182207108</t>
+    <t xml:space="preserve">0.28441721200943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997301340103</t>
+    <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477867126465</t>
+    <t xml:space="preserve">0.295477896928787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057926654816</t>
+    <t xml:space="preserve">0.297057896852493</t>
   </si>
   <si>
     <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157450199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040844917297</t>
+    <t xml:space="preserve">0.34604087471962</t>
   </si>
   <si>
     <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720487594604</t>
+    <t xml:space="preserve">0.339720517396927</t>
   </si>
   <si>
     <t xml:space="preserve">0.341300636529922</t>
@@ -1331,40 +1331,40 @@
     <t xml:space="preserve">0.336560368537903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.35236132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359283685684</t>
+    <t xml:space="preserve">0.295359313488007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944742202759</t>
+    <t xml:space="preserve">0.291944712400436</t>
   </si>
   <si>
     <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115629434586</t>
+    <t xml:space="preserve">0.285115599632263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822855472565</t>
+    <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
     <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29877382516861</t>
+    <t xml:space="preserve">0.298773854970932</t>
   </si>
   <si>
     <t xml:space="preserve">0.283408343791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27828648686409</t>
+    <t xml:space="preserve">0.278286516666412</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530170917511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993802309036</t>
+    <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
     <t xml:space="preserve">0.273164689540863</t>
@@ -1373,58 +1373,58 @@
     <t xml:space="preserve">0.276579201221466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750118255615</t>
+    <t xml:space="preserve">0.269750148057938</t>
   </si>
   <si>
     <t xml:space="preserve">0.281701058149338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871945381165</t>
+    <t xml:space="preserve">0.274871975183487</t>
   </si>
   <si>
     <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042832612991</t>
+    <t xml:space="preserve">0.268042862415314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895741701126</t>
+    <t xml:space="preserve">0.303895652294159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293652027845383</t>
+    <t xml:space="preserve">0.293651968240738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188396453857</t>
+    <t xml:space="preserve">0.30218842625618</t>
   </si>
   <si>
     <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310283184052</t>
+    <t xml:space="preserve">0.307310253381729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324382990598679</t>
+    <t xml:space="preserve">0.324383050203323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261193275452</t>
+    <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017539024353</t>
+    <t xml:space="preserve">0.309017479419708</t>
   </si>
   <si>
     <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432050704956</t>
+    <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724824666977</t>
+    <t xml:space="preserve">0.310724794864655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310288995504379</t>
+    <t xml:space="preserve">0.310288965702057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829840660095</t>
+    <t xml:space="preserve">0.29982978105545</t>
   </si>
   <si>
     <t xml:space="preserve">0.296343415975571</t>
@@ -1436,49 +1436,49 @@
     <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28762748837471</t>
+    <t xml:space="preserve">0.287627428770065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086643218994</t>
+    <t xml:space="preserve">0.298086583614349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560336828232</t>
+    <t xml:space="preserve">0.313560396432877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304652392864227</t>
+    <t xml:space="preserve">0.30465242266655</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306434005498886</t>
+    <t xml:space="preserve">0.306433975696564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089257001877</t>
+    <t xml:space="preserve">0.301089197397232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836445331573</t>
+    <t xml:space="preserve">0.286836504936218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618087768555</t>
+    <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
     <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307644367218</t>
+    <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962836265564</t>
+    <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054862499237</t>
+    <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273279666901</t>
+    <t xml:space="preserve">0.283273309469223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27971014380455</t>
+    <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
     <t xml:space="preserve">0.281491726636887</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">0.29218128323555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902150630951</t>
+    <t xml:space="preserve">0.289902120828629</t>
   </si>
   <si>
     <t xml:space="preserve">0.302665114402771</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">0.291725397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304488450288773</t>
+    <t xml:space="preserve">0.30448842048645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308135002851486</t>
+    <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3117815554142</t>
+    <t xml:space="preserve">0.311781585216522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31725138425827</t>
+    <t xml:space="preserve">0.317251414060593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331837683916092</t>
+    <t xml:space="preserve">0.33183765411377</t>
   </si>
   <si>
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897936820984</t>
+    <t xml:space="preserve">0.320897996425629</t>
   </si>
   <si>
     <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158161878586</t>
+    <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
@@ -1544,61 +1544,61 @@
     <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021164655685</t>
+    <t xml:space="preserve">0.326021134853363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432245731354</t>
+    <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117351055145</t>
+    <t xml:space="preserve">0.311117321252823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309254318475723</t>
+    <t xml:space="preserve">0.309254348278046</t>
   </si>
   <si>
     <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316706240177155</t>
+    <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569242954254</t>
+    <t xml:space="preserve">0.318569272756577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340925008058548</t>
+    <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473086357117</t>
+    <t xml:space="preserve">0.333473056554794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391405105591</t>
+    <t xml:space="preserve">0.307391375303268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353965818881989</t>
+    <t xml:space="preserve">0.353965848684311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34465092420578</t>
+    <t xml:space="preserve">0.344650954008102</t>
   </si>
   <si>
     <t xml:space="preserve">0.337199002504349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376929759979</t>
+    <t xml:space="preserve">0.348376899957657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732635259628</t>
+    <t xml:space="preserve">0.370732605457306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677319288254</t>
+    <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170051813126</t>
+    <t xml:space="preserve">0.419170022010803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40799218416214</t>
+    <t xml:space="preserve">0.407992154359818</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
@@ -1607,40 +1607,40 @@
     <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540262460709</t>
+    <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
     <t xml:space="preserve">0.391225397586823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3930883705616</t>
+    <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362424612045</t>
+    <t xml:space="preserve">0.389362394809723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458581209183</t>
+    <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376321583986282</t>
+    <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372595608234406</t>
+    <t xml:space="preserve">0.372595638036728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363280713558197</t>
+    <t xml:space="preserve">0.363280683755875</t>
   </si>
   <si>
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869692087173</t>
+    <t xml:space="preserve">0.368869632482529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378184527158737</t>
+    <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951373338699</t>
+    <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">0.392482101917267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394378155469894</t>
+    <t xml:space="preserve">0.394378125667572</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170202970505</t>
+    <t xml:space="preserve">0.398170232772827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274209022522</t>
+    <t xml:space="preserve">0.396274149417877</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097760915756</t>
+    <t xml:space="preserve">0.409097731113434</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605693340302</t>
+    <t xml:space="preserve">0.422605663537979</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -68489,7 +68489,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6190509259</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>20000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994336605072</t>
+    <t xml:space="preserve">0.175994321703911</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622867584229</t>
+    <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851547598839</t>
+    <t xml:space="preserve">0.172851592302322</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594455838203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051845669746</t>
+    <t xml:space="preserve">0.164051875472069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16970881819725</t>
+    <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966625332832</t>
+    <t xml:space="preserve">0.148966655135155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309682607651</t>
+    <t xml:space="preserve">0.143309652805328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783760309219</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195335149765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737930417061</t>
+    <t xml:space="preserve">0.1527379155159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15336649119854</t>
+    <t xml:space="preserve">0.153366476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789439678192</t>
+    <t xml:space="preserve">0.15078940987587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146452412009239</t>
+    <t xml:space="preserve">0.146452397108078</t>
   </si>
   <si>
     <t xml:space="preserve">0.139852628111839</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">0.139915496110916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052575945854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909816741943</t>
+    <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17033739387989</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817456483841</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423284888268</t>
+    <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137811183929</t>
+    <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
     <t xml:space="preserve">0.154623597860336</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909131169319</t>
+    <t xml:space="preserve">0.160909101366997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960595726967</t>
+    <t xml:space="preserve">0.158960565924644</t>
   </si>
   <si>
     <t xml:space="preserve">0.177314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251428365707</t>
+    <t xml:space="preserve">0.177251443266869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965939760208</t>
+    <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
     <t xml:space="preserve">0.165937498211861</t>
@@ -143,103 +143,103 @@
     <t xml:space="preserve">0.188565358519554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650929093361</t>
+    <t xml:space="preserve">0.192650958895683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708102822304</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165507555008</t>
+    <t xml:space="preserve">0.184165522456169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651294231415</t>
+    <t xml:space="preserve">0.181651309132576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136380434036</t>
+    <t xml:space="preserve">0.201136365532875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678975701332</t>
+    <t xml:space="preserve">0.208679005503654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073542237282</t>
+    <t xml:space="preserve">0.201073527336121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736499667168</t>
+    <t xml:space="preserve">0.196736544370651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222331047058</t>
+    <t xml:space="preserve">0.194222316145897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137080907822</t>
+    <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
     <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834524393082</t>
+    <t xml:space="preserve">0.169834539294243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451726436615</t>
+    <t xml:space="preserve">0.168451741337776</t>
   </si>
   <si>
     <t xml:space="preserve">0.162794768810272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606559753418</t>
+    <t xml:space="preserve">0.151606529951096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566073894501</t>
+    <t xml:space="preserve">0.16656605899334</t>
   </si>
   <si>
     <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109384536743</t>
+    <t xml:space="preserve">0.152109399437904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995051980019</t>
+    <t xml:space="preserve">0.15399506688118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640621066093</t>
+    <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051145195961</t>
+    <t xml:space="preserve">0.186051160097122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936797738075</t>
+    <t xml:space="preserve">0.187936782836914</t>
   </si>
   <si>
     <t xml:space="preserve">0.183536931872368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18171414732933</t>
+    <t xml:space="preserve">0.181714132428169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16719463467598</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
     <t xml:space="preserve">0.160280555486679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080972790718</t>
+    <t xml:space="preserve">0.147080987691879</t>
   </si>
   <si>
     <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338094353676</t>
+    <t xml:space="preserve">0.148338079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566774368286</t>
+    <t xml:space="preserve">0.144566759467125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394902944565</t>
+    <t xml:space="preserve">0.158394888043404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183290839195</t>
+    <t xml:space="preserve">0.16518323123455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651629567146</t>
+    <t xml:space="preserve">0.17065167427063</t>
   </si>
   <si>
     <t xml:space="preserve">0.172223031520844</t>
@@ -248,292 +248,292 @@
     <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507819652557</t>
+    <t xml:space="preserve">0.20050784945488</t>
   </si>
   <si>
     <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131431341171</t>
+    <t xml:space="preserve">0.17813141644001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765261650085</t>
+    <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010644435883</t>
+    <t xml:space="preserve">0.201010704040527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850847125053</t>
+    <t xml:space="preserve">0.194850876927376</t>
   </si>
   <si>
     <t xml:space="preserve">0.191770955920219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19987927377224</t>
+    <t xml:space="preserve">0.199879288673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078856468201</t>
+    <t xml:space="preserve">0.213078871369362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787308454514</t>
+    <t xml:space="preserve">0.216787323355675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563942670822</t>
+    <t xml:space="preserve">0.232563957571983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220915198326</t>
+    <t xml:space="preserve">0.238220930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420468091965</t>
+    <t xml:space="preserve">0.251420438289642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134249210358</t>
+    <t xml:space="preserve">0.26713427901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305449962616</t>
+    <t xml:space="preserve">0.275305390357971</t>
   </si>
   <si>
     <t xml:space="preserve">0.29039067029953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561811447144</t>
+    <t xml:space="preserve">0.298561781644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705986499786</t>
+    <t xml:space="preserve">0.257705956697464</t>
   </si>
   <si>
     <t xml:space="preserve">0.260157346725464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250226229429245</t>
+    <t xml:space="preserve">0.250226259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163406133652</t>
+    <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809355258942</t>
+    <t xml:space="preserve">0.242809280753136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249326944351</t>
+    <t xml:space="preserve">0.243249282240868</t>
   </si>
   <si>
     <t xml:space="preserve">0.243375018239021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22942116856575</t>
+    <t xml:space="preserve">0.229421198368073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23382106423378</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
     <t xml:space="preserve">0.210564643144608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20691904425621</t>
+    <t xml:space="preserve">0.206919029355049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821749806404</t>
+    <t xml:space="preserve">0.211821734905243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741873502731</t>
+    <t xml:space="preserve">0.208741888403893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592354416847</t>
+    <t xml:space="preserve">0.237592369318008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134919881821</t>
+    <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2308040112257</t>
+    <t xml:space="preserve">0.230803966522217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535516023636</t>
+    <t xml:space="preserve">0.227535486221313</t>
   </si>
   <si>
     <t xml:space="preserve">0.235706672072411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278424263</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135650157928</t>
+    <t xml:space="preserve">0.223135709762573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850146651268</t>
+    <t xml:space="preserve">0.216850191354752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381398081779</t>
+    <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
     <t xml:space="preserve">0.213141724467278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199233531952</t>
+    <t xml:space="preserve">0.201199263334274</t>
   </si>
   <si>
     <t xml:space="preserve">0.204279109835625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793338060379</t>
+    <t xml:space="preserve">0.206793367862701</t>
   </si>
   <si>
     <t xml:space="preserve">0.2061647772789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20742192864418</t>
+    <t xml:space="preserve">0.207421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804666996002</t>
+    <t xml:space="preserve">0.208804696798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947456002235</t>
+    <t xml:space="preserve">0.211947396397591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649908185005</t>
+    <t xml:space="preserve">0.225649893283844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867184758186</t>
+    <t xml:space="preserve">0.219867169857025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810011029243</t>
+    <t xml:space="preserve">0.220810040831566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484051465988</t>
+    <t xml:space="preserve">0.229484021663666</t>
   </si>
   <si>
     <t xml:space="preserve">0.234386771917343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518477916718</t>
+    <t xml:space="preserve">0.224518492817879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992890954018</t>
+    <t xml:space="preserve">0.219992905855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741493463516</t>
+    <t xml:space="preserve">0.219741478562355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912969946861</t>
+    <t xml:space="preserve">0.216912999749184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306836009026</t>
+    <t xml:space="preserve">0.231306791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038691043854</t>
+    <t xml:space="preserve">0.217038720846176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324239253998</t>
+    <t xml:space="preserve">0.223324209451675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297179013490677</t>
+    <t xml:space="preserve">0.297178983688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988673210144</t>
+    <t xml:space="preserve">0.351988643407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127885341644</t>
+    <t xml:space="preserve">0.465127915143967</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582354068756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070331573486</t>
+    <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843007802963</t>
+    <t xml:space="preserve">0.436843037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072142362595</t>
+    <t xml:space="preserve">0.422072112560272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987302064896</t>
+    <t xml:space="preserve">0.395987212657928</t>
   </si>
   <si>
     <t xml:space="preserve">0.364559680223465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215207099915</t>
+    <t xml:space="preserve">0.414215266704559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388218641281</t>
+    <t xml:space="preserve">0.367388188838959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987942934036</t>
+    <t xml:space="preserve">0.373988002538681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331745386124</t>
+    <t xml:space="preserve">0.346331685781479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903803110123</t>
+    <t xml:space="preserve">0.325903743505478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904153347015</t>
+    <t xml:space="preserve">0.314904123544693</t>
   </si>
   <si>
     <t xml:space="preserve">0.326532334089279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389269351959</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818262338638</t>
+    <t xml:space="preserve">0.321818202733994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845899105072</t>
+    <t xml:space="preserve">0.348845928907394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303259134293</t>
+    <t xml:space="preserve">0.34130334854126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846569776535</t>
+    <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361103534698</t>
+    <t xml:space="preserve">0.318361133337021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189641952515</t>
+    <t xml:space="preserve">0.321189671754837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132147789001</t>
+    <t xml:space="preserve">0.333132117986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989373683929</t>
+    <t xml:space="preserve">0.329989343881607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418366670609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332356452942</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275622367859</t>
+    <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
     <t xml:space="preserve">0.311761349439621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703534841537</t>
+    <t xml:space="preserve">0.334703505039215</t>
   </si>
   <si>
     <t xml:space="preserve">0.318046927452087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31678980588913</t>
+    <t xml:space="preserve">0.316789776086807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417986631393</t>
+    <t xml:space="preserve">0.328417927026749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075294494629</t>
+    <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103691339493</t>
+    <t xml:space="preserve">0.328103750944138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704555749893</t>
+    <t xml:space="preserve">0.301704585552216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504257678986</t>
+    <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
     <t xml:space="preserve">0.311069965362549</t>
@@ -545,34 +545,34 @@
     <t xml:space="preserve">0.325589537620544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274161815643</t>
+    <t xml:space="preserve">0.358274191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417636394501</t>
+    <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
     <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304019212723</t>
+    <t xml:space="preserve">0.3193039894104</t>
   </si>
   <si>
     <t xml:space="preserve">0.337846308946609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589858055115</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789455652237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701694250107</t>
+    <t xml:space="preserve">0.389701753854752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588136672974</t>
+    <t xml:space="preserve">0.369588106870651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959605693817</t>
+    <t xml:space="preserve">0.368959486484528</t>
   </si>
   <si>
     <t xml:space="preserve">0.370216637849808</t>
@@ -581,28 +581,28 @@
     <t xml:space="preserve">0.363616824150085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845228433609</t>
+    <t xml:space="preserve">0.370845198631287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074623823166</t>
+    <t xml:space="preserve">0.345074653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788725376129</t>
+    <t xml:space="preserve">0.349788755178452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502856731415</t>
+    <t xml:space="preserve">0.354502886533737</t>
   </si>
   <si>
     <t xml:space="preserve">0.367073863744736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38875886797905</t>
+    <t xml:space="preserve">0.388758927583694</t>
   </si>
   <si>
     <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759277820587</t>
+    <t xml:space="preserve">0.377759248018265</t>
   </si>
   <si>
     <t xml:space="preserve">0.377130717039108</t>
@@ -611,49 +611,49 @@
     <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444982528687</t>
+    <t xml:space="preserve">0.377444952726364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929688692093</t>
+    <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843857288361</t>
+    <t xml:space="preserve">0.414843797683716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215967178345</t>
+    <t xml:space="preserve">0.3922159075737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37681645154953</t>
+    <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386559069156647</t>
+    <t xml:space="preserve">0.38655897974968</t>
   </si>
   <si>
     <t xml:space="preserve">0.471413344144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357310533524</t>
+    <t xml:space="preserve">0.439357280731201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556848526001</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700293302536</t>
+    <t xml:space="preserve">0.433700382709503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100248575211</t>
+    <t xml:space="preserve">0.438100278377533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271300315857</t>
+    <t xml:space="preserve">0.446271419525146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985781908035</t>
+    <t xml:space="preserve">0.439985811710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386437654495</t>
+    <t xml:space="preserve">0.422386407852173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900621175766</t>
+    <t xml:space="preserve">0.424900680780411</t>
   </si>
   <si>
     <t xml:space="preserve">0.421129286289215</t>
@@ -662,64 +662,64 @@
     <t xml:space="preserve">0.40981537103653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044095754623</t>
+    <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
     <t xml:space="preserve">0.408558219671249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586676120758</t>
+    <t xml:space="preserve">0.413586735725403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272760868073</t>
+    <t xml:space="preserve">0.40227273106575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443171739578</t>
+    <t xml:space="preserve">0.432443261146545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357951402664</t>
+    <t xml:space="preserve">0.417358011007309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613672018051</t>
+    <t xml:space="preserve">0.462613582611084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414834499359</t>
+    <t xml:space="preserve">0.427414774894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758547544479</t>
+    <t xml:space="preserve">0.399758577346802</t>
   </si>
   <si>
     <t xml:space="preserve">0.418615102767944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643499612808</t>
+    <t xml:space="preserve">0.423643469810486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41107252240181</t>
+    <t xml:space="preserve">0.411072462797165</t>
   </si>
   <si>
     <t xml:space="preserve">0.398501455783844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786914587021</t>
+    <t xml:space="preserve">0.404786944389343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159113883972</t>
+    <t xml:space="preserve">0.382159143686295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416205644608</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444662094116</t>
+    <t xml:space="preserve">0.388444632291794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529912233353</t>
+    <t xml:space="preserve">0.403529852628708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43118605017662</t>
+    <t xml:space="preserve">0.431186109781265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872134923935</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
     <t xml:space="preserve">0.407301157712936</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">0.4123295545578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015639305115</t>
+    <t xml:space="preserve">0.40101569890976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100829839706</t>
+    <t xml:space="preserve">0.416100800037384</t>
   </si>
   <si>
     <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3658167719841</t>
+    <t xml:space="preserve">0.365816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36330258846283</t>
+    <t xml:space="preserve">0.363302618265152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674787759781</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
     <t xml:space="preserve">0.329360842704773</t>
@@ -755,52 +755,52 @@
     <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35701709985733</t>
+    <t xml:space="preserve">0.357017070055008</t>
   </si>
   <si>
     <t xml:space="preserve">0.344446063041687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33690345287323</t>
+    <t xml:space="preserve">0.336903482675552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160514831543</t>
+    <t xml:space="preserve">0.338160544633865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703095197678</t>
+    <t xml:space="preserve">0.345703184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102290391922</t>
+    <t xml:space="preserve">0.372102320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930418968201</t>
+    <t xml:space="preserve">0.385930448770523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245735168457</t>
+    <t xml:space="preserve">0.353245764970779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788375139236</t>
+    <t xml:space="preserve">0.360788404941559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387838602066</t>
+    <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873595476151</t>
+    <t xml:space="preserve">0.375873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37335941195488</t>
+    <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673357009888</t>
+    <t xml:space="preserve">0.384673327207565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958815813065</t>
+    <t xml:space="preserve">0.390958786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393472999334335</t>
+    <t xml:space="preserve">0.393473088741302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272119998932</t>
+    <t xml:space="preserve">0.424272030591965</t>
   </si>
   <si>
     <t xml:space="preserve">0.430557548999786</t>
@@ -809,61 +809,61 @@
     <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699592828751</t>
+    <t xml:space="preserve">0.455699533224106</t>
   </si>
   <si>
     <t xml:space="preserve">0.463955998420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181842565536</t>
+    <t xml:space="preserve">0.443181782960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332375526428</t>
+    <t xml:space="preserve">0.429332435131073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415482968091965</t>
+    <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870150327682</t>
+    <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257183551788</t>
+    <t xml:space="preserve">0.436257094144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719468355179</t>
+    <t xml:space="preserve">0.439719498157501</t>
   </si>
   <si>
     <t xml:space="preserve">0.432794749736786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945372104645</t>
+    <t xml:space="preserve">0.418945342302322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558309078217</t>
+    <t xml:space="preserve">0.408558249473572</t>
   </si>
   <si>
     <t xml:space="preserve">0.401633530855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020653486252</t>
+    <t xml:space="preserve">0.412020683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784123420715</t>
+    <t xml:space="preserve">0.387784093618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246438026428</t>
+    <t xml:space="preserve">0.391246557235718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095905065536</t>
+    <t xml:space="preserve">0.405095845460892</t>
   </si>
   <si>
     <t xml:space="preserve">0.422407686710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644186973572</t>
+    <t xml:space="preserve">0.446644216775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
     <t xml:space="preserve">0.450106471776962</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.453568905591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171186447144</t>
+    <t xml:space="preserve">0.398171216249466</t>
   </si>
   <si>
     <t xml:space="preserve">0.394708842039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859375</t>
+    <t xml:space="preserve">0.380859434604645</t>
   </si>
   <si>
     <t xml:space="preserve">0.373934715986252</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">0.384321749210358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009997367859</t>
+    <t xml:space="preserve">0.367009967565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696036815643</t>
+    <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
     <t xml:space="preserve">0.339311122894287</t>
@@ -908,40 +908,40 @@
     <t xml:space="preserve">0.353160530328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34623584151268</t>
+    <t xml:space="preserve">0.346235781908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386404275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612248420715</t>
+    <t xml:space="preserve">0.311612218618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314382076263428</t>
+    <t xml:space="preserve">0.314382135868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838062763214</t>
+    <t xml:space="preserve">0.290838092565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984416723251</t>
+    <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373539447784</t>
+    <t xml:space="preserve">0.278373628854752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.272833794355392</t>
   </si>
   <si>
     <t xml:space="preserve">0.261754274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134949684143</t>
+    <t xml:space="preserve">0.245135009288788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289825558662</t>
+    <t xml:space="preserve">0.249289810657501</t>
   </si>
   <si>
     <t xml:space="preserve">0.243749991059303</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">0.285298317670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683261394501</t>
+    <t xml:space="preserve">0.286683291196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448910236359</t>
+    <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
     <t xml:space="preserve">0.279758542776108</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">0.281143456697464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
     <t xml:space="preserve">0.303302586078644</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926149368286</t>
+    <t xml:space="preserve">0.337926119565964</t>
   </si>
   <si>
     <t xml:space="preserve">0.325461685657501</t>
@@ -983,40 +983,40 @@
     <t xml:space="preserve">0.343465894460678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547563552856</t>
+    <t xml:space="preserve">0.363547533750534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397119998932</t>
+    <t xml:space="preserve">0.377397000789642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231543302536</t>
+    <t xml:space="preserve">0.328231602907181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001430749893</t>
+    <t xml:space="preserve">0.331001460552216</t>
   </si>
   <si>
     <t xml:space="preserve">0.33654123544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698126316071</t>
+    <t xml:space="preserve">0.349698215723038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850838184357</t>
+    <t xml:space="preserve">0.344850867986679</t>
   </si>
   <si>
     <t xml:space="preserve">0.322691738605499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076682329178</t>
+    <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306854486465</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536967039108</t>
+    <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072503328323</t>
+    <t xml:space="preserve">0.306072443723679</t>
   </si>
   <si>
     <t xml:space="preserve">0.31715202331543</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762840986252</t>
+    <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913373947144</t>
+    <t xml:space="preserve">0.283913344144821</t>
   </si>
   <si>
     <t xml:space="preserve">0.288068205118179</t>
@@ -1037,196 +1037,196 @@
     <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294049263</t>
+    <t xml:space="preserve">0.267294079065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369330644608</t>
+    <t xml:space="preserve">0.26036936044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.265909105539322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063906908035</t>
+    <t xml:space="preserve">0.27006396651268</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223006486893</t>
+    <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
     <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453208446503</t>
+    <t xml:space="preserve">0.289453119039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809957742691</t>
+    <t xml:space="preserve">0.429809987545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647921323776</t>
+    <t xml:space="preserve">0.399647861719131</t>
   </si>
   <si>
     <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026319503784</t>
+    <t xml:space="preserve">0.377026259899139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945241689682</t>
+    <t xml:space="preserve">0.361945271492004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36948573589325</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
     <t xml:space="preserve">0.363453358411789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796521902084</t>
+    <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961445331573</t>
+    <t xml:space="preserve">0.364961475133896</t>
   </si>
   <si>
     <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847990036011</t>
+    <t xml:space="preserve">0.343847960233688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339873313904</t>
+    <t xml:space="preserve">0.342339903116226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323669672012</t>
+    <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896630764008</t>
+    <t xml:space="preserve">0.352896600961685</t>
   </si>
   <si>
     <t xml:space="preserve">0.34686416387558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388514041901</t>
+    <t xml:space="preserve">0.351388454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307436227798</t>
+    <t xml:space="preserve">0.336307466030121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799349308014</t>
+    <t xml:space="preserve">0.334799319505692</t>
   </si>
   <si>
     <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350511550903</t>
+    <t xml:space="preserve">0.437350481748581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958707332611</t>
+    <t xml:space="preserve">0.410958617925644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431529760361</t>
+    <t xml:space="preserve">0.452431559562683</t>
   </si>
   <si>
     <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120773553848</t>
+    <t xml:space="preserve">0.441120684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728909730911</t>
+    <t xml:space="preserve">0.414728969335556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418183326721</t>
+    <t xml:space="preserve">0.403418153524399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566783905029</t>
+    <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877599716187</t>
+    <t xml:space="preserve">0.395877540111542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188415527344</t>
+    <t xml:space="preserve">0.407188445329666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501939535141</t>
+    <t xml:space="preserve">0.372501969337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469591856003</t>
+    <t xml:space="preserve">0.36646956205368</t>
   </si>
   <si>
     <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356076955795</t>
+    <t xml:space="preserve">0.345356106758118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831756591797</t>
+    <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993852615356</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437124967575</t>
+    <t xml:space="preserve">0.360437154769897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977648973465</t>
+    <t xml:space="preserve">0.367977619171143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929067850113</t>
+    <t xml:space="preserve">0.358928978443146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31670206785202</t>
+    <t xml:space="preserve">0.316702097654343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112962722778</t>
+    <t xml:space="preserve">0.300112932920456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301621049642563</t>
+    <t xml:space="preserve">0.30162101984024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210154771805</t>
+    <t xml:space="preserve">0.318210184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718331098557</t>
+    <t xml:space="preserve">0.319718301296234</t>
   </si>
   <si>
     <t xml:space="preserve">0.32424259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258765697479</t>
   </si>
   <si>
     <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783175468445</t>
+    <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337815552949905</t>
+    <t xml:space="preserve">0.33781561255455</t>
   </si>
   <si>
     <t xml:space="preserve">0.328766912221909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30916154384613</t>
+    <t xml:space="preserve">0.309161514043808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653427124023</t>
+    <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129136562347</t>
+    <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685834407806</t>
+    <t xml:space="preserve">0.313685864210129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734475135803</t>
+    <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
     <t xml:space="preserve">0.317599177360535</t>
@@ -1235,43 +1235,43 @@
     <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314438968896866</t>
   </si>
   <si>
     <t xml:space="preserve">0.31917929649353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820040941238</t>
+    <t xml:space="preserve">0.331820011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400100469589</t>
+    <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759415626526</t>
+    <t xml:space="preserve">0.320759356021881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919534683228</t>
+    <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31285884976387</t>
+    <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378313779831</t>
+    <t xml:space="preserve">0.303378343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317658662796</t>
+    <t xml:space="preserve">0.292317628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798224449158</t>
+    <t xml:space="preserve">0.30179825425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019117832184</t>
+    <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218135118484</t>
+    <t xml:space="preserve">0.300218105316162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638015985489</t>
+    <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
     <t xml:space="preserve">0.290737569332123</t>
@@ -1280,106 +1280,106 @@
     <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577331066132</t>
+    <t xml:space="preserve">0.287577420473099</t>
   </si>
   <si>
     <t xml:space="preserve">0.279676884412766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096795082092</t>
+    <t xml:space="preserve">0.278096824884415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196348428726</t>
+    <t xml:space="preserve">0.270196288824081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257003545761</t>
+    <t xml:space="preserve">0.281256973743439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776437759399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28441721200943</t>
+    <t xml:space="preserve">0.284417152404785</t>
   </si>
   <si>
     <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477896928787</t>
+    <t xml:space="preserve">0.295477837324142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057926654816</t>
+    <t xml:space="preserve">0.297057956457138</t>
   </si>
   <si>
     <t xml:space="preserve">0.308118611574173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289157450199127</t>
+    <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
     <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140398263931</t>
+    <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720487594604</t>
   </si>
   <si>
     <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33498027920723</t>
+    <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
     <t xml:space="preserve">0.33656033873558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361261844635</t>
+    <t xml:space="preserve">0.352361291646957</t>
   </si>
   <si>
     <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944772005081</t>
+    <t xml:space="preserve">0.291944682598114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237486362457</t>
+    <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115599632263</t>
+    <t xml:space="preserve">0.285115629434586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822885274887</t>
+    <t xml:space="preserve">0.286822915077209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481110811234</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29877382516861</t>
+    <t xml:space="preserve">0.298773854970932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408313989639</t>
+    <t xml:space="preserve">0.283408343791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286516666412</t>
+    <t xml:space="preserve">0.27828648686409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288530170917511</t>
+    <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
     <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164689540863</t>
+    <t xml:space="preserve">0.273164629936218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579201221466</t>
+    <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750088453293</t>
+    <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
     <t xml:space="preserve">0.28170108795166</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">0.271457374095917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042832612991</t>
+    <t xml:space="preserve">0.268042862415314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895711898804</t>
+    <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
     <t xml:space="preserve">0.302188396453857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602967739105</t>
+    <t xml:space="preserve">0.305602997541428</t>
   </si>
   <si>
     <t xml:space="preserve">0.307310283184052</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">0.324383050203323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261252880096</t>
+    <t xml:space="preserve">0.319261193275452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017509222031</t>
+    <t xml:space="preserve">0.309017479419708</t>
   </si>
   <si>
     <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432050704956</t>
+    <t xml:space="preserve">0.312432110309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724765062332</t>
+    <t xml:space="preserve">0.310724824666977</t>
   </si>
   <si>
     <t xml:space="preserve">0.310289025306702</t>
@@ -1433,25 +1433,25 @@
     <t xml:space="preserve">0.299829810857773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343445777893</t>
+    <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316205739975</t>
+    <t xml:space="preserve">0.303316235542297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289370626211166</t>
+    <t xml:space="preserve">0.289370656013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627458572388</t>
+    <t xml:space="preserve">0.28762748837471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086673021317</t>
+    <t xml:space="preserve">0.298086583614349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560336828232</t>
+    <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30465242266655</t>
+    <t xml:space="preserve">0.304652392864227</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870839834213</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">0.301089197397232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836504936218</t>
+    <t xml:space="preserve">0.286836445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618087768555</t>
+    <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399700403214</t>
+    <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
     <t xml:space="preserve">0.299307614564896</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273279666901</t>
+    <t xml:space="preserve">0.283273249864578</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710114002228</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902091026306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302665084600449</t>
+    <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
     <t xml:space="preserve">0.291725426912308</t>
@@ -1511,70 +1511,70 @@
     <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3117815554142</t>
+    <t xml:space="preserve">0.311781525611877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31725138425827</t>
+    <t xml:space="preserve">0.317251414060593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074690341949</t>
+    <t xml:space="preserve">0.319074660539627</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191101551056</t>
+    <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33183765411377</t>
+    <t xml:space="preserve">0.331837683916092</t>
   </si>
   <si>
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897936820984</t>
+    <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32454451918602</t>
+    <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
     <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329747140407562</t>
+    <t xml:space="preserve">0.32974711060524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322295218706131</t>
+    <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610053777695</t>
+    <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021194458008</t>
+    <t xml:space="preserve">0.326021134853363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432245731354</t>
+    <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117321252823</t>
+    <t xml:space="preserve">0.311117351055145</t>
   </si>
   <si>
     <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335336029529572</t>
+    <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
     <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569272756577</t>
+    <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
     <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473056554794</t>
+    <t xml:space="preserve">0.333473116159439</t>
   </si>
   <si>
     <t xml:space="preserve">0.307391405105591</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">0.348376899957657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732635259628</t>
+    <t xml:space="preserve">0.370732605457306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677319288254</t>
+    <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170081615448</t>
+    <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407992213964462</t>
+    <t xml:space="preserve">0.40799218416214</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40985518693924</t>
+    <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
     <t xml:space="preserve">0.400540292263031</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">0.3912253677845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3930883705616</t>
+    <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
     <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458611011505</t>
+    <t xml:space="preserve">0.374458581209183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376321583986282</t>
+    <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.372595608234406</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">0.378184527158737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951343536377</t>
+    <t xml:space="preserve">0.394951373338699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407650500535965</t>
+    <t xml:space="preserve">0.407650470733643</t>
   </si>
   <si>
     <t xml:space="preserve">0.392482101917267</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40385839343071</t>
+    <t xml:space="preserve">0.403858363628387</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
@@ -68579,7 +68579,7 @@
     </row>
     <row r="2557">
       <c r="A2557" s="1" t="n">
-        <v>46045.6781597222</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2557" t="n">
         <v>64000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994351506233</t>
+    <t xml:space="preserve">0.175994321703911</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1728515625</t>
+    <t xml:space="preserve">0.172851577401161</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594470739365</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.164051875472069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16970881819725</t>
+    <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
     <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309682607651</t>
+    <t xml:space="preserve">0.14330966770649</t>
   </si>
   <si>
     <t xml:space="preserve">0.149783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195305347443</t>
+    <t xml:space="preserve">0.145195320248604</t>
   </si>
   <si>
     <t xml:space="preserve">0.152737945318222</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">0.153366476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.150789439678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146452397108078</t>
+    <t xml:space="preserve">0.146452456712723</t>
   </si>
   <si>
     <t xml:space="preserve">0.139852643013</t>
@@ -89,58 +89,58 @@
     <t xml:space="preserve">0.139538377523422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915496110916</t>
+    <t xml:space="preserve">0.139915481209755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052546143532</t>
+    <t xml:space="preserve">0.142052561044693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909801840782</t>
+    <t xml:space="preserve">0.138909816741943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15110370516777</t>
+    <t xml:space="preserve">0.151103690266609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337378978729</t>
+    <t xml:space="preserve">0.17033739387989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817501187325</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423284888268</t>
+    <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137796282768</t>
+    <t xml:space="preserve">0.157137811183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623597860336</t>
+    <t xml:space="preserve">0.154623612761497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595156311989</t>
+    <t xml:space="preserve">0.14959517121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692130327225</t>
+    <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
     <t xml:space="preserve">0.160909101366997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960595726967</t>
+    <t xml:space="preserve">0.158960610628128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314296364784</t>
+    <t xml:space="preserve">0.177314281463623</t>
   </si>
   <si>
     <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965924859047</t>
+    <t xml:space="preserve">0.170965909957886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937498211861</t>
+    <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565373420715</t>
+    <t xml:space="preserve">0.188565328717232</t>
   </si>
   <si>
     <t xml:space="preserve">0.192650899291039</t>
@@ -149,70 +149,70 @@
     <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165507555008</t>
+    <t xml:space="preserve">0.184165522456169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651294231415</t>
+    <t xml:space="preserve">0.181651264429092</t>
   </si>
   <si>
     <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678960800171</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
     <t xml:space="preserve">0.201073512434959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19673652946949</t>
+    <t xml:space="preserve">0.196736499667168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222286343575</t>
+    <t xml:space="preserve">0.194222316145897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17913706600666</t>
+    <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279825210571</t>
+    <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834554195404</t>
+    <t xml:space="preserve">0.169834524393082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451726436615</t>
+    <t xml:space="preserve">0.168451711535454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794753909111</t>
+    <t xml:space="preserve">0.162794768810272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606559753418</t>
+    <t xml:space="preserve">0.151606544852257</t>
   </si>
   <si>
     <t xml:space="preserve">0.16656605899334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074943184853</t>
+    <t xml:space="preserve">0.157074928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109384536743</t>
+    <t xml:space="preserve">0.152109369635582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995022177696</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640635967255</t>
+    <t xml:space="preserve">0.157640665769577</t>
   </si>
   <si>
     <t xml:space="preserve">0.186051160097122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936797738075</t>
+    <t xml:space="preserve">0.187936812639236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536931872368</t>
+    <t xml:space="preserve">0.183536946773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714117527008</t>
+    <t xml:space="preserve">0.18171414732933</t>
   </si>
   <si>
     <t xml:space="preserve">0.167194619774818</t>
@@ -236,55 +236,55 @@
     <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183261036873</t>
+    <t xml:space="preserve">0.16518323123455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651644468307</t>
+    <t xml:space="preserve">0.170651629567146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223031520844</t>
+    <t xml:space="preserve">0.172223001718521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594120502472</t>
+    <t xml:space="preserve">0.18259409070015</t>
   </si>
   <si>
     <t xml:space="preserve">0.200507834553719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.193593755364418</t>
   </si>
   <si>
     <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765276551247</t>
+    <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010689139366</t>
+    <t xml:space="preserve">0.201010659337044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850876927376</t>
+    <t xml:space="preserve">0.194850862026215</t>
   </si>
   <si>
     <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879243969917</t>
+    <t xml:space="preserve">0.199879288673401</t>
   </si>
   <si>
     <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787278652191</t>
+    <t xml:space="preserve">0.216787323355675</t>
   </si>
   <si>
     <t xml:space="preserve">0.232563927769661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220915198326</t>
+    <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420438289642</t>
+    <t xml:space="preserve">0.251420497894287</t>
   </si>
   <si>
     <t xml:space="preserve">0.267134249210358</t>
@@ -293,31 +293,31 @@
     <t xml:space="preserve">0.275305420160294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290390610694885</t>
+    <t xml:space="preserve">0.290390640497208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561781644821</t>
+    <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705956697464</t>
+    <t xml:space="preserve">0.257705926895142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157346725464</t>
+    <t xml:space="preserve">0.260157316923141</t>
   </si>
   <si>
     <t xml:space="preserve">0.250226199626923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163376331329</t>
+    <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809310555458</t>
+    <t xml:space="preserve">0.242809295654297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249341845512</t>
+    <t xml:space="preserve">0.243249282240868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243374988436699</t>
+    <t xml:space="preserve">0.24337500333786</t>
   </si>
   <si>
     <t xml:space="preserve">0.229421198368073</t>
@@ -326,130 +326,130 @@
     <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564628243446</t>
+    <t xml:space="preserve">0.21056467294693</t>
   </si>
   <si>
     <t xml:space="preserve">0.206919059157372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821749806404</t>
+    <t xml:space="preserve">0.211821764707565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741873502731</t>
+    <t xml:space="preserve">0.208741843700409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592369318008</t>
+    <t xml:space="preserve">0.237592354416847</t>
   </si>
   <si>
     <t xml:space="preserve">0.245134979486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803936719894</t>
+    <t xml:space="preserve">0.230803951621056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535545825958</t>
+    <t xml:space="preserve">0.227535516023636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706701874733</t>
+    <t xml:space="preserve">0.235706642270088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278394460678</t>
+    <t xml:space="preserve">0.226278424263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135650157928</t>
+    <t xml:space="preserve">0.223135679960251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850161552429</t>
+    <t xml:space="preserve">0.216850131750107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381383180618</t>
+    <t xml:space="preserve">0.222381398081779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141724467278</t>
+    <t xml:space="preserve">0.213141709566116</t>
   </si>
   <si>
     <t xml:space="preserve">0.201199248433113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279109835625</t>
+    <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20679335296154</t>
+    <t xml:space="preserve">0.206793323159218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164807081223</t>
+    <t xml:space="preserve">0.2061647772789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421869039536</t>
+    <t xml:space="preserve">0.207421913743019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804681897163</t>
+    <t xml:space="preserve">0.208804711699486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947441101074</t>
+    <t xml:space="preserve">0.211947426199913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649878382683</t>
+    <t xml:space="preserve">0.225649863481522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867199659348</t>
+    <t xml:space="preserve">0.219867244362831</t>
   </si>
   <si>
     <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484066367149</t>
+    <t xml:space="preserve">0.229484036564827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23438672721386</t>
+    <t xml:space="preserve">0.234386742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518463015556</t>
+    <t xml:space="preserve">0.224518477916718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992905855179</t>
+    <t xml:space="preserve">0.21999292075634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741493463516</t>
+    <t xml:space="preserve">0.219741463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912999749184</t>
+    <t xml:space="preserve">0.216913014650345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306806206703</t>
+    <t xml:space="preserve">0.231306850910187</t>
   </si>
   <si>
     <t xml:space="preserve">0.217038720846176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324239253998</t>
+    <t xml:space="preserve">0.223324194550514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178953886032</t>
+    <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988703012466</t>
+    <t xml:space="preserve">0.351988643407822</t>
   </si>
   <si>
     <t xml:space="preserve">0.465127855539322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582413673401</t>
+    <t xml:space="preserve">0.545582354068756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070420980453</t>
+    <t xml:space="preserve">0.477070331573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843037605286</t>
+    <t xml:space="preserve">0.43684309720993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072201967239</t>
+    <t xml:space="preserve">0.422072172164917</t>
   </si>
   <si>
     <t xml:space="preserve">0.395987242460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559650421143</t>
+    <t xml:space="preserve">0.364559680223465</t>
   </si>
   <si>
     <t xml:space="preserve">0.414215207099915</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.367388159036636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987942934036</t>
+    <t xml:space="preserve">0.373987972736359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331745386124</t>
+    <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3259037733078</t>
+    <t xml:space="preserve">0.325903803110123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904153347015</t>
+    <t xml:space="preserve">0.314904093742371</t>
   </si>
   <si>
     <t xml:space="preserve">0.326532363891602</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">0.321818202733994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34884586930275</t>
+    <t xml:space="preserve">0.348845958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303288936615</t>
+    <t xml:space="preserve">0.341303259134293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846569776535</t>
+    <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
     <t xml:space="preserve">0.318361163139343</t>
@@ -500,73 +500,73 @@
     <t xml:space="preserve">0.329989343881607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418307065964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332386255264</t>
+    <t xml:space="preserve">0.324332445859909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275592565536</t>
+    <t xml:space="preserve">0.314275622367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761349439621</t>
+    <t xml:space="preserve">0.311761409044266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703534841537</t>
+    <t xml:space="preserve">0.33470356464386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046867847443</t>
+    <t xml:space="preserve">0.318046897649765</t>
   </si>
   <si>
     <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328418016433716</t>
+    <t xml:space="preserve">0.328417956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075324296951</t>
+    <t xml:space="preserve">0.323075264692307</t>
   </si>
   <si>
     <t xml:space="preserve">0.328103750944138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704615354538</t>
+    <t xml:space="preserve">0.301704525947571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504287481308</t>
+    <t xml:space="preserve">0.310504257678986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069965362549</t>
+    <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
     <t xml:space="preserve">0.320561110973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589507818222</t>
+    <t xml:space="preserve">0.325589537620544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274132013321</t>
+    <t xml:space="preserve">0.358274191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417636394501</t>
+    <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
     <t xml:space="preserve">0.340046167373657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304049015045</t>
+    <t xml:space="preserve">0.3193039894104</t>
   </si>
   <si>
     <t xml:space="preserve">0.337846279144287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589858055115</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789455652237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701753854752</t>
+    <t xml:space="preserve">0.389701724052429</t>
   </si>
   <si>
     <t xml:space="preserve">0.369588077068329</t>
@@ -575,133 +575,133 @@
     <t xml:space="preserve">0.368959546089172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216637849808</t>
+    <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616913557053</t>
+    <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845198631287</t>
+    <t xml:space="preserve">0.370845228433609</t>
   </si>
   <si>
     <t xml:space="preserve">0.345074623823166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788695573807</t>
+    <t xml:space="preserve">0.349788755178452</t>
   </si>
   <si>
     <t xml:space="preserve">0.354502856731415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073863744736</t>
+    <t xml:space="preserve">0.367073893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758927583694</t>
+    <t xml:space="preserve">0.388758987188339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587406396866</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
     <t xml:space="preserve">0.37775930762291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130746841431</t>
+    <t xml:space="preserve">0.377130657434464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187510728836</t>
   </si>
   <si>
     <t xml:space="preserve">0.377444982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.407929748296738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843738079071</t>
+    <t xml:space="preserve">0.414843827486038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215937376022</t>
+    <t xml:space="preserve">0.392215967178345</t>
   </si>
   <si>
     <t xml:space="preserve">0.37681645154953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38655897974968</t>
+    <t xml:space="preserve">0.386559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413403749466</t>
+    <t xml:space="preserve">0.471413284540176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357310533524</t>
+    <t xml:space="preserve">0.439357250928879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556788921356</t>
+    <t xml:space="preserve">0.452556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700323104858</t>
+    <t xml:space="preserve">0.433700263500214</t>
   </si>
   <si>
     <t xml:space="preserve">0.438100248575211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271300315857</t>
+    <t xml:space="preserve">0.446271359920502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985811710358</t>
+    <t xml:space="preserve">0.43998584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386437654495</t>
+    <t xml:space="preserve">0.422386318445206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900621175766</t>
+    <t xml:space="preserve">0.424900680780411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129256486893</t>
+    <t xml:space="preserve">0.42112934589386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40981537103653</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
     <t xml:space="preserve">0.406044095754623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558219671249</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41358670592308</t>
+    <t xml:space="preserve">0.413586646318436</t>
   </si>
   <si>
     <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443141937256</t>
+    <t xml:space="preserve">0.432443261146545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357921600342</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613612413406</t>
+    <t xml:space="preserve">0.462613701820374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414804697037</t>
+    <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758487939835</t>
+    <t xml:space="preserve">0.399758577346802</t>
   </si>
   <si>
     <t xml:space="preserve">0.418615072965622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643499612808</t>
+    <t xml:space="preserve">0.423643529415131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072462797165</t>
+    <t xml:space="preserve">0.411072492599487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501455783844</t>
+    <t xml:space="preserve">0.398501485586166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404787003993988</t>
+    <t xml:space="preserve">0.404786974191666</t>
   </si>
   <si>
     <t xml:space="preserve">0.38215908408165</t>
@@ -710,205 +710,205 @@
     <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444572687149</t>
+    <t xml:space="preserve">0.388444632291794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529852628708</t>
+    <t xml:space="preserve">0.40352988243103</t>
   </si>
   <si>
     <t xml:space="preserve">0.431186139583588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41987219452858</t>
+    <t xml:space="preserve">0.419872224330902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301187515259</t>
+    <t xml:space="preserve">0.407301068305969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730180501938</t>
+    <t xml:space="preserve">0.394730150699615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329614162445</t>
+    <t xml:space="preserve">0.4123295545578</t>
   </si>
   <si>
     <t xml:space="preserve">0.401015669107437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100889444351</t>
+    <t xml:space="preserve">0.416100949048996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045496702194</t>
+    <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816831588745</t>
+    <t xml:space="preserve">0.365816801786423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36330258846283</t>
+    <t xml:space="preserve">0.363302528858185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674757957458</t>
+    <t xml:space="preserve">0.340674787759781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360872507095</t>
+    <t xml:space="preserve">0.329360753297806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531283378601</t>
+    <t xml:space="preserve">0.359531313180923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35701709985733</t>
+    <t xml:space="preserve">0.357017070055008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446063041687</t>
+    <t xml:space="preserve">0.344446003437042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33690345287323</t>
+    <t xml:space="preserve">0.336903423070908</t>
   </si>
   <si>
     <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703125</t>
+    <t xml:space="preserve">0.345703154802322</t>
   </si>
   <si>
     <t xml:space="preserve">0.372102320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930389165878</t>
+    <t xml:space="preserve">0.385930448770523</t>
   </si>
   <si>
     <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788375139236</t>
+    <t xml:space="preserve">0.360788345336914</t>
   </si>
   <si>
     <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873595476151</t>
+    <t xml:space="preserve">0.375873625278473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359322547913</t>
+    <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673297405243</t>
+    <t xml:space="preserve">0.384673357009888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958815813065</t>
+    <t xml:space="preserve">0.39095875620842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39347305893898</t>
+    <t xml:space="preserve">0.393472999334335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272000789642</t>
   </si>
   <si>
     <t xml:space="preserve">0.430557608604431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414074420929</t>
+    <t xml:space="preserve">0.449414014816284</t>
   </si>
   <si>
     <t xml:space="preserve">0.455699592828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955998420715</t>
+    <t xml:space="preserve">0.463955938816071</t>
   </si>
   <si>
     <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332375526428</t>
+    <t xml:space="preserve">0.429332435131073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483087301254</t>
+    <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870090723038</t>
+    <t xml:space="preserve">0.425870031118393</t>
   </si>
   <si>
     <t xml:space="preserve">0.436257153749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719468355179</t>
+    <t xml:space="preserve">0.439719408750534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794779539108</t>
+    <t xml:space="preserve">0.432794839143753</t>
   </si>
   <si>
     <t xml:space="preserve">0.418945342302322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633620262146</t>
+    <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020564079285</t>
+    <t xml:space="preserve">0.412020683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784093618393</t>
+    <t xml:space="preserve">0.387784123420715</t>
   </si>
   <si>
     <t xml:space="preserve">0.391246467828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095875263214</t>
+    <t xml:space="preserve">0.405095934867859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
+    <t xml:space="preserve">0.422407686710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644216775894</t>
+    <t xml:space="preserve">0.446644157171249</t>
   </si>
   <si>
     <t xml:space="preserve">0.526278436183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106590986252</t>
+    <t xml:space="preserve">0.450106531381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031339406967</t>
+    <t xml:space="preserve">0.45703136920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568935394287</t>
+    <t xml:space="preserve">0.453568905591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171186447144</t>
+    <t xml:space="preserve">0.398171156644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708842039108</t>
+    <t xml:space="preserve">0.394708812236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859404802322</t>
+    <t xml:space="preserve">0.380859464406967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934715986252</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085248947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472371578217</t>
+    <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384321719408035</t>
+    <t xml:space="preserve">0.384321808815002</t>
   </si>
   <si>
     <t xml:space="preserve">0.367009937763214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696096420288</t>
+    <t xml:space="preserve">0.340696036815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311093091965</t>
+    <t xml:space="preserve">0.339311122894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160530328751</t>
+    <t xml:space="preserve">0.353160560131073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34623584151268</t>
+    <t xml:space="preserve">0.346235811710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386434078217</t>
   </si>
   <si>
     <t xml:space="preserve">0.311612248420715</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">0.290838062763214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984386920929</t>
+    <t xml:space="preserve">0.258984416723251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373569250107</t>
+    <t xml:space="preserve">0.278373628854752</t>
   </si>
   <si>
     <t xml:space="preserve">0.263139218091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.272833853960037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754274368286</t>
+    <t xml:space="preserve">0.261754244565964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289810657501</t>
+    <t xml:space="preserve">0.249289765954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750020861626</t>
+    <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2852982878685</t>
+    <t xml:space="preserve">0.285298317670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683231592178</t>
+    <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448850631714</t>
+    <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27975857257843</t>
+    <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
     <t xml:space="preserve">0.281143516302109</t>
@@ -959,31 +959,31 @@
     <t xml:space="preserve">0.29499289393425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302556276321</t>
+    <t xml:space="preserve">0.303302586078644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842331171036</t>
+    <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926208972931</t>
+    <t xml:space="preserve">0.337926149368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461685657501</t>
+    <t xml:space="preserve">0.325461626052856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921940565109</t>
+    <t xml:space="preserve">0.319921910762787</t>
   </si>
   <si>
     <t xml:space="preserve">0.343465894460678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547563552856</t>
+    <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397000789642</t>
+    <t xml:space="preserve">0.377397030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231573104858</t>
+    <t xml:space="preserve">0.328231543302536</t>
   </si>
   <si>
     <t xml:space="preserve">0.331001430749893</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">0.349698156118393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850897789001</t>
+    <t xml:space="preserve">0.344850927591324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691798210144</t>
+    <t xml:space="preserve">0.322691768407822</t>
   </si>
   <si>
     <t xml:space="preserve">0.324076741933823</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536996841431</t>
+    <t xml:space="preserve">0.318536967039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072443723679</t>
+    <t xml:space="preserve">0.306072503328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31715202331543</t>
+    <t xml:space="preserve">0.317152053117752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3046875</t>
+    <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
     <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913373947144</t>
+    <t xml:space="preserve">0.283913403749466</t>
   </si>
   <si>
     <t xml:space="preserve">0.288068205118179</t>
@@ -1034,124 +1034,124 @@
     <t xml:space="preserve">0.267294019460678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26036936044693</t>
+    <t xml:space="preserve">0.260369300842285</t>
   </si>
   <si>
     <t xml:space="preserve">0.265909105539322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063936710358</t>
+    <t xml:space="preserve">0.27006396651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988655328751</t>
+    <t xml:space="preserve">0.276988625526428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223036289215</t>
+    <t xml:space="preserve">0.292223006486893</t>
   </si>
   <si>
     <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453089237213</t>
+    <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809987545013</t>
+    <t xml:space="preserve">0.429809927940369</t>
   </si>
   <si>
     <t xml:space="preserve">0.399647831916809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337075710297</t>
+    <t xml:space="preserve">0.388337105512619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026319503784</t>
+    <t xml:space="preserve">0.377026259899139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945241689682</t>
+    <t xml:space="preserve">0.36194521188736</t>
   </si>
   <si>
     <t xml:space="preserve">0.369485765695572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453358411789</t>
+    <t xml:space="preserve">0.363453328609467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796521902084</t>
+    <t xml:space="preserve">0.380796551704407</t>
   </si>
   <si>
     <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961475133896</t>
+    <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
     <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847960233688</t>
+    <t xml:space="preserve">0.343847990036011</t>
   </si>
   <si>
     <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323669672012</t>
+    <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896630764008</t>
+    <t xml:space="preserve">0.352896571159363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864223480225</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
     <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307436227798</t>
+    <t xml:space="preserve">0.336307495832443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799319505692</t>
+    <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
     <t xml:space="preserve">0.348372340202332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350571155548</t>
+    <t xml:space="preserve">0.437350511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958617925644</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431678771973</t>
+    <t xml:space="preserve">0.452431619167328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444890975952148</t>
+    <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120713949203</t>
+    <t xml:space="preserve">0.441120743751526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728939533234</t>
+    <t xml:space="preserve">0.414728969335556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418183326721</t>
+    <t xml:space="preserve">0.403418123722076</t>
   </si>
   <si>
     <t xml:space="preserve">0.392107337713242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566813707352</t>
+    <t xml:space="preserve">0.384566783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877569913864</t>
+    <t xml:space="preserve">0.395877540111542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188385725021</t>
+    <t xml:space="preserve">0.407188415527344</t>
   </si>
   <si>
     <t xml:space="preserve">0.372501969337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36646956205368</t>
+    <t xml:space="preserve">0.366469591856003</t>
   </si>
   <si>
     <t xml:space="preserve">0.354404717683792</t>
@@ -1160,49 +1160,49 @@
     <t xml:space="preserve">0.345356106758118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831786394119</t>
+    <t xml:space="preserve">0.340831756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993912220001</t>
+    <t xml:space="preserve">0.370993852615356</t>
   </si>
   <si>
     <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36797770857811</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929038047791</t>
+    <t xml:space="preserve">0.358929008245468</t>
   </si>
   <si>
     <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112932920456</t>
+    <t xml:space="preserve">0.300112992525101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30162101984024</t>
+    <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
     <t xml:space="preserve">0.318210184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718301296234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32424259185791</t>
+    <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330274999141693</t>
+    <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3317831158638</t>
+    <t xml:space="preserve">0.331783086061478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337815552949905</t>
+    <t xml:space="preserve">0.337815582752228</t>
   </si>
   <si>
     <t xml:space="preserve">0.328766942024231</t>
@@ -1214,103 +1214,103 @@
     <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129106760025</t>
+    <t xml:space="preserve">0.303129196166992</t>
   </si>
   <si>
     <t xml:space="preserve">0.313685864210129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734504938126</t>
+    <t xml:space="preserve">0.322734534740448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599147558212</t>
+    <t xml:space="preserve">0.317599236965179</t>
   </si>
   <si>
     <t xml:space="preserve">0.322339475154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314439028501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319179326295853</t>
+    <t xml:space="preserve">0.31917929649353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820040941238</t>
+    <t xml:space="preserve">0.331819981336594</t>
   </si>
   <si>
     <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759385824203</t>
+    <t xml:space="preserve">0.320759356021881</t>
   </si>
   <si>
     <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858909368515</t>
+    <t xml:space="preserve">0.312858879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.303378343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317688465118</t>
+    <t xml:space="preserve">0.292317718267441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798313856125</t>
+    <t xml:space="preserve">0.301798224449158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019088029861</t>
+    <t xml:space="preserve">0.316019117832184</t>
   </si>
   <si>
     <t xml:space="preserve">0.300218105316162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638045787811</t>
+    <t xml:space="preserve">0.298638015985489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737509727478</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837063074112</t>
+    <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
     <t xml:space="preserve">0.287577331066132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676914215088</t>
+    <t xml:space="preserve">0.279676884412766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516735553741</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096824884415</t>
+    <t xml:space="preserve">0.27809676527977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196318626404</t>
+    <t xml:space="preserve">0.270196348428726</t>
   </si>
   <si>
     <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776437759399</t>
+    <t xml:space="preserve">0.271776467561722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28441721200943</t>
+    <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
     <t xml:space="preserve">0.285997241735458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477837324142</t>
+    <t xml:space="preserve">0.295477867126465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29705798625946</t>
+    <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
     <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157450199127</t>
   </si>
   <si>
     <t xml:space="preserve">0.346040934324265</t>
@@ -1319,28 +1319,28 @@
     <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720547199249</t>
   </si>
   <si>
     <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980219602585</t>
+    <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336560308933258</t>
+    <t xml:space="preserve">0.33656033873558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361261844635</t>
+    <t xml:space="preserve">0.352361291646957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359313488007</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944712400436</t>
+    <t xml:space="preserve">0.291944742202759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237456560135</t>
+    <t xml:space="preserve">0.290237426757812</t>
   </si>
   <si>
     <t xml:space="preserve">0.285115629434586</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481170415878</t>
+    <t xml:space="preserve">0.300481110811234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298773884773254</t>
+    <t xml:space="preserve">0.29877382516861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408284187317</t>
+    <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27828648686409</t>
+    <t xml:space="preserve">0.278286516666412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288530170917511</t>
+    <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993832111359</t>
+    <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
     <t xml:space="preserve">0.273164659738541</t>
@@ -1379,49 +1379,49 @@
     <t xml:space="preserve">0.281701058149338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871975183487</t>
+    <t xml:space="preserve">0.274871915578842</t>
   </si>
   <si>
     <t xml:space="preserve">0.271457374095917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042832612991</t>
+    <t xml:space="preserve">0.268042862415314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895682096481</t>
+    <t xml:space="preserve">0.303895711898804</t>
   </si>
   <si>
     <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188396453857</t>
+    <t xml:space="preserve">0.30218842625618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602997541428</t>
+    <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310253381729</t>
+    <t xml:space="preserve">0.307310283184052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383050203323</t>
+    <t xml:space="preserve">0.324383020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261193275452</t>
+    <t xml:space="preserve">0.319261252880096</t>
   </si>
   <si>
     <t xml:space="preserve">0.309017479419708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139306545258</t>
+    <t xml:space="preserve">0.31413933634758</t>
   </si>
   <si>
     <t xml:space="preserve">0.312432110309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724794864655</t>
+    <t xml:space="preserve">0.310724824666977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310288995504379</t>
+    <t xml:space="preserve">0.310289025306702</t>
   </si>
   <si>
     <t xml:space="preserve">0.299829810857773</t>
@@ -1430,22 +1430,22 @@
     <t xml:space="preserve">0.296343445777893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316175937653</t>
+    <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289370626211166</t>
+    <t xml:space="preserve">0.289370596408844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627458572388</t>
+    <t xml:space="preserve">0.287627428770065</t>
   </si>
   <si>
     <t xml:space="preserve">0.298086643218994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560396432877</t>
+    <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30465242266655</t>
+    <t xml:space="preserve">0.304652452468872</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870839834213</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399640798569</t>
+    <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307614564896</t>
+    <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962866067886</t>
+    <t xml:space="preserve">0.293962836265564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054892301559</t>
+    <t xml:space="preserve">0.285054862499237</t>
   </si>
   <si>
     <t xml:space="preserve">0.283273309469223</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">0.281491696834564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29218128323555</t>
+    <t xml:space="preserve">0.292181223630905</t>
   </si>
   <si>
     <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902150630951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302665114402771</t>
+    <t xml:space="preserve">0.302665084600449</t>
   </si>
   <si>
     <t xml:space="preserve">0.291725397109985</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331837683916092</t>
+    <t xml:space="preserve">0.33183765411377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660989999771</t>
+    <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
     <t xml:space="preserve">0.320897966623306</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610083580017</t>
+    <t xml:space="preserve">0.331610113382339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021134853363</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
     <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117321252823</t>
+    <t xml:space="preserve">0.311117351055145</t>
   </si>
   <si>
     <t xml:space="preserve">0.309254318475723</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569272756577</t>
+    <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340925008058548</t>
+    <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
     <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391405105591</t>
+    <t xml:space="preserve">0.307391375303268</t>
   </si>
   <si>
     <t xml:space="preserve">0.301802426576614</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344650954008102</t>
+    <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199002504349</t>
+    <t xml:space="preserve">0.337199032306671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376899957657</t>
+    <t xml:space="preserve">0.348376929759979</t>
   </si>
   <si>
     <t xml:space="preserve">0.370732635259628</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362454414368</t>
+    <t xml:space="preserve">0.389362424612045</t>
   </si>
   <si>
     <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376321583986282</t>
+    <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.372595608234406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363280713558197</t>
+    <t xml:space="preserve">0.363280743360519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367006659507751</t>
+    <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869632482529</t>
+    <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37818455696106</t>
+    <t xml:space="preserve">0.378184527158737</t>
   </si>
   <si>
     <t xml:space="preserve">0.394951343536377</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">0.398170202970505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274209022522</t>
+    <t xml:space="preserve">0.3962741792202</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097760915756</t>
+    <t xml:space="preserve">0.409097731113434</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605693340302</t>
+    <t xml:space="preserve">0.422605663537979</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -68703,7 +68703,7 @@
     </row>
     <row r="2562">
       <c r="A2562" s="1" t="n">
-        <v>46052.4665625</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B2562" t="n">
         <v>4000</v>
@@ -68724,6 +68724,32 @@
         <v>582</v>
       </c>
       <c r="H2562" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" s="1" t="n">
+        <v>46055.4700231481</v>
+      </c>
+      <c r="B2563" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C2563" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D2563" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E2563" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F2563" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G2563" t="s">
+        <v>580</v>
+      </c>
+      <c r="H2563" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17599430680275</t>
+    <t xml:space="preserve">0.175994351506233</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622852683067</t>
+    <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
     <t xml:space="preserve">0.172851577401161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594470739365</t>
+    <t xml:space="preserve">0.171594485640526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051875472069</t>
+    <t xml:space="preserve">0.164051845669746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16970881819725</t>
+    <t xml:space="preserve">0.169708803296089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966655135155</t>
+    <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14330966770649</t>
+    <t xml:space="preserve">0.143309682607651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783730506897</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195335149765</t>
+    <t xml:space="preserve">0.145195350050926</t>
   </si>
   <si>
     <t xml:space="preserve">0.152737945318222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15336649119854</t>
+    <t xml:space="preserve">0.153366476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.150789439678192</t>
   </si>
   <si>
     <t xml:space="preserve">0.146452412009239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852643013</t>
+    <t xml:space="preserve">0.139852628111839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538362622261</t>
+    <t xml:space="preserve">0.139538377523422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915496110916</t>
+    <t xml:space="preserve">0.139915511012077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052546143532</t>
   </si>
   <si>
     <t xml:space="preserve">0.138909801840782</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337364077568</t>
+    <t xml:space="preserve">0.17033739387989</t>
   </si>
   <si>
     <t xml:space="preserve">0.166817471385002</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137811183929</t>
+    <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623568058014</t>
+    <t xml:space="preserve">0.154623582959175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595201015472</t>
+    <t xml:space="preserve">0.149595156311989</t>
   </si>
   <si>
     <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909101366997</t>
+    <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960610628128</t>
+    <t xml:space="preserve">0.158960595726967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314296364784</t>
+    <t xml:space="preserve">0.177314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17725145816803</t>
+    <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965924859047</t>
+    <t xml:space="preserve">0.170965939760208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937528014183</t>
+    <t xml:space="preserve">0.165937498211861</t>
   </si>
   <si>
     <t xml:space="preserve">0.188565388321877</t>
@@ -146,43 +146,43 @@
     <t xml:space="preserve">0.192650943994522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708102822304</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
     <t xml:space="preserve">0.184165492653847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651279330254</t>
+    <t xml:space="preserve">0.181651264429092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136395335197</t>
+    <t xml:space="preserve">0.201136410236359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208679005503654</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073527336121</t>
+    <t xml:space="preserve">0.201073497533798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736514568329</t>
+    <t xml:space="preserve">0.196736499667168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222316145897</t>
+    <t xml:space="preserve">0.194222286343575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137110710144</t>
+    <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
     <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834524393082</t>
+    <t xml:space="preserve">0.169834554195404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451696634293</t>
+    <t xml:space="preserve">0.168451726436615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794768810272</t>
+    <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
     <t xml:space="preserve">0.151606544852257</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109384536743</t>
+    <t xml:space="preserve">0.152109399437904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995037078857</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640635967255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051160097122</t>
+    <t xml:space="preserve">0.186051145195961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936797738075</t>
+    <t xml:space="preserve">0.187936827540398</t>
   </si>
   <si>
     <t xml:space="preserve">0.183536916971207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714132428169</t>
+    <t xml:space="preserve">0.18171414732933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194619774818</t>
+    <t xml:space="preserve">0.16719463467598</t>
   </si>
   <si>
     <t xml:space="preserve">0.160280555486679</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480823755264</t>
+    <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338094353676</t>
+    <t xml:space="preserve">0.148338079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566759467125</t>
+    <t xml:space="preserve">0.144566774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394917845726</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183246135712</t>
+    <t xml:space="preserve">0.165183261036873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651659369469</t>
+    <t xml:space="preserve">0.170651629567146</t>
   </si>
   <si>
     <t xml:space="preserve">0.172223016619682</t>
@@ -248,40 +248,40 @@
     <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507834553719</t>
+    <t xml:space="preserve">0.200507864356041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593740463257</t>
+    <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17813141644001</t>
+    <t xml:space="preserve">0.178131386637688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765261650085</t>
+    <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010659337044</t>
+    <t xml:space="preserve">0.201010674238205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850876927376</t>
+    <t xml:space="preserve">0.194850832223892</t>
   </si>
   <si>
     <t xml:space="preserve">0.191770955920219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879303574562</t>
+    <t xml:space="preserve">0.199879258871078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078871369362</t>
+    <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787323355675</t>
+    <t xml:space="preserve">0.216787293553352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563897967339</t>
+    <t xml:space="preserve">0.232563927769661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220900297165</t>
+    <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
     <t xml:space="preserve">0.251420468091965</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">0.267134249210358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305420160294</t>
+    <t xml:space="preserve">0.275305360555649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29039067029953</t>
+    <t xml:space="preserve">0.290390700101852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561781644821</t>
+    <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705956697464</t>
+    <t xml:space="preserve">0.257706016302109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157346725464</t>
+    <t xml:space="preserve">0.260157316923141</t>
   </si>
   <si>
     <t xml:space="preserve">0.250226199626923</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">0.250163376331329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809295654297</t>
+    <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249297142029</t>
+    <t xml:space="preserve">0.24324931204319</t>
   </si>
   <si>
     <t xml:space="preserve">0.243375033140182</t>
@@ -323,49 +323,49 @@
     <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821004629135</t>
+    <t xml:space="preserve">0.233821019530296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21056467294693</t>
+    <t xml:space="preserve">0.210564628243446</t>
   </si>
   <si>
     <t xml:space="preserve">0.20691904425621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821764707565</t>
+    <t xml:space="preserve">0.211821749806404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741873502731</t>
+    <t xml:space="preserve">0.208741843700409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592339515686</t>
+    <t xml:space="preserve">0.237592324614525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134979486465</t>
+    <t xml:space="preserve">0.245134919881821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230804026126862</t>
+    <t xml:space="preserve">0.230803981423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535545825958</t>
+    <t xml:space="preserve">0.227535501122475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706672072411</t>
+    <t xml:space="preserve">0.235706701874733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278424263</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
     <t xml:space="preserve">0.223135679960251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850116848946</t>
+    <t xml:space="preserve">0.216850131750107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381383180618</t>
+    <t xml:space="preserve">0.222381412982941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141694664955</t>
+    <t xml:space="preserve">0.213141724467278</t>
   </si>
   <si>
     <t xml:space="preserve">0.201199263334274</t>
@@ -377,43 +377,43 @@
     <t xml:space="preserve">0.20679335296154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164792180061</t>
+    <t xml:space="preserve">0.206164762377739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421854138374</t>
+    <t xml:space="preserve">0.207421913743019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804711699486</t>
+    <t xml:space="preserve">0.208804696798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947441101074</t>
+    <t xml:space="preserve">0.211947456002235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22564984858036</t>
+    <t xml:space="preserve">0.225649878382683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867199659348</t>
+    <t xml:space="preserve">0.219867184758186</t>
   </si>
   <si>
     <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484006762505</t>
+    <t xml:space="preserve">0.229484036564827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23438672721386</t>
+    <t xml:space="preserve">0.234386742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518477916718</t>
+    <t xml:space="preserve">0.22451850771904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992890954018</t>
+    <t xml:space="preserve">0.219992935657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741493463516</t>
+    <t xml:space="preserve">0.219741478562355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912984848022</t>
+    <t xml:space="preserve">0.216913029551506</t>
   </si>
   <si>
     <t xml:space="preserve">0.231306836009026</t>
@@ -422,31 +422,31 @@
     <t xml:space="preserve">0.217038735747337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324209451675</t>
+    <t xml:space="preserve">0.223324239253998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988613605499</t>
+    <t xml:space="preserve">0.351988703012466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127795934677</t>
+    <t xml:space="preserve">0.465127855539322</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070420980453</t>
+    <t xml:space="preserve">0.477070301771164</t>
   </si>
   <si>
     <t xml:space="preserve">0.436843127012253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072142362595</t>
+    <t xml:space="preserve">0.42207208275795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987272262573</t>
+    <t xml:space="preserve">0.395987123250961</t>
   </si>
   <si>
     <t xml:space="preserve">0.364559680223465</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">0.414215207099915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388188838959</t>
+    <t xml:space="preserve">0.367388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">0.373987972736359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331685781479</t>
+    <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
     <t xml:space="preserve">0.3259037733078</t>
@@ -473,25 +473,25 @@
     <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389239549637</t>
+    <t xml:space="preserve">0.334389269351959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818202733994</t>
+    <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
     <t xml:space="preserve">0.348845958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303318738937</t>
+    <t xml:space="preserve">0.341303259134293</t>
   </si>
   <si>
     <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361163139343</t>
+    <t xml:space="preserve">0.318361133337021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189671754837</t>
+    <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
     <t xml:space="preserve">0.333132117986679</t>
@@ -500,169 +500,169 @@
     <t xml:space="preserve">0.329989343881607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418366670609</t>
   </si>
   <si>
     <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275622367859</t>
+    <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
     <t xml:space="preserve">0.311761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703505039215</t>
+    <t xml:space="preserve">0.33470356464386</t>
   </si>
   <si>
     <t xml:space="preserve">0.318046897649765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789835691452</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
     <t xml:space="preserve">0.328417956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075264692307</t>
+    <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103750944138</t>
+    <t xml:space="preserve">0.328103691339493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704555749893</t>
+    <t xml:space="preserve">0.301704525947571</t>
   </si>
   <si>
     <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069935560226</t>
+    <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
     <t xml:space="preserve">0.320561110973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589537620544</t>
+    <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274221420288</t>
+    <t xml:space="preserve">0.358274191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417636394501</t>
+    <t xml:space="preserve">0.339417606592178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34004619717598</t>
+    <t xml:space="preserve">0.340046167373657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319303959608078</t>
+    <t xml:space="preserve">0.319304049015045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846279144287</t>
+    <t xml:space="preserve">0.337846338748932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589887857437</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789455652237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701753854752</t>
+    <t xml:space="preserve">0.389701664447784</t>
   </si>
   <si>
     <t xml:space="preserve">0.369588047266006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36895963549614</t>
+    <t xml:space="preserve">0.368959575891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37021666765213</t>
+    <t xml:space="preserve">0.370216637849808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616794347763</t>
+    <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
     <t xml:space="preserve">0.370845168828964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074623823166</t>
+    <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788725376129</t>
+    <t xml:space="preserve">0.349788695573807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35450291633606</t>
+    <t xml:space="preserve">0.354502856731415</t>
   </si>
   <si>
     <t xml:space="preserve">0.367073833942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758957386017</t>
+    <t xml:space="preserve">0.388758927583694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587406396866</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759248018265</t>
+    <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
     <t xml:space="preserve">0.377130776643753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187480926514</t>
+    <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444922924042</t>
+    <t xml:space="preserve">0.377444982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.407929688692093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843708276749</t>
+    <t xml:space="preserve">0.414843827486038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215996980667</t>
+    <t xml:space="preserve">0.392215967178345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376816481351852</t>
+    <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386558949947357</t>
+    <t xml:space="preserve">0.386559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413344144821</t>
+    <t xml:space="preserve">0.471413403749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357280731201</t>
+    <t xml:space="preserve">0.439357340335846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556848526001</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700233697891</t>
+    <t xml:space="preserve">0.433700263500214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100159168243</t>
+    <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
     <t xml:space="preserve">0.446271359920502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985781908035</t>
+    <t xml:space="preserve">0.439985871315002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386348247528</t>
+    <t xml:space="preserve">0.42238637804985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900650978088</t>
+    <t xml:space="preserve">0.424900591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42112934589386</t>
+    <t xml:space="preserve">0.421129256486893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40981537103653</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044125556946</t>
+    <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
     <t xml:space="preserve">0.408558279275894</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">0.41358670592308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272790670395</t>
+    <t xml:space="preserve">0.402272820472717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443171739578</t>
+    <t xml:space="preserve">0.432443231344223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417358011007309</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
     <t xml:space="preserve">0.462613672018051</t>
@@ -686,82 +686,82 @@
     <t xml:space="preserve">0.427414864301682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758607149124</t>
+    <t xml:space="preserve">0.399758517742157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615072965622</t>
+    <t xml:space="preserve">0.4186150431633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643529415131</t>
+    <t xml:space="preserve">0.423643499612808</t>
   </si>
   <si>
     <t xml:space="preserve">0.411072462797165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501425981522</t>
+    <t xml:space="preserve">0.398501455783844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786944389343</t>
+    <t xml:space="preserve">0.404787003993988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159173488617</t>
+    <t xml:space="preserve">0.382159113883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416205644608</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444632291794</t>
+    <t xml:space="preserve">0.388444572687149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529912233353</t>
+    <t xml:space="preserve">0.403529852628708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43118605017662</t>
+    <t xml:space="preserve">0.43118616938591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872224330902</t>
+    <t xml:space="preserve">0.419872134923935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301098108292</t>
+    <t xml:space="preserve">0.407301187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730120897293</t>
+    <t xml:space="preserve">0.394730150699615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329584360123</t>
+    <t xml:space="preserve">0.412329524755478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015669107437</t>
+    <t xml:space="preserve">0.401015728712082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100829839706</t>
+    <t xml:space="preserve">0.416100919246674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045496702194</t>
+    <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816742181778</t>
+    <t xml:space="preserve">0.365816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302558660507</t>
+    <t xml:space="preserve">0.363302528858185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674728155136</t>
+    <t xml:space="preserve">0.340674787759781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360842704773</t>
+    <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531313180923</t>
+    <t xml:space="preserve">0.359531253576279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017070055008</t>
+    <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
     <t xml:space="preserve">0.344446033239365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903393268585</t>
+    <t xml:space="preserve">0.33690345287323</t>
   </si>
   <si>
     <t xml:space="preserve">0.338160514831543</t>
@@ -770,43 +770,43 @@
     <t xml:space="preserve">0.345703154802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102320194244</t>
+    <t xml:space="preserve">0.372102290391922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930478572845</t>
+    <t xml:space="preserve">0.385930418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245705366135</t>
+    <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
     <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387808799744</t>
+    <t xml:space="preserve">0.378387838602066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873595476151</t>
+    <t xml:space="preserve">0.375873655080795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359441757202</t>
+    <t xml:space="preserve">0.37335941195488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673327207565</t>
+    <t xml:space="preserve">0.384673357009888</t>
   </si>
   <si>
     <t xml:space="preserve">0.390958786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393473029136658</t>
+    <t xml:space="preserve">0.393472999334335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557548999786</t>
+    <t xml:space="preserve">0.430557578802109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414014816284</t>
+    <t xml:space="preserve">0.449414044618607</t>
   </si>
   <si>
     <t xml:space="preserve">0.455699592828751</t>
@@ -818,100 +818,97 @@
     <t xml:space="preserve">0.443181872367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332435131073</t>
+    <t xml:space="preserve">0.429332405328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483057498932</t>
+    <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870031118393</t>
+    <t xml:space="preserve">0.425870001316071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257153749466</t>
+    <t xml:space="preserve">0.436257064342499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719468355179</t>
+    <t xml:space="preserve">0.439719438552856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794868946075</t>
+    <t xml:space="preserve">0.432794690132141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4189453125</t>
+    <t xml:space="preserve">0.418945372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558219671249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401633530855179</t>
+    <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
     <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784063816071</t>
+    <t xml:space="preserve">0.387784093618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246497631073</t>
+    <t xml:space="preserve">0.391246527433395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095845460892</t>
+    <t xml:space="preserve">0.405095875263214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422407686710358</t>
+    <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644186973572</t>
+    <t xml:space="preserve">0.446644246578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106590986252</t>
+    <t xml:space="preserve">0.450106531381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031190395355</t>
+    <t xml:space="preserve">0.457031309604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568905591965</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171246051788</t>
+    <t xml:space="preserve">0.398171126842499</t>
   </si>
   <si>
     <t xml:space="preserve">0.394708871841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859404802322</t>
+    <t xml:space="preserve">0.380859375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934656381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360085219144821</t>
+    <t xml:space="preserve">0.360085248947144</t>
   </si>
   <si>
     <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384321808815002</t>
+    <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009967565536</t>
+    <t xml:space="preserve">0.367009997367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696007013321</t>
+    <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311093091965</t>
+    <t xml:space="preserve">0.339311152696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160530328751</t>
+    <t xml:space="preserve">0.353160500526428</t>
   </si>
   <si>
     <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386344671249</t>
   </si>
   <si>
     <t xml:space="preserve">0.311612248420715</t>
@@ -920,112 +917,115 @@
     <t xml:space="preserve">0.31438210606575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838122367859</t>
+    <t xml:space="preserve">0.290838032960892</t>
   </si>
   <si>
     <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373628854752</t>
+    <t xml:space="preserve">0.278373658657074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833794355392</t>
+    <t xml:space="preserve">0.272833824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754274368286</t>
+    <t xml:space="preserve">0.261754244565964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
     <t xml:space="preserve">0.24928979575634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750020861626</t>
+    <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298317670822</t>
+    <t xml:space="preserve">0.285298347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683261394501</t>
+    <t xml:space="preserve">0.286683291196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448880434036</t>
+    <t xml:space="preserve">0.271448910236359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758542776108</t>
+    <t xml:space="preserve">0.279758602380753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143456697464</t>
+    <t xml:space="preserve">0.281143516302109</t>
   </si>
   <si>
     <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302586078644</t>
+    <t xml:space="preserve">0.303302556276321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842360973358</t>
+    <t xml:space="preserve">0.308842390775681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926179170609</t>
+    <t xml:space="preserve">0.337926208972931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461655855179</t>
+    <t xml:space="preserve">0.325461715459824</t>
   </si>
   <si>
     <t xml:space="preserve">0.319921910762787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465924263</t>
+    <t xml:space="preserve">0.343465954065323</t>
   </si>
   <si>
     <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397030591965</t>
+    <t xml:space="preserve">0.377397090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231602907181</t>
+    <t xml:space="preserve">0.328231543302536</t>
   </si>
   <si>
     <t xml:space="preserve">0.331001430749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33654123544693</t>
+    <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698156118393</t>
+    <t xml:space="preserve">0.349698185920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850867986679</t>
+    <t xml:space="preserve">0.344850897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691768407822</t>
+    <t xml:space="preserve">0.322691798210144</t>
   </si>
   <si>
     <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306794881821</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
     <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072443723679</t>
+    <t xml:space="preserve">0.306072473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317151993513107</t>
+    <t xml:space="preserve">0.31715202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687529802322</t>
+    <t xml:space="preserve">0.304687470197678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762840986252</t>
+    <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913344144821</t>
+    <t xml:space="preserve">0.283913373947144</t>
   </si>
   <si>
     <t xml:space="preserve">0.288068205118179</t>
@@ -1034,148 +1034,148 @@
     <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294079065323</t>
+    <t xml:space="preserve">0.267294049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369300842285</t>
+    <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
     <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27006396651268</t>
+    <t xml:space="preserve">0.270063906908035</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223036289215</t>
+    <t xml:space="preserve">0.292223006486893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377837657928</t>
+    <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453148841858</t>
+    <t xml:space="preserve">0.289453119039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429810017347336</t>
+    <t xml:space="preserve">0.429809987545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647861719131</t>
+    <t xml:space="preserve">0.399647891521454</t>
   </si>
   <si>
     <t xml:space="preserve">0.388337045907974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026319503784</t>
+    <t xml:space="preserve">0.377026259899139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945241689682</t>
+    <t xml:space="preserve">0.36194521188736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485765695572</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453328609467</t>
+    <t xml:space="preserve">0.363453358411789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380796521902084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
     <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880337715149</t>
+    <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
     <t xml:space="preserve">0.343847960233688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339873313904</t>
+    <t xml:space="preserve">0.342339903116226</t>
   </si>
   <si>
     <t xml:space="preserve">0.339323669672012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.35289654135704</t>
   </si>
   <si>
     <t xml:space="preserve">0.34686416387558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388514041901</t>
+    <t xml:space="preserve">0.351388484239578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307406425476</t>
+    <t xml:space="preserve">0.336307495832443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799408912659</t>
+    <t xml:space="preserve">0.334799379110336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372310400009</t>
+    <t xml:space="preserve">0.348372340202332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350481748581</t>
+    <t xml:space="preserve">0.437350511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958647727966</t>
+    <t xml:space="preserve">0.410958737134933</t>
   </si>
   <si>
     <t xml:space="preserve">0.452431589365005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444890946149826</t>
+    <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120684146881</t>
+    <t xml:space="preserve">0.441120713949203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728939533234</t>
+    <t xml:space="preserve">0.414728909730911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418213129044</t>
+    <t xml:space="preserve">0.403418183326721</t>
   </si>
   <si>
     <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566813707352</t>
+    <t xml:space="preserve">0.384566783905029</t>
   </si>
   <si>
     <t xml:space="preserve">0.395877599716187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188445329666</t>
+    <t xml:space="preserve">0.407188385725021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501969337463</t>
+    <t xml:space="preserve">0.372501939535141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469621658325</t>
+    <t xml:space="preserve">0.366469532251358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404717683792</t>
+    <t xml:space="preserve">0.354404747486115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34535613656044</t>
+    <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831786394119</t>
+    <t xml:space="preserve">0.340831726789474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993822813034</t>
+    <t xml:space="preserve">0.370993852615356</t>
   </si>
   <si>
     <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36797770857811</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929067850113</t>
+    <t xml:space="preserve">0.358929008245468</t>
   </si>
   <si>
     <t xml:space="preserve">0.316702097654343</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">0.30162101984024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31821021437645</t>
+    <t xml:space="preserve">0.318210184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718301296234</t>
   </si>
   <si>
     <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258765697479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330274999141693</t>
+    <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783145666122</t>
+    <t xml:space="preserve">0.331783086061478</t>
   </si>
   <si>
     <t xml:space="preserve">0.337815582752228</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">0.30916154384613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653456926346</t>
+    <t xml:space="preserve">0.307653427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30312916636467</t>
+    <t xml:space="preserve">0.303129196166992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685894012451</t>
+    <t xml:space="preserve">0.313685834407806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734475135803</t>
+    <t xml:space="preserve">0.322734534740448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599177360535</t>
+    <t xml:space="preserve">0.317599236965179</t>
   </si>
   <si>
     <t xml:space="preserve">0.322339475154877</t>
@@ -1235,31 +1235,31 @@
     <t xml:space="preserve">0.314438998699188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31917929649353</t>
+    <t xml:space="preserve">0.319179326295853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820070743561</t>
+    <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400160074234</t>
+    <t xml:space="preserve">0.333400189876556</t>
   </si>
   <si>
     <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919504880905</t>
+    <t xml:space="preserve">0.323919534683228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858879566193</t>
+    <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378313779831</t>
+    <t xml:space="preserve">0.303378283977509</t>
   </si>
   <si>
     <t xml:space="preserve">0.292317688465118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798224449158</t>
+    <t xml:space="preserve">0.30179825425148</t>
   </si>
   <si>
     <t xml:space="preserve">0.316019088029861</t>
@@ -1283,76 +1283,76 @@
     <t xml:space="preserve">0.279676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516735553741</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096824884415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196318626404</t>
+    <t xml:space="preserve">0.270196288824081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257063150406</t>
+    <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776378154755</t>
+    <t xml:space="preserve">0.271776437759399</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997301340103</t>
+    <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477837324142</t>
+    <t xml:space="preserve">0.295477896928787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057896852493</t>
+    <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118641376495</t>
+    <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289157450199127</t>
+    <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
     <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140428066254</t>
+    <t xml:space="preserve">0.338140457868576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720547199249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3413006067276</t>
+    <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980189800262</t>
+    <t xml:space="preserve">0.334980219602585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560368537903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.35236132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359253883362</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944772005081</t>
+    <t xml:space="preserve">0.291944712400436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237456560135</t>
+    <t xml:space="preserve">0.290237426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115569829941</t>
+    <t xml:space="preserve">0.285115659236908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822915077209</t>
+    <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481110811234</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
     <t xml:space="preserve">0.298773854970932</t>
@@ -1370,31 +1370,31 @@
     <t xml:space="preserve">0.279993802309036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164629936218</t>
+    <t xml:space="preserve">0.273164659738541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579231023788</t>
+    <t xml:space="preserve">0.276579201221466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750148057938</t>
+    <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701117753983</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871975183487</t>
+    <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
     <t xml:space="preserve">0.271457374095917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042832612991</t>
+    <t xml:space="preserve">0.268042862415314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895682096481</t>
+    <t xml:space="preserve">0.303895711898804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
     <t xml:space="preserve">0.30218842625618</t>
@@ -1403,34 +1403,34 @@
     <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310283184052</t>
+    <t xml:space="preserve">0.307310223579407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383050203323</t>
+    <t xml:space="preserve">0.324383020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261252880096</t>
+    <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017568826675</t>
+    <t xml:space="preserve">0.309017539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139395952225</t>
+    <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432110309601</t>
+    <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724824666977</t>
+    <t xml:space="preserve">0.310724765062332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310288965702057</t>
+    <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
     <t xml:space="preserve">0.299829810857773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343445777893</t>
+    <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
     <t xml:space="preserve">0.303316205739975</t>
@@ -1448,97 +1448,97 @@
     <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30465242266655</t>
+    <t xml:space="preserve">0.304652392864227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302870839834213</t>
+    <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306433975696564</t>
+    <t xml:space="preserve">0.306434035301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089227199554</t>
+    <t xml:space="preserve">0.301089197397232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836475133896</t>
+    <t xml:space="preserve">0.286836504936218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618057966232</t>
+    <t xml:space="preserve">0.288618087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399670600891</t>
+    <t xml:space="preserve">0.290399700403214</t>
   </si>
   <si>
     <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962836265564</t>
+    <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
     <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273309469223</t>
+    <t xml:space="preserve">0.283273249864578</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710084199905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491726636887</t>
+    <t xml:space="preserve">0.281491696834564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292181253433228</t>
+    <t xml:space="preserve">0.29218128323555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295371979475021</t>
+    <t xml:space="preserve">0.295372009277344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289902120828629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302665114402771</t>
+    <t xml:space="preserve">0.302665084600449</t>
   </si>
   <si>
     <t xml:space="preserve">0.291725426912308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488390684128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308135002851486</t>
+    <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781585216522</t>
+    <t xml:space="preserve">0.3117815554142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31725138425827</t>
+    <t xml:space="preserve">0.317251414060593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313604831695557</t>
+    <t xml:space="preserve">0.313604861497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191131353378</t>
+    <t xml:space="preserve">0.328191101551056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331837683916092</t>
+    <t xml:space="preserve">0.331837624311447</t>
   </si>
   <si>
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897966623306</t>
+    <t xml:space="preserve">0.320897936820984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324544548988342</t>
+    <t xml:space="preserve">0.32454451918602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158161878586</t>
+    <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329747140407562</t>
+    <t xml:space="preserve">0.32974711060524</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021134853363</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432215929031</t>
+    <t xml:space="preserve">0.320432245731354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117351055145</t>
+    <t xml:space="preserve">0.311117321252823</t>
   </si>
   <si>
     <t xml:space="preserve">0.309254318475723</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569272756577</t>
+    <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340924978256226</t>
+    <t xml:space="preserve">0.340925008058548</t>
   </si>
   <si>
     <t xml:space="preserve">0.333473086357117</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">0.344650954008102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199002504349</t>
+    <t xml:space="preserve">0.337199032306671</t>
   </si>
   <si>
     <t xml:space="preserve">0.348376899957657</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40799218416214</t>
+    <t xml:space="preserve">0.407992213964462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417307108640671</t>
+    <t xml:space="preserve">0.417307078838348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409855157136917</t>
+    <t xml:space="preserve">0.40985518693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540322065353</t>
+    <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
     <t xml:space="preserve">0.3912253677845</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362424612045</t>
+    <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
     <t xml:space="preserve">0.374458611011505</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869632482529</t>
+    <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378184527158737</t>
+    <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
     <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407650470733643</t>
+    <t xml:space="preserve">0.407650500535965</t>
   </si>
   <si>
     <t xml:space="preserve">0.392482101917267</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403858363628387</t>
+    <t xml:space="preserve">0.40385839343071</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
@@ -26188,7 +26188,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26214,7 +26214,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26240,7 +26240,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26266,7 +26266,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26292,7 +26292,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26318,7 +26318,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26344,7 +26344,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26370,7 +26370,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26396,7 +26396,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26422,7 +26422,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26448,7 +26448,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26474,7 +26474,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26500,7 +26500,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26526,7 +26526,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26552,7 +26552,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26578,7 +26578,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26630,7 +26630,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26656,7 +26656,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26682,7 +26682,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26708,7 +26708,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26734,7 +26734,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26760,7 +26760,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26786,7 +26786,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26812,7 +26812,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26838,7 +26838,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26864,7 +26864,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26890,7 +26890,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26916,7 +26916,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26942,7 +26942,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26968,7 +26968,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26994,7 +26994,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27020,7 +27020,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27046,7 +27046,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27072,7 +27072,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27098,7 +27098,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27176,7 +27176,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27254,7 +27254,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27280,7 +27280,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27332,7 +27332,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27358,7 +27358,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27384,7 +27384,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27410,7 +27410,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27566,7 +27566,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27592,7 +27592,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27618,7 +27618,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27696,7 +27696,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27722,7 +27722,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28138,7 +28138,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28164,7 +28164,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28190,7 +28190,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28216,7 +28216,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28242,7 +28242,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28294,7 +28294,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28320,7 +28320,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28346,7 +28346,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28398,7 +28398,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28424,7 +28424,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28450,7 +28450,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28476,7 +28476,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28502,7 +28502,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28528,7 +28528,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28554,7 +28554,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28580,7 +28580,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28606,7 +28606,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28632,7 +28632,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28658,7 +28658,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28736,7 +28736,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28762,7 +28762,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28788,7 +28788,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28814,7 +28814,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28840,7 +28840,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28866,7 +28866,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28892,7 +28892,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28918,7 +28918,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28944,7 +28944,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28970,7 +28970,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28996,7 +28996,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29022,7 +29022,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29048,7 +29048,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29074,7 +29074,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29100,7 +29100,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29126,7 +29126,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29152,7 +29152,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29178,7 +29178,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29204,7 +29204,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29230,7 +29230,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29256,7 +29256,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29360,7 +29360,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29412,7 +29412,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29490,7 +29490,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29516,7 +29516,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29542,7 +29542,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29568,7 +29568,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29594,7 +29594,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29620,7 +29620,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29646,7 +29646,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29672,7 +29672,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29698,7 +29698,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29724,7 +29724,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29750,7 +29750,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29776,7 +29776,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29802,7 +29802,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29828,7 +29828,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29854,7 +29854,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29880,7 +29880,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29906,7 +29906,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29932,7 +29932,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29958,7 +29958,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30140,7 +30140,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30270,7 +30270,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30296,7 +30296,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30322,7 +30322,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30374,7 +30374,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30400,7 +30400,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30478,7 +30478,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30868,7 +30868,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30894,7 +30894,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30998,7 +30998,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31050,7 +31050,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31076,7 +31076,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31102,7 +31102,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31206,7 +31206,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31232,7 +31232,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31258,7 +31258,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31310,7 +31310,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31336,7 +31336,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31362,7 +31362,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31388,7 +31388,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31414,7 +31414,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31440,7 +31440,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31466,7 +31466,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31492,7 +31492,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31518,7 +31518,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31544,7 +31544,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31570,7 +31570,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31596,7 +31596,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31622,7 +31622,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31648,7 +31648,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31674,7 +31674,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31700,7 +31700,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31726,7 +31726,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31752,7 +31752,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31778,7 +31778,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31804,7 +31804,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31830,7 +31830,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31856,7 +31856,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31882,7 +31882,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31908,7 +31908,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31934,7 +31934,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31960,7 +31960,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31986,7 +31986,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32038,7 +32038,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32064,7 +32064,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32090,7 +32090,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32142,7 +32142,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32324,7 +32324,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32350,7 +32350,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32376,7 +32376,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32402,7 +32402,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32740,7 +32740,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33234,7 +33234,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34274,7 +34274,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34482,7 +34482,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34508,7 +34508,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35002,7 +35002,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35652,7 +35652,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35678,7 +35678,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35730,7 +35730,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35756,7 +35756,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35782,7 +35782,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35808,7 +35808,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35860,7 +35860,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35886,7 +35886,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35912,7 +35912,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35964,7 +35964,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35990,7 +35990,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36016,7 +36016,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36042,7 +36042,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36068,7 +36068,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36094,7 +36094,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36120,7 +36120,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36146,7 +36146,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36172,7 +36172,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -68810,7 +68810,7 @@
     </row>
     <row r="2566">
       <c r="A2566" s="1" t="n">
-        <v>46058.4438773148</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2566" t="n">
         <v>4000</v>
@@ -68831,6 +68831,32 @@
         <v>579</v>
       </c>
       <c r="H2566" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" s="1" t="n">
+        <v>46059.675462963</v>
+      </c>
+      <c r="B2567" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C2567" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D2567" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="E2567" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="F2567" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2567" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -47,91 +47,91 @@
     <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851592302322</t>
+    <t xml:space="preserve">0.172851607203484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594470739365</t>
+    <t xml:space="preserve">0.171594500541687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051830768585</t>
+    <t xml:space="preserve">0.164051860570908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169708833098412</t>
+    <t xml:space="preserve">0.169708847999573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966640233994</t>
+    <t xml:space="preserve">0.148966655135155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309682607651</t>
+    <t xml:space="preserve">0.14330966770649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783730506897</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195320248604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737960219383</t>
+    <t xml:space="preserve">0.152737930417061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153366506099701</t>
+    <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789439678192</t>
+    <t xml:space="preserve">0.150789424777031</t>
   </si>
   <si>
     <t xml:space="preserve">0.1464524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852628111839</t>
+    <t xml:space="preserve">0.139852643013</t>
   </si>
   <si>
     <t xml:space="preserve">0.1395383477211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915511012077</t>
+    <t xml:space="preserve">0.139915481209755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052575945854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909801840782</t>
+    <t xml:space="preserve">0.138909816741943</t>
   </si>
   <si>
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337349176407</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817486286163</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423269987106</t>
+    <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137796282768</t>
+    <t xml:space="preserve">0.157137811183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623582959175</t>
+    <t xml:space="preserve">0.154623597860336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595215916634</t>
+    <t xml:space="preserve">0.14959517121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692130327225</t>
+    <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909101366997</t>
+    <t xml:space="preserve">0.160909131169319</t>
   </si>
   <si>
     <t xml:space="preserve">0.158960595726967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314311265945</t>
+    <t xml:space="preserve">0.177314266562462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251413464546</t>
+    <t xml:space="preserve">0.177251443266869</t>
   </si>
   <si>
     <t xml:space="preserve">0.170965939760208</t>
@@ -140,157 +140,157 @@
     <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565403223038</t>
+    <t xml:space="preserve">0.188565373420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650929093361</t>
+    <t xml:space="preserve">0.1926509141922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708117723465</t>
+    <t xml:space="preserve">0.191708102822304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165492653847</t>
+    <t xml:space="preserve">0.184165507555008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651294231415</t>
+    <t xml:space="preserve">0.181651279330254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136380434036</t>
+    <t xml:space="preserve">0.201136365532875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208679005503654</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073497533798</t>
+    <t xml:space="preserve">0.201073512434959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736499667168</t>
+    <t xml:space="preserve">0.19673652946949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222301244736</t>
+    <t xml:space="preserve">0.194222286343575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137125611305</t>
+    <t xml:space="preserve">0.17913706600666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279840111732</t>
+    <t xml:space="preserve">0.182279825210571</t>
   </si>
   <si>
     <t xml:space="preserve">0.169834539294243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451711535454</t>
+    <t xml:space="preserve">0.168451726436615</t>
   </si>
   <si>
     <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606544852257</t>
+    <t xml:space="preserve">0.151606574654579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16656605899334</t>
+    <t xml:space="preserve">0.166566044092178</t>
   </si>
   <si>
     <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109369635582</t>
+    <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15399506688118</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051174998283</t>
+    <t xml:space="preserve">0.1860511302948</t>
   </si>
   <si>
     <t xml:space="preserve">0.187936797738075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536976575851</t>
+    <t xml:space="preserve">0.183536931872368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18171414732933</t>
+    <t xml:space="preserve">0.181714162230492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194604873657</t>
+    <t xml:space="preserve">0.16719463467598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160280555486679</t>
+    <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080987691879</t>
+    <t xml:space="preserve">0.147080957889557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480823755264</t>
+    <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
     <t xml:space="preserve">0.148338079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566774368286</t>
+    <t xml:space="preserve">0.144566789269447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394888043404</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183261036873</t>
+    <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17065167427063</t>
+    <t xml:space="preserve">0.170651659369469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223016619682</t>
+    <t xml:space="preserve">0.172223031520844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594120502472</t>
+    <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507804751396</t>
+    <t xml:space="preserve">0.200507819652557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593725562096</t>
+    <t xml:space="preserve">0.193593755364418</t>
   </si>
   <si>
     <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765276551247</t>
+    <t xml:space="preserve">0.190765336155891</t>
   </si>
   <si>
     <t xml:space="preserve">0.201010689139366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850876927376</t>
+    <t xml:space="preserve">0.194850862026215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770955920219</t>
+    <t xml:space="preserve">0.191770941019058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19987927377224</t>
+    <t xml:space="preserve">0.199879288673401</t>
   </si>
   <si>
     <t xml:space="preserve">0.213078826665878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787338256836</t>
+    <t xml:space="preserve">0.216787278652191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2325639128685</t>
+    <t xml:space="preserve">0.232563927769661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220870494843</t>
+    <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420527696609</t>
+    <t xml:space="preserve">0.251420468091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134249210358</t>
+    <t xml:space="preserve">0.267134219408035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305390357971</t>
+    <t xml:space="preserve">0.275305420160294</t>
   </si>
   <si>
     <t xml:space="preserve">0.290390640497208</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">0.298561781644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705986499786</t>
+    <t xml:space="preserve">0.257706016302109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157346725464</t>
+    <t xml:space="preserve">0.260157376527786</t>
   </si>
   <si>
     <t xml:space="preserve">0.2502261698246</t>
@@ -311,64 +311,64 @@
     <t xml:space="preserve">0.250163376331329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809325456619</t>
+    <t xml:space="preserve">0.24280934035778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249282240868</t>
+    <t xml:space="preserve">0.243249326944351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375018239021</t>
+    <t xml:space="preserve">0.243374988436699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421198368073</t>
+    <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23382106423378</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564628243446</t>
+    <t xml:space="preserve">0.210564687848091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919014453888</t>
+    <t xml:space="preserve">0.206919059157372</t>
   </si>
   <si>
     <t xml:space="preserve">0.211821734905243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741843700409</t>
+    <t xml:space="preserve">0.20874185860157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592324614525</t>
+    <t xml:space="preserve">0.237592339515686</t>
   </si>
   <si>
     <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803966522217</t>
+    <t xml:space="preserve">0.2308040112257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535516023636</t>
+    <t xml:space="preserve">0.227535501122475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706686973572</t>
+    <t xml:space="preserve">0.235706701874733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278424263</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135650157928</t>
+    <t xml:space="preserve">0.223135679960251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850161552429</t>
+    <t xml:space="preserve">0.216850191354752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381383180618</t>
+    <t xml:space="preserve">0.222381398081779</t>
   </si>
   <si>
     <t xml:space="preserve">0.213141694664955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199248433113</t>
+    <t xml:space="preserve">0.201199233531952</t>
   </si>
   <si>
     <t xml:space="preserve">0.204279124736786</t>
@@ -377,37 +377,37 @@
     <t xml:space="preserve">0.20679335296154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164792180061</t>
+    <t xml:space="preserve">0.2061647772789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421883940697</t>
+    <t xml:space="preserve">0.207421913743019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804726600647</t>
+    <t xml:space="preserve">0.208804666996002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947441101074</t>
+    <t xml:space="preserve">0.211947456002235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22564984858036</t>
+    <t xml:space="preserve">0.225649863481522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867214560509</t>
+    <t xml:space="preserve">0.219867199659348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22080996632576</t>
+    <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484051465988</t>
+    <t xml:space="preserve">0.229484081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386757016182</t>
+    <t xml:space="preserve">0.234386742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518492817879</t>
+    <t xml:space="preserve">0.224518477916718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992876052856</t>
+    <t xml:space="preserve">0.21999292075634</t>
   </si>
   <si>
     <t xml:space="preserve">0.219741493463516</t>
@@ -416,40 +416,40 @@
     <t xml:space="preserve">0.216912999749184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306806206703</t>
+    <t xml:space="preserve">0.231306836009026</t>
   </si>
   <si>
     <t xml:space="preserve">0.217038735747337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324224352837</t>
+    <t xml:space="preserve">0.223324239253998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
     <t xml:space="preserve">0.351988643407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127825737</t>
+    <t xml:space="preserve">0.465127855539322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582354068756</t>
+    <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070301771164</t>
+    <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843067407608</t>
+    <t xml:space="preserve">0.436843037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072172164917</t>
+    <t xml:space="preserve">0.422072142362595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987182855606</t>
+    <t xml:space="preserve">0.395987242460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559680223465</t>
+    <t xml:space="preserve">0.364559650421143</t>
   </si>
   <si>
     <t xml:space="preserve">0.414215207099915</t>
@@ -458,211 +458,211 @@
     <t xml:space="preserve">0.367388188838959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373988002538681</t>
+    <t xml:space="preserve">0.373987942934036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331655979156</t>
+    <t xml:space="preserve">0.346331745386124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903743505478</t>
+    <t xml:space="preserve">0.325903713703156</t>
   </si>
   <si>
     <t xml:space="preserve">0.314904153347015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532393693924</t>
+    <t xml:space="preserve">0.326532304286957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389209747314</t>
+    <t xml:space="preserve">0.334389269351959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818202733994</t>
+    <t xml:space="preserve">0.321818262338638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845928907394</t>
+    <t xml:space="preserve">0.348845899105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34130334854126</t>
+    <t xml:space="preserve">0.341303318738937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846539974213</t>
+    <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361192941666</t>
+    <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.321189612150192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132117986679</t>
+    <t xml:space="preserve">0.333132088184357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989403486252</t>
+    <t xml:space="preserve">0.329989373683929</t>
   </si>
   <si>
     <t xml:space="preserve">0.317418366670609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332416057587</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275592565536</t>
+    <t xml:space="preserve">0.314275622367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761409044266</t>
+    <t xml:space="preserve">0.311761349439621</t>
   </si>
   <si>
     <t xml:space="preserve">0.334703505039215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046927452087</t>
+    <t xml:space="preserve">0.318046867847443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789776086807</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
     <t xml:space="preserve">0.328417986631393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075354099274</t>
+    <t xml:space="preserve">0.323075294494629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32810366153717</t>
+    <t xml:space="preserve">0.328103721141815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704555749893</t>
+    <t xml:space="preserve">0.301704496145248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31050431728363</t>
+    <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069995164871</t>
+    <t xml:space="preserve">0.311070024967194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561110973358</t>
+    <t xml:space="preserve">0.320561081171036</t>
   </si>
   <si>
     <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35827425122261</t>
+    <t xml:space="preserve">0.358274132013321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417666196823</t>
+    <t xml:space="preserve">0.339417695999146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046226978302</t>
+    <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3193039894104</t>
+    <t xml:space="preserve">0.319304019212723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846279144287</t>
+    <t xml:space="preserve">0.337846308946609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31458991765976</t>
+    <t xml:space="preserve">0.314589887857437</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701753854752</t>
+    <t xml:space="preserve">0.389701724052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588136672974</t>
+    <t xml:space="preserve">0.369588077068329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959546089172</t>
+    <t xml:space="preserve">0.36895951628685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216637849808</t>
+    <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616913557053</t>
+    <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845168828964</t>
+    <t xml:space="preserve">0.370845139026642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074564218521</t>
+    <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788755178452</t>
+    <t xml:space="preserve">0.349788695573807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502826929092</t>
+    <t xml:space="preserve">0.354502886533737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073953151703</t>
+    <t xml:space="preserve">0.367073863744736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758897781372</t>
+    <t xml:space="preserve">0.388758838176727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587346792221</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759248018265</t>
+    <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130806446075</t>
+    <t xml:space="preserve">0.377130746841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187451124191</t>
+    <t xml:space="preserve">0.387187510728836</t>
   </si>
   <si>
     <t xml:space="preserve">0.377444982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.407929748296738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843767881393</t>
+    <t xml:space="preserve">0.414843827486038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3922159075737</t>
+    <t xml:space="preserve">0.392215937376022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37681645154953</t>
+    <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386558949947357</t>
+    <t xml:space="preserve">0.38655897974968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413373947144</t>
+    <t xml:space="preserve">0.471413403749466</t>
   </si>
   <si>
     <t xml:space="preserve">0.439357310533524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556848526001</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700323104858</t>
+    <t xml:space="preserve">0.433700382709503</t>
   </si>
   <si>
     <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271300315857</t>
+    <t xml:space="preserve">0.446271359920502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985752105713</t>
+    <t xml:space="preserve">0.43998584151268</t>
   </si>
   <si>
     <t xml:space="preserve">0.42238637804985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900561571121</t>
+    <t xml:space="preserve">0.424900591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129256486893</t>
+    <t xml:space="preserve">0.421129375696182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815311431885</t>
+    <t xml:space="preserve">0.409815341234207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044006347656</t>
+    <t xml:space="preserve">0.406044036149979</t>
   </si>
   <si>
     <t xml:space="preserve">0.408558249473572</t>
@@ -671,154 +671,154 @@
     <t xml:space="preserve">0.41358670592308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272760868073</t>
+    <t xml:space="preserve">0.40227273106575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443201541901</t>
+    <t xml:space="preserve">0.432443261146545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417358011007309</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613612413406</t>
+    <t xml:space="preserve">0.462613672018051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414804697037</t>
+    <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758547544479</t>
+    <t xml:space="preserve">0.399758577346802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615013360977</t>
+    <t xml:space="preserve">0.418615102767944</t>
   </si>
   <si>
     <t xml:space="preserve">0.423643469810486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072462797165</t>
+    <t xml:space="preserve">0.41107252240181</t>
   </si>
   <si>
     <t xml:space="preserve">0.398501425981522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786914587021</t>
+    <t xml:space="preserve">0.404786944389343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38215908408165</t>
+    <t xml:space="preserve">0.382159054279327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38341623544693</t>
+    <t xml:space="preserve">0.383416205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444602489471</t>
+    <t xml:space="preserve">0.388444572687149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529822826385</t>
+    <t xml:space="preserve">0.403529912233353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186109781265</t>
+    <t xml:space="preserve">0.431186139583588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872164726257</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301157712936</t>
+    <t xml:space="preserve">0.407301247119904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730180501938</t>
+    <t xml:space="preserve">0.394730150699615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329584360123</t>
+    <t xml:space="preserve">0.4123295545578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015609502792</t>
+    <t xml:space="preserve">0.401015639305115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100829839706</t>
+    <t xml:space="preserve">0.416100889444351</t>
   </si>
   <si>
     <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816861391068</t>
+    <t xml:space="preserve">0.365816801786423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36330258846283</t>
+    <t xml:space="preserve">0.363302558660507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674698352814</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360783100128</t>
+    <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
     <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017070055008</t>
+    <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446033239365</t>
+    <t xml:space="preserve">0.344446063041687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903423070908</t>
+    <t xml:space="preserve">0.33690345287323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160485029221</t>
+    <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703184604645</t>
+    <t xml:space="preserve">0.345703214406967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102349996567</t>
+    <t xml:space="preserve">0.3721022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930478572845</t>
+    <t xml:space="preserve">0.385930389165878</t>
   </si>
   <si>
     <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788434743881</t>
+    <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387808799744</t>
+    <t xml:space="preserve">0.378387778997421</t>
   </si>
   <si>
     <t xml:space="preserve">0.375873595476151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359352350235</t>
+    <t xml:space="preserve">0.37335941195488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673237800598</t>
+    <t xml:space="preserve">0.384673297405243</t>
   </si>
   <si>
     <t xml:space="preserve">0.390958875417709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393472999334335</t>
+    <t xml:space="preserve">0.39347305893898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272060394287</t>
   </si>
   <si>
     <t xml:space="preserve">0.430557578802109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414044618607</t>
+    <t xml:space="preserve">0.449414134025574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699592828751</t>
+    <t xml:space="preserve">0.455699622631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955968618393</t>
+    <t xml:space="preserve">0.463956087827682</t>
   </si>
   <si>
     <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332405328751</t>
+    <t xml:space="preserve">0.429332375526428</t>
   </si>
   <si>
     <t xml:space="preserve">0.415483027696609</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257064342499</t>
+    <t xml:space="preserve">0.436257123947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719527959824</t>
+    <t xml:space="preserve">0.439719498157501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794749736786</t>
+    <t xml:space="preserve">0.432794839143753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945342302322</t>
+    <t xml:space="preserve">0.418945372104645</t>
   </si>
   <si>
     <t xml:space="preserve">0.408558219671249</t>
@@ -845,49 +845,49 @@
     <t xml:space="preserve">0.401633530855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020683288574</t>
+    <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
     <t xml:space="preserve">0.387784123420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246408224106</t>
+    <t xml:space="preserve">0.391246467828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095964670181</t>
+    <t xml:space="preserve">0.405095905065536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
+    <t xml:space="preserve">0.422407686710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644127368927</t>
+    <t xml:space="preserve">0.446644216775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.52627831697464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106590986252</t>
+    <t xml:space="preserve">0.450106531381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45703125</t>
+    <t xml:space="preserve">0.457031279802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45356884598732</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
     <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708871841431</t>
+    <t xml:space="preserve">0.394708782434464</t>
   </si>
   <si>
     <t xml:space="preserve">0.380859434604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360085159540176</t>
+    <t xml:space="preserve">0.360085189342499</t>
   </si>
   <si>
     <t xml:space="preserve">0.370472311973572</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009967565536</t>
+    <t xml:space="preserve">0.367009907960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696036815643</t>
+    <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
     <t xml:space="preserve">0.339311122894287</t>
@@ -908,61 +908,61 @@
     <t xml:space="preserve">0.353160530328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235811710358</t>
+    <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
     <t xml:space="preserve">0.332386374473572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612248420715</t>
+    <t xml:space="preserve">0.311612188816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314382135868073</t>
+    <t xml:space="preserve">0.31438210606575</t>
   </si>
   <si>
     <t xml:space="preserve">0.290838092565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984416723251</t>
+    <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373569250107</t>
+    <t xml:space="preserve">0.278373599052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.26313915848732</t>
   </si>
   <si>
     <t xml:space="preserve">0.272833794355392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754244565964</t>
+    <t xml:space="preserve">0.261754274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134979486465</t>
+    <t xml:space="preserve">0.245135009288788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289780855179</t>
+    <t xml:space="preserve">0.24928979575634</t>
   </si>
   <si>
     <t xml:space="preserve">0.243749991059303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298347473145</t>
+    <t xml:space="preserve">0.2852982878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683291196823</t>
+    <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448850631714</t>
+    <t xml:space="preserve">0.271448910236359</t>
   </si>
   <si>
     <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143426895142</t>
+    <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.29499289393425</t>
   </si>
   <si>
     <t xml:space="preserve">0.303302586078644</t>
@@ -971,61 +971,61 @@
     <t xml:space="preserve">0.308842331171036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926208972931</t>
+    <t xml:space="preserve">0.337926149368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461655855179</t>
+    <t xml:space="preserve">0.325461685657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921880960464</t>
+    <t xml:space="preserve">0.319921910762787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465983867645</t>
+    <t xml:space="preserve">0.343465894460678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547623157501</t>
+    <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
     <t xml:space="preserve">0.377397060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231602907181</t>
+    <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001430749893</t>
+    <t xml:space="preserve">0.331001400947571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33654123544693</t>
+    <t xml:space="preserve">0.336541175842285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698215723038</t>
+    <t xml:space="preserve">0.349698185920715</t>
   </si>
   <si>
     <t xml:space="preserve">0.344850867986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691768407822</t>
+    <t xml:space="preserve">0.322691798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076771736145</t>
+    <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306794881821</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536967039108</t>
+    <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072443723679</t>
+    <t xml:space="preserve">0.306072473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317152053117752</t>
+    <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687559604645</t>
+    <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762781381607</t>
+    <t xml:space="preserve">0.297762811183929</t>
   </si>
   <si>
     <t xml:space="preserve">0.283913403749466</t>
@@ -1034,40 +1034,40 @@
     <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524191617966</t>
+    <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294019460678</t>
+    <t xml:space="preserve">0.267294049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26036936044693</t>
+    <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909105539322</t>
+    <t xml:space="preserve">0.265909165143967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063936710358</t>
+    <t xml:space="preserve">0.270063906908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988685131073</t>
+    <t xml:space="preserve">0.276988625526428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223006486893</t>
+    <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377867460251</t>
+    <t xml:space="preserve">0.296377837657928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453208446503</t>
+    <t xml:space="preserve">0.28945317864418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429810017347336</t>
+    <t xml:space="preserve">0.429809927940369</t>
   </si>
   <si>
     <t xml:space="preserve">0.399647802114487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337016105652</t>
+    <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
@@ -1076,70 +1076,70 @@
     <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36948573589325</t>
+    <t xml:space="preserve">0.369485765695572</t>
   </si>
   <si>
     <t xml:space="preserve">0.363453358411789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796521902084</t>
+    <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961445331573</t>
+    <t xml:space="preserve">0.364961475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880397319794</t>
+    <t xml:space="preserve">0.349880367517471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847990036011</t>
+    <t xml:space="preserve">0.343847960233688</t>
   </si>
   <si>
     <t xml:space="preserve">0.342339843511581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323699474335</t>
+    <t xml:space="preserve">0.339323610067368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.352896571159363</t>
   </si>
   <si>
     <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388484239578</t>
+    <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307466030121</t>
+    <t xml:space="preserve">0.336307436227798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799349308014</t>
+    <t xml:space="preserve">0.334799319505692</t>
   </si>
   <si>
     <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350481748581</t>
+    <t xml:space="preserve">0.437350451946259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958647727966</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431559562683</t>
+    <t xml:space="preserve">0.452431589365005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444890946149826</t>
+    <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120743751526</t>
+    <t xml:space="preserve">0.441120713949203</t>
   </si>
   <si>
     <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418183326721</t>
+    <t xml:space="preserve">0.403418153524399</t>
   </si>
   <si>
     <t xml:space="preserve">0.392107307910919</t>
@@ -1160,100 +1160,100 @@
     <t xml:space="preserve">0.36646956205368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404717683792</t>
+    <t xml:space="preserve">0.354404747486115</t>
   </si>
   <si>
     <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831756591797</t>
+    <t xml:space="preserve">0.340831816196442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993912220001</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
     <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977648973465</t>
+    <t xml:space="preserve">0.367977678775787</t>
   </si>
   <si>
     <t xml:space="preserve">0.358929038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316702127456665</t>
+    <t xml:space="preserve">0.316702097654343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112962722778</t>
+    <t xml:space="preserve">0.300112932920456</t>
   </si>
   <si>
     <t xml:space="preserve">0.30162101984024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210154771805</t>
+    <t xml:space="preserve">0.318210184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718331098557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324242651462555</t>
+    <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330275028944016</t>
+    <t xml:space="preserve">0.330274999141693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783145666122</t>
+    <t xml:space="preserve">0.3317831158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33781561255455</t>
+    <t xml:space="preserve">0.337815552949905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766852617264</t>
+    <t xml:space="preserve">0.328766942024231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309161573648453</t>
+    <t xml:space="preserve">0.309161603450775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653427124023</t>
+    <t xml:space="preserve">0.307653486728668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129136562347</t>
+    <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
     <t xml:space="preserve">0.313685894012451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734504938126</t>
+    <t xml:space="preserve">0.322734534740448</t>
   </si>
   <si>
     <t xml:space="preserve">0.317599236965179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322339415550232</t>
+    <t xml:space="preserve">0.322339504957199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314439028501511</t>
+    <t xml:space="preserve">0.314438998699188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31917929649353</t>
+    <t xml:space="preserve">0.319179326295853</t>
   </si>
   <si>
     <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400130271912</t>
+    <t xml:space="preserve">0.333400160074234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759356021881</t>
+    <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919534683228</t>
+    <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858909368515</t>
+    <t xml:space="preserve">0.312858879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.303378373384476</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">0.292317658662796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30179825425148</t>
+    <t xml:space="preserve">0.301798194646835</t>
   </si>
   <si>
     <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218164920807</t>
+    <t xml:space="preserve">0.300218105316162</t>
   </si>
   <si>
     <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737599134445</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
     <t xml:space="preserve">0.282837092876434</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">0.287577331066132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676854610443</t>
+    <t xml:space="preserve">0.27967694401741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096824884415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196318626404</t>
+    <t xml:space="preserve">0.270196348428726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281256973743439</t>
+    <t xml:space="preserve">0.281257033348083</t>
   </si>
   <si>
     <t xml:space="preserve">0.271776437759399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417122602463</t>
+    <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
     <t xml:space="preserve">0.285997241735458</t>
@@ -1316,112 +1316,112 @@
     <t xml:space="preserve">0.308118611574173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289157450199127</t>
+    <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
     <t xml:space="preserve">0.34604087471962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140368461609</t>
+    <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720547199249</t>
+    <t xml:space="preserve">0.339720517396927</t>
   </si>
   <si>
     <t xml:space="preserve">0.3413006067276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980189800262</t>
+    <t xml:space="preserve">0.334980219602585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560308933258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.352361261844635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359253883362</t>
+    <t xml:space="preserve">0.295359313488007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944742202759</t>
+    <t xml:space="preserve">0.291944772005081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237456560135</t>
+    <t xml:space="preserve">0.290237486362457</t>
   </si>
   <si>
     <t xml:space="preserve">0.285115629434586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822855472565</t>
+    <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481170415878</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29877382516861</t>
+    <t xml:space="preserve">0.298773854970932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408343791962</t>
+    <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286516666412</t>
+    <t xml:space="preserve">0.27828648686409</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993802309036</t>
+    <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164689540863</t>
+    <t xml:space="preserve">0.273164659738541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579201221466</t>
+    <t xml:space="preserve">0.276579260826111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750118255615</t>
+    <t xml:space="preserve">0.269750148057938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701028347015</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871945381165</t>
+    <t xml:space="preserve">0.274871975183487</t>
   </si>
   <si>
     <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042802810669</t>
+    <t xml:space="preserve">0.268042832612991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895682096481</t>
+    <t xml:space="preserve">0.303895711898804</t>
   </si>
   <si>
     <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188366651535</t>
+    <t xml:space="preserve">0.302188456058502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602997541428</t>
+    <t xml:space="preserve">0.305602937936783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310223579407</t>
+    <t xml:space="preserve">0.307310253381729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383050203323</t>
+    <t xml:space="preserve">0.324382990598679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261163473129</t>
+    <t xml:space="preserve">0.319261193275452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017539024353</t>
+    <t xml:space="preserve">0.309017479419708</t>
   </si>
   <si>
     <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432110309601</t>
+    <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
     <t xml:space="preserve">0.310724794864655</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">0.299829840660095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343415975571</t>
+    <t xml:space="preserve">0.296343445777893</t>
   </si>
   <si>
     <t xml:space="preserve">0.303316205739975</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">0.289370656013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627398967743</t>
+    <t xml:space="preserve">0.287627428770065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086643218994</t>
+    <t xml:space="preserve">0.298086613416672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560426235199</t>
+    <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30465242266655</t>
+    <t xml:space="preserve">0.304652392864227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302870810031891</t>
+    <t xml:space="preserve">0.302870839834213</t>
   </si>
   <si>
     <t xml:space="preserve">0.306434005498886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089257001877</t>
+    <t xml:space="preserve">0.301089227199554</t>
   </si>
   <si>
     <t xml:space="preserve">0.286836475133896</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290399670600891</t>
+    <t xml:space="preserve">0.290399640798569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307584762573</t>
+    <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
     <t xml:space="preserve">0.293962836265564</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">0.283273309469223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279710084199905</t>
+    <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
     <t xml:space="preserve">0.281491726636887</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
     <t xml:space="preserve">0.289902120828629</t>
@@ -1508,40 +1508,40 @@
     <t xml:space="preserve">0.30448842048645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308135002851486</t>
+    <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781585216522</t>
+    <t xml:space="preserve">0.311781525611877</t>
   </si>
   <si>
     <t xml:space="preserve">0.317251414060593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074690341949</t>
+    <t xml:space="preserve">0.319074660539627</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191101551056</t>
+    <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
     <t xml:space="preserve">0.331837683916092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660989999771</t>
+    <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897996425629</t>
+    <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
     <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158161878586</t>
+    <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329747140407562</t>
+    <t xml:space="preserve">0.32974711060524</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569272756577</t>
+    <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
     <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473086357117</t>
+    <t xml:space="preserve">0.333473116159439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391375303268</t>
+    <t xml:space="preserve">0.307391405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802426576614</t>
+    <t xml:space="preserve">0.301802456378937</t>
   </si>
   <si>
     <t xml:space="preserve">0.353965818881989</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">0.348376899957657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732635259628</t>
+    <t xml:space="preserve">0.370732605457306</t>
   </si>
   <si>
     <t xml:space="preserve">0.398677289485931</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540322065353</t>
+    <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
     <t xml:space="preserve">0.3912253677845</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362424612045</t>
+    <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458611011505</t>
+    <t xml:space="preserve">0.374458581209183</t>
   </si>
   <si>
     <t xml:space="preserve">0.37632155418396</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869632482529</t>
+    <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
     <t xml:space="preserve">0.378184527158737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951343536377</t>
+    <t xml:space="preserve">0.394951373338699</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">0.398170202970505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3962741792202</t>
+    <t xml:space="preserve">0.396274209022522</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097731113434</t>
+    <t xml:space="preserve">0.409097760915756</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605663537979</t>
+    <t xml:space="preserve">0.422605693340302</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -68865,7 +68865,7 @@
     </row>
     <row r="2568">
       <c r="A2568" s="1" t="n">
-        <v>46062.340787037</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2568" t="n">
         <v>4000</v>
@@ -68886,6 +68886,32 @@
         <v>590</v>
       </c>
       <c r="H2568" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" s="1" t="n">
+        <v>46063.3385300926</v>
+      </c>
+      <c r="B2569" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2569" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D2569" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E2569" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="F2569" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="G2569" t="s">
+        <v>580</v>
+      </c>
+      <c r="H2569" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,133 +38,133 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994321703911</t>
+    <t xml:space="preserve">0.175994336605072</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622867584229</t>
+    <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1728515625</t>
+    <t xml:space="preserve">0.172851607203484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594470739365</t>
+    <t xml:space="preserve">0.171594485640526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051875472069</t>
+    <t xml:space="preserve">0.16405189037323</t>
   </si>
   <si>
     <t xml:space="preserve">0.16970881819725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966655135155</t>
+    <t xml:space="preserve">0.148966625332832</t>
   </si>
   <si>
     <t xml:space="preserve">0.14330966770649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783760309219</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195320248604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737945318222</t>
+    <t xml:space="preserve">0.152737960219383</t>
   </si>
   <si>
     <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.15078940987587</t>
   </si>
   <si>
     <t xml:space="preserve">0.146452412009239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852628111839</t>
+    <t xml:space="preserve">0.139852643013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538362622261</t>
+    <t xml:space="preserve">0.139538377523422</t>
   </si>
   <si>
     <t xml:space="preserve">0.139915496110916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052575945854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909816741943</t>
+    <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15110370516777</t>
+    <t xml:space="preserve">0.151103690266609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337349176407</t>
+    <t xml:space="preserve">0.170337378978729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817486286163</t>
+    <t xml:space="preserve">0.166817456483841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423299789429</t>
+    <t xml:space="preserve">0.163423284888268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137796282768</t>
+    <t xml:space="preserve">0.157137811183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623568058014</t>
+    <t xml:space="preserve">0.154623582959175</t>
   </si>
   <si>
     <t xml:space="preserve">0.149595201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692130327225</t>
+    <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909101366997</t>
+    <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960610628128</t>
+    <t xml:space="preserve">0.158960580825806</t>
   </si>
   <si>
     <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251428365707</t>
+    <t xml:space="preserve">0.177251443266869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965924859047</t>
+    <t xml:space="preserve">0.170965909957886</t>
   </si>
   <si>
     <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565358519554</t>
+    <t xml:space="preserve">0.188565373420715</t>
   </si>
   <si>
     <t xml:space="preserve">0.192650943994522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708102822304</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
     <t xml:space="preserve">0.184165507555008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651309132576</t>
+    <t xml:space="preserve">0.181651324033737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136380434036</t>
+    <t xml:space="preserve">0.201136365532875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208679005503654</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073527336121</t>
+    <t xml:space="preserve">0.201073542237282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736499667168</t>
+    <t xml:space="preserve">0.196736514568329</t>
   </si>
   <si>
     <t xml:space="preserve">0.194222286343575</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">0.179137080907822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279855012894</t>
+    <t xml:space="preserve">0.182279825210571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834554195404</t>
+    <t xml:space="preserve">0.169834539294243</t>
   </si>
   <si>
     <t xml:space="preserve">0.168451726436615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794753909111</t>
+    <t xml:space="preserve">0.162794768810272</t>
   </si>
   <si>
     <t xml:space="preserve">0.151606559753418</t>
@@ -191,49 +191,49 @@
     <t xml:space="preserve">0.166566044092178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074958086014</t>
+    <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109399437904</t>
+    <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995022177696</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640650868416</t>
+    <t xml:space="preserve">0.157640635967255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051145195961</t>
+    <t xml:space="preserve">0.186051160097122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936812639236</t>
+    <t xml:space="preserve">0.187936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536946773529</t>
+    <t xml:space="preserve">0.18353696167469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18171414732933</t>
+    <t xml:space="preserve">0.181714162230492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194619774818</t>
+    <t xml:space="preserve">0.167194604873657</t>
   </si>
   <si>
     <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080987691879</t>
+    <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480823755264</t>
+    <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
     <t xml:space="preserve">0.148338079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566759467125</t>
+    <t xml:space="preserve">0.144566774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394902944565</t>
+    <t xml:space="preserve">0.158394917845726</t>
   </si>
   <si>
     <t xml:space="preserve">0.165183246135712</t>
@@ -242,46 +242,46 @@
     <t xml:space="preserve">0.170651659369469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223016619682</t>
+    <t xml:space="preserve">0.172223031520844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594120502472</t>
+    <t xml:space="preserve">0.18259409070015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507894158363</t>
+    <t xml:space="preserve">0.200507804751396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.19359378516674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131386637688</t>
+    <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010659337044</t>
+    <t xml:space="preserve">0.201010644435883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850847125053</t>
+    <t xml:space="preserve">0.194850891828537</t>
   </si>
   <si>
     <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19987927377224</t>
+    <t xml:space="preserve">0.199879288673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078871369362</t>
+    <t xml:space="preserve">0.213078856468201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787278652191</t>
+    <t xml:space="preserve">0.216787293553352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563927769661</t>
+    <t xml:space="preserve">0.232563942670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220885396004</t>
+    <t xml:space="preserve">0.238220915198326</t>
   </si>
   <si>
     <t xml:space="preserve">0.251420438289642</t>
@@ -305,244 +305,244 @@
     <t xml:space="preserve">0.260157346725464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2502261698246</t>
+    <t xml:space="preserve">0.250226199626923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163346529007</t>
+    <t xml:space="preserve">0.250163376331329</t>
   </si>
   <si>
     <t xml:space="preserve">0.242809325456619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249267339706</t>
+    <t xml:space="preserve">0.24324931204319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375077843666</t>
+    <t xml:space="preserve">0.243375018239021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421138763428</t>
+    <t xml:space="preserve">0.229421213269234</t>
   </si>
   <si>
     <t xml:space="preserve">0.233821034431458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564687848091</t>
+    <t xml:space="preserve">0.210564643144608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919074058533</t>
+    <t xml:space="preserve">0.20691904425621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821734905243</t>
+    <t xml:space="preserve">0.211821720004082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741843700409</t>
+    <t xml:space="preserve">0.208741828799248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592309713364</t>
+    <t xml:space="preserve">0.237592354416847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134934782982</t>
+    <t xml:space="preserve">0.245134979486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803966522217</t>
+    <t xml:space="preserve">0.230803981423378</t>
   </si>
   <si>
     <t xml:space="preserve">0.227535545825958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706672072411</t>
+    <t xml:space="preserve">0.235706716775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278454065323</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135620355606</t>
+    <t xml:space="preserve">0.22313566505909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850146651268</t>
+    <t xml:space="preserve">0.21685017645359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381442785263</t>
+    <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141709566116</t>
+    <t xml:space="preserve">0.213141679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199233531952</t>
+    <t xml:space="preserve">0.201199248433113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279109835625</t>
+    <t xml:space="preserve">0.204279154539108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793338060379</t>
+    <t xml:space="preserve">0.20679335296154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164792180061</t>
+    <t xml:space="preserve">0.206164821982384</t>
   </si>
   <si>
     <t xml:space="preserve">0.207421869039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804711699486</t>
+    <t xml:space="preserve">0.208804741501808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947470903397</t>
+    <t xml:space="preserve">0.211947411298752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649818778038</t>
+    <t xml:space="preserve">0.225649878382683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867199659348</t>
+    <t xml:space="preserve">0.219867184758186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810040831566</t>
+    <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484006762505</t>
+    <t xml:space="preserve">0.229484051465988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23438672721386</t>
+    <t xml:space="preserve">0.234386771917343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518492817879</t>
+    <t xml:space="preserve">0.224518463015556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21999292075634</t>
+    <t xml:space="preserve">0.219992890954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741523265839</t>
+    <t xml:space="preserve">0.219741493463516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216913014650345</t>
+    <t xml:space="preserve">0.216912999749184</t>
   </si>
   <si>
     <t xml:space="preserve">0.231306836009026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038720846176</t>
+    <t xml:space="preserve">0.217038691043854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324239253998</t>
+    <t xml:space="preserve">0.223324209451675</t>
   </si>
   <si>
     <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988643407822</t>
+    <t xml:space="preserve">0.351988673210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127855539322</t>
+    <t xml:space="preserve">0.465127885341644</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070391178131</t>
+    <t xml:space="preserve">0.477070271968842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43684309720993</t>
+    <t xml:space="preserve">0.436843037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072142362595</t>
+    <t xml:space="preserve">0.422072172164917</t>
   </si>
   <si>
     <t xml:space="preserve">0.395987212657928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559710025787</t>
+    <t xml:space="preserve">0.364559650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215266704559</t>
+    <t xml:space="preserve">0.414215207099915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388188838959</t>
+    <t xml:space="preserve">0.367388159036636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987972736359</t>
+    <t xml:space="preserve">0.373987913131714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331655979156</t>
+    <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
     <t xml:space="preserve">0.3259037733078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904123544693</t>
+    <t xml:space="preserve">0.314904153347015</t>
   </si>
   <si>
     <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389239549637</t>
+    <t xml:space="preserve">0.334389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818202733994</t>
+    <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845899105072</t>
+    <t xml:space="preserve">0.348845988512039</t>
   </si>
   <si>
     <t xml:space="preserve">0.341303318738937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846599578857</t>
+    <t xml:space="preserve">0.326846569776535</t>
   </si>
   <si>
     <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189641952515</t>
+    <t xml:space="preserve">0.321189671754837</t>
   </si>
   <si>
     <t xml:space="preserve">0.333132088184357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989314079285</t>
+    <t xml:space="preserve">0.329989373683929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418366670609</t>
+    <t xml:space="preserve">0.317418336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332416057587</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275592565536</t>
+    <t xml:space="preserve">0.314275622367859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761409044266</t>
+    <t xml:space="preserve">0.311761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703594446182</t>
+    <t xml:space="preserve">0.334703505039215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046867847443</t>
+    <t xml:space="preserve">0.318046897649765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31678980588913</t>
+    <t xml:space="preserve">0.316789835691452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417956829071</t>
+    <t xml:space="preserve">0.328418016433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075294494629</t>
+    <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103750944138</t>
+    <t xml:space="preserve">0.32810378074646</t>
   </si>
   <si>
     <t xml:space="preserve">0.301704585552216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504287481308</t>
+    <t xml:space="preserve">0.31050431728363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069935560226</t>
+    <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
     <t xml:space="preserve">0.320561081171036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589507818222</t>
+    <t xml:space="preserve">0.325589537620544</t>
   </si>
   <si>
     <t xml:space="preserve">0.358274161815643</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">0.339417636394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046167373657</t>
+    <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304049015045</t>
+    <t xml:space="preserve">0.319304019212723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846249341965</t>
+    <t xml:space="preserve">0.337846279144287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589858055115</t>
+    <t xml:space="preserve">0.314589887857437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327789485454559</t>
+    <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701694250107</t>
+    <t xml:space="preserve">0.389701783657074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588136672974</t>
+    <t xml:space="preserve">0.369588106870651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959575891495</t>
+    <t xml:space="preserve">0.368959546089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.37021666765213</t>
@@ -581,46 +581,46 @@
     <t xml:space="preserve">0.36361688375473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845168828964</t>
+    <t xml:space="preserve">0.370845228433609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074594020844</t>
+    <t xml:space="preserve">0.345074623823166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788755178452</t>
+    <t xml:space="preserve">0.349788725376129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502856731415</t>
+    <t xml:space="preserve">0.354502886533737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073893547058</t>
+    <t xml:space="preserve">0.36707392334938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758897781372</t>
+    <t xml:space="preserve">0.388758838176727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587406396866</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
     <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130717039108</t>
+    <t xml:space="preserve">0.377130746841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187570333481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377445042133331</t>
+    <t xml:space="preserve">0.377445012331009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929748296738</t>
+    <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
     <t xml:space="preserve">0.414843738079071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215996980667</t>
+    <t xml:space="preserve">0.392215967178345</t>
   </si>
   <si>
     <t xml:space="preserve">0.37681645154953</t>
@@ -629,334 +629,334 @@
     <t xml:space="preserve">0.386559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413344144821</t>
+    <t xml:space="preserve">0.471413433551788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357250928879</t>
+    <t xml:space="preserve">0.439357280731201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556908130646</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700293302536</t>
+    <t xml:space="preserve">0.433700352907181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100099563599</t>
+    <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271240711212</t>
+    <t xml:space="preserve">0.446271330118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43998584151268</t>
+    <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
     <t xml:space="preserve">0.42238637804985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900531768799</t>
+    <t xml:space="preserve">0.424900621175766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129375696182</t>
+    <t xml:space="preserve">0.421129286289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40981537103653</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044125556946</t>
+    <t xml:space="preserve">0.406044036149979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558219671249</t>
+    <t xml:space="preserve">0.408558309078217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586676120758</t>
+    <t xml:space="preserve">0.41358670592308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272760868073</t>
+    <t xml:space="preserve">0.40227273106575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443201541901</t>
+    <t xml:space="preserve">0.432443171739578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417358011007309</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
     <t xml:space="preserve">0.462613672018051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414774894714</t>
+    <t xml:space="preserve">0.427414804697037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758547544479</t>
+    <t xml:space="preserve">0.399758577346802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615102767944</t>
+    <t xml:space="preserve">0.4186150431633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643469810486</t>
+    <t xml:space="preserve">0.423643440008163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072462797165</t>
+    <t xml:space="preserve">0.41107240319252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501455783844</t>
+    <t xml:space="preserve">0.398501425981522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786944389343</t>
+    <t xml:space="preserve">0.404786974191666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159113883972</t>
+    <t xml:space="preserve">0.38215908408165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416205644608</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
     <t xml:space="preserve">0.388444572687149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529852628708</t>
+    <t xml:space="preserve">0.40352988243103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186139583588</t>
+    <t xml:space="preserve">0.431186109781265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872224330902</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301157712936</t>
+    <t xml:space="preserve">0.407301127910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730091094971</t>
+    <t xml:space="preserve">0.394730120897293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329584360123</t>
+    <t xml:space="preserve">0.412329643964767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015788316727</t>
+    <t xml:space="preserve">0.401015609502792</t>
   </si>
   <si>
     <t xml:space="preserve">0.416100889444351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045437097549</t>
+    <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816861391068</t>
+    <t xml:space="preserve">0.3658167719841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302618265152</t>
+    <t xml:space="preserve">0.363302648067474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674698352814</t>
+    <t xml:space="preserve">0.340674757957458</t>
   </si>
   <si>
     <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531223773956</t>
+    <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017070055008</t>
+    <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446033239365</t>
+    <t xml:space="preserve">0.344446063041687</t>
   </si>
   <si>
     <t xml:space="preserve">0.33690345287323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160544633865</t>
+    <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703125</t>
+    <t xml:space="preserve">0.345703214406967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102290391922</t>
+    <t xml:space="preserve">0.372102320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930448770523</t>
+    <t xml:space="preserve">0.385930418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245735168457</t>
+    <t xml:space="preserve">0.353245764970779</t>
   </si>
   <si>
     <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387808799744</t>
+    <t xml:space="preserve">0.378387838602066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873625278473</t>
+    <t xml:space="preserve">0.375873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37335941195488</t>
+    <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673327207565</t>
+    <t xml:space="preserve">0.384673297405243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958875417709</t>
+    <t xml:space="preserve">0.390958845615387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393472999334335</t>
+    <t xml:space="preserve">0.393473029136658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272119998932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557519197464</t>
+    <t xml:space="preserve">0.430557548999786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414134025574</t>
+    <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699652433395</t>
+    <t xml:space="preserve">0.455699622631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463956087827682</t>
+    <t xml:space="preserve">0.46395605802536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181842565536</t>
+    <t xml:space="preserve">0.443181872367859</t>
   </si>
   <si>
     <t xml:space="preserve">0.429332375526428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415482997894287</t>
+    <t xml:space="preserve">0.415483027696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870090723038</t>
+    <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257094144821</t>
+    <t xml:space="preserve">0.436257123947144</t>
   </si>
   <si>
     <t xml:space="preserve">0.439719468355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794809341431</t>
+    <t xml:space="preserve">0.432794779539108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945401906967</t>
+    <t xml:space="preserve">0.418945342302322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558249473572</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633560657501</t>
+    <t xml:space="preserve">0.401633501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020653486252</t>
+    <t xml:space="preserve">0.412020623683929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784093618393</t>
+    <t xml:space="preserve">0.387784123420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246467828751</t>
+    <t xml:space="preserve">0.391246408224106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095845460892</t>
+    <t xml:space="preserve">0.405095905065536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422407686710358</t>
+    <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
     <t xml:space="preserve">0.446644246578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278376579285</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106501579285</t>
+    <t xml:space="preserve">0.450106620788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031220197678</t>
+    <t xml:space="preserve">0.45703125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568905591965</t>
+    <t xml:space="preserve">0.453568875789642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171216249466</t>
+    <t xml:space="preserve">0.398171126842499</t>
   </si>
   <si>
     <t xml:space="preserve">0.394708812236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859375</t>
+    <t xml:space="preserve">0.38085949420929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934656381607</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085219144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472311973572</t>
+    <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384321749210358</t>
+    <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009937763214</t>
+    <t xml:space="preserve">0.367009967565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696007013321</t>
+    <t xml:space="preserve">0.340696036815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311063289642</t>
+    <t xml:space="preserve">0.339311152696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160500526428</t>
+    <t xml:space="preserve">0.353160530328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235811710358</t>
+    <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386404275894</t>
+    <t xml:space="preserve">0.332386374473572</t>
   </si>
   <si>
     <t xml:space="preserve">0.311612248420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314382165670395</t>
+    <t xml:space="preserve">0.314382076263428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838092565536</t>
+    <t xml:space="preserve">0.290838062763214</t>
   </si>
   <si>
     <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373599052429</t>
+    <t xml:space="preserve">0.278373628854752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139188289642</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.272833794355392</t>
   </si>
   <si>
     <t xml:space="preserve">0.261754244565964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289825558662</t>
+    <t xml:space="preserve">0.24928979575634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750050663948</t>
+    <t xml:space="preserve">0.243749991059303</t>
   </si>
   <si>
     <t xml:space="preserve">0.285298347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683291196823</t>
+    <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
     <t xml:space="preserve">0.271448850631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758512973785</t>
+    <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143486499786</t>
+    <t xml:space="preserve">0.281143456697464</t>
   </si>
   <si>
     <t xml:space="preserve">0.294992953538895</t>
@@ -965,52 +965,52 @@
     <t xml:space="preserve">0.303302556276321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842390775681</t>
+    <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
     <t xml:space="preserve">0.337926179170609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461685657501</t>
+    <t xml:space="preserve">0.325461626052856</t>
   </si>
   <si>
     <t xml:space="preserve">0.319921880960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465954065323</t>
+    <t xml:space="preserve">0.343465924263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547533750534</t>
+    <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397119998932</t>
+    <t xml:space="preserve">0.377397060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231602907181</t>
+    <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001460552216</t>
+    <t xml:space="preserve">0.331001400947571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33654123544693</t>
+    <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698185920715</t>
+    <t xml:space="preserve">0.349698215723038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850867986679</t>
+    <t xml:space="preserve">0.344850897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691768407822</t>
+    <t xml:space="preserve">0.322691798210144</t>
   </si>
   <si>
     <t xml:space="preserve">0.324076741933823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306854486465</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536937236786</t>
+    <t xml:space="preserve">0.318536967039108</t>
   </si>
   <si>
     <t xml:space="preserve">0.306072473526001</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">0.31715202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687529802322</t>
+    <t xml:space="preserve">0.3046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.297762781381607</t>
@@ -1031,55 +1031,55 @@
     <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524161815643</t>
+    <t xml:space="preserve">0.264524191617966</t>
   </si>
   <si>
     <t xml:space="preserve">0.267294049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369300842285</t>
+    <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909135341644</t>
+    <t xml:space="preserve">0.265909105539322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063906908035</t>
+    <t xml:space="preserve">0.270063936710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988625526428</t>
+    <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223066091537</t>
+    <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377867460251</t>
+    <t xml:space="preserve">0.296377837657928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28945317864418</t>
+    <t xml:space="preserve">0.289453119039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809957742691</t>
+    <t xml:space="preserve">0.429809927940369</t>
   </si>
   <si>
     <t xml:space="preserve">0.399647831916809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337045907974</t>
+    <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945271492004</t>
+    <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36948573589325</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453298807144</t>
+    <t xml:space="preserve">0.363453328609467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796581506729</t>
+    <t xml:space="preserve">0.380796492099762</t>
   </si>
   <si>
     <t xml:space="preserve">0.37401008605957</t>
@@ -1088,28 +1088,28 @@
     <t xml:space="preserve">0.364961475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880427122116</t>
+    <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
     <t xml:space="preserve">0.343847960233688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339903116226</t>
+    <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323669672012</t>
+    <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.352896630764008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34686416387558</t>
+    <t xml:space="preserve">0.346864223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388484239578</t>
+    <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307466030121</t>
+    <t xml:space="preserve">0.336307436227798</t>
   </si>
   <si>
     <t xml:space="preserve">0.334799349308014</t>
@@ -1118,91 +1118,91 @@
     <t xml:space="preserve">0.348372280597687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350481748581</t>
+    <t xml:space="preserve">0.437350451946259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958737134933</t>
+    <t xml:space="preserve">0.410958707332611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431559562683</t>
+    <t xml:space="preserve">0.45243164896965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444891005754471</t>
+    <t xml:space="preserve">0.444891035556793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120684146881</t>
+    <t xml:space="preserve">0.441120773553848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728879928589</t>
+    <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418153524399</t>
+    <t xml:space="preserve">0.403418123722076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107367515564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566783905029</t>
+    <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877540111542</t>
+    <t xml:space="preserve">0.395877569913864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188415527344</t>
+    <t xml:space="preserve">0.407188445329666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501969337463</t>
+    <t xml:space="preserve">0.372501999139786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469591856003</t>
+    <t xml:space="preserve">0.366469532251358</t>
   </si>
   <si>
     <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356106758118</t>
+    <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831756591797</t>
+    <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993852615356</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
     <t xml:space="preserve">0.360437154769897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977678775787</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929067850113</t>
+    <t xml:space="preserve">0.358928978443146</t>
   </si>
   <si>
     <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112903118134</t>
+    <t xml:space="preserve">0.300112932920456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301620990037918</t>
+    <t xml:space="preserve">0.301621079444885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31821021437645</t>
+    <t xml:space="preserve">0.318210154771805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718331098557</t>
+    <t xml:space="preserve">0.319718271493912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32424259185791</t>
+    <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330274999141693</t>
+    <t xml:space="preserve">0.330275058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3317831158638</t>
+    <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
     <t xml:space="preserve">0.337815552949905</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">0.328766942024231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30916154384613</t>
+    <t xml:space="preserve">0.309161573648453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653427124023</t>
+    <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30312916636467</t>
+    <t xml:space="preserve">0.303129136562347</t>
   </si>
   <si>
     <t xml:space="preserve">0.313685864210129</t>
@@ -1232,52 +1232,52 @@
     <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438968896866</t>
+    <t xml:space="preserve">0.314438939094543</t>
   </si>
   <si>
     <t xml:space="preserve">0.319179326295853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820011138916</t>
+    <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400160074234</t>
+    <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759385824203</t>
+    <t xml:space="preserve">0.320759356021881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919504880905</t>
+    <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858879566193</t>
+    <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378373384476</t>
+    <t xml:space="preserve">0.303378343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317688465118</t>
+    <t xml:space="preserve">0.292317628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30179825425148</t>
+    <t xml:space="preserve">0.301798194646835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019088029861</t>
+    <t xml:space="preserve">0.316019058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218135118484</t>
+    <t xml:space="preserve">0.300218164920807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638015985489</t>
+    <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2907375395298</t>
+    <t xml:space="preserve">0.290737599134445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837092876434</t>
+    <t xml:space="preserve">0.282837122678757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577390670776</t>
+    <t xml:space="preserve">0.287577331066132</t>
   </si>
   <si>
     <t xml:space="preserve">0.279676884412766</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096824884415</t>
+    <t xml:space="preserve">0.278096795082092</t>
   </si>
   <si>
     <t xml:space="preserve">0.270196348428726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257033348083</t>
+    <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776437759399</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997301340103</t>
+    <t xml:space="preserve">0.285997241735458</t>
   </si>
   <si>
     <t xml:space="preserve">0.295477867126465</t>
@@ -1310,55 +1310,55 @@
     <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118611574173</t>
+    <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
     <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34604087471962</t>
+    <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140398263931</t>
+    <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720487594604</t>
+    <t xml:space="preserve">0.339720547199249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3413006067276</t>
+    <t xml:space="preserve">0.341300666332245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980249404907</t>
+    <t xml:space="preserve">0.334980219602585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336560368537903</t>
+    <t xml:space="preserve">0.33656033873558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.352361351251602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359283685684</t>
+    <t xml:space="preserve">0.295359313488007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944772005081</t>
+    <t xml:space="preserve">0.291944742202759</t>
   </si>
   <si>
     <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115629434586</t>
+    <t xml:space="preserve">0.285115599632263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822885274887</t>
+    <t xml:space="preserve">0.286822915077209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481140613556</t>
+    <t xml:space="preserve">0.300481110811234</t>
   </si>
   <si>
     <t xml:space="preserve">0.298773854970932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408343791962</t>
+    <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
     <t xml:space="preserve">0.278286516666412</t>
@@ -1370,34 +1370,34 @@
     <t xml:space="preserve">0.279993802309036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164659738541</t>
+    <t xml:space="preserve">0.273164629936218</t>
   </si>
   <si>
     <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750088453293</t>
+    <t xml:space="preserve">0.269750148057938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701058149338</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871975183487</t>
+    <t xml:space="preserve">0.274871915578842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457403898239</t>
+    <t xml:space="preserve">0.271457344293594</t>
   </si>
   <si>
     <t xml:space="preserve">0.268042832612991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895711898804</t>
+    <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
     <t xml:space="preserve">0.29365199804306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188396453857</t>
+    <t xml:space="preserve">0.30218842625618</t>
   </si>
   <si>
     <t xml:space="preserve">0.305602937936783</t>
@@ -1412,28 +1412,28 @@
     <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017539024353</t>
+    <t xml:space="preserve">0.309017509222031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31413933634758</t>
+    <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
     <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724854469299</t>
+    <t xml:space="preserve">0.310724824666977</t>
   </si>
   <si>
     <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829840660095</t>
+    <t xml:space="preserve">0.299829810857773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343415975571</t>
+    <t xml:space="preserve">0.296343445777893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316175937653</t>
+    <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
     <t xml:space="preserve">0.289370626211166</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304652392864227</t>
+    <t xml:space="preserve">0.30465242266655</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306433975696564</t>
+    <t xml:space="preserve">0.306434005498886</t>
   </si>
   <si>
     <t xml:space="preserve">0.301089197397232</t>
@@ -1469,28 +1469,28 @@
     <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307614564896</t>
+    <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962895870209</t>
+    <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054922103882</t>
+    <t xml:space="preserve">0.285054862499237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273309469223</t>
+    <t xml:space="preserve">0.283273249864578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279710114002228</t>
+    <t xml:space="preserve">0.279710084199905</t>
   </si>
   <si>
     <t xml:space="preserve">0.281491726636887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292181253433228</t>
+    <t xml:space="preserve">0.29218128323555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295371979475021</t>
+    <t xml:space="preserve">0.295372009277344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289902120828629</t>
@@ -1499,22 +1499,22 @@
     <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291725426912308</t>
+    <t xml:space="preserve">0.291725397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488390684128</t>
   </si>
   <si>
     <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781525611877</t>
+    <t xml:space="preserve">0.311781585216522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317251414060593</t>
+    <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897966623306</t>
+    <t xml:space="preserve">0.320897936820984</t>
   </si>
   <si>
     <t xml:space="preserve">0.324544548988342</t>
@@ -1538,25 +1538,25 @@
     <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32974711060524</t>
+    <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610083580017</t>
+    <t xml:space="preserve">0.331610113382339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021134853363</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
     <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117351055145</t>
+    <t xml:space="preserve">0.311117321252823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309254318475723</t>
+    <t xml:space="preserve">0.309254348278046</t>
   </si>
   <si>
     <t xml:space="preserve">0.335336059331894</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473116159439</t>
+    <t xml:space="preserve">0.333473056554794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391405105591</t>
+    <t xml:space="preserve">0.307391375303268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353965818881989</t>
+    <t xml:space="preserve">0.353965848684311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344650954008102</t>
+    <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199002504349</t>
+    <t xml:space="preserve">0.337199032306671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376899957657</t>
+    <t xml:space="preserve">0.348376929759979</t>
   </si>
   <si>
     <t xml:space="preserve">0.370732605457306</t>
@@ -1598,37 +1598,37 @@
     <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170051813126</t>
+    <t xml:space="preserve">0.419170022010803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40799218416214</t>
+    <t xml:space="preserve">0.407992154359818</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409855157136917</t>
+    <t xml:space="preserve">0.40985518693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3912253677845</t>
+    <t xml:space="preserve">0.391225397586823</t>
   </si>
   <si>
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362454414368</t>
+    <t xml:space="preserve">0.389362424612045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458581209183</t>
+    <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
     <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372595608234406</t>
+    <t xml:space="preserve">0.372595638036728</t>
   </si>
   <si>
     <t xml:space="preserve">0.363280713558197</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378184527158737</t>
+    <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951373338699</t>
+    <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170202970505</t>
+    <t xml:space="preserve">0.398170232772827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274209022522</t>
+    <t xml:space="preserve">0.396274149417877</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403858363628387</t>
+    <t xml:space="preserve">0.40385839343071</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097760915756</t>
+    <t xml:space="preserve">0.409097731113434</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605693340302</t>
+    <t xml:space="preserve">0.422605663537979</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -69050,7 +69050,7 @@
     </row>
     <row r="2575">
       <c r="A2575" s="1" t="n">
-        <v>46071.5671412037</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2575" t="n">
         <v>40000</v>
@@ -69071,6 +69071,32 @@
         <v>591</v>
       </c>
       <c r="H2575" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" s="1" t="n">
+        <v>46072.4575925926</v>
+      </c>
+      <c r="B2576" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C2576" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2576" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E2576" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2576" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994336605072</t>
+    <t xml:space="preserve">0.17599430680275</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17662288248539</t>
+    <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851607203484</t>
+    <t xml:space="preserve">0.172851592302322</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594485640526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16405189037323</t>
+    <t xml:space="preserve">0.164051860570908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16970881819725</t>
+    <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
     <t xml:space="preserve">0.148966625332832</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">0.14330966770649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783760309219</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195320248604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737960219383</t>
+    <t xml:space="preserve">0.152737945318222</t>
   </si>
   <si>
     <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15078940987587</t>
+    <t xml:space="preserve">0.150789424777031</t>
   </si>
   <si>
     <t xml:space="preserve">0.146452412009239</t>
@@ -92,94 +92,94 @@
     <t xml:space="preserve">0.139915496110916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052575945854</t>
+    <t xml:space="preserve">0.142052561044693</t>
   </si>
   <si>
     <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151103690266609</t>
+    <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337378978729</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817456483841</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423284888268</t>
+    <t xml:space="preserve">0.16342331469059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137811183929</t>
+    <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
     <t xml:space="preserve">0.154623582959175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595201015472</t>
+    <t xml:space="preserve">0.149595186114311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692145228386</t>
+    <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
     <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960580825806</t>
+    <t xml:space="preserve">0.158960625529289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314296364784</t>
+    <t xml:space="preserve">0.177314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251443266869</t>
+    <t xml:space="preserve">0.177251413464546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965909957886</t>
+    <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
     <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565373420715</t>
+    <t xml:space="preserve">0.188565358519554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650943994522</t>
+    <t xml:space="preserve">0.192650929093361</t>
   </si>
   <si>
     <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165507555008</t>
+    <t xml:space="preserve">0.184165477752686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651324033737</t>
+    <t xml:space="preserve">0.181651264429092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136365532875</t>
+    <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678990602493</t>
+    <t xml:space="preserve">0.208678975701332</t>
   </si>
   <si>
     <t xml:space="preserve">0.201073542237282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736514568329</t>
+    <t xml:space="preserve">0.196736484766006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222286343575</t>
+    <t xml:space="preserve">0.194222301244736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137080907822</t>
+    <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279825210571</t>
+    <t xml:space="preserve">0.182279869914055</t>
   </si>
   <si>
     <t xml:space="preserve">0.169834539294243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451726436615</t>
+    <t xml:space="preserve">0.168451711535454</t>
   </si>
   <si>
     <t xml:space="preserve">0.162794768810272</t>
@@ -188,118 +188,118 @@
     <t xml:space="preserve">0.151606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566044092178</t>
+    <t xml:space="preserve">0.166566029191017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074943184853</t>
+    <t xml:space="preserve">0.15707491338253</t>
   </si>
   <si>
     <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995051980019</t>
+    <t xml:space="preserve">0.153995037078857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640635967255</t>
+    <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051160097122</t>
+    <t xml:space="preserve">0.1860511302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936782836914</t>
+    <t xml:space="preserve">0.187936812639236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18353696167469</t>
+    <t xml:space="preserve">0.183536946773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714162230492</t>
+    <t xml:space="preserve">0.181714102625847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194604873657</t>
+    <t xml:space="preserve">0.167194589972496</t>
   </si>
   <si>
     <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080972790718</t>
+    <t xml:space="preserve">0.147080987691879</t>
   </si>
   <si>
     <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338079452515</t>
+    <t xml:space="preserve">0.148338064551353</t>
   </si>
   <si>
     <t xml:space="preserve">0.144566774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394917845726</t>
+    <t xml:space="preserve">0.158394888043404</t>
   </si>
   <si>
     <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651659369469</t>
+    <t xml:space="preserve">0.170651644468307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223031520844</t>
+    <t xml:space="preserve">0.172223016619682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18259409070015</t>
+    <t xml:space="preserve">0.182594120502472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507804751396</t>
+    <t xml:space="preserve">0.200507834553719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19359378516674</t>
+    <t xml:space="preserve">0.193593755364418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131401538849</t>
+    <t xml:space="preserve">0.178131386637688</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010644435883</t>
+    <t xml:space="preserve">0.201010659337044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850891828537</t>
+    <t xml:space="preserve">0.194850847125053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770970821381</t>
+    <t xml:space="preserve">0.191770926117897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879288673401</t>
+    <t xml:space="preserve">0.19987927377224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078856468201</t>
+    <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787293553352</t>
+    <t xml:space="preserve">0.216787323355675</t>
   </si>
   <si>
     <t xml:space="preserve">0.232563942670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220915198326</t>
+    <t xml:space="preserve">0.238220930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420438289642</t>
+    <t xml:space="preserve">0.251420468091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26713427901268</t>
+    <t xml:space="preserve">0.267134249210358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305390357971</t>
+    <t xml:space="preserve">0.275305420160294</t>
   </si>
   <si>
     <t xml:space="preserve">0.290390640497208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561781644821</t>
+    <t xml:space="preserve">0.298561751842499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705986499786</t>
+    <t xml:space="preserve">0.257705956697464</t>
   </si>
   <si>
     <t xml:space="preserve">0.260157346725464</t>
@@ -308,88 +308,88 @@
     <t xml:space="preserve">0.250226199626923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163376331329</t>
+    <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809325456619</t>
+    <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24324931204319</t>
+    <t xml:space="preserve">0.243249297142029</t>
   </si>
   <si>
     <t xml:space="preserve">0.243375018239021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421213269234</t>
+    <t xml:space="preserve">0.229421228170395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821034431458</t>
+    <t xml:space="preserve">0.23382106423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564643144608</t>
+    <t xml:space="preserve">0.210564687848091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20691904425621</t>
+    <t xml:space="preserve">0.206919014453888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821720004082</t>
+    <t xml:space="preserve">0.211821794509888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741828799248</t>
+    <t xml:space="preserve">0.20874185860157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592354416847</t>
+    <t xml:space="preserve">0.237592309713364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134979486465</t>
+    <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
     <t xml:space="preserve">0.230803981423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535545825958</t>
+    <t xml:space="preserve">0.227535516023636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706716775894</t>
+    <t xml:space="preserve">0.235706642270088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278439164162</t>
+    <t xml:space="preserve">0.226278424263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22313566505909</t>
+    <t xml:space="preserve">0.223135679960251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21685017645359</t>
+    <t xml:space="preserve">0.216850161552429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381427884102</t>
+    <t xml:space="preserve">0.222381398081779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141679763794</t>
+    <t xml:space="preserve">0.213141724467278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199248433113</t>
+    <t xml:space="preserve">0.201199233531952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279154539108</t>
+    <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20679335296154</t>
+    <t xml:space="preserve">0.206793338060379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164821982384</t>
+    <t xml:space="preserve">0.206164762377739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421869039536</t>
+    <t xml:space="preserve">0.207421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804741501808</t>
+    <t xml:space="preserve">0.208804711699486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947411298752</t>
+    <t xml:space="preserve">0.211947500705719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649878382683</t>
+    <t xml:space="preserve">0.22564984858036</t>
   </si>
   <si>
     <t xml:space="preserve">0.219867184758186</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484051465988</t>
+    <t xml:space="preserve">0.229484036564827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386771917343</t>
+    <t xml:space="preserve">0.23438672721386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518463015556</t>
+    <t xml:space="preserve">0.224518448114395</t>
   </si>
   <si>
     <t xml:space="preserve">0.219992890954018</t>
@@ -416,49 +416,49 @@
     <t xml:space="preserve">0.216912999749184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306836009026</t>
+    <t xml:space="preserve">0.231306791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038691043854</t>
+    <t xml:space="preserve">0.217038705945015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324209451675</t>
+    <t xml:space="preserve">0.223324254155159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297179013490677</t>
+    <t xml:space="preserve">0.297178983688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988673210144</t>
+    <t xml:space="preserve">0.351988613605499</t>
   </si>
   <si>
     <t xml:space="preserve">0.465127885341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582413673401</t>
+    <t xml:space="preserve">0.545582354068756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070271968842</t>
+    <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843037605286</t>
+    <t xml:space="preserve">0.436843127012253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072172164917</t>
+    <t xml:space="preserve">0.422072112560272</t>
   </si>
   <si>
     <t xml:space="preserve">0.395987212657928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559650421143</t>
+    <t xml:space="preserve">0.36455973982811</t>
   </si>
   <si>
     <t xml:space="preserve">0.414215207099915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388159036636</t>
+    <t xml:space="preserve">0.367388188838959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987913131714</t>
+    <t xml:space="preserve">0.373988002538681</t>
   </si>
   <si>
     <t xml:space="preserve">0.346331715583801</t>
@@ -470,70 +470,70 @@
     <t xml:space="preserve">0.314904153347015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532363891602</t>
+    <t xml:space="preserve">0.326532334089279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389209747314</t>
+    <t xml:space="preserve">0.334389179944992</t>
   </si>
   <si>
     <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845988512039</t>
+    <t xml:space="preserve">0.348845928907394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303318738937</t>
+    <t xml:space="preserve">0.341303288936615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846569776535</t>
+    <t xml:space="preserve">0.32684662938118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361163139343</t>
+    <t xml:space="preserve">0.318361192941666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189671754837</t>
+    <t xml:space="preserve">0.321189612150192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132088184357</t>
+    <t xml:space="preserve">0.333132058382034</t>
   </si>
   <si>
     <t xml:space="preserve">0.329989373683929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418366670609</t>
   </si>
   <si>
     <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275622367859</t>
+    <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761379241943</t>
+    <t xml:space="preserve">0.311761409044266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703505039215</t>
+    <t xml:space="preserve">0.33470356464386</t>
   </si>
   <si>
     <t xml:space="preserve">0.318046897649765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789835691452</t>
+    <t xml:space="preserve">0.316789776086807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328418016433716</t>
+    <t xml:space="preserve">0.328417986631393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075324296951</t>
+    <t xml:space="preserve">0.323075294494629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32810378074646</t>
+    <t xml:space="preserve">0.328103721141815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704585552216</t>
+    <t xml:space="preserve">0.301704555749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31050431728363</t>
+    <t xml:space="preserve">0.310504257678986</t>
   </si>
   <si>
     <t xml:space="preserve">0.311069995164871</t>
@@ -545,31 +545,31 @@
     <t xml:space="preserve">0.325589537620544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274161815643</t>
+    <t xml:space="preserve">0.358274191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417636394501</t>
+    <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
     <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304019212723</t>
+    <t xml:space="preserve">0.3193039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846279144287</t>
+    <t xml:space="preserve">0.337846249341965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589887857437</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701783657074</t>
+    <t xml:space="preserve">0.389701694250107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588106870651</t>
+    <t xml:space="preserve">0.369588077068329</t>
   </si>
   <si>
     <t xml:space="preserve">0.368959546089172</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36361688375473</t>
+    <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845228433609</t>
+    <t xml:space="preserve">0.370845168828964</t>
   </si>
   <si>
     <t xml:space="preserve">0.345074623823166</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">0.349788725376129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502886533737</t>
+    <t xml:space="preserve">0.354502826929092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36707392334938</t>
+    <t xml:space="preserve">0.367073893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758838176727</t>
+    <t xml:space="preserve">0.388758897781372</t>
   </si>
   <si>
     <t xml:space="preserve">0.391587376594543</t>
@@ -605,214 +605,214 @@
     <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130746841431</t>
+    <t xml:space="preserve">0.377130717039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187570333481</t>
+    <t xml:space="preserve">0.387187510728836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377445012331009</t>
+    <t xml:space="preserve">0.377444922924042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.40792977809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843738079071</t>
+    <t xml:space="preserve">0.414843797683716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215967178345</t>
+    <t xml:space="preserve">0.3922159075737</t>
   </si>
   <si>
     <t xml:space="preserve">0.37681645154953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386559009552002</t>
+    <t xml:space="preserve">0.38655897974968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413433551788</t>
+    <t xml:space="preserve">0.471413284540176</t>
   </si>
   <si>
     <t xml:space="preserve">0.439357280731201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556878328323</t>
+    <t xml:space="preserve">0.452556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700352907181</t>
+    <t xml:space="preserve">0.433700323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100188970566</t>
+    <t xml:space="preserve">0.438100159168243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271330118179</t>
+    <t xml:space="preserve">0.446271359920502</t>
   </si>
   <si>
     <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42238637804985</t>
+    <t xml:space="preserve">0.422386348247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900621175766</t>
+    <t xml:space="preserve">0.424900591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129286289215</t>
+    <t xml:space="preserve">0.421129375696182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815400838852</t>
+    <t xml:space="preserve">0.409815430641174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044036149979</t>
+    <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558309078217</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41358670592308</t>
+    <t xml:space="preserve">0.413586676120758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40227273106575</t>
+    <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443171739578</t>
+    <t xml:space="preserve">0.432443261146545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357981204987</t>
+    <t xml:space="preserve">0.417357951402664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613672018051</t>
+    <t xml:space="preserve">0.462613582611084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414804697037</t>
+    <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758577346802</t>
+    <t xml:space="preserve">0.399758547544479</t>
   </si>
   <si>
     <t xml:space="preserve">0.4186150431633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643440008163</t>
+    <t xml:space="preserve">0.423643589019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41107240319252</t>
+    <t xml:space="preserve">0.411072492599487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501425981522</t>
+    <t xml:space="preserve">0.398501485586166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786974191666</t>
+    <t xml:space="preserve">0.404786884784698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38215908408165</t>
+    <t xml:space="preserve">0.382159143686295</t>
   </si>
   <si>
     <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444572687149</t>
+    <t xml:space="preserve">0.388444602489471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40352988243103</t>
+    <t xml:space="preserve">0.403529822826385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186109781265</t>
+    <t xml:space="preserve">0.431186139583588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41987219452858</t>
+    <t xml:space="preserve">0.419872224330902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301127910614</t>
+    <t xml:space="preserve">0.407301157712936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730120897293</t>
+    <t xml:space="preserve">0.394730091094971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329643964767</t>
+    <t xml:space="preserve">0.412329524755478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015609502792</t>
+    <t xml:space="preserve">0.401015669107437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100889444351</t>
+    <t xml:space="preserve">0.416100829839706</t>
   </si>
   <si>
     <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3658167719841</t>
+    <t xml:space="preserve">0.365816801786423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302648067474</t>
+    <t xml:space="preserve">0.363302528858185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674757957458</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
     <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531283378601</t>
+    <t xml:space="preserve">0.359531313180923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017040252686</t>
+    <t xml:space="preserve">0.35701709985733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446063041687</t>
+    <t xml:space="preserve">0.344446033239365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33690345287323</t>
+    <t xml:space="preserve">0.336903423070908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160514831543</t>
+    <t xml:space="preserve">0.338160574436188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703214406967</t>
+    <t xml:space="preserve">0.345703184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102320194244</t>
+    <t xml:space="preserve">0.3721022605896</t>
   </si>
   <si>
     <t xml:space="preserve">0.385930418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245764970779</t>
+    <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
     <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387838602066</t>
+    <t xml:space="preserve">0.378387868404388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873565673828</t>
+    <t xml:space="preserve">0.375873625278473</t>
   </si>
   <si>
     <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673297405243</t>
+    <t xml:space="preserve">0.384673327207565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958845615387</t>
+    <t xml:space="preserve">0.39095875620842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393473029136658</t>
+    <t xml:space="preserve">0.393472969532013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272119998932</t>
+    <t xml:space="preserve">0.424272030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557548999786</t>
+    <t xml:space="preserve">0.430557608604431</t>
   </si>
   <si>
     <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699622631073</t>
+    <t xml:space="preserve">0.455699652433395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46395605802536</t>
+    <t xml:space="preserve">0.463956028223038</t>
   </si>
   <si>
     <t xml:space="preserve">0.443181872367859</t>
@@ -827,97 +827,97 @@
     <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257123947144</t>
+    <t xml:space="preserve">0.436257183551788</t>
   </si>
   <si>
     <t xml:space="preserve">0.439719468355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794779539108</t>
+    <t xml:space="preserve">0.432794839143753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945342302322</t>
+    <t xml:space="preserve">0.4189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558279275894</t>
+    <t xml:space="preserve">0.408558219671249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633501052856</t>
+    <t xml:space="preserve">0.401633620262146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020623683929</t>
+    <t xml:space="preserve">0.412020683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784123420715</t>
+    <t xml:space="preserve">0.387784063816071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246408224106</t>
+    <t xml:space="preserve">0.391246497631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095905065536</t>
+    <t xml:space="preserve">0.405095845460892</t>
   </si>
   <si>
     <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644246578217</t>
+    <t xml:space="preserve">0.446644306182861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278495788574</t>
+    <t xml:space="preserve">0.526278436183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106620788574</t>
+    <t xml:space="preserve">0.450106590986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45703125</t>
+    <t xml:space="preserve">0.457031309604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568875789642</t>
+    <t xml:space="preserve">0.453568905591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171126842499</t>
+    <t xml:space="preserve">0.398171216249466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708812236786</t>
+    <t xml:space="preserve">0.394708782434464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38085949420929</t>
+    <t xml:space="preserve">0.380859404802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934656381607</t>
+    <t xml:space="preserve">0.373934686183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360085219144821</t>
+    <t xml:space="preserve">0.360085248947144</t>
   </si>
   <si>
     <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38432177901268</t>
+    <t xml:space="preserve">0.384321808815002</t>
   </si>
   <si>
     <t xml:space="preserve">0.367009967565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696036815643</t>
+    <t xml:space="preserve">0.340695977210999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311152696609</t>
+    <t xml:space="preserve">0.339311093091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160530328751</t>
+    <t xml:space="preserve">0.353160500526428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34623584151268</t>
+    <t xml:space="preserve">0.346235811710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386404275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612248420715</t>
+    <t xml:space="preserve">0.311612218618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314382076263428</t>
+    <t xml:space="preserve">0.31438210606575</t>
   </si>
   <si>
     <t xml:space="preserve">0.290838062763214</t>
@@ -926,55 +926,55 @@
     <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373628854752</t>
+    <t xml:space="preserve">0.278373599052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139247894287</t>
+    <t xml:space="preserve">0.263139218091965</t>
   </si>
   <si>
     <t xml:space="preserve">0.272833794355392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754244565964</t>
+    <t xml:space="preserve">0.261754214763641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24928979575634</t>
+    <t xml:space="preserve">0.249289780855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243749991059303</t>
+    <t xml:space="preserve">0.243750020861626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298347473145</t>
+    <t xml:space="preserve">0.285298317670822</t>
   </si>
   <si>
     <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448850631714</t>
+    <t xml:space="preserve">0.271448880434036</t>
   </si>
   <si>
     <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143456697464</t>
+    <t xml:space="preserve">0.281143516302109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.29499289393425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302556276321</t>
+    <t xml:space="preserve">0.303302586078644</t>
   </si>
   <si>
     <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926179170609</t>
+    <t xml:space="preserve">0.337926149368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461626052856</t>
+    <t xml:space="preserve">0.325461655855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921880960464</t>
+    <t xml:space="preserve">0.319921940565109</t>
   </si>
   <si>
     <t xml:space="preserve">0.343465924263</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397060394287</t>
+    <t xml:space="preserve">0.377397030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231573104858</t>
+    <t xml:space="preserve">0.328231543302536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001400947571</t>
+    <t xml:space="preserve">0.331001460552216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336541205644608</t>
+    <t xml:space="preserve">0.33654123544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698215723038</t>
+    <t xml:space="preserve">0.349698185920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850897789001</t>
+    <t xml:space="preserve">0.344850867986679</t>
   </si>
   <si>
     <t xml:space="preserve">0.322691798210144</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">0.318536967039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072473526001</t>
+    <t xml:space="preserve">0.306072443723679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31715202331543</t>
+    <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3046875</t>
+    <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762781381607</t>
+    <t xml:space="preserve">0.297762811183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913373947144</t>
+    <t xml:space="preserve">0.283913403749466</t>
   </si>
   <si>
     <t xml:space="preserve">0.288068205118179</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">0.267294049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369330644608</t>
+    <t xml:space="preserve">0.260369271039963</t>
   </si>
   <si>
     <t xml:space="preserve">0.265909105539322</t>
@@ -1049,46 +1049,46 @@
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223036289215</t>
+    <t xml:space="preserve">0.292223006486893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377837657928</t>
+    <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453119039536</t>
+    <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809927940369</t>
+    <t xml:space="preserve">0.429809957742691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647831916809</t>
+    <t xml:space="preserve">0.399647861719131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337075710297</t>
+    <t xml:space="preserve">0.388337045907974</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945241689682</t>
+    <t xml:space="preserve">0.361945271492004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485795497894</t>
+    <t xml:space="preserve">0.369485765695572</t>
   </si>
   <si>
     <t xml:space="preserve">0.363453328609467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796492099762</t>
+    <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
     <t xml:space="preserve">0.37401008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961475133896</t>
+    <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880397319794</t>
+    <t xml:space="preserve">0.349880367517471</t>
   </si>
   <si>
     <t xml:space="preserve">0.343847960233688</t>
@@ -1097,49 +1097,49 @@
     <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33932363986969</t>
+    <t xml:space="preserve">0.339323669672012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896630764008</t>
+    <t xml:space="preserve">0.352896600961685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864223480225</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
     <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307436227798</t>
+    <t xml:space="preserve">0.336307466030121</t>
   </si>
   <si>
     <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372280597687</t>
+    <t xml:space="preserve">0.348372340202332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350451946259</t>
+    <t xml:space="preserve">0.437350541353226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958707332611</t>
+    <t xml:space="preserve">0.410958647727966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45243164896965</t>
+    <t xml:space="preserve">0.452431619167328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444891035556793</t>
+    <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120773553848</t>
+    <t xml:space="preserve">0.441120684146881</t>
   </si>
   <si>
     <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418123722076</t>
+    <t xml:space="preserve">0.403418183326721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107367515564</t>
+    <t xml:space="preserve">0.392107337713242</t>
   </si>
   <si>
     <t xml:space="preserve">0.384566813707352</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">0.395877569913864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188445329666</t>
+    <t xml:space="preserve">0.407188385725021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501999139786</t>
+    <t xml:space="preserve">0.372501969337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469532251358</t>
+    <t xml:space="preserve">0.366469591856003</t>
   </si>
   <si>
     <t xml:space="preserve">0.354404717683792</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831786394119</t>
+    <t xml:space="preserve">0.340831756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993882417679</t>
+    <t xml:space="preserve">0.370993822813034</t>
   </si>
   <si>
     <t xml:space="preserve">0.360437154769897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977648973465</t>
+    <t xml:space="preserve">0.367977678775787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358928978443146</t>
+    <t xml:space="preserve">0.358929067850113</t>
   </si>
   <si>
     <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112932920456</t>
+    <t xml:space="preserve">0.300112903118134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301621079444885</t>
+    <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
     <t xml:space="preserve">0.318210154771805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718301296234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324242621660233</t>
+    <t xml:space="preserve">0.32424259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258795499802</t>
+    <t xml:space="preserve">0.327258825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330275058746338</t>
+    <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783145666122</t>
+    <t xml:space="preserve">0.3317831158638</t>
   </si>
   <si>
     <t xml:space="preserve">0.337815552949905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766942024231</t>
+    <t xml:space="preserve">0.328766912221909</t>
   </si>
   <si>
     <t xml:space="preserve">0.309161573648453</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">0.313685864210129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734504938126</t>
+    <t xml:space="preserve">0.322734534740448</t>
   </si>
   <si>
     <t xml:space="preserve">0.317599207162857</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438939094543</t>
+    <t xml:space="preserve">0.314438998699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.319179326295853</t>
@@ -1241,103 +1241,103 @@
     <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400130271912</t>
+    <t xml:space="preserve">0.333400100469589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759356021881</t>
+    <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
     <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858909368515</t>
+    <t xml:space="preserve">0.312858879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.303378343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317628860474</t>
+    <t xml:space="preserve">0.292317688465118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798194646835</t>
+    <t xml:space="preserve">0.301798224449158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019058227539</t>
+    <t xml:space="preserve">0.316019117832184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218164920807</t>
+    <t xml:space="preserve">0.300218135118484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638045787811</t>
+    <t xml:space="preserve">0.298638015985489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737599134445</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837122678757</t>
+    <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577331066132</t>
+    <t xml:space="preserve">0.287577360868454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676884412766</t>
+    <t xml:space="preserve">0.27967694401741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516705751419</t>
+    <t xml:space="preserve">0.276516675949097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096795082092</t>
+    <t xml:space="preserve">0.278096824884415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196348428726</t>
+    <t xml:space="preserve">0.270196318626404</t>
   </si>
   <si>
     <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776437759399</t>
+    <t xml:space="preserve">0.271776407957077</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997241735458</t>
+    <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477867126465</t>
+    <t xml:space="preserve">0.295477837324142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057926654816</t>
+    <t xml:space="preserve">0.297057896852493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118581771851</t>
+    <t xml:space="preserve">0.308118641376495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157509803772</t>
   </si>
   <si>
     <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140428066254</t>
+    <t xml:space="preserve">0.338140457868576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720547199249</t>
+    <t xml:space="preserve">0.339720517396927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341300666332245</t>
+    <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980219602585</t>
+    <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560308933258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361351251602</t>
+    <t xml:space="preserve">0.352361291646957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359313488007</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
     <t xml:space="preserve">0.291944742202759</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115599632263</t>
+    <t xml:space="preserve">0.285115629434586</t>
   </si>
   <si>
     <t xml:space="preserve">0.286822915077209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481110811234</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298773854970932</t>
+    <t xml:space="preserve">0.29877382516861</t>
   </si>
   <si>
     <t xml:space="preserve">0.283408313989639</t>
@@ -1370,37 +1370,37 @@
     <t xml:space="preserve">0.279993802309036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164629936218</t>
+    <t xml:space="preserve">0.273164689540863</t>
   </si>
   <si>
     <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750148057938</t>
+    <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28170108795166</t>
+    <t xml:space="preserve">0.281701058149338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871915578842</t>
+    <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457344293594</t>
+    <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042832612991</t>
+    <t xml:space="preserve">0.268042802810669</t>
   </si>
   <si>
     <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30218842625618</t>
+    <t xml:space="preserve">0.302188456058502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602937936783</t>
+    <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
     <t xml:space="preserve">0.307310253381729</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">0.324383020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261223077774</t>
+    <t xml:space="preserve">0.319261193275452</t>
   </si>
   <si>
     <t xml:space="preserve">0.309017509222031</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432080507278</t>
+    <t xml:space="preserve">0.312432110309601</t>
   </si>
   <si>
     <t xml:space="preserve">0.310724824666977</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829810857773</t>
+    <t xml:space="preserve">0.299829840660095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343445777893</t>
+    <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
     <t xml:space="preserve">0.303316205739975</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627458572388</t>
+    <t xml:space="preserve">0.287627428770065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086643218994</t>
+    <t xml:space="preserve">0.298086613416672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560366630554</t>
+    <t xml:space="preserve">0.313560396432877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30465242266655</t>
+    <t xml:space="preserve">0.304652392864227</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870810031891</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">0.301089197397232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836475133896</t>
+    <t xml:space="preserve">0.286836445331573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288618087768555</t>
+    <t xml:space="preserve">0.288618057966232</t>
   </si>
   <si>
     <t xml:space="preserve">0.290399670600891</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962866067886</t>
+    <t xml:space="preserve">0.293962836265564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054862499237</t>
+    <t xml:space="preserve">0.285054922103882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273249864578</t>
+    <t xml:space="preserve">0.283273309469223</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710084199905</t>
@@ -1487,40 +1487,40 @@
     <t xml:space="preserve">0.281491726636887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29218128323555</t>
+    <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902150630951</t>
   </si>
   <si>
     <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291725397109985</t>
+    <t xml:space="preserve">0.291725426912308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304488390684128</t>
+    <t xml:space="preserve">0.30448842048645</t>
   </si>
   <si>
     <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781585216522</t>
+    <t xml:space="preserve">0.311781525611877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31725138425827</t>
+    <t xml:space="preserve">0.317251414060593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074690341949</t>
+    <t xml:space="preserve">0.319074660539627</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191131353378</t>
+    <t xml:space="preserve">0.328191101551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.331837683916092</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897936820984</t>
+    <t xml:space="preserve">0.320897996425629</t>
   </si>
   <si>
     <t xml:space="preserve">0.324544548988342</t>
@@ -1538,25 +1538,25 @@
     <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329747140407562</t>
+    <t xml:space="preserve">0.32974711060524</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610113382339</t>
+    <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021164655685</t>
+    <t xml:space="preserve">0.326021134853363</t>
   </si>
   <si>
     <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117321252823</t>
+    <t xml:space="preserve">0.311117351055145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309254348278046</t>
+    <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
     <t xml:space="preserve">0.335336059331894</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473056554794</t>
+    <t xml:space="preserve">0.333473116159439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391375303268</t>
+    <t xml:space="preserve">0.307391405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802426576614</t>
+    <t xml:space="preserve">0.301802456378937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353965848684311</t>
+    <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34465092420578</t>
+    <t xml:space="preserve">0.344650954008102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199032306671</t>
+    <t xml:space="preserve">0.337199002504349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376929759979</t>
+    <t xml:space="preserve">0.348376899957657</t>
   </si>
   <si>
     <t xml:space="preserve">0.370732605457306</t>
@@ -1598,37 +1598,37 @@
     <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170022010803</t>
+    <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407992154359818</t>
+    <t xml:space="preserve">0.40799218416214</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40985518693924</t>
+    <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
     <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391225397586823</t>
+    <t xml:space="preserve">0.3912253677845</t>
   </si>
   <si>
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362424612045</t>
+    <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458611011505</t>
+    <t xml:space="preserve">0.374458581209183</t>
   </si>
   <si>
     <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372595638036728</t>
+    <t xml:space="preserve">0.372595608234406</t>
   </si>
   <si>
     <t xml:space="preserve">0.363280713558197</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37818455696106</t>
+    <t xml:space="preserve">0.378184527158737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951343536377</t>
+    <t xml:space="preserve">0.394951373338699</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170232772827</t>
+    <t xml:space="preserve">0.398170202970505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274149417877</t>
+    <t xml:space="preserve">0.396274209022522</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40385839343071</t>
+    <t xml:space="preserve">0.403858363628387</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097731113434</t>
+    <t xml:space="preserve">0.409097760915756</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605663537979</t>
+    <t xml:space="preserve">0.422605693340302</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -69076,7 +69076,7 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46072.4575925926</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2576" t="n">
         <v>12000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17599430680275</t>
+    <t xml:space="preserve">0.175994336605072</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622867584229</t>
+    <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851592302322</t>
+    <t xml:space="preserve">0.172851577401161</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594485640526</t>
@@ -59,34 +59,34 @@
     <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966625332832</t>
+    <t xml:space="preserve">0.148966640233994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14330966770649</t>
+    <t xml:space="preserve">0.143309652805328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783760309219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195320248604</t>
+    <t xml:space="preserve">0.145195335149765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737945318222</t>
+    <t xml:space="preserve">0.152737930417061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15336649119854</t>
+    <t xml:space="preserve">0.153366476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.150789439678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146452412009239</t>
+    <t xml:space="preserve">0.1464524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852643013</t>
+    <t xml:space="preserve">0.139852657914162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538377523422</t>
+    <t xml:space="preserve">0.139538362622261</t>
   </si>
   <si>
     <t xml:space="preserve">0.139915496110916</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337364077568</t>
+    <t xml:space="preserve">0.170337378978729</t>
   </si>
   <si>
     <t xml:space="preserve">0.166817471385002</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">0.16342331469059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137796282768</t>
+    <t xml:space="preserve">0.157137781381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623582959175</t>
+    <t xml:space="preserve">0.154623597860336</t>
   </si>
   <si>
     <t xml:space="preserve">0.149595186114311</t>
@@ -122,37 +122,37 @@
     <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909116268158</t>
+    <t xml:space="preserve">0.160909086465836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960625529289</t>
+    <t xml:space="preserve">0.158960595726967</t>
   </si>
   <si>
     <t xml:space="preserve">0.177314281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251413464546</t>
+    <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965924859047</t>
+    <t xml:space="preserve">0.170965939760208</t>
   </si>
   <si>
     <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565358519554</t>
+    <t xml:space="preserve">0.188565388321877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650929093361</t>
+    <t xml:space="preserve">0.1926509141922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708117723465</t>
+    <t xml:space="preserve">0.191708102822304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165477752686</t>
+    <t xml:space="preserve">0.184165522456169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651264429092</t>
+    <t xml:space="preserve">0.181651309132576</t>
   </si>
   <si>
     <t xml:space="preserve">0.201136380434036</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">0.208678975701332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073542237282</t>
+    <t xml:space="preserve">0.201073512434959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196736484766006</t>
+    <t xml:space="preserve">0.19673652946949</t>
   </si>
   <si>
     <t xml:space="preserve">0.194222301244736</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">0.179137095808983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279869914055</t>
+    <t xml:space="preserve">0.182279855012894</t>
   </si>
   <si>
     <t xml:space="preserve">0.169834539294243</t>
@@ -182,49 +182,49 @@
     <t xml:space="preserve">0.168451711535454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794768810272</t>
+    <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606559753418</t>
+    <t xml:space="preserve">0.151606529951096</t>
   </si>
   <si>
     <t xml:space="preserve">0.166566029191017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15707491338253</t>
+    <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109384536743</t>
+    <t xml:space="preserve">0.152109399437904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995037078857</t>
+    <t xml:space="preserve">0.153995022177696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640650868416</t>
+    <t xml:space="preserve">0.157640635967255</t>
   </si>
   <si>
     <t xml:space="preserve">0.1860511302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936812639236</t>
+    <t xml:space="preserve">0.187936797738075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536946773529</t>
+    <t xml:space="preserve">0.18353696167469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714102625847</t>
+    <t xml:space="preserve">0.181714117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194589972496</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160280540585518</t>
+    <t xml:space="preserve">0.16028057038784</t>
   </si>
   <si>
     <t xml:space="preserve">0.147080987691879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480838656425</t>
+    <t xml:space="preserve">0.151480823755264</t>
   </si>
   <si>
     <t xml:space="preserve">0.148338064551353</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">0.144566774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394888043404</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
     <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651644468307</t>
+    <t xml:space="preserve">0.170651629567146</t>
   </si>
   <si>
     <t xml:space="preserve">0.172223016619682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594120502472</t>
+    <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507834553719</t>
+    <t xml:space="preserve">0.200507864356041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593755364418</t>
+    <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131386637688</t>
+    <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765291452408</t>
+    <t xml:space="preserve">0.190765276551247</t>
   </si>
   <si>
     <t xml:space="preserve">0.201010659337044</t>
@@ -266,169 +266,169 @@
     <t xml:space="preserve">0.194850847125053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770926117897</t>
+    <t xml:space="preserve">0.191770955920219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19987927377224</t>
+    <t xml:space="preserve">0.199879288673401</t>
   </si>
   <si>
     <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787323355675</t>
+    <t xml:space="preserve">0.21678726375103</t>
   </si>
   <si>
     <t xml:space="preserve">0.232563942670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220930099487</t>
+    <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
     <t xml:space="preserve">0.251420468091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134249210358</t>
+    <t xml:space="preserve">0.267134219408035</t>
   </si>
   <si>
     <t xml:space="preserve">0.275305420160294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290390640497208</t>
+    <t xml:space="preserve">0.29039067029953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561751842499</t>
+    <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705956697464</t>
+    <t xml:space="preserve">0.257705986499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157346725464</t>
+    <t xml:space="preserve">0.260157316923141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250226199626923</t>
+    <t xml:space="preserve">0.250226229429245</t>
   </si>
   <si>
     <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809310555458</t>
+    <t xml:space="preserve">0.242809325456619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249297142029</t>
+    <t xml:space="preserve">0.243249267339706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375018239021</t>
+    <t xml:space="preserve">0.243375033140182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421228170395</t>
+    <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23382106423378</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564687848091</t>
+    <t xml:space="preserve">0.21056467294693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919014453888</t>
+    <t xml:space="preserve">0.206919074058533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821794509888</t>
+    <t xml:space="preserve">0.211821749806404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20874185860157</t>
+    <t xml:space="preserve">0.208741828799248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592309713364</t>
+    <t xml:space="preserve">0.237592324614525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134949684143</t>
+    <t xml:space="preserve">0.245134979486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803981423378</t>
+    <t xml:space="preserve">0.230803996324539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535516023636</t>
+    <t xml:space="preserve">0.227535530924797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706642270088</t>
+    <t xml:space="preserve">0.235706701874733</t>
   </si>
   <si>
     <t xml:space="preserve">0.226278424263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135679960251</t>
+    <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850161552429</t>
+    <t xml:space="preserve">0.216850116848946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381398081779</t>
+    <t xml:space="preserve">0.222381412982941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141724467278</t>
+    <t xml:space="preserve">0.2131417542696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199233531952</t>
+    <t xml:space="preserve">0.201199218630791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279139637947</t>
+    <t xml:space="preserve">0.204279080033302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793338060379</t>
+    <t xml:space="preserve">0.206793323159218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164762377739</t>
+    <t xml:space="preserve">0.206164807081223</t>
   </si>
   <si>
     <t xml:space="preserve">0.207421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804711699486</t>
+    <t xml:space="preserve">0.208804681897163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947500705719</t>
+    <t xml:space="preserve">0.211947441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22564984858036</t>
+    <t xml:space="preserve">0.225649878382683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867184758186</t>
+    <t xml:space="preserve">0.21986722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810025930405</t>
+    <t xml:space="preserve">0.220810055732727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484036564827</t>
+    <t xml:space="preserve">0.229484081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23438672721386</t>
+    <t xml:space="preserve">0.234386757016182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518448114395</t>
+    <t xml:space="preserve">0.224518492817879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992890954018</t>
+    <t xml:space="preserve">0.21999292075634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741493463516</t>
+    <t xml:space="preserve">0.219741508364677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912999749184</t>
+    <t xml:space="preserve">0.216912984848022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306791305542</t>
+    <t xml:space="preserve">0.231306821107864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038705945015</t>
+    <t xml:space="preserve">0.217038691043854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324254155159</t>
+    <t xml:space="preserve">0.223324224352837</t>
   </si>
   <si>
     <t xml:space="preserve">0.297178983688354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988613605499</t>
+    <t xml:space="preserve">0.351988673210144</t>
   </si>
   <si>
     <t xml:space="preserve">0.465127885341644</t>
@@ -440,85 +440,85 @@
     <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843127012253</t>
+    <t xml:space="preserve">0.436843007802963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072112560272</t>
+    <t xml:space="preserve">0.422072172164917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987212657928</t>
+    <t xml:space="preserve">0.395987272262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36455973982811</t>
+    <t xml:space="preserve">0.364559710025787</t>
   </si>
   <si>
     <t xml:space="preserve">0.414215207099915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388188838959</t>
+    <t xml:space="preserve">0.367388159036636</t>
   </si>
   <si>
     <t xml:space="preserve">0.373988002538681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331715583801</t>
+    <t xml:space="preserve">0.346331685781479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3259037733078</t>
+    <t xml:space="preserve">0.325903743505478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904153347015</t>
+    <t xml:space="preserve">0.314904123544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532334089279</t>
+    <t xml:space="preserve">0.326532393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389179944992</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818232536316</t>
+    <t xml:space="preserve">0.321818172931671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845928907394</t>
+    <t xml:space="preserve">0.34884586930275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303288936615</t>
+    <t xml:space="preserve">0.341303259134293</t>
   </si>
   <si>
     <t xml:space="preserve">0.32684662938118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361192941666</t>
+    <t xml:space="preserve">0.318361133337021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189612150192</t>
+    <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
     <t xml:space="preserve">0.333132058382034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989373683929</t>
+    <t xml:space="preserve">0.329989314079285</t>
   </si>
   <si>
     <t xml:space="preserve">0.317418366670609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332386255264</t>
+    <t xml:space="preserve">0.324332356452942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275592565536</t>
+    <t xml:space="preserve">0.314275562763214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761409044266</t>
+    <t xml:space="preserve">0.311761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33470356464386</t>
+    <t xml:space="preserve">0.334703534841537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046897649765</t>
+    <t xml:space="preserve">0.318046867847443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789776086807</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
     <t xml:space="preserve">0.328417986631393</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">0.310504257678986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069995164871</t>
+    <t xml:space="preserve">0.311069965362549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561081171036</t>
+    <t xml:space="preserve">0.320561140775681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589537620544</t>
+    <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
     <t xml:space="preserve">0.358274191617966</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34004619717598</t>
+    <t xml:space="preserve">0.340046226978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.3193039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846249341965</t>
+    <t xml:space="preserve">0.337846279144287</t>
   </si>
   <si>
     <t xml:space="preserve">0.31458991765976</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">0.389701694250107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588077068329</t>
+    <t xml:space="preserve">0.369588047266006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959546089172</t>
+    <t xml:space="preserve">0.368959575891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37021666765213</t>
+    <t xml:space="preserve">0.370216637849808</t>
   </si>
   <si>
     <t xml:space="preserve">0.363616853952408</t>
@@ -587,175 +587,175 @@
     <t xml:space="preserve">0.345074623823166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788725376129</t>
+    <t xml:space="preserve">0.349788784980774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502826929092</t>
+    <t xml:space="preserve">0.354502856731415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073893547058</t>
+    <t xml:space="preserve">0.36707392334938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758897781372</t>
+    <t xml:space="preserve">0.388758927583694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587376594543</t>
+    <t xml:space="preserve">0.391587406396866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759277820587</t>
+    <t xml:space="preserve">0.37775930762291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130717039108</t>
+    <t xml:space="preserve">0.377130776643753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187510728836</t>
+    <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444922924042</t>
+    <t xml:space="preserve">0.377444893121719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40792977809906</t>
+    <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
     <t xml:space="preserve">0.414843797683716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3922159075737</t>
+    <t xml:space="preserve">0.392215877771378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37681645154953</t>
+    <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38655897974968</t>
+    <t xml:space="preserve">0.386558949947357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413284540176</t>
+    <t xml:space="preserve">0.471413403749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357280731201</t>
+    <t xml:space="preserve">0.439357310533524</t>
   </si>
   <si>
     <t xml:space="preserve">0.452556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700323104858</t>
+    <t xml:space="preserve">0.433700233697891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100159168243</t>
+    <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271359920502</t>
+    <t xml:space="preserve">0.446271300315857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985781908035</t>
+    <t xml:space="preserve">0.43998584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386348247528</t>
+    <t xml:space="preserve">0.422386407852173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900591373444</t>
+    <t xml:space="preserve">0.424900650978088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129375696182</t>
+    <t xml:space="preserve">0.42112934589386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815430641174</t>
+    <t xml:space="preserve">0.409815341234207</t>
   </si>
   <si>
     <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558279275894</t>
+    <t xml:space="preserve">0.408558160066605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586676120758</t>
+    <t xml:space="preserve">0.413586646318436</t>
   </si>
   <si>
     <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443261146545</t>
+    <t xml:space="preserve">0.432443201541901</t>
   </si>
   <si>
     <t xml:space="preserve">0.417357951402664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613582611084</t>
+    <t xml:space="preserve">0.462613642215729</t>
   </si>
   <si>
     <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758547544479</t>
+    <t xml:space="preserve">0.399758577346802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4186150431633</t>
+    <t xml:space="preserve">0.418615132570267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643589019775</t>
+    <t xml:space="preserve">0.423643499612808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072492599487</t>
+    <t xml:space="preserve">0.411072432994843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501485586166</t>
+    <t xml:space="preserve">0.398501455783844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786884784698</t>
+    <t xml:space="preserve">0.404786974191666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159143686295</t>
+    <t xml:space="preserve">0.382159113883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38341623544693</t>
+    <t xml:space="preserve">0.383416205644608</t>
   </si>
   <si>
     <t xml:space="preserve">0.388444602489471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529822826385</t>
+    <t xml:space="preserve">0.403529912233353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186139583588</t>
+    <t xml:space="preserve">0.431186079978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.419872224330902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301157712936</t>
+    <t xml:space="preserve">0.407301187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730091094971</t>
+    <t xml:space="preserve">0.394730120897293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329524755478</t>
+    <t xml:space="preserve">0.412329614162445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015669107437</t>
+    <t xml:space="preserve">0.401015728712082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100829839706</t>
+    <t xml:space="preserve">0.416100919246674</t>
   </si>
   <si>
     <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816801786423</t>
+    <t xml:space="preserve">0.3658167719841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302528858185</t>
+    <t xml:space="preserve">0.363302618265152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674728155136</t>
+    <t xml:space="preserve">0.340674757957458</t>
   </si>
   <si>
     <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531313180923</t>
+    <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35701709985733</t>
+    <t xml:space="preserve">0.357017129659653</t>
   </si>
   <si>
     <t xml:space="preserve">0.344446033239365</t>
@@ -764,160 +764,160 @@
     <t xml:space="preserve">0.336903423070908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160574436188</t>
+    <t xml:space="preserve">0.338160485029221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703184604645</t>
+    <t xml:space="preserve">0.345703154802322</t>
   </si>
   <si>
     <t xml:space="preserve">0.3721022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930418968201</t>
+    <t xml:space="preserve">0.385930448770523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245735168457</t>
+    <t xml:space="preserve">0.353245764970779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788375139236</t>
+    <t xml:space="preserve">0.360788404941559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387868404388</t>
+    <t xml:space="preserve">0.378387749195099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873625278473</t>
+    <t xml:space="preserve">0.375873595476151</t>
   </si>
   <si>
     <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673327207565</t>
+    <t xml:space="preserve">0.384673297405243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39095875620842</t>
+    <t xml:space="preserve">0.390958786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393472969532013</t>
+    <t xml:space="preserve">0.39347305893898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557608604431</t>
+    <t xml:space="preserve">0.430557519197464</t>
   </si>
   <si>
     <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699652433395</t>
+    <t xml:space="preserve">0.455699592828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463956028223038</t>
+    <t xml:space="preserve">0.463955968618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181872367859</t>
+    <t xml:space="preserve">0.443181782960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332375526428</t>
+    <t xml:space="preserve">0.429332345724106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483027696609</t>
+    <t xml:space="preserve">0.415483057498932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870060920715</t>
+    <t xml:space="preserve">0.425870031118393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257183551788</t>
+    <t xml:space="preserve">0.436257153749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719468355179</t>
+    <t xml:space="preserve">0.439719527959824</t>
   </si>
   <si>
     <t xml:space="preserve">0.432794839143753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4189453125</t>
+    <t xml:space="preserve">0.418945401906967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558219671249</t>
+    <t xml:space="preserve">0.408558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633620262146</t>
+    <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
     <t xml:space="preserve">0.412020683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784063816071</t>
+    <t xml:space="preserve">0.387784093618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246497631073</t>
+    <t xml:space="preserve">0.391246467828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095845460892</t>
+    <t xml:space="preserve">0.405095934867859</t>
   </si>
   <si>
     <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644306182861</t>
+    <t xml:space="preserve">0.446644186973572</t>
   </si>
   <si>
     <t xml:space="preserve">0.526278436183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106590986252</t>
+    <t xml:space="preserve">0.450106501579285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031309604645</t>
+    <t xml:space="preserve">0.457031339406967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568905591965</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171216249466</t>
+    <t xml:space="preserve">0.398171156644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708782434464</t>
+    <t xml:space="preserve">0.394708842039108</t>
   </si>
   <si>
     <t xml:space="preserve">0.380859404802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934745788574</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085248947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472341775894</t>
+    <t xml:space="preserve">0.370472401380539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384321808815002</t>
+    <t xml:space="preserve">0.384321749210358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009967565536</t>
+    <t xml:space="preserve">0.367009907960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340695977210999</t>
+    <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311093091965</t>
+    <t xml:space="preserve">0.33931103348732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160500526428</t>
+    <t xml:space="preserve">0.353160560131073</t>
   </si>
   <si>
     <t xml:space="preserve">0.346235811710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386404275894</t>
+    <t xml:space="preserve">0.332386374473572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612218618393</t>
+    <t xml:space="preserve">0.311612248420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31438210606575</t>
+    <t xml:space="preserve">0.314382135868073</t>
   </si>
   <si>
     <t xml:space="preserve">0.290838062763214</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373599052429</t>
+    <t xml:space="preserve">0.278373569250107</t>
   </si>
   <si>
     <t xml:space="preserve">0.263139218091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833794355392</t>
+    <t xml:space="preserve">0.272833853960037</t>
   </si>
   <si>
     <t xml:space="preserve">0.261754214763641</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">0.249289780855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750020861626</t>
+    <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298317670822</t>
+    <t xml:space="preserve">0.285298347473145</t>
   </si>
   <si>
     <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448880434036</t>
+    <t xml:space="preserve">0.271448910236359</t>
   </si>
   <si>
     <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143516302109</t>
+    <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29499289393425</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302586078644</t>
+    <t xml:space="preserve">0.303302556276321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842360973358</t>
+    <t xml:space="preserve">0.308842390775681</t>
   </si>
   <si>
     <t xml:space="preserve">0.337926149368286</t>
@@ -980,19 +980,19 @@
     <t xml:space="preserve">0.343465924263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547593355179</t>
+    <t xml:space="preserve">0.363547563552856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397030591965</t>
+    <t xml:space="preserve">0.377397060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231543302536</t>
+    <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
     <t xml:space="preserve">0.331001460552216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33654123544693</t>
+    <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
     <t xml:space="preserve">0.349698185920715</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">0.344850867986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691798210144</t>
+    <t xml:space="preserve">0.322691768407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076741933823</t>
+    <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306824684143</t>
+    <t xml:space="preserve">0.321306794881821</t>
   </si>
   <si>
     <t xml:space="preserve">0.318536967039108</t>
@@ -1019,37 +1019,37 @@
     <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687529802322</t>
+    <t xml:space="preserve">0.3046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.297762811183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913403749466</t>
+    <t xml:space="preserve">0.283913373947144</t>
   </si>
   <si>
     <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524191617966</t>
+    <t xml:space="preserve">0.264524132013321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294049263</t>
+    <t xml:space="preserve">0.267294079065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369271039963</t>
+    <t xml:space="preserve">0.260369300842285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909105539322</t>
+    <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063936710358</t>
+    <t xml:space="preserve">0.270063906908035</t>
   </si>
   <si>
     <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223006486893</t>
+    <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
     <t xml:space="preserve">0.296377867460251</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809957742691</t>
+    <t xml:space="preserve">0.429810017347336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647861719131</t>
+    <t xml:space="preserve">0.399647831916809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337045907974</t>
+    <t xml:space="preserve">0.388337016105652</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945271492004</t>
+    <t xml:space="preserve">0.36194521188736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485765695572</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
     <t xml:space="preserve">0.363453328609467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796581506729</t>
+    <t xml:space="preserve">0.380796551704407</t>
   </si>
   <si>
     <t xml:space="preserve">0.37401008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961445331573</t>
+    <t xml:space="preserve">0.364961475133896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349880367517471</t>
+    <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
     <t xml:space="preserve">0.343847960233688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339873313904</t>
+    <t xml:space="preserve">0.342339932918549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323669672012</t>
+    <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">0.352896600961685</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388514041901</t>
+    <t xml:space="preserve">0.351388484239578</t>
   </si>
   <si>
     <t xml:space="preserve">0.336307466030121</t>
@@ -1115,46 +1115,46 @@
     <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372340202332</t>
+    <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350541353226</t>
+    <t xml:space="preserve">0.437350451946259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958647727966</t>
+    <t xml:space="preserve">0.410958707332611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431619167328</t>
+    <t xml:space="preserve">0.452431589365005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444891005754471</t>
+    <t xml:space="preserve">0.444890975952148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120684146881</t>
+    <t xml:space="preserve">0.441120803356171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728939533234</t>
+    <t xml:space="preserve">0.414728909730911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418183326721</t>
+    <t xml:space="preserve">0.403418153524399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107278108597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566813707352</t>
+    <t xml:space="preserve">0.384566843509674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877569913864</t>
+    <t xml:space="preserve">0.395877540111542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188385725021</t>
+    <t xml:space="preserve">0.407188415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501969337463</t>
+    <t xml:space="preserve">0.372501999139786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469591856003</t>
+    <t xml:space="preserve">0.366469532251358</t>
   </si>
   <si>
     <t xml:space="preserve">0.354404717683792</t>
@@ -1163,85 +1163,85 @@
     <t xml:space="preserve">0.345356076955795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831756591797</t>
+    <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993822813034</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437154769897</t>
+    <t xml:space="preserve">0.36043718457222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977678775787</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929067850113</t>
+    <t xml:space="preserve">0.358929038047791</t>
   </si>
   <si>
     <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112903118134</t>
+    <t xml:space="preserve">0.300112962722778</t>
   </si>
   <si>
     <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210154771805</t>
+    <t xml:space="preserve">0.31821021437645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718301296234</t>
+    <t xml:space="preserve">0.319718271493912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32424259185791</t>
+    <t xml:space="preserve">0.324242651462555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330275028944016</t>
+    <t xml:space="preserve">0.330275058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3317831158638</t>
+    <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
     <t xml:space="preserve">0.337815552949905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766912221909</t>
+    <t xml:space="preserve">0.328766942024231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309161573648453</t>
+    <t xml:space="preserve">0.30916154384613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653456926346</t>
+    <t xml:space="preserve">0.307653397321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.303129136562347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685864210129</t>
+    <t xml:space="preserve">0.313685923814774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734534740448</t>
+    <t xml:space="preserve">0.322734475135803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599207162857</t>
+    <t xml:space="preserve">0.317599177360535</t>
   </si>
   <si>
     <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314439028501511</t>
   </si>
   <si>
     <t xml:space="preserve">0.319179326295853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820040941238</t>
+    <t xml:space="preserve">0.331820011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400100469589</t>
+    <t xml:space="preserve">0.333400160074234</t>
   </si>
   <si>
     <t xml:space="preserve">0.320759385824203</t>
@@ -1256,19 +1256,19 @@
     <t xml:space="preserve">0.303378343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317688465118</t>
+    <t xml:space="preserve">0.292317658662796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798224449158</t>
+    <t xml:space="preserve">0.30179825425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019117832184</t>
+    <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218135118484</t>
+    <t xml:space="preserve">0.300218164920807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638015985489</t>
+    <t xml:space="preserve">0.298637986183167</t>
   </si>
   <si>
     <t xml:space="preserve">0.290737569332123</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577360868454</t>
+    <t xml:space="preserve">0.287577390670776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27967694401741</t>
+    <t xml:space="preserve">0.279676884412766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096824884415</t>
+    <t xml:space="preserve">0.278096795082092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196318626404</t>
+    <t xml:space="preserve">0.270196288824081</t>
   </si>
   <si>
     <t xml:space="preserve">0.281257003545761</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">0.271776407957077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417182207108</t>
+    <t xml:space="preserve">0.284417152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997271537781</t>
+    <t xml:space="preserve">0.285997241735458</t>
   </si>
   <si>
     <t xml:space="preserve">0.295477837324142</t>
@@ -1310,58 +1310,58 @@
     <t xml:space="preserve">0.297057896852493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118641376495</t>
+    <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289157509803772</t>
+    <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
     <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140457868576</t>
+    <t xml:space="preserve">0.338140398263931</t>
   </si>
   <si>
     <t xml:space="preserve">0.339720517396927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341300636529922</t>
+    <t xml:space="preserve">0.3413006067276</t>
   </si>
   <si>
     <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336560308933258</t>
+    <t xml:space="preserve">0.33656033873558</t>
   </si>
   <si>
     <t xml:space="preserve">0.352361291646957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359283685684</t>
+    <t xml:space="preserve">0.295359313488007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944742202759</t>
+    <t xml:space="preserve">0.291944712400436</t>
   </si>
   <si>
     <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115629434586</t>
+    <t xml:space="preserve">0.285115659236908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822915077209</t>
+    <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
     <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29877382516861</t>
+    <t xml:space="preserve">0.298773854970932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408313989639</t>
+    <t xml:space="preserve">0.283408343791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286516666412</t>
+    <t xml:space="preserve">0.27828648686409</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530170917511</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">0.279993802309036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164689540863</t>
+    <t xml:space="preserve">0.273164659738541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579231023788</t>
+    <t xml:space="preserve">0.276579201221466</t>
   </si>
   <si>
     <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701058149338</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
     <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457403898239</t>
+    <t xml:space="preserve">0.271457344293594</t>
   </si>
   <si>
     <t xml:space="preserve">0.268042802810669</t>
@@ -1394,58 +1394,58 @@
     <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293652027845383</t>
+    <t xml:space="preserve">0.29365199804306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188456058502</t>
+    <t xml:space="preserve">0.302188396453857</t>
   </si>
   <si>
     <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310253381729</t>
+    <t xml:space="preserve">0.307310223579407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383020401001</t>
+    <t xml:space="preserve">0.324383050203323</t>
   </si>
   <si>
     <t xml:space="preserve">0.319261193275452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017509222031</t>
+    <t xml:space="preserve">0.309017479419708</t>
   </si>
   <si>
     <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432110309601</t>
+    <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724824666977</t>
+    <t xml:space="preserve">0.310724854469299</t>
   </si>
   <si>
     <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829840660095</t>
+    <t xml:space="preserve">0.299829810857773</t>
   </si>
   <si>
     <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316205739975</t>
+    <t xml:space="preserve">0.303316235542297</t>
   </si>
   <si>
     <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627428770065</t>
+    <t xml:space="preserve">0.28762748837471</t>
   </si>
   <si>
     <t xml:space="preserve">0.298086613416672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560396432877</t>
+    <t xml:space="preserve">0.313560336828232</t>
   </si>
   <si>
     <t xml:space="preserve">0.304652392864227</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">0.306434005498886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089197397232</t>
+    <t xml:space="preserve">0.301089227199554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836445331573</t>
+    <t xml:space="preserve">0.286836475133896</t>
   </si>
   <si>
     <t xml:space="preserve">0.288618057966232</t>
@@ -1469,31 +1469,31 @@
     <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307644367218</t>
+    <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962836265564</t>
+    <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054922103882</t>
+    <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273309469223</t>
+    <t xml:space="preserve">0.283273279666901</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710084199905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491726636887</t>
+    <t xml:space="preserve">0.281491696834564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292181253433228</t>
+    <t xml:space="preserve">0.29218128323555</t>
   </si>
   <si>
     <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902150630951</t>
+    <t xml:space="preserve">0.289902120828629</t>
   </si>
   <si>
     <t xml:space="preserve">0.302665114402771</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">0.291725426912308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488450288773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781525611877</t>
+    <t xml:space="preserve">0.3117815554142</t>
   </si>
   <si>
     <t xml:space="preserve">0.317251414060593</t>
@@ -1520,25 +1520,25 @@
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191101551056</t>
+    <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331837683916092</t>
+    <t xml:space="preserve">0.33183765411377</t>
   </si>
   <si>
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897996425629</t>
+    <t xml:space="preserve">0.320897936820984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324544548988342</t>
+    <t xml:space="preserve">0.32454451918602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158191680908</t>
+    <t xml:space="preserve">0.324158161878586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32974711060524</t>
+    <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021134853363</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432215929031</t>
+    <t xml:space="preserve">0.320432245731354</t>
   </si>
   <si>
     <t xml:space="preserve">0.311117351055145</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316706269979477</t>
+    <t xml:space="preserve">0.316706240177155</t>
   </si>
   <si>
     <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340924978256226</t>
+    <t xml:space="preserve">0.340925008058548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473116159439</t>
+    <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
     <t xml:space="preserve">0.307391405105591</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344650954008102</t>
+    <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
     <t xml:space="preserve">0.337199002504349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348376899957657</t>
+    <t xml:space="preserve">0.348376929759979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732605457306</t>
+    <t xml:space="preserve">0.370732635259628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677289485931</t>
+    <t xml:space="preserve">0.398677319288254</t>
   </si>
   <si>
     <t xml:space="preserve">0.419170051813126</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540292263031</t>
+    <t xml:space="preserve">0.400540262460709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3912253677845</t>
+    <t xml:space="preserve">0.391225397586823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393088340759277</t>
+    <t xml:space="preserve">0.3930883705616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362454414368</t>
+    <t xml:space="preserve">0.389362424612045</t>
   </si>
   <si>
     <t xml:space="preserve">0.374458581209183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37632155418396</t>
+    <t xml:space="preserve">0.376321583986282</t>
   </si>
   <si>
     <t xml:space="preserve">0.372595608234406</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869662284851</t>
+    <t xml:space="preserve">0.368869692087173</t>
   </si>
   <si>
     <t xml:space="preserve">0.378184527158737</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">0.392482101917267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394378125667572</t>
+    <t xml:space="preserve">0.394378155469894</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754417181015</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403858363628387</t>
+    <t xml:space="preserve">0.40385839343071</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
@@ -69100,6 +69100,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46073.3333333333</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2577" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" s="1" t="n">
+        <v>46076.5939351852</v>
+      </c>
+      <c r="B2578" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2578" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D2578" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E2578" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2578" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -44,70 +44,70 @@
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17662288248539</t>
+    <t xml:space="preserve">0.176622852683067</t>
   </si>
   <si>
     <t xml:space="preserve">0.172851577401161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594485640526</t>
+    <t xml:space="preserve">0.171594470739365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051860570908</t>
+    <t xml:space="preserve">0.164051875472069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169708833098412</t>
+    <t xml:space="preserve">0.169708803296089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966640233994</t>
+    <t xml:space="preserve">0.148966625332832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309652805328</t>
+    <t xml:space="preserve">0.14330966770649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783760309219</t>
+    <t xml:space="preserve">0.149783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195335149765</t>
+    <t xml:space="preserve">0.145195320248604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737930417061</t>
+    <t xml:space="preserve">0.152737945318222</t>
   </si>
   <si>
     <t xml:space="preserve">0.153366476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789439678192</t>
+    <t xml:space="preserve">0.150789424777031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1464524269104</t>
+    <t xml:space="preserve">0.146452412009239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852657914162</t>
+    <t xml:space="preserve">0.139852628111839</t>
   </si>
   <si>
     <t xml:space="preserve">0.139538362622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915496110916</t>
+    <t xml:space="preserve">0.139915481209755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052575945854</t>
   </si>
   <si>
     <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15110370516777</t>
+    <t xml:space="preserve">0.151103720068932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337378978729</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
     <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16342331469059</t>
+    <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
     <t xml:space="preserve">0.157137781381607</t>
@@ -122,31 +122,31 @@
     <t xml:space="preserve">0.155692130327225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909086465836</t>
+    <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
     <t xml:space="preserve">0.158960595726967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314281463623</t>
+    <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251428365707</t>
+    <t xml:space="preserve">0.17725145816803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965939760208</t>
+    <t xml:space="preserve">0.170965954661369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937513113022</t>
+    <t xml:space="preserve">0.165937528014183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565388321877</t>
+    <t xml:space="preserve">0.188565343618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1926509141922</t>
+    <t xml:space="preserve">0.192650899291039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708102822304</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
     <t xml:space="preserve">0.184165522456169</t>
@@ -158,52 +158,52 @@
     <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678975701332</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073512434959</t>
+    <t xml:space="preserve">0.201073572039604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.19673652946949</t>
+    <t xml:space="preserve">0.196736514568329</t>
   </si>
   <si>
     <t xml:space="preserve">0.194222301244736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137095808983</t>
+    <t xml:space="preserve">0.179137110710144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279855012894</t>
+    <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834539294243</t>
+    <t xml:space="preserve">0.169834524393082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451711535454</t>
+    <t xml:space="preserve">0.168451726436615</t>
   </si>
   <si>
     <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606529951096</t>
+    <t xml:space="preserve">0.151606544852257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566029191017</t>
+    <t xml:space="preserve">0.166566044092178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074943184853</t>
+    <t xml:space="preserve">0.157074928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109399437904</t>
+    <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995022177696</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157640635967255</t>
+    <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1860511302948</t>
+    <t xml:space="preserve">0.186051145195961</t>
   </si>
   <si>
     <t xml:space="preserve">0.187936797738075</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">0.18353696167469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181714117527008</t>
+    <t xml:space="preserve">0.181714177131653</t>
   </si>
   <si>
     <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16028057038784</t>
+    <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080987691879</t>
+    <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480823755264</t>
+    <t xml:space="preserve">0.151480868458748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338064551353</t>
+    <t xml:space="preserve">0.148338094353676</t>
   </si>
   <si>
     <t xml:space="preserve">0.144566774368286</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183246135712</t>
+    <t xml:space="preserve">0.165183261036873</t>
   </si>
   <si>
     <t xml:space="preserve">0.170651629567146</t>
@@ -245,16 +245,16 @@
     <t xml:space="preserve">0.172223016619682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594105601311</t>
+    <t xml:space="preserve">0.18259409070015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507864356041</t>
+    <t xml:space="preserve">0.200507819652557</t>
   </si>
   <si>
     <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131401538849</t>
+    <t xml:space="preserve">0.17813141644001</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765276551247</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">0.201010659337044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850847125053</t>
+    <t xml:space="preserve">0.194850906729698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770955920219</t>
+    <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879288673401</t>
+    <t xml:space="preserve">0.19987927377224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078841567039</t>
+    <t xml:space="preserve">0.213078811764717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21678726375103</t>
+    <t xml:space="preserve">0.216787308454514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563942670822</t>
+    <t xml:space="preserve">0.232563957571983</t>
   </si>
   <si>
     <t xml:space="preserve">0.238220885396004</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">0.251420468091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134219408035</t>
+    <t xml:space="preserve">0.26713427901268</t>
   </si>
   <si>
     <t xml:space="preserve">0.275305420160294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29039067029953</t>
+    <t xml:space="preserve">0.290390640497208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561811447144</t>
+    <t xml:space="preserve">0.298561841249466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705986499786</t>
+    <t xml:space="preserve">0.257706016302109</t>
   </si>
   <si>
     <t xml:space="preserve">0.260157316923141</t>
@@ -311,40 +311,40 @@
     <t xml:space="preserve">0.250163346529007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809325456619</t>
+    <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249267339706</t>
+    <t xml:space="preserve">0.243249297142029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375033140182</t>
+    <t xml:space="preserve">0.243375018239021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421183466911</t>
+    <t xml:space="preserve">0.22942116856575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821049332619</t>
+    <t xml:space="preserve">0.23382106423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21056467294693</t>
+    <t xml:space="preserve">0.210564658045769</t>
   </si>
   <si>
     <t xml:space="preserve">0.206919074058533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821749806404</t>
+    <t xml:space="preserve">0.211821764707565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741828799248</t>
+    <t xml:space="preserve">0.20874185860157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592324614525</t>
+    <t xml:space="preserve">0.23759238421917</t>
   </si>
   <si>
     <t xml:space="preserve">0.245134979486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803996324539</t>
+    <t xml:space="preserve">0.230803981423378</t>
   </si>
   <si>
     <t xml:space="preserve">0.227535530924797</t>
@@ -353,157 +353,157 @@
     <t xml:space="preserve">0.235706701874733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278424263</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
     <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850116848946</t>
+    <t xml:space="preserve">0.21685017645359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381412982941</t>
+    <t xml:space="preserve">0.222381398081779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2131417542696</t>
+    <t xml:space="preserve">0.213141709566116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199218630791</t>
+    <t xml:space="preserve">0.201199248433113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279080033302</t>
+    <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793323159218</t>
+    <t xml:space="preserve">0.206793338060379</t>
   </si>
   <si>
     <t xml:space="preserve">0.206164807081223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421898841858</t>
+    <t xml:space="preserve">0.207421913743019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208804681897163</t>
+    <t xml:space="preserve">0.208804711699486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947441101074</t>
+    <t xml:space="preserve">0.211947411298752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649878382683</t>
+    <t xml:space="preserve">0.225649863481522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21986722946167</t>
+    <t xml:space="preserve">0.219867214560509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810055732727</t>
+    <t xml:space="preserve">0.220810025930405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484081268311</t>
+    <t xml:space="preserve">0.229484006762505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386757016182</t>
+    <t xml:space="preserve">0.23438672721386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518492817879</t>
+    <t xml:space="preserve">0.224518448114395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21999292075634</t>
+    <t xml:space="preserve">0.219992890954018</t>
   </si>
   <si>
     <t xml:space="preserve">0.219741508364677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912984848022</t>
+    <t xml:space="preserve">0.216913044452667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306821107864</t>
+    <t xml:space="preserve">0.231306836009026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038691043854</t>
+    <t xml:space="preserve">0.217038735747337</t>
   </si>
   <si>
     <t xml:space="preserve">0.223324224352837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
     <t xml:space="preserve">0.351988673210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127885341644</t>
+    <t xml:space="preserve">0.465127915143967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582354068756</t>
+    <t xml:space="preserve">0.545582473278046</t>
   </si>
   <si>
     <t xml:space="preserve">0.477070361375809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843007802963</t>
+    <t xml:space="preserve">0.43684309720993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072172164917</t>
+    <t xml:space="preserve">0.422072142362595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987272262573</t>
+    <t xml:space="preserve">0.395987182855606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559710025787</t>
+    <t xml:space="preserve">0.364559680223465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215207099915</t>
+    <t xml:space="preserve">0.414215266704559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388159036636</t>
+    <t xml:space="preserve">0.367388129234314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373988002538681</t>
+    <t xml:space="preserve">0.373987972736359</t>
   </si>
   <si>
     <t xml:space="preserve">0.346331685781479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903743505478</t>
+    <t xml:space="preserve">0.3259037733078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904123544693</t>
+    <t xml:space="preserve">0.314904153347015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532393693924</t>
+    <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
     <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818172931671</t>
+    <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34884586930275</t>
+    <t xml:space="preserve">0.348845988512039</t>
   </si>
   <si>
     <t xml:space="preserve">0.341303259134293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32684662938118</t>
+    <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361133337021</t>
+    <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132058382034</t>
+    <t xml:space="preserve">0.333132088184357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989314079285</t>
+    <t xml:space="preserve">0.329989403486252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418366670609</t>
+    <t xml:space="preserve">0.317418396472931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332356452942</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
     <t xml:space="preserve">0.314275562763214</t>
@@ -515,130 +515,130 @@
     <t xml:space="preserve">0.334703534841537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046867847443</t>
+    <t xml:space="preserve">0.318046927452087</t>
   </si>
   <si>
     <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328417986631393</t>
+    <t xml:space="preserve">0.328418016433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075294494629</t>
+    <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103721141815</t>
+    <t xml:space="preserve">0.328103750944138</t>
   </si>
   <si>
     <t xml:space="preserve">0.301704555749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504257678986</t>
+    <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
     <t xml:space="preserve">0.311069965362549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561140775681</t>
+    <t xml:space="preserve">0.320561081171036</t>
   </si>
   <si>
     <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274191617966</t>
+    <t xml:space="preserve">0.358274221420288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417666196823</t>
+    <t xml:space="preserve">0.339417606592178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046226978302</t>
+    <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
     <t xml:space="preserve">0.3193039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846279144287</t>
+    <t xml:space="preserve">0.337846308946609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31458991765976</t>
+    <t xml:space="preserve">0.314589887857437</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701694250107</t>
+    <t xml:space="preserve">0.389701813459396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588047266006</t>
+    <t xml:space="preserve">0.369588106870651</t>
   </si>
   <si>
     <t xml:space="preserve">0.368959575891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216637849808</t>
+    <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
     <t xml:space="preserve">0.363616853952408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845168828964</t>
+    <t xml:space="preserve">0.370845198631287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074623823166</t>
+    <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788784980774</t>
+    <t xml:space="preserve">0.349788755178452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502856731415</t>
+    <t xml:space="preserve">0.35450291633606</t>
   </si>
   <si>
     <t xml:space="preserve">0.36707392334938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758927583694</t>
+    <t xml:space="preserve">0.38875886797905</t>
   </si>
   <si>
     <t xml:space="preserve">0.391587406396866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37775930762291</t>
+    <t xml:space="preserve">0.377759248018265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130776643753</t>
+    <t xml:space="preserve">0.377130687236786</t>
   </si>
   <si>
     <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444893121719</t>
+    <t xml:space="preserve">0.377444982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929718494415</t>
+    <t xml:space="preserve">0.40792977809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843797683716</t>
+    <t xml:space="preserve">0.414843827486038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215877771378</t>
+    <t xml:space="preserve">0.392215996980667</t>
   </si>
   <si>
     <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386558949947357</t>
+    <t xml:space="preserve">0.386559039354324</t>
   </si>
   <si>
     <t xml:space="preserve">0.471413403749466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357310533524</t>
+    <t xml:space="preserve">0.439357280731201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556848526001</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700233697891</t>
+    <t xml:space="preserve">0.433700352907181</t>
   </si>
   <si>
     <t xml:space="preserve">0.438100188970566</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">0.446271300315857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43998584151268</t>
+    <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
     <t xml:space="preserve">0.422386407852173</t>
@@ -656,43 +656,43 @@
     <t xml:space="preserve">0.424900650978088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42112934589386</t>
+    <t xml:space="preserve">0.421129316091537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815341234207</t>
+    <t xml:space="preserve">0.40981537103653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044065952301</t>
+    <t xml:space="preserve">0.406044095754623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558160066605</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586646318436</t>
+    <t xml:space="preserve">0.413586676120758</t>
   </si>
   <si>
     <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443201541901</t>
+    <t xml:space="preserve">0.432443231344223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357951402664</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613642215729</t>
+    <t xml:space="preserve">0.462613672018051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414834499359</t>
+    <t xml:space="preserve">0.427414864301682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758577346802</t>
+    <t xml:space="preserve">0.399758547544479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615132570267</t>
+    <t xml:space="preserve">0.418615102767944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643499612808</t>
+    <t xml:space="preserve">0.423643529415131</t>
   </si>
   <si>
     <t xml:space="preserve">0.411072432994843</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">0.398501455783844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786974191666</t>
+    <t xml:space="preserve">0.404787003993988</t>
   </si>
   <si>
     <t xml:space="preserve">0.382159113883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416205644608</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
     <t xml:space="preserve">0.388444602489471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529912233353</t>
+    <t xml:space="preserve">0.403529852628708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186079978943</t>
+    <t xml:space="preserve">0.43118605017662</t>
   </si>
   <si>
     <t xml:space="preserve">0.419872224330902</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">0.407301187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730120897293</t>
+    <t xml:space="preserve">0.394730150699615</t>
   </si>
   <si>
     <t xml:space="preserve">0.412329614162445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015728712082</t>
+    <t xml:space="preserve">0.401015639305115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416100919246674</t>
+    <t xml:space="preserve">0.416100889444351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045466899872</t>
+    <t xml:space="preserve">0.362045496702194</t>
   </si>
   <si>
     <t xml:space="preserve">0.3658167719841</t>
@@ -746,136 +746,133 @@
     <t xml:space="preserve">0.363302618265152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674757957458</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329360812902451</t>
+    <t xml:space="preserve">0.329360842704773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531283378601</t>
+    <t xml:space="preserve">0.359531223773956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017129659653</t>
+    <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
     <t xml:space="preserve">0.344446033239365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903423070908</t>
+    <t xml:space="preserve">0.33690345287323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160485029221</t>
+    <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
     <t xml:space="preserve">0.345703154802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3721022605896</t>
+    <t xml:space="preserve">0.372102290391922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930448770523</t>
+    <t xml:space="preserve">0.385930418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245764970779</t>
+    <t xml:space="preserve">0.353245705366135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788404941559</t>
+    <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378387749195099</t>
+    <t xml:space="preserve">0.378387778997421</t>
   </si>
   <si>
     <t xml:space="preserve">0.375873595476151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359382152557</t>
+    <t xml:space="preserve">0.373359441757202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673297405243</t>
+    <t xml:space="preserve">0.384673357009888</t>
   </si>
   <si>
     <t xml:space="preserve">0.390958786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39347305893898</t>
+    <t xml:space="preserve">0.393473029136658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272060394287</t>
+    <t xml:space="preserve">0.424272030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557519197464</t>
+    <t xml:space="preserve">0.430557608604431</t>
   </si>
   <si>
     <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699592828751</t>
+    <t xml:space="preserve">0.455699622631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955968618393</t>
+    <t xml:space="preserve">0.463956028223038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181782960892</t>
+    <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332345724106</t>
+    <t xml:space="preserve">0.429332435131073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483057498932</t>
+    <t xml:space="preserve">0.415482968091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870031118393</t>
+    <t xml:space="preserve">0.42587012052536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257153749466</t>
+    <t xml:space="preserve">0.436257064342499</t>
   </si>
   <si>
     <t xml:space="preserve">0.439719527959824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794839143753</t>
+    <t xml:space="preserve">0.432794779539108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418945401906967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408558189868927</t>
+    <t xml:space="preserve">0.4189453125</t>
   </si>
   <si>
     <t xml:space="preserve">0.401633560657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020683288574</t>
+    <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784093618393</t>
+    <t xml:space="preserve">0.387784153223038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246467828751</t>
+    <t xml:space="preserve">0.391246438026428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095934867859</t>
+    <t xml:space="preserve">0.405095845460892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
+    <t xml:space="preserve">0.422407746315002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644186973572</t>
+    <t xml:space="preserve">0.446644216775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106501579285</t>
+    <t xml:space="preserve">0.450106590986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031339406967</t>
+    <t xml:space="preserve">0.457031309604645</t>
   </si>
   <si>
     <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398171156644821</t>
+    <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
     <t xml:space="preserve">0.394708842039108</t>
@@ -884,37 +881,37 @@
     <t xml:space="preserve">0.380859404802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934745788574</t>
+    <t xml:space="preserve">0.373934656381607</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085248947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472401380539</t>
+    <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
     <t xml:space="preserve">0.384321749210358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009907960892</t>
+    <t xml:space="preserve">0.367009997367859</t>
   </si>
   <si>
     <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33931103348732</t>
+    <t xml:space="preserve">0.339311122894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160560131073</t>
+    <t xml:space="preserve">0.353160530328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235811710358</t>
+    <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386344671249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612248420715</t>
+    <t xml:space="preserve">0.311612218618393</t>
   </si>
   <si>
     <t xml:space="preserve">0.314382135868073</t>
@@ -923,70 +920,73 @@
     <t xml:space="preserve">0.290838062763214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984386920929</t>
+    <t xml:space="preserve">0.258984357118607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373569250107</t>
+    <t xml:space="preserve">0.278373658657074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
     <t xml:space="preserve">0.272833853960037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754214763641</t>
+    <t xml:space="preserve">0.261754304170609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289780855179</t>
+    <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750005960464</t>
+    <t xml:space="preserve">0.249289765954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298347473145</t>
+    <t xml:space="preserve">0.243750020861626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683261394501</t>
+    <t xml:space="preserve">0.285298317670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448910236359</t>
+    <t xml:space="preserve">0.286683231592178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279758542776108</t>
+    <t xml:space="preserve">0.271448880434036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279758512973785</t>
   </si>
   <si>
     <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992923736572</t>
+    <t xml:space="preserve">0.294992953538895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302556276321</t>
+    <t xml:space="preserve">0.303302586078644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842390775681</t>
+    <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926149368286</t>
+    <t xml:space="preserve">0.337926179170609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461655855179</t>
+    <t xml:space="preserve">0.325461715459824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921940565109</t>
+    <t xml:space="preserve">0.319921910762787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465924263</t>
+    <t xml:space="preserve">0.343465894460678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547563552856</t>
+    <t xml:space="preserve">0.363547623157501</t>
   </si>
   <si>
     <t xml:space="preserve">0.377397060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231573104858</t>
+    <t xml:space="preserve">0.328231483697891</t>
   </si>
   <si>
     <t xml:space="preserve">0.331001460552216</t>
@@ -995,34 +995,34 @@
     <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698185920715</t>
+    <t xml:space="preserve">0.349698215723038</t>
   </si>
   <si>
     <t xml:space="preserve">0.344850867986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691768407822</t>
+    <t xml:space="preserve">0.322691798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3240767121315</t>
+    <t xml:space="preserve">0.324076741933823</t>
   </si>
   <si>
     <t xml:space="preserve">0.321306794881821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536967039108</t>
+    <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072443723679</t>
+    <t xml:space="preserve">0.306072473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317151993513107</t>
+    <t xml:space="preserve">0.317152053117752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3046875</t>
+    <t xml:space="preserve">0.304687559604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762811183929</t>
+    <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
     <t xml:space="preserve">0.283913373947144</t>
@@ -1031,28 +1031,28 @@
     <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524132013321</t>
+    <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294079065323</t>
+    <t xml:space="preserve">0.267294019460678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369300842285</t>
+    <t xml:space="preserve">0.26036936044693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909135341644</t>
+    <t xml:space="preserve">0.265909075737</t>
   </si>
   <si>
     <t xml:space="preserve">0.270063906908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988655328751</t>
+    <t xml:space="preserve">0.276988685131073</t>
   </si>
   <si>
     <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377867460251</t>
+    <t xml:space="preserve">0.296377837657928</t>
   </si>
   <si>
     <t xml:space="preserve">0.289453148841858</t>
@@ -1061,55 +1061,55 @@
     <t xml:space="preserve">0.429810017347336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647831916809</t>
+    <t xml:space="preserve">0.399647891521454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337016105652</t>
+    <t xml:space="preserve">0.388337045907974</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36194521188736</t>
+    <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
     <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453328609467</t>
+    <t xml:space="preserve">0.363453388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796551704407</t>
+    <t xml:space="preserve">0.380796521902084</t>
   </si>
   <si>
     <t xml:space="preserve">0.37401008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961475133896</t>
+    <t xml:space="preserve">0.364961415529251</t>
   </si>
   <si>
     <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847960233688</t>
+    <t xml:space="preserve">0.343847990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339932918549</t>
+    <t xml:space="preserve">0.342339903116226</t>
   </si>
   <si>
     <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.35289666056633</t>
   </si>
   <si>
     <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388484239578</t>
+    <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307466030121</t>
+    <t xml:space="preserve">0.336307436227798</t>
   </si>
   <si>
     <t xml:space="preserve">0.334799349308014</t>
@@ -1118,46 +1118,46 @@
     <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350451946259</t>
+    <t xml:space="preserve">0.437350541353226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958707332611</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
     <t xml:space="preserve">0.452431589365005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444890975952148</t>
+    <t xml:space="preserve">0.444891035556793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120803356171</t>
+    <t xml:space="preserve">0.441120684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728909730911</t>
+    <t xml:space="preserve">0.414728969335556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418153524399</t>
+    <t xml:space="preserve">0.403418123722076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107278108597</t>
+    <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566843509674</t>
+    <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877540111542</t>
+    <t xml:space="preserve">0.395877629518509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188415527344</t>
+    <t xml:space="preserve">0.407188385725021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501999139786</t>
+    <t xml:space="preserve">0.372501969337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469532251358</t>
+    <t xml:space="preserve">0.36646956205368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404717683792</t>
+    <t xml:space="preserve">0.354404747486115</t>
   </si>
   <si>
     <t xml:space="preserve">0.345356076955795</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36043718457222</t>
+    <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977648973465</t>
+    <t xml:space="preserve">0.367977678775787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929038047791</t>
+    <t xml:space="preserve">0.358928978443146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31670206785202</t>
+    <t xml:space="preserve">0.316702097654343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112962722778</t>
+    <t xml:space="preserve">0.300112903118134</t>
   </si>
   <si>
     <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31821021437645</t>
+    <t xml:space="preserve">0.318210184574127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718271493912</t>
+    <t xml:space="preserve">0.319718331098557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324242651462555</t>
+    <t xml:space="preserve">0.32424259185791</t>
   </si>
   <si>
     <t xml:space="preserve">0.327258795499802</t>
@@ -1208,52 +1208,52 @@
     <t xml:space="preserve">0.337815552949905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766942024231</t>
+    <t xml:space="preserve">0.328766882419586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30916154384613</t>
+    <t xml:space="preserve">0.309161573648453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653397321701</t>
+    <t xml:space="preserve">0.307653427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129136562347</t>
+    <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685923814774</t>
+    <t xml:space="preserve">0.313685894012451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734475135803</t>
+    <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599177360535</t>
+    <t xml:space="preserve">0.317599207162857</t>
   </si>
   <si>
     <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314439028501511</t>
+    <t xml:space="preserve">0.314438968896866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319179326295853</t>
+    <t xml:space="preserve">0.319179266691208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820011138916</t>
+    <t xml:space="preserve">0.331820040941238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400160074234</t>
+    <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
     <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32391956448555</t>
+    <t xml:space="preserve">0.323919594287872</t>
   </si>
   <si>
     <t xml:space="preserve">0.312858879566193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378343582153</t>
+    <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
     <t xml:space="preserve">0.292317658662796</t>
@@ -1265,109 +1265,109 @@
     <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218164920807</t>
+    <t xml:space="preserve">0.300218135118484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298637986183167</t>
+    <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737569332123</t>
+    <t xml:space="preserve">0.2907375395298</t>
   </si>
   <si>
     <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577390670776</t>
+    <t xml:space="preserve">0.287577331066132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676884412766</t>
+    <t xml:space="preserve">0.279676854610443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516705751419</t>
+    <t xml:space="preserve">0.276516675949097</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096795082092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196288824081</t>
+    <t xml:space="preserve">0.270196318626404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257003545761</t>
+    <t xml:space="preserve">0.281256973743439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776467561722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417152404785</t>
+    <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997241735458</t>
+    <t xml:space="preserve">0.285997301340103</t>
   </si>
   <si>
     <t xml:space="preserve">0.295477837324142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057896852493</t>
+    <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118581771851</t>
+    <t xml:space="preserve">0.308118611574173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157450199127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040904521942</t>
+    <t xml:space="preserve">0.346040934324265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140398263931</t>
+    <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720487594604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3413006067276</t>
+    <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980249404907</t>
+    <t xml:space="preserve">0.33498027920723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560398340225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.352361261844635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359313488007</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944712400436</t>
+    <t xml:space="preserve">0.291944742202759</t>
   </si>
   <si>
     <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115659236908</t>
+    <t xml:space="preserve">0.285115629434586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822885274887</t>
+    <t xml:space="preserve">0.286822855472565</t>
   </si>
   <si>
     <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298773854970932</t>
+    <t xml:space="preserve">0.29877382516861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408343791962</t>
+    <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
     <t xml:space="preserve">0.27828648686409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288530170917511</t>
+    <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993802309036</t>
+    <t xml:space="preserve">0.279993832111359</t>
   </si>
   <si>
     <t xml:space="preserve">0.273164659738541</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">0.276579201221466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750118255615</t>
+    <t xml:space="preserve">0.269750088453293</t>
   </si>
   <si>
     <t xml:space="preserve">0.28170108795166</t>
@@ -1385,43 +1385,43 @@
     <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457344293594</t>
+    <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042802810669</t>
+    <t xml:space="preserve">0.268042832612991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895682096481</t>
+    <t xml:space="preserve">0.303895711898804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293652057647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188396453857</t>
+    <t xml:space="preserve">0.302188366651535</t>
   </si>
   <si>
     <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310223579407</t>
+    <t xml:space="preserve">0.307310253381729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383050203323</t>
+    <t xml:space="preserve">0.324383020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261193275452</t>
+    <t xml:space="preserve">0.319261163473129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017479419708</t>
+    <t xml:space="preserve">0.309017568826675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139366149902</t>
+    <t xml:space="preserve">0.31413933634758</t>
   </si>
   <si>
     <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724854469299</t>
+    <t xml:space="preserve">0.310724765062332</t>
   </si>
   <si>
     <t xml:space="preserve">0.310288995504379</t>
@@ -1430,28 +1430,28 @@
     <t xml:space="preserve">0.299829810857773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343415975571</t>
+    <t xml:space="preserve">0.296343445777893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316235542297</t>
+    <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
     <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28762748837471</t>
+    <t xml:space="preserve">0.287627458572388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086613416672</t>
+    <t xml:space="preserve">0.298086643218994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560336828232</t>
+    <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304652392864227</t>
+    <t xml:space="preserve">0.304652363061905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302870810031891</t>
+    <t xml:space="preserve">0.302870839834213</t>
   </si>
   <si>
     <t xml:space="preserve">0.306434005498886</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307614564896</t>
+    <t xml:space="preserve">0.299307644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962866067886</t>
+    <t xml:space="preserve">0.293962836265564</t>
   </si>
   <si>
     <t xml:space="preserve">0.285054892301559</t>
@@ -1481,31 +1481,31 @@
     <t xml:space="preserve">0.283273279666901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279710084199905</t>
+    <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491696834564</t>
+    <t xml:space="preserve">0.281491756439209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29218128323555</t>
+    <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295371979475021</t>
+    <t xml:space="preserve">0.295372009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902150630951</t>
   </si>
   <si>
     <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291725426912308</t>
+    <t xml:space="preserve">0.291725397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304488450288773</t>
+    <t xml:space="preserve">0.304488390684128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308134973049164</t>
+    <t xml:space="preserve">0.308134943246841</t>
   </si>
   <si>
     <t xml:space="preserve">0.3117815554142</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">0.317251414060593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191131353378</t>
+    <t xml:space="preserve">0.328191101551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.33183765411377</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897936820984</t>
+    <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32454451918602</t>
+    <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158161878586</t>
+    <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
@@ -1544,91 +1544,91 @@
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610083580017</t>
+    <t xml:space="preserve">0.331610113382339</t>
   </si>
   <si>
     <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432245731354</t>
+    <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117351055145</t>
+    <t xml:space="preserve">0.311117321252823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309254318475723</t>
+    <t xml:space="preserve">0.309254348278046</t>
   </si>
   <si>
     <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316706240177155</t>
+    <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
     <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340925008058548</t>
+    <t xml:space="preserve">0.340924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473086357117</t>
+    <t xml:space="preserve">0.333473056554794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391405105591</t>
+    <t xml:space="preserve">0.307391375303268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353965818881989</t>
+    <t xml:space="preserve">0.353965848684311</t>
   </si>
   <si>
     <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199002504349</t>
+    <t xml:space="preserve">0.337199032306671</t>
   </si>
   <si>
     <t xml:space="preserve">0.348376929759979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732635259628</t>
+    <t xml:space="preserve">0.370732605457306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677319288254</t>
+    <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170051813126</t>
+    <t xml:space="preserve">0.419170022010803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40799218416214</t>
+    <t xml:space="preserve">0.407992154359818</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409855157136917</t>
+    <t xml:space="preserve">0.40985518693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540262460709</t>
+    <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
     <t xml:space="preserve">0.391225397586823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3930883705616</t>
+    <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
     <t xml:space="preserve">0.389362424612045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458581209183</t>
+    <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376321583986282</t>
+    <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372595608234406</t>
+    <t xml:space="preserve">0.372595638036728</t>
   </si>
   <si>
     <t xml:space="preserve">0.363280713558197</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869692087173</t>
+    <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378184527158737</t>
+    <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951373338699</t>
+    <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">0.392482101917267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394378155469894</t>
+    <t xml:space="preserve">0.394378125667572</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170202970505</t>
+    <t xml:space="preserve">0.398170232772827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274209022522</t>
+    <t xml:space="preserve">0.396274149417877</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097760915756</t>
+    <t xml:space="preserve">0.409097731113434</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605693340302</t>
+    <t xml:space="preserve">0.422605663537979</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -26194,7 +26194,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26220,7 +26220,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26246,7 +26246,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26272,7 +26272,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26298,7 +26298,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26324,7 +26324,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26350,7 +26350,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26376,7 +26376,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26402,7 +26402,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26428,7 +26428,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26454,7 +26454,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26480,7 +26480,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26506,7 +26506,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26532,7 +26532,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26558,7 +26558,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26584,7 +26584,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26636,7 +26636,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26662,7 +26662,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26688,7 +26688,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26714,7 +26714,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26740,7 +26740,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26766,7 +26766,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26792,7 +26792,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26818,7 +26818,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26844,7 +26844,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26870,7 +26870,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26896,7 +26896,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26922,7 +26922,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26948,7 +26948,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26974,7 +26974,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27000,7 +27000,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27026,7 +27026,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27052,7 +27052,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27078,7 +27078,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27104,7 +27104,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27182,7 +27182,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27260,7 +27260,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27286,7 +27286,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27338,7 +27338,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27364,7 +27364,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27390,7 +27390,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27416,7 +27416,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27572,7 +27572,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27598,7 +27598,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27624,7 +27624,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27702,7 +27702,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27728,7 +27728,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28144,7 +28144,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28170,7 +28170,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28196,7 +28196,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28222,7 +28222,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28248,7 +28248,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28274,7 +28274,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28300,7 +28300,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28326,7 +28326,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28352,7 +28352,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28404,7 +28404,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28430,7 +28430,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28456,7 +28456,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28482,7 +28482,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28508,7 +28508,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28534,7 +28534,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28560,7 +28560,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28586,7 +28586,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28612,7 +28612,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28638,7 +28638,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28664,7 +28664,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28742,7 +28742,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28768,7 +28768,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28794,7 +28794,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28820,7 +28820,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28846,7 +28846,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28872,7 +28872,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28898,7 +28898,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28924,7 +28924,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28950,7 +28950,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28976,7 +28976,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29002,7 +29002,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29028,7 +29028,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29054,7 +29054,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29080,7 +29080,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29106,7 +29106,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29132,7 +29132,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29158,7 +29158,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29184,7 +29184,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29210,7 +29210,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29236,7 +29236,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29262,7 +29262,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29366,7 +29366,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29418,7 +29418,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29496,7 +29496,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29522,7 +29522,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29548,7 +29548,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29574,7 +29574,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29600,7 +29600,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29626,7 +29626,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29652,7 +29652,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29678,7 +29678,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29704,7 +29704,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29730,7 +29730,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29756,7 +29756,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29782,7 +29782,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29808,7 +29808,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29834,7 +29834,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29860,7 +29860,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29886,7 +29886,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29912,7 +29912,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29938,7 +29938,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29964,7 +29964,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30146,7 +30146,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30276,7 +30276,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30302,7 +30302,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30328,7 +30328,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30380,7 +30380,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30406,7 +30406,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30484,7 +30484,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30874,7 +30874,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30900,7 +30900,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31004,7 +31004,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31056,7 +31056,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31082,7 +31082,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31108,7 +31108,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31212,7 +31212,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31238,7 +31238,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31264,7 +31264,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31316,7 +31316,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31342,7 +31342,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31368,7 +31368,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31394,7 +31394,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31420,7 +31420,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31446,7 +31446,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31472,7 +31472,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31498,7 +31498,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31524,7 +31524,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31550,7 +31550,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31576,7 +31576,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31602,7 +31602,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31628,7 +31628,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31654,7 +31654,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31680,7 +31680,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31706,7 +31706,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31732,7 +31732,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31758,7 +31758,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31784,7 +31784,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31810,7 +31810,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31836,7 +31836,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31862,7 +31862,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31888,7 +31888,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31914,7 +31914,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31940,7 +31940,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31966,7 +31966,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31992,7 +31992,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32044,7 +32044,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32070,7 +32070,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32096,7 +32096,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32148,7 +32148,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32330,7 +32330,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32356,7 +32356,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32382,7 +32382,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32408,7 +32408,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32746,7 +32746,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33240,7 +33240,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34280,7 +34280,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34488,7 +34488,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34514,7 +34514,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35008,7 +35008,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35658,7 +35658,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35736,7 +35736,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35762,7 +35762,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35788,7 +35788,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35814,7 +35814,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35866,7 +35866,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35892,7 +35892,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35918,7 +35918,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35970,7 +35970,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35996,7 +35996,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36022,7 +36022,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36048,7 +36048,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36074,7 +36074,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36100,7 +36100,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36126,7 +36126,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36152,7 +36152,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36178,7 +36178,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -69128,7 +69128,7 @@
     </row>
     <row r="2578">
       <c r="A2578" s="1" t="n">
-        <v>46076.5939351852</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B2578" t="n">
         <v>4000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994336605072</t>
+    <t xml:space="preserve">0.175994351506233</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17662288248539</t>
+    <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851592302322</t>
+    <t xml:space="preserve">0.1728515625</t>
   </si>
   <si>
     <t xml:space="preserve">0.171594500541687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051875472069</t>
+    <t xml:space="preserve">0.164051860570908</t>
   </si>
   <si>
     <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966640233994</t>
+    <t xml:space="preserve">0.148966655135155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309697508812</t>
+    <t xml:space="preserve">0.143309682607651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783760309219</t>
+    <t xml:space="preserve">0.149783745408058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195320248604</t>
+    <t xml:space="preserve">0.145195350050926</t>
   </si>
   <si>
     <t xml:space="preserve">0.152737945318222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15336649119854</t>
+    <t xml:space="preserve">0.153366521000862</t>
   </si>
   <si>
     <t xml:space="preserve">0.150789424777031</t>
@@ -83,46 +83,46 @@
     <t xml:space="preserve">0.146452412009239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852628111839</t>
+    <t xml:space="preserve">0.139852643013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538362622261</t>
+    <t xml:space="preserve">0.139538377523422</t>
   </si>
   <si>
     <t xml:space="preserve">0.139915496110916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052561044693</t>
+    <t xml:space="preserve">0.142052546143532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138909831643105</t>
+    <t xml:space="preserve">0.138909816741943</t>
   </si>
   <si>
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337378978729</t>
+    <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817486286163</t>
+    <t xml:space="preserve">0.166817456483841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423284888268</t>
+    <t xml:space="preserve">0.163423299789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137811183929</t>
+    <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623582959175</t>
+    <t xml:space="preserve">0.154623597860336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595186114311</t>
+    <t xml:space="preserve">0.149595201015472</t>
   </si>
   <si>
     <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909116268158</t>
+    <t xml:space="preserve">0.160909131169319</t>
   </si>
   <si>
     <t xml:space="preserve">0.158960580825806</t>
@@ -134,31 +134,31 @@
     <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170965909957886</t>
+    <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937528014183</t>
+    <t xml:space="preserve">0.165937513113022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565373420715</t>
+    <t xml:space="preserve">0.188565343618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650929093361</t>
+    <t xml:space="preserve">0.192650943994522</t>
   </si>
   <si>
     <t xml:space="preserve">0.191708147525787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184165522456169</t>
+    <t xml:space="preserve">0.184165507555008</t>
   </si>
   <si>
     <t xml:space="preserve">0.181651294231415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136395335197</t>
+    <t xml:space="preserve">0.201136365532875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678975701332</t>
+    <t xml:space="preserve">0.208678960800171</t>
   </si>
   <si>
     <t xml:space="preserve">0.201073557138443</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">0.196736499667168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222286343575</t>
+    <t xml:space="preserve">0.194222301244736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17913706600666</t>
+    <t xml:space="preserve">0.179137080907822</t>
   </si>
   <si>
     <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834524393082</t>
+    <t xml:space="preserve">0.169834539294243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451711535454</t>
+    <t xml:space="preserve">0.168451696634293</t>
   </si>
   <si>
     <t xml:space="preserve">0.162794768810272</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">0.16656605899334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074928283691</t>
+    <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152109369635582</t>
+    <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
     <t xml:space="preserve">0.153995037078857</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051174998283</t>
+    <t xml:space="preserve">0.186051145195961</t>
   </si>
   <si>
     <t xml:space="preserve">0.187936782836914</t>
@@ -215,91 +215,91 @@
     <t xml:space="preserve">0.18171414732933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194604873657</t>
+    <t xml:space="preserve">0.167194619774818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16028057038784</t>
+    <t xml:space="preserve">0.160280555486679</t>
   </si>
   <si>
     <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480853557587</t>
+    <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
     <t xml:space="preserve">0.148338064551353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566759467125</t>
+    <t xml:space="preserve">0.144566789269447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394888043404</t>
+    <t xml:space="preserve">0.158394902944565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183275938034</t>
+    <t xml:space="preserve">0.165183261036873</t>
   </si>
   <si>
     <t xml:space="preserve">0.170651644468307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223001718521</t>
+    <t xml:space="preserve">0.17222298681736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594105601311</t>
+    <t xml:space="preserve">0.18259409070015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507804751396</t>
+    <t xml:space="preserve">0.20050784945488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593800067902</t>
+    <t xml:space="preserve">0.193593770265579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17813141644001</t>
+    <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010659337044</t>
+    <t xml:space="preserve">0.201010644435883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850876927376</t>
+    <t xml:space="preserve">0.194850847125053</t>
   </si>
   <si>
     <t xml:space="preserve">0.191770970821381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879229068756</t>
+    <t xml:space="preserve">0.199879243969917</t>
   </si>
   <si>
     <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787293553352</t>
+    <t xml:space="preserve">0.216787308454514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563927769661</t>
+    <t xml:space="preserve">0.2325639128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220915198326</t>
+    <t xml:space="preserve">0.238220885396004</t>
   </si>
   <si>
     <t xml:space="preserve">0.251420497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267134219408035</t>
+    <t xml:space="preserve">0.267134308815002</t>
   </si>
   <si>
     <t xml:space="preserve">0.275305390357971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290390640497208</t>
+    <t xml:space="preserve">0.290390700101852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561781644821</t>
+    <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257706046104431</t>
+    <t xml:space="preserve">0.257705986499786</t>
   </si>
   <si>
     <t xml:space="preserve">0.260157346725464</t>
@@ -308,79 +308,79 @@
     <t xml:space="preserve">0.250226199626923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163346529007</t>
+    <t xml:space="preserve">0.250163316726685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809370160103</t>
+    <t xml:space="preserve">0.242809325456619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24324931204319</t>
+    <t xml:space="preserve">0.243249297142029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24337500333786</t>
+    <t xml:space="preserve">0.243375033140182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421213269234</t>
+    <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821049332619</t>
+    <t xml:space="preserve">0.233821019530296</t>
   </si>
   <si>
     <t xml:space="preserve">0.210564643144608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20691904425621</t>
+    <t xml:space="preserve">0.206919074058533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821749806404</t>
+    <t xml:space="preserve">0.211821734905243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741813898087</t>
+    <t xml:space="preserve">0.208741873502731</t>
   </si>
   <si>
     <t xml:space="preserve">0.237592354416847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134949684143</t>
+    <t xml:space="preserve">0.245134994387627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803966522217</t>
+    <t xml:space="preserve">0.230803951621056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535530924797</t>
+    <t xml:space="preserve">0.227535516023636</t>
   </si>
   <si>
     <t xml:space="preserve">0.235706657171249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278454065323</t>
+    <t xml:space="preserve">0.226278439164162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135679960251</t>
+    <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
     <t xml:space="preserve">0.216850131750107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381383180618</t>
+    <t xml:space="preserve">0.222381427884102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2131417542696</t>
+    <t xml:space="preserve">0.213141724467278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199248433113</t>
+    <t xml:space="preserve">0.201199233531952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279154539108</t>
+    <t xml:space="preserve">0.204279124736786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20679335296154</t>
+    <t xml:space="preserve">0.206793367862701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164821982384</t>
+    <t xml:space="preserve">0.206164792180061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421898841858</t>
+    <t xml:space="preserve">0.207421869039536</t>
   </si>
   <si>
     <t xml:space="preserve">0.208804711699486</t>
@@ -389,55 +389,55 @@
     <t xml:space="preserve">0.211947456002235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649878382683</t>
+    <t xml:space="preserve">0.225649863481522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867199659348</t>
+    <t xml:space="preserve">0.219867184758186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810055732727</t>
+    <t xml:space="preserve">0.220810040831566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484021663666</t>
+    <t xml:space="preserve">0.229484036564827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386742115021</t>
+    <t xml:space="preserve">0.234386757016182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518477916718</t>
+    <t xml:space="preserve">0.224518448114395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21999292075634</t>
+    <t xml:space="preserve">0.219992846250534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741553068161</t>
+    <t xml:space="preserve">0.219741493463516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216912940144539</t>
+    <t xml:space="preserve">0.216913014650345</t>
   </si>
   <si>
     <t xml:space="preserve">0.231306865811348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038661241531</t>
+    <t xml:space="preserve">0.217038720846176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223324224352837</t>
+    <t xml:space="preserve">0.223324254155159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297179013490677</t>
+    <t xml:space="preserve">0.297178953886032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988673210144</t>
+    <t xml:space="preserve">0.351988703012466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127855539322</t>
+    <t xml:space="preserve">0.465127825737</t>
   </si>
   <si>
     <t xml:space="preserve">0.545582354068756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070361375809</t>
+    <t xml:space="preserve">0.477070331573486</t>
   </si>
   <si>
     <t xml:space="preserve">0.436843067407608</t>
@@ -446,37 +446,37 @@
     <t xml:space="preserve">0.422072112560272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987242460251</t>
+    <t xml:space="preserve">0.395987272262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.364559680223465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215236902237</t>
+    <t xml:space="preserve">0.414215177297592</t>
   </si>
   <si>
     <t xml:space="preserve">0.367388188838959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373988002538681</t>
+    <t xml:space="preserve">0.373987972736359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331715583801</t>
+    <t xml:space="preserve">0.346331685781479</t>
   </si>
   <si>
     <t xml:space="preserve">0.325903743505478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904183149338</t>
+    <t xml:space="preserve">0.314904153347015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532393693924</t>
+    <t xml:space="preserve">0.326532334089279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389209747314</t>
+    <t xml:space="preserve">0.334389239549637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818232536316</t>
+    <t xml:space="preserve">0.321818262338638</t>
   </si>
   <si>
     <t xml:space="preserve">0.348845899105072</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">0.341303288936615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846569776535</t>
+    <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361192941666</t>
+    <t xml:space="preserve">0.318361222743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189612150192</t>
+    <t xml:space="preserve">0.321189671754837</t>
   </si>
   <si>
     <t xml:space="preserve">0.333132117986679</t>
@@ -500,52 +500,52 @@
     <t xml:space="preserve">0.329989373683929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418366670609</t>
+    <t xml:space="preserve">0.317418336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332416057587</t>
+    <t xml:space="preserve">0.324332356452942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275622367859</t>
+    <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
     <t xml:space="preserve">0.311761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703534841537</t>
+    <t xml:space="preserve">0.334703505039215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046867847443</t>
+    <t xml:space="preserve">0.318046897649765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316789776086807</t>
+    <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328418016433716</t>
+    <t xml:space="preserve">0.328418046236038</t>
   </si>
   <si>
     <t xml:space="preserve">0.323075324296951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103750944138</t>
+    <t xml:space="preserve">0.328103721141815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704555749893</t>
+    <t xml:space="preserve">0.301704525947571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504227876663</t>
+    <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
     <t xml:space="preserve">0.311069965362549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561140775681</t>
+    <t xml:space="preserve">0.320561110973358</t>
   </si>
   <si>
     <t xml:space="preserve">0.325589537620544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274132013321</t>
+    <t xml:space="preserve">0.358274161815643</t>
   </si>
   <si>
     <t xml:space="preserve">0.339417666196823</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.340046226978302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319303959608078</t>
+    <t xml:space="preserve">0.319304019212723</t>
   </si>
   <si>
     <t xml:space="preserve">0.337846279144287</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701753854752</t>
+    <t xml:space="preserve">0.389701694250107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588106870651</t>
+    <t xml:space="preserve">0.369588047266006</t>
   </si>
   <si>
     <t xml:space="preserve">0.368959575891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370216637849808</t>
+    <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616853952408</t>
+    <t xml:space="preserve">0.36361688375473</t>
   </si>
   <si>
     <t xml:space="preserve">0.370845198631287</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788725376129</t>
+    <t xml:space="preserve">0.349788695573807</t>
   </si>
   <si>
     <t xml:space="preserve">0.354502856731415</t>
@@ -596,61 +596,61 @@
     <t xml:space="preserve">0.367073893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38875886797905</t>
+    <t xml:space="preserve">0.388758897781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587436199188</t>
+    <t xml:space="preserve">0.391587406396866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759277820587</t>
+    <t xml:space="preserve">0.377759248018265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130746841431</t>
+    <t xml:space="preserve">0.377130687236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187600135803</t>
+    <t xml:space="preserve">0.387187540531158</t>
   </si>
   <si>
     <t xml:space="preserve">0.377444952726364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929658889771</t>
+    <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843797683716</t>
+    <t xml:space="preserve">0.414843738079071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3922159075737</t>
+    <t xml:space="preserve">0.392215937376022</t>
   </si>
   <si>
     <t xml:space="preserve">0.37681645154953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386558949947357</t>
+    <t xml:space="preserve">0.386558920145035</t>
   </si>
   <si>
     <t xml:space="preserve">0.471413314342499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357310533524</t>
+    <t xml:space="preserve">0.439357191324234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556908130646</t>
+    <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
     <t xml:space="preserve">0.433700263500214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100248575211</t>
+    <t xml:space="preserve">0.438100218772888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271359920502</t>
+    <t xml:space="preserve">0.446271300315857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43998584151268</t>
+    <t xml:space="preserve">0.439985692501068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386437654495</t>
+    <t xml:space="preserve">0.42238637804985</t>
   </si>
   <si>
     <t xml:space="preserve">0.424900621175766</t>
@@ -662,82 +662,82 @@
     <t xml:space="preserve">0.409815341234207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044125556946</t>
+    <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558309078217</t>
+    <t xml:space="preserve">0.408558249473572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41358670592308</t>
+    <t xml:space="preserve">0.413586735725403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272790670395</t>
+    <t xml:space="preserve">0.40227273106575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443171739578</t>
+    <t xml:space="preserve">0.432443201541901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357951402664</t>
+    <t xml:space="preserve">0.417357921600342</t>
   </si>
   <si>
     <t xml:space="preserve">0.462613731622696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414804697037</t>
+    <t xml:space="preserve">0.427414774894714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758458137512</t>
+    <t xml:space="preserve">0.399758487939835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4186150431633</t>
+    <t xml:space="preserve">0.418615013360977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643499612808</t>
+    <t xml:space="preserve">0.423643469810486</t>
   </si>
   <si>
     <t xml:space="preserve">0.411072432994843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501485586166</t>
+    <t xml:space="preserve">0.398501425981522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786944389343</t>
+    <t xml:space="preserve">0.404786914587021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38215908408165</t>
+    <t xml:space="preserve">0.382159054279327</t>
   </si>
   <si>
     <t xml:space="preserve">0.383416295051575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444572687149</t>
+    <t xml:space="preserve">0.388444602489471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40352988243103</t>
+    <t xml:space="preserve">0.403529822826385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431186139583588</t>
+    <t xml:space="preserve">0.43118605017662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41987219452858</t>
+    <t xml:space="preserve">0.419872164726257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301127910614</t>
+    <t xml:space="preserve">0.407301187515259</t>
   </si>
   <si>
     <t xml:space="preserve">0.394730180501938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329643964767</t>
+    <t xml:space="preserve">0.412329584360123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015609502792</t>
+    <t xml:space="preserve">0.40101569890976</t>
   </si>
   <si>
     <t xml:space="preserve">0.416100859642029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045496702194</t>
+    <t xml:space="preserve">0.362045437097549</t>
   </si>
   <si>
     <t xml:space="preserve">0.3658167719841</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">0.36330258846283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674757957458</t>
+    <t xml:space="preserve">0.340674728155136</t>
   </si>
   <si>
     <t xml:space="preserve">0.329360812902451</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017070055008</t>
+    <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446003437042</t>
+    <t xml:space="preserve">0.34444597363472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903423070908</t>
+    <t xml:space="preserve">0.336903393268585</t>
   </si>
   <si>
     <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703184604645</t>
+    <t xml:space="preserve">0.345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102349996567</t>
+    <t xml:space="preserve">0.372102290391922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930418968201</t>
+    <t xml:space="preserve">0.385930448770523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245764970779</t>
+    <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788404941559</t>
+    <t xml:space="preserve">0.360788375139236</t>
   </si>
   <si>
     <t xml:space="preserve">0.378387808799744</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">0.375873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359352350235</t>
+    <t xml:space="preserve">0.373359382152557</t>
   </si>
   <si>
     <t xml:space="preserve">0.384673297405243</t>
@@ -800,61 +800,61 @@
     <t xml:space="preserve">0.393472999334335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272000789642</t>
+    <t xml:space="preserve">0.424272030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557608604431</t>
+    <t xml:space="preserve">0.430557548999786</t>
   </si>
   <si>
     <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699652433395</t>
+    <t xml:space="preserve">0.455699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955998420715</t>
+    <t xml:space="preserve">0.463955968618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181812763214</t>
+    <t xml:space="preserve">0.443181872367859</t>
   </si>
   <si>
     <t xml:space="preserve">0.429332405328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415483027696609</t>
+    <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42587012052536</t>
+    <t xml:space="preserve">0.425870090723038</t>
   </si>
   <si>
     <t xml:space="preserve">0.436257123947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719438552856</t>
+    <t xml:space="preserve">0.439719408750534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794809341431</t>
+    <t xml:space="preserve">0.432794719934464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4189453125</t>
+    <t xml:space="preserve">0.41894543170929</t>
   </si>
   <si>
     <t xml:space="preserve">0.401633530855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020593881607</t>
+    <t xml:space="preserve">0.412020683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784123420715</t>
+    <t xml:space="preserve">0.387784093618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246497631073</t>
+    <t xml:space="preserve">0.391246467828751</t>
   </si>
   <si>
     <t xml:space="preserve">0.405095905065536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422407776117325</t>
+    <t xml:space="preserve">0.42240771651268</t>
   </si>
   <si>
     <t xml:space="preserve">0.446644186973572</t>
@@ -866,85 +866,85 @@
     <t xml:space="preserve">0.450106590986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031309604645</t>
+    <t xml:space="preserve">0.457031220197678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568905591965</t>
+    <t xml:space="preserve">0.453568935394287</t>
   </si>
   <si>
     <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708782434464</t>
+    <t xml:space="preserve">0.394708812236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859404802322</t>
+    <t xml:space="preserve">0.380859434604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934715986252</t>
+    <t xml:space="preserve">0.373934686183929</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085248947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472341775894</t>
+    <t xml:space="preserve">0.370472371578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384321749210358</t>
+    <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009967565536</t>
+    <t xml:space="preserve">0.367010027170181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696066617966</t>
+    <t xml:space="preserve">0.340696007013321</t>
   </si>
   <si>
     <t xml:space="preserve">0.339311093091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353160530328751</t>
+    <t xml:space="preserve">0.353160470724106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34623584151268</t>
+    <t xml:space="preserve">0.346235811710358</t>
   </si>
   <si>
     <t xml:space="preserve">0.332386374473572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612218618393</t>
+    <t xml:space="preserve">0.311612248420715</t>
   </si>
   <si>
     <t xml:space="preserve">0.31438210606575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838092565536</t>
+    <t xml:space="preserve">0.290838122367859</t>
   </si>
   <si>
     <t xml:space="preserve">0.258984386920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373569250107</t>
+    <t xml:space="preserve">0.278373658657074</t>
   </si>
   <si>
     <t xml:space="preserve">0.263139218091965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.272833794355392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754244565964</t>
+    <t xml:space="preserve">0.261754274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289780855179</t>
+    <t xml:space="preserve">0.249289825558662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243750050663948</t>
+    <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
     <t xml:space="preserve">0.285298317670822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683291196823</t>
+    <t xml:space="preserve">0.286683231592178</t>
   </si>
   <si>
     <t xml:space="preserve">0.271448880434036</t>
@@ -959,52 +959,52 @@
     <t xml:space="preserve">0.294992953538895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302556276321</t>
+    <t xml:space="preserve">0.303302586078644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842301368713</t>
+    <t xml:space="preserve">0.308842360973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926149368286</t>
+    <t xml:space="preserve">0.337926179170609</t>
   </si>
   <si>
     <t xml:space="preserve">0.325461685657501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921851158142</t>
+    <t xml:space="preserve">0.319921880960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465924263</t>
+    <t xml:space="preserve">0.343465954065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547593355179</t>
+    <t xml:space="preserve">0.363547563552856</t>
   </si>
   <si>
     <t xml:space="preserve">0.377397090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231573104858</t>
+    <t xml:space="preserve">0.328231602907181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331001400947571</t>
+    <t xml:space="preserve">0.331001430749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33654123544693</t>
+    <t xml:space="preserve">0.336541205644608</t>
   </si>
   <si>
     <t xml:space="preserve">0.349698156118393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850897789001</t>
+    <t xml:space="preserve">0.344850838184357</t>
   </si>
   <si>
     <t xml:space="preserve">0.322691798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3240767121315</t>
+    <t xml:space="preserve">0.324076682329178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306854486465</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
     <t xml:space="preserve">0.318536967039108</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">0.306072473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31715202331543</t>
+    <t xml:space="preserve">0.317151993513107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687559604645</t>
+    <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762811183929</t>
+    <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
     <t xml:space="preserve">0.283913373947144</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524191617966</t>
+    <t xml:space="preserve">0.264524161815643</t>
   </si>
   <si>
     <t xml:space="preserve">0.267294079065323</t>
@@ -1040,58 +1040,58 @@
     <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063936710358</t>
+    <t xml:space="preserve">0.27006396651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988655328751</t>
+    <t xml:space="preserve">0.276988625526428</t>
   </si>
   <si>
     <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296377837657928</t>
+    <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
     <t xml:space="preserve">0.289453148841858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809957742691</t>
+    <t xml:space="preserve">0.429809987545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647831916809</t>
+    <t xml:space="preserve">0.399647861719131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337045907974</t>
+    <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026319503784</t>
+    <t xml:space="preserve">0.377026289701462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945241689682</t>
+    <t xml:space="preserve">0.361945271492004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36948573589325</t>
+    <t xml:space="preserve">0.369485795497894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453358411789</t>
+    <t xml:space="preserve">0.363453298807144</t>
   </si>
   <si>
     <t xml:space="preserve">0.380796521902084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374010056257248</t>
+    <t xml:space="preserve">0.37401008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961475133896</t>
+    <t xml:space="preserve">0.364961445331573</t>
   </si>
   <si>
     <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847990036011</t>
+    <t xml:space="preserve">0.343848019838333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339843511581</t>
+    <t xml:space="preserve">0.342339873313904</t>
   </si>
   <si>
     <t xml:space="preserve">0.33932363986969</t>
@@ -1100,28 +1100,28 @@
     <t xml:space="preserve">0.352896571159363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864193677902</t>
+    <t xml:space="preserve">0.346864223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351388543844223</t>
+    <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307406425476</t>
+    <t xml:space="preserve">0.336307436227798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799379110336</t>
+    <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
     <t xml:space="preserve">0.348372280597687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350451946259</t>
+    <t xml:space="preserve">0.437350481748581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958707332611</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431589365005</t>
+    <t xml:space="preserve">0.452431529760361</t>
   </si>
   <si>
     <t xml:space="preserve">0.444891065359116</t>
@@ -1133,85 +1133,85 @@
     <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418183326721</t>
+    <t xml:space="preserve">0.403418153524399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107367515564</t>
+    <t xml:space="preserve">0.392107337713242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566813707352</t>
+    <t xml:space="preserve">0.384566783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395877569913864</t>
+    <t xml:space="preserve">0.395877540111542</t>
   </si>
   <si>
     <t xml:space="preserve">0.407188415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501969337463</t>
+    <t xml:space="preserve">0.372501999139786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469591856003</t>
+    <t xml:space="preserve">0.36646956205368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404717683792</t>
+    <t xml:space="preserve">0.354404747486115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356106758118</t>
+    <t xml:space="preserve">0.34535613656044</t>
   </si>
   <si>
     <t xml:space="preserve">0.340831786394119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993912220001</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
     <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367977678775787</t>
+    <t xml:space="preserve">0.367977648973465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358929067850113</t>
+    <t xml:space="preserve">0.358929038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316702097654343</t>
+    <t xml:space="preserve">0.31670206785202</t>
   </si>
   <si>
     <t xml:space="preserve">0.300112903118134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30162101984024</t>
+    <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318210184574127</t>
+    <t xml:space="preserve">0.31821021437645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319718301296234</t>
+    <t xml:space="preserve">0.319718271493912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324242621660233</t>
+    <t xml:space="preserve">0.32424259185791</t>
   </si>
   <si>
     <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330275028944016</t>
+    <t xml:space="preserve">0.330274999141693</t>
   </si>
   <si>
     <t xml:space="preserve">0.331783145666122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33781561255455</t>
+    <t xml:space="preserve">0.337815552949905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766912221909</t>
+    <t xml:space="preserve">0.328766942024231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30916154384613</t>
+    <t xml:space="preserve">0.309161573648453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653486728668</t>
+    <t xml:space="preserve">0.307653397321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.303129136562347</t>
@@ -1220,40 +1220,40 @@
     <t xml:space="preserve">0.313685864210129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734504938126</t>
+    <t xml:space="preserve">0.322734475135803</t>
   </si>
   <si>
     <t xml:space="preserve">0.317599207162857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322339475154877</t>
+    <t xml:space="preserve">0.322339415550232</t>
   </si>
   <si>
     <t xml:space="preserve">0.314438998699188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319179326295853</t>
+    <t xml:space="preserve">0.31917929649353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331820040941238</t>
+    <t xml:space="preserve">0.331820011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400130271912</t>
+    <t xml:space="preserve">0.333400100469589</t>
   </si>
   <si>
     <t xml:space="preserve">0.320759385824203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32391956448555</t>
+    <t xml:space="preserve">0.323919594287872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858879566193</t>
+    <t xml:space="preserve">0.312858939170837</t>
   </si>
   <si>
     <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317658662796</t>
+    <t xml:space="preserve">0.292317688465118</t>
   </si>
   <si>
     <t xml:space="preserve">0.30179825425148</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218135118484</t>
+    <t xml:space="preserve">0.300218164920807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298638015985489</t>
+    <t xml:space="preserve">0.298637986183167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737599134445</t>
+    <t xml:space="preserve">0.290737569332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282837092876434</t>
+    <t xml:space="preserve">0.282837122678757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577390670776</t>
+    <t xml:space="preserve">0.287577360868454</t>
   </si>
   <si>
     <t xml:space="preserve">0.279676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516646146774</t>
+    <t xml:space="preserve">0.276516675949097</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096795082092</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">0.281257003545761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776437759399</t>
+    <t xml:space="preserve">0.271776407957077</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997301340103</t>
+    <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295477837324142</t>
+    <t xml:space="preserve">0.295477867126465</t>
   </si>
   <si>
     <t xml:space="preserve">0.297057956457138</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040904521942</t>
+    <t xml:space="preserve">0.34604087471962</t>
   </si>
   <si>
     <t xml:space="preserve">0.338140428066254</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">0.3413006067276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334980219602585</t>
+    <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
     <t xml:space="preserve">0.33656033873558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361261844635</t>
+    <t xml:space="preserve">0.35236132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359313488007</t>
+    <t xml:space="preserve">0.295359253883362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944742202759</t>
+    <t xml:space="preserve">0.291944712400436</t>
   </si>
   <si>
     <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285115599632263</t>
+    <t xml:space="preserve">0.285115629434586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286822915077209</t>
+    <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481110811234</t>
+    <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298773854970932</t>
+    <t xml:space="preserve">0.29877382516861</t>
   </si>
   <si>
     <t xml:space="preserve">0.283408313989639</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">0.278286516666412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288530141115189</t>
+    <t xml:space="preserve">0.288530200719833</t>
   </si>
   <si>
     <t xml:space="preserve">0.279993772506714</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750148057938</t>
+    <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
     <t xml:space="preserve">0.281701058149338</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">0.274871975183487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457374095917</t>
+    <t xml:space="preserve">0.271457403898239</t>
   </si>
   <si>
     <t xml:space="preserve">0.268042832612991</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293652057647705</t>
+    <t xml:space="preserve">0.29365199804306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188456058502</t>
+    <t xml:space="preserve">0.30218842625618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602937936783</t>
+    <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
     <t xml:space="preserve">0.307310253381729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383109807968</t>
+    <t xml:space="preserve">0.324383050203323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319261193275452</t>
+    <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
     <t xml:space="preserve">0.309017509222031</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">0.314139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432080507278</t>
+    <t xml:space="preserve">0.312432110309601</t>
   </si>
   <si>
     <t xml:space="preserve">0.310724794864655</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">0.310288995504379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829840660095</t>
+    <t xml:space="preserve">0.299829810857773</t>
   </si>
   <si>
     <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316175937653</t>
+    <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
     <t xml:space="preserve">0.289370626211166</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">0.298086613416672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560366630554</t>
+    <t xml:space="preserve">0.313560396432877</t>
   </si>
   <si>
     <t xml:space="preserve">0.30465242266655</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">0.306434005498886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089197397232</t>
+    <t xml:space="preserve">0.301089257001877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286836504936218</t>
+    <t xml:space="preserve">0.286836475133896</t>
   </si>
   <si>
     <t xml:space="preserve">0.288618057966232</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054892301559</t>
+    <t xml:space="preserve">0.285054922103882</t>
   </si>
   <si>
     <t xml:space="preserve">0.283273279666901</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">0.281491726636887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29218128323555</t>
+    <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295371979475021</t>
+    <t xml:space="preserve">0.295372009277344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289902120828629</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">0.30448842048645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308134973049164</t>
+    <t xml:space="preserve">0.308135002851486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311781585216522</t>
+    <t xml:space="preserve">0.3117815554142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317251414060593</t>
+    <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074690341949</t>
+    <t xml:space="preserve">0.319074660539627</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33183765411377</t>
+    <t xml:space="preserve">0.331837713718414</t>
   </si>
   <si>
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897996425629</t>
+    <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
     <t xml:space="preserve">0.324544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158191680908</t>
+    <t xml:space="preserve">0.324158161878586</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610083580017</t>
+    <t xml:space="preserve">0.331610113382339</t>
   </si>
   <si>
     <t xml:space="preserve">0.326021134853363</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117321252823</t>
+    <t xml:space="preserve">0.311117351055145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309254348278046</t>
+    <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
     <t xml:space="preserve">0.335336059331894</t>
@@ -1562,25 +1562,25 @@
     <t xml:space="preserve">0.316706269979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318569272756577</t>
+    <t xml:space="preserve">0.318569242954254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340924978256226</t>
+    <t xml:space="preserve">0.340925008058548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473056554794</t>
+    <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391375303268</t>
+    <t xml:space="preserve">0.307391405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802426576614</t>
+    <t xml:space="preserve">0.301802456378937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353965848684311</t>
+    <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344650954008102</t>
+    <t xml:space="preserve">0.34465092420578</t>
   </si>
   <si>
     <t xml:space="preserve">0.337199002504349</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170022010803</t>
+    <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407992154359818</t>
+    <t xml:space="preserve">0.40799218416214</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
@@ -1610,37 +1610,37 @@
     <t xml:space="preserve">0.400540292263031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391225397586823</t>
+    <t xml:space="preserve">0.3912253677845</t>
   </si>
   <si>
     <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389362394809723</t>
+    <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458611011505</t>
+    <t xml:space="preserve">0.374458581209183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37632155418396</t>
+    <t xml:space="preserve">0.376321583986282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372595638036728</t>
+    <t xml:space="preserve">0.372595608234406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363280683755875</t>
+    <t xml:space="preserve">0.363280713558197</t>
   </si>
   <si>
     <t xml:space="preserve">0.367006689310074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869632482529</t>
+    <t xml:space="preserve">0.368869662284851</t>
   </si>
   <si>
     <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951343536377</t>
+    <t xml:space="preserve">0.394951373338699</t>
   </si>
   <si>
     <t xml:space="preserve">0.407650470733643</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">0.405754417181015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398170232772827</t>
+    <t xml:space="preserve">0.398170202970505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274149417877</t>
+    <t xml:space="preserve">0.396274209022522</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40385839343071</t>
+    <t xml:space="preserve">0.403858363628387</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097731113434</t>
+    <t xml:space="preserve">0.409097760915756</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605663537979</t>
+    <t xml:space="preserve">0.422605693340302</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -69232,7 +69232,7 @@
     </row>
     <row r="2582">
       <c r="A2582" s="1" t="n">
-        <v>46080.6388194444</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B2582" t="n">
         <v>24000</v>
@@ -69253,6 +69253,32 @@
         <v>578</v>
       </c>
       <c r="H2582" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46083.6911111111</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>588</v>
+      </c>
+      <c r="H2583" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="593">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994351506233</t>
+    <t xml:space="preserve">0.175994336605072</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
@@ -47,52 +47,52 @@
     <t xml:space="preserve">0.176622867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1728515625</t>
+    <t xml:space="preserve">0.172851592302322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594500541687</t>
+    <t xml:space="preserve">0.171594470739365</t>
   </si>
   <si>
     <t xml:space="preserve">0.164051860570908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169708833098412</t>
+    <t xml:space="preserve">0.169708847999573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148966655135155</t>
+    <t xml:space="preserve">0.148966625332832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143309682607651</t>
+    <t xml:space="preserve">0.143309652805328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783775210381</t>
   </si>
   <si>
     <t xml:space="preserve">0.145195350050926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737945318222</t>
+    <t xml:space="preserve">0.152737960219383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153366521000862</t>
+    <t xml:space="preserve">0.15336649119854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150789424777031</t>
+    <t xml:space="preserve">0.150789439678192</t>
   </si>
   <si>
     <t xml:space="preserve">0.146452412009239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852643013</t>
+    <t xml:space="preserve">0.139852613210678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538377523422</t>
+    <t xml:space="preserve">0.139538392424583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139915496110916</t>
+    <t xml:space="preserve">0.139915481209755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142052546143532</t>
+    <t xml:space="preserve">0.142052531242371</t>
   </si>
   <si>
     <t xml:space="preserve">0.138909816741943</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.15110370516777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170337364077568</t>
+    <t xml:space="preserve">0.170337349176407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817456483841</t>
+    <t xml:space="preserve">0.166817471385002</t>
   </si>
   <si>
     <t xml:space="preserve">0.163423299789429</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623597860336</t>
+    <t xml:space="preserve">0.154623568058014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595201015472</t>
+    <t xml:space="preserve">0.14959517121315</t>
   </si>
   <si>
     <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909131169319</t>
+    <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960580825806</t>
+    <t xml:space="preserve">0.158960610628128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314311265945</t>
+    <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251428365707</t>
+    <t xml:space="preserve">0.17725145816803</t>
   </si>
   <si>
     <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937513113022</t>
+    <t xml:space="preserve">0.165937528014183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565343618393</t>
+    <t xml:space="preserve">0.188565373420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650943994522</t>
+    <t xml:space="preserve">0.192650929093361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708147525787</t>
+    <t xml:space="preserve">0.191708117723465</t>
   </si>
   <si>
     <t xml:space="preserve">0.184165507555008</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">0.181651294231415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136365532875</t>
+    <t xml:space="preserve">0.201136380434036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678960800171</t>
+    <t xml:space="preserve">0.208678990602493</t>
   </si>
   <si>
     <t xml:space="preserve">0.201073557138443</t>
@@ -167,55 +167,55 @@
     <t xml:space="preserve">0.196736499667168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222301244736</t>
+    <t xml:space="preserve">0.194222316145897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137080907822</t>
+    <t xml:space="preserve">0.179137110710144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182279840111732</t>
+    <t xml:space="preserve">0.182279855012894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834539294243</t>
+    <t xml:space="preserve">0.169834554195404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168451696634293</t>
+    <t xml:space="preserve">0.168451711535454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162794768810272</t>
+    <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606544852257</t>
+    <t xml:space="preserve">0.151606559753418</t>
   </si>
   <si>
     <t xml:space="preserve">0.16656605899334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074943184853</t>
+    <t xml:space="preserve">0.157074928283691</t>
   </si>
   <si>
     <t xml:space="preserve">0.152109384536743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153995037078857</t>
+    <t xml:space="preserve">0.153995051980019</t>
   </si>
   <si>
     <t xml:space="preserve">0.157640650868416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051145195961</t>
+    <t xml:space="preserve">0.186051174998283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936782836914</t>
+    <t xml:space="preserve">0.187936812639236</t>
   </si>
   <si>
     <t xml:space="preserve">0.183536946773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18171414732933</t>
+    <t xml:space="preserve">0.181714177131653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194619774818</t>
+    <t xml:space="preserve">0.167194604873657</t>
   </si>
   <si>
     <t xml:space="preserve">0.160280555486679</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">0.147080972790718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151480838656425</t>
+    <t xml:space="preserve">0.151480853557587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338064551353</t>
+    <t xml:space="preserve">0.148338079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566789269447</t>
+    <t xml:space="preserve">0.144566759467125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158394902944565</t>
+    <t xml:space="preserve">0.158394917845726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165183261036873</t>
+    <t xml:space="preserve">0.165183275938034</t>
   </si>
   <si>
     <t xml:space="preserve">0.170651644468307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17222298681736</t>
+    <t xml:space="preserve">0.172223016619682</t>
   </si>
   <si>
     <t xml:space="preserve">0.18259409070015</t>
@@ -251,37 +251,37 @@
     <t xml:space="preserve">0.20050784945488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.193593755364418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178131401538849</t>
+    <t xml:space="preserve">0.17813141644001</t>
   </si>
   <si>
     <t xml:space="preserve">0.190765291452408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010644435883</t>
+    <t xml:space="preserve">0.201010629534721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850847125053</t>
+    <t xml:space="preserve">0.194850862026215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770970821381</t>
+    <t xml:space="preserve">0.191770955920219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879243969917</t>
+    <t xml:space="preserve">0.199879258871078</t>
   </si>
   <si>
     <t xml:space="preserve">0.213078841567039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787308454514</t>
+    <t xml:space="preserve">0.216787278652191</t>
   </si>
   <si>
     <t xml:space="preserve">0.2325639128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220885396004</t>
+    <t xml:space="preserve">0.238220945000648</t>
   </si>
   <si>
     <t xml:space="preserve">0.251420497894287</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.298561811447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257705986499786</t>
+    <t xml:space="preserve">0.257705956697464</t>
   </si>
   <si>
     <t xml:space="preserve">0.260157346725464</t>
@@ -308,49 +308,49 @@
     <t xml:space="preserve">0.250226199626923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163316726685</t>
+    <t xml:space="preserve">0.250163376331329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809325456619</t>
+    <t xml:space="preserve">0.242809310555458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249297142029</t>
+    <t xml:space="preserve">0.243249282240868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375033140182</t>
+    <t xml:space="preserve">0.24337500333786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421183466911</t>
+    <t xml:space="preserve">0.229421198368073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821019530296</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210564643144608</t>
+    <t xml:space="preserve">0.21056467294693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919074058533</t>
+    <t xml:space="preserve">0.206919029355049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821734905243</t>
+    <t xml:space="preserve">0.211821749806404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741873502731</t>
+    <t xml:space="preserve">0.208741843700409</t>
   </si>
   <si>
     <t xml:space="preserve">0.237592354416847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134994387627</t>
+    <t xml:space="preserve">0.245134949684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230803951621056</t>
+    <t xml:space="preserve">0.230803981423378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535516023636</t>
+    <t xml:space="preserve">0.227535471320152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706657171249</t>
+    <t xml:space="preserve">0.235706716775894</t>
   </si>
   <si>
     <t xml:space="preserve">0.226278439164162</t>
@@ -359,124 +359,124 @@
     <t xml:space="preserve">0.223135650157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850131750107</t>
+    <t xml:space="preserve">0.216850161552429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381427884102</t>
+    <t xml:space="preserve">0.222381412982941</t>
   </si>
   <si>
     <t xml:space="preserve">0.213141724467278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201199233531952</t>
+    <t xml:space="preserve">0.201199263334274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279124736786</t>
+    <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206793367862701</t>
+    <t xml:space="preserve">0.206793338060379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164792180061</t>
+    <t xml:space="preserve">0.206164807081223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421869039536</t>
+    <t xml:space="preserve">0.207421898841858</t>
   </si>
   <si>
     <t xml:space="preserve">0.208804711699486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947456002235</t>
+    <t xml:space="preserve">0.211947441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649863481522</t>
+    <t xml:space="preserve">0.225649878382683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867184758186</t>
+    <t xml:space="preserve">0.219867244362831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810040831566</t>
+    <t xml:space="preserve">0.220810055732727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484036564827</t>
+    <t xml:space="preserve">0.229484051465988</t>
   </si>
   <si>
     <t xml:space="preserve">0.234386757016182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518448114395</t>
+    <t xml:space="preserve">0.224518492817879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219992846250534</t>
+    <t xml:space="preserve">0.21999292075634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741493463516</t>
+    <t xml:space="preserve">0.219741523265839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216913014650345</t>
+    <t xml:space="preserve">0.216913029551506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306865811348</t>
+    <t xml:space="preserve">0.231306850910187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038720846176</t>
+    <t xml:space="preserve">0.217038705945015</t>
   </si>
   <si>
     <t xml:space="preserve">0.223324254155159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178953886032</t>
+    <t xml:space="preserve">0.297179013490677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988703012466</t>
+    <t xml:space="preserve">0.351988673210144</t>
   </si>
   <si>
     <t xml:space="preserve">0.465127825737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582354068756</t>
+    <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477070331573486</t>
+    <t xml:space="preserve">0.477070391178131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843067407608</t>
+    <t xml:space="preserve">0.436843127012253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072112560272</t>
+    <t xml:space="preserve">0.422072172164917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987272262573</t>
+    <t xml:space="preserve">0.395987242460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364559680223465</t>
+    <t xml:space="preserve">0.364559710025787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215177297592</t>
+    <t xml:space="preserve">0.414215266704559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388188838959</t>
+    <t xml:space="preserve">0.367388248443604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987972736359</t>
+    <t xml:space="preserve">0.373987942934036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346331685781479</t>
+    <t xml:space="preserve">0.346331715583801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903743505478</t>
+    <t xml:space="preserve">0.3259037733078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314904153347015</t>
+    <t xml:space="preserve">0.314904123544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326532334089279</t>
+    <t xml:space="preserve">0.326532393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389239549637</t>
+    <t xml:space="preserve">0.334389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818262338638</t>
+    <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
     <t xml:space="preserve">0.348845899105072</t>
@@ -488,22 +488,22 @@
     <t xml:space="preserve">0.326846599578857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318361222743988</t>
+    <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189671754837</t>
+    <t xml:space="preserve">0.321189641952515</t>
   </si>
   <si>
     <t xml:space="preserve">0.333132117986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329989373683929</t>
+    <t xml:space="preserve">0.329989314079285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418336868286</t>
+    <t xml:space="preserve">0.317418366670609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332356452942</t>
+    <t xml:space="preserve">0.324332386255264</t>
   </si>
   <si>
     <t xml:space="preserve">0.314275592565536</t>
@@ -515,187 +515,187 @@
     <t xml:space="preserve">0.334703505039215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318046897649765</t>
+    <t xml:space="preserve">0.318046867847443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31678980588913</t>
+    <t xml:space="preserve">0.316789835691452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328418046236038</t>
+    <t xml:space="preserve">0.328418016433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075324296951</t>
+    <t xml:space="preserve">0.323075354099274</t>
   </si>
   <si>
     <t xml:space="preserve">0.328103721141815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301704525947571</t>
+    <t xml:space="preserve">0.301704555749893</t>
   </si>
   <si>
     <t xml:space="preserve">0.310504287481308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311069965362549</t>
+    <t xml:space="preserve">0.311069935560226</t>
   </si>
   <si>
     <t xml:space="preserve">0.320561110973358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325589537620544</t>
+    <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274161815643</t>
+    <t xml:space="preserve">0.358274221420288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417666196823</t>
+    <t xml:space="preserve">0.339417695999146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340046226978302</t>
+    <t xml:space="preserve">0.34004619717598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319304019212723</t>
+    <t xml:space="preserve">0.319304049015045</t>
   </si>
   <si>
     <t xml:space="preserve">0.337846279144287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314589828252792</t>
+    <t xml:space="preserve">0.31458991765976</t>
   </si>
   <si>
     <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701694250107</t>
+    <t xml:space="preserve">0.389701724052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588047266006</t>
+    <t xml:space="preserve">0.369588106870651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959575891495</t>
+    <t xml:space="preserve">0.368959546089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36361688375473</t>
+    <t xml:space="preserve">0.363616824150085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845198631287</t>
+    <t xml:space="preserve">0.370845139026642</t>
   </si>
   <si>
     <t xml:space="preserve">0.345074594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788695573807</t>
+    <t xml:space="preserve">0.349788755178452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502856731415</t>
+    <t xml:space="preserve">0.35450291633606</t>
   </si>
   <si>
     <t xml:space="preserve">0.367073893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758897781372</t>
+    <t xml:space="preserve">0.38875886797905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587406396866</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377759248018265</t>
+    <t xml:space="preserve">0.377759277820587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130687236786</t>
+    <t xml:space="preserve">0.377130746841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187510728836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444952726364</t>
+    <t xml:space="preserve">0.377445012331009</t>
   </si>
   <si>
     <t xml:space="preserve">0.407929718494415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843738079071</t>
+    <t xml:space="preserve">0.414843797683716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392215937376022</t>
+    <t xml:space="preserve">0.3922159075737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37681645154953</t>
+    <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386558920145035</t>
+    <t xml:space="preserve">0.386559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413314342499</t>
+    <t xml:space="preserve">0.471413433551788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357191324234</t>
+    <t xml:space="preserve">0.439357280731201</t>
   </si>
   <si>
     <t xml:space="preserve">0.452556878328323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700263500214</t>
+    <t xml:space="preserve">0.433700323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100218772888</t>
+    <t xml:space="preserve">0.438100129365921</t>
   </si>
   <si>
     <t xml:space="preserve">0.446271300315857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439985692501068</t>
+    <t xml:space="preserve">0.43998584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42238637804985</t>
+    <t xml:space="preserve">0.422386407852173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900621175766</t>
+    <t xml:space="preserve">0.424900501966476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421129286289215</t>
+    <t xml:space="preserve">0.42112934589386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409815341234207</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406044065952301</t>
+    <t xml:space="preserve">0.406044095754623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558249473572</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413586735725403</t>
+    <t xml:space="preserve">0.413586676120758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40227273106575</t>
+    <t xml:space="preserve">0.402272760868073</t>
   </si>
   <si>
     <t xml:space="preserve">0.432443201541901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357921600342</t>
+    <t xml:space="preserve">0.417357981204987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613731622696</t>
+    <t xml:space="preserve">0.462613701820374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414774894714</t>
+    <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758487939835</t>
+    <t xml:space="preserve">0.399758517742157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615013360977</t>
+    <t xml:space="preserve">0.418615102767944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643469810486</t>
+    <t xml:space="preserve">0.423643499612808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072432994843</t>
+    <t xml:space="preserve">0.411072462797165</t>
   </si>
   <si>
     <t xml:space="preserve">0.398501425981522</t>
@@ -704,31 +704,31 @@
     <t xml:space="preserve">0.404786914587021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159054279327</t>
+    <t xml:space="preserve">0.382159113883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383416295051575</t>
+    <t xml:space="preserve">0.38341623544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444602489471</t>
+    <t xml:space="preserve">0.388444632291794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529822826385</t>
+    <t xml:space="preserve">0.40352988243103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43118605017662</t>
+    <t xml:space="preserve">0.43118616938591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419872164726257</t>
+    <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301187515259</t>
+    <t xml:space="preserve">0.407301127910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730180501938</t>
+    <t xml:space="preserve">0.39473021030426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329584360123</t>
+    <t xml:space="preserve">0.412329614162445</t>
   </si>
   <si>
     <t xml:space="preserve">0.40101569890976</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.416100859642029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045437097549</t>
+    <t xml:space="preserve">0.362045466899872</t>
   </si>
   <si>
     <t xml:space="preserve">0.3658167719841</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">0.36330258846283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340674728155136</t>
+    <t xml:space="preserve">0.340674698352814</t>
   </si>
   <si>
     <t xml:space="preserve">0.329360812902451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359531283378601</t>
+    <t xml:space="preserve">0.359531313180923</t>
   </si>
   <si>
     <t xml:space="preserve">0.357017040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34444597363472</t>
+    <t xml:space="preserve">0.344446033239365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336903393268585</t>
+    <t xml:space="preserve">0.336903423070908</t>
   </si>
   <si>
     <t xml:space="preserve">0.338160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703125</t>
+    <t xml:space="preserve">0.345703184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102290391922</t>
+    <t xml:space="preserve">0.372102349996567</t>
   </si>
   <si>
     <t xml:space="preserve">0.385930448770523</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">0.353245735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788375139236</t>
+    <t xml:space="preserve">0.360788345336914</t>
   </si>
   <si>
     <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873565673828</t>
+    <t xml:space="preserve">0.375873625278473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359382152557</t>
+    <t xml:space="preserve">0.373359352350235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673297405243</t>
+    <t xml:space="preserve">0.384673327207565</t>
   </si>
   <si>
     <t xml:space="preserve">0.390958845615387</t>
@@ -800,73 +800,73 @@
     <t xml:space="preserve">0.393472999334335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272030591965</t>
+    <t xml:space="preserve">0.424272090196609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557548999786</t>
+    <t xml:space="preserve">0.430557578802109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414104223251</t>
+    <t xml:space="preserve">0.449414074420929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699682235718</t>
+    <t xml:space="preserve">0.455699592828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463955968618393</t>
+    <t xml:space="preserve">0.46395605802536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181872367859</t>
+    <t xml:space="preserve">0.443181842565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429332405328751</t>
+    <t xml:space="preserve">0.429332464933395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415482997894287</t>
+    <t xml:space="preserve">0.415483027696609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870090723038</t>
+    <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257123947144</t>
+    <t xml:space="preserve">0.436257094144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719408750534</t>
+    <t xml:space="preserve">0.439719498157501</t>
   </si>
   <si>
     <t xml:space="preserve">0.432794719934464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41894543170929</t>
+    <t xml:space="preserve">0.4189453125</t>
   </si>
   <si>
     <t xml:space="preserve">0.401633530855179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020683288574</t>
+    <t xml:space="preserve">0.412020653486252</t>
   </si>
   <si>
     <t xml:space="preserve">0.387784093618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246467828751</t>
+    <t xml:space="preserve">0.391246497631073</t>
   </si>
   <si>
     <t xml:space="preserve">0.405095905065536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
+    <t xml:space="preserve">0.422407776117325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446644186973572</t>
+    <t xml:space="preserve">0.446644157171249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526278436183929</t>
+    <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106590986252</t>
+    <t xml:space="preserve">0.450106561183929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457031220197678</t>
+    <t xml:space="preserve">0.457031309604645</t>
   </si>
   <si>
     <t xml:space="preserve">0.453568935394287</t>
@@ -875,64 +875,64 @@
     <t xml:space="preserve">0.398171186447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394708812236786</t>
+    <t xml:space="preserve">0.394708871841431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859434604645</t>
+    <t xml:space="preserve">0.380859404802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934715986252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360085248947144</t>
+    <t xml:space="preserve">0.360085219144821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370472371578217</t>
+    <t xml:space="preserve">0.370472341775894</t>
   </si>
   <si>
     <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367010027170181</t>
+    <t xml:space="preserve">0.367009967565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696007013321</t>
+    <t xml:space="preserve">0.340696066617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339311093091965</t>
+    <t xml:space="preserve">0.339311122894287</t>
   </si>
   <si>
     <t xml:space="preserve">0.353160470724106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235811710358</t>
+    <t xml:space="preserve">0.34623584151268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332386374473572</t>
+    <t xml:space="preserve">0.332386344671249</t>
   </si>
   <si>
     <t xml:space="preserve">0.311612248420715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31438210606575</t>
+    <t xml:space="preserve">0.314382165670395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290838122367859</t>
+    <t xml:space="preserve">0.290838032960892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258984386920929</t>
+    <t xml:space="preserve">0.258984357118607</t>
   </si>
   <si>
     <t xml:space="preserve">0.278373658657074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263139218091965</t>
+    <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833794355392</t>
+    <t xml:space="preserve">0.272833824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261754274368286</t>
+    <t xml:space="preserve">0.261754244565964</t>
   </si>
   <si>
     <t xml:space="preserve">0.249289825558662</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298317670822</t>
+    <t xml:space="preserve">0.285298347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683231592178</t>
+    <t xml:space="preserve">0.286683291196823</t>
   </si>
   <si>
     <t xml:space="preserve">0.271448880434036</t>
@@ -953,73 +953,73 @@
     <t xml:space="preserve">0.27975857257843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143456697464</t>
+    <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.294992923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302586078644</t>
+    <t xml:space="preserve">0.303302556276321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842360973358</t>
+    <t xml:space="preserve">0.308842390775681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926179170609</t>
+    <t xml:space="preserve">0.337926149368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461685657501</t>
+    <t xml:space="preserve">0.325461626052856</t>
   </si>
   <si>
     <t xml:space="preserve">0.319921880960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465954065323</t>
+    <t xml:space="preserve">0.343465924263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363547563552856</t>
+    <t xml:space="preserve">0.363547593355179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377397090196609</t>
+    <t xml:space="preserve">0.377397030591965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328231602907181</t>
+    <t xml:space="preserve">0.328231573104858</t>
   </si>
   <si>
     <t xml:space="preserve">0.331001430749893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336541205644608</t>
+    <t xml:space="preserve">0.336541175842285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698156118393</t>
+    <t xml:space="preserve">0.349698215723038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344850838184357</t>
+    <t xml:space="preserve">0.344850897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322691798210144</t>
+    <t xml:space="preserve">0.322691738605499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324076682329178</t>
+    <t xml:space="preserve">0.3240767121315</t>
   </si>
   <si>
     <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536967039108</t>
+    <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072473526001</t>
+    <t xml:space="preserve">0.306072443723679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317151993513107</t>
+    <t xml:space="preserve">0.31715202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304687529802322</t>
+    <t xml:space="preserve">0.3046875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762781381607</t>
+    <t xml:space="preserve">0.297762811183929</t>
   </si>
   <si>
     <t xml:space="preserve">0.283913373947144</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">0.288068205118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524161815643</t>
+    <t xml:space="preserve">0.264524191617966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267294079065323</t>
+    <t xml:space="preserve">0.267294019460678</t>
   </si>
   <si>
     <t xml:space="preserve">0.260369300842285</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">0.265909135341644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27006396651268</t>
+    <t xml:space="preserve">0.270063936710358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988625526428</t>
+    <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223036289215</t>
+    <t xml:space="preserve">0.292223006486893</t>
   </si>
   <si>
     <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453148841858</t>
+    <t xml:space="preserve">0.289453119039536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429809987545013</t>
+    <t xml:space="preserve">0.429809957742691</t>
   </si>
   <si>
     <t xml:space="preserve">0.399647861719131</t>
@@ -1064,82 +1064,82 @@
     <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377026289701462</t>
+    <t xml:space="preserve">0.377026259899139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361945271492004</t>
+    <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485795497894</t>
+    <t xml:space="preserve">0.369485825300217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453298807144</t>
+    <t xml:space="preserve">0.363453358411789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380796521902084</t>
+    <t xml:space="preserve">0.380796581506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37401008605957</t>
+    <t xml:space="preserve">0.374010056257248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364961445331573</t>
+    <t xml:space="preserve">0.364961385726929</t>
   </si>
   <si>
     <t xml:space="preserve">0.349880397319794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343848019838333</t>
+    <t xml:space="preserve">0.343847990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342339873313904</t>
+    <t xml:space="preserve">0.342339903116226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33932363986969</t>
+    <t xml:space="preserve">0.339323669672012</t>
   </si>
   <si>
     <t xml:space="preserve">0.352896571159363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864223480225</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
     <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307436227798</t>
+    <t xml:space="preserve">0.336307495832443</t>
   </si>
   <si>
     <t xml:space="preserve">0.334799349308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372280597687</t>
+    <t xml:space="preserve">0.348372370004654</t>
   </si>
   <si>
     <t xml:space="preserve">0.437350481748581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958677530289</t>
+    <t xml:space="preserve">0.410958647727966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431529760361</t>
+    <t xml:space="preserve">0.452431559562683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444891065359116</t>
+    <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120773553848</t>
+    <t xml:space="preserve">0.441120743751526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414728939533234</t>
+    <t xml:space="preserve">0.414728909730911</t>
   </si>
   <si>
     <t xml:space="preserve">0.403418153524399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107278108597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384566783905029</t>
+    <t xml:space="preserve">0.384566813707352</t>
   </si>
   <si>
     <t xml:space="preserve">0.395877540111542</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">0.372501999139786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36646956205368</t>
+    <t xml:space="preserve">0.366469532251358</t>
   </si>
   <si>
     <t xml:space="preserve">0.354404747486115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34535613656044</t>
+    <t xml:space="preserve">0.345356106758118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831786394119</t>
+    <t xml:space="preserve">0.340831756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993882417679</t>
+    <t xml:space="preserve">0.370993852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360437124967575</t>
+    <t xml:space="preserve">0.360437154769897</t>
   </si>
   <si>
     <t xml:space="preserve">0.367977648973465</t>
@@ -1175,61 +1175,61 @@
     <t xml:space="preserve">0.358929038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31670206785202</t>
+    <t xml:space="preserve">0.316702038049698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112903118134</t>
+    <t xml:space="preserve">0.300112962722778</t>
   </si>
   <si>
     <t xml:space="preserve">0.301621049642563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31821021437645</t>
+    <t xml:space="preserve">0.318210154771805</t>
   </si>
   <si>
     <t xml:space="preserve">0.319718271493912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32424259185791</t>
+    <t xml:space="preserve">0.324242651462555</t>
   </si>
   <si>
     <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330274999141693</t>
+    <t xml:space="preserve">0.330275028944016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331783145666122</t>
+    <t xml:space="preserve">0.3317831158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337815552949905</t>
+    <t xml:space="preserve">0.337815582752228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328766942024231</t>
+    <t xml:space="preserve">0.328766882419586</t>
   </si>
   <si>
     <t xml:space="preserve">0.309161573648453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653397321701</t>
+    <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303129136562347</t>
+    <t xml:space="preserve">0.30312916636467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313685864210129</t>
+    <t xml:space="preserve">0.313685894012451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734475135803</t>
+    <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317599207162857</t>
+    <t xml:space="preserve">0.317599236965179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322339415550232</t>
+    <t xml:space="preserve">0.322339445352554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314439028501511</t>
   </si>
   <si>
     <t xml:space="preserve">0.31917929649353</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">0.331820011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333400100469589</t>
+    <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759385824203</t>
+    <t xml:space="preserve">0.320759356021881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919594287872</t>
+    <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312858939170837</t>
+    <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
     <t xml:space="preserve">0.303378313779831</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">0.292317688465118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30179825425148</t>
+    <t xml:space="preserve">0.301798224449158</t>
   </si>
   <si>
     <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218164920807</t>
+    <t xml:space="preserve">0.300218135118484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298637986183167</t>
+    <t xml:space="preserve">0.298638015985489</t>
   </si>
   <si>
     <t xml:space="preserve">0.290737569332123</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">0.287577360868454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676914215088</t>
+    <t xml:space="preserve">0.279676884412766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516675949097</t>
+    <t xml:space="preserve">0.276516705751419</t>
   </si>
   <si>
     <t xml:space="preserve">0.278096795082092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196288824081</t>
+    <t xml:space="preserve">0.270196318626404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257003545761</t>
+    <t xml:space="preserve">0.281256973743439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776437759399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284417182207108</t>
+    <t xml:space="preserve">0.284417152404785</t>
   </si>
   <si>
     <t xml:space="preserve">0.285997271537781</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">0.295477867126465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297057956457138</t>
+    <t xml:space="preserve">0.297057896852493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118611574173</t>
+    <t xml:space="preserve">0.308118581771851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28915748000145</t>
+    <t xml:space="preserve">0.289157509803772</t>
   </si>
   <si>
     <t xml:space="preserve">0.34604087471962</t>
@@ -1319,28 +1319,28 @@
     <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720517396927</t>
+    <t xml:space="preserve">0.339720577001572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3413006067276</t>
+    <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
     <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33656033873558</t>
+    <t xml:space="preserve">0.336560398340225</t>
   </si>
   <si>
     <t xml:space="preserve">0.35236132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359253883362</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944712400436</t>
+    <t xml:space="preserve">0.291944742202759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237456560135</t>
+    <t xml:space="preserve">0.290237486362457</t>
   </si>
   <si>
     <t xml:space="preserve">0.285115629434586</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">0.286822885274887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300481140613556</t>
+    <t xml:space="preserve">0.300481110811234</t>
   </si>
   <si>
     <t xml:space="preserve">0.29877382516861</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">0.283408313989639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278286516666412</t>
+    <t xml:space="preserve">0.27828648686409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288530200719833</t>
+    <t xml:space="preserve">0.288530170917511</t>
   </si>
   <si>
     <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164659738541</t>
+    <t xml:space="preserve">0.273164689540863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276579231023788</t>
+    <t xml:space="preserve">0.276579201221466</t>
   </si>
   <si>
     <t xml:space="preserve">0.269750118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701058149338</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871975183487</t>
+    <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457403898239</t>
+    <t xml:space="preserve">0.271457344293594</t>
   </si>
   <si>
     <t xml:space="preserve">0.268042832612991</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293652027845383</t>
   </si>
   <si>
     <t xml:space="preserve">0.30218842625618</t>
@@ -1400,34 +1400,34 @@
     <t xml:space="preserve">0.305602967739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307310253381729</t>
+    <t xml:space="preserve">0.307310223579407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324383050203323</t>
+    <t xml:space="preserve">0.324382990598679</t>
   </si>
   <si>
     <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017509222031</t>
+    <t xml:space="preserve">0.309017539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139366149902</t>
+    <t xml:space="preserve">0.314139395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312432110309601</t>
+    <t xml:space="preserve">0.312432080507278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310724794864655</t>
+    <t xml:space="preserve">0.310724765062332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310288995504379</t>
+    <t xml:space="preserve">0.310288965702057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829810857773</t>
+    <t xml:space="preserve">0.299829840660095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296343415975571</t>
+    <t xml:space="preserve">0.296343445777893</t>
   </si>
   <si>
     <t xml:space="preserve">0.303316205739975</t>
@@ -1436,25 +1436,25 @@
     <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627428770065</t>
+    <t xml:space="preserve">0.287627458572388</t>
   </si>
   <si>
     <t xml:space="preserve">0.298086613416672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313560396432877</t>
+    <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30465242266655</t>
+    <t xml:space="preserve">0.304652392864227</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306434005498886</t>
+    <t xml:space="preserve">0.306434035301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301089257001877</t>
+    <t xml:space="preserve">0.301089197397232</t>
   </si>
   <si>
     <t xml:space="preserve">0.286836475133896</t>
@@ -1466,28 +1466,28 @@
     <t xml:space="preserve">0.290399670600891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299307644367218</t>
+    <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
     <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054922103882</t>
+    <t xml:space="preserve">0.285054892301559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283273279666901</t>
+    <t xml:space="preserve">0.283273249864578</t>
   </si>
   <si>
     <t xml:space="preserve">0.279710084199905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491726636887</t>
+    <t xml:space="preserve">0.281491696834564</t>
   </si>
   <si>
     <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
     <t xml:space="preserve">0.289902120828629</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">0.302665114402771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291725397109985</t>
+    <t xml:space="preserve">0.291725426912308</t>
   </si>
   <si>
     <t xml:space="preserve">0.30448842048645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308135002851486</t>
+    <t xml:space="preserve">0.308134973049164</t>
   </si>
   <si>
     <t xml:space="preserve">0.3117815554142</t>
@@ -1511,46 +1511,46 @@
     <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074660539627</t>
+    <t xml:space="preserve">0.319074690341949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313604831695557</t>
+    <t xml:space="preserve">0.313604861497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191131353378</t>
+    <t xml:space="preserve">0.328191101551056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331837713718414</t>
+    <t xml:space="preserve">0.33183765411377</t>
   </si>
   <si>
     <t xml:space="preserve">0.333660960197449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320897966623306</t>
+    <t xml:space="preserve">0.320897936820984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324544548988342</t>
+    <t xml:space="preserve">0.32454451918602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158161878586</t>
+    <t xml:space="preserve">0.324158191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329747140407562</t>
+    <t xml:space="preserve">0.32974711060524</t>
   </si>
   <si>
     <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610113382339</t>
+    <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021134853363</t>
+    <t xml:space="preserve">0.326021164655685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432215929031</t>
+    <t xml:space="preserve">0.320432245731354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311117351055145</t>
+    <t xml:space="preserve">0.311117321252823</t>
   </si>
   <si>
     <t xml:space="preserve">0.309254318475723</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307391405105591</t>
+    <t xml:space="preserve">0.307391375303268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
     <t xml:space="preserve">0.353965818881989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34465092420578</t>
+    <t xml:space="preserve">0.344650954008102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337199002504349</t>
+    <t xml:space="preserve">0.337199032306671</t>
   </si>
   <si>
     <t xml:space="preserve">0.348376899957657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370732605457306</t>
+    <t xml:space="preserve">0.370732635259628</t>
   </si>
   <si>
     <t xml:space="preserve">0.398677289485931</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40799218416214</t>
+    <t xml:space="preserve">0.407992213964462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417307108640671</t>
+    <t xml:space="preserve">0.417307078838348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409855157136917</t>
+    <t xml:space="preserve">0.40985518693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.400540292263031</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">0.389362454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374458581209183</t>
+    <t xml:space="preserve">0.374458611011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376321583986282</t>
+    <t xml:space="preserve">0.37632155418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.372595608234406</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394951373338699</t>
+    <t xml:space="preserve">0.394951343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407650470733643</t>
+    <t xml:space="preserve">0.407650500535965</t>
   </si>
   <si>
     <t xml:space="preserve">0.392482101917267</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">0.398170202970505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396274209022522</t>
+    <t xml:space="preserve">0.3962741792202</t>
   </si>
   <si>
     <t xml:space="preserve">0.400066256523132</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">0.413338601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403858363628387</t>
+    <t xml:space="preserve">0.40385839343071</t>
   </si>
   <si>
     <t xml:space="preserve">0.420675963163376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409097760915756</t>
+    <t xml:space="preserve">0.409097731113434</t>
   </si>
   <si>
     <t xml:space="preserve">0.407168030738831</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">0.414886862039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422605693340302</t>
+    <t xml:space="preserve">0.422605663537979</t>
   </si>
   <si>
     <t xml:space="preserve">0.411027461290359</t>
@@ -1788,6 +1788,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.514999985694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
   </si>
 </sst>
 </file>
@@ -69258,7 +69261,7 @@
     </row>
     <row r="2583">
       <c r="A2583" s="1" t="n">
-        <v>46083.6911111111</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B2583" t="n">
         <v>16000</v>
@@ -69279,6 +69282,32 @@
         <v>588</v>
       </c>
       <c r="H2583" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" s="1" t="n">
+        <v>46084.5562731481</v>
+      </c>
+      <c r="B2584" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C2584" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D2584" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E2584" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2584" t="s">
+        <v>592</v>
+      </c>
+      <c r="H2584" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175994351506233</t>
+    <t xml:space="preserve">0.175994321703911</t>
   </si>
   <si>
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622912287712</t>
+    <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172851592302322</t>
+    <t xml:space="preserve">0.172851577401161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171594485640526</t>
+    <t xml:space="preserve">0.171594455838203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164051845669746</t>
+    <t xml:space="preserve">0.164051860570908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16970881819725</t>
+    <t xml:space="preserve">0.169708833098412</t>
   </si>
   <si>
     <t xml:space="preserve">0.148966640233994</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">0.143309682607651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149783745408058</t>
+    <t xml:space="preserve">0.149783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145195320248604</t>
+    <t xml:space="preserve">0.145195350050926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152737930417061</t>
+    <t xml:space="preserve">0.152737945318222</t>
   </si>
   <si>
     <t xml:space="preserve">0.15336649119854</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">0.150789424777031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1464524269104</t>
+    <t xml:space="preserve">0.146452397108078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139852613210678</t>
+    <t xml:space="preserve">0.139852643013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139538362622261</t>
+    <t xml:space="preserve">0.139538377523422</t>
   </si>
   <si>
     <t xml:space="preserve">0.139915496110916</t>
@@ -98,85 +98,85 @@
     <t xml:space="preserve">0.138909801840782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15110370516777</t>
+    <t xml:space="preserve">0.151103690266609</t>
   </si>
   <si>
     <t xml:space="preserve">0.170337364077568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166817471385002</t>
+    <t xml:space="preserve">0.166817486286163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163423329591751</t>
+    <t xml:space="preserve">0.163423284888268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157137781381607</t>
+    <t xml:space="preserve">0.157137796282768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154623597860336</t>
+    <t xml:space="preserve">0.154623568058014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149595215916634</t>
+    <t xml:space="preserve">0.149595201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155692130327225</t>
+    <t xml:space="preserve">0.155692145228386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160909086465836</t>
+    <t xml:space="preserve">0.160909116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158960610628128</t>
+    <t xml:space="preserve">0.158960595726967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177314281463623</t>
+    <t xml:space="preserve">0.177314296364784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177251443266869</t>
+    <t xml:space="preserve">0.177251428365707</t>
   </si>
   <si>
     <t xml:space="preserve">0.170965924859047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165937513113022</t>
+    <t xml:space="preserve">0.165937528014183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188565343618393</t>
+    <t xml:space="preserve">0.188565358519554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.192650958895683</t>
+    <t xml:space="preserve">0.192650943994522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191708117723465</t>
+    <t xml:space="preserve">0.191708132624626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18416553735733</t>
+    <t xml:space="preserve">0.184165507555008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181651279330254</t>
+    <t xml:space="preserve">0.181651309132576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201136395335197</t>
+    <t xml:space="preserve">0.201136350631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208678990602493</t>
+    <t xml:space="preserve">0.208678975701332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201073542237282</t>
+    <t xml:space="preserve">0.201073527336121</t>
   </si>
   <si>
     <t xml:space="preserve">0.196736514568329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194222331047058</t>
+    <t xml:space="preserve">0.194222301244736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179137095808983</t>
+    <t xml:space="preserve">0.179137110710144</t>
   </si>
   <si>
     <t xml:space="preserve">0.182279840111732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169834569096565</t>
+    <t xml:space="preserve">0.169834539294243</t>
   </si>
   <si>
     <t xml:space="preserve">0.168451711535454</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">0.162794753909111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151606544852257</t>
+    <t xml:space="preserve">0.151606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166566073894501</t>
+    <t xml:space="preserve">0.16656605899334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157074928283691</t>
+    <t xml:space="preserve">0.157074943184853</t>
   </si>
   <si>
     <t xml:space="preserve">0.152109384536743</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">0.157640635967255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.186051160097122</t>
+    <t xml:space="preserve">0.186051189899445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187936797738075</t>
+    <t xml:space="preserve">0.187936827540398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183536946773529</t>
+    <t xml:space="preserve">0.183536931872368</t>
   </si>
   <si>
     <t xml:space="preserve">0.18171414732933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167194619774818</t>
+    <t xml:space="preserve">0.167194604873657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16028057038784</t>
+    <t xml:space="preserve">0.160280540585518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147080972790718</t>
+    <t xml:space="preserve">0.147080957889557</t>
   </si>
   <si>
     <t xml:space="preserve">0.151480838656425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148338079452515</t>
+    <t xml:space="preserve">0.148338094353676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144566774368286</t>
+    <t xml:space="preserve">0.144566789269447</t>
   </si>
   <si>
     <t xml:space="preserve">0.158394902944565</t>
@@ -239,232 +239,232 @@
     <t xml:space="preserve">0.165183246135712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170651659369469</t>
+    <t xml:space="preserve">0.170651644468307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172223001718521</t>
+    <t xml:space="preserve">0.172223016619682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182594120502472</t>
+    <t xml:space="preserve">0.182594105601311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200507834553719</t>
+    <t xml:space="preserve">0.20050784945488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193593770265579</t>
+    <t xml:space="preserve">0.193593740463257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17813141644001</t>
+    <t xml:space="preserve">0.178131401538849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.190765306353569</t>
+    <t xml:space="preserve">0.190765276551247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201010689139366</t>
+    <t xml:space="preserve">0.201010644435883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.194850891828537</t>
+    <t xml:space="preserve">0.194850862026215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.191770941019058</t>
+    <t xml:space="preserve">0.191770955920219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.199879258871078</t>
+    <t xml:space="preserve">0.19987927377224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213078856468201</t>
+    <t xml:space="preserve">0.213078826665878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216787323355675</t>
+    <t xml:space="preserve">0.216787278652191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232563942670822</t>
+    <t xml:space="preserve">0.232563897967339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238220855593681</t>
+    <t xml:space="preserve">0.238220930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251420497894287</t>
+    <t xml:space="preserve">0.251420438289642</t>
   </si>
   <si>
     <t xml:space="preserve">0.26713427901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275305420160294</t>
+    <t xml:space="preserve">0.275305360555649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290390640497208</t>
+    <t xml:space="preserve">0.290390700101852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298561841249466</t>
+    <t xml:space="preserve">0.298561781644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257706016302109</t>
+    <t xml:space="preserve">0.257705956697464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260157316923141</t>
+    <t xml:space="preserve">0.260157346725464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250226229429245</t>
+    <t xml:space="preserve">0.250226199626923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250163376331329</t>
+    <t xml:space="preserve">0.250163316726685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242809325456619</t>
+    <t xml:space="preserve">0.242809370160103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243249356746674</t>
+    <t xml:space="preserve">0.243249297142029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.243375033140182</t>
+    <t xml:space="preserve">0.243375018239021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229421213269234</t>
+    <t xml:space="preserve">0.229421183466911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233821019530296</t>
+    <t xml:space="preserve">0.233821049332619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21056467294693</t>
+    <t xml:space="preserve">0.210564658045769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206919059157372</t>
+    <t xml:space="preserve">0.206919014453888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211821779608727</t>
+    <t xml:space="preserve">0.211821749806404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208741873502731</t>
+    <t xml:space="preserve">0.208741843700409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237592354416847</t>
+    <t xml:space="preserve">0.237592324614525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245134949684143</t>
+    <t xml:space="preserve">0.245134994387627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.230804026126862</t>
+    <t xml:space="preserve">0.2308040112257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227535516023636</t>
+    <t xml:space="preserve">0.227535530924797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235706701874733</t>
+    <t xml:space="preserve">0.235706716775894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226278439164162</t>
+    <t xml:space="preserve">0.226278454065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.223135635256767</t>
+    <t xml:space="preserve">0.22313566505909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216850191354752</t>
+    <t xml:space="preserve">0.216850161552429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222381427884102</t>
+    <t xml:space="preserve">0.222381398081779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213141724467278</t>
+    <t xml:space="preserve">0.213141694664955</t>
   </si>
   <si>
     <t xml:space="preserve">0.201199218630791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.204279124736786</t>
+    <t xml:space="preserve">0.204279139637947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20679335296154</t>
+    <t xml:space="preserve">0.206793323159218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.206164747476578</t>
+    <t xml:space="preserve">0.206164807081223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.207421898841858</t>
+    <t xml:space="preserve">0.207421883940697</t>
   </si>
   <si>
     <t xml:space="preserve">0.208804726600647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211947441101074</t>
+    <t xml:space="preserve">0.211947426199913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.225649863481522</t>
+    <t xml:space="preserve">0.225649878382683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219867184758186</t>
+    <t xml:space="preserve">0.219867199659348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.220810025930405</t>
+    <t xml:space="preserve">0.220810011029243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229484021663666</t>
+    <t xml:space="preserve">0.229484066367149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234386757016182</t>
+    <t xml:space="preserve">0.23438672721386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.224518463015556</t>
+    <t xml:space="preserve">0.224518522620201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21999292075634</t>
+    <t xml:space="preserve">0.219992890954018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.219741478562355</t>
+    <t xml:space="preserve">0.219741493463516</t>
   </si>
   <si>
     <t xml:space="preserve">0.216913014650345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231306821107864</t>
+    <t xml:space="preserve">0.231306880712509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217038750648499</t>
+    <t xml:space="preserve">0.217038705945015</t>
   </si>
   <si>
     <t xml:space="preserve">0.223324239253998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297178983688354</t>
+    <t xml:space="preserve">0.297179043292999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351988703012466</t>
+    <t xml:space="preserve">0.351988643407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465127885341644</t>
+    <t xml:space="preserve">0.465127795934677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545582473278046</t>
+    <t xml:space="preserve">0.545582413673401</t>
   </si>
   <si>
     <t xml:space="preserve">0.477070301771164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436843127012253</t>
+    <t xml:space="preserve">0.436843037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422072142362595</t>
+    <t xml:space="preserve">0.422072112560272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395987212657928</t>
+    <t xml:space="preserve">0.395987272262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.364559680223465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414215117692947</t>
+    <t xml:space="preserve">0.414215236902237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367388188838959</t>
+    <t xml:space="preserve">0.367388159036636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373987972736359</t>
+    <t xml:space="preserve">0.373987942934036</t>
   </si>
   <si>
     <t xml:space="preserve">0.346331685781479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325903743505478</t>
+    <t xml:space="preserve">0.325903832912445</t>
   </si>
   <si>
     <t xml:space="preserve">0.314904123544693</t>
@@ -473,46 +473,46 @@
     <t xml:space="preserve">0.326532363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334389239549637</t>
+    <t xml:space="preserve">0.334389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321818172931671</t>
+    <t xml:space="preserve">0.321818232536316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348845839500427</t>
+    <t xml:space="preserve">0.348845899105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341303318738937</t>
+    <t xml:space="preserve">0.341303288936615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326846659183502</t>
+    <t xml:space="preserve">0.326846569776535</t>
   </si>
   <si>
     <t xml:space="preserve">0.318361163139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321189612150192</t>
+    <t xml:space="preserve">0.321189671754837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333132147789001</t>
+    <t xml:space="preserve">0.333132117986679</t>
   </si>
   <si>
     <t xml:space="preserve">0.329989343881607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317418366670609</t>
+    <t xml:space="preserve">0.317418336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324332445859909</t>
+    <t xml:space="preserve">0.324332416057587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314275562763214</t>
+    <t xml:space="preserve">0.314275592565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311761349439621</t>
+    <t xml:space="preserve">0.311761379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334703505039215</t>
+    <t xml:space="preserve">0.334703475236893</t>
   </si>
   <si>
     <t xml:space="preserve">0.318046867847443</t>
@@ -521,43 +521,43 @@
     <t xml:space="preserve">0.31678980588913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328418016433716</t>
+    <t xml:space="preserve">0.328417986631393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323075324296951</t>
+    <t xml:space="preserve">0.323075294494629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328103691339493</t>
+    <t xml:space="preserve">0.328103721141815</t>
   </si>
   <si>
     <t xml:space="preserve">0.301704585552216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310504287481308</t>
+    <t xml:space="preserve">0.310504257678986</t>
   </si>
   <si>
     <t xml:space="preserve">0.311069995164871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320561140775681</t>
+    <t xml:space="preserve">0.320561081171036</t>
   </si>
   <si>
     <t xml:space="preserve">0.325589507818222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358274191617966</t>
+    <t xml:space="preserve">0.358274221420288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339417636394501</t>
+    <t xml:space="preserve">0.339417666196823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34004619717598</t>
+    <t xml:space="preserve">0.340046226978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.319304019212723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337846308946609</t>
+    <t xml:space="preserve">0.337846279144287</t>
   </si>
   <si>
     <t xml:space="preserve">0.314589887857437</t>
@@ -566,154 +566,154 @@
     <t xml:space="preserve">0.327789425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389701783657074</t>
+    <t xml:space="preserve">0.389701724052429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369588136672974</t>
+    <t xml:space="preserve">0.369588077068329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368959575891495</t>
+    <t xml:space="preserve">0.368959546089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.37021666765213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363616824150085</t>
+    <t xml:space="preserve">0.36361688375473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370845198631287</t>
+    <t xml:space="preserve">0.370845168828964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345074594020844</t>
+    <t xml:space="preserve">0.345074653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349788755178452</t>
+    <t xml:space="preserve">0.349788725376129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354502886533737</t>
+    <t xml:space="preserve">0.354502856731415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367073893547058</t>
+    <t xml:space="preserve">0.367073863744736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388758838176727</t>
+    <t xml:space="preserve">0.38875886797905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391587436199188</t>
+    <t xml:space="preserve">0.391587376594543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37775930762291</t>
+    <t xml:space="preserve">0.377759218215942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377130687236786</t>
+    <t xml:space="preserve">0.377130717039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387187540531158</t>
+    <t xml:space="preserve">0.387187480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377444952726364</t>
+    <t xml:space="preserve">0.377445042133331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407929629087448</t>
+    <t xml:space="preserve">0.407929688692093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414843797683716</t>
+    <t xml:space="preserve">0.414843767881393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3922159075737</t>
+    <t xml:space="preserve">0.392215937376022</t>
   </si>
   <si>
     <t xml:space="preserve">0.376816421747208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38655897974968</t>
+    <t xml:space="preserve">0.386559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471413403749466</t>
+    <t xml:space="preserve">0.471413433551788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439357280731201</t>
+    <t xml:space="preserve">0.439357340335846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452556878328323</t>
+    <t xml:space="preserve">0.452556908130646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433700382709503</t>
+    <t xml:space="preserve">0.433700323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438100159168243</t>
+    <t xml:space="preserve">0.438100188970566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446271270513535</t>
+    <t xml:space="preserve">0.446271330118179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43998584151268</t>
+    <t xml:space="preserve">0.439985781908035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422386407852173</t>
+    <t xml:space="preserve">0.422386437654495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424900561571121</t>
+    <t xml:space="preserve">0.424900621175766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42112934589386</t>
+    <t xml:space="preserve">0.421129316091537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40981537103653</t>
+    <t xml:space="preserve">0.409815400838852</t>
   </si>
   <si>
     <t xml:space="preserve">0.406044065952301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558249473572</t>
+    <t xml:space="preserve">0.408558279275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41358670592308</t>
+    <t xml:space="preserve">0.413586646318436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402272790670395</t>
+    <t xml:space="preserve">0.402272701263428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432443231344223</t>
+    <t xml:space="preserve">0.432443261146545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417357981204987</t>
+    <t xml:space="preserve">0.417357951402664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462613642215729</t>
+    <t xml:space="preserve">0.462613761425018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427414774894714</t>
+    <t xml:space="preserve">0.427414834499359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399758517742157</t>
+    <t xml:space="preserve">0.399758547544479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418615102767944</t>
+    <t xml:space="preserve">0.418615072965622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423643559217453</t>
+    <t xml:space="preserve">0.423643499612808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411072373390198</t>
+    <t xml:space="preserve">0.411072462797165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398501425981522</t>
+    <t xml:space="preserve">0.398501485586166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404786944389343</t>
+    <t xml:space="preserve">0.404786884784698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382159143686295</t>
+    <t xml:space="preserve">0.38215908408165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38341623544693</t>
+    <t xml:space="preserve">0.383416265249252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388444662094116</t>
+    <t xml:space="preserve">0.388444602489471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403529852628708</t>
+    <t xml:space="preserve">0.40352988243103</t>
   </si>
   <si>
     <t xml:space="preserve">0.431186109781265</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">0.41987219452858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407301187515259</t>
+    <t xml:space="preserve">0.407301157712936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394730150699615</t>
+    <t xml:space="preserve">0.394730240106583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412329494953156</t>
+    <t xml:space="preserve">0.412329614162445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401015669107437</t>
+    <t xml:space="preserve">0.40101569890976</t>
   </si>
   <si>
     <t xml:space="preserve">0.416100859642029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362045466899872</t>
+    <t xml:space="preserve">0.362045496702194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365816742181778</t>
+    <t xml:space="preserve">0.3658167719841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363302558660507</t>
+    <t xml:space="preserve">0.363302618265152</t>
   </si>
   <si>
     <t xml:space="preserve">0.340674728155136</t>
@@ -755,67 +755,67 @@
     <t xml:space="preserve">0.359531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357017040252686</t>
+    <t xml:space="preserve">0.357017070055008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344446003437042</t>
+    <t xml:space="preserve">0.344446033239365</t>
   </si>
   <si>
     <t xml:space="preserve">0.336903423070908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338160514831543</t>
+    <t xml:space="preserve">0.338160455226898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345703184604645</t>
+    <t xml:space="preserve">0.345703154802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372102320194244</t>
+    <t xml:space="preserve">0.372102379798889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385930508375168</t>
+    <t xml:space="preserve">0.38593053817749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353245824575424</t>
+    <t xml:space="preserve">0.353245764970779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360788345336914</t>
+    <t xml:space="preserve">0.360788404941559</t>
   </si>
   <si>
     <t xml:space="preserve">0.378387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375873595476151</t>
+    <t xml:space="preserve">0.375873655080795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373359471559525</t>
+    <t xml:space="preserve">0.373359352350235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384673327207565</t>
+    <t xml:space="preserve">0.384673237800598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390958786010742</t>
+    <t xml:space="preserve">0.390958815813065</t>
   </si>
   <si>
     <t xml:space="preserve">0.393473029136658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424272060394287</t>
+    <t xml:space="preserve">0.42427197098732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430557578802109</t>
+    <t xml:space="preserve">0.430557548999786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449414163827896</t>
+    <t xml:space="preserve">0.449414104223251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455699652433395</t>
+    <t xml:space="preserve">0.455699592828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463956028223038</t>
+    <t xml:space="preserve">0.463955968618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443181842565536</t>
+    <t xml:space="preserve">0.443181782960892</t>
   </si>
   <si>
     <t xml:space="preserve">0.429332464933395</t>
@@ -824,55 +824,52 @@
     <t xml:space="preserve">0.415482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425870090723038</t>
+    <t xml:space="preserve">0.425870060920715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436257094144821</t>
+    <t xml:space="preserve">0.436257123947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439719498157501</t>
+    <t xml:space="preserve">0.439719557762146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432794809341431</t>
+    <t xml:space="preserve">0.432794779539108</t>
   </si>
   <si>
     <t xml:space="preserve">0.418945342302322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408558279275894</t>
+    <t xml:space="preserve">0.401633501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401633530855179</t>
+    <t xml:space="preserve">0.412020593881607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412020623683929</t>
+    <t xml:space="preserve">0.387784093618393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387784153223038</t>
+    <t xml:space="preserve">0.391246467828751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391246438026428</t>
+    <t xml:space="preserve">0.405095875263214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405095905065536</t>
+    <t xml:space="preserve">0.422407776117325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42240771651268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446644276380539</t>
+    <t xml:space="preserve">0.446644097566605</t>
   </si>
   <si>
     <t xml:space="preserve">0.526278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450106531381607</t>
+    <t xml:space="preserve">0.450106501579285</t>
   </si>
   <si>
     <t xml:space="preserve">0.457031279802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453568935394287</t>
+    <t xml:space="preserve">0.453568994998932</t>
   </si>
   <si>
     <t xml:space="preserve">0.398171186447144</t>
@@ -881,10 +878,10 @@
     <t xml:space="preserve">0.394708842039108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380859404802322</t>
+    <t xml:space="preserve">0.380859434604645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373934686183929</t>
+    <t xml:space="preserve">0.373934715986252</t>
   </si>
   <si>
     <t xml:space="preserve">0.360085248947144</t>
@@ -893,13 +890,13 @@
     <t xml:space="preserve">0.370472371578217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384321689605713</t>
+    <t xml:space="preserve">0.38432177901268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009997367859</t>
+    <t xml:space="preserve">0.367009967565536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340696066617966</t>
+    <t xml:space="preserve">0.340695977210999</t>
   </si>
   <si>
     <t xml:space="preserve">0.339311122894287</t>
@@ -908,13 +905,13 @@
     <t xml:space="preserve">0.353160530328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346235811710358</t>
+    <t xml:space="preserve">0.346235781908035</t>
   </si>
   <si>
     <t xml:space="preserve">0.332386404275894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311612278223038</t>
+    <t xml:space="preserve">0.311612218618393</t>
   </si>
   <si>
     <t xml:space="preserve">0.314382135868073</t>
@@ -932,52 +929,55 @@
     <t xml:space="preserve">0.263139247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272833824157715</t>
+    <t xml:space="preserve">0.27283376455307</t>
   </si>
   <si>
     <t xml:space="preserve">0.261754244565964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249289810657501</t>
+    <t xml:space="preserve">0.245134964585304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249289780855179</t>
   </si>
   <si>
     <t xml:space="preserve">0.243750005960464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285298317670822</t>
+    <t xml:space="preserve">0.2852982878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286683231592178</t>
+    <t xml:space="preserve">0.286683261394501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271448880434036</t>
+    <t xml:space="preserve">0.271448850631714</t>
   </si>
   <si>
     <t xml:space="preserve">0.279758542776108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281143516302109</t>
+    <t xml:space="preserve">0.281143486499786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294992953538895</t>
+    <t xml:space="preserve">0.29499289393425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303302586078644</t>
+    <t xml:space="preserve">0.303302526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308842360973358</t>
+    <t xml:space="preserve">0.308842331171036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337926179170609</t>
+    <t xml:space="preserve">0.337926149368286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325461655855179</t>
+    <t xml:space="preserve">0.325461626052856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319921910762787</t>
+    <t xml:space="preserve">0.319921970367432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343465894460678</t>
+    <t xml:space="preserve">0.343465954065323</t>
   </si>
   <si>
     <t xml:space="preserve">0.363547593355179</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">0.331001460552216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336541205644608</t>
+    <t xml:space="preserve">0.33654123544693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349698215723038</t>
+    <t xml:space="preserve">0.349698156118393</t>
   </si>
   <si>
     <t xml:space="preserve">0.344850897789001</t>
@@ -1004,67 +1004,67 @@
     <t xml:space="preserve">0.322691768407822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3240767121315</t>
+    <t xml:space="preserve">0.324076741933823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321306794881821</t>
+    <t xml:space="preserve">0.321306824684143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318536967039108</t>
+    <t xml:space="preserve">0.318536937236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306072413921356</t>
+    <t xml:space="preserve">0.306072473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317151993513107</t>
+    <t xml:space="preserve">0.317152053117752</t>
   </si>
   <si>
     <t xml:space="preserve">0.304687529802322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297762811183929</t>
+    <t xml:space="preserve">0.297762781381607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283913403749466</t>
+    <t xml:space="preserve">0.283913373947144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288068205118179</t>
+    <t xml:space="preserve">0.288068175315857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264524161815643</t>
+    <t xml:space="preserve">0.264524191617966</t>
   </si>
   <si>
     <t xml:space="preserve">0.267294079065323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260369300842285</t>
+    <t xml:space="preserve">0.260369330644608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265909135341644</t>
+    <t xml:space="preserve">0.265909105539322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270063936710358</t>
+    <t xml:space="preserve">0.27006396651268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276988685131073</t>
+    <t xml:space="preserve">0.276988655328751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292223006486893</t>
+    <t xml:space="preserve">0.292223036289215</t>
   </si>
   <si>
     <t xml:space="preserve">0.296377867460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289453119039536</t>
+    <t xml:space="preserve">0.28945317864418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429810017347336</t>
+    <t xml:space="preserve">0.429809987545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399647891521454</t>
+    <t xml:space="preserve">0.399647802114487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388337045907974</t>
+    <t xml:space="preserve">0.388337075710297</t>
   </si>
   <si>
     <t xml:space="preserve">0.377026289701462</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">0.361945241689682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369485795497894</t>
+    <t xml:space="preserve">0.369485825300217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363453328609467</t>
+    <t xml:space="preserve">0.363453298807144</t>
   </si>
   <si>
     <t xml:space="preserve">0.380796551704407</t>
@@ -1091,55 +1091,55 @@
     <t xml:space="preserve">0.349880367517471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343847960233688</t>
+    <t xml:space="preserve">0.343847990036011</t>
   </si>
   <si>
     <t xml:space="preserve">0.342339903116226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339323669672012</t>
+    <t xml:space="preserve">0.33932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352896600961685</t>
+    <t xml:space="preserve">0.352896630764008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346864134073257</t>
+    <t xml:space="preserve">0.346864193677902</t>
   </si>
   <si>
     <t xml:space="preserve">0.351388514041901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336307466030121</t>
+    <t xml:space="preserve">0.336307495832443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334799349308014</t>
+    <t xml:space="preserve">0.334799289703369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348372280597687</t>
+    <t xml:space="preserve">0.348372310400009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437350481748581</t>
+    <t xml:space="preserve">0.437350451946259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410958647727966</t>
+    <t xml:space="preserve">0.410958677530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452431529760361</t>
+    <t xml:space="preserve">0.452431619167328</t>
   </si>
   <si>
     <t xml:space="preserve">0.444891005754471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441120773553848</t>
+    <t xml:space="preserve">0.441120713949203</t>
   </si>
   <si>
     <t xml:space="preserve">0.414728939533234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403418153524399</t>
+    <t xml:space="preserve">0.403418123722076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392107337713242</t>
+    <t xml:space="preserve">0.392107307910919</t>
   </si>
   <si>
     <t xml:space="preserve">0.384566813707352</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">0.395877569913864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407188415527344</t>
+    <t xml:space="preserve">0.407188385725021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372501999139786</t>
+    <t xml:space="preserve">0.372501969337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366469502449036</t>
+    <t xml:space="preserve">0.366469591856003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354404747486115</t>
+    <t xml:space="preserve">0.354404717683792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345356047153473</t>
+    <t xml:space="preserve">0.345356106758118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340831786394119</t>
+    <t xml:space="preserve">0.340831756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370993912220001</t>
+    <t xml:space="preserve">0.370993882417679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36043718457222</t>
+    <t xml:space="preserve">0.360437124967575</t>
   </si>
   <si>
     <t xml:space="preserve">0.367977648973465</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">0.358929067850113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31670206785202</t>
+    <t xml:space="preserve">0.316702038049698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300112932920456</t>
+    <t xml:space="preserve">0.300112903118134</t>
   </si>
   <si>
     <t xml:space="preserve">0.301621049642563</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">0.324242621660233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327258825302124</t>
+    <t xml:space="preserve">0.327258795499802</t>
   </si>
   <si>
     <t xml:space="preserve">0.330275028944016</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">0.328766912221909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309161573648453</t>
+    <t xml:space="preserve">0.30916154384613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307653427124023</t>
+    <t xml:space="preserve">0.307653456926346</t>
   </si>
   <si>
     <t xml:space="preserve">0.30312916636467</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">0.313685864210129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322734534740448</t>
+    <t xml:space="preserve">0.322734504938126</t>
   </si>
   <si>
     <t xml:space="preserve">0.317599207162857</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">0.322339475154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314438998699188</t>
+    <t xml:space="preserve">0.314438968896866</t>
   </si>
   <si>
     <t xml:space="preserve">0.31917929649353</t>
@@ -1244,64 +1244,64 @@
     <t xml:space="preserve">0.333400130271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320759385824203</t>
+    <t xml:space="preserve">0.320759415626526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323919594287872</t>
+    <t xml:space="preserve">0.32391956448555</t>
   </si>
   <si>
     <t xml:space="preserve">0.312858909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303378343582153</t>
+    <t xml:space="preserve">0.303378313779831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292317658662796</t>
+    <t xml:space="preserve">0.292317688465118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301798224449158</t>
+    <t xml:space="preserve">0.30179825425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316019117832184</t>
+    <t xml:space="preserve">0.316019088029861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300218164920807</t>
+    <t xml:space="preserve">0.300218135118484</t>
   </si>
   <si>
     <t xml:space="preserve">0.298638045787811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290737599134445</t>
+    <t xml:space="preserve">0.2907375395298</t>
   </si>
   <si>
     <t xml:space="preserve">0.282837092876434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287577360868454</t>
+    <t xml:space="preserve">0.287577390670776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279676884412766</t>
+    <t xml:space="preserve">0.279676914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276516705751419</t>
+    <t xml:space="preserve">0.276516675949097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278096795082092</t>
+    <t xml:space="preserve">0.278096824884415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270196288824081</t>
+    <t xml:space="preserve">0.270196348428726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281257033348083</t>
+    <t xml:space="preserve">0.281256973743439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271776407957077</t>
+    <t xml:space="preserve">0.271776378154755</t>
   </si>
   <si>
     <t xml:space="preserve">0.284417182207108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285997301340103</t>
+    <t xml:space="preserve">0.285997271537781</t>
   </si>
   <si>
     <t xml:space="preserve">0.295477867126465</t>
@@ -1310,40 +1310,40 @@
     <t xml:space="preserve">0.297057926654816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308118641376495</t>
+    <t xml:space="preserve">0.308118611574173</t>
   </si>
   <si>
     <t xml:space="preserve">0.28915748000145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346040934324265</t>
+    <t xml:space="preserve">0.346040904521942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338140457868576</t>
+    <t xml:space="preserve">0.338140428066254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339720487594604</t>
+    <t xml:space="preserve">0.339720547199249</t>
   </si>
   <si>
     <t xml:space="preserve">0.341300636529922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33498027920723</t>
+    <t xml:space="preserve">0.334980249404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336560368537903</t>
+    <t xml:space="preserve">0.336560308933258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352361291646957</t>
+    <t xml:space="preserve">0.35236132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295359313488007</t>
+    <t xml:space="preserve">0.295359283685684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291944712400436</t>
+    <t xml:space="preserve">0.291944772005081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290237426757812</t>
+    <t xml:space="preserve">0.290237456560135</t>
   </si>
   <si>
     <t xml:space="preserve">0.285115599632263</t>
@@ -1355,52 +1355,52 @@
     <t xml:space="preserve">0.300481140613556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298773854970932</t>
+    <t xml:space="preserve">0.29877382516861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283408343791962</t>
+    <t xml:space="preserve">0.283408284187317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27828648686409</t>
+    <t xml:space="preserve">0.278286516666412</t>
   </si>
   <si>
     <t xml:space="preserve">0.288530170917511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279993742704391</t>
+    <t xml:space="preserve">0.279993772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273164659738541</t>
+    <t xml:space="preserve">0.273164629936218</t>
   </si>
   <si>
     <t xml:space="preserve">0.276579231023788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269750088453293</t>
+    <t xml:space="preserve">0.269750148057938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281701028347015</t>
+    <t xml:space="preserve">0.28170108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274871915578842</t>
+    <t xml:space="preserve">0.274871945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271457344293594</t>
+    <t xml:space="preserve">0.271457374095917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268042802810669</t>
+    <t xml:space="preserve">0.268042832612991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303895711898804</t>
+    <t xml:space="preserve">0.303895682096481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29365199804306</t>
+    <t xml:space="preserve">0.293651968240738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302188396453857</t>
+    <t xml:space="preserve">0.30218842625618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305602967739105</t>
+    <t xml:space="preserve">0.305602997541428</t>
   </si>
   <si>
     <t xml:space="preserve">0.307310253381729</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">0.319261223077774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309017539024353</t>
+    <t xml:space="preserve">0.309017509222031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314139395952225</t>
+    <t xml:space="preserve">0.31413933634758</t>
   </si>
   <si>
     <t xml:space="preserve">0.312432080507278</t>
@@ -1424,37 +1424,37 @@
     <t xml:space="preserve">0.310724824666977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310288995504379</t>
+    <t xml:space="preserve">0.310288965702057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299829810857773</t>
+    <t xml:space="preserve">0.29982978105545</t>
   </si>
   <si>
     <t xml:space="preserve">0.296343415975571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303316235542297</t>
+    <t xml:space="preserve">0.303316205739975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289370656013489</t>
+    <t xml:space="preserve">0.289370626211166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287627428770065</t>
+    <t xml:space="preserve">0.287627458572388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298086613416672</t>
+    <t xml:space="preserve">0.298086673021317</t>
   </si>
   <si>
     <t xml:space="preserve">0.313560366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304652392864227</t>
+    <t xml:space="preserve">0.304652452468872</t>
   </si>
   <si>
     <t xml:space="preserve">0.302870810031891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306434005498886</t>
+    <t xml:space="preserve">0.306433975696564</t>
   </si>
   <si>
     <t xml:space="preserve">0.301089227199554</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">0.299307614564896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293962806463242</t>
+    <t xml:space="preserve">0.293962866067886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285054892301559</t>
+    <t xml:space="preserve">0.285054862499237</t>
   </si>
   <si>
     <t xml:space="preserve">0.283273279666901</t>
@@ -1484,73 +1484,73 @@
     <t xml:space="preserve">0.279710114002228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281491696834564</t>
+    <t xml:space="preserve">0.281491756439209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292181223630905</t>
+    <t xml:space="preserve">0.292181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295372009277344</t>
+    <t xml:space="preserve">0.295371979475021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289902120828629</t>
+    <t xml:space="preserve">0.289902150630951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302665114402771</t>
+    <t xml:space="preserve">0.302665084600449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29172545671463</t>
+    <t xml:space="preserve">0.291725397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30448842048645</t>
+    <t xml:space="preserve">0.304488390684128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308134973049164</t>
+    <t xml:space="preserve">0.308135002851486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3117815554142</t>
+    <t xml:space="preserve">0.311781585216522</t>
   </si>
   <si>
     <t xml:space="preserve">0.31725138425827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319074690341949</t>
+    <t xml:space="preserve">0.319074660539627</t>
   </si>
   <si>
     <t xml:space="preserve">0.313604831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328191101551056</t>
+    <t xml:space="preserve">0.328191131353378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33183765411377</t>
+    <t xml:space="preserve">0.331837683916092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333660960197449</t>
+    <t xml:space="preserve">0.333660989999771</t>
   </si>
   <si>
     <t xml:space="preserve">0.320897966623306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324544548988342</t>
+    <t xml:space="preserve">0.32454451918602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324158191680908</t>
+    <t xml:space="preserve">0.324158161878586</t>
   </si>
   <si>
     <t xml:space="preserve">0.329747140407562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322295218706131</t>
+    <t xml:space="preserve">0.322295188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331610053777695</t>
+    <t xml:space="preserve">0.331610083580017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326021194458008</t>
+    <t xml:space="preserve">0.326021134853363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320432245731354</t>
+    <t xml:space="preserve">0.320432215929031</t>
   </si>
   <si>
     <t xml:space="preserve">0.311117321252823</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">0.309254318475723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335336029529572</t>
+    <t xml:space="preserve">0.335336059331894</t>
   </si>
   <si>
     <t xml:space="preserve">0.316706269979477</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">0.318569272756577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340924978256226</t>
+    <t xml:space="preserve">0.340925008058548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333473056554794</t>
+    <t xml:space="preserve">0.333473086357117</t>
   </si>
   <si>
     <t xml:space="preserve">0.307391405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301802456378937</t>
+    <t xml:space="preserve">0.301802426576614</t>
   </si>
   <si>
     <t xml:space="preserve">0.353965818881989</t>
@@ -1595,28 +1595,28 @@
     <t xml:space="preserve">0.370732635259628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398677319288254</t>
+    <t xml:space="preserve">0.398677289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419170081615448</t>
+    <t xml:space="preserve">0.419170051813126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407992213964462</t>
+    <t xml:space="preserve">0.40799218416214</t>
   </si>
   <si>
     <t xml:space="preserve">0.417307108640671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40985518693924</t>
+    <t xml:space="preserve">0.409855157136917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400540292263031</t>
+    <t xml:space="preserve">0.400540322065353</t>
   </si>
   <si>
     <t xml:space="preserve">0.3912253677845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3930883705616</t>
+    <t xml:space="preserve">0.393088340759277</t>
   </si>
   <si>
     <t xml:space="preserve">0.389362454414368</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">0.363280713558197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367006689310074</t>
+    <t xml:space="preserve">0.367006659507751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368869662284851</t>
+    <t xml:space="preserve">0.368869632482529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378184527158737</t>
+    <t xml:space="preserve">0.37818455696106</t>
   </si>
   <si>
     <t xml:space="preserve">0.394951343536377</t>
@@ -26203,7 +26203,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G926" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26229,7 +26229,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26255,7 +26255,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G928" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26281,7 +26281,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G929" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26307,7 +26307,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G930" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26333,7 +26333,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G931" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26359,7 +26359,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G932" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26385,7 +26385,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G933" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26411,7 +26411,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G934" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26437,7 +26437,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G935" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26463,7 +26463,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G936" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26489,7 +26489,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G937" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26515,7 +26515,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G938" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26541,7 +26541,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G939" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26567,7 +26567,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G940" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26593,7 +26593,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G941" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26645,7 +26645,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G943" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26671,7 +26671,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G944" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26697,7 +26697,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G945" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26723,7 +26723,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G946" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26749,7 +26749,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G947" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26775,7 +26775,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G948" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26801,7 +26801,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G949" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26827,7 +26827,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G950" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26853,7 +26853,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G951" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26879,7 +26879,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G952" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26905,7 +26905,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G953" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26931,7 +26931,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G954" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26957,7 +26957,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G955" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26983,7 +26983,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G956" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27009,7 +27009,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G957" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27035,7 +27035,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G958" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27061,7 +27061,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G959" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27087,7 +27087,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G960" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27113,7 +27113,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G961" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27191,7 +27191,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G964" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27269,7 +27269,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27295,7 +27295,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G968" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27347,7 +27347,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G970" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27373,7 +27373,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G971" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27399,7 +27399,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G972" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27425,7 +27425,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G973" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27581,7 +27581,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G979" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27607,7 +27607,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27633,7 +27633,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27711,7 +27711,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27737,7 +27737,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28153,7 +28153,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1001" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28179,7 +28179,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1002" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28205,7 +28205,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1003" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28231,7 +28231,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1004" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28257,7 +28257,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28283,7 +28283,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28309,7 +28309,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1007" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28335,7 +28335,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1008" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28361,7 +28361,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1009" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28413,7 +28413,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1011" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28439,7 +28439,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1012" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28465,7 +28465,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1013" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28491,7 +28491,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28517,7 +28517,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28543,7 +28543,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1016" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28569,7 +28569,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1017" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28595,7 +28595,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1018" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28621,7 +28621,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28647,7 +28647,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1020" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28673,7 +28673,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1021" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28751,7 +28751,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1024" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28777,7 +28777,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1025" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28803,7 +28803,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1026" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28829,7 +28829,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28855,7 +28855,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28881,7 +28881,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1029" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28907,7 +28907,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28933,7 +28933,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1031" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28959,7 +28959,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28985,7 +28985,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29011,7 +29011,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29037,7 +29037,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1035" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29063,7 +29063,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29089,7 +29089,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1037" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29115,7 +29115,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1038" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29141,7 +29141,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1039" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29167,7 +29167,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1040" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29193,7 +29193,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1041" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29219,7 +29219,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1042" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29245,7 +29245,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1043" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29271,7 +29271,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1044" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29375,7 +29375,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1048" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29427,7 +29427,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1050" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29505,7 +29505,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1053" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29531,7 +29531,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1054" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29557,7 +29557,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1055" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29583,7 +29583,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1056" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29609,7 +29609,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1057" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29635,7 +29635,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1058" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29661,7 +29661,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1059" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29687,7 +29687,7 @@
         <v>0.5</v>
       </c>
       <c r="G1060" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29713,7 +29713,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1061" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29739,7 +29739,7 @@
         <v>0.5</v>
       </c>
       <c r="G1062" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29765,7 +29765,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1063" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29791,7 +29791,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29817,7 +29817,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1065" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29843,7 +29843,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1066" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29869,7 +29869,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1067" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29895,7 +29895,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1068" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29921,7 +29921,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1069" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29947,7 +29947,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1070" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29973,7 +29973,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1071" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30155,7 +30155,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1078" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30285,7 +30285,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1083" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30311,7 +30311,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1084" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30337,7 +30337,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1085" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30389,7 +30389,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1087" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30415,7 +30415,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30493,7 +30493,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30883,7 +30883,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30909,7 +30909,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31013,7 +31013,7 @@
         <v>0.5</v>
       </c>
       <c r="G1111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31065,7 +31065,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31091,7 +31091,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31117,7 +31117,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31221,7 +31221,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31247,7 +31247,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31273,7 +31273,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31325,7 +31325,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31351,7 +31351,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31377,7 +31377,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31403,7 +31403,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31429,7 +31429,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31455,7 +31455,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31481,7 +31481,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31507,7 +31507,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31533,7 +31533,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31559,7 +31559,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31585,7 +31585,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31611,7 +31611,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31637,7 +31637,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31663,7 +31663,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31689,7 +31689,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1137" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31715,7 +31715,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1138" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31741,7 +31741,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1139" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31767,7 +31767,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31793,7 +31793,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31819,7 +31819,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31845,7 +31845,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31871,7 +31871,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31897,7 +31897,7 @@
         <v>0.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31923,7 +31923,7 @@
         <v>0.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31949,7 +31949,7 @@
         <v>0.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31975,7 +31975,7 @@
         <v>0.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32001,7 +32001,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32053,7 +32053,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32079,7 +32079,7 @@
         <v>0.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32105,7 +32105,7 @@
         <v>0.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32157,7 +32157,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32339,7 +32339,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1162" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32365,7 +32365,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1163" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32391,7 +32391,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32417,7 +32417,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1165" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32755,7 +32755,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1178" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33249,7 +33249,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34289,7 +34289,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34497,7 +34497,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34523,7 +34523,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35017,7 +35017,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1265" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35667,7 +35667,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1290" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35693,7 +35693,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1291" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35745,7 +35745,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35771,7 +35771,7 @@
         <v>0.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35797,7 +35797,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35823,7 +35823,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35875,7 +35875,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1298" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35901,7 +35901,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1299" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35927,7 +35927,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1300" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35979,7 +35979,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1302" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36005,7 +36005,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1303" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36031,7 +36031,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1304" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36057,7 +36057,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1305" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36083,7 +36083,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36109,7 +36109,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36135,7 +36135,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1308" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36161,7 +36161,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1309" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36187,7 +36187,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1310" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -69345,7 +69345,7 @@
     </row>
     <row r="2586">
       <c r="A2586" s="1" t="n">
-        <v>46086.3339699074</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B2586" t="n">
         <v>8000</v>

--- a/data/POPR.MI.xlsx
+++ b/data/POPR.MI.xlsx
@@ -44,70 +44,70 @@
     <t xml:space="preserve">POPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176622867584229</t>
+    <t xml:space="preserve">0.17662288248539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1728515625</t>
+    <t xml:space="preserve">0.172851577401161</t>
   </si